--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A29A02-8990-4060-BEF4-23B8734519E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E9DD6C-CC1A-4119-9DCE-2A013E25D48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -562,7 +562,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -576,6 +576,21 @@
       <top/>
       <bottom style="medium">
         <color rgb="FFE7E7E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -599,11 +614,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2865,13 +2880,13 @@
         <v>132</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2880,43 +2895,43 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="11">
         <f>IFERROR((F2/E2)*100,0)</f>
         <v>0</v>
       </c>
-      <c r="J2" s="15">
+      <c r="J2" s="14">
         <f>IFERROR(C2/E2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="15">
+        <v>-1.9</v>
+      </c>
+      <c r="K2" s="14">
         <f>IFERROR(D2/E2,0)</f>
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="M2">
-        <f>C2+T2</f>
-        <v>0</v>
+        <f t="shared" ref="M2:R2" si="0">C2+T2</f>
+        <v>-1.9</v>
       </c>
       <c r="N2">
-        <f>D2+U2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>-0.38</v>
       </c>
       <c r="O2">
-        <f>E2+V2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="P2">
-        <f>F2+W2</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q2">
-        <f>G2+X2</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R2">
-        <f>H2+Y2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -2945,39 +2960,39 @@
         <v>0</v>
       </c>
       <c r="I3" s="11">
-        <f t="shared" ref="I3:I66" si="0">IFERROR((F3/E3)*100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J3" s="15">
-        <f t="shared" ref="J3:J66" si="1">IFERROR(C3/E3,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="15">
-        <f t="shared" ref="K3:K66" si="2">IFERROR(D3/E3,0)</f>
+        <f t="shared" ref="I3:I66" si="1">IFERROR((F3/E3)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="14">
+        <f t="shared" ref="J3:J66" si="2">IFERROR(C3/E3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="14">
+        <f t="shared" ref="K3:K66" si="3">IFERROR(D3/E3,0)</f>
         <v>0</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M66" si="3">C3+T3</f>
+        <f t="shared" ref="M3:M66" si="4">C3+T3</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f>D3+U3</f>
+        <f t="shared" ref="N3:N17" si="5">D3+U3</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>E3+V3</f>
+        <f t="shared" ref="O3:O17" si="6">E3+V3</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>F3+W3</f>
+        <f t="shared" ref="P3:P17" si="7">F3+W3</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>G3+X3</f>
+        <f t="shared" ref="Q3:Q17" si="8">G3+X3</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>H3+Y3</f>
+        <f t="shared" ref="R3:R17" si="9">H3+Y3</f>
         <v>0</v>
       </c>
     </row>
@@ -2989,58 +3004,58 @@
         <v>135</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J4" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>33.333333333333329</v>
+      </c>
+      <c r="J4" s="14">
+        <f t="shared" si="2"/>
+        <v>-0.9</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" si="3"/>
+        <v>-0.18000000000000002</v>
       </c>
       <c r="M4">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>-2.7</v>
       </c>
       <c r="N4">
-        <f>D4+U4</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>-0.54</v>
       </c>
       <c r="O4">
-        <f>E4+V4</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
       <c r="P4">
-        <f>F4+W4</f>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <f>G4+X4</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>H4+Y4</f>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -3069,39 +3084,39 @@
         <v>0</v>
       </c>
       <c r="I5" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J5" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N5">
-        <f>D5+U5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>E5+V5</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>F5+W5</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>G5+X5</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>H5+Y5</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -3113,13 +3128,13 @@
         <v>134</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3128,43 +3143,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="14">
+        <f t="shared" si="2"/>
+        <v>-2.5</v>
+      </c>
+      <c r="K6" s="14">
+        <f t="shared" si="3"/>
+        <v>-0.5</v>
       </c>
       <c r="M6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>-2.5</v>
       </c>
       <c r="N6">
-        <f>D6+U6</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>-0.5</v>
       </c>
       <c r="O6">
-        <f>E6+V6</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="P6">
-        <f>F6+W6</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>G6+X6</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>H6+Y6</f>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -3193,39 +3208,39 @@
         <v>0</v>
       </c>
       <c r="I7" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="J7" s="15">
-        <f t="shared" si="1"/>
+      <c r="J7" s="14">
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="K7" s="15">
-        <f t="shared" si="2"/>
+      <c r="K7" s="14">
+        <f t="shared" si="3"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="N7">
-        <f>D7+U7</f>
+        <f t="shared" si="5"/>
         <v>1.2</v>
       </c>
       <c r="O7">
-        <f>E7+V7</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="P7">
-        <f>F7+W7</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="Q7">
-        <f>G7+X7</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>H7+Y7</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -3255,39 +3270,39 @@
         <v>0</v>
       </c>
       <c r="I8" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N8">
-        <f>D8+U8</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>E8+V8</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>F8+W8</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>G8+X8</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R8">
-        <f>H8+Y8</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -3317,39 +3332,39 @@
         <v>0</v>
       </c>
       <c r="I9" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N9">
-        <f>D9+U9</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>E9+V9</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>F9+W9</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>G9+X9</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>H9+Y9</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -3379,39 +3394,39 @@
         <v>1</v>
       </c>
       <c r="I10" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="14">
+        <f t="shared" si="2"/>
         <v>-6</v>
       </c>
-      <c r="K10" s="15">
-        <f t="shared" si="2"/>
+      <c r="K10" s="14">
+        <f t="shared" si="3"/>
         <v>-1.2</v>
       </c>
       <c r="M10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-6</v>
       </c>
       <c r="N10">
-        <f>D10+U10</f>
+        <f t="shared" si="5"/>
         <v>-1.2</v>
       </c>
       <c r="O10">
-        <f>E10+V10</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="P10">
-        <f>F10+W10</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>G10+X10</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R10">
-        <f>H10+Y10</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -3423,58 +3438,58 @@
         <v>72</v>
       </c>
       <c r="C11">
-        <v>35</v>
+        <v>30.1</v>
       </c>
       <c r="D11">
-        <v>7.0000000000000009</v>
+        <v>6.0200000000000005</v>
       </c>
       <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11">
         <v>5</v>
       </c>
-      <c r="F11">
-        <v>4</v>
-      </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="11">
-        <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="J11" s="15">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="K11" s="15">
-        <f t="shared" si="2"/>
-        <v>1.4000000000000001</v>
+        <f t="shared" si="1"/>
+        <v>62.5</v>
+      </c>
+      <c r="J11" s="14">
+        <f t="shared" si="2"/>
+        <v>3.7625000000000002</v>
+      </c>
+      <c r="K11" s="14">
+        <f t="shared" si="3"/>
+        <v>0.75250000000000006</v>
       </c>
       <c r="M11">
-        <f t="shared" si="3"/>
-        <v>35</v>
+        <f t="shared" si="4"/>
+        <v>30.1</v>
       </c>
       <c r="N11">
-        <f>D11+U11</f>
-        <v>7.0000000000000009</v>
+        <f t="shared" si="5"/>
+        <v>6.0200000000000005</v>
       </c>
       <c r="O11">
-        <f>E11+V11</f>
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="P11">
-        <f>F11+W11</f>
-        <v>4</v>
-      </c>
       <c r="Q11">
-        <f>G11+X11</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R11">
-        <f>H11+Y11</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
@@ -3503,39 +3518,39 @@
         <v>0</v>
       </c>
       <c r="I12" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N12">
-        <f>D12+U12</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>E12+V12</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>F12+W12</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>G12+X12</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R12">
-        <f>H12+Y12</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -3565,39 +3580,39 @@
         <v>2</v>
       </c>
       <c r="I13" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>33.333333333333329</v>
       </c>
-      <c r="J13" s="15">
-        <f t="shared" si="1"/>
+      <c r="J13" s="14">
+        <f t="shared" si="2"/>
         <v>-4</v>
       </c>
-      <c r="K13" s="15">
-        <f t="shared" si="2"/>
+      <c r="K13" s="14">
+        <f t="shared" si="3"/>
         <v>-0.79999999999999993</v>
       </c>
       <c r="M13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-12</v>
       </c>
       <c r="N13">
-        <f>D13+U13</f>
+        <f t="shared" si="5"/>
         <v>-2.4</v>
       </c>
       <c r="O13">
-        <f>E13+V13</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="P13">
-        <f>F13+W13</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="Q13">
-        <f>G13+X13</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R13">
-        <f>H13+Y13</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -3609,13 +3624,13 @@
         <v>60</v>
       </c>
       <c r="C14">
-        <v>40</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>7.36</v>
       </c>
       <c r="E14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3624,43 +3639,43 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14" s="11">
-        <f t="shared" si="0"/>
-        <v>71.428571428571431</v>
-      </c>
-      <c r="J14" s="15">
-        <f t="shared" si="1"/>
-        <v>5.7142857142857144</v>
-      </c>
-      <c r="K14" s="15">
-        <f t="shared" si="2"/>
-        <v>1.1428571428571428</v>
+        <f t="shared" si="1"/>
+        <v>55.555555555555557</v>
+      </c>
+      <c r="J14" s="14">
+        <f t="shared" si="2"/>
+        <v>4.0888888888888886</v>
+      </c>
+      <c r="K14" s="14">
+        <f t="shared" si="3"/>
+        <v>0.81777777777777783</v>
       </c>
       <c r="M14">
-        <f t="shared" si="3"/>
-        <v>40</v>
+        <f t="shared" si="4"/>
+        <v>36.799999999999997</v>
       </c>
       <c r="N14">
-        <f>D14+U14</f>
-        <v>8</v>
+        <f t="shared" si="5"/>
+        <v>7.36</v>
       </c>
       <c r="O14">
-        <f>E14+V14</f>
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>9</v>
       </c>
       <c r="P14">
-        <f>F14+W14</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="Q14">
-        <f>G14+X14</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R14">
-        <f>H14+Y14</f>
-        <v>2</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -3671,16 +3686,16 @@
         <v>67</v>
       </c>
       <c r="C15">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E15">
+        <v>9</v>
+      </c>
+      <c r="F15">
         <v>6</v>
-      </c>
-      <c r="D15">
-        <v>1.2</v>
-      </c>
-      <c r="E15">
-        <v>8</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3689,39 +3704,39 @@
         <v>3</v>
       </c>
       <c r="I15" s="11">
-        <f t="shared" si="0"/>
-        <v>62.5</v>
-      </c>
-      <c r="J15" s="15">
-        <f t="shared" si="1"/>
-        <v>0.75</v>
-      </c>
-      <c r="K15" s="15">
-        <f t="shared" si="2"/>
-        <v>0.15</v>
+        <f t="shared" si="1"/>
+        <v>66.666666666666657</v>
+      </c>
+      <c r="J15" s="14">
+        <f t="shared" si="2"/>
+        <v>1.2222222222222223</v>
+      </c>
+      <c r="K15" s="14">
+        <f t="shared" si="3"/>
+        <v>0.24444444444444446</v>
       </c>
       <c r="M15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="5"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="N15">
-        <f>D15+U15</f>
-        <v>1.2</v>
-      </c>
-      <c r="O15">
-        <f>E15+V15</f>
-        <v>8</v>
-      </c>
-      <c r="P15">
-        <f>F15+W15</f>
-        <v>5</v>
-      </c>
       <c r="Q15">
-        <f>G15+X15</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R15">
-        <f>H15+Y15</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -3733,13 +3748,13 @@
         <v>94</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -3748,43 +3763,43 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="14">
+        <f t="shared" si="2"/>
+        <v>-0.9</v>
+      </c>
+      <c r="K16" s="14">
+        <f t="shared" si="3"/>
+        <v>-0.18</v>
       </c>
       <c r="M16">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>-1.8</v>
       </c>
       <c r="N16">
-        <f>D16+U16</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>-0.36</v>
       </c>
       <c r="O16">
-        <f>E16+V16</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>2</v>
       </c>
       <c r="P16">
-        <f>F16+W16</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q16">
-        <f>G16+X16</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R16">
-        <f>H16+Y16</f>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -3813,39 +3828,39 @@
         <v>0</v>
       </c>
       <c r="I17" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N17">
-        <f>D17+U17</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O17">
-        <f>E17+V17</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P17">
-        <f>F17+W17</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f>G17+X17</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R17">
-        <f>H17+Y17</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -3875,39 +3890,39 @@
         <v>4</v>
       </c>
       <c r="I18" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="J18" s="15">
-        <f t="shared" si="1"/>
+      <c r="J18" s="14">
+        <f t="shared" si="2"/>
         <v>-1.4875</v>
       </c>
-      <c r="K18" s="15">
-        <f t="shared" si="2"/>
+      <c r="K18" s="14">
+        <f t="shared" si="3"/>
         <v>-0.29750000000000004</v>
       </c>
       <c r="M18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-11.9</v>
       </c>
       <c r="N18">
-        <f t="shared" ref="N18:N67" si="4">D18+U18</f>
+        <f t="shared" ref="N18:N67" si="10">D18+U18</f>
         <v>-2.3800000000000003</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:O67" si="5">E18+V18</f>
+        <f t="shared" ref="O18:O67" si="11">E18+V18</f>
         <v>8</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18:P67" si="6">F18+W18</f>
+        <f t="shared" ref="P18:P67" si="12">F18+W18</f>
         <v>4</v>
       </c>
       <c r="Q18">
-        <f>G18+X18</f>
+        <f t="shared" ref="Q18:Q49" si="13">G18+X18</f>
         <v>0</v>
       </c>
       <c r="R18">
-        <f>H18+Y18</f>
+        <f t="shared" ref="R18:R49" si="14">H18+Y18</f>
         <v>4</v>
       </c>
     </row>
@@ -3937,39 +3952,39 @@
         <v>0</v>
       </c>
       <c r="I19" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q19">
-        <f>G19+X19</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R19">
-        <f>H19+Y19</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -3981,16 +3996,16 @@
         <v>69</v>
       </c>
       <c r="C20">
-        <v>-0.10000000000000142</v>
+        <v>5.6999999999999984</v>
       </c>
       <c r="D20">
-        <v>-2.0000000000000285E-2</v>
+        <v>1.1399999999999997</v>
       </c>
       <c r="E20">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -3999,39 +4014,39 @@
         <v>12</v>
       </c>
       <c r="I20" s="11">
-        <f t="shared" si="0"/>
-        <v>38.095238095238095</v>
-      </c>
-      <c r="J20" s="15">
-        <f t="shared" si="1"/>
-        <v>-4.76190476190483E-3</v>
-      </c>
-      <c r="K20" s="15">
-        <f t="shared" si="2"/>
-        <v>-9.5238095238096593E-4</v>
+        <f t="shared" si="1"/>
+        <v>43.478260869565219</v>
+      </c>
+      <c r="J20" s="14">
+        <f t="shared" si="2"/>
+        <v>0.24782608695652167</v>
+      </c>
+      <c r="K20" s="14">
+        <f t="shared" si="3"/>
+        <v>4.9565217391304331E-2</v>
       </c>
       <c r="M20">
-        <f t="shared" si="3"/>
-        <v>-0.10000000000000142</v>
+        <f t="shared" si="4"/>
+        <v>5.6999999999999984</v>
       </c>
       <c r="N20">
-        <f t="shared" si="4"/>
-        <v>-2.0000000000000285E-2</v>
+        <f t="shared" si="10"/>
+        <v>1.1399999999999997</v>
       </c>
       <c r="O20">
-        <f t="shared" si="5"/>
-        <v>21</v>
+        <f t="shared" si="11"/>
+        <v>23</v>
       </c>
       <c r="P20">
-        <f t="shared" si="6"/>
-        <v>8</v>
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <f>G20+X20</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R20">
-        <f>H20+Y20</f>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
     </row>
@@ -4061,39 +4076,39 @@
         <v>1</v>
       </c>
       <c r="I21" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="J21" s="15">
-        <f t="shared" si="1"/>
+      <c r="J21" s="14">
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="K21" s="15">
-        <f t="shared" si="2"/>
+      <c r="K21" s="14">
+        <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
       <c r="M21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="O21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="P21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="Q21">
-        <f>G21+X21</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R21">
-        <f>H21+Y21</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -4105,16 +4120,16 @@
         <v>121</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4123,39 +4138,39 @@
         <v>0</v>
       </c>
       <c r="I22" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="J22" s="14">
+        <f t="shared" si="2"/>
+        <v>1.2</v>
+      </c>
+      <c r="K22" s="14">
+        <f t="shared" si="3"/>
+        <v>0.24</v>
       </c>
       <c r="M22">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1.2</v>
       </c>
       <c r="N22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>0.24</v>
       </c>
       <c r="O22">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="P22">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="Q22">
-        <f>G22+X22</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R22">
-        <f>H22+Y22</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4167,13 +4182,13 @@
         <v>66</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="D23">
-        <v>1.4000000000000001</v>
+        <v>1.1400000000000001</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -4182,43 +4197,43 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="11">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="J23" s="15">
-        <f t="shared" si="1"/>
-        <v>1.75</v>
-      </c>
-      <c r="K23" s="15">
-        <f t="shared" si="2"/>
-        <v>0.35000000000000003</v>
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="J23" s="14">
+        <f t="shared" si="2"/>
+        <v>1.1400000000000001</v>
+      </c>
+      <c r="K23" s="14">
+        <f t="shared" si="3"/>
+        <v>0.22800000000000004</v>
       </c>
       <c r="M23">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <f t="shared" si="4"/>
+        <v>5.7</v>
       </c>
       <c r="N23">
-        <f t="shared" si="4"/>
-        <v>1.4000000000000001</v>
+        <f t="shared" si="10"/>
+        <v>1.1400000000000001</v>
       </c>
       <c r="O23">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <f t="shared" si="11"/>
+        <v>5</v>
       </c>
       <c r="P23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="Q23">
-        <f>G23+X23</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R23">
-        <f>H23+Y23</f>
-        <v>1</v>
+        <f t="shared" si="14"/>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -4247,39 +4262,39 @@
         <v>0</v>
       </c>
       <c r="I24" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O24">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q24">
-        <f>G24+X24</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R24">
-        <f>H24+Y24</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4309,39 +4324,39 @@
         <v>0</v>
       </c>
       <c r="I25" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q25">
-        <f>G25+X25</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R25">
-        <f>H25+Y25</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4371,39 +4386,39 @@
         <v>0</v>
       </c>
       <c r="I26" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q26">
-        <f>G26+X26</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R26">
-        <f>H26+Y26</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4415,58 +4430,58 @@
         <v>70</v>
       </c>
       <c r="C27">
-        <v>47</v>
+        <v>36.9</v>
       </c>
       <c r="D27">
-        <v>9.4</v>
+        <v>7.3800000000000008</v>
       </c>
       <c r="E27">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I27" s="11">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="J27" s="15">
-        <f t="shared" si="1"/>
-        <v>7.833333333333333</v>
-      </c>
-      <c r="K27" s="15">
-        <f t="shared" si="2"/>
-        <v>1.5666666666666667</v>
+        <f t="shared" si="1"/>
+        <v>71.428571428571431</v>
+      </c>
+      <c r="J27" s="14">
+        <f t="shared" si="2"/>
+        <v>2.6357142857142857</v>
+      </c>
+      <c r="K27" s="14">
+        <f t="shared" si="3"/>
+        <v>0.52714285714285725</v>
       </c>
       <c r="M27">
-        <f t="shared" si="3"/>
-        <v>47</v>
+        <f t="shared" si="4"/>
+        <v>36.9</v>
       </c>
       <c r="N27">
-        <f t="shared" si="4"/>
-        <v>9.4</v>
+        <f t="shared" si="10"/>
+        <v>7.3800000000000008</v>
       </c>
       <c r="O27">
-        <f t="shared" si="5"/>
-        <v>6</v>
+        <f t="shared" si="11"/>
+        <v>14</v>
       </c>
       <c r="P27">
-        <f t="shared" si="6"/>
-        <v>6</v>
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <f>G27+X27</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R27">
-        <f>H27+Y27</f>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -4477,13 +4492,13 @@
         <v>130</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -4492,43 +4507,43 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.3</v>
+      </c>
+      <c r="K28" s="14">
+        <f t="shared" si="3"/>
+        <v>-0.26</v>
       </c>
       <c r="M28">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>-1.3</v>
       </c>
       <c r="N28">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-0.26</v>
       </c>
       <c r="O28">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="P28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q28">
-        <f>G28+X28</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R28">
-        <f>H28+Y28</f>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -4557,39 +4572,39 @@
         <v>7</v>
       </c>
       <c r="I29" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>27.27272727272727</v>
       </c>
-      <c r="J29" s="15">
-        <f t="shared" si="1"/>
+      <c r="J29" s="14">
+        <f t="shared" si="2"/>
         <v>-3.6363636363636362</v>
       </c>
-      <c r="K29" s="15">
-        <f t="shared" si="2"/>
+      <c r="K29" s="14">
+        <f t="shared" si="3"/>
         <v>-0.72727272727272729</v>
       </c>
       <c r="M29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-40</v>
       </c>
       <c r="N29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>-8</v>
       </c>
       <c r="O29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="P29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="Q29">
-        <f>G29+X29</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R29">
-        <f>H29+Y29</f>
+        <f t="shared" si="14"/>
         <v>7</v>
       </c>
     </row>
@@ -4601,16 +4616,16 @@
         <v>128</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4619,39 +4634,39 @@
         <v>0</v>
       </c>
       <c r="I30" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="J30" s="14">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="K30" s="14">
+        <f t="shared" si="3"/>
+        <v>0.06</v>
       </c>
       <c r="M30">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>0.3</v>
       </c>
       <c r="N30">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>0.06</v>
       </c>
       <c r="O30">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="P30">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="Q30">
-        <f>G30+X30</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R30">
-        <f>H30+Y30</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4681,39 +4696,39 @@
         <v>0</v>
       </c>
       <c r="I31" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q31">
-        <f>G31+X31</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R31">
-        <f>H31+Y31</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4725,16 +4740,16 @@
         <v>124</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4743,39 +4758,39 @@
         <v>0</v>
       </c>
       <c r="I32" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J32" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="J32" s="14">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+      <c r="K32" s="14">
+        <f t="shared" si="3"/>
+        <v>0.18</v>
       </c>
       <c r="M32">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>0.9</v>
       </c>
       <c r="N32">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>0.18</v>
       </c>
       <c r="O32">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="P32">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="Q32">
-        <f>G32+X32</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R32">
-        <f>H32+Y32</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4787,13 +4802,13 @@
         <v>127</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -4802,43 +4817,43 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="14">
+        <f t="shared" si="2"/>
+        <v>-10</v>
+      </c>
+      <c r="K33" s="14">
+        <f t="shared" si="3"/>
+        <v>-2</v>
       </c>
       <c r="M33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>-10</v>
       </c>
       <c r="N33">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-2</v>
       </c>
       <c r="O33">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="P33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q33">
-        <f>G33+X33</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R33">
-        <f>H33+Y33</f>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -4867,39 +4882,39 @@
         <v>0</v>
       </c>
       <c r="I34" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q34">
-        <f>G34+X34</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R34">
-        <f>H34+Y34</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4911,16 +4926,16 @@
         <v>131</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4929,39 +4944,39 @@
         <v>0</v>
       </c>
       <c r="I35" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J35" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K35" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="J35" s="14">
+        <f t="shared" si="2"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K35" s="14">
+        <f t="shared" si="3"/>
+        <v>0.45999999999999996</v>
       </c>
       <c r="M35">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>2.2999999999999998</v>
       </c>
       <c r="N35">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>0.45999999999999996</v>
       </c>
       <c r="O35">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="P35">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="Q35">
-        <f>G35+X35</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R35">
-        <f>H35+Y35</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4991,39 +5006,39 @@
         <v>0</v>
       </c>
       <c r="I36" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J36" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K36" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q36">
-        <f>G36+X36</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R36">
-        <f>H36+Y36</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -5053,39 +5068,39 @@
         <v>0</v>
       </c>
       <c r="I37" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K37" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q37">
-        <f>G37+X37</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R37">
-        <f>H37+Y37</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -5115,39 +5130,39 @@
         <v>1</v>
       </c>
       <c r="I38" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="J38" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K38" s="15">
-        <f t="shared" si="2"/>
+      <c r="J38" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O38">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="P38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="Q38">
-        <f>G38+X38</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R38">
-        <f>H38+Y38</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -5177,39 +5192,39 @@
         <v>0</v>
       </c>
       <c r="I39" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="J39" s="15">
-        <f t="shared" si="1"/>
+      <c r="J39" s="14">
+        <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
-      <c r="K39" s="15">
-        <f t="shared" si="2"/>
+      <c r="K39" s="14">
+        <f t="shared" si="3"/>
         <v>0.3</v>
       </c>
       <c r="M39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="N39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>1.2</v>
       </c>
       <c r="O39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="P39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="Q39">
-        <f>G39+X39</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R39">
-        <f>H39+Y39</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -5221,58 +5236,58 @@
         <v>87</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>-3.4</v>
       </c>
       <c r="D40">
-        <v>-0.2</v>
+        <v>-0.67999999999999994</v>
       </c>
       <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>2</v>
       </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
       <c r="I40" s="11">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="J40" s="15">
-        <f t="shared" si="1"/>
-        <v>-0.5</v>
-      </c>
-      <c r="K40" s="15">
-        <f t="shared" si="2"/>
-        <v>-0.1</v>
+        <f t="shared" si="1"/>
+        <v>33.333333333333329</v>
+      </c>
+      <c r="J40" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.1333333333333333</v>
+      </c>
+      <c r="K40" s="14">
+        <f t="shared" si="3"/>
+        <v>-0.22666666666666666</v>
       </c>
       <c r="M40">
-        <f t="shared" si="3"/>
-        <v>-1</v>
+        <f t="shared" si="4"/>
+        <v>-3.4</v>
       </c>
       <c r="N40">
-        <f t="shared" si="4"/>
-        <v>-0.2</v>
+        <f t="shared" si="10"/>
+        <v>-0.67999999999999994</v>
       </c>
       <c r="O40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="P40">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <f t="shared" si="14"/>
         <v>2</v>
-      </c>
-      <c r="P40">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q40">
-        <f>G40+X40</f>
-        <v>0</v>
-      </c>
-      <c r="R40">
-        <f>H40+Y40</f>
-        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -5301,39 +5316,39 @@
         <v>0</v>
       </c>
       <c r="I41" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K41" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q41">
-        <f>G41+X41</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R41">
-        <f>H41+Y41</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -5363,39 +5378,39 @@
         <v>0</v>
       </c>
       <c r="I42" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K42" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q42">
-        <f>G42+X42</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R42">
-        <f>H42+Y42</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -5425,39 +5440,39 @@
         <v>0</v>
       </c>
       <c r="I43" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K43" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O43">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q43">
-        <f>G43+X43</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R43">
-        <f>H43+Y43</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -5469,13 +5484,13 @@
         <v>79</v>
       </c>
       <c r="C44">
-        <v>15</v>
+        <v>12.4</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F44">
         <v>3</v>
@@ -5484,43 +5499,43 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="11">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="J44" s="15">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K44" s="15">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="J44" s="14">
+        <f t="shared" si="2"/>
+        <v>3.1</v>
+      </c>
+      <c r="K44" s="14">
+        <f t="shared" si="3"/>
+        <v>0.62</v>
       </c>
       <c r="M44">
-        <f t="shared" si="3"/>
-        <v>15</v>
+        <f t="shared" si="4"/>
+        <v>12.4</v>
       </c>
       <c r="N44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
+        <v>2.48</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="P44">
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="O44">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="P44">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
       <c r="Q44">
-        <f>G44+X44</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R44">
-        <f>H44+Y44</f>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -5549,39 +5564,39 @@
         <v>0</v>
       </c>
       <c r="I45" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J45" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K45" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N45">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q45">
-        <f>G45+X45</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R45">
-        <f>H45+Y45</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -5611,39 +5626,39 @@
         <v>0</v>
       </c>
       <c r="I46" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J46" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q46">
-        <f>G46+X46</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R46">
-        <f>H46+Y46</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -5673,39 +5688,39 @@
         <v>0</v>
       </c>
       <c r="I47" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J47" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K47" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N47">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q47">
-        <f>G47+X47</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R47">
-        <f>H47+Y47</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -5735,39 +5750,39 @@
         <v>2</v>
       </c>
       <c r="I48" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J48" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="14">
+        <f t="shared" si="2"/>
         <v>-6</v>
       </c>
-      <c r="K48" s="15">
-        <f t="shared" si="2"/>
+      <c r="K48" s="14">
+        <f t="shared" si="3"/>
         <v>-1.2</v>
       </c>
       <c r="M48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-12</v>
       </c>
       <c r="N48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>-2.4</v>
       </c>
       <c r="O48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="P48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q48">
-        <f>G48+X48</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R48">
-        <f>H48+Y48</f>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
     </row>
@@ -5797,39 +5812,39 @@
         <v>2</v>
       </c>
       <c r="I49" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="J49" s="15">
-        <f t="shared" si="1"/>
+      <c r="J49" s="14">
+        <f t="shared" si="2"/>
         <v>-0.58000000000000007</v>
       </c>
-      <c r="K49" s="15">
-        <f t="shared" si="2"/>
+      <c r="K49" s="14">
+        <f t="shared" si="3"/>
         <v>-0.11600000000000002</v>
       </c>
       <c r="M49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.9000000000000004</v>
       </c>
       <c r="N49">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>-0.58000000000000007</v>
       </c>
       <c r="O49">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="P49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="Q49">
-        <f>G49+X49</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R49">
-        <f>H49+Y49</f>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
     </row>
@@ -5859,39 +5874,39 @@
         <v>0</v>
       </c>
       <c r="I50" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J50" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K50" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q50">
-        <f>G50+X50</f>
+        <f t="shared" ref="Q50:Q67" si="15">G50+X50</f>
         <v>0</v>
       </c>
       <c r="R50">
-        <f>H50+Y50</f>
+        <f t="shared" ref="R50:R67" si="16">H50+Y50</f>
         <v>0</v>
       </c>
     </row>
@@ -5921,39 +5936,39 @@
         <v>0</v>
       </c>
       <c r="I51" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q51">
-        <f>G51+X51</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R51">
-        <f>H51+Y51</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -5983,39 +5998,39 @@
         <v>0</v>
       </c>
       <c r="I52" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J52" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K52" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N52">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q52">
-        <f>G52+X52</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R52">
-        <f>H52+Y52</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -6027,16 +6042,16 @@
         <v>78</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>0.33999999999999997</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -6045,39 +6060,39 @@
         <v>0</v>
       </c>
       <c r="I53" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K53" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="J53" s="14">
+        <f t="shared" si="2"/>
+        <v>1.7</v>
+      </c>
+      <c r="K53" s="14">
+        <f t="shared" si="3"/>
+        <v>0.33999999999999997</v>
       </c>
       <c r="M53">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1.7</v>
       </c>
       <c r="N53">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>0.33999999999999997</v>
       </c>
       <c r="O53">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="P53">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="Q53">
-        <f>G53+X53</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R53">
-        <f>H53+Y53</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -6107,39 +6122,39 @@
         <v>0</v>
       </c>
       <c r="I54" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K54" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N54">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q54">
-        <f>G54+X54</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R54">
-        <f>H54+Y54</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -6151,58 +6166,58 @@
         <v>73</v>
       </c>
       <c r="C55">
-        <v>-6.1</v>
+        <v>-5.7999999999999989</v>
       </c>
       <c r="D55">
-        <v>-1.22</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I55" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J55" s="15">
-        <f t="shared" si="1"/>
-        <v>-2.0333333333333332</v>
-      </c>
-      <c r="K55" s="15">
-        <f t="shared" si="2"/>
-        <v>-0.40666666666666668</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="J55" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.1599999999999997</v>
+      </c>
+      <c r="K55" s="14">
+        <f t="shared" si="3"/>
+        <v>-0.23199999999999998</v>
       </c>
       <c r="M55">
-        <f t="shared" si="3"/>
-        <v>-6.1</v>
+        <f t="shared" si="4"/>
+        <v>-5.7999999999999989</v>
       </c>
       <c r="N55">
-        <f t="shared" si="4"/>
-        <v>-1.22</v>
+        <f t="shared" si="10"/>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="O55">
-        <f t="shared" si="5"/>
-        <v>3</v>
+        <f t="shared" si="11"/>
+        <v>5</v>
       </c>
       <c r="P55">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="Q55">
-        <f>G55+X55</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R55">
-        <f>H55+Y55</f>
-        <v>3</v>
+        <f t="shared" si="16"/>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
@@ -6213,13 +6228,13 @@
         <v>114</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -6228,43 +6243,43 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K56" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="14">
+        <f t="shared" si="2"/>
+        <v>-1.2</v>
+      </c>
+      <c r="K56" s="14">
+        <f t="shared" si="3"/>
+        <v>-0.24</v>
       </c>
       <c r="M56">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>-1.2</v>
       </c>
       <c r="N56">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-0.24</v>
       </c>
       <c r="O56">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="P56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q56">
-        <f>G56+X56</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R56">
-        <f>H56+Y56</f>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
@@ -6293,39 +6308,39 @@
         <v>0</v>
       </c>
       <c r="I57" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N57">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O57">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P57">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q57">
-        <f>G57+X57</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R57">
-        <f>H57+Y57</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -6355,39 +6370,39 @@
         <v>0</v>
       </c>
       <c r="I58" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O58">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q58">
-        <f>G58+X58</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R58">
-        <f>H58+Y58</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -6417,39 +6432,39 @@
         <v>0</v>
       </c>
       <c r="I59" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K59" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M59">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N59">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O59">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q59">
-        <f>G59+X59</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R59">
-        <f>H59+Y59</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -6479,39 +6494,39 @@
         <v>0</v>
       </c>
       <c r="I60" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K60" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K60" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N60">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O60">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P60">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q60">
-        <f>G60+X60</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R60">
-        <f>H60+Y60</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -6541,39 +6556,39 @@
         <v>0</v>
       </c>
       <c r="I61" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K61" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K61" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M61">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N61">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O61">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q61">
-        <f>G61+X61</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R61">
-        <f>H61+Y61</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -6603,39 +6618,39 @@
         <v>0</v>
       </c>
       <c r="I62" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J62" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K62" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M62">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N62">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O62">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P62">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q62">
-        <f>G62+X62</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R62">
-        <f>H62+Y62</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -6647,13 +6662,13 @@
         <v>62</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="E63">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63">
         <v>7</v>
@@ -6662,43 +6677,43 @@
         <v>0</v>
       </c>
       <c r="H63">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I63" s="11">
-        <f t="shared" si="0"/>
-        <v>53.846153846153847</v>
-      </c>
-      <c r="J63" s="15">
-        <f t="shared" si="1"/>
-        <v>0.38461538461538464</v>
-      </c>
-      <c r="K63" s="15">
-        <f t="shared" si="2"/>
-        <v>7.6923076923076927E-2</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="J63" s="14">
+        <f t="shared" si="2"/>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="K63" s="14">
+        <f t="shared" si="3"/>
+        <v>0.04</v>
       </c>
       <c r="M63">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>2.8</v>
       </c>
       <c r="N63">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>0.56000000000000005</v>
       </c>
       <c r="O63">
-        <f t="shared" si="5"/>
-        <v>13</v>
+        <f t="shared" si="11"/>
+        <v>14</v>
       </c>
       <c r="P63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="Q63">
-        <f>G63+X63</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R63">
-        <f>H63+Y63</f>
-        <v>6</v>
+        <f t="shared" si="16"/>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -6709,16 +6724,16 @@
         <v>61</v>
       </c>
       <c r="C64">
-        <v>29.1</v>
+        <v>35.5</v>
       </c>
       <c r="D64">
-        <v>5.82</v>
+        <v>7.1000000000000005</v>
       </c>
       <c r="E64">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F64">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6727,39 +6742,39 @@
         <v>5</v>
       </c>
       <c r="I64" s="11">
-        <f t="shared" si="0"/>
-        <v>72.222222222222214</v>
-      </c>
-      <c r="J64" s="15">
-        <f t="shared" si="1"/>
-        <v>1.6166666666666667</v>
-      </c>
-      <c r="K64" s="15">
-        <f t="shared" si="2"/>
-        <v>0.32333333333333336</v>
+        <f t="shared" si="1"/>
+        <v>76.19047619047619</v>
+      </c>
+      <c r="J64" s="14">
+        <f t="shared" si="2"/>
+        <v>1.6904761904761905</v>
+      </c>
+      <c r="K64" s="14">
+        <f t="shared" si="3"/>
+        <v>0.33809523809523812</v>
       </c>
       <c r="M64">
-        <f t="shared" si="3"/>
-        <v>29.1</v>
+        <f t="shared" si="4"/>
+        <v>35.5</v>
       </c>
       <c r="N64">
-        <f t="shared" si="4"/>
-        <v>5.82</v>
+        <f t="shared" si="10"/>
+        <v>7.1000000000000005</v>
       </c>
       <c r="O64">
-        <f t="shared" si="5"/>
-        <v>18</v>
+        <f t="shared" si="11"/>
+        <v>21</v>
       </c>
       <c r="P64">
-        <f t="shared" si="6"/>
-        <v>13</v>
+        <f t="shared" si="12"/>
+        <v>16</v>
       </c>
       <c r="Q64">
-        <f>G64+X64</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R64">
-        <f>H64+Y64</f>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
     </row>
@@ -6789,39 +6804,39 @@
         <v>0</v>
       </c>
       <c r="I65" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K65" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J65" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K65" s="14">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q65">
-        <f>G65+X65</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R65">
-        <f>H65+Y65</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -6833,16 +6848,16 @@
         <v>63</v>
       </c>
       <c r="C66">
-        <v>22.9</v>
+        <v>28.4</v>
       </c>
       <c r="D66">
-        <v>4.58</v>
+        <v>5.68</v>
       </c>
       <c r="E66">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6851,39 +6866,39 @@
         <v>2</v>
       </c>
       <c r="I66" s="11">
-        <f t="shared" si="0"/>
-        <v>62.5</v>
-      </c>
-      <c r="J66" s="15">
-        <f t="shared" si="1"/>
-        <v>2.8624999999999998</v>
-      </c>
-      <c r="K66" s="15">
-        <f t="shared" si="2"/>
-        <v>0.57250000000000001</v>
+        <f t="shared" si="1"/>
+        <v>66.666666666666657</v>
+      </c>
+      <c r="J66" s="14">
+        <f t="shared" si="2"/>
+        <v>3.1555555555555554</v>
+      </c>
+      <c r="K66" s="14">
+        <f t="shared" si="3"/>
+        <v>0.63111111111111107</v>
       </c>
       <c r="M66">
-        <f t="shared" si="3"/>
-        <v>22.9</v>
+        <f t="shared" si="4"/>
+        <v>28.4</v>
       </c>
       <c r="N66">
-        <f t="shared" si="4"/>
-        <v>4.58</v>
+        <f t="shared" si="10"/>
+        <v>5.68</v>
       </c>
       <c r="O66">
-        <f t="shared" si="5"/>
-        <v>8</v>
+        <f t="shared" si="11"/>
+        <v>9</v>
       </c>
       <c r="P66">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f t="shared" si="12"/>
+        <v>6</v>
       </c>
       <c r="Q66">
-        <f>G66+X66</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R66">
-        <f>H66+Y66</f>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
     </row>
@@ -6913,39 +6928,39 @@
         <v>0</v>
       </c>
       <c r="I67" s="11">
-        <f t="shared" ref="I67" si="7">IFERROR((F67/E67)*100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="15">
-        <f t="shared" ref="J67" si="8">IFERROR(C67/E67,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="15">
-        <f t="shared" ref="K67" si="9">IFERROR(D67/E67,0)</f>
+        <f t="shared" ref="I67" si="17">IFERROR((F67/E67)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="14">
+        <f t="shared" ref="J67" si="18">IFERROR(C67/E67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K67" s="14">
+        <f t="shared" ref="K67" si="19">IFERROR(D67/E67,0)</f>
         <v>0</v>
       </c>
       <c r="M67">
-        <f t="shared" ref="M67" si="10">C67+T67</f>
+        <f t="shared" ref="M67" si="20">C67+T67</f>
         <v>0</v>
       </c>
       <c r="N67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O67">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q67">
-        <f>G67+X67</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R67">
-        <f>H67+Y67</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -7203,7 +7218,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
-    <col min="8" max="28" width="9.140625" style="13"/>
+    <col min="8" max="28" width="6.28515625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7215,7 +7230,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
+      <c r="A2" s="13"/>
       <c r="B2" t="s">
         <v>136</v>
       </c>
@@ -7234,7 +7249,7 @@
       <c r="G2" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>141</v>
       </c>
     </row>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E9DD6C-CC1A-4119-9DCE-2A013E25D48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2525A5C4-1803-469C-8A55-F74E7C44C991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2880,13 +2880,13 @@
         <v>132</v>
       </c>
       <c r="C2">
-        <v>-1.9</v>
+        <v>-23.9</v>
       </c>
       <c r="D2">
-        <v>-0.38</v>
+        <v>-4.7799999999999994</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" s="11">
         <f>IFERROR((F2/E2)*100,0)</f>
@@ -2903,23 +2903,23 @@
       </c>
       <c r="J2" s="14">
         <f>IFERROR(C2/E2,0)</f>
-        <v>-1.9</v>
+        <v>-11.95</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(D2/E2,0)</f>
-        <v>-0.38</v>
+        <v>-2.3899999999999997</v>
       </c>
       <c r="M2">
         <f t="shared" ref="M2:R2" si="0">C2+T2</f>
-        <v>-1.9</v>
+        <v>-23.9</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>-0.38</v>
+        <v>-4.7799999999999994</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -3004,13 +3004,13 @@
         <v>135</v>
       </c>
       <c r="C4">
-        <v>-2.7</v>
+        <v>-20.9</v>
       </c>
       <c r="D4">
-        <v>-0.54</v>
+        <v>-4.18</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -3019,31 +3019,31 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" si="1"/>
-        <v>33.333333333333329</v>
+        <v>20</v>
       </c>
       <c r="J4" s="14">
         <f t="shared" si="2"/>
-        <v>-0.9</v>
+        <v>-4.18</v>
       </c>
       <c r="K4" s="14">
         <f t="shared" si="3"/>
-        <v>-0.18000000000000002</v>
+        <v>-0.83599999999999997</v>
       </c>
       <c r="M4">
         <f t="shared" si="4"/>
-        <v>-2.7</v>
+        <v>-20.9</v>
       </c>
       <c r="N4">
         <f t="shared" si="5"/>
-        <v>-0.54</v>
+        <v>-4.18</v>
       </c>
       <c r="O4">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <f t="shared" si="7"/>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="R4">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -3128,16 +3128,16 @@
         <v>134</v>
       </c>
       <c r="C6">
-        <v>-2.5</v>
+        <v>-1.9</v>
       </c>
       <c r="D6">
-        <v>-0.5</v>
+        <v>-0.38</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3147,31 +3147,31 @@
       </c>
       <c r="I6" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J6" s="14">
         <f t="shared" si="2"/>
-        <v>-2.5</v>
+        <v>-0.95</v>
       </c>
       <c r="K6" s="14">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.19</v>
       </c>
       <c r="M6">
         <f t="shared" si="4"/>
-        <v>-2.5</v>
+        <v>-1.9</v>
       </c>
       <c r="N6">
         <f t="shared" si="5"/>
-        <v>-0.5</v>
+        <v>-0.38</v>
       </c>
       <c r="O6">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6">
         <f t="shared" si="8"/>
@@ -3438,50 +3438,50 @@
         <v>72</v>
       </c>
       <c r="C11">
-        <v>30.1</v>
+        <v>19.2</v>
       </c>
       <c r="D11">
-        <v>6.0200000000000005</v>
+        <v>3.8400000000000003</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F11">
+        <v>6</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>5</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>3</v>
-      </c>
       <c r="I11" s="11">
         <f t="shared" si="1"/>
-        <v>62.5</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="J11" s="14">
         <f t="shared" si="2"/>
-        <v>3.7625000000000002</v>
+        <v>1.7454545454545454</v>
       </c>
       <c r="K11" s="14">
         <f t="shared" si="3"/>
-        <v>0.75250000000000006</v>
+        <v>0.34909090909090912</v>
       </c>
       <c r="M11">
         <f t="shared" si="4"/>
-        <v>30.1</v>
+        <v>19.2</v>
       </c>
       <c r="N11">
         <f t="shared" si="5"/>
-        <v>6.0200000000000005</v>
+        <v>3.8400000000000003</v>
       </c>
       <c r="O11">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P11">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <f t="shared" si="8"/>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="R11">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
@@ -3624,50 +3624,50 @@
         <v>60</v>
       </c>
       <c r="C14">
-        <v>36.799999999999997</v>
+        <v>24.4</v>
       </c>
       <c r="D14">
-        <v>7.36</v>
+        <v>4.8800000000000008</v>
       </c>
       <c r="E14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F14">
+        <v>6</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>5</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>4</v>
-      </c>
       <c r="I14" s="11">
         <f t="shared" si="1"/>
-        <v>55.555555555555557</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="2"/>
-        <v>4.0888888888888886</v>
+        <v>2.2181818181818183</v>
       </c>
       <c r="K14" s="14">
         <f t="shared" si="3"/>
-        <v>0.81777777777777783</v>
+        <v>0.44363636363636372</v>
       </c>
       <c r="M14">
         <f t="shared" si="4"/>
-        <v>36.799999999999997</v>
+        <v>24.4</v>
       </c>
       <c r="N14">
         <f t="shared" si="5"/>
-        <v>7.36</v>
+        <v>4.8800000000000008</v>
       </c>
       <c r="O14">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P14">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <f t="shared" si="8"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R14">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -3686,16 +3686,16 @@
         <v>67</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>15.4</v>
       </c>
       <c r="D15">
-        <v>2.2000000000000002</v>
+        <v>3.08</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3705,31 +3705,31 @@
       </c>
       <c r="I15" s="11">
         <f t="shared" si="1"/>
-        <v>66.666666666666657</v>
+        <v>70</v>
       </c>
       <c r="J15" s="14">
         <f t="shared" si="2"/>
-        <v>1.2222222222222223</v>
+        <v>1.54</v>
       </c>
       <c r="K15" s="14">
         <f t="shared" si="3"/>
-        <v>0.24444444444444446</v>
+        <v>0.308</v>
       </c>
       <c r="M15">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>15.4</v>
       </c>
       <c r="N15">
         <f t="shared" si="5"/>
-        <v>2.2000000000000002</v>
+        <v>3.08</v>
       </c>
       <c r="O15">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <f t="shared" si="8"/>
@@ -3996,16 +3996,16 @@
         <v>69</v>
       </c>
       <c r="C20">
-        <v>5.6999999999999984</v>
+        <v>7.6999999999999984</v>
       </c>
       <c r="D20">
-        <v>1.1399999999999997</v>
+        <v>1.5399999999999996</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -4015,31 +4015,31 @@
       </c>
       <c r="I20" s="11">
         <f t="shared" si="1"/>
-        <v>43.478260869565219</v>
+        <v>48</v>
       </c>
       <c r="J20" s="14">
         <f t="shared" si="2"/>
-        <v>0.24782608695652167</v>
+        <v>0.30799999999999994</v>
       </c>
       <c r="K20" s="14">
         <f t="shared" si="3"/>
-        <v>4.9565217391304331E-2</v>
+        <v>6.1599999999999981E-2</v>
       </c>
       <c r="M20">
         <f t="shared" si="4"/>
-        <v>5.6999999999999984</v>
+        <v>7.6999999999999984</v>
       </c>
       <c r="N20">
         <f t="shared" si="10"/>
-        <v>1.1399999999999997</v>
+        <v>1.5399999999999996</v>
       </c>
       <c r="O20">
         <f t="shared" si="11"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P20">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q20">
         <f t="shared" si="13"/>
@@ -4120,13 +4120,13 @@
         <v>121</v>
       </c>
       <c r="C22">
-        <v>1.2</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="D22">
-        <v>0.24</v>
+        <v>-0.38</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -4135,31 +4135,31 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="11">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J22" s="14">
         <f t="shared" si="2"/>
-        <v>1.2</v>
+        <v>-0.95000000000000007</v>
       </c>
       <c r="K22" s="14">
         <f t="shared" si="3"/>
-        <v>0.24</v>
+        <v>-0.19</v>
       </c>
       <c r="M22">
         <f t="shared" si="4"/>
-        <v>1.2</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="N22">
         <f t="shared" si="10"/>
-        <v>0.24</v>
+        <v>-0.38</v>
       </c>
       <c r="O22">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P22">
         <f t="shared" si="12"/>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="R22">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -4182,13 +4182,13 @@
         <v>66</v>
       </c>
       <c r="C23">
-        <v>5.7</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="D23">
-        <v>1.1400000000000001</v>
+        <v>0.66000000000000014</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -4197,31 +4197,31 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" s="11">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J23" s="14">
         <f t="shared" si="2"/>
-        <v>1.1400000000000001</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K23" s="14">
         <f t="shared" si="3"/>
-        <v>0.22800000000000004</v>
+        <v>0.11000000000000003</v>
       </c>
       <c r="M23">
         <f t="shared" si="4"/>
-        <v>5.7</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="N23">
         <f t="shared" si="10"/>
-        <v>1.1400000000000001</v>
+        <v>0.66000000000000014</v>
       </c>
       <c r="O23">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <f t="shared" si="12"/>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="R23">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -4430,50 +4430,50 @@
         <v>70</v>
       </c>
       <c r="C27">
-        <v>36.9</v>
+        <v>31.4</v>
       </c>
       <c r="D27">
-        <v>7.3800000000000008</v>
+        <v>6.2800000000000011</v>
       </c>
       <c r="E27">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I27" s="11">
         <f t="shared" si="1"/>
-        <v>71.428571428571431</v>
+        <v>57.894736842105267</v>
       </c>
       <c r="J27" s="14">
         <f t="shared" si="2"/>
-        <v>2.6357142857142857</v>
+        <v>1.6526315789473685</v>
       </c>
       <c r="K27" s="14">
         <f t="shared" si="3"/>
-        <v>0.52714285714285725</v>
+        <v>0.33052631578947372</v>
       </c>
       <c r="M27">
         <f t="shared" si="4"/>
-        <v>36.9</v>
+        <v>31.4</v>
       </c>
       <c r="N27">
         <f t="shared" si="10"/>
-        <v>7.3800000000000008</v>
+        <v>6.2800000000000011</v>
       </c>
       <c r="O27">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P27">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q27">
         <f t="shared" si="13"/>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="R27">
         <f t="shared" si="14"/>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -4616,13 +4616,13 @@
         <v>128</v>
       </c>
       <c r="C30">
-        <v>0.3</v>
+        <v>-3.5</v>
       </c>
       <c r="D30">
-        <v>0.06</v>
+        <v>-0.7</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -4631,31 +4631,31 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="11">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J30" s="14">
         <f t="shared" si="2"/>
-        <v>0.3</v>
+        <v>-1.75</v>
       </c>
       <c r="K30" s="14">
         <f t="shared" si="3"/>
-        <v>0.06</v>
+        <v>-0.35</v>
       </c>
       <c r="M30">
         <f t="shared" si="4"/>
-        <v>0.3</v>
+        <v>-3.5</v>
       </c>
       <c r="N30">
         <f t="shared" si="10"/>
-        <v>0.06</v>
+        <v>-0.7</v>
       </c>
       <c r="O30">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30">
         <f t="shared" si="12"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="R30">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -4740,16 +4740,16 @@
         <v>124</v>
       </c>
       <c r="C32">
-        <v>0.9</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D32">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4763,27 +4763,27 @@
       </c>
       <c r="J32" s="14">
         <f t="shared" si="2"/>
-        <v>0.9</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K32" s="14">
         <f t="shared" si="3"/>
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="M32">
         <f t="shared" si="4"/>
-        <v>0.9</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N32">
         <f t="shared" si="10"/>
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="O32">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32">
         <f t="shared" si="13"/>
@@ -4802,16 +4802,16 @@
         <v>127</v>
       </c>
       <c r="C33">
-        <v>-10</v>
+        <v>-1.1999999999999993</v>
       </c>
       <c r="D33">
-        <v>-2</v>
+        <v>-0.24</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4821,31 +4821,31 @@
       </c>
       <c r="I33" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J33" s="14">
         <f t="shared" si="2"/>
-        <v>-10</v>
+        <v>-0.59999999999999964</v>
       </c>
       <c r="K33" s="14">
         <f t="shared" si="3"/>
-        <v>-2</v>
+        <v>-0.12</v>
       </c>
       <c r="M33">
         <f t="shared" si="4"/>
-        <v>-10</v>
+        <v>-1.1999999999999993</v>
       </c>
       <c r="N33">
         <f t="shared" si="10"/>
-        <v>-2</v>
+        <v>-0.24</v>
       </c>
       <c r="O33">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P33">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33">
         <f t="shared" si="13"/>
@@ -4926,13 +4926,13 @@
         <v>131</v>
       </c>
       <c r="C35">
-        <v>2.2999999999999998</v>
+        <v>-0.40000000000000036</v>
       </c>
       <c r="D35">
-        <v>0.45999999999999996</v>
+        <v>-8.0000000000000071E-2</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -4941,31 +4941,31 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="11">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J35" s="14">
         <f t="shared" si="2"/>
-        <v>2.2999999999999998</v>
+        <v>-0.20000000000000018</v>
       </c>
       <c r="K35" s="14">
         <f t="shared" si="3"/>
-        <v>0.45999999999999996</v>
+        <v>-4.0000000000000036E-2</v>
       </c>
       <c r="M35">
         <f t="shared" si="4"/>
-        <v>2.2999999999999998</v>
+        <v>-0.40000000000000036</v>
       </c>
       <c r="N35">
         <f t="shared" si="10"/>
-        <v>0.45999999999999996</v>
+        <v>-8.0000000000000071E-2</v>
       </c>
       <c r="O35">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P35">
         <f t="shared" si="12"/>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="R35">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -5236,46 +5236,46 @@
         <v>87</v>
       </c>
       <c r="C40">
-        <v>-3.4</v>
+        <v>-6.5</v>
       </c>
       <c r="D40">
-        <v>-0.67999999999999994</v>
+        <v>-1.2999999999999998</v>
       </c>
       <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>3</v>
       </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>2</v>
-      </c>
       <c r="I40" s="11">
         <f t="shared" si="1"/>
-        <v>33.333333333333329</v>
+        <v>25</v>
       </c>
       <c r="J40" s="14">
         <f t="shared" si="2"/>
-        <v>-1.1333333333333333</v>
+        <v>-1.625</v>
       </c>
       <c r="K40" s="14">
         <f t="shared" si="3"/>
-        <v>-0.22666666666666666</v>
+        <v>-0.32499999999999996</v>
       </c>
       <c r="M40">
         <f t="shared" si="4"/>
-        <v>-3.4</v>
+        <v>-6.5</v>
       </c>
       <c r="N40">
         <f t="shared" si="10"/>
-        <v>-0.67999999999999994</v>
+        <v>-1.2999999999999998</v>
       </c>
       <c r="O40">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P40">
         <f t="shared" si="12"/>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="R40">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -5484,13 +5484,13 @@
         <v>79</v>
       </c>
       <c r="C44">
-        <v>12.4</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="D44">
-        <v>2.48</v>
+        <v>0.37999999999999989</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F44">
         <v>3</v>
@@ -5499,31 +5499,31 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="11">
         <f t="shared" si="1"/>
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J44" s="14">
         <f t="shared" si="2"/>
-        <v>3.1</v>
+        <v>0.38000000000000006</v>
       </c>
       <c r="K44" s="14">
         <f t="shared" si="3"/>
-        <v>0.62</v>
+        <v>7.5999999999999984E-2</v>
       </c>
       <c r="M44">
         <f t="shared" si="4"/>
-        <v>12.4</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="N44">
         <f t="shared" si="10"/>
-        <v>2.48</v>
+        <v>0.37999999999999989</v>
       </c>
       <c r="O44">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P44">
         <f t="shared" si="12"/>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="R44">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -5856,13 +5856,13 @@
         <v>108</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -5871,7 +5871,7 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="11">
         <f t="shared" si="1"/>
@@ -5879,23 +5879,23 @@
       </c>
       <c r="J50" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="K50" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="M50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="N50">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="O50">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50">
         <f t="shared" si="12"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="R50">
         <f t="shared" ref="R50:R67" si="16">H50+Y50</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
@@ -6042,13 +6042,13 @@
         <v>78</v>
       </c>
       <c r="C53">
-        <v>1.7</v>
+        <v>-2.8999999999999995</v>
       </c>
       <c r="D53">
-        <v>0.33999999999999997</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -6057,31 +6057,31 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="11">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J53" s="14">
         <f t="shared" si="2"/>
-        <v>1.7</v>
+        <v>-1.4499999999999997</v>
       </c>
       <c r="K53" s="14">
         <f t="shared" si="3"/>
-        <v>0.33999999999999997</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="M53">
         <f t="shared" si="4"/>
-        <v>1.7</v>
+        <v>-2.8999999999999995</v>
       </c>
       <c r="N53">
         <f t="shared" si="10"/>
-        <v>0.33999999999999997</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="O53">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P53">
         <f t="shared" si="12"/>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="R53">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
@@ -6166,16 +6166,16 @@
         <v>73</v>
       </c>
       <c r="C55">
-        <v>-5.7999999999999989</v>
+        <v>1.6000000000000014</v>
       </c>
       <c r="D55">
-        <v>-1.1599999999999999</v>
+        <v>0.32000000000000006</v>
       </c>
       <c r="E55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -6185,31 +6185,31 @@
       </c>
       <c r="I55" s="11">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J55" s="14">
         <f t="shared" si="2"/>
-        <v>-1.1599999999999997</v>
+        <v>0.26666666666666689</v>
       </c>
       <c r="K55" s="14">
         <f t="shared" si="3"/>
-        <v>-0.23199999999999998</v>
+        <v>5.3333333333333344E-2</v>
       </c>
       <c r="M55">
         <f t="shared" si="4"/>
-        <v>-5.7999999999999989</v>
+        <v>1.6000000000000014</v>
       </c>
       <c r="N55">
         <f t="shared" si="10"/>
-        <v>-1.1599999999999999</v>
+        <v>0.32000000000000006</v>
       </c>
       <c r="O55">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P55">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q55">
         <f t="shared" si="15"/>
@@ -6662,13 +6662,13 @@
         <v>62</v>
       </c>
       <c r="C63">
-        <v>2.8</v>
+        <v>-14.3</v>
       </c>
       <c r="D63">
-        <v>0.56000000000000005</v>
+        <v>-2.86</v>
       </c>
       <c r="E63">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F63">
         <v>7</v>
@@ -6677,31 +6677,31 @@
         <v>0</v>
       </c>
       <c r="H63">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I63" s="11">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>46.666666666666664</v>
       </c>
       <c r="J63" s="14">
         <f t="shared" si="2"/>
-        <v>0.19999999999999998</v>
+        <v>-0.95333333333333337</v>
       </c>
       <c r="K63" s="14">
         <f t="shared" si="3"/>
-        <v>0.04</v>
+        <v>-0.19066666666666665</v>
       </c>
       <c r="M63">
         <f t="shared" si="4"/>
-        <v>2.8</v>
+        <v>-14.3</v>
       </c>
       <c r="N63">
         <f t="shared" si="10"/>
-        <v>0.56000000000000005</v>
+        <v>-2.86</v>
       </c>
       <c r="O63">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P63">
         <f t="shared" si="12"/>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="R63">
         <f t="shared" si="16"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -6724,50 +6724,50 @@
         <v>61</v>
       </c>
       <c r="C64">
-        <v>35.5</v>
+        <v>32.6</v>
       </c>
       <c r="D64">
-        <v>7.1000000000000005</v>
+        <v>6.5200000000000005</v>
       </c>
       <c r="E64">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F64">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G64">
         <v>0</v>
       </c>
       <c r="H64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I64" s="11">
         <f t="shared" si="1"/>
-        <v>76.19047619047619</v>
+        <v>70.833333333333343</v>
       </c>
       <c r="J64" s="14">
         <f t="shared" si="2"/>
-        <v>1.6904761904761905</v>
+        <v>1.3583333333333334</v>
       </c>
       <c r="K64" s="14">
         <f t="shared" si="3"/>
-        <v>0.33809523809523812</v>
+        <v>0.27166666666666667</v>
       </c>
       <c r="M64">
         <f t="shared" si="4"/>
-        <v>35.5</v>
+        <v>32.6</v>
       </c>
       <c r="N64">
         <f t="shared" si="10"/>
-        <v>7.1000000000000005</v>
+        <v>6.5200000000000005</v>
       </c>
       <c r="O64">
         <f t="shared" si="11"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P64">
         <f t="shared" si="12"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q64">
         <f t="shared" si="15"/>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="R64">
         <f t="shared" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -6848,13 +6848,13 @@
         <v>63</v>
       </c>
       <c r="C66">
-        <v>28.4</v>
+        <v>17.5</v>
       </c>
       <c r="D66">
-        <v>5.68</v>
+        <v>3.4999999999999996</v>
       </c>
       <c r="E66">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F66">
         <v>6</v>
@@ -6863,31 +6863,31 @@
         <v>1</v>
       </c>
       <c r="H66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I66" s="11">
         <f t="shared" si="1"/>
-        <v>66.666666666666657</v>
+        <v>60</v>
       </c>
       <c r="J66" s="14">
         <f t="shared" si="2"/>
-        <v>3.1555555555555554</v>
+        <v>1.75</v>
       </c>
       <c r="K66" s="14">
         <f t="shared" si="3"/>
-        <v>0.63111111111111107</v>
+        <v>0.35</v>
       </c>
       <c r="M66">
         <f t="shared" si="4"/>
-        <v>28.4</v>
+        <v>17.5</v>
       </c>
       <c r="N66">
         <f t="shared" si="10"/>
-        <v>5.68</v>
+        <v>3.4999999999999996</v>
       </c>
       <c r="O66">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P66">
         <f t="shared" si="12"/>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="R66">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
@@ -7221,7 +7221,7 @@
     <col min="8" max="28" width="6.28515625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>140</v>
       </c>
@@ -7229,7 +7229,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="B2" t="s">
         <v>136</v>
@@ -7253,21 +7253,21 @@
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>132</v>
       </c>
       <c r="B3">
         <f>SUM(H3:AB3)</f>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="C3">
         <f>(B3/$C$1)*100</f>
-        <v>0</v>
+        <v>-4.3999999999999995</v>
       </c>
       <c r="D3">
         <f>COUNTA(H3:AB3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f>COUNTIF(H3:AB3, "&gt;0")</f>
@@ -7279,10 +7279,13 @@
       </c>
       <c r="G3">
         <f>COUNTIF(H3:AB3, "&lt;0")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H3" s="15">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -7311,21 +7314,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>135</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-18.2</v>
       </c>
       <c r="C5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-3.64</v>
       </c>
       <c r="D5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <f t="shared" si="3"/>
@@ -7337,10 +7340,16 @@
       </c>
       <c r="G5">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H5" s="15">
+        <v>-4.2</v>
+      </c>
+      <c r="I5" s="15">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>133</v>
       </c>
@@ -7369,25 +7378,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>134</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="D7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <f t="shared" si="4"/>
@@ -7397,8 +7406,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H7" s="15">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>74</v>
       </c>
@@ -7427,7 +7439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>99</v>
       </c>
@@ -7456,7 +7468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>101</v>
       </c>
@@ -7485,7 +7497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>77</v>
       </c>
@@ -7514,25 +7526,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>72</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10.900000000000002</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2.1800000000000002</v>
       </c>
       <c r="D12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <f t="shared" si="4"/>
@@ -7540,10 +7552,19 @@
       </c>
       <c r="G12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H12" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="I12" s="15">
+        <v>-9.3000000000000007</v>
+      </c>
+      <c r="J12" s="15">
+        <v>-2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>102</v>
       </c>
@@ -7572,7 +7593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -7601,25 +7622,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-12.4</v>
       </c>
       <c r="C15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2.48</v>
       </c>
       <c r="D15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <f t="shared" si="4"/>
@@ -7627,28 +7648,34 @@
       </c>
       <c r="G15">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-17.5</v>
+      </c>
+      <c r="I15" s="15">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>67</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="C16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="D16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <f t="shared" si="4"/>
@@ -7658,8 +7685,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="15">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -7688,7 +7718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>95</v>
       </c>
@@ -7717,7 +7747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -7746,7 +7776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -7775,25 +7805,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>69</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21">
         <f t="shared" si="4"/>
@@ -7803,8 +7833,14 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="15">
+        <v>1.3</v>
+      </c>
+      <c r="I21" s="15">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>85</v>
       </c>
@@ -7833,21 +7869,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>121</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-3.1</v>
       </c>
       <c r="C23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="D23">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <f t="shared" si="3"/>
@@ -7859,24 +7895,27 @@
       </c>
       <c r="G23">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>66</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="C24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-0.48</v>
       </c>
       <c r="D24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <f t="shared" si="3"/>
@@ -7888,10 +7927,13 @@
       </c>
       <c r="G24">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>120</v>
       </c>
@@ -7920,7 +7962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>122</v>
       </c>
@@ -7949,7 +7991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>123</v>
       </c>
@@ -7978,25 +8020,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>70</v>
       </c>
       <c r="B28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-5.5</v>
       </c>
       <c r="C28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1.0999999999999999</v>
       </c>
       <c r="D28">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <f t="shared" si="4"/>
@@ -8004,10 +8046,25 @@
       </c>
       <c r="G28">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="H28" s="15">
+        <v>3.7</v>
+      </c>
+      <c r="I28" s="15">
+        <v>-1.2</v>
+      </c>
+      <c r="J28" s="15">
+        <v>-0.9</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-4</v>
+      </c>
+      <c r="L28" s="15">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>130</v>
       </c>
@@ -8036,7 +8093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -8065,21 +8122,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>128</v>
       </c>
       <c r="B31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-3.8</v>
       </c>
       <c r="C31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-0.76</v>
       </c>
       <c r="D31">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <f t="shared" si="3"/>
@@ -8091,10 +8148,13 @@
       </c>
       <c r="G31">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>126</v>
       </c>
@@ -8123,25 +8183,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>124</v>
       </c>
       <c r="B33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D33">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
         <f t="shared" si="4"/>
@@ -8151,26 +8211,29 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33" s="15">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>127</v>
       </c>
       <c r="B34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="C34">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="D34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34">
         <f t="shared" si="4"/>
@@ -8180,8 +8243,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H34" s="15">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>129</v>
       </c>
@@ -8210,21 +8276,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>131</v>
       </c>
       <c r="B36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="C36">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="D36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36">
         <f t="shared" si="3"/>
@@ -8236,10 +8302,13 @@
       </c>
       <c r="G36">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H36" s="15">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>117</v>
       </c>
@@ -8268,7 +8337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>98</v>
       </c>
@@ -8297,7 +8366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -8326,7 +8395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -8355,21 +8424,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>87</v>
       </c>
       <c r="B41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-3.1</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="D41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41">
         <f t="shared" si="3"/>
@@ -8381,10 +8450,13 @@
       </c>
       <c r="G41">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H41" s="15">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>118</v>
       </c>
@@ -8413,7 +8485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>119</v>
       </c>
@@ -8442,7 +8514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>125</v>
       </c>
@@ -8471,21 +8543,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>79</v>
       </c>
       <c r="B45">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10.5</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="D45">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45">
         <f t="shared" si="3"/>
@@ -8497,10 +8569,13 @@
       </c>
       <c r="G45">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H45" s="15">
+        <v>-10.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>106</v>
       </c>
@@ -8529,7 +8604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>97</v>
       </c>
@@ -8558,7 +8633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -8587,7 +8662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -8616,7 +8691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -8645,21 +8720,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>108</v>
       </c>
       <c r="B51">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C51">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="D51">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51">
         <f t="shared" si="3"/>
@@ -8671,10 +8746,13 @@
       </c>
       <c r="G51">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H51" s="15">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>71</v>
       </c>
@@ -8703,7 +8781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -8732,21 +8810,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>78</v>
       </c>
       <c r="B54">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="C54">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-0.91999999999999993</v>
       </c>
       <c r="D54">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54">
         <f t="shared" si="3"/>
@@ -8758,10 +8836,13 @@
       </c>
       <c r="G54">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H54" s="15">
+        <v>-4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -8790,25 +8871,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>73</v>
       </c>
       <c r="B56">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="C56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="D56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56">
         <f t="shared" si="4"/>
@@ -8818,8 +8899,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56" s="15">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>114</v>
       </c>
@@ -8848,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -8877,7 +8961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -8906,7 +8990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -8935,7 +9019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>115</v>
       </c>
@@ -8964,7 +9048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>112</v>
       </c>
@@ -8993,7 +9077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>116</v>
       </c>
@@ -9022,21 +9106,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>62</v>
       </c>
       <c r="B64">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-17.100000000000001</v>
       </c>
       <c r="C64">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-3.42</v>
       </c>
       <c r="D64">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64">
         <f t="shared" si="3"/>
@@ -9048,28 +9132,31 @@
       </c>
       <c r="G64">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H64" s="15">
+        <v>-17.100000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>61</v>
       </c>
       <c r="B65">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2.9</v>
       </c>
       <c r="C65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="D65">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E65">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65">
         <f t="shared" si="4"/>
@@ -9077,10 +9164,19 @@
       </c>
       <c r="G65">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H65" s="15">
+        <v>-7</v>
+      </c>
+      <c r="I65" s="15">
+        <v>4.2</v>
+      </c>
+      <c r="J65" s="15">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>96</v>
       </c>
@@ -9109,21 +9205,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>63</v>
       </c>
       <c r="B67">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10.9</v>
       </c>
       <c r="C67">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2.1800000000000002</v>
       </c>
       <c r="D67">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <f t="shared" si="3"/>
@@ -9135,10 +9231,13 @@
       </c>
       <c r="G67">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H67" s="15">
+        <v>-10.9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>104</v>
       </c>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2525A5C4-1803-469C-8A55-F74E7C44C991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58760FCF-D965-4304-81F8-230913DD994F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
@@ -2880,13 +2880,13 @@
         <v>132</v>
       </c>
       <c r="C2">
-        <v>-23.9</v>
+        <v>-25.799999999999997</v>
       </c>
       <c r="D2">
-        <v>-4.7799999999999994</v>
+        <v>-5.1599999999999993</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="11">
         <f>IFERROR((F2/E2)*100,0)</f>
@@ -2903,23 +2903,23 @@
       </c>
       <c r="J2" s="14">
         <f>IFERROR(C2/E2,0)</f>
-        <v>-11.95</v>
+        <v>-8.6</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(D2/E2,0)</f>
-        <v>-2.3899999999999997</v>
+        <v>-1.7199999999999998</v>
       </c>
       <c r="M2">
         <f t="shared" ref="M2:R2" si="0">C2+T2</f>
-        <v>-23.9</v>
+        <v>-25.799999999999997</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>-4.7799999999999994</v>
+        <v>-5.1599999999999993</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -3004,16 +3004,16 @@
         <v>135</v>
       </c>
       <c r="C4">
-        <v>-20.9</v>
+        <v>-19.899999999999999</v>
       </c>
       <c r="D4">
-        <v>-4.18</v>
+        <v>-3.9799999999999995</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3023,31 +3023,31 @@
       </c>
       <c r="I4" s="11">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J4" s="14">
         <f t="shared" si="2"/>
-        <v>-4.18</v>
+        <v>-3.3166666666666664</v>
       </c>
       <c r="K4" s="14">
         <f t="shared" si="3"/>
-        <v>-0.83599999999999997</v>
+        <v>-0.66333333333333322</v>
       </c>
       <c r="M4">
         <f t="shared" si="4"/>
-        <v>-20.9</v>
+        <v>-19.899999999999999</v>
       </c>
       <c r="N4">
         <f t="shared" si="5"/>
-        <v>-4.18</v>
+        <v>-3.9799999999999995</v>
       </c>
       <c r="O4">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4">
         <f t="shared" si="8"/>
@@ -3128,46 +3128,46 @@
         <v>134</v>
       </c>
       <c r="C6">
-        <v>-1.9</v>
+        <v>-2.9</v>
       </c>
       <c r="D6">
-        <v>-0.38</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>2</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
       <c r="I6" s="11">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J6" s="14">
         <f t="shared" si="2"/>
-        <v>-0.95</v>
+        <v>-0.96666666666666667</v>
       </c>
       <c r="K6" s="14">
         <f t="shared" si="3"/>
-        <v>-0.19</v>
+        <v>-0.19333333333333336</v>
       </c>
       <c r="M6">
         <f t="shared" si="4"/>
-        <v>-1.9</v>
+        <v>-2.9</v>
       </c>
       <c r="N6">
         <f t="shared" si="5"/>
-        <v>-0.38</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="O6">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6">
         <f t="shared" si="7"/>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="R6">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -3438,16 +3438,16 @@
         <v>72</v>
       </c>
       <c r="C11">
-        <v>19.2</v>
+        <v>26.799999999999997</v>
       </c>
       <c r="D11">
-        <v>3.8400000000000003</v>
+        <v>5.36</v>
       </c>
       <c r="E11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3457,31 +3457,31 @@
       </c>
       <c r="I11" s="11">
         <f t="shared" si="1"/>
-        <v>54.54545454545454</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="J11" s="14">
         <f t="shared" si="2"/>
-        <v>1.7454545454545454</v>
+        <v>2.2333333333333329</v>
       </c>
       <c r="K11" s="14">
         <f t="shared" si="3"/>
-        <v>0.34909090909090912</v>
+        <v>0.44666666666666671</v>
       </c>
       <c r="M11">
         <f t="shared" si="4"/>
-        <v>19.2</v>
+        <v>26.799999999999997</v>
       </c>
       <c r="N11">
         <f t="shared" si="5"/>
-        <v>3.8400000000000003</v>
+        <v>5.36</v>
       </c>
       <c r="O11">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P11">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <f t="shared" si="8"/>
@@ -3630,28 +3630,28 @@
         <v>4.8800000000000008</v>
       </c>
       <c r="E14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>6</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>5</v>
-      </c>
       <c r="I14" s="11">
         <f t="shared" si="1"/>
-        <v>54.54545454545454</v>
+        <v>53.846153846153847</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="2"/>
-        <v>2.2181818181818183</v>
+        <v>1.8769230769230769</v>
       </c>
       <c r="K14" s="14">
         <f t="shared" si="3"/>
-        <v>0.44363636363636372</v>
+        <v>0.37538461538461543</v>
       </c>
       <c r="M14">
         <f t="shared" si="4"/>
@@ -3663,11 +3663,11 @@
       </c>
       <c r="O14">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P14">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <f t="shared" si="8"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R14">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -3686,16 +3686,16 @@
         <v>67</v>
       </c>
       <c r="C15">
-        <v>15.4</v>
+        <v>20.2</v>
       </c>
       <c r="D15">
-        <v>3.08</v>
+        <v>4.04</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3705,31 +3705,31 @@
       </c>
       <c r="I15" s="11">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>72.727272727272734</v>
       </c>
       <c r="J15" s="14">
         <f t="shared" si="2"/>
-        <v>1.54</v>
+        <v>1.8363636363636362</v>
       </c>
       <c r="K15" s="14">
         <f t="shared" si="3"/>
-        <v>0.308</v>
+        <v>0.36727272727272725</v>
       </c>
       <c r="M15">
         <f t="shared" si="4"/>
-        <v>15.4</v>
+        <v>20.2</v>
       </c>
       <c r="N15">
         <f t="shared" si="5"/>
-        <v>3.08</v>
+        <v>4.04</v>
       </c>
       <c r="O15">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P15">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <f t="shared" si="8"/>
@@ -3996,50 +3996,50 @@
         <v>69</v>
       </c>
       <c r="C20">
-        <v>7.6999999999999984</v>
+        <v>9.0999999999999979</v>
       </c>
       <c r="D20">
-        <v>1.5399999999999996</v>
+        <v>1.8199999999999996</v>
       </c>
       <c r="E20">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I20" s="11">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>48.148148148148145</v>
       </c>
       <c r="J20" s="14">
         <f t="shared" si="2"/>
-        <v>0.30799999999999994</v>
+        <v>0.33703703703703697</v>
       </c>
       <c r="K20" s="14">
         <f t="shared" si="3"/>
-        <v>6.1599999999999981E-2</v>
+        <v>6.7407407407407388E-2</v>
       </c>
       <c r="M20">
         <f t="shared" si="4"/>
-        <v>7.6999999999999984</v>
+        <v>9.0999999999999979</v>
       </c>
       <c r="N20">
         <f t="shared" si="10"/>
-        <v>1.5399999999999996</v>
+        <v>1.8199999999999996</v>
       </c>
       <c r="O20">
         <f t="shared" si="11"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P20">
         <f t="shared" si="12"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q20">
         <f t="shared" si="13"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="R20">
         <f t="shared" si="14"/>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -4430,16 +4430,16 @@
         <v>70</v>
       </c>
       <c r="C27">
-        <v>31.4</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="D27">
-        <v>6.2800000000000011</v>
+        <v>7.8600000000000012</v>
       </c>
       <c r="E27">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F27">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -4449,31 +4449,31 @@
       </c>
       <c r="I27" s="11">
         <f t="shared" si="1"/>
-        <v>57.894736842105267</v>
+        <v>63.636363636363633</v>
       </c>
       <c r="J27" s="14">
         <f t="shared" si="2"/>
-        <v>1.6526315789473685</v>
+        <v>1.7863636363636362</v>
       </c>
       <c r="K27" s="14">
         <f t="shared" si="3"/>
-        <v>0.33052631578947372</v>
+        <v>0.35727272727272735</v>
       </c>
       <c r="M27">
         <f t="shared" si="4"/>
-        <v>31.4</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="N27">
         <f t="shared" si="10"/>
-        <v>6.2800000000000011</v>
+        <v>7.8600000000000012</v>
       </c>
       <c r="O27">
         <f t="shared" si="11"/>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P27">
         <f t="shared" si="12"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q27">
         <f t="shared" si="13"/>
@@ -4616,46 +4616,46 @@
         <v>128</v>
       </c>
       <c r="C30">
-        <v>-3.5</v>
+        <v>-5.8</v>
       </c>
       <c r="D30">
-        <v>-0.7</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
         <v>2</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
       <c r="I30" s="11">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J30" s="14">
         <f t="shared" si="2"/>
-        <v>-1.75</v>
+        <v>-1.9333333333333333</v>
       </c>
       <c r="K30" s="14">
         <f t="shared" si="3"/>
-        <v>-0.35</v>
+        <v>-0.38666666666666666</v>
       </c>
       <c r="M30">
         <f t="shared" si="4"/>
-        <v>-3.5</v>
+        <v>-5.8</v>
       </c>
       <c r="N30">
         <f t="shared" si="10"/>
-        <v>-0.7</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="O30">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P30">
         <f t="shared" si="12"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="R30">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -4740,16 +4740,16 @@
         <v>124</v>
       </c>
       <c r="C32">
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="D32">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4763,27 +4763,27 @@
       </c>
       <c r="J32" s="14">
         <f t="shared" si="2"/>
-        <v>0.55000000000000004</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="K32" s="14">
         <f t="shared" si="3"/>
-        <v>0.11</v>
+        <v>8.666666666666667E-2</v>
       </c>
       <c r="M32">
         <f t="shared" si="4"/>
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="N32">
         <f t="shared" si="10"/>
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="O32">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P32">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32">
         <f t="shared" si="13"/>
@@ -4802,17 +4802,17 @@
         <v>127</v>
       </c>
       <c r="C33">
-        <v>-1.1999999999999993</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="D33">
-        <v>-0.24</v>
+        <v>0.91999999999999993</v>
       </c>
       <c r="E33">
+        <v>3</v>
+      </c>
+      <c r="F33">
         <v>2</v>
       </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
       <c r="G33">
         <v>0</v>
       </c>
@@ -4821,31 +4821,31 @@
       </c>
       <c r="I33" s="11">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J33" s="14">
         <f t="shared" si="2"/>
-        <v>-0.59999999999999964</v>
+        <v>1.5333333333333334</v>
       </c>
       <c r="K33" s="14">
         <f t="shared" si="3"/>
-        <v>-0.12</v>
+        <v>0.30666666666666664</v>
       </c>
       <c r="M33">
         <f t="shared" si="4"/>
-        <v>-1.1999999999999993</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="N33">
         <f t="shared" si="10"/>
-        <v>-0.24</v>
+        <v>0.91999999999999993</v>
       </c>
       <c r="O33">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P33">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q33">
         <f t="shared" si="13"/>
@@ -4926,17 +4926,17 @@
         <v>131</v>
       </c>
       <c r="C35">
-        <v>-0.40000000000000036</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="D35">
-        <v>-8.0000000000000071E-2</v>
+        <v>0.41999999999999993</v>
       </c>
       <c r="E35">
+        <v>3</v>
+      </c>
+      <c r="F35">
         <v>2</v>
       </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
       <c r="G35">
         <v>0</v>
       </c>
@@ -4945,31 +4945,31 @@
       </c>
       <c r="I35" s="11">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J35" s="14">
         <f t="shared" si="2"/>
-        <v>-0.20000000000000018</v>
+        <v>0.69999999999999984</v>
       </c>
       <c r="K35" s="14">
         <f t="shared" si="3"/>
-        <v>-4.0000000000000036E-2</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="M35">
         <f t="shared" si="4"/>
-        <v>-0.40000000000000036</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="N35">
         <f t="shared" si="10"/>
-        <v>-8.0000000000000071E-2</v>
+        <v>0.41999999999999993</v>
       </c>
       <c r="O35">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P35">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q35">
         <f t="shared" si="13"/>
@@ -5856,16 +5856,16 @@
         <v>108</v>
       </c>
       <c r="C50">
-        <v>-3</v>
+        <v>-1.7</v>
       </c>
       <c r="D50">
-        <v>-0.6</v>
+        <v>-0.33999999999999997</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5875,31 +5875,31 @@
       </c>
       <c r="I50" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J50" s="14">
         <f t="shared" si="2"/>
-        <v>-3</v>
+        <v>-0.85</v>
       </c>
       <c r="K50" s="14">
         <f t="shared" si="3"/>
-        <v>-0.6</v>
+        <v>-0.16999999999999998</v>
       </c>
       <c r="M50">
         <f t="shared" si="4"/>
-        <v>-3</v>
+        <v>-1.7</v>
       </c>
       <c r="N50">
         <f t="shared" si="10"/>
-        <v>-0.6</v>
+        <v>-0.33999999999999997</v>
       </c>
       <c r="O50">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P50">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50">
         <f t="shared" ref="Q50:Q67" si="15">G50+X50</f>
@@ -6042,46 +6042,46 @@
         <v>78</v>
       </c>
       <c r="C53">
-        <v>-2.8999999999999995</v>
+        <v>-3.1999999999999993</v>
       </c>
       <c r="D53">
-        <v>-0.57999999999999996</v>
+        <v>-0.6399999999999999</v>
       </c>
       <c r="E53">
+        <v>3</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
         <v>2</v>
       </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
-        <v>1</v>
-      </c>
       <c r="I53" s="11">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J53" s="14">
         <f t="shared" si="2"/>
-        <v>-1.4499999999999997</v>
+        <v>-1.0666666666666664</v>
       </c>
       <c r="K53" s="14">
         <f t="shared" si="3"/>
-        <v>-0.28999999999999998</v>
+        <v>-0.21333333333333329</v>
       </c>
       <c r="M53">
         <f t="shared" si="4"/>
-        <v>-2.8999999999999995</v>
+        <v>-3.1999999999999993</v>
       </c>
       <c r="N53">
         <f t="shared" si="10"/>
-        <v>-0.57999999999999996</v>
+        <v>-0.6399999999999999</v>
       </c>
       <c r="O53">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P53">
         <f t="shared" si="12"/>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="R53">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
@@ -6662,16 +6662,16 @@
         <v>62</v>
       </c>
       <c r="C63">
-        <v>-14.3</v>
+        <v>-10.8</v>
       </c>
       <c r="D63">
-        <v>-2.86</v>
+        <v>-2.1599999999999997</v>
       </c>
       <c r="E63">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F63">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6681,31 +6681,31 @@
       </c>
       <c r="I63" s="11">
         <f t="shared" si="1"/>
-        <v>46.666666666666664</v>
+        <v>50</v>
       </c>
       <c r="J63" s="14">
         <f t="shared" si="2"/>
-        <v>-0.95333333333333337</v>
+        <v>-0.67500000000000004</v>
       </c>
       <c r="K63" s="14">
         <f t="shared" si="3"/>
-        <v>-0.19066666666666665</v>
+        <v>-0.13499999999999998</v>
       </c>
       <c r="M63">
         <f t="shared" si="4"/>
-        <v>-14.3</v>
+        <v>-10.8</v>
       </c>
       <c r="N63">
         <f t="shared" si="10"/>
-        <v>-2.86</v>
+        <v>-2.1599999999999997</v>
       </c>
       <c r="O63">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P63">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q63">
         <f t="shared" si="15"/>
@@ -6724,50 +6724,50 @@
         <v>61</v>
       </c>
       <c r="C64">
-        <v>32.6</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="D64">
-        <v>6.5200000000000005</v>
+        <v>7.04</v>
       </c>
       <c r="E64">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G64">
         <v>0</v>
       </c>
       <c r="H64">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I64" s="11">
         <f t="shared" si="1"/>
-        <v>70.833333333333343</v>
+        <v>69.230769230769226</v>
       </c>
       <c r="J64" s="14">
         <f t="shared" si="2"/>
-        <v>1.3583333333333334</v>
+        <v>1.3538461538461539</v>
       </c>
       <c r="K64" s="14">
         <f t="shared" si="3"/>
-        <v>0.27166666666666667</v>
+        <v>0.27076923076923076</v>
       </c>
       <c r="M64">
         <f t="shared" si="4"/>
-        <v>32.6</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="N64">
         <f t="shared" si="10"/>
-        <v>6.5200000000000005</v>
+        <v>7.04</v>
       </c>
       <c r="O64">
         <f t="shared" si="11"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P64">
         <f t="shared" si="12"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q64">
         <f t="shared" si="15"/>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="R64">
         <f t="shared" si="16"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -7221,7 +7221,7 @@
     <col min="8" max="28" width="6.28515625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>140</v>
       </c>
@@ -7229,7 +7229,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="B2" t="s">
         <v>136</v>
@@ -7253,21 +7253,21 @@
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>132</v>
       </c>
       <c r="B3">
         <f>SUM(H3:AB3)</f>
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <f>(B3/$C$1)*100</f>
-        <v>-4.3999999999999995</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f>COUNTA(H3:AB3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <f>COUNTIF(H3:AB3, "&gt;0")</f>
@@ -7279,13 +7279,10 @@
       </c>
       <c r="G3">
         <f>COUNTIF(H3:AB3, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H3" s="15">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -7314,21 +7311,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>135</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>-18.2</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <f t="shared" si="1"/>
-        <v>-3.64</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <f t="shared" si="3"/>
@@ -7340,16 +7337,10 @@
       </c>
       <c r="G5">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="H5" s="15">
-        <v>-4.2</v>
-      </c>
-      <c r="I5" s="15">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>133</v>
       </c>
@@ -7378,25 +7369,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>134</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <f t="shared" si="1"/>
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <f t="shared" si="4"/>
@@ -7406,11 +7397,8 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H7" s="15">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>74</v>
       </c>
@@ -7439,7 +7427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>99</v>
       </c>
@@ -7468,7 +7456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>101</v>
       </c>
@@ -7497,7 +7485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>77</v>
       </c>
@@ -7526,25 +7514,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>72</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
-        <v>-10.900000000000002</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-2.1800000000000002</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <f t="shared" si="4"/>
@@ -7552,19 +7540,10 @@
       </c>
       <c r="G12">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="H12" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="I12" s="15">
-        <v>-9.3000000000000007</v>
-      </c>
-      <c r="J12" s="15">
-        <v>-2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>102</v>
       </c>
@@ -7593,7 +7572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -7622,25 +7601,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
-        <v>-12.4</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <f t="shared" si="1"/>
-        <v>-2.48</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <f t="shared" si="4"/>
@@ -7648,34 +7627,28 @@
       </c>
       <c r="G15">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-17.5</v>
-      </c>
-      <c r="I15" s="15">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>67</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
-        <v>4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <f t="shared" si="1"/>
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <f t="shared" si="4"/>
@@ -7685,11 +7658,8 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H16" s="15">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -7718,7 +7688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>95</v>
       </c>
@@ -7747,7 +7717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -7776,7 +7746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -7805,25 +7775,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>69</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <f t="shared" si="4"/>
@@ -7833,14 +7803,8 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H21" s="15">
-        <v>1.3</v>
-      </c>
-      <c r="I21" s="15">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>85</v>
       </c>
@@ -7869,21 +7833,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>121</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
-        <v>-3.1</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <f t="shared" si="1"/>
-        <v>-0.62</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <f t="shared" si="3"/>
@@ -7895,27 +7859,24 @@
       </c>
       <c r="G23">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>66</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
-        <v>-2.4</v>
+        <v>0</v>
       </c>
       <c r="C24">
         <f t="shared" si="1"/>
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <f t="shared" si="3"/>
@@ -7927,13 +7888,10 @@
       </c>
       <c r="G24">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H24" s="15">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>120</v>
       </c>
@@ -7962,7 +7920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>122</v>
       </c>
@@ -7991,7 +7949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>123</v>
       </c>
@@ -8020,25 +7978,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>70</v>
       </c>
       <c r="B28">
         <f t="shared" si="0"/>
-        <v>-5.5</v>
+        <v>0</v>
       </c>
       <c r="C28">
         <f t="shared" si="1"/>
-        <v>-1.0999999999999999</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <f t="shared" si="4"/>
@@ -8046,25 +8004,10 @@
       </c>
       <c r="G28">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="H28" s="15">
-        <v>3.7</v>
-      </c>
-      <c r="I28" s="15">
-        <v>-1.2</v>
-      </c>
-      <c r="J28" s="15">
-        <v>-0.9</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-4</v>
-      </c>
-      <c r="L28" s="15">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>130</v>
       </c>
@@ -8093,7 +8036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -8122,21 +8065,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>128</v>
       </c>
       <c r="B31">
         <f t="shared" si="0"/>
-        <v>-3.8</v>
+        <v>0</v>
       </c>
       <c r="C31">
         <f t="shared" si="1"/>
-        <v>-0.76</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <f t="shared" si="3"/>
@@ -8148,13 +8091,10 @@
       </c>
       <c r="G31">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>126</v>
       </c>
@@ -8183,25 +8123,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>124</v>
       </c>
       <c r="B33">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C33">
         <f t="shared" si="1"/>
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <f t="shared" si="4"/>
@@ -8211,29 +8151,26 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H33" s="15">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>127</v>
       </c>
       <c r="B34">
         <f t="shared" si="0"/>
-        <v>8.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="C34">
         <f t="shared" si="1"/>
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <f t="shared" si="4"/>
@@ -8243,11 +8180,8 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H34" s="15">
-        <v>8.8000000000000007</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>129</v>
       </c>
@@ -8276,21 +8210,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>131</v>
       </c>
       <c r="B36">
         <f t="shared" si="0"/>
-        <v>-2.7</v>
+        <v>0</v>
       </c>
       <c r="C36">
         <f t="shared" si="1"/>
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <f t="shared" si="3"/>
@@ -8302,13 +8236,10 @@
       </c>
       <c r="G36">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H36" s="15">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>117</v>
       </c>
@@ -8337,7 +8268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>98</v>
       </c>
@@ -8366,7 +8297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -8395,7 +8326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -8424,21 +8355,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>87</v>
       </c>
       <c r="B41">
         <f t="shared" si="0"/>
-        <v>-3.1</v>
+        <v>0</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
-        <v>-0.62</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <f t="shared" si="3"/>
@@ -8450,13 +8381,10 @@
       </c>
       <c r="G41">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H41" s="15">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>118</v>
       </c>
@@ -8485,7 +8413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>119</v>
       </c>
@@ -8514,7 +8442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>125</v>
       </c>
@@ -8543,21 +8471,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>79</v>
       </c>
       <c r="B45">
         <f t="shared" si="0"/>
-        <v>-10.5</v>
+        <v>0</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
-        <v>-2.1</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <f t="shared" si="3"/>
@@ -8569,13 +8497,10 @@
       </c>
       <c r="G45">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H45" s="15">
-        <v>-10.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>106</v>
       </c>
@@ -8604,7 +8529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>97</v>
       </c>
@@ -8633,7 +8558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -8662,7 +8587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -8691,7 +8616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -8720,21 +8645,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>108</v>
       </c>
       <c r="B51">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C51">
         <f t="shared" si="1"/>
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <f t="shared" si="3"/>
@@ -8746,13 +8671,10 @@
       </c>
       <c r="G51">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H51" s="15">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>71</v>
       </c>
@@ -8781,7 +8703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -8810,21 +8732,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>78</v>
       </c>
       <c r="B54">
         <f t="shared" si="0"/>
-        <v>-4.5999999999999996</v>
+        <v>0</v>
       </c>
       <c r="C54">
         <f t="shared" si="1"/>
-        <v>-0.91999999999999993</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54">
         <f t="shared" si="3"/>
@@ -8836,13 +8758,10 @@
       </c>
       <c r="G54">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H54" s="15">
-        <v>-4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -8871,25 +8790,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>73</v>
       </c>
       <c r="B56">
         <f t="shared" si="0"/>
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="C56">
         <f t="shared" si="1"/>
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56">
         <f t="shared" si="4"/>
@@ -8899,11 +8818,8 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H56" s="15">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>114</v>
       </c>
@@ -8932,7 +8848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -8961,7 +8877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -8990,7 +8906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -9019,7 +8935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>115</v>
       </c>
@@ -9048,7 +8964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>112</v>
       </c>
@@ -9077,7 +8993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>116</v>
       </c>
@@ -9106,21 +9022,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>62</v>
       </c>
       <c r="B64">
         <f t="shared" si="0"/>
-        <v>-17.100000000000001</v>
+        <v>0</v>
       </c>
       <c r="C64">
         <f t="shared" si="1"/>
-        <v>-3.42</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64">
         <f t="shared" si="3"/>
@@ -9132,31 +9048,28 @@
       </c>
       <c r="G64">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H64" s="15">
-        <v>-17.100000000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>61</v>
       </c>
       <c r="B65">
         <f t="shared" si="0"/>
-        <v>-2.9</v>
+        <v>0</v>
       </c>
       <c r="C65">
         <f t="shared" si="1"/>
-        <v>-0.57999999999999996</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E65">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <f t="shared" si="4"/>
@@ -9164,19 +9077,10 @@
       </c>
       <c r="G65">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="H65" s="15">
-        <v>-7</v>
-      </c>
-      <c r="I65" s="15">
-        <v>4.2</v>
-      </c>
-      <c r="J65" s="15">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>96</v>
       </c>
@@ -9205,21 +9109,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>63</v>
       </c>
       <c r="B67">
         <f t="shared" si="0"/>
-        <v>-10.9</v>
+        <v>0</v>
       </c>
       <c r="C67">
         <f t="shared" si="1"/>
-        <v>-2.1800000000000002</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67">
         <f t="shared" si="3"/>
@@ -9231,13 +9135,10 @@
       </c>
       <c r="G67">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H67" s="15">
-        <v>-10.9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>104</v>
       </c>
@@ -9268,5 +9169,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58760FCF-D965-4304-81F8-230913DD994F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB4D674-76F5-4B03-99B4-CB81B1A17139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
-    <sheet name="История запусков" sheetId="3" r:id="rId2"/>
-    <sheet name="Результаты" sheetId="4" r:id="rId3"/>
-    <sheet name="СумматорСегодня" sheetId="5" r:id="rId4"/>
+    <sheet name="Результаты" sheetId="4" r:id="rId2"/>
+    <sheet name="СумматорСегодня" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="133">
   <si>
     <t>AQUA</t>
   </si>
@@ -204,21 +203,6 @@
     <t>UEG4_FALCON</t>
   </si>
   <si>
-    <t>Отлично</t>
-  </si>
-  <si>
-    <t>Хорошо</t>
-  </si>
-  <si>
-    <t>Нейтрально</t>
-  </si>
-  <si>
-    <t>Плохо</t>
-  </si>
-  <si>
-    <t>Ужасно</t>
-  </si>
-  <si>
     <t>LEG2_DRINKER</t>
   </si>
   <si>
@@ -279,21 +263,6 @@
     <t>SEG3_FORCE</t>
   </si>
   <si>
-    <t>Пойдет</t>
-  </si>
-  <si>
-    <t>Коррекция</t>
-  </si>
-  <si>
-    <t>от 10</t>
-  </si>
-  <si>
-    <t>от 1 до 3</t>
-  </si>
-  <si>
-    <t>от 4 до 9</t>
-  </si>
-  <si>
     <t>PEG13_DWDDCr</t>
   </si>
   <si>
@@ -303,22 +272,13 @@
     <t>PEG4_UNIVERSAL</t>
   </si>
   <si>
-    <t>Сумма</t>
-  </si>
-  <si>
     <t>Кол-во</t>
   </si>
   <si>
-    <t>Среднее</t>
-  </si>
-  <si>
     <t>Прибыль</t>
   </si>
   <si>
     <t>Убыток</t>
-  </si>
-  <si>
-    <t>П%</t>
   </si>
   <si>
     <t>LEG2_HOTS</t>
@@ -481,10 +441,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -499,8 +456,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6A9955"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -534,24 +498,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,7 +544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -608,17 +554,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1127,1672 +1072,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B2F1F35-A707-4D30-9F4E-850918EC1F71}">
-  <dimension ref="B1:V111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="6" max="7" width="12.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="C1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N1" t="s">
-        <v>92</v>
-      </c>
-      <c r="O1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <f t="shared" ref="J2:J25" si="0">C2*10+D2*5+E2-G2-H2*5-I2*10</f>
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <f>SUM(C2:I2)</f>
-        <v>3</v>
-      </c>
-      <c r="L2" s="10">
-        <f>J2/K2</f>
-        <v>2.3333333333333335</v>
-      </c>
-      <c r="M2">
-        <f>SUM(C2:E2)</f>
-        <v>3</v>
-      </c>
-      <c r="N2">
-        <f>SUM(G2:I2)</f>
-        <v>0</v>
-      </c>
-      <c r="O2" s="11">
-        <f>(M2/(M2+N2))*100</f>
-        <v>100</v>
-      </c>
-      <c r="U2" t="s">
-        <v>83</v>
-      </c>
-      <c r="V2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <f t="shared" si="0"/>
-        <v>-5</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K35" si="1">SUM(C3:I3)</f>
-        <v>1</v>
-      </c>
-      <c r="L3" s="10">
-        <f t="shared" ref="L3:L35" si="2">J3/K3</f>
-        <v>-5</v>
-      </c>
-      <c r="M3">
-        <f t="shared" ref="M3:M35" si="3">SUM(C3:E3)</f>
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <f t="shared" ref="N3:N35" si="4">SUM(G3:I3)</f>
-        <v>1</v>
-      </c>
-      <c r="O3" s="11">
-        <f t="shared" ref="O3:O35" si="5">(M3/(M3+N3))*100</f>
-        <v>0</v>
-      </c>
-      <c r="U3" t="s">
-        <v>84</v>
-      </c>
-      <c r="V3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L4" s="10">
-        <f t="shared" si="2"/>
-        <v>5.8</v>
-      </c>
-      <c r="M4">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="N4">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="O4" s="11">
-        <f t="shared" si="5"/>
-        <v>80</v>
-      </c>
-      <c r="U4" t="s">
-        <v>82</v>
-      </c>
-      <c r="V4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="L5" s="10">
-        <f t="shared" si="2"/>
-        <v>-3.3333333333333335</v>
-      </c>
-      <c r="M5">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="O5" s="11">
-        <f t="shared" si="5"/>
-        <v>33.333333333333329</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="L6" s="10">
-        <f t="shared" si="2"/>
-        <v>4.4444444444444446</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="O6" s="11">
-        <f t="shared" si="5"/>
-        <v>85.714285714285708</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L7" s="10">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="O7" s="11">
-        <f t="shared" si="5"/>
-        <v>62.5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="0"/>
-        <v>-14</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L8" s="10">
-        <f t="shared" si="2"/>
-        <v>-1.75</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="O8" s="11">
-        <f t="shared" si="5"/>
-        <v>42.857142857142854</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9">
-        <v>6</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="L9" s="10">
-        <f t="shared" si="2"/>
-        <v>0.38095238095238093</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="O9" s="11">
-        <f t="shared" si="5"/>
-        <v>42.105263157894733</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L10" s="10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="O10" s="11">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>2</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="0"/>
-        <v>-15</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="L11" s="10">
-        <f t="shared" si="2"/>
-        <v>-2.1428571428571428</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="O11" s="11">
-        <f t="shared" si="5"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="E12">
-        <v>3</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="L12" s="10">
-        <f t="shared" si="2"/>
-        <v>6.1428571428571432</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="N12">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="11">
-        <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>3</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="0"/>
-        <v>-27</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="L13" s="10">
-        <f t="shared" si="2"/>
-        <v>-2.4545454545454546</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="O13" s="11">
-        <f t="shared" si="5"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L14" s="10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="O14" s="11">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15">
-        <v>4</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L15" s="10">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="11">
-        <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L16" s="10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="O16" s="11">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L17" s="10">
-        <f t="shared" si="2"/>
-        <v>3.2</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="N17">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="11">
-        <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>2</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="0"/>
-        <v>-11</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="L18" s="10">
-        <f t="shared" si="2"/>
-        <v>-3.6666666666666665</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="O18" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>2</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="0"/>
-        <v>-4</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L19" s="10">
-        <f t="shared" si="2"/>
-        <v>-0.8</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="O19" s="11">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="0"/>
-        <v>-15</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L20" s="10">
-        <f t="shared" si="2"/>
-        <v>-7.5</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="O20" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="0"/>
-        <v>-5</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L21" s="10">
-        <f t="shared" si="2"/>
-        <v>-5</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="O21" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="0"/>
-        <v>-6</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="L22" s="10">
-        <f t="shared" si="2"/>
-        <v>-2</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="O22" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>4</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-      <c r="H23">
-        <v>3</v>
-      </c>
-      <c r="I23">
-        <v>2</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="0"/>
-        <v>-3</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L23" s="10">
-        <f t="shared" si="2"/>
-        <v>-0.2</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="O23" s="11">
-        <f t="shared" si="5"/>
-        <v>53.333333333333336</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <v>8</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>3</v>
-      </c>
-      <c r="H24">
-        <v>2</v>
-      </c>
-      <c r="J24">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="L24" s="10">
-        <f t="shared" si="2"/>
-        <v>1.1111111111111112</v>
-      </c>
-      <c r="M24">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="N24">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="O24" s="11">
-        <f t="shared" si="5"/>
-        <v>70.588235294117652</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>2</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L25" s="10">
-        <f t="shared" si="2"/>
-        <v>2.625</v>
-      </c>
-      <c r="M25">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="N25">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="O25" s="11">
-        <f t="shared" si="5"/>
-        <v>83.333333333333343</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J26">
-        <f t="shared" ref="J26:J35" si="6">C26*10+D26*5+E26-G26-H26*5-I26*10</f>
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J27">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M27">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O27" s="11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M29">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J30">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L30" s="10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O30" s="11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J31">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M31">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O31" s="11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J32">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L32" s="10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M32">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O32" s="11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="33" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="J33">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L33" s="10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O33" s="11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="34" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="J34">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L34" s="10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O34" s="11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="35" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="J35">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L35" s="10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M35">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O35" s="11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="36" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O36" s="11"/>
-    </row>
-    <row r="37" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O37" s="11"/>
-    </row>
-    <row r="38" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O38" s="11"/>
-    </row>
-    <row r="39" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O39" s="11"/>
-    </row>
-    <row r="40" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O40" s="11"/>
-    </row>
-    <row r="41" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O41" s="11"/>
-    </row>
-    <row r="42" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O42" s="11"/>
-    </row>
-    <row r="43" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O43" s="11"/>
-    </row>
-    <row r="44" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O44" s="11"/>
-    </row>
-    <row r="45" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O45" s="11"/>
-    </row>
-    <row r="46" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O46" s="11"/>
-    </row>
-    <row r="47" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O47" s="11"/>
-    </row>
-    <row r="48" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="O48" s="11"/>
-    </row>
-    <row r="49" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O49" s="11"/>
-    </row>
-    <row r="50" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O50" s="11"/>
-    </row>
-    <row r="51" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O51" s="11"/>
-    </row>
-    <row r="52" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O52" s="11"/>
-    </row>
-    <row r="53" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O53" s="11"/>
-    </row>
-    <row r="54" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O54" s="11"/>
-    </row>
-    <row r="55" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O55" s="11"/>
-    </row>
-    <row r="56" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O56" s="11"/>
-    </row>
-    <row r="57" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O57" s="11"/>
-    </row>
-    <row r="58" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O58" s="11"/>
-    </row>
-    <row r="59" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O59" s="11"/>
-    </row>
-    <row r="60" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O60" s="11"/>
-    </row>
-    <row r="61" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O61" s="11"/>
-    </row>
-    <row r="62" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O62" s="11"/>
-    </row>
-    <row r="63" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O63" s="11"/>
-    </row>
-    <row r="64" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O64" s="11"/>
-    </row>
-    <row r="65" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O65" s="11"/>
-    </row>
-    <row r="66" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O66" s="11"/>
-    </row>
-    <row r="67" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O67" s="11"/>
-    </row>
-    <row r="68" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O68" s="11"/>
-    </row>
-    <row r="69" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O69" s="11"/>
-    </row>
-    <row r="70" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O70" s="11"/>
-    </row>
-    <row r="71" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O71" s="11"/>
-    </row>
-    <row r="72" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O72" s="11"/>
-    </row>
-    <row r="73" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O73" s="11"/>
-    </row>
-    <row r="74" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O74" s="11"/>
-    </row>
-    <row r="75" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O75" s="11"/>
-    </row>
-    <row r="76" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O76" s="11"/>
-    </row>
-    <row r="77" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O77" s="11"/>
-    </row>
-    <row r="78" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O78" s="11"/>
-    </row>
-    <row r="79" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O79" s="11"/>
-    </row>
-    <row r="80" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O80" s="11"/>
-    </row>
-    <row r="81" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O81" s="11"/>
-    </row>
-    <row r="82" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O82" s="11"/>
-    </row>
-    <row r="83" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O83" s="11"/>
-    </row>
-    <row r="84" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O84" s="11"/>
-    </row>
-    <row r="85" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O85" s="11"/>
-    </row>
-    <row r="86" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O86" s="11"/>
-    </row>
-    <row r="87" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O87" s="11"/>
-    </row>
-    <row r="88" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O88" s="11"/>
-    </row>
-    <row r="89" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O89" s="11"/>
-    </row>
-    <row r="90" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O90" s="11"/>
-    </row>
-    <row r="91" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O91" s="11"/>
-    </row>
-    <row r="92" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O92" s="11"/>
-    </row>
-    <row r="93" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O93" s="11"/>
-    </row>
-    <row r="94" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O94" s="11"/>
-    </row>
-    <row r="95" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O95" s="11"/>
-    </row>
-    <row r="96" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O96" s="11"/>
-    </row>
-    <row r="97" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O97" s="11"/>
-    </row>
-    <row r="98" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O98" s="11"/>
-    </row>
-    <row r="99" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O99" s="11"/>
-    </row>
-    <row r="100" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O100" s="11"/>
-    </row>
-    <row r="101" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O101" s="11"/>
-    </row>
-    <row r="102" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O102" s="11"/>
-    </row>
-    <row r="103" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O103" s="11"/>
-    </row>
-    <row r="104" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O104" s="11"/>
-    </row>
-    <row r="105" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O105" s="11"/>
-    </row>
-    <row r="106" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O106" s="11"/>
-    </row>
-    <row r="107" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O107" s="11"/>
-    </row>
-    <row r="108" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O108" s="11"/>
-    </row>
-    <row r="109" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O109" s="11"/>
-    </row>
-    <row r="110" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O110" s="11"/>
-    </row>
-    <row r="111" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O111" s="11"/>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:J25">
-    <sortCondition ref="B2:B25"/>
-  </sortState>
-  <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="dataBar" priority="6">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ED4A8701-D9DC-40D7-9041-8B0437552167}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K1048576">
-    <cfRule type="dataBar" priority="5">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{EB2A134E-270B-4C6D-9190-D08FFE1547A3}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D1DED9E8-95D3-492F-AAD6-CB2AEB1A5320}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="dataBar" priority="3">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20F88C69-918B-40C1-841B-A5C1C0EC7E7B}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N1048576">
-    <cfRule type="dataBar" priority="2">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF555A"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B5ED438B-4F7A-4DFB-80CC-570E56939A31}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O1048576">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{EF194CE7-ABEE-4D80-83A4-68A3FD9BBB53}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ED4A8701-D9DC-40D7-9041-8B0437552167}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FFFFB628"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>J1:J1048576</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{EB2A134E-270B-4C6D-9190-D08FFE1547A3}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>K1:K1048576</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D1DED9E8-95D3-492F-AAD6-CB2AEB1A5320}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FFFFB628"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L1:L1048576</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{20F88C69-918B-40C1-841B-A5C1C0EC7E7B}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FFFFB628"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>M1:M1048576</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B5ED438B-4F7A-4DFB-80CC-570E56939A31}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FFFF555A"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>N1:N1048576</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{EF194CE7-ABEE-4D80-83A4-68A3FD9BBB53}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FFFFB628"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>O1:O1048576</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8FFDFC-F0D8-484F-BD9F-73CE26658A10}">
   <dimension ref="A1:Y77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2803,73 +1082,73 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C1" s="3" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
@@ -2877,53 +1156,53 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="C2">
-        <v>-25.799999999999997</v>
+        <v>-24.9</v>
       </c>
       <c r="D2">
-        <v>-5.1599999999999993</v>
+        <v>-4.9799999999999995</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2" s="11">
+        <v>4</v>
+      </c>
+      <c r="I2" s="7">
         <f>IFERROR((F2/E2)*100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="14">
+        <v>20</v>
+      </c>
+      <c r="J2" s="10">
         <f>IFERROR(C2/E2,0)</f>
-        <v>-8.6</v>
-      </c>
-      <c r="K2" s="14">
+        <v>-4.9799999999999995</v>
+      </c>
+      <c r="K2" s="10">
         <f>IFERROR(D2/E2,0)</f>
-        <v>-1.7199999999999998</v>
+        <v>-0.99599999999999989</v>
       </c>
       <c r="M2">
         <f t="shared" ref="M2:R2" si="0">C2+T2</f>
-        <v>-25.799999999999997</v>
+        <v>-24.9</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>-5.1599999999999993</v>
+        <v>-4.9799999999999995</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
@@ -2931,7 +1210,7 @@
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -2939,7 +1218,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -2959,15 +1238,15 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="7">
         <f t="shared" ref="I3:I66" si="1">IFERROR((F3/E3)*100,0)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="10">
         <f t="shared" ref="J3:J66" si="2">IFERROR(C3/E3,0)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="10">
         <f t="shared" ref="K3:K66" si="3">IFERROR(D3/E3,0)</f>
         <v>0</v>
       </c>
@@ -3001,19 +1280,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="C4">
-        <v>-19.899999999999999</v>
+        <v>-8.8999999999999986</v>
       </c>
       <c r="D4">
-        <v>-3.9799999999999995</v>
+        <v>-1.7799999999999998</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3021,33 +1300,33 @@
       <c r="H4">
         <v>4</v>
       </c>
-      <c r="I4" s="11">
-        <f t="shared" si="1"/>
-        <v>33.333333333333329</v>
-      </c>
-      <c r="J4" s="14">
-        <f t="shared" si="2"/>
-        <v>-3.3166666666666664</v>
-      </c>
-      <c r="K4" s="14">
-        <f t="shared" si="3"/>
-        <v>-0.66333333333333322</v>
+      <c r="I4" s="7">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="J4" s="10">
+        <f t="shared" si="2"/>
+        <v>-1.1124999999999998</v>
+      </c>
+      <c r="K4" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.22249999999999998</v>
       </c>
       <c r="M4">
         <f t="shared" si="4"/>
-        <v>-19.899999999999999</v>
+        <v>-8.8999999999999986</v>
       </c>
       <c r="N4">
         <f t="shared" si="5"/>
-        <v>-3.9799999999999995</v>
+        <v>-1.7799999999999998</v>
       </c>
       <c r="O4">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q4">
         <f t="shared" si="8"/>
@@ -3063,7 +1342,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -3083,15 +1362,15 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J5" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="14">
+      <c r="I5" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3125,16 +1404,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C6">
-        <v>-2.9</v>
+        <v>-7.5</v>
       </c>
       <c r="D6">
-        <v>-0.58000000000000007</v>
+        <v>-1.5</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -3143,31 +1422,31 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="1"/>
-        <v>33.333333333333329</v>
-      </c>
-      <c r="J6" s="14">
-        <f t="shared" si="2"/>
-        <v>-0.96666666666666667</v>
-      </c>
-      <c r="K6" s="14">
-        <f t="shared" si="3"/>
-        <v>-0.19333333333333336</v>
+        <v>4</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="J6" s="10">
+        <f t="shared" si="2"/>
+        <v>-1.5</v>
+      </c>
+      <c r="K6" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.3</v>
       </c>
       <c r="M6">
         <f t="shared" si="4"/>
-        <v>-2.9</v>
+        <v>-7.5</v>
       </c>
       <c r="N6">
         <f t="shared" si="5"/>
-        <v>-0.58000000000000007</v>
+        <v>-1.5</v>
       </c>
       <c r="O6">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <f t="shared" si="7"/>
@@ -3179,7 +1458,7 @@
       </c>
       <c r="R6">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -3187,7 +1466,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -3207,15 +1486,15 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="7">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="10">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="10">
         <f t="shared" si="3"/>
         <v>0.39999999999999997</v>
       </c>
@@ -3249,7 +1528,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -3269,15 +1548,15 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="14">
+      <c r="I8" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3311,7 +1590,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -3331,15 +1610,15 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="14">
+      <c r="I9" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3373,7 +1652,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C10">
         <v>-6</v>
@@ -3393,15 +1672,15 @@
       <c r="H10">
         <v>1</v>
       </c>
-      <c r="I10" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="14">
+      <c r="I10" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="10">
         <f t="shared" si="2"/>
         <v>-6</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="10">
         <f t="shared" si="3"/>
         <v>-1.2</v>
       </c>
@@ -3435,49 +1714,49 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C11">
-        <v>26.799999999999997</v>
+        <v>24.599999999999998</v>
       </c>
       <c r="D11">
-        <v>5.36</v>
+        <v>4.92</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11">
         <v>7</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>5</v>
-      </c>
-      <c r="I11" s="11">
-        <f t="shared" si="1"/>
-        <v>58.333333333333336</v>
-      </c>
-      <c r="J11" s="14">
-        <f t="shared" si="2"/>
-        <v>2.2333333333333329</v>
-      </c>
-      <c r="K11" s="14">
-        <f t="shared" si="3"/>
-        <v>0.44666666666666671</v>
+        <v>6</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="J11" s="10">
+        <f t="shared" si="2"/>
+        <v>1.7571428571428569</v>
+      </c>
+      <c r="K11" s="10">
+        <f t="shared" si="3"/>
+        <v>0.35142857142857142</v>
       </c>
       <c r="M11">
         <f t="shared" si="4"/>
-        <v>26.799999999999997</v>
+        <v>24.599999999999998</v>
       </c>
       <c r="N11">
         <f t="shared" si="5"/>
-        <v>5.36</v>
+        <v>4.92</v>
       </c>
       <c r="O11">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P11">
         <f t="shared" si="7"/>
@@ -3485,11 +1764,11 @@
       </c>
       <c r="Q11">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
@@ -3497,7 +1776,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -3517,15 +1796,15 @@
       <c r="H12">
         <v>0</v>
       </c>
-      <c r="I12" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="14">
+      <c r="I12" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3559,7 +1838,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C13">
         <v>-12</v>
@@ -3579,15 +1858,15 @@
       <c r="H13">
         <v>2</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="7">
         <f t="shared" si="1"/>
         <v>33.333333333333329</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="10">
         <f t="shared" si="2"/>
         <v>-4</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="10">
         <f t="shared" si="3"/>
         <v>-0.79999999999999993</v>
       </c>
@@ -3621,16 +1900,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C14">
-        <v>24.4</v>
+        <v>6.5999999999999988</v>
       </c>
       <c r="D14">
-        <v>4.8800000000000008</v>
+        <v>1.3200000000000007</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F14">
         <v>7</v>
@@ -3639,31 +1918,31 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>6</v>
-      </c>
-      <c r="I14" s="11">
-        <f t="shared" si="1"/>
-        <v>53.846153846153847</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="2"/>
-        <v>1.8769230769230769</v>
-      </c>
-      <c r="K14" s="14">
-        <f t="shared" si="3"/>
-        <v>0.37538461538461543</v>
+        <v>10</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="1"/>
+        <v>41.17647058823529</v>
+      </c>
+      <c r="J14" s="10">
+        <f t="shared" si="2"/>
+        <v>0.38823529411764701</v>
+      </c>
+      <c r="K14" s="10">
+        <f t="shared" si="3"/>
+        <v>7.7647058823529458E-2</v>
       </c>
       <c r="M14">
         <f t="shared" si="4"/>
-        <v>24.4</v>
+        <v>6.5999999999999988</v>
       </c>
       <c r="N14">
         <f t="shared" si="5"/>
-        <v>4.8800000000000008</v>
+        <v>1.3200000000000007</v>
       </c>
       <c r="O14">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P14">
         <f t="shared" si="7"/>
@@ -3675,7 +1954,7 @@
       </c>
       <c r="R14">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -3683,53 +1962,53 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C15">
-        <v>20.2</v>
+        <v>15.7</v>
       </c>
       <c r="D15">
-        <v>4.04</v>
+        <v>3.14</v>
       </c>
       <c r="E15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>3</v>
-      </c>
-      <c r="I15" s="11">
-        <f t="shared" si="1"/>
-        <v>72.727272727272734</v>
-      </c>
-      <c r="J15" s="14">
-        <f t="shared" si="2"/>
-        <v>1.8363636363636362</v>
-      </c>
-      <c r="K15" s="14">
-        <f t="shared" si="3"/>
-        <v>0.36727272727272725</v>
+        <v>4</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="1"/>
+        <v>69.230769230769226</v>
+      </c>
+      <c r="J15" s="10">
+        <f t="shared" si="2"/>
+        <v>1.2076923076923076</v>
+      </c>
+      <c r="K15" s="10">
+        <f t="shared" si="3"/>
+        <v>0.24153846153846154</v>
       </c>
       <c r="M15">
         <f t="shared" si="4"/>
-        <v>20.2</v>
+        <v>15.7</v>
       </c>
       <c r="N15">
         <f t="shared" si="5"/>
-        <v>4.04</v>
+        <v>3.14</v>
       </c>
       <c r="O15">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P15">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <f t="shared" si="8"/>
@@ -3737,7 +2016,7 @@
       </c>
       <c r="R15">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
@@ -3745,7 +2024,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C16">
         <v>-1.8</v>
@@ -3765,15 +2044,15 @@
       <c r="H16">
         <v>2</v>
       </c>
-      <c r="I16" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="14">
+      <c r="I16" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="2"/>
         <v>-0.9</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="10">
         <f t="shared" si="3"/>
         <v>-0.18</v>
       </c>
@@ -3807,7 +2086,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3827,15 +2106,15 @@
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="I17" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="14">
+      <c r="I17" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3869,7 +2148,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C18">
         <v>-11.9</v>
@@ -3889,15 +2168,15 @@
       <c r="H18">
         <v>4</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="7">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="10">
         <f t="shared" si="2"/>
         <v>-1.4875</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="10">
         <f t="shared" si="3"/>
         <v>-0.29750000000000004</v>
       </c>
@@ -3931,7 +2210,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3951,15 +2230,15 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="14">
+      <c r="I19" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3993,53 +2272,53 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C20">
-        <v>9.0999999999999979</v>
+        <v>15.199999999999996</v>
       </c>
       <c r="D20">
-        <v>1.8199999999999996</v>
+        <v>3.0399999999999996</v>
       </c>
       <c r="E20">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F20">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>13</v>
-      </c>
-      <c r="I20" s="11">
-        <f t="shared" si="1"/>
-        <v>48.148148148148145</v>
-      </c>
-      <c r="J20" s="14">
-        <f t="shared" si="2"/>
-        <v>0.33703703703703697</v>
-      </c>
-      <c r="K20" s="14">
-        <f t="shared" si="3"/>
-        <v>6.7407407407407388E-2</v>
+        <v>14</v>
+      </c>
+      <c r="I20" s="7">
+        <f t="shared" si="1"/>
+        <v>51.612903225806448</v>
+      </c>
+      <c r="J20" s="10">
+        <f t="shared" si="2"/>
+        <v>0.49032258064516115</v>
+      </c>
+      <c r="K20" s="10">
+        <f t="shared" si="3"/>
+        <v>9.8064516129032248E-2</v>
       </c>
       <c r="M20">
         <f t="shared" si="4"/>
-        <v>9.0999999999999979</v>
+        <v>15.199999999999996</v>
       </c>
       <c r="N20">
         <f t="shared" si="10"/>
-        <v>1.8199999999999996</v>
+        <v>3.0399999999999996</v>
       </c>
       <c r="O20">
         <f t="shared" si="11"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="P20">
         <f t="shared" si="12"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q20">
         <f t="shared" si="13"/>
@@ -4047,7 +2326,7 @@
       </c>
       <c r="R20">
         <f t="shared" si="14"/>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -4055,7 +2334,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -4075,15 +2354,15 @@
       <c r="H21">
         <v>1</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="7">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="10">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="10">
         <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
@@ -4117,7 +2396,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C22">
         <v>-1.9000000000000001</v>
@@ -4137,15 +2416,15 @@
       <c r="H22">
         <v>1</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="7">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="10">
         <f t="shared" si="2"/>
         <v>-0.95000000000000007</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="10">
         <f t="shared" si="3"/>
         <v>-0.19</v>
       </c>
@@ -4179,7 +2458,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C23">
         <v>3.3000000000000003</v>
@@ -4199,15 +2478,15 @@
       <c r="H23">
         <v>3</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="7">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="10">
         <f t="shared" si="2"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="10">
         <f t="shared" si="3"/>
         <v>0.11000000000000003</v>
       </c>
@@ -4241,7 +2520,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -4261,15 +2540,15 @@
       <c r="H24">
         <v>0</v>
       </c>
-      <c r="I24" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="14">
+      <c r="I24" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4303,7 +2582,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -4323,15 +2602,15 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="I25" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="14">
+      <c r="I25" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4365,7 +2644,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -4385,15 +2664,15 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="14">
+      <c r="I26" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4427,53 +2706,53 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C27">
-        <v>39.299999999999997</v>
+        <v>64.3</v>
       </c>
       <c r="D27">
-        <v>7.8600000000000012</v>
+        <v>12.860000000000003</v>
       </c>
       <c r="E27">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F27">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>8</v>
-      </c>
-      <c r="I27" s="11">
-        <f t="shared" si="1"/>
-        <v>63.636363636363633</v>
-      </c>
-      <c r="J27" s="14">
-        <f t="shared" si="2"/>
-        <v>1.7863636363636362</v>
-      </c>
-      <c r="K27" s="14">
-        <f t="shared" si="3"/>
-        <v>0.35727272727272735</v>
+        <v>10</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" si="1"/>
+        <v>64.285714285714292</v>
+      </c>
+      <c r="J27" s="10">
+        <f t="shared" si="2"/>
+        <v>2.2964285714285713</v>
+      </c>
+      <c r="K27" s="10">
+        <f t="shared" si="3"/>
+        <v>0.45928571428571441</v>
       </c>
       <c r="M27">
         <f t="shared" si="4"/>
-        <v>39.299999999999997</v>
+        <v>64.3</v>
       </c>
       <c r="N27">
         <f t="shared" si="10"/>
-        <v>7.8600000000000012</v>
+        <v>12.860000000000003</v>
       </c>
       <c r="O27">
         <f t="shared" si="11"/>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="P27">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q27">
         <f t="shared" si="13"/>
@@ -4481,7 +2760,7 @@
       </c>
       <c r="R27">
         <f t="shared" si="14"/>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -4489,7 +2768,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C28">
         <v>-1.3</v>
@@ -4509,15 +2788,15 @@
       <c r="H28">
         <v>1</v>
       </c>
-      <c r="I28" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="14">
+      <c r="I28" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="10">
         <f t="shared" si="2"/>
         <v>-1.3</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="10">
         <f t="shared" si="3"/>
         <v>-0.26</v>
       </c>
@@ -4551,7 +2830,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C29">
         <v>-40</v>
@@ -4571,15 +2850,15 @@
       <c r="H29">
         <v>7</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="7">
         <f t="shared" si="1"/>
         <v>27.27272727272727</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="10">
         <f t="shared" si="2"/>
         <v>-3.6363636363636362</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="10">
         <f t="shared" si="3"/>
         <v>-0.72727272727272729</v>
       </c>
@@ -4613,16 +2892,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C30">
-        <v>-5.8</v>
+        <v>-9.1</v>
       </c>
       <c r="D30">
-        <v>-1.1599999999999999</v>
+        <v>-1.82</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -4631,31 +2910,31 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>2</v>
-      </c>
-      <c r="I30" s="11">
-        <f t="shared" si="1"/>
-        <v>33.333333333333329</v>
-      </c>
-      <c r="J30" s="14">
-        <f t="shared" si="2"/>
-        <v>-1.9333333333333333</v>
-      </c>
-      <c r="K30" s="14">
-        <f t="shared" si="3"/>
-        <v>-0.38666666666666666</v>
+        <v>4</v>
+      </c>
+      <c r="I30" s="7">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="J30" s="10">
+        <f t="shared" si="2"/>
+        <v>-1.8199999999999998</v>
+      </c>
+      <c r="K30" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.36399999999999999</v>
       </c>
       <c r="M30">
         <f t="shared" si="4"/>
-        <v>-5.8</v>
+        <v>-9.1</v>
       </c>
       <c r="N30">
         <f t="shared" si="10"/>
-        <v>-1.1599999999999999</v>
+        <v>-1.82</v>
       </c>
       <c r="O30">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P30">
         <f t="shared" si="12"/>
@@ -4667,7 +2946,7 @@
       </c>
       <c r="R30">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -4675,7 +2954,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -4695,15 +2974,15 @@
       <c r="H31">
         <v>0</v>
       </c>
-      <c r="I31" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="14">
+      <c r="I31" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4737,49 +3016,49 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C32">
-        <v>1.3</v>
+        <v>-6.2</v>
       </c>
       <c r="D32">
-        <v>0.26</v>
+        <v>-1.24</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F32">
         <v>3</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32" s="11">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="J32" s="14">
-        <f t="shared" si="2"/>
-        <v>0.43333333333333335</v>
-      </c>
-      <c r="K32" s="14">
-        <f t="shared" si="3"/>
-        <v>8.666666666666667E-2</v>
+        <v>1</v>
+      </c>
+      <c r="I32" s="7">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="J32" s="10">
+        <f t="shared" si="2"/>
+        <v>-1.24</v>
+      </c>
+      <c r="K32" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.248</v>
       </c>
       <c r="M32">
         <f t="shared" si="4"/>
-        <v>1.3</v>
+        <v>-6.2</v>
       </c>
       <c r="N32">
         <f t="shared" si="10"/>
-        <v>0.26</v>
+        <v>-1.24</v>
       </c>
       <c r="O32">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P32">
         <f t="shared" si="12"/>
@@ -4787,11 +3066,11 @@
       </c>
       <c r="Q32">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -4799,53 +3078,53 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C33">
-        <v>4.6000000000000005</v>
+        <v>-1.3000000000000007</v>
       </c>
       <c r="D33">
-        <v>0.91999999999999993</v>
+        <v>-0.26000000000000023</v>
       </c>
       <c r="E33">
+        <v>5</v>
+      </c>
+      <c r="F33">
         <v>3</v>
       </c>
-      <c r="F33">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>2</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33" s="11">
-        <f t="shared" si="1"/>
-        <v>66.666666666666657</v>
-      </c>
-      <c r="J33" s="14">
-        <f t="shared" si="2"/>
-        <v>1.5333333333333334</v>
-      </c>
-      <c r="K33" s="14">
-        <f t="shared" si="3"/>
-        <v>0.30666666666666664</v>
+      <c r="I33" s="7">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="J33" s="10">
+        <f t="shared" si="2"/>
+        <v>-0.26000000000000012</v>
+      </c>
+      <c r="K33" s="10">
+        <f t="shared" si="3"/>
+        <v>-5.2000000000000046E-2</v>
       </c>
       <c r="M33">
         <f t="shared" si="4"/>
-        <v>4.6000000000000005</v>
+        <v>-1.3000000000000007</v>
       </c>
       <c r="N33">
         <f t="shared" si="10"/>
-        <v>0.91999999999999993</v>
+        <v>-0.26000000000000023</v>
       </c>
       <c r="O33">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33">
         <f t="shared" si="13"/>
@@ -4853,7 +3132,7 @@
       </c>
       <c r="R33">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -4861,7 +3140,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -4881,15 +3160,15 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="14">
+      <c r="I34" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4923,16 +3202,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C35">
-        <v>2.0999999999999996</v>
+        <v>-3.8000000000000007</v>
       </c>
       <c r="D35">
-        <v>0.41999999999999993</v>
+        <v>-0.76000000000000023</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F35">
         <v>2</v>
@@ -4941,31 +3220,31 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="I35" s="11">
-        <f t="shared" si="1"/>
-        <v>66.666666666666657</v>
-      </c>
-      <c r="J35" s="14">
-        <f t="shared" si="2"/>
-        <v>0.69999999999999984</v>
-      </c>
-      <c r="K35" s="14">
-        <f t="shared" si="3"/>
-        <v>0.13999999999999999</v>
+        <v>3</v>
+      </c>
+      <c r="I35" s="7">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="J35" s="10">
+        <f t="shared" si="2"/>
+        <v>-0.76000000000000012</v>
+      </c>
+      <c r="K35" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.15200000000000005</v>
       </c>
       <c r="M35">
         <f t="shared" si="4"/>
-        <v>2.0999999999999996</v>
+        <v>-3.8000000000000007</v>
       </c>
       <c r="N35">
         <f t="shared" si="10"/>
-        <v>0.41999999999999993</v>
+        <v>-0.76000000000000023</v>
       </c>
       <c r="O35">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P35">
         <f t="shared" si="12"/>
@@ -4977,7 +3256,7 @@
       </c>
       <c r="R35">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -4985,7 +3264,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -5005,15 +3284,15 @@
       <c r="H36">
         <v>0</v>
       </c>
-      <c r="I36" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J36" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K36" s="14">
+      <c r="I36" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5047,7 +3326,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -5067,15 +3346,15 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K37" s="14">
+      <c r="I37" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5109,7 +3388,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -5129,15 +3408,15 @@
       <c r="H38">
         <v>1</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="7">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="J38" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K38" s="14">
+      <c r="J38" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5171,7 +3450,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>6</v>
@@ -5191,15 +3470,15 @@
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39" s="7">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="J39" s="14">
+      <c r="J39" s="10">
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="10">
         <f t="shared" si="3"/>
         <v>0.3</v>
       </c>
@@ -5233,7 +3512,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C40">
         <v>-6.5</v>
@@ -5253,15 +3532,15 @@
       <c r="H40">
         <v>3</v>
       </c>
-      <c r="I40" s="11">
+      <c r="I40" s="7">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="J40" s="14">
+      <c r="J40" s="10">
         <f t="shared" si="2"/>
         <v>-1.625</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="10">
         <f t="shared" si="3"/>
         <v>-0.32499999999999996</v>
       </c>
@@ -5295,7 +3574,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -5315,15 +3594,15 @@
       <c r="H41">
         <v>0</v>
       </c>
-      <c r="I41" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K41" s="14">
+      <c r="I41" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5357,7 +3636,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -5377,15 +3656,15 @@
       <c r="H42">
         <v>0</v>
       </c>
-      <c r="I42" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K42" s="14">
+      <c r="I42" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5419,7 +3698,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -5439,15 +3718,15 @@
       <c r="H43">
         <v>0</v>
       </c>
-      <c r="I43" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K43" s="14">
+      <c r="I43" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5481,7 +3760,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C44">
         <v>1.9000000000000004</v>
@@ -5501,15 +3780,15 @@
       <c r="H44">
         <v>2</v>
       </c>
-      <c r="I44" s="11">
+      <c r="I44" s="7">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="J44" s="14">
+      <c r="J44" s="10">
         <f t="shared" si="2"/>
         <v>0.38000000000000006</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="10">
         <f t="shared" si="3"/>
         <v>7.5999999999999984E-2</v>
       </c>
@@ -5543,7 +3822,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -5563,15 +3842,15 @@
       <c r="H45">
         <v>0</v>
       </c>
-      <c r="I45" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J45" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K45" s="14">
+      <c r="I45" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5605,7 +3884,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -5625,15 +3904,15 @@
       <c r="H46">
         <v>0</v>
       </c>
-      <c r="I46" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J46" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="14">
+      <c r="I46" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5667,7 +3946,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -5687,15 +3966,15 @@
       <c r="H47">
         <v>0</v>
       </c>
-      <c r="I47" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J47" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K47" s="14">
+      <c r="I47" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5749,15 +4028,15 @@
       <c r="H48">
         <v>2</v>
       </c>
-      <c r="I48" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J48" s="14">
+      <c r="I48" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="10">
         <f t="shared" si="2"/>
         <v>-6</v>
       </c>
-      <c r="K48" s="14">
+      <c r="K48" s="10">
         <f t="shared" si="3"/>
         <v>-1.2</v>
       </c>
@@ -5791,7 +4070,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C49">
         <v>-2.9000000000000004</v>
@@ -5811,15 +4090,15 @@
       <c r="H49">
         <v>2</v>
       </c>
-      <c r="I49" s="11">
+      <c r="I49" s="7">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="J49" s="14">
+      <c r="J49" s="10">
         <f t="shared" si="2"/>
         <v>-0.58000000000000007</v>
       </c>
-      <c r="K49" s="14">
+      <c r="K49" s="10">
         <f t="shared" si="3"/>
         <v>-0.11600000000000002</v>
       </c>
@@ -5853,16 +4132,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C50">
-        <v>-1.7</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="D50">
-        <v>-0.33999999999999997</v>
+        <v>-0.88</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -5871,31 +4150,31 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50" s="11">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="J50" s="14">
-        <f t="shared" si="2"/>
-        <v>-0.85</v>
-      </c>
-      <c r="K50" s="14">
-        <f t="shared" si="3"/>
-        <v>-0.16999999999999998</v>
+        <v>2</v>
+      </c>
+      <c r="I50" s="7">
+        <f t="shared" si="1"/>
+        <v>33.333333333333329</v>
+      </c>
+      <c r="J50" s="10">
+        <f t="shared" si="2"/>
+        <v>-1.4666666666666668</v>
+      </c>
+      <c r="K50" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.29333333333333333</v>
       </c>
       <c r="M50">
         <f t="shared" si="4"/>
-        <v>-1.7</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="N50">
         <f t="shared" si="10"/>
-        <v>-0.33999999999999997</v>
+        <v>-0.88</v>
       </c>
       <c r="O50">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P50">
         <f t="shared" si="12"/>
@@ -5907,7 +4186,7 @@
       </c>
       <c r="R50">
         <f t="shared" ref="R50:R67" si="16">H50+Y50</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
@@ -5915,7 +4194,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -5935,15 +4214,15 @@
       <c r="H51">
         <v>0</v>
       </c>
-      <c r="I51" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="14">
+      <c r="I51" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5977,7 +4256,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -5997,15 +4276,15 @@
       <c r="H52">
         <v>0</v>
       </c>
-      <c r="I52" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J52" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K52" s="14">
+      <c r="I52" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6039,16 +4318,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C53">
-        <v>-3.1999999999999993</v>
+        <v>-4.2999999999999989</v>
       </c>
       <c r="D53">
-        <v>-0.6399999999999999</v>
+        <v>-0.85999999999999988</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -6057,31 +4336,31 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>2</v>
-      </c>
-      <c r="I53" s="11">
-        <f t="shared" si="1"/>
-        <v>33.333333333333329</v>
-      </c>
-      <c r="J53" s="14">
-        <f t="shared" si="2"/>
-        <v>-1.0666666666666664</v>
-      </c>
-      <c r="K53" s="14">
-        <f t="shared" si="3"/>
-        <v>-0.21333333333333329</v>
+        <v>4</v>
+      </c>
+      <c r="I53" s="7">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="J53" s="10">
+        <f t="shared" si="2"/>
+        <v>-0.85999999999999976</v>
+      </c>
+      <c r="K53" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.17199999999999999</v>
       </c>
       <c r="M53">
         <f t="shared" si="4"/>
-        <v>-3.1999999999999993</v>
+        <v>-4.2999999999999989</v>
       </c>
       <c r="N53">
         <f t="shared" si="10"/>
-        <v>-0.6399999999999999</v>
+        <v>-0.85999999999999988</v>
       </c>
       <c r="O53">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P53">
         <f t="shared" si="12"/>
@@ -6093,7 +4372,7 @@
       </c>
       <c r="R53">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
@@ -6101,7 +4380,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -6121,15 +4400,15 @@
       <c r="H54">
         <v>0</v>
       </c>
-      <c r="I54" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K54" s="14">
+      <c r="I54" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6163,7 +4442,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C55">
         <v>1.6000000000000014</v>
@@ -6183,15 +4462,15 @@
       <c r="H55">
         <v>4</v>
       </c>
-      <c r="I55" s="11">
+      <c r="I55" s="7">
         <f t="shared" si="1"/>
         <v>33.333333333333329</v>
       </c>
-      <c r="J55" s="14">
+      <c r="J55" s="10">
         <f t="shared" si="2"/>
         <v>0.26666666666666689</v>
       </c>
-      <c r="K55" s="14">
+      <c r="K55" s="10">
         <f t="shared" si="3"/>
         <v>5.3333333333333344E-2</v>
       </c>
@@ -6225,19 +4504,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="C56">
-        <v>-1.2</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D56">
-        <v>-0.24</v>
+        <v>0.2</v>
       </c>
       <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="F56">
         <v>1</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -6245,33 +4524,33 @@
       <c r="H56">
         <v>1</v>
       </c>
-      <c r="I56" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="14">
-        <f t="shared" si="2"/>
-        <v>-1.2</v>
-      </c>
-      <c r="K56" s="14">
-        <f t="shared" si="3"/>
-        <v>-0.24</v>
+      <c r="I56" s="7">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="J56" s="10">
+        <f t="shared" si="2"/>
+        <v>0.50000000000000011</v>
+      </c>
+      <c r="K56" s="10">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
       </c>
       <c r="M56">
         <f t="shared" si="4"/>
-        <v>-1.2</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="N56">
         <f t="shared" si="10"/>
-        <v>-0.24</v>
+        <v>0.2</v>
       </c>
       <c r="O56">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P56">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56">
         <f t="shared" si="15"/>
@@ -6287,7 +4566,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -6307,15 +4586,15 @@
       <c r="H57">
         <v>0</v>
       </c>
-      <c r="I57" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="14">
+      <c r="I57" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6349,7 +4628,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -6369,15 +4648,15 @@
       <c r="H58">
         <v>0</v>
       </c>
-      <c r="I58" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="14">
+      <c r="I58" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6411,7 +4690,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -6431,15 +4710,15 @@
       <c r="H59">
         <v>0</v>
       </c>
-      <c r="I59" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K59" s="14">
+      <c r="I59" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6473,7 +4752,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -6493,15 +4772,15 @@
       <c r="H60">
         <v>0</v>
       </c>
-      <c r="I60" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K60" s="14">
+      <c r="I60" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K60" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6535,7 +4814,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -6555,15 +4834,15 @@
       <c r="H61">
         <v>0</v>
       </c>
-      <c r="I61" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K61" s="14">
+      <c r="I61" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K61" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6597,7 +4876,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -6617,15 +4896,15 @@
       <c r="H62">
         <v>0</v>
       </c>
-      <c r="I62" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J62" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K62" s="14">
+      <c r="I62" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6659,53 +4938,53 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C63">
-        <v>-10.8</v>
+        <v>-18.100000000000001</v>
       </c>
       <c r="D63">
-        <v>-2.1599999999999997</v>
+        <v>-3.6199999999999997</v>
       </c>
       <c r="E63">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F63">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63">
-        <v>8</v>
-      </c>
-      <c r="I63" s="11">
+        <v>9</v>
+      </c>
+      <c r="I63" s="7">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="J63" s="14">
-        <f t="shared" si="2"/>
-        <v>-0.67500000000000004</v>
-      </c>
-      <c r="K63" s="14">
-        <f t="shared" si="3"/>
-        <v>-0.13499999999999998</v>
+      <c r="J63" s="10">
+        <f t="shared" si="2"/>
+        <v>-1.0055555555555555</v>
+      </c>
+      <c r="K63" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.2011111111111111</v>
       </c>
       <c r="M63">
         <f t="shared" si="4"/>
-        <v>-10.8</v>
+        <v>-18.100000000000001</v>
       </c>
       <c r="N63">
         <f t="shared" si="10"/>
-        <v>-2.1599999999999997</v>
+        <v>-3.6199999999999997</v>
       </c>
       <c r="O63">
         <f t="shared" si="11"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P63">
         <f t="shared" si="12"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q63">
         <f t="shared" si="15"/>
@@ -6713,7 +4992,7 @@
       </c>
       <c r="R63">
         <f t="shared" si="16"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -6721,16 +5000,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C64">
-        <v>35.200000000000003</v>
+        <v>27</v>
       </c>
       <c r="D64">
-        <v>7.04</v>
+        <v>5.4</v>
       </c>
       <c r="E64">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F64">
         <v>18</v>
@@ -6739,31 +5018,31 @@
         <v>0</v>
       </c>
       <c r="H64">
-        <v>8</v>
-      </c>
-      <c r="I64" s="11">
-        <f t="shared" si="1"/>
-        <v>69.230769230769226</v>
-      </c>
-      <c r="J64" s="14">
-        <f t="shared" si="2"/>
-        <v>1.3538461538461539</v>
-      </c>
-      <c r="K64" s="14">
-        <f t="shared" si="3"/>
-        <v>0.27076923076923076</v>
+        <v>12</v>
+      </c>
+      <c r="I64" s="7">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="J64" s="10">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+      <c r="K64" s="10">
+        <f t="shared" si="3"/>
+        <v>0.18000000000000002</v>
       </c>
       <c r="M64">
         <f t="shared" si="4"/>
-        <v>35.200000000000003</v>
+        <v>27</v>
       </c>
       <c r="N64">
         <f t="shared" si="10"/>
-        <v>7.04</v>
+        <v>5.4</v>
       </c>
       <c r="O64">
         <f t="shared" si="11"/>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="P64">
         <f t="shared" si="12"/>
@@ -6775,7 +5054,7 @@
       </c>
       <c r="R64">
         <f t="shared" si="16"/>
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -6783,7 +5062,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -6803,15 +5082,15 @@
       <c r="H65">
         <v>0</v>
       </c>
-      <c r="I65" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K65" s="14">
+      <c r="I65" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J65" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K65" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6845,7 +5124,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C66">
         <v>17.5</v>
@@ -6865,15 +5144,15 @@
       <c r="H66">
         <v>3</v>
       </c>
-      <c r="I66" s="11">
+      <c r="I66" s="7">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="J66" s="14">
+      <c r="J66" s="10">
         <f t="shared" si="2"/>
         <v>1.75</v>
       </c>
-      <c r="K66" s="14">
+      <c r="K66" s="10">
         <f t="shared" si="3"/>
         <v>0.35</v>
       </c>
@@ -6907,7 +5186,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -6927,15 +5206,15 @@
       <c r="H67">
         <v>0</v>
       </c>
-      <c r="I67" s="11">
+      <c r="I67" s="7">
         <f t="shared" ref="I67" si="17">IFERROR((F67/E67)*100,0)</f>
         <v>0</v>
       </c>
-      <c r="J67" s="14">
+      <c r="J67" s="10">
         <f t="shared" ref="J67" si="18">IFERROR(C67/E67,0)</f>
         <v>0</v>
       </c>
-      <c r="K67" s="14">
+      <c r="K67" s="10">
         <f t="shared" ref="K67" si="19">IFERROR(D67/E67,0)</f>
         <v>0</v>
       </c>
@@ -6965,13 +5244,13 @@
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B75" s="12"/>
+      <c r="B75" s="8"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B76" s="12"/>
+      <c r="B76" s="8"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B77" s="12"/>
+      <c r="B77" s="8"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B106">
@@ -7212,50 +5491,50 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A53AFF8-0615-4AA5-B49F-FDA402810813}">
   <dimension ref="A1:AB68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
-    <col min="8" max="28" width="6.28515625" style="15" customWidth="1"/>
+    <col min="8" max="28" width="6.28515625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C1">
         <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
+      <c r="A2" s="9"/>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>141</v>
+        <v>80</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="B3">
         <f>SUM(H3:AB3)</f>
@@ -7284,7 +5563,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B4">
         <f t="shared" ref="B4:B67" si="0">SUM(H4:AB4)</f>
@@ -7313,7 +5592,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
@@ -7342,7 +5621,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
@@ -7371,7 +5650,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -7400,7 +5679,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
@@ -7429,7 +5708,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -7458,7 +5737,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
@@ -7487,7 +5766,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -7516,7 +5795,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -7542,10 +5821,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="H12" s="12"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -7574,7 +5854,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -7603,7 +5883,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
@@ -7632,7 +5912,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
@@ -7658,10 +5938,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
@@ -7688,9 +5969,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -7717,9 +5998,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
@@ -7746,9 +6027,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
@@ -7775,9 +6056,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
@@ -7804,9 +6085,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B22">
         <f t="shared" si="0"/>
@@ -7833,9 +6114,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
@@ -7862,9 +6143,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
@@ -7891,9 +6172,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B25">
         <f t="shared" si="0"/>
@@ -7920,9 +6201,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B26">
         <f t="shared" si="0"/>
@@ -7949,9 +6230,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B27">
         <f t="shared" si="0"/>
@@ -7978,9 +6259,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B28">
         <f t="shared" si="0"/>
@@ -8006,10 +6287,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I28" s="12"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B29">
         <f t="shared" si="0"/>
@@ -8036,9 +6318,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B30">
         <f t="shared" si="0"/>
@@ -8065,9 +6347,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="B31">
         <f t="shared" si="0"/>
@@ -8094,9 +6376,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B32">
         <f t="shared" si="0"/>
@@ -8125,7 +6407,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="B33">
         <f t="shared" si="0"/>
@@ -8154,7 +6436,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B34">
         <f t="shared" si="0"/>
@@ -8183,7 +6465,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B35">
         <f t="shared" si="0"/>
@@ -8212,7 +6494,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="B36">
         <f t="shared" si="0"/>
@@ -8241,7 +6523,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B37">
         <f t="shared" si="0"/>
@@ -8270,7 +6552,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B38">
         <f t="shared" si="0"/>
@@ -8299,7 +6581,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B39">
         <f t="shared" si="0"/>
@@ -8328,7 +6610,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B40">
         <f t="shared" si="0"/>
@@ -8357,7 +6639,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B41">
         <f t="shared" si="0"/>
@@ -8386,7 +6668,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="B42">
         <f t="shared" si="0"/>
@@ -8415,7 +6697,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="B43">
         <f t="shared" si="0"/>
@@ -8444,7 +6726,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B44">
         <f t="shared" si="0"/>
@@ -8473,7 +6755,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B45">
         <f t="shared" si="0"/>
@@ -8502,7 +6784,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B46">
         <f t="shared" si="0"/>
@@ -8531,7 +6813,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B47">
         <f t="shared" si="0"/>
@@ -8560,7 +6842,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B48">
         <f t="shared" si="0"/>
@@ -8618,7 +6900,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B50">
         <f t="shared" si="0"/>
@@ -8647,7 +6929,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B51">
         <f t="shared" si="0"/>
@@ -8676,7 +6958,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B52">
         <f t="shared" si="0"/>
@@ -8705,7 +6987,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B53">
         <f t="shared" si="0"/>
@@ -8734,7 +7016,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B54">
         <f t="shared" si="0"/>
@@ -8763,7 +7045,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B55">
         <f t="shared" si="0"/>
@@ -8792,7 +7074,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B56">
         <f t="shared" si="0"/>
@@ -8821,7 +7103,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B57">
         <f t="shared" si="0"/>
@@ -8850,7 +7132,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B58">
         <f t="shared" si="0"/>
@@ -8879,7 +7161,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B59">
         <f t="shared" si="0"/>
@@ -8908,7 +7190,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="B60">
         <f t="shared" si="0"/>
@@ -8937,7 +7219,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B61">
         <f t="shared" si="0"/>
@@ -8966,7 +7248,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B62">
         <f t="shared" si="0"/>
@@ -8995,7 +7277,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B63">
         <f t="shared" si="0"/>
@@ -9024,7 +7306,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B64">
         <f t="shared" si="0"/>
@@ -9051,9 +7333,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B65">
         <f t="shared" si="0"/>
@@ -9079,10 +7361,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I65" s="12"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B66">
         <f t="shared" si="0"/>
@@ -9109,9 +7392,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B67">
         <f t="shared" si="0"/>
@@ -9138,9 +7421,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B68">
         <f t="shared" ref="B68" si="6">SUM(H68:AB68)</f>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B731C22F-C3F2-478C-814C-C0C7E9CAC9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE45F690-3B35-4CB0-9986-731FB61E0F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="148">
   <si>
     <t>AQUA</t>
   </si>
@@ -294,9 +294,6 @@
     <t>WEG4_DOG</t>
   </si>
   <si>
-    <t>UEG2_GGD</t>
-  </si>
-  <si>
     <t>PEG20_HOGGER</t>
   </si>
   <si>
@@ -318,12 +315,6 @@
     <t>WEG7_PARADOX</t>
   </si>
   <si>
-    <t>UEG2_GOOSE</t>
-  </si>
-  <si>
-    <t>UEG2_DUCK</t>
-  </si>
-  <si>
     <t>UEG6_DUELDODO</t>
   </si>
   <si>
@@ -490,6 +481,9 @@
   </si>
   <si>
     <t>Сумма по полю Убыток</t>
+  </si>
+  <si>
+    <t>UEG4_CANADIAN</t>
   </si>
 </sst>
 </file>
@@ -644,7 +638,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46285.695046643516" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="66" xr:uid="{1976E921-BE3A-4FF1-A5EF-18E3F04892B4}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:L67" sheet="Результаты"/>
+    <worksheetSource ref="A1:L65" sheet="Результаты"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="Номер" numFmtId="0">
@@ -1696,7 +1690,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5C6C209-71EC-45CD-876E-D40B4E36B838}" name="Сводная таблица1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5C6C209-71EC-45CD-876E-D40B4E36B838}" name="Сводная таблица1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:G10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -2368,30 +2362,30 @@
   <sheetData>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" t="s">
         <v>145</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>146</v>
-      </c>
-      <c r="E3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G3" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B4" s="13">
         <v>-20.100000000000001</v>
@@ -2414,7 +2408,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B5" s="13">
         <v>19.699999999999992</v>
@@ -2437,7 +2431,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B6" s="13">
         <v>1.9000000000000004</v>
@@ -2460,7 +2454,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B7" s="13">
         <v>-21</v>
@@ -2483,7 +2477,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B8" s="13">
         <v>-18.100000000000001</v>
@@ -2506,7 +2500,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B9" s="13">
         <v>44.5</v>
@@ -2529,7 +2523,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B10" s="13">
         <v>6.8999999999999915</v>
@@ -2557,7 +2551,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8FFDFC-F0D8-484F-BD9F-73CE26658A10}">
-  <dimension ref="A1:Z77"/>
+  <dimension ref="A1:Z75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.28515625" customWidth="1"/>
@@ -2566,16 +2560,16 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>78</v>
@@ -2584,31 +2578,31 @@
         <v>79</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>80</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="M1" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>78</v>
@@ -2617,19 +2611,19 @@
         <v>79</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>80</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="W1" s="4" t="s">
         <v>78</v>
@@ -2638,7 +2632,7 @@
         <v>79</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Z1" s="4" t="s">
         <v>80</v>
@@ -2649,7 +2643,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C2">
         <v>-24.9</v>
@@ -2670,15 +2664,15 @@
         <v>4</v>
       </c>
       <c r="I2" s="7">
-        <f>IFERROR((F2/E2)*100,0)</f>
+        <f t="shared" ref="I2:I33" si="0">IFERROR((F2/E2)*100,0)</f>
         <v>20</v>
       </c>
       <c r="J2" s="10">
-        <f>IFERROR(C2/E2,0)</f>
+        <f t="shared" ref="J2:J33" si="1">IFERROR(C2/E2,0)</f>
         <v>-4.9799999999999995</v>
       </c>
       <c r="K2" s="10">
-        <f>IFERROR(D2/E2,0)</f>
+        <f t="shared" ref="K2:K33" si="2">IFERROR(D2/E2,0)</f>
         <v>-0.99599999999999989</v>
       </c>
       <c r="L2" s="10" t="str">
@@ -2686,27 +2680,27 @@
         <v>LEG</v>
       </c>
       <c r="N2">
-        <f>C2+U2</f>
+        <f t="shared" ref="N2:S2" si="3">C2+U2</f>
         <v>-24.9</v>
       </c>
       <c r="O2">
-        <f>D2+V2</f>
+        <f t="shared" si="3"/>
         <v>-4.9799999999999995</v>
       </c>
       <c r="P2">
-        <f>E2+W2</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="Q2">
-        <f>F2+X2</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R2">
-        <f>G2+Y2</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S2">
-        <f>H2+Z2</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -2715,7 +2709,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -2736,43 +2730,43 @@
         <v>0</v>
       </c>
       <c r="I3" s="7">
-        <f>IFERROR((F3/E3)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J3" s="10">
-        <f>IFERROR(C3/E3,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K3" s="10">
-        <f>IFERROR(D3/E3,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="10" t="str">
-        <f t="shared" ref="L3:L66" si="0">LEFT(B3,3)</f>
+        <f t="shared" ref="L3:L64" si="4">LEFT(B3,3)</f>
         <v>LEG</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N66" si="1">C3+U3</f>
+        <f t="shared" ref="N3:N64" si="5">C3+U3</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O17" si="2">D3+V3</f>
+        <f t="shared" ref="O3:O17" si="6">D3+V3</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P17" si="3">E3+W3</f>
+        <f t="shared" ref="P3:P17" si="7">E3+W3</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q17" si="4">F3+X3</f>
+        <f t="shared" ref="Q3:Q17" si="8">F3+X3</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R17" si="5">G3+Y3</f>
+        <f t="shared" ref="R3:R17" si="9">G3+Y3</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S17" si="6">H3+Z3</f>
+        <f t="shared" ref="S3:S17" si="10">H3+Z3</f>
         <v>0</v>
       </c>
     </row>
@@ -2781,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C4">
         <v>-8.8999999999999986</v>
@@ -2802,43 +2796,43 @@
         <v>4</v>
       </c>
       <c r="I4" s="7">
-        <f>IFERROR((F4/E4)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J4" s="10">
-        <f>IFERROR(C4/E4,0)</f>
+        <f t="shared" si="1"/>
         <v>-1.1124999999999998</v>
       </c>
       <c r="K4" s="10">
-        <f>IFERROR(D4/E4,0)</f>
+        <f t="shared" si="2"/>
         <v>-0.22249999999999998</v>
       </c>
       <c r="L4" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-8.8999999999999986</v>
       </c>
       <c r="O4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-1.7799999999999998</v>
       </c>
       <c r="P4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="R4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
     </row>
@@ -2847,7 +2841,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -2868,43 +2862,43 @@
         <v>0</v>
       </c>
       <c r="I5" s="7">
-        <f>IFERROR((F5/E5)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J5" s="10">
-        <f>IFERROR(C5/E5,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K5" s="10">
-        <f>IFERROR(D5/E5,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -2913,7 +2907,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C6">
         <v>-7.5</v>
@@ -2934,43 +2928,43 @@
         <v>4</v>
       </c>
       <c r="I6" s="7">
-        <f>IFERROR((F6/E6)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J6" s="10">
-        <f>IFERROR(C6/E6,0)</f>
+        <f t="shared" si="1"/>
         <v>-1.5</v>
       </c>
       <c r="K6" s="10">
-        <f>IFERROR(D6/E6,0)</f>
+        <f t="shared" si="2"/>
         <v>-0.3</v>
       </c>
       <c r="L6" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-7.5</v>
       </c>
       <c r="O6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-1.5</v>
       </c>
       <c r="P6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
     </row>
@@ -3000,43 +2994,43 @@
         <v>0</v>
       </c>
       <c r="I7" s="7">
-        <f>IFERROR((F7/E7)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="J7" s="10">
-        <f>IFERROR(C7/E7,0)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="K7" s="10">
-        <f>IFERROR(D7/E7,0)</f>
+        <f t="shared" si="2"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="L7" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.2</v>
       </c>
       <c r="P7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="R7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -3045,7 +3039,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -3066,43 +3060,43 @@
         <v>0</v>
       </c>
       <c r="I8" s="7">
-        <f>IFERROR((F8/E8)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J8" s="10">
-        <f>IFERROR(C8/E8,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K8" s="10">
-        <f>IFERROR(D8/E8,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -3111,7 +3105,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -3132,43 +3126,43 @@
         <v>0</v>
       </c>
       <c r="I9" s="7">
-        <f>IFERROR((F9/E9)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J9" s="10">
-        <f>IFERROR(C9/E9,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K9" s="10">
-        <f>IFERROR(D9/E9,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -3198,43 +3192,43 @@
         <v>1</v>
       </c>
       <c r="I10" s="7">
-        <f>IFERROR((F10/E10)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J10" s="10">
-        <f>IFERROR(C10/E10,0)</f>
+        <f t="shared" si="1"/>
         <v>-6</v>
       </c>
       <c r="K10" s="10">
-        <f>IFERROR(D10/E10,0)</f>
+        <f t="shared" si="2"/>
         <v>-1.2</v>
       </c>
       <c r="L10" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-6</v>
       </c>
       <c r="O10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-1.2</v>
       </c>
       <c r="P10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -3264,43 +3258,43 @@
         <v>6</v>
       </c>
       <c r="I11" s="7">
-        <f>IFERROR((F11/E11)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J11" s="10">
-        <f>IFERROR(C11/E11,0)</f>
+        <f t="shared" si="1"/>
         <v>1.7571428571428569</v>
       </c>
       <c r="K11" s="10">
-        <f>IFERROR(D11/E11,0)</f>
+        <f t="shared" si="2"/>
         <v>0.35142857142857142</v>
       </c>
       <c r="L11" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>24.599999999999998</v>
       </c>
       <c r="O11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>4.92</v>
       </c>
       <c r="P11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="R11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="S11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
     </row>
@@ -3309,7 +3303,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -3330,43 +3324,43 @@
         <v>0</v>
       </c>
       <c r="I12" s="7">
-        <f>IFERROR((F12/E12)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J12" s="10">
-        <f>IFERROR(C12/E12,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K12" s="10">
-        <f>IFERROR(D12/E12,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -3396,43 +3390,43 @@
         <v>2</v>
       </c>
       <c r="I13" s="7">
-        <f>IFERROR((F13/E13)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>33.333333333333329</v>
       </c>
       <c r="J13" s="10">
-        <f>IFERROR(C13/E13,0)</f>
+        <f t="shared" si="1"/>
         <v>-4</v>
       </c>
       <c r="K13" s="10">
-        <f>IFERROR(D13/E13,0)</f>
+        <f t="shared" si="2"/>
         <v>-0.79999999999999993</v>
       </c>
       <c r="L13" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-12</v>
       </c>
       <c r="O13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-2.4</v>
       </c>
       <c r="P13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
     </row>
@@ -3462,43 +3456,43 @@
         <v>10</v>
       </c>
       <c r="I14" s="7">
-        <f>IFERROR((F14/E14)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>41.17647058823529</v>
       </c>
       <c r="J14" s="10">
-        <f>IFERROR(C14/E14,0)</f>
+        <f t="shared" si="1"/>
         <v>0.38823529411764701</v>
       </c>
       <c r="K14" s="10">
-        <f>IFERROR(D14/E14,0)</f>
+        <f t="shared" si="2"/>
         <v>7.7647058823529458E-2</v>
       </c>
       <c r="L14" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6.5999999999999988</v>
       </c>
       <c r="O14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.3200000000000007</v>
       </c>
       <c r="P14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="R14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
     </row>
@@ -3528,43 +3522,43 @@
         <v>4</v>
       </c>
       <c r="I15" s="7">
-        <f>IFERROR((F15/E15)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>69.230769230769226</v>
       </c>
       <c r="J15" s="10">
-        <f>IFERROR(C15/E15,0)</f>
+        <f t="shared" si="1"/>
         <v>1.2076923076923076</v>
       </c>
       <c r="K15" s="10">
-        <f>IFERROR(D15/E15,0)</f>
+        <f t="shared" si="2"/>
         <v>0.24153846153846154</v>
       </c>
       <c r="L15" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>15.7</v>
       </c>
       <c r="O15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>3.14</v>
       </c>
       <c r="P15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="R15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
     </row>
@@ -3594,43 +3588,43 @@
         <v>2</v>
       </c>
       <c r="I16" s="7">
-        <f>IFERROR((F16/E16)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J16" s="10">
-        <f>IFERROR(C16/E16,0)</f>
+        <f t="shared" si="1"/>
         <v>-0.9</v>
       </c>
       <c r="K16" s="10">
-        <f>IFERROR(D16/E16,0)</f>
+        <f t="shared" si="2"/>
         <v>-0.18</v>
       </c>
       <c r="L16" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-1.8</v>
       </c>
       <c r="O16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.36</v>
       </c>
       <c r="P16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
     </row>
@@ -3660,43 +3654,43 @@
         <v>0</v>
       </c>
       <c r="I17" s="7">
-        <f>IFERROR((F17/E17)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J17" s="10">
-        <f>IFERROR(C17/E17,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K17" s="10">
-        <f>IFERROR(D17/E17,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -3726,43 +3720,43 @@
         <v>4</v>
       </c>
       <c r="I18" s="7">
-        <f>IFERROR((F18/E18)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J18" s="10">
-        <f>IFERROR(C18/E18,0)</f>
+        <f t="shared" si="1"/>
         <v>-1.4875</v>
       </c>
       <c r="K18" s="10">
-        <f>IFERROR(D18/E18,0)</f>
+        <f t="shared" si="2"/>
         <v>-0.29750000000000004</v>
       </c>
       <c r="L18" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-11.9</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:O67" si="7">D18+V18</f>
+        <f t="shared" ref="O18:O65" si="11">D18+V18</f>
         <v>-2.3800000000000003</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18:P67" si="8">E18+W18</f>
+        <f t="shared" ref="P18:P65" si="12">E18+W18</f>
         <v>8</v>
       </c>
       <c r="Q18">
-        <f t="shared" ref="Q18:Q67" si="9">F18+X18</f>
+        <f t="shared" ref="Q18:Q65" si="13">F18+X18</f>
         <v>4</v>
       </c>
       <c r="R18">
-        <f t="shared" ref="R18:R49" si="10">G18+Y18</f>
+        <f t="shared" ref="R18:R47" si="14">G18+Y18</f>
         <v>0</v>
       </c>
       <c r="S18">
-        <f t="shared" ref="S18:S49" si="11">H18+Z18</f>
+        <f t="shared" ref="S18:S47" si="15">H18+Z18</f>
         <v>4</v>
       </c>
     </row>
@@ -3771,7 +3765,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3792,43 +3786,43 @@
         <v>0</v>
       </c>
       <c r="I19" s="7">
-        <f>IFERROR((F19/E19)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J19" s="10">
-        <f>IFERROR(C19/E19,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K19" s="10">
-        <f>IFERROR(D19/E19,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>LEG</v>
       </c>
       <c r="N19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P19">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -3858,43 +3852,43 @@
         <v>14</v>
       </c>
       <c r="I20" s="7">
-        <f>IFERROR((F20/E20)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>51.612903225806448</v>
       </c>
       <c r="J20" s="10">
-        <f>IFERROR(C20/E20,0)</f>
+        <f t="shared" si="1"/>
         <v>0.49032258064516115</v>
       </c>
       <c r="K20" s="10">
-        <f>IFERROR(D20/E20,0)</f>
+        <f t="shared" si="2"/>
         <v>9.8064516129032248E-2</v>
       </c>
       <c r="L20" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>15.199999999999996</v>
       </c>
       <c r="O20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>3.0399999999999996</v>
       </c>
       <c r="P20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="Q20">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>16</v>
       </c>
       <c r="R20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="S20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
     </row>
@@ -3924,43 +3918,43 @@
         <v>1</v>
       </c>
       <c r="I21" s="7">
-        <f>IFERROR((F21/E21)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J21" s="10">
-        <f>IFERROR(C21/E21,0)</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K21" s="10">
-        <f>IFERROR(D21/E21,0)</f>
+        <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
       <c r="L21" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="P21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -3969,7 +3963,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C22">
         <v>-1.9000000000000001</v>
@@ -3990,43 +3984,43 @@
         <v>1</v>
       </c>
       <c r="I22" s="7">
-        <f>IFERROR((F22/E22)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J22" s="10">
-        <f>IFERROR(C22/E22,0)</f>
+        <f t="shared" si="1"/>
         <v>-0.95000000000000007</v>
       </c>
       <c r="K22" s="10">
-        <f>IFERROR(D22/E22,0)</f>
+        <f t="shared" si="2"/>
         <v>-0.19</v>
       </c>
       <c r="L22" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-1.9000000000000001</v>
       </c>
       <c r="O22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>-0.38</v>
       </c>
       <c r="P22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R22">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -4056,43 +4050,43 @@
         <v>3</v>
       </c>
       <c r="I23" s="7">
-        <f>IFERROR((F23/E23)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J23" s="10">
-        <f>IFERROR(C23/E23,0)</f>
+        <f t="shared" si="1"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="K23" s="10">
-        <f>IFERROR(D23/E23,0)</f>
+        <f t="shared" si="2"/>
         <v>0.11000000000000003</v>
       </c>
       <c r="L23" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.3000000000000003</v>
       </c>
       <c r="O23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.66000000000000014</v>
       </c>
       <c r="P23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>6</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="R23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
     </row>
@@ -4101,7 +4095,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -4122,43 +4116,43 @@
         <v>0</v>
       </c>
       <c r="I24" s="7">
-        <f>IFERROR((F24/E24)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J24" s="10">
-        <f>IFERROR(C24/E24,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K24" s="10">
-        <f>IFERROR(D24/E24,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4167,7 +4161,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -4188,43 +4182,43 @@
         <v>0</v>
       </c>
       <c r="I25" s="7">
-        <f>IFERROR((F25/E25)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J25" s="10">
-        <f>IFERROR(C25/E25,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K25" s="10">
-        <f>IFERROR(D25/E25,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4233,7 +4227,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -4254,43 +4248,43 @@
         <v>0</v>
       </c>
       <c r="I26" s="7">
-        <f>IFERROR((F26/E26)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J26" s="10">
-        <f>IFERROR(C26/E26,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K26" s="10">
-        <f>IFERROR(D26/E26,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4320,43 +4314,43 @@
         <v>10</v>
       </c>
       <c r="I27" s="7">
-        <f>IFERROR((F27/E27)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>64.285714285714292</v>
       </c>
       <c r="J27" s="10">
-        <f>IFERROR(C27/E27,0)</f>
+        <f t="shared" si="1"/>
         <v>2.2964285714285713</v>
       </c>
       <c r="K27" s="10">
-        <f>IFERROR(D27/E27,0)</f>
+        <f t="shared" si="2"/>
         <v>0.45928571428571441</v>
       </c>
       <c r="L27" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>64.3</v>
       </c>
       <c r="O27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>12.860000000000003</v>
       </c>
       <c r="P27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>28</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>18</v>
       </c>
       <c r="R27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S27">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>10</v>
       </c>
     </row>
@@ -4365,7 +4359,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C28">
         <v>-1.3</v>
@@ -4386,43 +4380,43 @@
         <v>1</v>
       </c>
       <c r="I28" s="7">
-        <f>IFERROR((F28/E28)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J28" s="10">
-        <f>IFERROR(C28/E28,0)</f>
+        <f t="shared" si="1"/>
         <v>-1.3</v>
       </c>
       <c r="K28" s="10">
-        <f>IFERROR(D28/E28,0)</f>
+        <f t="shared" si="2"/>
         <v>-0.26</v>
       </c>
       <c r="L28" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-1.3</v>
       </c>
       <c r="O28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>-0.26</v>
       </c>
       <c r="P28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -4452,43 +4446,43 @@
         <v>7</v>
       </c>
       <c r="I29" s="7">
-        <f>IFERROR((F29/E29)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>27.27272727272727</v>
       </c>
       <c r="J29" s="10">
-        <f>IFERROR(C29/E29,0)</f>
+        <f t="shared" si="1"/>
         <v>-3.6363636363636362</v>
       </c>
       <c r="K29" s="10">
-        <f>IFERROR(D29/E29,0)</f>
+        <f t="shared" si="2"/>
         <v>-0.72727272727272729</v>
       </c>
       <c r="L29" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-40</v>
       </c>
       <c r="O29">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>-8</v>
       </c>
       <c r="P29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11</v>
       </c>
       <c r="Q29">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="R29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="S29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
     </row>
@@ -4497,7 +4491,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C30">
         <v>-9.1</v>
@@ -4518,43 +4512,43 @@
         <v>4</v>
       </c>
       <c r="I30" s="7">
-        <f>IFERROR((F30/E30)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J30" s="10">
-        <f>IFERROR(C30/E30,0)</f>
+        <f t="shared" si="1"/>
         <v>-1.8199999999999998</v>
       </c>
       <c r="K30" s="10">
-        <f>IFERROR(D30/E30,0)</f>
+        <f t="shared" si="2"/>
         <v>-0.36399999999999999</v>
       </c>
       <c r="L30" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-9.1</v>
       </c>
       <c r="O30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>-1.82</v>
       </c>
       <c r="P30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S30">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
     </row>
@@ -4563,7 +4557,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -4584,43 +4578,43 @@
         <v>0</v>
       </c>
       <c r="I31" s="7">
-        <f>IFERROR((F31/E31)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J31" s="10">
-        <f>IFERROR(C31/E31,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K31" s="10">
-        <f>IFERROR(D31/E31,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S31">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4629,7 +4623,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C32">
         <v>-6.2</v>
@@ -4650,43 +4644,43 @@
         <v>1</v>
       </c>
       <c r="I32" s="7">
-        <f>IFERROR((F32/E32)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="J32" s="10">
-        <f>IFERROR(C32/E32,0)</f>
+        <f t="shared" si="1"/>
         <v>-1.24</v>
       </c>
       <c r="K32" s="10">
-        <f>IFERROR(D32/E32,0)</f>
+        <f t="shared" si="2"/>
         <v>-0.248</v>
       </c>
       <c r="L32" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-6.2</v>
       </c>
       <c r="O32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>-1.24</v>
       </c>
       <c r="P32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="R32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="S32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -4695,7 +4689,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C33">
         <v>-1.3000000000000007</v>
@@ -4716,43 +4710,43 @@
         <v>2</v>
       </c>
       <c r="I33" s="7">
-        <f>IFERROR((F33/E33)*100,0)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="J33" s="10">
-        <f>IFERROR(C33/E33,0)</f>
+        <f t="shared" si="1"/>
         <v>-0.26000000000000012</v>
       </c>
       <c r="K33" s="10">
-        <f>IFERROR(D33/E33,0)</f>
+        <f t="shared" si="2"/>
         <v>-5.2000000000000046E-2</v>
       </c>
       <c r="L33" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-1.3000000000000007</v>
       </c>
       <c r="O33">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>-0.26000000000000023</v>
       </c>
       <c r="P33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="R33">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S33">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
@@ -4761,7 +4755,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -4782,43 +4776,43 @@
         <v>0</v>
       </c>
       <c r="I34" s="7">
-        <f>IFERROR((F34/E34)*100,0)</f>
+        <f t="shared" ref="I34:I65" si="16">IFERROR((F34/E34)*100,0)</f>
         <v>0</v>
       </c>
       <c r="J34" s="10">
-        <f>IFERROR(C34/E34,0)</f>
+        <f t="shared" ref="J34:J65" si="17">IFERROR(C34/E34,0)</f>
         <v>0</v>
       </c>
       <c r="K34" s="10">
-        <f>IFERROR(D34/E34,0)</f>
+        <f t="shared" ref="K34:K65" si="18">IFERROR(D34/E34,0)</f>
         <v>0</v>
       </c>
       <c r="L34" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R34">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S34">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4827,7 +4821,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C35">
         <v>-3.8000000000000007</v>
@@ -4848,43 +4842,43 @@
         <v>3</v>
       </c>
       <c r="I35" s="7">
-        <f>IFERROR((F35/E35)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>40</v>
       </c>
       <c r="J35" s="10">
-        <f>IFERROR(C35/E35,0)</f>
+        <f t="shared" si="17"/>
         <v>-0.76000000000000012</v>
       </c>
       <c r="K35" s="10">
-        <f>IFERROR(D35/E35,0)</f>
+        <f t="shared" si="18"/>
         <v>-0.15200000000000005</v>
       </c>
       <c r="L35" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-3.8000000000000007</v>
       </c>
       <c r="O35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>-0.76000000000000023</v>
       </c>
       <c r="P35">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="R35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S35">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
     </row>
@@ -4893,7 +4887,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -4914,43 +4908,43 @@
         <v>0</v>
       </c>
       <c r="I36" s="7">
-        <f>IFERROR((F36/E36)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J36" s="10">
-        <f>IFERROR(C36/E36,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K36" s="10">
-        <f>IFERROR(D36/E36,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L36" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4959,7 +4953,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -4980,43 +4974,43 @@
         <v>0</v>
       </c>
       <c r="I37" s="7">
-        <f>IFERROR((F37/E37)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J37" s="10">
-        <f>IFERROR(C37/E37,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K37" s="10">
-        <f>IFERROR(D37/E37,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L37" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5046,43 +5040,43 @@
         <v>1</v>
       </c>
       <c r="I38" s="7">
-        <f>IFERROR((F38/E38)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
       <c r="J38" s="10">
-        <f>IFERROR(C38/E38,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K38" s="10">
-        <f>IFERROR(D38/E38,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L38" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O38">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P38">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S38">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -5112,43 +5106,43 @@
         <v>0</v>
       </c>
       <c r="I39" s="7">
-        <f>IFERROR((F39/E39)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>100</v>
       </c>
       <c r="J39" s="10">
-        <f>IFERROR(C39/E39,0)</f>
+        <f t="shared" si="17"/>
         <v>1.5</v>
       </c>
       <c r="K39" s="10">
-        <f>IFERROR(D39/E39,0)</f>
+        <f t="shared" si="18"/>
         <v>0.3</v>
       </c>
       <c r="L39" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1.2</v>
       </c>
       <c r="P39">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="Q39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="R39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5178,43 +5172,43 @@
         <v>3</v>
       </c>
       <c r="I40" s="7">
-        <f>IFERROR((F40/E40)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>25</v>
       </c>
       <c r="J40" s="10">
-        <f>IFERROR(C40/E40,0)</f>
+        <f t="shared" si="17"/>
         <v>-1.625</v>
       </c>
       <c r="K40" s="10">
-        <f>IFERROR(D40/E40,0)</f>
+        <f t="shared" si="18"/>
         <v>-0.32499999999999996</v>
       </c>
       <c r="L40" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-6.5</v>
       </c>
       <c r="O40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>-1.2999999999999998</v>
       </c>
       <c r="P40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="Q40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
     </row>
@@ -5223,7 +5217,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -5244,43 +5238,43 @@
         <v>0</v>
       </c>
       <c r="I41" s="7">
-        <f>IFERROR((F41/E41)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J41" s="10">
-        <f>IFERROR(C41/E41,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K41" s="10">
-        <f>IFERROR(D41/E41,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L41" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R41">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5289,7 +5283,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -5310,43 +5304,43 @@
         <v>0</v>
       </c>
       <c r="I42" s="7">
-        <f>IFERROR((F42/E42)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J42" s="10">
-        <f>IFERROR(C42/E42,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K42" s="10">
-        <f>IFERROR(D42/E42,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L42" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>PEG</v>
       </c>
       <c r="N42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P42">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q42">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R42">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S42">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5355,7 +5349,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -5376,43 +5370,43 @@
         <v>0</v>
       </c>
       <c r="I43" s="7">
-        <f>IFERROR((F43/E43)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J43" s="10">
-        <f>IFERROR(C43/E43,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K43" s="10">
-        <f>IFERROR(D43/E43,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L43" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>SEG</v>
       </c>
       <c r="N43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S43">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5442,43 +5436,43 @@
         <v>2</v>
       </c>
       <c r="I44" s="7">
-        <f>IFERROR((F44/E44)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>60</v>
       </c>
       <c r="J44" s="10">
-        <f>IFERROR(C44/E44,0)</f>
+        <f t="shared" si="17"/>
         <v>0.38000000000000006</v>
       </c>
       <c r="K44" s="10">
-        <f>IFERROR(D44/E44,0)</f>
+        <f t="shared" si="18"/>
         <v>7.5999999999999984E-2</v>
       </c>
       <c r="L44" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>SEG</v>
       </c>
       <c r="N44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>1.9000000000000004</v>
       </c>
       <c r="O44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.37999999999999989</v>
       </c>
       <c r="P44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="R44">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S44">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
@@ -5487,7 +5481,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -5508,43 +5502,43 @@
         <v>0</v>
       </c>
       <c r="I45" s="7">
-        <f>IFERROR((F45/E45)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J45" s="10">
-        <f>IFERROR(C45/E45,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K45" s="10">
-        <f>IFERROR(D45/E45,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L45" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O45">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P45">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5553,16 +5547,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -5571,47 +5565,47 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46" s="7">
-        <f>IFERROR((F46/E46)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J46" s="10">
-        <f>IFERROR(C46/E46,0)</f>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>-6</v>
       </c>
       <c r="K46" s="10">
-        <f>IFERROR(D46/E46,0)</f>
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>-1.2</v>
       </c>
       <c r="L46" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N46">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>-12</v>
       </c>
       <c r="O46">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>-2.4</v>
       </c>
       <c r="P46">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R46">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S46">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
@@ -5619,65 +5613,65 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47" s="7">
-        <f>IFERROR((F47/E47)*100,0)</f>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>60</v>
       </c>
       <c r="J47" s="10">
-        <f>IFERROR(C47/E47,0)</f>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="K47" s="10">
-        <f>IFERROR(D47/E47,0)</f>
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>-0.11600000000000002</v>
       </c>
       <c r="L47" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N47">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="O47">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="P47">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>5</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>3</v>
       </c>
       <c r="R47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S47">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
@@ -5685,19 +5679,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="C48">
-        <v>-12</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="D48">
-        <v>-2.4</v>
+        <v>-0.88</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5706,43 +5700,43 @@
         <v>2</v>
       </c>
       <c r="I48" s="7">
-        <f>IFERROR((F48/E48)*100,0)</f>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>33.333333333333329</v>
       </c>
       <c r="J48" s="10">
-        <f>IFERROR(C48/E48,0)</f>
-        <v>-6</v>
+        <f t="shared" si="17"/>
+        <v>-1.4666666666666668</v>
       </c>
       <c r="K48" s="10">
-        <f>IFERROR(D48/E48,0)</f>
-        <v>-1.2</v>
+        <f t="shared" si="18"/>
+        <v>-0.29333333333333333</v>
       </c>
       <c r="L48" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N48">
-        <f t="shared" si="1"/>
-        <v>-12</v>
+        <f t="shared" si="5"/>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="O48">
-        <f t="shared" si="7"/>
-        <v>-2.4</v>
+        <f t="shared" si="11"/>
+        <v>-0.88</v>
       </c>
       <c r="P48">
-        <f t="shared" si="8"/>
-        <v>2</v>
+        <f t="shared" si="12"/>
+        <v>3</v>
       </c>
       <c r="Q48">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="R48">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="R48:R65" si="19">G48+Y48</f>
         <v>0</v>
       </c>
       <c r="S48">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="S48:S65" si="20">H48+Z48</f>
         <v>2</v>
       </c>
     </row>
@@ -5751,65 +5745,65 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C49">
-        <v>-2.9000000000000004</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>-0.58000000000000007</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" s="7">
-        <f>IFERROR((F49/E49)*100,0)</f>
-        <v>60</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="J49" s="10">
-        <f>IFERROR(C49/E49,0)</f>
-        <v>-0.58000000000000007</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="K49" s="10">
-        <f>IFERROR(D49/E49,0)</f>
-        <v>-0.11600000000000002</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="L49" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N49">
-        <f t="shared" si="1"/>
-        <v>-2.9000000000000004</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="O49">
-        <f t="shared" si="7"/>
-        <v>-0.58000000000000007</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="P49">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
       <c r="R49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S49">
-        <f t="shared" si="11"/>
-        <v>2</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
@@ -5817,65 +5811,65 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C50">
-        <v>-4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>-0.88</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I50" s="7">
-        <f>IFERROR((F50/E50)*100,0)</f>
-        <v>33.333333333333329</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="J50" s="10">
-        <f>IFERROR(C50/E50,0)</f>
-        <v>-1.4666666666666668</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="K50" s="10">
-        <f>IFERROR(D50/E50,0)</f>
-        <v>-0.29333333333333333</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="L50" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N50">
-        <f t="shared" si="1"/>
-        <v>-4.4000000000000004</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="O50">
-        <f t="shared" si="7"/>
-        <v>-0.88</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="P50">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
       <c r="R50">
-        <f t="shared" ref="R50:R67" si="12">G50+Y50</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S50">
-        <f t="shared" ref="S50:S67" si="13">H50+Z50</f>
-        <v>2</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
@@ -5883,65 +5877,65 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>-4.2999999999999989</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>-0.85999999999999988</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I51" s="7">
-        <f>IFERROR((F51/E51)*100,0)</f>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>20</v>
       </c>
       <c r="J51" s="10">
-        <f>IFERROR(C51/E51,0)</f>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>-0.85999999999999976</v>
       </c>
       <c r="K51" s="10">
-        <f>IFERROR(D51/E51,0)</f>
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>-0.17199999999999999</v>
       </c>
       <c r="L51" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N51">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>-4.2999999999999989</v>
       </c>
       <c r="O51">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>-0.85999999999999988</v>
       </c>
       <c r="P51">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>5</v>
       </c>
       <c r="Q51">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="R51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S51">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
@@ -5949,7 +5943,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -5970,43 +5964,43 @@
         <v>0</v>
       </c>
       <c r="I52" s="7">
-        <f>IFERROR((F52/E52)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J52" s="10">
-        <f>IFERROR(C52/E52,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K52" s="10">
-        <f>IFERROR(D52/E52,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L52" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O52">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P52">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q52">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R52">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S52">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -6015,19 +6009,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C53">
-        <v>-4.2999999999999989</v>
+        <v>1.6000000000000014</v>
       </c>
       <c r="D53">
-        <v>-0.85999999999999988</v>
+        <v>0.32000000000000006</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -6036,43 +6030,43 @@
         <v>4</v>
       </c>
       <c r="I53" s="7">
-        <f>IFERROR((F53/E53)*100,0)</f>
-        <v>20</v>
+        <f t="shared" si="16"/>
+        <v>33.333333333333329</v>
       </c>
       <c r="J53" s="10">
-        <f>IFERROR(C53/E53,0)</f>
-        <v>-0.85999999999999976</v>
+        <f t="shared" si="17"/>
+        <v>0.26666666666666689</v>
       </c>
       <c r="K53" s="10">
-        <f>IFERROR(D53/E53,0)</f>
-        <v>-0.17199999999999999</v>
+        <f t="shared" si="18"/>
+        <v>5.3333333333333344E-2</v>
       </c>
       <c r="L53" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N53">
-        <f t="shared" si="1"/>
-        <v>-4.2999999999999989</v>
+        <f t="shared" si="5"/>
+        <v>1.6000000000000014</v>
       </c>
       <c r="O53">
-        <f t="shared" si="7"/>
-        <v>-0.85999999999999988</v>
+        <f t="shared" si="11"/>
+        <v>0.32000000000000006</v>
       </c>
       <c r="P53">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <f t="shared" si="12"/>
+        <v>6</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <f t="shared" si="13"/>
+        <v>2</v>
       </c>
       <c r="R53">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
     </row>
@@ -6081,65 +6075,65 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" s="7">
-        <f>IFERROR((F54/E54)*100,0)</f>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>50</v>
       </c>
       <c r="J54" s="10">
-        <f>IFERROR(C54/E54,0)</f>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>0.50000000000000011</v>
       </c>
       <c r="K54" s="10">
-        <f>IFERROR(D54/E54,0)</f>
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>0.1</v>
       </c>
       <c r="L54" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N54">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1.0000000000000002</v>
       </c>
       <c r="O54">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>0.2</v>
       </c>
       <c r="P54">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
       <c r="Q54">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="R54">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S54">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
@@ -6147,65 +6141,65 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C55">
-        <v>1.6000000000000014</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>0.32000000000000006</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I55" s="7">
-        <f>IFERROR((F55/E55)*100,0)</f>
-        <v>33.333333333333329</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="J55" s="10">
-        <f>IFERROR(C55/E55,0)</f>
-        <v>0.26666666666666689</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="K55" s="10">
-        <f>IFERROR(D55/E55,0)</f>
-        <v>5.3333333333333344E-2</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="L55" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N55">
-        <f t="shared" si="1"/>
-        <v>1.6000000000000014</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="O55">
-        <f t="shared" si="7"/>
-        <v>0.32000000000000006</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="P55">
-        <f t="shared" si="8"/>
-        <v>6</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="Q55">
-        <f t="shared" si="9"/>
-        <v>2</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
       <c r="R55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S55">
-        <f t="shared" si="13"/>
-        <v>4</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
@@ -6213,65 +6207,65 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C56">
-        <v>1.0000000000000002</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" s="7">
-        <f>IFERROR((F56/E56)*100,0)</f>
-        <v>50</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="J56" s="10">
-        <f>IFERROR(C56/E56,0)</f>
-        <v>0.50000000000000011</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="K56" s="10">
-        <f>IFERROR(D56/E56,0)</f>
-        <v>0.1</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="L56" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N56">
-        <f t="shared" si="1"/>
-        <v>1.0000000000000002</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="O56">
-        <f t="shared" si="7"/>
-        <v>0.2</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="P56">
-        <f t="shared" si="8"/>
-        <v>2</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
       <c r="R56">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S56">
-        <f t="shared" si="13"/>
-        <v>1</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
@@ -6300,43 +6294,43 @@
         <v>0</v>
       </c>
       <c r="I57" s="7">
-        <f>IFERROR((F57/E57)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J57" s="10">
-        <f>IFERROR(C57/E57,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K57" s="10">
-        <f>IFERROR(D57/E57,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L57" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O57">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P57">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q57">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R57">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S57">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -6345,7 +6339,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -6366,43 +6360,43 @@
         <v>0</v>
       </c>
       <c r="I58" s="7">
-        <f>IFERROR((F58/E58)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J58" s="10">
-        <f>IFERROR(C58/E58,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K58" s="10">
-        <f>IFERROR(D58/E58,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L58" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O58">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q58">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R58">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S58">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -6411,7 +6405,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -6432,43 +6426,43 @@
         <v>0</v>
       </c>
       <c r="I59" s="7">
-        <f>IFERROR((F59/E59)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <f>IFERROR(C59/E59,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K59" s="10">
-        <f>IFERROR(D59/E59,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L59" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O59">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q59">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R59">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S59">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -6477,7 +6471,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -6498,43 +6492,43 @@
         <v>0</v>
       </c>
       <c r="I60" s="7">
-        <f>IFERROR((F60/E60)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J60" s="10">
-        <f>IFERROR(C60/E60,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K60" s="10">
-        <f>IFERROR(D60/E60,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L60" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>UEG</v>
       </c>
       <c r="N60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q60">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R60">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S60">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -6543,65 +6537,65 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>-18.100000000000001</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>-3.6199999999999997</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I61" s="7">
-        <f>IFERROR((F61/E61)*100,0)</f>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>50</v>
       </c>
       <c r="J61" s="10">
-        <f>IFERROR(C61/E61,0)</f>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>-1.0055555555555555</v>
       </c>
       <c r="K61" s="10">
-        <f>IFERROR(D61/E61,0)</f>
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>-0.2011111111111111</v>
       </c>
       <c r="L61" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>UEG</v>
+        <f t="shared" si="4"/>
+        <v>VEG</v>
       </c>
       <c r="N61">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>-18.100000000000001</v>
       </c>
       <c r="O61">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>-3.6199999999999997</v>
       </c>
       <c r="P61">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>18</v>
       </c>
       <c r="Q61">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>9</v>
       </c>
       <c r="R61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S61">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
@@ -6609,65 +6603,65 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G62">
         <v>0</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I62" s="7">
-        <f>IFERROR((F62/E62)*100,0)</f>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>60</v>
       </c>
       <c r="J62" s="10">
-        <f>IFERROR(C62/E62,0)</f>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>0.9</v>
       </c>
       <c r="K62" s="10">
-        <f>IFERROR(D62/E62,0)</f>
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>0.18000000000000002</v>
       </c>
       <c r="L62" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>UEG</v>
+        <f t="shared" si="4"/>
+        <v>WEG</v>
       </c>
       <c r="N62">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>27</v>
       </c>
       <c r="O62">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>5.4</v>
       </c>
       <c r="P62">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>30</v>
       </c>
       <c r="Q62">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>18</v>
       </c>
       <c r="R62">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S62">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
@@ -6675,65 +6669,65 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C63">
-        <v>-18.100000000000001</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>-3.6199999999999997</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I63" s="7">
-        <f>IFERROR((F63/E63)*100,0)</f>
-        <v>50</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="J63" s="10">
-        <f>IFERROR(C63/E63,0)</f>
-        <v>-1.0055555555555555</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="K63" s="10">
-        <f>IFERROR(D63/E63,0)</f>
-        <v>-0.2011111111111111</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="L63" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>VEG</v>
+        <f t="shared" si="4"/>
+        <v>WEG</v>
       </c>
       <c r="N63">
-        <f t="shared" si="1"/>
-        <v>-18.100000000000001</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="O63">
-        <f t="shared" si="7"/>
-        <v>-3.6199999999999997</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="P63">
-        <f t="shared" si="8"/>
-        <v>18</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <f t="shared" si="9"/>
-        <v>9</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
       <c r="R63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S63">
-        <f t="shared" si="13"/>
-        <v>9</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
@@ -6741,65 +6735,65 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C64">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="D64">
-        <v>5.4</v>
+        <v>3.4999999999999996</v>
       </c>
       <c r="E64">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F64">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I64" s="7">
-        <f>IFERROR((F64/E64)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>60</v>
       </c>
       <c r="J64" s="10">
-        <f>IFERROR(C64/E64,0)</f>
-        <v>0.9</v>
+        <f t="shared" si="17"/>
+        <v>1.75</v>
       </c>
       <c r="K64" s="10">
-        <f>IFERROR(D64/E64,0)</f>
-        <v>0.18000000000000002</v>
+        <f t="shared" si="18"/>
+        <v>0.35</v>
       </c>
       <c r="L64" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>WEG</v>
       </c>
       <c r="N64">
-        <f t="shared" si="1"/>
-        <v>27</v>
+        <f t="shared" si="5"/>
+        <v>17.5</v>
       </c>
       <c r="O64">
-        <f t="shared" si="7"/>
-        <v>5.4</v>
+        <f t="shared" si="11"/>
+        <v>3.4999999999999996</v>
       </c>
       <c r="P64">
-        <f t="shared" si="8"/>
-        <v>30</v>
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="Q64">
-        <f t="shared" si="9"/>
-        <v>18</v>
+        <f t="shared" si="13"/>
+        <v>6</v>
       </c>
       <c r="R64">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="S64">
-        <f t="shared" si="13"/>
-        <v>12</v>
+        <f t="shared" si="20"/>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
@@ -6807,7 +6801,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -6828,190 +6822,58 @@
         <v>0</v>
       </c>
       <c r="I65" s="7">
-        <f>IFERROR((F65/E65)*100,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J65" s="10">
-        <f>IFERROR(C65/E65,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K65" s="10">
-        <f>IFERROR(D65/E65,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L65" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L65" si="21">LEFT(B65,3)</f>
         <v>WEG</v>
       </c>
       <c r="N65">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="N65" si="22">C65+U65</f>
         <v>0</v>
       </c>
       <c r="O65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R65">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="S65">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="s">
-        <v>58</v>
-      </c>
-      <c r="C66">
-        <v>17.5</v>
-      </c>
-      <c r="D66">
-        <v>3.4999999999999996</v>
-      </c>
-      <c r="E66">
-        <v>10</v>
-      </c>
-      <c r="F66">
-        <v>6</v>
-      </c>
-      <c r="G66">
-        <v>1</v>
-      </c>
-      <c r="H66">
-        <v>3</v>
-      </c>
-      <c r="I66" s="7">
-        <f>IFERROR((F66/E66)*100,0)</f>
-        <v>60</v>
-      </c>
-      <c r="J66" s="10">
-        <f>IFERROR(C66/E66,0)</f>
-        <v>1.75</v>
-      </c>
-      <c r="K66" s="10">
-        <f>IFERROR(D66/E66,0)</f>
-        <v>0.35</v>
-      </c>
-      <c r="L66" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>WEG</v>
-      </c>
-      <c r="N66">
-        <f t="shared" si="1"/>
-        <v>17.5</v>
-      </c>
-      <c r="O66">
-        <f t="shared" si="7"/>
-        <v>3.4999999999999996</v>
-      </c>
-      <c r="P66">
-        <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="Q66">
-        <f t="shared" si="9"/>
-        <v>6</v>
-      </c>
-      <c r="R66">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="S66">
-        <f t="shared" si="13"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="s">
-        <v>91</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-      <c r="E67">
-        <v>0</v>
-      </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67" s="7">
-        <f>IFERROR((F67/E67)*100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="10">
-        <f>IFERROR(C67/E67,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="10">
-        <f>IFERROR(D67/E67,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L67" s="10" t="str">
-        <f t="shared" ref="L67" si="14">LEFT(B67,3)</f>
-        <v>WEG</v>
-      </c>
-      <c r="N67">
-        <f t="shared" ref="N67" si="15">C67+U67</f>
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B73" s="8"/>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B74" s="8"/>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B75" s="8"/>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="8"/>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="8"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B106">
-    <sortCondition ref="B1:B106"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B104">
+    <sortCondition ref="B1:B104"/>
   </sortState>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="dataBar" priority="10">
@@ -7140,6 +7002,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -7250,7 +7113,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A53AFF8-0615-4AA5-B49F-FDA402810813}">
-  <dimension ref="A1:AB68"/>
+  <dimension ref="A1:AB66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -7259,7 +7122,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C1">
         <v>500</v>
@@ -7268,10 +7131,10 @@
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
         <v>78</v>
@@ -7280,18 +7143,18 @@
         <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G2" t="s">
         <v>80</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B3">
         <f>SUM(H3:AB3)</f>
@@ -7320,36 +7183,36 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B67" si="0">SUM(H4:AB4)</f>
+        <f t="shared" ref="B4:B65" si="0">SUM(H4:AB4)</f>
         <v>0</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C67" si="1">(B4/$C$1)*100</f>
+        <f t="shared" ref="C4:C65" si="1">(B4/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:D67" si="2">COUNTA(H4:AB4)</f>
+        <f t="shared" ref="D4:D65" si="2">COUNTA(H4:AB4)</f>
         <v>0</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E67" si="3">COUNTIF(H4:AB4, "&gt;0")</f>
+        <f t="shared" ref="E4:E65" si="3">COUNTIF(H4:AB4, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F67" si="4">COUNTIF(H4:AB4, "=0")</f>
+        <f t="shared" ref="F4:F65" si="4">COUNTIF(H4:AB4, "=0")</f>
         <v>0</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G67" si="5">COUNTIF(H4:AB4, "&lt;0")</f>
+        <f t="shared" ref="G4:G65" si="5">COUNTIF(H4:AB4, "&lt;0")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
@@ -7378,7 +7241,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
@@ -7407,7 +7270,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -7465,7 +7328,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -7494,7 +7357,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
@@ -7582,7 +7445,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -7786,7 +7649,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
@@ -7873,7 +7736,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
@@ -7931,7 +7794,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B25">
         <f t="shared" si="0"/>
@@ -7960,7 +7823,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B26">
         <f t="shared" si="0"/>
@@ -7989,7 +7852,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B27">
         <f t="shared" si="0"/>
@@ -8048,7 +7911,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B29">
         <f t="shared" si="0"/>
@@ -8106,7 +7969,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B31">
         <f t="shared" si="0"/>
@@ -8135,7 +7998,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B32">
         <f t="shared" si="0"/>
@@ -8164,7 +8027,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B33">
         <f t="shared" si="0"/>
@@ -8193,7 +8056,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B34">
         <f t="shared" si="0"/>
@@ -8222,7 +8085,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B35">
         <f t="shared" si="0"/>
@@ -8251,7 +8114,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B36">
         <f t="shared" si="0"/>
@@ -8280,7 +8143,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B37">
         <f t="shared" si="0"/>
@@ -8309,7 +8172,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B38">
         <f t="shared" si="0"/>
@@ -8425,7 +8288,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B42">
         <f t="shared" si="0"/>
@@ -8454,7 +8317,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B43">
         <f t="shared" si="0"/>
@@ -8483,7 +8346,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B44">
         <f t="shared" si="0"/>
@@ -8541,7 +8404,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="B46">
         <f t="shared" si="0"/>
@@ -8570,7 +8433,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="B47">
         <f t="shared" si="0"/>
@@ -8599,7 +8462,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B48">
         <f t="shared" si="0"/>
@@ -8626,9 +8489,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="B49">
         <f t="shared" si="0"/>
@@ -8655,9 +8518,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B50">
         <f t="shared" si="0"/>
@@ -8684,9 +8547,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B51">
         <f t="shared" si="0"/>
@@ -8713,9 +8576,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B52">
         <f t="shared" si="0"/>
@@ -8742,9 +8605,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B53">
         <f t="shared" si="0"/>
@@ -8771,9 +8634,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B54">
         <f t="shared" si="0"/>
@@ -8800,9 +8663,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B55">
         <f t="shared" si="0"/>
@@ -8829,9 +8692,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="B56">
         <f t="shared" si="0"/>
@@ -8858,9 +8721,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B57">
         <f t="shared" si="0"/>
@@ -8887,7 +8750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>97</v>
       </c>
@@ -8916,9 +8779,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B59">
         <f t="shared" si="0"/>
@@ -8945,9 +8808,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B60">
         <f t="shared" si="0"/>
@@ -8974,9 +8837,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B61">
         <f t="shared" si="0"/>
@@ -9003,9 +8866,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="B62">
         <f t="shared" si="0"/>
@@ -9032,9 +8895,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="B63">
         <f t="shared" si="0"/>
@@ -9060,10 +8923,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I63" s="12"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="B64">
         <f t="shared" si="0"/>
@@ -9090,9 +8954,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B65">
         <f t="shared" si="0"/>
@@ -9118,92 +8982,33 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I65" s="12"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B66">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B66" si="6">SUM(H66:AB66)</f>
         <v>0</v>
       </c>
       <c r="C66">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C66" si="7">(B66/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D66">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D66" si="8">COUNTA(H66:AB66)</f>
         <v>0</v>
       </c>
       <c r="E66">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E66" si="9">COUNTIF(H66:AB66, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F66">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="F66" si="10">COUNTIF(H66:AB66, "=0")</f>
         <v>0</v>
       </c>
       <c r="G66">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>58</v>
-      </c>
-      <c r="B67">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C67">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E67">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F67">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G67">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>91</v>
-      </c>
-      <c r="B68">
-        <f t="shared" ref="B68" si="6">SUM(H68:AB68)</f>
-        <v>0</v>
-      </c>
-      <c r="C68">
-        <f t="shared" ref="C68" si="7">(B68/$C$1)*100</f>
-        <v>0</v>
-      </c>
-      <c r="D68">
-        <f t="shared" ref="D68" si="8">COUNTA(H68:AB68)</f>
-        <v>0</v>
-      </c>
-      <c r="E68">
-        <f t="shared" ref="E68" si="9">COUNTIF(H68:AB68, "&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="F68">
-        <f t="shared" ref="F68" si="10">COUNTIF(H68:AB68, "=0")</f>
-        <v>0</v>
-      </c>
-      <c r="G68">
-        <f t="shared" ref="G68" si="11">COUNTIF(H68:AB68, "&lt;0")</f>
+        <f t="shared" ref="G66" si="11">COUNTIF(H66:AB66, "&lt;0")</f>
         <v>0</v>
       </c>
     </row>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBA1CB3-64D8-4763-B174-B5E9853B0305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC2AEDA-D1CB-43AE-A066-EAF4561E280C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
-    <pivotCache cacheId="3" r:id="rId6"/>
+    <pivotCache cacheId="2" r:id="rId5"/>
+    <pivotCache cacheId="10" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -594,7 +594,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -624,6 +624,9 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -642,131 +645,6 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46285.695046643516" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="66" xr:uid="{1976E921-BE3A-4FF1-A5EF-18E3F04892B4}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:L65" sheet="Результаты"/>
-  </cacheSource>
-  <cacheFields count="12">
-    <cacheField name="Номер" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="66"/>
-    </cacheField>
-    <cacheField name="Стратегия" numFmtId="0">
-      <sharedItems count="66">
-        <s v="LEG1_BIBI2"/>
-        <s v="LEG1_BORSCH"/>
-        <s v="LEG1_CC2"/>
-        <s v="LEG1_IGOGOSHA2"/>
-        <s v="LEG1_IRONANNY2"/>
-        <s v="LEG1_LAKSAe"/>
-        <s v="LEG1_OKROSHKA"/>
-        <s v="LEG1_PHOBO"/>
-        <s v="LEG1_PHOGA"/>
-        <s v="LEG1_PIN"/>
-        <s v="LEG2_ALKASH"/>
-        <s v="LEG2_DRG"/>
-        <s v="LEG2_DRINKER"/>
-        <s v="LEG2_FENNEC"/>
-        <s v="LEG2_HOTS"/>
-        <s v="LEG2_LOGAN"/>
-        <s v="LEG2_LYNX"/>
-        <s v="LEG2_MONSTER"/>
-        <s v="PEG11_KUSURUKEN"/>
-        <s v="PEG13_DWDDCr"/>
-        <s v="PEG14_RANGER"/>
-        <s v="PEG14_RENEGADE"/>
-        <s v="PEG14_RWDDCr"/>
-        <s v="PEG15_ANNA"/>
-        <s v="PEG15_SILVANA"/>
-        <s v="PEG17_PHOENIX"/>
-        <s v="PEG18_ANDUIN"/>
-        <s v="PEG18_BLAZE"/>
-        <s v="PEG18_DIABLO2"/>
-        <s v="PEG18_REXXAR2"/>
-        <s v="PEG18_UTER"/>
-        <s v="PEG18_UTER2"/>
-        <s v="PEG18_VARIAN2"/>
-        <s v="PEG19_ANUBARAK"/>
-        <s v="PEG2_SDDCr"/>
-        <s v="PEG20_HOGGER"/>
-        <s v="PEG26_UNKNOWN"/>
-        <s v="PEG4_U3"/>
-        <s v="PEG4_UNIVERSAL"/>
-        <s v="PEG8_DOBBY"/>
-        <s v="PEG8_LOBSTER"/>
-        <s v="SEG1_LITE"/>
-        <s v="SEG3_FORCE"/>
-        <s v="UEG2_DUCK"/>
-        <s v="UEG2_GGD"/>
-        <s v="UEG2_GOOSE"/>
-        <s v="UEG4_FALCON"/>
-        <s v="UEG4_PELICAN"/>
-        <s v="UEG6_ADVENTURE"/>
-        <s v="UEG6_DODO"/>
-        <s v="UEG6_DUELDODO"/>
-        <s v="UEG6_PIGEON"/>
-        <s v="UEG6_SHERIFF"/>
-        <s v="UEG6_VULTURE"/>
-        <s v="UEG7_ADVENTURE"/>
-        <s v="UEG7_DODO"/>
-        <s v="UEG7_DUELDODO"/>
-        <s v="UEG7_PIGEON"/>
-        <s v="UEG7_SHERIFF"/>
-        <s v="UEG7_VULTURE"/>
-        <s v="UEG8_AVENGER"/>
-        <s v="VEG1_VENUS"/>
-        <s v="WEG3_BATYA"/>
-        <s v="WEG4_DOG"/>
-        <s v="WEG4_PUPPY"/>
-        <s v="WEG7_PARADOX"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Абс" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-40" maxValue="64.3"/>
-    </cacheField>
-    <cacheField name="Отн" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-8" maxValue="12.860000000000003"/>
-    </cacheField>
-    <cacheField name="Кол-во" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="31"/>
-    </cacheField>
-    <cacheField name="Прибыль" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="18"/>
-    </cacheField>
-    <cacheField name="Нейтрал" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="Убыток" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="14"/>
-    </cacheField>
-    <cacheField name="ПроцПД" numFmtId="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="100"/>
-    </cacheField>
-    <cacheField name="САП" numFmtId="2">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-6" maxValue="2.2964285714285713"/>
-    </cacheField>
-    <cacheField name="СОП" numFmtId="2">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-1.2" maxValue="0.45928571428571441"/>
-    </cacheField>
-    <cacheField name="Тип" numFmtId="2">
-      <sharedItems count="6">
-        <s v="LEG"/>
-        <s v="PEG"/>
-        <s v="SEG"/>
-        <s v="UEG"/>
-        <s v="VEG"/>
-        <s v="WEG"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46286.961164004628" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="41" xr:uid="{93B0B297-F304-40FC-B21C-BCAAF0FA44CB}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:L42" sheet="Результаты"/>
@@ -824,936 +702,65 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="66">
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="-24.9"/>
-    <n v="-4.9799999999999995"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="20"/>
-    <n v="-4.9799999999999995"/>
-    <n v="-0.99599999999999989"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <n v="-8.8999999999999986"/>
-    <n v="-1.7799999999999998"/>
-    <n v="8"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="50"/>
-    <n v="-1.1124999999999998"/>
-    <n v="-0.22249999999999998"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <n v="-7.5"/>
-    <n v="-1.5"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="20"/>
-    <n v="-1.5"/>
-    <n v="-0.3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <n v="6"/>
-    <n v="1.2"/>
-    <n v="3"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="2"/>
-    <n v="0.39999999999999997"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <n v="-6"/>
-    <n v="-1.2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-6"/>
-    <n v="-1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <n v="24.599999999999998"/>
-    <n v="4.92"/>
-    <n v="14"/>
-    <n v="7"/>
-    <n v="1"/>
-    <n v="6"/>
-    <n v="50"/>
-    <n v="1.7571428571428569"/>
-    <n v="0.35142857142857142"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="11"/>
-    <x v="10"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="12"/>
-    <x v="11"/>
-    <n v="-12"/>
-    <n v="-2.4"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="33.333333333333329"/>
-    <n v="-4"/>
-    <n v="-0.79999999999999993"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="13"/>
-    <x v="12"/>
-    <n v="6.5999999999999988"/>
-    <n v="1.3200000000000007"/>
-    <n v="17"/>
-    <n v="7"/>
-    <n v="0"/>
-    <n v="10"/>
-    <n v="41.17647058823529"/>
-    <n v="0.38823529411764701"/>
-    <n v="7.7647058823529458E-2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="14"/>
-    <x v="13"/>
-    <n v="15.7"/>
-    <n v="3.14"/>
-    <n v="13"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="69.230769230769226"/>
-    <n v="1.2076923076923076"/>
-    <n v="0.24153846153846154"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="15"/>
-    <x v="14"/>
-    <n v="-1.8"/>
-    <n v="-0.36"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="-0.9"/>
-    <n v="-0.18"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="16"/>
-    <x v="15"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="17"/>
-    <x v="16"/>
-    <n v="-11.9"/>
-    <n v="-2.3800000000000003"/>
-    <n v="8"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="50"/>
-    <n v="-1.4875"/>
-    <n v="-0.29750000000000004"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="18"/>
-    <x v="17"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="19"/>
-    <x v="18"/>
-    <n v="15.199999999999996"/>
-    <n v="3.0399999999999996"/>
-    <n v="31"/>
-    <n v="16"/>
-    <n v="1"/>
-    <n v="14"/>
-    <n v="51.612903225806448"/>
-    <n v="0.49032258064516115"/>
-    <n v="9.8064516129032248E-2"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="20"/>
-    <x v="19"/>
-    <n v="1"/>
-    <n v="0.2"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="0.5"/>
-    <n v="0.1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="21"/>
-    <x v="20"/>
-    <n v="-1.9000000000000001"/>
-    <n v="-0.38"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="-0.95000000000000007"/>
-    <n v="-0.19"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="22"/>
-    <x v="21"/>
-    <n v="3.3000000000000003"/>
-    <n v="0.66000000000000014"/>
-    <n v="6"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="50"/>
-    <n v="0.55000000000000004"/>
-    <n v="0.11000000000000003"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="23"/>
-    <x v="22"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="24"/>
-    <x v="23"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="25"/>
-    <x v="24"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="26"/>
-    <x v="25"/>
-    <n v="64.3"/>
-    <n v="12.860000000000003"/>
-    <n v="28"/>
-    <n v="18"/>
-    <n v="0"/>
-    <n v="10"/>
-    <n v="64.285714285714292"/>
-    <n v="2.2964285714285713"/>
-    <n v="0.45928571428571441"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="27"/>
-    <x v="26"/>
-    <n v="-1.3"/>
-    <n v="-0.26"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-1.3"/>
-    <n v="-0.26"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="28"/>
-    <x v="27"/>
-    <n v="-40"/>
-    <n v="-8"/>
-    <n v="11"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="7"/>
-    <n v="27.27272727272727"/>
-    <n v="-3.6363636363636362"/>
-    <n v="-0.72727272727272729"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="29"/>
-    <x v="28"/>
-    <n v="-9.1"/>
-    <n v="-1.82"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="20"/>
-    <n v="-1.8199999999999998"/>
-    <n v="-0.36399999999999999"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="30"/>
-    <x v="29"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="31"/>
-    <x v="30"/>
-    <n v="-6.2"/>
-    <n v="-1.24"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="60"/>
-    <n v="-1.24"/>
-    <n v="-0.248"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="32"/>
-    <x v="31"/>
-    <n v="-1.3000000000000007"/>
-    <n v="-0.26000000000000023"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="60"/>
-    <n v="-0.26000000000000012"/>
-    <n v="-5.2000000000000046E-2"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="33"/>
-    <x v="32"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="34"/>
-    <x v="33"/>
-    <n v="-3.8000000000000007"/>
-    <n v="-0.76000000000000023"/>
-    <n v="5"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="40"/>
-    <n v="-0.76000000000000012"/>
-    <n v="-0.15200000000000005"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="35"/>
-    <x v="34"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="36"/>
-    <x v="35"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="37"/>
-    <x v="36"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="38"/>
-    <x v="37"/>
-    <n v="6"/>
-    <n v="1.2"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="1.5"/>
-    <n v="0.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="39"/>
-    <x v="38"/>
-    <n v="-6.5"/>
-    <n v="-1.2999999999999998"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="25"/>
-    <n v="-1.625"/>
-    <n v="-0.32499999999999996"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="40"/>
-    <x v="39"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="41"/>
-    <x v="40"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="42"/>
-    <x v="41"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="43"/>
-    <x v="42"/>
-    <n v="1.9000000000000004"/>
-    <n v="0.37999999999999989"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="60"/>
-    <n v="0.38000000000000006"/>
-    <n v="7.5999999999999984E-2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="44"/>
-    <x v="43"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="45"/>
-    <x v="44"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="46"/>
-    <x v="45"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="47"/>
-    <x v="46"/>
-    <n v="-12"/>
-    <n v="-2.4"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="-6"/>
-    <n v="-1.2"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="48"/>
-    <x v="47"/>
-    <n v="-2.9000000000000004"/>
-    <n v="-0.58000000000000007"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="60"/>
-    <n v="-0.58000000000000007"/>
-    <n v="-0.11600000000000002"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="49"/>
-    <x v="48"/>
-    <n v="-4.4000000000000004"/>
-    <n v="-0.88"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="33.333333333333329"/>
-    <n v="-1.4666666666666668"/>
-    <n v="-0.29333333333333333"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="50"/>
-    <x v="49"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="51"/>
-    <x v="50"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="52"/>
-    <x v="51"/>
-    <n v="-4.2999999999999989"/>
-    <n v="-0.85999999999999988"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="20"/>
-    <n v="-0.85999999999999976"/>
-    <n v="-0.17199999999999999"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="53"/>
-    <x v="52"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="54"/>
-    <x v="53"/>
-    <n v="1.6000000000000014"/>
-    <n v="0.32000000000000006"/>
-    <n v="6"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="33.333333333333329"/>
-    <n v="0.26666666666666689"/>
-    <n v="5.3333333333333344E-2"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="55"/>
-    <x v="54"/>
-    <n v="1.0000000000000002"/>
-    <n v="0.2"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="0.50000000000000011"/>
-    <n v="0.1"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="56"/>
-    <x v="55"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="57"/>
-    <x v="56"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="58"/>
-    <x v="57"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="59"/>
-    <x v="58"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="60"/>
-    <x v="59"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="61"/>
-    <x v="60"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="62"/>
-    <x v="61"/>
-    <n v="-18.100000000000001"/>
-    <n v="-3.6199999999999997"/>
-    <n v="18"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="9"/>
-    <n v="50"/>
-    <n v="-1.0055555555555555"/>
-    <n v="-0.2011111111111111"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="63"/>
-    <x v="62"/>
-    <n v="27"/>
-    <n v="5.4"/>
-    <n v="30"/>
-    <n v="18"/>
-    <n v="0"/>
-    <n v="12"/>
-    <n v="60"/>
-    <n v="0.9"/>
-    <n v="0.18000000000000002"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="64"/>
-    <x v="63"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="65"/>
-    <x v="64"/>
-    <n v="17.5"/>
-    <n v="3.4999999999999996"/>
-    <n v="10"/>
-    <n v="6"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="60"/>
-    <n v="1.75"/>
-    <n v="0.35"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="66"/>
-    <x v="65"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="5"/>
-  </r>
-</pivotCacheRecords>
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46287.786514004627" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="64" xr:uid="{1976E921-BE3A-4FF1-A5EF-18E3F04892B4}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:L65" sheet="Результаты"/>
+  </cacheSource>
+  <cacheFields count="12">
+    <cacheField name="Номер" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="64"/>
+    </cacheField>
+    <cacheField name="Стратегия" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Абс" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-45.8" maxValue="95.199999999999989"/>
+    </cacheField>
+    <cacheField name="Отн" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-9.16" maxValue="19.040000000000006"/>
+    </cacheField>
+    <cacheField name="Кол-во" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="38"/>
+    </cacheField>
+    <cacheField name="Прибыль" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="25"/>
+    </cacheField>
+    <cacheField name="Нейтрал" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Убыток" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="15"/>
+    </cacheField>
+    <cacheField name="ПроцПД" numFmtId="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="100"/>
+    </cacheField>
+    <cacheField name="САП" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-15.35" maxValue="7.8"/>
+    </cacheField>
+    <cacheField name="СОП" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-3.0700000000000003" maxValue="1.56"/>
+    </cacheField>
+    <cacheField name="Тип" numFmtId="2">
+      <sharedItems count="6">
+        <s v="PEG"/>
+        <s v="WEG"/>
+        <s v="LEG"/>
+        <s v="VEG"/>
+        <s v="UEG"/>
+        <s v="SEG"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="41">
   <r>
     <n v="1"/>
@@ -2332,8 +1339,909 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="64">
+  <r>
+    <n v="1"/>
+    <s v="PEG17_PHOENIX"/>
+    <n v="95.199999999999989"/>
+    <n v="19.040000000000006"/>
+    <n v="38"/>
+    <n v="25"/>
+    <n v="0"/>
+    <n v="13"/>
+    <n v="65.789473684210535"/>
+    <n v="2.5052631578947366"/>
+    <n v="0.50105263157894753"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <s v="PEG11_KUSURUKEN"/>
+    <n v="37.9"/>
+    <n v="7.58"/>
+    <n v="33"/>
+    <n v="17"/>
+    <n v="1"/>
+    <n v="15"/>
+    <n v="51.515151515151516"/>
+    <n v="1.1484848484848484"/>
+    <n v="0.22969696969696971"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <s v="WEG3_BATYA"/>
+    <n v="27.6"/>
+    <n v="5.5200000000000005"/>
+    <n v="32"/>
+    <n v="19"/>
+    <n v="0"/>
+    <n v="13"/>
+    <n v="59.375"/>
+    <n v="0.86250000000000004"/>
+    <n v="0.17250000000000001"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <s v="LEG2_DRINKER"/>
+    <n v="9.5"/>
+    <n v="1.9000000000000008"/>
+    <n v="19"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="10"/>
+    <n v="47.368421052631575"/>
+    <n v="0.5"/>
+    <n v="0.10000000000000005"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <s v="VEG1_VENUS"/>
+    <n v="-18.100000000000001"/>
+    <n v="-3.6199999999999997"/>
+    <n v="18"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="9"/>
+    <n v="50"/>
+    <n v="-1.0055555555555555"/>
+    <n v="-0.2011111111111111"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <s v="LEG2_FENNEC"/>
+    <n v="22.4"/>
+    <n v="4.4800000000000004"/>
+    <n v="17"/>
+    <n v="12"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="70.588235294117652"/>
+    <n v="1.3176470588235294"/>
+    <n v="0.2635294117647059"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <s v="LEG1_PIN"/>
+    <n v="15.399999999999999"/>
+    <n v="3.08"/>
+    <n v="16"/>
+    <n v="7"/>
+    <n v="1"/>
+    <n v="8"/>
+    <n v="43.75"/>
+    <n v="0.96249999999999991"/>
+    <n v="0.1925"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <s v="PEG18_BLAZE"/>
+    <n v="-45.8"/>
+    <n v="-9.16"/>
+    <n v="13"/>
+    <n v="4"/>
+    <n v="1"/>
+    <n v="8"/>
+    <n v="30.76923076923077"/>
+    <n v="-3.523076923076923"/>
+    <n v="-0.70461538461538464"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <s v="LEG2_LYNX"/>
+    <n v="7.7999999999999989"/>
+    <n v="1.5599999999999998"/>
+    <n v="12"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="66.666666666666657"/>
+    <n v="0.64999999999999991"/>
+    <n v="0.12999999999999998"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <s v="WEG4_PUPPY"/>
+    <n v="17.5"/>
+    <n v="3.4999999999999996"/>
+    <n v="10"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="60"/>
+    <n v="1.75"/>
+    <n v="0.35"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <s v="PEG4_UNIVERSAL"/>
+    <n v="6.9"/>
+    <n v="1.3800000000000003"/>
+    <n v="10"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="50"/>
+    <n v="0.69000000000000006"/>
+    <n v="0.13800000000000004"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <s v="UEG6_PIGEON"/>
+    <n v="0.50000000000000178"/>
+    <n v="0.10000000000000009"/>
+    <n v="9"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="6"/>
+    <n v="33.333333333333329"/>
+    <n v="5.5555555555555754E-2"/>
+    <n v="1.111111111111112E-2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <s v="UEG6_ADVENTURE"/>
+    <n v="4.3999999999999986"/>
+    <n v="0.87999999999999978"/>
+    <n v="9"/>
+    <n v="4"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="44.444444444444443"/>
+    <n v="0.48888888888888871"/>
+    <n v="9.7777777777777755E-2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <s v="LEG1_CC2"/>
+    <n v="-8.8999999999999986"/>
+    <n v="-1.7799999999999998"/>
+    <n v="8"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="50"/>
+    <n v="-1.1124999999999998"/>
+    <n v="-0.22249999999999998"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <s v="UEG6_VULTURE"/>
+    <n v="-9.6999999999999993"/>
+    <n v="-1.9400000000000002"/>
+    <n v="8"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="37.5"/>
+    <n v="-1.2124999999999999"/>
+    <n v="-0.24250000000000002"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <s v="PEG18_UTER2"/>
+    <n v="-13"/>
+    <n v="-2.6000000000000005"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="42.857142857142854"/>
+    <n v="-1.8571428571428572"/>
+    <n v="-0.3714285714285715"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <s v="LEG1_BIBI2"/>
+    <n v="-10"/>
+    <n v="-1.9999999999999991"/>
+    <n v="7"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="28.571428571428569"/>
+    <n v="-1.4285714285714286"/>
+    <n v="-0.28571428571428559"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <s v="PEG14_RENEGADE"/>
+    <n v="3.3000000000000003"/>
+    <n v="0.66000000000000014"/>
+    <n v="6"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="50"/>
+    <n v="0.55000000000000004"/>
+    <n v="0.11000000000000003"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <s v="PEG4_U3"/>
+    <n v="5.6"/>
+    <n v="1.1199999999999999"/>
+    <n v="6"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="83.333333333333343"/>
+    <n v="0.93333333333333324"/>
+    <n v="0.18666666666666665"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <s v="SEG3_FORCE"/>
+    <n v="1.9000000000000004"/>
+    <n v="0.37999999999999989"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="60"/>
+    <n v="0.38000000000000006"/>
+    <n v="7.5999999999999984E-2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <s v="UEG4_PELICAN"/>
+    <n v="-2.9000000000000004"/>
+    <n v="-0.58000000000000007"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="60"/>
+    <n v="-0.58000000000000007"/>
+    <n v="-0.11600000000000002"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <s v="PEG19_ANUBARAK"/>
+    <n v="-3.8000000000000007"/>
+    <n v="-0.76000000000000023"/>
+    <n v="5"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="40"/>
+    <n v="-0.76000000000000012"/>
+    <n v="-0.15200000000000005"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <s v="PEG18_UTER"/>
+    <n v="-6.2"/>
+    <n v="-1.24"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="60"/>
+    <n v="-1.24"/>
+    <n v="-0.248"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <s v="LEG1_IRONANNY2"/>
+    <n v="-7.5"/>
+    <n v="-1.5"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="-1.5"/>
+    <n v="-0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <s v="PEG18_DIABLO2"/>
+    <n v="-9.1"/>
+    <n v="-1.82"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="-1.8199999999999998"/>
+    <n v="-0.36399999999999999"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <s v="PEG26_UNKNOWN"/>
+    <n v="-0.5"/>
+    <n v="-9.9999999999999978E-2"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="50"/>
+    <n v="-0.125"/>
+    <n v="-2.4999999999999994E-2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <s v="LEG1_LAKSAe"/>
+    <n v="6"/>
+    <n v="1.2"/>
+    <n v="3"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="2"/>
+    <n v="0.39999999999999997"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <s v="LEG2_DRG"/>
+    <n v="-12"/>
+    <n v="-2.4"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="33.333333333333329"/>
+    <n v="-4"/>
+    <n v="-0.79999999999999993"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <s v="LEG2_LOGAN"/>
+    <n v="-8.0000000000000018"/>
+    <n v="-1.6000000000000003"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="66.666666666666657"/>
+    <n v="-2.6666666666666674"/>
+    <n v="-0.53333333333333344"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <s v="UEG7_ADVENTURE"/>
+    <n v="1.0000000000000002"/>
+    <n v="0.2"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="0.50000000000000011"/>
+    <n v="0.1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <s v="PEG13_DWDDCr"/>
+    <n v="1"/>
+    <n v="0.2"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="0.5"/>
+    <n v="0.1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <s v="LEG2_HOTS"/>
+    <n v="-1.8"/>
+    <n v="-0.36"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="-0.9"/>
+    <n v="-0.18"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <s v="PEG14_RANGER"/>
+    <n v="-1.9000000000000001"/>
+    <n v="-0.38"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="-0.95000000000000007"/>
+    <n v="-0.19"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <s v="UEG4_FALCON"/>
+    <n v="-12"/>
+    <n v="-2.4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="-6"/>
+    <n v="-1.2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <s v="SEG1_LITE"/>
+    <n v="14"/>
+    <n v="2.8"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="7"/>
+    <n v="1.4"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <s v="UEG7_PIGEON"/>
+    <n v="1.7"/>
+    <n v="0.34"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="0.85"/>
+    <n v="0.17"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <s v="LEG1_IGOGOSHA2"/>
+    <n v="1.7000000000000002"/>
+    <n v="0.34000000000000008"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="0.85000000000000009"/>
+    <n v="0.17000000000000004"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <s v="UEG6_SHERIFF"/>
+    <n v="15.6"/>
+    <n v="3.12"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="7.8"/>
+    <n v="1.56"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <s v="LEG2_ALKASH"/>
+    <n v="-30.7"/>
+    <n v="-6.1400000000000006"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="-15.35"/>
+    <n v="-3.0700000000000003"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <s v="PEG18_ANDUIN"/>
+    <n v="-1.3"/>
+    <n v="-0.26"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="-1.3"/>
+    <n v="-0.26"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="41"/>
+    <s v="LEG1_PHOGA"/>
+    <n v="-6"/>
+    <n v="-1.2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="-6"/>
+    <n v="-1.2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="42"/>
+    <s v="LEG1_BORSCH"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="43"/>
+    <s v="LEG1_OKROSHKA"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="44"/>
+    <s v="LEG1_PHOBO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="45"/>
+    <s v="LEG2_MONSTER"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="46"/>
+    <s v="PEG14_RWDDCr"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="47"/>
+    <s v="PEG15_ANNA"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="48"/>
+    <s v="PEG15_SILVANA"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="49"/>
+    <s v="PEG18_REXXAR2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="50"/>
+    <s v="PEG18_VARIAN2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="51"/>
+    <s v="PEG2_SDDCr"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="52"/>
+    <s v="PEG20_HOGGER"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="53"/>
+    <s v="PEG8_DOBBY"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="54"/>
+    <s v="PEG8_LOBSTER"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="55"/>
+    <s v="UEG4_CANADIAN"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="56"/>
+    <s v="UEG6_DODO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="57"/>
+    <s v="UEG6_DUELDODO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="58"/>
+    <s v="UEG7_DODO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="59"/>
+    <s v="UEG7_DUELDODO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="60"/>
+    <s v="UEG7_SHERIFF"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="61"/>
+    <s v="UEG7_VULTURE"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="62"/>
+    <s v="UEG8_AVENGER"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="63"/>
+    <s v="WEG4_DOG"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="64"/>
+    <s v="WEG7_PARADOX"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C4CB1275-447E-4587-B9C3-BDD7EB80BE41}" name="Сводная таблица2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C4CB1275-447E-4587-B9C3-BDD7EB80BE41}" name="Сводная таблица2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A12:G19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -2429,81 +2337,11 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5C6C209-71EC-45CD-876E-D40B4E36B838}" name="Сводная таблица1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5C6C209-71EC-45CD-876E-D40B4E36B838}" name="Сводная таблица1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:G10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="67">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -2515,12 +2353,12 @@
     <pivotField numFmtId="2" showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="7">
+        <item x="2"/>
         <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="3"/>
         <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3101,7 +2939,7 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
-        <v>46285</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3132,22 +2970,22 @@
         <v>136</v>
       </c>
       <c r="B4" s="12">
-        <v>-20.100000000000001</v>
+        <v>-22.100000000000005</v>
       </c>
       <c r="C4" s="12">
-        <v>-4.0199999999999996</v>
+        <v>-4.4199999999999982</v>
       </c>
       <c r="D4" s="12">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E4" s="12">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F4" s="12">
         <v>1</v>
       </c>
       <c r="G4" s="12">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3155,22 +2993,22 @@
         <v>137</v>
       </c>
       <c r="B5" s="12">
-        <v>19.699999999999992</v>
+        <v>68.3</v>
       </c>
       <c r="C5" s="12">
-        <v>3.9400000000000013</v>
+        <v>13.660000000000002</v>
       </c>
       <c r="D5" s="12">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="E5" s="12">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F5" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" s="12">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3178,16 +3016,16 @@
         <v>138</v>
       </c>
       <c r="B6" s="12">
-        <v>1.9000000000000004</v>
+        <v>15.9</v>
       </c>
       <c r="C6" s="12">
-        <v>0.37999999999999989</v>
+        <v>3.1799999999999997</v>
       </c>
       <c r="D6" s="12">
+        <v>7</v>
+      </c>
+      <c r="E6" s="12">
         <v>5</v>
-      </c>
-      <c r="E6" s="12">
-        <v>3</v>
       </c>
       <c r="F6" s="12">
         <v>0</v>
@@ -3201,22 +3039,22 @@
         <v>139</v>
       </c>
       <c r="B7" s="12">
-        <v>-21</v>
+        <v>-1.4000000000000004</v>
       </c>
       <c r="C7" s="12">
-        <v>-4.1999999999999993</v>
+        <v>-0.28000000000000025</v>
       </c>
       <c r="D7" s="12">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E7" s="12">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F7" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="12">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3247,22 +3085,22 @@
         <v>141</v>
       </c>
       <c r="B9" s="12">
-        <v>44.5</v>
+        <v>45.1</v>
       </c>
       <c r="C9" s="12">
-        <v>8.9</v>
+        <v>9.02</v>
       </c>
       <c r="D9" s="12">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" s="12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9" s="12">
         <v>1</v>
       </c>
       <c r="G9" s="12">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3270,22 +3108,22 @@
         <v>134</v>
       </c>
       <c r="B10" s="12">
-        <v>6.8999999999999915</v>
+        <v>87.699999999999989</v>
       </c>
       <c r="C10" s="12">
-        <v>1.3800000000000026</v>
+        <v>17.540000000000006</v>
       </c>
       <c r="D10" s="12">
-        <v>276</v>
+        <v>343</v>
       </c>
       <c r="E10" s="12">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="F10" s="12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G10" s="12">
-        <v>133</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3579,34 +3417,34 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>68.399999999999991</v>
+        <v>95.199999999999989</v>
       </c>
       <c r="D2">
-        <v>13.680000000000003</v>
+        <v>19.040000000000006</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" s="7">
         <f>IFERROR((F2/E2)*100,0)</f>
-        <v>63.636363636363633</v>
+        <v>65.789473684210535</v>
       </c>
       <c r="J2" s="10">
         <f>IFERROR(C2/E2,0)</f>
-        <v>2.0727272727272723</v>
+        <v>2.5052631578947366</v>
       </c>
       <c r="K2" s="10">
         <f>IFERROR(D2/E2,0)</f>
-        <v>0.41454545454545466</v>
+        <v>0.50105263157894753</v>
       </c>
       <c r="L2" s="10" t="str">
         <f>LEFT(B2,3)</f>
@@ -3614,19 +3452,19 @@
       </c>
       <c r="N2">
         <f t="shared" ref="N2:S2" si="0">C2+U2</f>
-        <v>68.399999999999991</v>
+        <v>95.199999999999989</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>13.680000000000003</v>
+        <v>19.040000000000006</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
@@ -3634,7 +3472,7 @@
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -3645,13 +3483,13 @@
         <v>64</v>
       </c>
       <c r="C3">
-        <v>43.3</v>
+        <v>37.9</v>
       </c>
       <c r="D3">
-        <v>8.66</v>
+        <v>7.58</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>17</v>
@@ -3660,19 +3498,19 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="7">
         <f>IFERROR((F3/E3)*100,0)</f>
-        <v>53.125</v>
+        <v>51.515151515151516</v>
       </c>
       <c r="J3" s="10">
         <f>IFERROR(C3/E3,0)</f>
-        <v>1.3531249999999999</v>
+        <v>1.1484848484848484</v>
       </c>
       <c r="K3" s="10">
         <f>IFERROR(D3/E3,0)</f>
-        <v>0.270625</v>
+        <v>0.22969696969696971</v>
       </c>
       <c r="L3" s="10" t="str">
         <f>LEFT(B3,3)</f>
@@ -3680,15 +3518,15 @@
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N64" si="1">C3+U3</f>
-        <v>43.3</v>
+        <v>37.9</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O17" si="2">D3+V3</f>
-        <v>8.66</v>
+        <v>7.58</v>
       </c>
       <c r="P3">
         <f t="shared" ref="P3:P17" si="3">E3+W3</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q17" si="4">F3+X3</f>
@@ -3700,7 +3538,7 @@
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S17" si="6">H3+Z3</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -3711,16 +3549,16 @@
         <v>56</v>
       </c>
       <c r="C4">
-        <v>26.6</v>
+        <v>27.6</v>
       </c>
       <c r="D4">
-        <v>5.32</v>
+        <v>5.5200000000000005</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3730,15 +3568,15 @@
       </c>
       <c r="I4" s="7">
         <f>IFERROR((F4/E4)*100,0)</f>
-        <v>58.064516129032263</v>
+        <v>59.375</v>
       </c>
       <c r="J4" s="10">
         <f>IFERROR(C4/E4,0)</f>
-        <v>0.85806451612903234</v>
+        <v>0.86250000000000004</v>
       </c>
       <c r="K4" s="10">
         <f>IFERROR(D4/E4,0)</f>
-        <v>0.17161290322580647</v>
+        <v>0.17250000000000001</v>
       </c>
       <c r="L4" s="10" t="str">
         <f>LEFT(B4,3)</f>
@@ -3746,19 +3584,19 @@
       </c>
       <c r="N4">
         <f t="shared" si="1"/>
-        <v>26.6</v>
+        <v>27.6</v>
       </c>
       <c r="O4">
         <f t="shared" si="2"/>
-        <v>5.32</v>
+        <v>5.5200000000000005</v>
       </c>
       <c r="P4">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q4">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R4">
         <f t="shared" si="5"/>
@@ -3777,16 +3615,16 @@
         <v>55</v>
       </c>
       <c r="C5">
-        <v>8.1999999999999993</v>
+        <v>9.5</v>
       </c>
       <c r="D5">
-        <v>1.6400000000000008</v>
+        <v>1.9000000000000008</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -3796,15 +3634,15 @@
       </c>
       <c r="I5" s="7">
         <f>IFERROR((F5/E5)*100,0)</f>
-        <v>44.444444444444443</v>
+        <v>47.368421052631575</v>
       </c>
       <c r="J5" s="10">
         <f>IFERROR(C5/E5,0)</f>
-        <v>0.45555555555555549</v>
+        <v>0.5</v>
       </c>
       <c r="K5" s="10">
         <f>IFERROR(D5/E5,0)</f>
-        <v>9.1111111111111157E-2</v>
+        <v>0.10000000000000005</v>
       </c>
       <c r="L5" s="10" t="str">
         <f>LEFT(B5,3)</f>
@@ -3812,19 +3650,19 @@
       </c>
       <c r="N5">
         <f t="shared" si="1"/>
-        <v>8.1999999999999993</v>
+        <v>9.5</v>
       </c>
       <c r="O5">
         <f t="shared" si="2"/>
-        <v>1.6400000000000008</v>
+        <v>1.9000000000000008</v>
       </c>
       <c r="P5">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q5">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <f t="shared" si="5"/>
@@ -3906,37 +3744,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C7">
-        <v>18.099999999999998</v>
+        <v>22.4</v>
       </c>
       <c r="D7">
-        <v>3.62</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I7" s="7">
         <f>IFERROR((F7/E7)*100,0)</f>
-        <v>46.666666666666664</v>
+        <v>70.588235294117652</v>
       </c>
       <c r="J7" s="10">
         <f>IFERROR(C7/E7,0)</f>
-        <v>1.2066666666666666</v>
+        <v>1.3176470588235294</v>
       </c>
       <c r="K7" s="10">
         <f>IFERROR(D7/E7,0)</f>
-        <v>0.24133333333333334</v>
+        <v>0.2635294117647059</v>
       </c>
       <c r="L7" s="10" t="str">
         <f>LEFT(B7,3)</f>
@@ -3944,27 +3782,27 @@
       </c>
       <c r="N7">
         <f t="shared" si="1"/>
-        <v>18.099999999999998</v>
+        <v>22.4</v>
       </c>
       <c r="O7">
         <f t="shared" si="2"/>
-        <v>3.62</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="P7">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q7">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R7">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -3972,37 +3810,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C8">
-        <v>13.1</v>
+        <v>15.399999999999999</v>
       </c>
       <c r="D8">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I8" s="7">
         <f>IFERROR((F8/E8)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>43.75</v>
       </c>
       <c r="J8" s="10">
         <f>IFERROR(C8/E8,0)</f>
-        <v>0.87333333333333329</v>
+        <v>0.96249999999999991</v>
       </c>
       <c r="K8" s="10">
         <f>IFERROR(D8/E8,0)</f>
-        <v>0.17466666666666666</v>
+        <v>0.1925</v>
       </c>
       <c r="L8" s="10" t="str">
         <f>LEFT(B8,3)</f>
@@ -4010,27 +3848,27 @@
       </c>
       <c r="N8">
         <f t="shared" si="1"/>
-        <v>13.1</v>
+        <v>15.399999999999999</v>
       </c>
       <c r="O8">
         <f t="shared" si="2"/>
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="P8">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -4041,13 +3879,13 @@
         <v>59</v>
       </c>
       <c r="C9">
-        <v>-38.4</v>
+        <v>-45.8</v>
       </c>
       <c r="D9">
-        <v>-7.68</v>
+        <v>-9.16</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9">
         <v>4</v>
@@ -4056,19 +3894,19 @@
         <v>1</v>
       </c>
       <c r="H9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" s="7">
         <f>IFERROR((F9/E9)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="J9" s="10">
         <f>IFERROR(C9/E9,0)</f>
-        <v>-3.1999999999999997</v>
+        <v>-3.523076923076923</v>
       </c>
       <c r="K9" s="10">
         <f>IFERROR(D9/E9,0)</f>
-        <v>-0.64</v>
+        <v>-0.70461538461538464</v>
       </c>
       <c r="L9" s="10" t="str">
         <f>LEFT(B9,3)</f>
@@ -4076,15 +3914,15 @@
       </c>
       <c r="N9">
         <f t="shared" si="1"/>
-        <v>-38.4</v>
+        <v>-45.8</v>
       </c>
       <c r="O9">
         <f t="shared" si="2"/>
-        <v>-7.68</v>
+        <v>-9.16</v>
       </c>
       <c r="P9">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q9">
         <f t="shared" si="4"/>
@@ -4096,7 +3934,7 @@
       </c>
       <c r="S9">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -4104,65 +3942,65 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10">
-        <v>17.5</v>
+        <v>7.7999999999999989</v>
       </c>
       <c r="D10">
-        <v>3.4999999999999996</v>
+        <v>1.5599999999999998</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="7">
         <f>IFERROR((F10/E10)*100,0)</f>
-        <v>60</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J10" s="10">
         <f>IFERROR(C10/E10,0)</f>
-        <v>1.75</v>
+        <v>0.64999999999999991</v>
       </c>
       <c r="K10" s="10">
         <f>IFERROR(D10/E10,0)</f>
-        <v>0.35</v>
+        <v>0.12999999999999998</v>
       </c>
       <c r="L10" s="10" t="str">
         <f>LEFT(B10,3)</f>
-        <v>WEG</v>
+        <v>LEG</v>
       </c>
       <c r="N10">
         <f t="shared" si="1"/>
-        <v>17.5</v>
+        <v>7.7999999999999989</v>
       </c>
       <c r="O10">
         <f t="shared" si="2"/>
-        <v>3.4999999999999996</v>
+        <v>1.5599999999999998</v>
       </c>
       <c r="P10">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q10">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -4170,13 +4008,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C11">
-        <v>-1.3000000000000007</v>
+        <v>17.5</v>
       </c>
       <c r="D11">
-        <v>-0.26000000000000023</v>
+        <v>3.4999999999999996</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -4185,10 +4023,10 @@
         <v>6</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" s="7">
         <f>IFERROR((F11/E11)*100,0)</f>
@@ -4196,23 +4034,23 @@
       </c>
       <c r="J11" s="10">
         <f>IFERROR(C11/E11,0)</f>
-        <v>-0.13000000000000006</v>
+        <v>1.75</v>
       </c>
       <c r="K11" s="10">
         <f>IFERROR(D11/E11,0)</f>
-        <v>-2.6000000000000023E-2</v>
+        <v>0.35</v>
       </c>
       <c r="L11" s="10" t="str">
         <f>LEFT(B11,3)</f>
-        <v>LEG</v>
+        <v>WEG</v>
       </c>
       <c r="N11">
         <f t="shared" si="1"/>
-        <v>-1.3000000000000007</v>
+        <v>17.5</v>
       </c>
       <c r="O11">
         <f t="shared" si="2"/>
-        <v>-0.26000000000000023</v>
+        <v>3.4999999999999996</v>
       </c>
       <c r="P11">
         <f t="shared" si="3"/>
@@ -4224,11 +4062,11 @@
       </c>
       <c r="R11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -4236,22 +4074,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="C12">
-        <v>-8.8999999999999986</v>
+        <v>6.9</v>
       </c>
       <c r="D12">
-        <v>-1.7799999999999998</v>
+        <v>1.3800000000000003</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>4</v>
@@ -4262,35 +4100,35 @@
       </c>
       <c r="J12" s="10">
         <f>IFERROR(C12/E12,0)</f>
-        <v>-1.1124999999999998</v>
+        <v>0.69000000000000006</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(D12/E12,0)</f>
-        <v>-0.22249999999999998</v>
+        <v>0.13800000000000004</v>
       </c>
       <c r="L12" s="10" t="str">
         <f>LEFT(B12,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N12">
         <f t="shared" si="1"/>
-        <v>-8.8999999999999986</v>
+        <v>6.9</v>
       </c>
       <c r="O12">
         <f t="shared" si="2"/>
-        <v>-1.7799999999999998</v>
+        <v>1.3800000000000003</v>
       </c>
       <c r="P12">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12">
         <f t="shared" si="6"/>
@@ -4302,53 +4140,53 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C13">
-        <v>3.8000000000000007</v>
+        <v>0.50000000000000178</v>
       </c>
       <c r="D13">
-        <v>0.76000000000000023</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F13">
         <v>3</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
         <f>IFERROR((F13/E13)*100,0)</f>
-        <v>42.857142857142854</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J13" s="10">
         <f>IFERROR(C13/E13,0)</f>
-        <v>0.54285714285714293</v>
+        <v>5.5555555555555754E-2</v>
       </c>
       <c r="K13" s="10">
         <f>IFERROR(D13/E13,0)</f>
-        <v>0.10857142857142861</v>
+        <v>1.111111111111112E-2</v>
       </c>
       <c r="L13" s="10" t="str">
         <f>LEFT(B13,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N13">
         <f t="shared" si="1"/>
-        <v>3.8000000000000007</v>
+        <v>0.50000000000000178</v>
       </c>
       <c r="O13">
         <f t="shared" si="2"/>
-        <v>0.76000000000000023</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="P13">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q13">
         <f t="shared" si="4"/>
@@ -4356,11 +4194,11 @@
       </c>
       <c r="R13">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
@@ -4368,37 +4206,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C14">
-        <v>-8.4999999999999982</v>
+        <v>4.3999999999999986</v>
       </c>
       <c r="D14">
-        <v>-1.6999999999999997</v>
+        <v>0.87999999999999978</v>
       </c>
       <c r="E14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
       <c r="H14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I14" s="7">
         <f>IFERROR((F14/E14)*100,0)</f>
-        <v>14.285714285714285</v>
+        <v>44.444444444444443</v>
       </c>
       <c r="J14" s="10">
         <f>IFERROR(C14/E14,0)</f>
-        <v>-1.214285714285714</v>
+        <v>0.48888888888888871</v>
       </c>
       <c r="K14" s="10">
         <f>IFERROR(D14/E14,0)</f>
-        <v>-0.24285714285714283</v>
+        <v>9.7777777777777755E-2</v>
       </c>
       <c r="L14" s="10" t="str">
         <f>LEFT(B14,3)</f>
@@ -4406,27 +4244,27 @@
       </c>
       <c r="N14">
         <f t="shared" si="1"/>
-        <v>-8.4999999999999982</v>
+        <v>4.3999999999999986</v>
       </c>
       <c r="O14">
         <f t="shared" si="2"/>
-        <v>-1.6999999999999997</v>
+        <v>0.87999999999999978</v>
       </c>
       <c r="P14">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q14">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R14">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
@@ -4434,57 +4272,57 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C15">
-        <v>-10.799999999999999</v>
+        <v>-8.8999999999999986</v>
       </c>
       <c r="D15">
-        <v>-2.16</v>
+        <v>-1.7799999999999998</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I15" s="7">
         <f>IFERROR((F15/E15)*100,0)</f>
-        <v>28.571428571428569</v>
+        <v>50</v>
       </c>
       <c r="J15" s="10">
         <f>IFERROR(C15/E15,0)</f>
-        <v>-1.5428571428571427</v>
+        <v>-1.1124999999999998</v>
       </c>
       <c r="K15" s="10">
         <f>IFERROR(D15/E15,0)</f>
-        <v>-0.30857142857142861</v>
+        <v>-0.22249999999999998</v>
       </c>
       <c r="L15" s="10" t="str">
         <f>LEFT(B15,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N15">
         <f t="shared" si="1"/>
-        <v>-10.799999999999999</v>
+        <v>-8.8999999999999986</v>
       </c>
       <c r="O15">
         <f t="shared" si="2"/>
-        <v>-2.16</v>
+        <v>-1.7799999999999998</v>
       </c>
       <c r="P15">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R15">
         <f t="shared" si="5"/>
@@ -4492,7 +4330,7 @@
       </c>
       <c r="S15">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -4500,16 +4338,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C16">
-        <v>3.3000000000000003</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="D16">
-        <v>0.66000000000000014</v>
+        <v>-1.9400000000000002</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>3</v>
@@ -4518,35 +4356,35 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I16" s="7">
         <f>IFERROR((F16/E16)*100,0)</f>
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="J16" s="10">
         <f>IFERROR(C16/E16,0)</f>
-        <v>0.55000000000000004</v>
+        <v>-1.2124999999999999</v>
       </c>
       <c r="K16" s="10">
         <f>IFERROR(D16/E16,0)</f>
-        <v>0.11000000000000003</v>
+        <v>-0.24250000000000002</v>
       </c>
       <c r="L16" s="10" t="str">
         <f>LEFT(B16,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N16">
         <f t="shared" si="1"/>
-        <v>3.3000000000000003</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="O16">
         <f t="shared" si="2"/>
-        <v>0.66000000000000014</v>
+        <v>-1.9400000000000002</v>
       </c>
       <c r="P16">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <f t="shared" si="4"/>
@@ -4558,7 +4396,7 @@
       </c>
       <c r="S16">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -4566,65 +4404,65 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C17">
-        <v>-0.70000000000000062</v>
+        <v>-13</v>
       </c>
       <c r="D17">
-        <v>-0.14000000000000001</v>
+        <v>-2.6000000000000005</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="7">
         <f>IFERROR((F17/E17)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="J17" s="10">
         <f>IFERROR(C17/E17,0)</f>
-        <v>-0.11666666666666677</v>
+        <v>-1.8571428571428572</v>
       </c>
       <c r="K17" s="10">
         <f>IFERROR(D17/E17,0)</f>
-        <v>-2.3333333333333334E-2</v>
+        <v>-0.3714285714285715</v>
       </c>
       <c r="L17" s="10" t="str">
         <f>LEFT(B17,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N17">
         <f t="shared" si="1"/>
-        <v>-0.70000000000000062</v>
+        <v>-13</v>
       </c>
       <c r="O17">
         <f t="shared" si="2"/>
-        <v>-0.14000000000000001</v>
+        <v>-2.6000000000000005</v>
       </c>
       <c r="P17">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R17">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -4632,57 +4470,57 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C18">
-        <v>-7.8000000000000007</v>
+        <v>-10</v>
       </c>
       <c r="D18">
-        <v>-1.5600000000000003</v>
+        <v>-1.9999999999999991</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I18" s="7">
         <f>IFERROR((F18/E18)*100,0)</f>
-        <v>50</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="J18" s="10">
         <f>IFERROR(C18/E18,0)</f>
-        <v>-1.3</v>
+        <v>-1.4285714285714286</v>
       </c>
       <c r="K18" s="10">
         <f>IFERROR(D18/E18,0)</f>
-        <v>-0.26000000000000006</v>
+        <v>-0.28571428571428559</v>
       </c>
       <c r="L18" s="10" t="str">
         <f>LEFT(B18,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N18">
         <f t="shared" si="1"/>
-        <v>-7.8000000000000007</v>
+        <v>-10</v>
       </c>
       <c r="O18">
         <f t="shared" ref="O18:O65" si="7">D18+V18</f>
-        <v>-1.5600000000000003</v>
+        <v>-1.9999999999999991</v>
       </c>
       <c r="P18">
         <f t="shared" ref="P18:P65" si="8">E18+W18</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <f t="shared" ref="Q18:Q65" si="9">F18+X18</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R18">
         <f t="shared" ref="R18:R47" si="10">G18+Y18</f>
@@ -4690,7 +4528,7 @@
       </c>
       <c r="S18">
         <f t="shared" ref="S18:S47" si="11">H18+Z18</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -4698,49 +4536,49 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C19">
-        <v>-25</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="D19">
-        <v>-4.9999999999999991</v>
+        <v>0.66000000000000014</v>
       </c>
       <c r="E19">
         <v>6</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I19" s="7">
         <f>IFERROR((F19/E19)*100,0)</f>
-        <v>16.666666666666664</v>
+        <v>50</v>
       </c>
       <c r="J19" s="10">
         <f>IFERROR(C19/E19,0)</f>
-        <v>-4.166666666666667</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K19" s="10">
         <f>IFERROR(D19/E19,0)</f>
-        <v>-0.83333333333333315</v>
+        <v>0.11000000000000003</v>
       </c>
       <c r="L19" s="10" t="str">
         <f>LEFT(B19,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N19">
         <f t="shared" si="1"/>
-        <v>-25</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="O19">
         <f t="shared" si="7"/>
-        <v>-4.9999999999999991</v>
+        <v>0.66000000000000014</v>
       </c>
       <c r="P19">
         <f t="shared" si="8"/>
@@ -4748,7 +4586,7 @@
       </c>
       <c r="Q19">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R19">
         <f t="shared" si="10"/>
@@ -4756,7 +4594,7 @@
       </c>
       <c r="S19">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -4767,16 +4605,16 @@
         <v>63</v>
       </c>
       <c r="C20">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="D20">
-        <v>0.55999999999999994</v>
+        <v>1.1199999999999999</v>
       </c>
       <c r="E20">
+        <v>6</v>
+      </c>
+      <c r="F20">
         <v>5</v>
-      </c>
-      <c r="F20">
-        <v>4</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4786,15 +4624,15 @@
       </c>
       <c r="I20" s="7">
         <f>IFERROR((F20/E20)*100,0)</f>
-        <v>80</v>
+        <v>83.333333333333343</v>
       </c>
       <c r="J20" s="10">
         <f>IFERROR(C20/E20,0)</f>
-        <v>0.55999999999999994</v>
+        <v>0.93333333333333324</v>
       </c>
       <c r="K20" s="10">
         <f>IFERROR(D20/E20,0)</f>
-        <v>0.11199999999999999</v>
+        <v>0.18666666666666665</v>
       </c>
       <c r="L20" s="10" t="str">
         <f>LEFT(B20,3)</f>
@@ -4802,19 +4640,19 @@
       </c>
       <c r="N20">
         <f t="shared" si="1"/>
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="O20">
         <f t="shared" si="7"/>
-        <v>0.55999999999999994</v>
+        <v>1.1199999999999999</v>
       </c>
       <c r="P20">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R20">
         <f t="shared" si="10"/>
@@ -5226,57 +5064,57 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>-0.5</v>
       </c>
       <c r="D27">
-        <v>1.2</v>
+        <v>-9.9999999999999978E-2</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" s="7">
         <f>IFERROR((F27/E27)*100,0)</f>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J27" s="10">
         <f>IFERROR(C27/E27,0)</f>
-        <v>2</v>
+        <v>-0.125</v>
       </c>
       <c r="K27" s="10">
         <f>IFERROR(D27/E27,0)</f>
-        <v>0.39999999999999997</v>
+        <v>-2.4999999999999994E-2</v>
       </c>
       <c r="L27" s="10" t="str">
         <f>LEFT(B27,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N27">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>-0.5</v>
       </c>
       <c r="O27">
         <f t="shared" si="7"/>
-        <v>1.2</v>
+        <v>-9.9999999999999978E-2</v>
       </c>
       <c r="P27">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q27">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R27">
         <f t="shared" si="10"/>
@@ -5284,7 +5122,7 @@
       </c>
       <c r="S27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -5292,49 +5130,49 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C28">
-        <v>-3.4</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>-0.67999999999999994</v>
+        <v>1.2</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" s="7">
         <f>IFERROR((F28/E28)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J28" s="10">
         <f>IFERROR(C28/E28,0)</f>
-        <v>-1.1333333333333333</v>
+        <v>2</v>
       </c>
       <c r="K28" s="10">
         <f>IFERROR(D28/E28,0)</f>
-        <v>-0.22666666666666666</v>
+        <v>0.39999999999999997</v>
       </c>
       <c r="L28" s="10" t="str">
         <f>LEFT(B28,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N28">
         <f t="shared" si="1"/>
-        <v>-3.4</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <f t="shared" si="7"/>
-        <v>-0.67999999999999994</v>
+        <v>1.2</v>
       </c>
       <c r="P28">
         <f t="shared" si="8"/>
@@ -5342,7 +5180,7 @@
       </c>
       <c r="Q28">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R28">
         <f t="shared" si="10"/>
@@ -5350,7 +5188,7 @@
       </c>
       <c r="S28">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -5424,19 +5262,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="C30">
-        <v>1.0000000000000002</v>
+        <v>-8.0000000000000018</v>
       </c>
       <c r="D30">
-        <v>0.2</v>
+        <v>-1.6000000000000003</v>
       </c>
       <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30">
         <v>2</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -5446,35 +5284,35 @@
       </c>
       <c r="I30" s="7">
         <f>IFERROR((F30/E30)*100,0)</f>
-        <v>50</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J30" s="10">
         <f>IFERROR(C30/E30,0)</f>
-        <v>0.50000000000000011</v>
+        <v>-2.6666666666666674</v>
       </c>
       <c r="K30" s="10">
         <f>IFERROR(D30/E30,0)</f>
-        <v>0.1</v>
+        <v>-0.53333333333333344</v>
       </c>
       <c r="L30" s="10" t="str">
         <f>LEFT(B30,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N30">
         <f t="shared" si="1"/>
-        <v>1.0000000000000002</v>
+        <v>-8.0000000000000018</v>
       </c>
       <c r="O30">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>-1.6000000000000003</v>
       </c>
       <c r="P30">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30">
         <f t="shared" si="10"/>
@@ -5490,10 +5328,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D31">
         <v>0.2</v>
@@ -5516,7 +5354,7 @@
       </c>
       <c r="J31" s="10">
         <f>IFERROR(C31/E31,0)</f>
-        <v>0.5</v>
+        <v>0.50000000000000011</v>
       </c>
       <c r="K31" s="10">
         <f>IFERROR(D31/E31,0)</f>
@@ -5524,11 +5362,11 @@
       </c>
       <c r="L31" s="10" t="str">
         <f>LEFT(B31,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N31">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="O31">
         <f t="shared" si="7"/>
@@ -5556,49 +5394,49 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C32">
-        <v>-1.8</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>-0.36</v>
+        <v>0.2</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="7">
         <f>IFERROR((F32/E32)*100,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J32" s="10">
         <f>IFERROR(C32/E32,0)</f>
-        <v>-0.9</v>
+        <v>0.5</v>
       </c>
       <c r="K32" s="10">
         <f>IFERROR(D32/E32,0)</f>
-        <v>-0.18</v>
+        <v>0.1</v>
       </c>
       <c r="L32" s="10" t="str">
         <f>LEFT(B32,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N32">
         <f t="shared" si="1"/>
-        <v>-1.8</v>
+        <v>1</v>
       </c>
       <c r="O32">
         <f t="shared" si="7"/>
-        <v>-0.36</v>
+        <v>0.2</v>
       </c>
       <c r="P32">
         <f t="shared" si="8"/>
@@ -5606,7 +5444,7 @@
       </c>
       <c r="Q32">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32">
         <f t="shared" si="10"/>
@@ -5614,7 +5452,7 @@
       </c>
       <c r="S32">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
@@ -5622,49 +5460,49 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="C33">
-        <v>-1.9000000000000001</v>
+        <v>-1.8</v>
       </c>
       <c r="D33">
-        <v>-0.38</v>
+        <v>-0.36</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" s="7">
         <f>IFERROR((F33/E33)*100,0)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J33" s="10">
         <f>IFERROR(C33/E33,0)</f>
-        <v>-0.95000000000000007</v>
+        <v>-0.9</v>
       </c>
       <c r="K33" s="10">
         <f>IFERROR(D33/E33,0)</f>
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="L33" s="10" t="str">
         <f>LEFT(B33,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N33">
         <f t="shared" si="1"/>
-        <v>-1.9000000000000001</v>
+        <v>-1.8</v>
       </c>
       <c r="O33">
         <f t="shared" si="7"/>
-        <v>-0.38</v>
+        <v>-0.36</v>
       </c>
       <c r="P33">
         <f t="shared" si="8"/>
@@ -5672,7 +5510,7 @@
       </c>
       <c r="Q33">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33">
         <f t="shared" si="10"/>
@@ -5680,7 +5518,7 @@
       </c>
       <c r="S33">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
@@ -5688,49 +5526,49 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C34">
-        <v>-12</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="D34">
-        <v>-2.4</v>
+        <v>-0.38</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" s="7">
         <f>IFERROR((F34/E34)*100,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J34" s="10">
         <f>IFERROR(C34/E34,0)</f>
-        <v>-6</v>
+        <v>-0.95000000000000007</v>
       </c>
       <c r="K34" s="10">
         <f>IFERROR(D34/E34,0)</f>
-        <v>-1.2</v>
+        <v>-0.19</v>
       </c>
       <c r="L34" s="10" t="str">
         <f>LEFT(B34,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N34">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="O34">
         <f t="shared" si="7"/>
-        <v>-2.4</v>
+        <v>-0.38</v>
       </c>
       <c r="P34">
         <f t="shared" si="8"/>
@@ -5738,7 +5576,7 @@
       </c>
       <c r="Q34">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34">
         <f t="shared" si="10"/>
@@ -5746,7 +5584,7 @@
       </c>
       <c r="S34">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
@@ -5754,57 +5592,57 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>-12</v>
       </c>
       <c r="D35">
-        <v>1.6</v>
+        <v>-2.4</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" s="7">
         <f>IFERROR((F35/E35)*100,0)</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J35" s="10">
         <f>IFERROR(C35/E35,0)</f>
-        <v>8</v>
+        <v>-6</v>
       </c>
       <c r="K35" s="10">
         <f>IFERROR(D35/E35,0)</f>
-        <v>1.6</v>
+        <v>-1.2</v>
       </c>
       <c r="L35" s="10" t="str">
         <f>LEFT(B35,3)</f>
-        <v>SEG</v>
+        <v>UEG</v>
       </c>
       <c r="N35">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>-12</v>
       </c>
       <c r="O35">
         <f t="shared" si="7"/>
-        <v>1.6</v>
+        <v>-2.4</v>
       </c>
       <c r="P35">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q35">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35">
         <f t="shared" si="10"/>
@@ -5812,7 +5650,7 @@
       </c>
       <c r="S35">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
@@ -5820,19 +5658,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="C36">
-        <v>1.2</v>
+        <v>14</v>
       </c>
       <c r="D36">
-        <v>0.24</v>
+        <v>2.8</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -5846,31 +5684,31 @@
       </c>
       <c r="J36" s="10">
         <f>IFERROR(C36/E36,0)</f>
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="K36" s="10">
         <f>IFERROR(D36/E36,0)</f>
-        <v>0.24</v>
+        <v>1.4</v>
       </c>
       <c r="L36" s="10" t="str">
         <f>LEFT(B36,3)</f>
-        <v>LEG</v>
+        <v>SEG</v>
       </c>
       <c r="N36">
         <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>14</v>
       </c>
       <c r="O36">
         <f t="shared" si="7"/>
-        <v>0.24</v>
+        <v>2.8</v>
       </c>
       <c r="P36">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q36">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36">
         <f t="shared" si="10"/>
@@ -5889,16 +5727,16 @@
         <v>97</v>
       </c>
       <c r="C37">
-        <v>-0.2</v>
+        <v>1.7</v>
       </c>
       <c r="D37">
-        <v>-0.04</v>
+        <v>0.34</v>
       </c>
       <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37">
         <v>1</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -5908,15 +5746,15 @@
       </c>
       <c r="I37" s="7">
         <f>IFERROR((F37/E37)*100,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J37" s="10">
         <f>IFERROR(C37/E37,0)</f>
-        <v>-0.2</v>
+        <v>0.85</v>
       </c>
       <c r="K37" s="10">
         <f>IFERROR(D37/E37,0)</f>
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="L37" s="10" t="str">
         <f>LEFT(B37,3)</f>
@@ -5924,19 +5762,19 @@
       </c>
       <c r="N37">
         <f t="shared" si="1"/>
-        <v>-0.2</v>
+        <v>1.7</v>
       </c>
       <c r="O37">
         <f t="shared" si="7"/>
-        <v>-0.04</v>
+        <v>0.34</v>
       </c>
       <c r="P37">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q37">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37">
         <f t="shared" si="10"/>
@@ -5952,19 +5790,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C38">
-        <v>-1.3</v>
+        <v>1.7000000000000002</v>
       </c>
       <c r="D38">
-        <v>-0.26</v>
+        <v>0.34000000000000008</v>
       </c>
       <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38">
         <v>1</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5974,35 +5812,35 @@
       </c>
       <c r="I38" s="7">
         <f>IFERROR((F38/E38)*100,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J38" s="10">
         <f>IFERROR(C38/E38,0)</f>
-        <v>-1.3</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="K38" s="10">
         <f>IFERROR(D38/E38,0)</f>
-        <v>-0.26</v>
+        <v>0.17000000000000004</v>
       </c>
       <c r="L38" s="10" t="str">
         <f>LEFT(B38,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N38">
         <f t="shared" si="1"/>
-        <v>-1.3</v>
+        <v>1.7000000000000002</v>
       </c>
       <c r="O38">
         <f t="shared" si="7"/>
-        <v>-0.26</v>
+        <v>0.34000000000000008</v>
       </c>
       <c r="P38">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38">
         <f t="shared" si="10"/>
@@ -6018,19 +5856,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C39">
-        <v>-5.8</v>
+        <v>15.6</v>
       </c>
       <c r="D39">
-        <v>-1.1599999999999999</v>
+        <v>3.12</v>
       </c>
       <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39">
         <v>1</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -6040,35 +5878,35 @@
       </c>
       <c r="I39" s="7">
         <f>IFERROR((F39/E39)*100,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J39" s="10">
         <f>IFERROR(C39/E39,0)</f>
-        <v>-5.8</v>
+        <v>7.8</v>
       </c>
       <c r="K39" s="10">
         <f>IFERROR(D39/E39,0)</f>
-        <v>-1.1599999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="L39" s="10" t="str">
         <f>LEFT(B39,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N39">
         <f t="shared" si="1"/>
-        <v>-5.8</v>
+        <v>15.6</v>
       </c>
       <c r="O39">
         <f t="shared" si="7"/>
-        <v>-1.1599999999999999</v>
+        <v>3.12</v>
       </c>
       <c r="P39">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39">
         <f t="shared" si="10"/>
@@ -6084,16 +5922,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C40">
-        <v>-6</v>
+        <v>-30.7</v>
       </c>
       <c r="D40">
-        <v>-1.2</v>
+        <v>-6.1400000000000006</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -6102,7 +5940,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="7">
         <f>IFERROR((F40/E40)*100,0)</f>
@@ -6110,11 +5948,11 @@
       </c>
       <c r="J40" s="10">
         <f>IFERROR(C40/E40,0)</f>
-        <v>-6</v>
+        <v>-15.35</v>
       </c>
       <c r="K40" s="10">
         <f>IFERROR(D40/E40,0)</f>
-        <v>-1.2</v>
+        <v>-3.0700000000000003</v>
       </c>
       <c r="L40" s="10" t="str">
         <f>LEFT(B40,3)</f>
@@ -6122,15 +5960,15 @@
       </c>
       <c r="N40">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-30.7</v>
       </c>
       <c r="O40">
         <f t="shared" si="7"/>
-        <v>-1.2</v>
+        <v>-6.1400000000000006</v>
       </c>
       <c r="P40">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40">
         <f t="shared" si="9"/>
@@ -6142,7 +5980,7 @@
       </c>
       <c r="S40">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -6150,13 +5988,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="C41">
-        <v>-6.9</v>
+        <v>-1.3</v>
       </c>
       <c r="D41">
-        <v>-1.3800000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -6176,23 +6014,23 @@
       </c>
       <c r="J41" s="10">
         <f>IFERROR(C41/E41,0)</f>
-        <v>-6.9</v>
+        <v>-1.3</v>
       </c>
       <c r="K41" s="10">
         <f>IFERROR(D41/E41,0)</f>
-        <v>-1.3800000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="L41" s="10" t="str">
         <f>LEFT(B41,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N41">
         <f t="shared" si="1"/>
-        <v>-6.9</v>
+        <v>-1.3</v>
       </c>
       <c r="O41">
         <f t="shared" si="7"/>
-        <v>-1.3800000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="P41">
         <f t="shared" si="8"/>
@@ -6216,13 +6054,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C42">
-        <v>-18.2</v>
+        <v>-6</v>
       </c>
       <c r="D42">
-        <v>-3.64</v>
+        <v>-1.2</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -6242,11 +6080,11 @@
       </c>
       <c r="J42" s="10">
         <f>IFERROR(C42/E42,0)</f>
-        <v>-18.2</v>
+        <v>-6</v>
       </c>
       <c r="K42" s="10">
         <f>IFERROR(D42/E42,0)</f>
-        <v>-3.64</v>
+        <v>-1.2</v>
       </c>
       <c r="L42" s="10" t="str">
         <f>LEFT(B42,3)</f>
@@ -6254,11 +6092,11 @@
       </c>
       <c r="N42">
         <f t="shared" si="1"/>
-        <v>-18.2</v>
+        <v>-6</v>
       </c>
       <c r="O42">
         <f t="shared" si="7"/>
-        <v>-3.64</v>
+        <v>-1.2</v>
       </c>
       <c r="P42">
         <f t="shared" si="8"/>
@@ -6347,7 +6185,7 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="5" t="s">
         <v>85</v>
       </c>
       <c r="C44">
@@ -6545,7 +6383,7 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="5" t="s">
         <v>104</v>
       </c>
       <c r="C47">
@@ -6611,7 +6449,7 @@
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="5" t="s">
         <v>106</v>
       </c>
       <c r="C48">
@@ -6677,7 +6515,7 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="5" t="s">
         <v>107</v>
       </c>
       <c r="C49">
@@ -7601,7 +7439,7 @@
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="5" t="s">
         <v>100</v>
       </c>
       <c r="C63">
@@ -7667,7 +7505,7 @@
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C64">
@@ -7733,7 +7571,7 @@
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="5" t="s">
         <v>90</v>
       </c>
       <c r="C65">
@@ -7805,8 +7643,8 @@
       <c r="B75" s="8"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L76">
-    <sortCondition descending="1" ref="E2:E76"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L65">
+    <sortCondition descending="1" ref="E2:E65"/>
   </sortState>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="dataBar" priority="10">
@@ -8113,11 +7951,11 @@
         <f>COUNTIF(H3:AB3, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -8147,7 +7985,7 @@
         <f>COUNTIF(H4:AB4, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H4" s="17"/>
+      <c r="H4" s="18"/>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
     </row>
@@ -8179,7 +8017,7 @@
         <f>COUNTIF(H5:AB5, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H5" s="17"/>
+      <c r="H5" s="18"/>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
     </row>
@@ -8247,7 +8085,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B8">
         <f>SUM(H8:AB8)</f>
@@ -8273,12 +8111,12 @@
         <f>COUNTIF(H8:AB8, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H8" s="17"/>
+      <c r="H8" s="18"/>
       <c r="I8" s="17"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B9">
         <f>SUM(H9:AB9)</f>
@@ -8304,7 +8142,8 @@
         <f>COUNTIF(H9:AB9, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H9" s="17"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -8334,11 +8173,13 @@
         <f>COUNTIF(H10:AB10, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H10" s="17"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B11">
         <f>SUM(H11:AB11)</f>
@@ -8365,10 +8206,12 @@
         <v>0</v>
       </c>
       <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B12">
         <f>SUM(H12:AB12)</f>
@@ -8395,10 +8238,11 @@
         <v>0</v>
       </c>
       <c r="H12" s="18"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="B13">
         <f>SUM(H13:AB13)</f>
@@ -8425,10 +8269,11 @@
         <v>0</v>
       </c>
       <c r="H13" s="18"/>
+      <c r="I13" s="17"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B14">
         <f>SUM(H14:AB14)</f>
@@ -8454,11 +8299,13 @@
         <f>COUNTIF(H14:AB14, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H14" s="17"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B15">
         <f>SUM(H15:AB15)</f>
@@ -8485,10 +8332,11 @@
         <v>0</v>
       </c>
       <c r="H15" s="18"/>
+      <c r="I15" s="15"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="B16">
         <f>SUM(H16:AB16)</f>
@@ -8519,7 +8367,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B17">
         <f>SUM(H17:AB17)</f>
@@ -8549,7 +8397,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B18">
         <f>SUM(H18:AB18)</f>
@@ -8576,10 +8424,12 @@
         <v>0</v>
       </c>
       <c r="H18" s="18"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B19">
         <f>SUM(H19:AB19)</f>
@@ -8610,7 +8460,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="B20">
         <f>SUM(H20:AB20)</f>
@@ -8636,7 +8486,7 @@
         <f>COUNTIF(H20:AB20, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H20" s="17"/>
+      <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -8757,7 +8607,6 @@
         <v>0</v>
       </c>
       <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -8787,6 +8636,8 @@
         <f>COUNTIF(H25:AB25, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -8816,6 +8667,7 @@
         <f>COUNTIF(H26:AB26, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H26" s="17"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -8845,10 +8697,11 @@
         <f>COUNTIF(H27:AB27, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B28">
         <f>SUM(H28:AB28)</f>
@@ -8874,6 +8727,7 @@
         <f>COUNTIF(H28:AB28, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H28" s="17"/>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
@@ -8881,7 +8735,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B29">
         <f>SUM(H29:AB29)</f>
@@ -8907,6 +8761,7 @@
         <f>COUNTIF(H29:AB29, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -8936,11 +8791,11 @@
         <f>COUNTIF(H30:AB30, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H30" s="15"/>
+      <c r="H30" s="19"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="B31">
         <f>SUM(H31:AB31)</f>
@@ -8966,10 +8821,12 @@
         <f>COUNTIF(H31:AB31, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="B32">
         <f>SUM(H32:AB32)</f>
@@ -8998,7 +8855,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B33">
         <f>SUM(H33:AB33)</f>
@@ -9027,7 +8884,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="B34">
         <f>SUM(H34:AB34)</f>
@@ -9057,7 +8914,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="B35">
         <f>SUM(H35:AB35)</f>
@@ -9086,7 +8943,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="B36">
         <f>SUM(H36:AB36)</f>
@@ -9112,10 +8969,11 @@
         <f>COUNTIF(H36:AB36, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H36" s="15"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="B37">
         <f>SUM(H37:AB37)</f>
@@ -9141,6 +8999,8 @@
         <f>COUNTIF(H37:AB37, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -9170,10 +9030,11 @@
         <f>COUNTIF(H38:AB38, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H38" s="15"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B39">
         <f>SUM(H39:AB39)</f>
@@ -9203,7 +9064,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="B40">
         <f>SUM(H40:AB40)</f>
@@ -9233,7 +9094,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="B41">
         <f>SUM(H41:AB41)</f>
@@ -9265,7 +9126,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="B42">
         <f>SUM(H42:AB42)</f>
@@ -9291,10 +9152,11 @@
         <f>COUNTIF(H42:AB42, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H42" s="15"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B43">
         <f>SUM(H43:AB43)</f>
@@ -9320,6 +9182,7 @@
         <f>COUNTIF(H43:AB43, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H43" s="15"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -10000,8 +9863,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB66">
-    <sortCondition descending="1" ref="D3:D66"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB66">
+    <sortCondition descending="1" ref="D2:D66"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC2AEDA-D1CB-43AE-A066-EAF4561E280C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4850DF-602C-41FA-AEB2-166B8692F6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
     <sheet name="СтатПоТипу" sheetId="6" r:id="rId2"/>
-    <sheet name="Результаты" sheetId="4" r:id="rId3"/>
-    <sheet name="СумматорСегодня" sheetId="5" r:id="rId4"/>
+    <sheet name="Динамика" sheetId="7" r:id="rId3"/>
+    <sheet name="Результаты" sheetId="4" r:id="rId4"/>
+    <sheet name="СумматорСегодня" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId5"/>
-    <pivotCache cacheId="10" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="4" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="148">
   <si>
     <t>AQUA</t>
   </si>
@@ -644,65 +645,1365 @@
 </styleSheet>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46286.961164004628" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="41" xr:uid="{93B0B297-F304-40FC-B21C-BCAAF0FA44CB}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:L42" sheet="Результаты"/>
-  </cacheSource>
-  <cacheFields count="12">
-    <cacheField name="Номер" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="41"/>
-    </cacheField>
-    <cacheField name="Стратегия" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Абс" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-38.4" maxValue="68.399999999999991"/>
-    </cacheField>
-    <cacheField name="Отн" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-7.68" maxValue="13.680000000000003"/>
-    </cacheField>
-    <cacheField name="Кол-во" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="33"/>
-    </cacheField>
-    <cacheField name="Прибыль" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="21"/>
-    </cacheField>
-    <cacheField name="Нейтрал" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="Убыток" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="14"/>
-    </cacheField>
-    <cacheField name="ПроцПД" numFmtId="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="100"/>
-    </cacheField>
-    <cacheField name="САП" numFmtId="2">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-18.2" maxValue="8"/>
-    </cacheField>
-    <cacheField name="СОП" numFmtId="2">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-3.64" maxValue="1.6"/>
-    </cacheField>
-    <cacheField name="Тип" numFmtId="2">
-      <sharedItems count="6">
-        <s v="PEG"/>
-        <s v="WEG"/>
-        <s v="LEG"/>
-        <s v="VEG"/>
-        <s v="UEG"/>
-        <s v="SEG"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Динамика!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LEG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Динамика!$B$2:$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>46285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46287</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46288</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Динамика!$B$3:$E$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-20.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-39.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-22.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C8F5-4770-9D74-C7A222ED5A91}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Динамика!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PEG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Динамика!$B$2:$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>46285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46287</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46288</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Динамика!$B$4:$E$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C8F5-4770-9D74-C7A222ED5A91}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Динамика!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SEG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Динамика!$B$2:$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>46285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46287</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46288</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Динамика!$B$5:$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.100000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C8F5-4770-9D74-C7A222ED5A91}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Динамика!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>UEG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Динамика!$B$2:$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>46285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46287</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46288</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Динамика!$B$6:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-21</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-41</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C8F5-4770-9D74-C7A222ED5A91}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Динамика!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>VEG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Динамика!$B$2:$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>46285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46287</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46288</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Динамика!$B$7:$E$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-22.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-C8F5-4770-9D74-C7A222ED5A91}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Динамика!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>WEG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Динамика!$B$2:$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>46285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46287</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46288</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Динамика!$B$8:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>44.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>59.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-C8F5-4770-9D74-C7A222ED5A91}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1657593872"/>
+        <c:axId val="1332094976"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1657593872"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1332094976"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1332094976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1657593872"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>590549</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>104774</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C4DE348-C853-4C12-8B37-B46EB6F1F415}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46287.786514004627" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="64" xr:uid="{1976E921-BE3A-4FF1-A5EF-18E3F04892B4}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:L65" sheet="Результаты"/>
@@ -760,586 +2061,65 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="41">
-  <r>
-    <n v="1"/>
-    <s v="PEG17_PHOENIX"/>
-    <n v="68.399999999999991"/>
-    <n v="13.680000000000003"/>
-    <n v="33"/>
-    <n v="21"/>
-    <n v="0"/>
-    <n v="12"/>
-    <n v="63.636363636363633"/>
-    <n v="2.0727272727272723"/>
-    <n v="0.41454545454545466"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <s v="PEG11_KUSURUKEN"/>
-    <n v="43.3"/>
-    <n v="8.66"/>
-    <n v="32"/>
-    <n v="17"/>
-    <n v="1"/>
-    <n v="14"/>
-    <n v="53.125"/>
-    <n v="1.3531249999999999"/>
-    <n v="0.270625"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <s v="WEG3_BATYA"/>
-    <n v="26.6"/>
-    <n v="5.32"/>
-    <n v="31"/>
-    <n v="18"/>
-    <n v="0"/>
-    <n v="13"/>
-    <n v="58.064516129032263"/>
-    <n v="0.85806451612903234"/>
-    <n v="0.17161290322580647"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <s v="LEG2_DRINKER"/>
-    <n v="8.1999999999999993"/>
-    <n v="1.6400000000000008"/>
-    <n v="18"/>
-    <n v="8"/>
-    <n v="0"/>
-    <n v="10"/>
-    <n v="44.444444444444443"/>
-    <n v="0.45555555555555549"/>
-    <n v="9.1111111111111157E-2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <s v="VEG1_VENUS"/>
-    <n v="-18.100000000000001"/>
-    <n v="-3.6199999999999997"/>
-    <n v="18"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="9"/>
-    <n v="50"/>
-    <n v="-1.0055555555555555"/>
-    <n v="-0.2011111111111111"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <s v="LEG1_PIN"/>
-    <n v="18.099999999999998"/>
-    <n v="3.62"/>
-    <n v="15"/>
-    <n v="7"/>
-    <n v="1"/>
-    <n v="7"/>
-    <n v="46.666666666666664"/>
-    <n v="1.2066666666666666"/>
-    <n v="0.24133333333333334"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <s v="LEG2_FENNEC"/>
-    <n v="13.1"/>
-    <n v="2.62"/>
-    <n v="15"/>
-    <n v="10"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="66.666666666666657"/>
-    <n v="0.87333333333333329"/>
-    <n v="0.17466666666666666"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <s v="PEG18_BLAZE"/>
-    <n v="-38.4"/>
-    <n v="-7.68"/>
-    <n v="12"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="7"/>
-    <n v="33.333333333333329"/>
-    <n v="-3.1999999999999997"/>
-    <n v="-0.64"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <s v="WEG4_PUPPY"/>
-    <n v="17.5"/>
-    <n v="3.4999999999999996"/>
-    <n v="10"/>
-    <n v="6"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="60"/>
-    <n v="1.75"/>
-    <n v="0.35"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <s v="LEG2_LYNX"/>
-    <n v="-1.3000000000000007"/>
-    <n v="-0.26000000000000023"/>
-    <n v="10"/>
-    <n v="6"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="60"/>
-    <n v="-0.13000000000000006"/>
-    <n v="-2.6000000000000023E-2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="11"/>
-    <s v="LEG1_CC2"/>
-    <n v="-8.8999999999999986"/>
-    <n v="-1.7799999999999998"/>
-    <n v="8"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="50"/>
-    <n v="-1.1124999999999998"/>
-    <n v="-0.22249999999999998"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="12"/>
-    <s v="PEG4_UNIVERSAL"/>
-    <n v="3.8000000000000007"/>
-    <n v="0.76000000000000023"/>
-    <n v="7"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="42.857142857142854"/>
-    <n v="0.54285714285714293"/>
-    <n v="0.10857142857142861"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="13"/>
-    <s v="UEG6_PIGEON"/>
-    <n v="-8.4999999999999982"/>
-    <n v="-1.6999999999999997"/>
-    <n v="7"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="6"/>
-    <n v="14.285714285714285"/>
-    <n v="-1.214285714285714"/>
-    <n v="-0.24285714285714283"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="14"/>
-    <s v="UEG6_VULTURE"/>
-    <n v="-10.799999999999999"/>
-    <n v="-2.16"/>
-    <n v="7"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="28.571428571428569"/>
-    <n v="-1.5428571428571427"/>
-    <n v="-0.30857142857142861"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="15"/>
-    <s v="PEG14_RENEGADE"/>
-    <n v="3.3000000000000003"/>
-    <n v="0.66000000000000014"/>
-    <n v="6"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="50"/>
-    <n v="0.55000000000000004"/>
-    <n v="0.11000000000000003"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="16"/>
-    <s v="UEG6_ADVENTURE"/>
-    <n v="-0.70000000000000062"/>
-    <n v="-0.14000000000000001"/>
-    <n v="6"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="33.333333333333329"/>
-    <n v="-0.11666666666666677"/>
-    <n v="-2.3333333333333334E-2"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="17"/>
-    <s v="PEG18_UTER2"/>
-    <n v="-7.8000000000000007"/>
-    <n v="-1.5600000000000003"/>
-    <n v="6"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="50"/>
-    <n v="-1.3"/>
-    <n v="-0.26000000000000006"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="18"/>
-    <s v="LEG1_BIBI2"/>
-    <n v="-25"/>
-    <n v="-4.9999999999999991"/>
-    <n v="6"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="16.666666666666664"/>
-    <n v="-4.166666666666667"/>
-    <n v="-0.83333333333333315"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="19"/>
-    <s v="PEG4_U3"/>
-    <n v="2.8"/>
-    <n v="0.55999999999999994"/>
-    <n v="5"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="80"/>
-    <n v="0.55999999999999994"/>
-    <n v="0.11199999999999999"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="20"/>
-    <s v="SEG3_FORCE"/>
-    <n v="1.9000000000000004"/>
-    <n v="0.37999999999999989"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="60"/>
-    <n v="0.38000000000000006"/>
-    <n v="7.5999999999999984E-2"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="21"/>
-    <s v="UEG4_PELICAN"/>
-    <n v="-2.9000000000000004"/>
-    <n v="-0.58000000000000007"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="60"/>
-    <n v="-0.58000000000000007"/>
-    <n v="-0.11600000000000002"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="22"/>
-    <s v="PEG19_ANUBARAK"/>
-    <n v="-3.8000000000000007"/>
-    <n v="-0.76000000000000023"/>
-    <n v="5"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="40"/>
-    <n v="-0.76000000000000012"/>
-    <n v="-0.15200000000000005"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="23"/>
-    <s v="PEG18_UTER"/>
-    <n v="-6.2"/>
-    <n v="-1.24"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="60"/>
-    <n v="-1.24"/>
-    <n v="-0.248"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="24"/>
-    <s v="LEG1_IRONANNY2"/>
-    <n v="-7.5"/>
-    <n v="-1.5"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="20"/>
-    <n v="-1.5"/>
-    <n v="-0.3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="25"/>
-    <s v="PEG18_DIABLO2"/>
-    <n v="-9.1"/>
-    <n v="-1.82"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="20"/>
-    <n v="-1.8199999999999998"/>
-    <n v="-0.36399999999999999"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="26"/>
-    <s v="LEG1_LAKSAe"/>
-    <n v="6"/>
-    <n v="1.2"/>
-    <n v="3"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="2"/>
-    <n v="0.39999999999999997"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="27"/>
-    <s v="PEG26_UNKNOWN"/>
-    <n v="-3.4"/>
-    <n v="-0.67999999999999994"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="33.333333333333329"/>
-    <n v="-1.1333333333333333"/>
-    <n v="-0.22666666666666666"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="28"/>
-    <s v="LEG2_DRG"/>
-    <n v="-12"/>
-    <n v="-2.4"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="33.333333333333329"/>
-    <n v="-4"/>
-    <n v="-0.79999999999999993"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="29"/>
-    <s v="UEG7_ADVENTURE"/>
-    <n v="1.0000000000000002"/>
-    <n v="0.2"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="0.50000000000000011"/>
-    <n v="0.1"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="30"/>
-    <s v="PEG13_DWDDCr"/>
-    <n v="1"/>
-    <n v="0.2"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="0.5"/>
-    <n v="0.1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="31"/>
-    <s v="LEG2_HOTS"/>
-    <n v="-1.8"/>
-    <n v="-0.36"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="-0.9"/>
-    <n v="-0.18"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="32"/>
-    <s v="PEG14_RANGER"/>
-    <n v="-1.9000000000000001"/>
-    <n v="-0.38"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="-0.95000000000000007"/>
-    <n v="-0.19"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="33"/>
-    <s v="UEG4_FALCON"/>
-    <n v="-12"/>
-    <n v="-2.4"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="-6"/>
-    <n v="-1.2"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="34"/>
-    <s v="SEG1_LITE"/>
-    <n v="8"/>
-    <n v="1.6"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="8"/>
-    <n v="1.6"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="35"/>
-    <s v="LEG2_LOGAN"/>
-    <n v="1.2"/>
-    <n v="0.24"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="1.2"/>
-    <n v="0.24"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="36"/>
-    <s v="UEG7_PIGEON"/>
-    <n v="-0.2"/>
-    <n v="-0.04"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-0.2"/>
-    <n v="-0.04"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="37"/>
-    <s v="PEG18_ANDUIN"/>
-    <n v="-1.3"/>
-    <n v="-0.26"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-1.3"/>
-    <n v="-0.26"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="38"/>
-    <s v="LEG1_IGOGOSHA2"/>
-    <n v="-5.8"/>
-    <n v="-1.1599999999999999"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-5.8"/>
-    <n v="-1.1599999999999999"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="39"/>
-    <s v="LEG1_PHOGA"/>
-    <n v="-6"/>
-    <n v="-1.2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-6"/>
-    <n v="-1.2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="40"/>
-    <s v="UEG6_SHERIFF"/>
-    <n v="-6.9"/>
-    <n v="-1.3800000000000001"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-6.9"/>
-    <n v="-1.3800000000000001"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="41"/>
-    <s v="LEG2_ALKASH"/>
-    <n v="-18.2"/>
-    <n v="-3.64"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-18.2"/>
-    <n v="-3.64"/>
-    <x v="2"/>
-  </r>
-</pivotCacheRecords>
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46288.785760416664" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="41" xr:uid="{93B0B297-F304-40FC-B21C-BCAAF0FA44CB}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:L42" sheet="Результаты"/>
+  </cacheSource>
+  <cacheFields count="12">
+    <cacheField name="Номер" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="41"/>
+    </cacheField>
+    <cacheField name="Стратегия" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Абс" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-44.3" maxValue="111.79999999999998"/>
+    </cacheField>
+    <cacheField name="Отн" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-8.86" maxValue="22.360000000000007"/>
+    </cacheField>
+    <cacheField name="Кол-во" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="44"/>
+    </cacheField>
+    <cacheField name="Прибыль" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="30"/>
+    </cacheField>
+    <cacheField name="Нейтрал" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
+    </cacheField>
+    <cacheField name="Убыток" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="15"/>
+    </cacheField>
+    <cacheField name="ПроцПД" numFmtId="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="100"/>
+    </cacheField>
+    <cacheField name="САП" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-11.533333333333333" maxValue="5.7333333333333334"/>
+    </cacheField>
+    <cacheField name="СОП" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-2.3066666666666671" maxValue="1.1466666666666667"/>
+    </cacheField>
+    <cacheField name="Тип" numFmtId="2">
+      <sharedItems count="6">
+        <s v="PEG"/>
+        <s v="WEG"/>
+        <s v="LEG"/>
+        <s v="VEG"/>
+        <s v="UEG"/>
+        <s v="SEG"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="64">
   <r>
     <n v="1"/>
@@ -2240,8 +3020,587 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="41">
+  <r>
+    <n v="1"/>
+    <s v="PEG17_PHOENIX"/>
+    <n v="111.79999999999998"/>
+    <n v="22.360000000000007"/>
+    <n v="44"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="14"/>
+    <n v="68.181818181818173"/>
+    <n v="2.5409090909090906"/>
+    <n v="0.50818181818181829"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <s v="PEG11_KUSURUKEN"/>
+    <n v="41.9"/>
+    <n v="8.3800000000000008"/>
+    <n v="34"/>
+    <n v="18"/>
+    <n v="1"/>
+    <n v="15"/>
+    <n v="52.941176470588239"/>
+    <n v="1.2323529411764707"/>
+    <n v="0.24647058823529414"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <s v="WEG3_BATYA"/>
+    <n v="41.900000000000006"/>
+    <n v="8.3800000000000008"/>
+    <n v="33"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="13"/>
+    <n v="60.606060606060609"/>
+    <n v="1.2696969696969698"/>
+    <n v="0.25393939393939396"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <s v="LEG2_DRINKER"/>
+    <n v="10"/>
+    <n v="2.0000000000000009"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="10"/>
+    <n v="50"/>
+    <n v="0.5"/>
+    <n v="0.10000000000000005"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <s v="VEG1_VENUS"/>
+    <n v="-22.700000000000003"/>
+    <n v="-4.5399999999999991"/>
+    <n v="19"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="10"/>
+    <n v="47.368421052631575"/>
+    <n v="-1.1947368421052633"/>
+    <n v="-0.23894736842105258"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <s v="LEG2_FENNEC"/>
+    <n v="34"/>
+    <n v="6.8000000000000007"/>
+    <n v="19"/>
+    <n v="14"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="73.68421052631578"/>
+    <n v="1.7894736842105263"/>
+    <n v="0.35789473684210532"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <s v="LEG1_PIN"/>
+    <n v="11.2"/>
+    <n v="2.2400000000000002"/>
+    <n v="17"/>
+    <n v="7"/>
+    <n v="1"/>
+    <n v="9"/>
+    <n v="41.17647058823529"/>
+    <n v="0.6588235294117647"/>
+    <n v="0.13176470588235295"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <s v="PEG18_BLAZE"/>
+    <n v="-44.3"/>
+    <n v="-8.86"/>
+    <n v="14"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="8"/>
+    <n v="35.714285714285715"/>
+    <n v="-3.1642857142857141"/>
+    <n v="-0.63285714285714278"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <s v="LEG2_LYNX"/>
+    <n v="17.899999999999999"/>
+    <n v="3.58"/>
+    <n v="14"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="71.428571428571431"/>
+    <n v="1.2785714285714285"/>
+    <n v="0.25571428571428573"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <s v="PEG4_UNIVERSAL"/>
+    <n v="10.9"/>
+    <n v="2.1800000000000006"/>
+    <n v="13"/>
+    <n v="7"/>
+    <n v="1"/>
+    <n v="5"/>
+    <n v="53.846153846153847"/>
+    <n v="0.83846153846153848"/>
+    <n v="0.16769230769230775"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <s v="UEG6_ADVENTURE"/>
+    <n v="5.5999999999999988"/>
+    <n v="1.1199999999999997"/>
+    <n v="12"/>
+    <n v="5"/>
+    <n v="2"/>
+    <n v="5"/>
+    <n v="41.666666666666671"/>
+    <n v="0.46666666666666656"/>
+    <n v="9.333333333333331E-2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <s v="UEG6_PIGEON"/>
+    <n v="-0.89999999999999813"/>
+    <n v="-0.17999999999999988"/>
+    <n v="11"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="7"/>
+    <n v="36.363636363636367"/>
+    <n v="-8.1818181818181651E-2"/>
+    <n v="-1.6363636363636355E-2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <s v="WEG4_PUPPY"/>
+    <n v="17.5"/>
+    <n v="3.4999999999999996"/>
+    <n v="10"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="60"/>
+    <n v="1.75"/>
+    <n v="0.35"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <s v="LEG1_CC2"/>
+    <n v="-8.8999999999999986"/>
+    <n v="-1.7799999999999998"/>
+    <n v="8"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="50"/>
+    <n v="-1.1124999999999998"/>
+    <n v="-0.22249999999999998"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <s v="UEG6_VULTURE"/>
+    <n v="-9.6999999999999993"/>
+    <n v="-1.9400000000000002"/>
+    <n v="8"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="37.5"/>
+    <n v="-1.2124999999999999"/>
+    <n v="-0.24250000000000002"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <s v="LEG1_BIBI2"/>
+    <n v="-9.4"/>
+    <n v="-1.879999999999999"/>
+    <n v="8"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="37.5"/>
+    <n v="-1.175"/>
+    <n v="-0.23499999999999988"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <s v="PEG18_UTER2"/>
+    <n v="-13"/>
+    <n v="-2.6000000000000005"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="42.857142857142854"/>
+    <n v="-1.8571428571428572"/>
+    <n v="-0.3714285714285715"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <s v="PEG4_U3"/>
+    <n v="1.1999999999999993"/>
+    <n v="0.23999999999999988"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="71.428571428571431"/>
+    <n v="0.17142857142857132"/>
+    <n v="3.4285714285714267E-2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <s v="PEG14_RENEGADE"/>
+    <n v="3.3000000000000003"/>
+    <n v="0.66000000000000014"/>
+    <n v="6"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="50"/>
+    <n v="0.55000000000000004"/>
+    <n v="0.11000000000000003"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <s v="SEG3_FORCE"/>
+    <n v="1.9000000000000004"/>
+    <n v="0.37999999999999989"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="60"/>
+    <n v="0.38000000000000006"/>
+    <n v="7.5999999999999984E-2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <s v="UEG4_PELICAN"/>
+    <n v="-2.9000000000000004"/>
+    <n v="-0.58000000000000007"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="60"/>
+    <n v="-0.58000000000000007"/>
+    <n v="-0.11600000000000002"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <s v="PEG19_ANUBARAK"/>
+    <n v="-3.8000000000000007"/>
+    <n v="-0.76000000000000023"/>
+    <n v="5"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="40"/>
+    <n v="-0.76000000000000012"/>
+    <n v="-0.15200000000000005"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <s v="PEG18_UTER"/>
+    <n v="-6.2"/>
+    <n v="-1.24"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="60"/>
+    <n v="-1.24"/>
+    <n v="-0.248"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <s v="LEG1_IRONANNY2"/>
+    <n v="-7.5"/>
+    <n v="-1.5"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="-1.5"/>
+    <n v="-0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <s v="PEG18_DIABLO2"/>
+    <n v="-9.1"/>
+    <n v="-1.82"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="-1.8199999999999998"/>
+    <n v="-0.36399999999999999"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <s v="PEG26_UNKNOWN"/>
+    <n v="-7.5"/>
+    <n v="-1.5"/>
+    <n v="5"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="40"/>
+    <n v="-1.5"/>
+    <n v="-0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <s v="LEG2_LOGAN"/>
+    <n v="-5.6000000000000014"/>
+    <n v="-1.1200000000000003"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="75"/>
+    <n v="-1.4000000000000004"/>
+    <n v="-0.28000000000000008"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <s v="LEG1_LAKSAe"/>
+    <n v="6"/>
+    <n v="1.2"/>
+    <n v="3"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="2"/>
+    <n v="0.39999999999999997"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <s v="LEG2_DRG"/>
+    <n v="-12"/>
+    <n v="-2.4"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="33.333333333333329"/>
+    <n v="-4"/>
+    <n v="-0.79999999999999993"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <s v="SEG1_LITE"/>
+    <n v="16.2"/>
+    <n v="3.2399999999999998"/>
+    <n v="3"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="5.3999999999999995"/>
+    <n v="1.0799999999999998"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <s v="UEG7_PIGEON"/>
+    <n v="-0.19999999999999996"/>
+    <n v="-3.999999999999998E-2"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="33.333333333333329"/>
+    <n v="-6.6666666666666652E-2"/>
+    <n v="-1.3333333333333327E-2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <s v="LEG1_IGOGOSHA2"/>
+    <n v="5.8"/>
+    <n v="1.1599999999999999"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="66.666666666666657"/>
+    <n v="1.9333333333333333"/>
+    <n v="0.38666666666666666"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <s v="UEG6_SHERIFF"/>
+    <n v="17.2"/>
+    <n v="3.44"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="66.666666666666657"/>
+    <n v="5.7333333333333334"/>
+    <n v="1.1466666666666667"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <s v="LEG2_ALKASH"/>
+    <n v="-34.6"/>
+    <n v="-6.9200000000000008"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="-11.533333333333333"/>
+    <n v="-2.3066666666666671"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <s v="UEG7_ADVENTURE"/>
+    <n v="1.0000000000000002"/>
+    <n v="0.2"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="0.50000000000000011"/>
+    <n v="0.1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <s v="PEG13_DWDDCr"/>
+    <n v="1"/>
+    <n v="0.2"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="0.5"/>
+    <n v="0.1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <s v="LEG2_HOTS"/>
+    <n v="-1.8"/>
+    <n v="-0.36"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="-0.9"/>
+    <n v="-0.18"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <s v="PEG14_RANGER"/>
+    <n v="-1.9000000000000001"/>
+    <n v="-0.38"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="-0.95000000000000007"/>
+    <n v="-0.19"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <s v="UEG4_FALCON"/>
+    <n v="-12"/>
+    <n v="-2.4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="-6"/>
+    <n v="-1.2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <s v="PEG18_ANDUIN"/>
+    <n v="-1.3"/>
+    <n v="-0.26"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="-1.3"/>
+    <n v="-0.26"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="41"/>
+    <s v="LEG1_PHOGA"/>
+    <n v="-6"/>
+    <n v="-1.2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="-6"/>
+    <n v="-1.2"/>
+    <x v="2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C4CB1275-447E-4587-B9C3-BDD7EB80BE41}" name="Сводная таблица2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C4CB1275-447E-4587-B9C3-BDD7EB80BE41}" name="Сводная таблица2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A12:G19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -2337,7 +3696,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5C6C209-71EC-45CD-876E-D40B4E36B838}" name="Сводная таблица1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5C6C209-71EC-45CD-876E-D40B4E36B838}" name="Сводная таблица1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:G10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -3128,7 +4487,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
-        <v>46286</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3159,22 +4518,22 @@
         <v>136</v>
       </c>
       <c r="B13" s="12">
-        <v>-39.900000000000006</v>
+        <v>-0.90000000000001545</v>
       </c>
       <c r="C13" s="12">
-        <v>-7.9799999999999969</v>
+        <v>-0.17999999999999994</v>
       </c>
       <c r="D13" s="12">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="E13" s="12">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F13" s="12">
         <v>1</v>
       </c>
       <c r="G13" s="12">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3182,22 +4541,22 @@
         <v>137</v>
       </c>
       <c r="B14" s="12">
-        <v>50.699999999999982</v>
+        <v>83</v>
       </c>
       <c r="C14" s="12">
-        <v>10.140000000000004</v>
+        <v>16.600000000000005</v>
       </c>
       <c r="D14" s="12">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="E14" s="12">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="F14" s="12">
         <v>4</v>
       </c>
       <c r="G14" s="12">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3205,16 +4564,16 @@
         <v>138</v>
       </c>
       <c r="B15" s="12">
-        <v>9.9</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="C15" s="12">
-        <v>1.98</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="D15" s="12">
+        <v>8</v>
+      </c>
+      <c r="E15" s="12">
         <v>6</v>
-      </c>
-      <c r="E15" s="12">
-        <v>4</v>
       </c>
       <c r="F15" s="12">
         <v>0</v>
@@ -3228,22 +4587,22 @@
         <v>139</v>
       </c>
       <c r="B16" s="12">
-        <v>-41</v>
+        <v>-1.8999999999999986</v>
       </c>
       <c r="C16" s="12">
-        <v>-8.1999999999999993</v>
+        <v>-0.38000000000000034</v>
       </c>
       <c r="D16" s="12">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E16" s="12">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F16" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="12">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3251,13 +4610,13 @@
         <v>140</v>
       </c>
       <c r="B17" s="12">
-        <v>-18.100000000000001</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="C17" s="12">
-        <v>-3.6199999999999997</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="D17" s="12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17" s="12">
         <v>9</v>
@@ -3266,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3274,16 +4633,16 @@
         <v>141</v>
       </c>
       <c r="B18" s="12">
-        <v>44.1</v>
+        <v>59.400000000000006</v>
       </c>
       <c r="C18" s="12">
-        <v>8.82</v>
+        <v>11.88</v>
       </c>
       <c r="D18" s="12">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E18" s="12">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F18" s="12">
         <v>1</v>
@@ -3297,22 +4656,22 @@
         <v>134</v>
       </c>
       <c r="B19" s="12">
-        <v>5.6999999999999744</v>
+        <v>135</v>
       </c>
       <c r="C19" s="12">
-        <v>1.1400000000000095</v>
+        <v>27.000000000000007</v>
       </c>
       <c r="D19" s="12">
-        <v>309</v>
+        <v>376</v>
       </c>
       <c r="E19" s="12">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="F19" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G19" s="12">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3321,6 +4680,299 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8DFA0FD-4A38-4441-810F-67EAE4BA7EB9}">
+  <dimension ref="A2:X16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="24" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B2" s="16">
+        <v>46285</v>
+      </c>
+      <c r="C2" s="16">
+        <v>46286</v>
+      </c>
+      <c r="D2" s="16">
+        <v>46287</v>
+      </c>
+      <c r="E2" s="16">
+        <v>46288</v>
+      </c>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3">
+        <v>-20.100000000000001</v>
+      </c>
+      <c r="C3">
+        <v>-39.9</v>
+      </c>
+      <c r="D3">
+        <v>-22.1</v>
+      </c>
+      <c r="E3">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4">
+        <v>19.7</v>
+      </c>
+      <c r="C4">
+        <v>50.7</v>
+      </c>
+      <c r="D4">
+        <v>68.3</v>
+      </c>
+      <c r="E4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5">
+        <v>1.9</v>
+      </c>
+      <c r="C5">
+        <v>9.9</v>
+      </c>
+      <c r="D5">
+        <v>15.9</v>
+      </c>
+      <c r="E5">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6">
+        <v>-21</v>
+      </c>
+      <c r="C6">
+        <v>-41</v>
+      </c>
+      <c r="D6">
+        <v>-1.4</v>
+      </c>
+      <c r="E6">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7">
+        <v>-18.100000000000001</v>
+      </c>
+      <c r="C7">
+        <v>-18.100000000000001</v>
+      </c>
+      <c r="D7">
+        <v>-18.100000000000001</v>
+      </c>
+      <c r="E7">
+        <v>-22.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8">
+        <v>44.5</v>
+      </c>
+      <c r="C8">
+        <v>44.1</v>
+      </c>
+      <c r="D8">
+        <v>45.1</v>
+      </c>
+      <c r="E8">
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B10" s="16">
+        <f>B2</f>
+        <v>46285</v>
+      </c>
+      <c r="C10" s="16">
+        <f t="shared" ref="C10:E10" si="0">C2</f>
+        <v>46286</v>
+      </c>
+      <c r="D10" s="16">
+        <f t="shared" si="0"/>
+        <v>46287</v>
+      </c>
+      <c r="E10" s="16">
+        <f t="shared" si="0"/>
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11">
+        <f>B3</f>
+        <v>-20.100000000000001</v>
+      </c>
+      <c r="C11">
+        <f>C3-B3</f>
+        <v>-19.799999999999997</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ref="D11:E11" si="1">D3-C3</f>
+        <v>17.799999999999997</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>21.200000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12">
+        <f t="shared" ref="B12:B16" si="2">B4</f>
+        <v>19.7</v>
+      </c>
+      <c r="C12">
+        <f t="shared" ref="C12:E16" si="3">C4-B4</f>
+        <v>31.000000000000004</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="3"/>
+        <v>17.599999999999994</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="3"/>
+        <v>14.700000000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="2"/>
+        <v>1.9</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>2.2000000000000011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="2"/>
+        <v>-21</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="3"/>
+        <v>-20</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="3"/>
+        <v>39.6</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="3"/>
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="2"/>
+        <v>-18.100000000000001</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="3"/>
+        <v>-4.5999999999999979</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="2"/>
+        <v>44.5</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="3"/>
+        <v>-0.39999999999999858</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="3"/>
+        <v>14.299999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8FFDFC-F0D8-484F-BD9F-73CE26658A10}">
   <dimension ref="A1:Z75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3417,34 +5069,34 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>95.199999999999989</v>
+        <v>111.79999999999998</v>
       </c>
       <c r="D2">
-        <v>19.040000000000006</v>
+        <v>22.360000000000007</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="7">
         <f>IFERROR((F2/E2)*100,0)</f>
-        <v>65.789473684210535</v>
+        <v>68.181818181818173</v>
       </c>
       <c r="J2" s="10">
         <f>IFERROR(C2/E2,0)</f>
-        <v>2.5052631578947366</v>
+        <v>2.5409090909090906</v>
       </c>
       <c r="K2" s="10">
         <f>IFERROR(D2/E2,0)</f>
-        <v>0.50105263157894753</v>
+        <v>0.50818181818181829</v>
       </c>
       <c r="L2" s="10" t="str">
         <f>LEFT(B2,3)</f>
@@ -3452,19 +5104,19 @@
       </c>
       <c r="N2">
         <f t="shared" ref="N2:S2" si="0">C2+U2</f>
-        <v>95.199999999999989</v>
+        <v>111.79999999999998</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>19.040000000000006</v>
+        <v>22.360000000000007</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
@@ -3472,7 +5124,7 @@
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -3483,16 +5135,16 @@
         <v>64</v>
       </c>
       <c r="C3">
-        <v>37.9</v>
+        <v>41.9</v>
       </c>
       <c r="D3">
-        <v>7.58</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -3502,15 +5154,15 @@
       </c>
       <c r="I3" s="7">
         <f>IFERROR((F3/E3)*100,0)</f>
-        <v>51.515151515151516</v>
+        <v>52.941176470588239</v>
       </c>
       <c r="J3" s="10">
         <f>IFERROR(C3/E3,0)</f>
-        <v>1.1484848484848484</v>
+        <v>1.2323529411764707</v>
       </c>
       <c r="K3" s="10">
         <f>IFERROR(D3/E3,0)</f>
-        <v>0.22969696969696971</v>
+        <v>0.24647058823529414</v>
       </c>
       <c r="L3" s="10" t="str">
         <f>LEFT(B3,3)</f>
@@ -3518,19 +5170,19 @@
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N64" si="1">C3+U3</f>
-        <v>37.9</v>
+        <v>41.9</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O17" si="2">D3+V3</f>
-        <v>7.58</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="P3">
         <f t="shared" ref="P3:P17" si="3">E3+W3</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q17" si="4">F3+X3</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R17" si="5">G3+Y3</f>
@@ -3549,16 +5201,16 @@
         <v>56</v>
       </c>
       <c r="C4">
-        <v>27.6</v>
+        <v>41.900000000000006</v>
       </c>
       <c r="D4">
-        <v>5.5200000000000005</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3568,15 +5220,15 @@
       </c>
       <c r="I4" s="7">
         <f>IFERROR((F4/E4)*100,0)</f>
-        <v>59.375</v>
+        <v>60.606060606060609</v>
       </c>
       <c r="J4" s="10">
         <f>IFERROR(C4/E4,0)</f>
-        <v>0.86250000000000004</v>
+        <v>1.2696969696969698</v>
       </c>
       <c r="K4" s="10">
         <f>IFERROR(D4/E4,0)</f>
-        <v>0.17250000000000001</v>
+        <v>0.25393939393939396</v>
       </c>
       <c r="L4" s="10" t="str">
         <f>LEFT(B4,3)</f>
@@ -3584,19 +5236,19 @@
       </c>
       <c r="N4">
         <f t="shared" si="1"/>
-        <v>27.6</v>
+        <v>41.900000000000006</v>
       </c>
       <c r="O4">
         <f t="shared" si="2"/>
-        <v>5.5200000000000005</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="P4">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q4">
         <f t="shared" si="4"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R4">
         <f t="shared" si="5"/>
@@ -3615,16 +5267,16 @@
         <v>55</v>
       </c>
       <c r="C5">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>1.9000000000000008</v>
+        <v>2.0000000000000009</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -3634,7 +5286,7 @@
       </c>
       <c r="I5" s="7">
         <f>IFERROR((F5/E5)*100,0)</f>
-        <v>47.368421052631575</v>
+        <v>50</v>
       </c>
       <c r="J5" s="10">
         <f>IFERROR(C5/E5,0)</f>
@@ -3650,19 +5302,19 @@
       </c>
       <c r="N5">
         <f t="shared" si="1"/>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <f t="shared" si="2"/>
-        <v>1.9000000000000008</v>
+        <v>2.0000000000000009</v>
       </c>
       <c r="P5">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q5">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <f t="shared" si="5"/>
@@ -3681,13 +5333,13 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>-18.100000000000001</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="D6">
-        <v>-3.6199999999999997</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -3696,19 +5348,19 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" s="7">
         <f>IFERROR((F6/E6)*100,0)</f>
-        <v>50</v>
+        <v>47.368421052631575</v>
       </c>
       <c r="J6" s="10">
         <f>IFERROR(C6/E6,0)</f>
-        <v>-1.0055555555555555</v>
+        <v>-1.1947368421052633</v>
       </c>
       <c r="K6" s="10">
         <f>IFERROR(D6/E6,0)</f>
-        <v>-0.2011111111111111</v>
+        <v>-0.23894736842105258</v>
       </c>
       <c r="L6" s="10" t="str">
         <f>LEFT(B6,3)</f>
@@ -3716,15 +5368,15 @@
       </c>
       <c r="N6">
         <f t="shared" si="1"/>
-        <v>-18.100000000000001</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="O6">
         <f t="shared" si="2"/>
-        <v>-3.6199999999999997</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="P6">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q6">
         <f t="shared" si="4"/>
@@ -3736,7 +5388,7 @@
       </c>
       <c r="S6">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -3747,16 +5399,16 @@
         <v>62</v>
       </c>
       <c r="C7">
-        <v>22.4</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>4.4800000000000004</v>
+        <v>6.8000000000000007</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -3766,15 +5418,15 @@
       </c>
       <c r="I7" s="7">
         <f>IFERROR((F7/E7)*100,0)</f>
-        <v>70.588235294117652</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="J7" s="10">
         <f>IFERROR(C7/E7,0)</f>
-        <v>1.3176470588235294</v>
+        <v>1.7894736842105263</v>
       </c>
       <c r="K7" s="10">
         <f>IFERROR(D7/E7,0)</f>
-        <v>0.2635294117647059</v>
+        <v>0.35789473684210532</v>
       </c>
       <c r="L7" s="10" t="str">
         <f>LEFT(B7,3)</f>
@@ -3782,19 +5434,19 @@
       </c>
       <c r="N7">
         <f t="shared" si="1"/>
-        <v>22.4</v>
+        <v>34</v>
       </c>
       <c r="O7">
         <f t="shared" si="2"/>
-        <v>4.4800000000000004</v>
+        <v>6.8000000000000007</v>
       </c>
       <c r="P7">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q7">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R7">
         <f t="shared" si="5"/>
@@ -3813,13 +5465,13 @@
         <v>67</v>
       </c>
       <c r="C8">
-        <v>15.399999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="D8">
-        <v>3.08</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -3828,19 +5480,19 @@
         <v>1</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="7">
         <f>IFERROR((F8/E8)*100,0)</f>
-        <v>43.75</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="J8" s="10">
         <f>IFERROR(C8/E8,0)</f>
-        <v>0.96249999999999991</v>
+        <v>0.6588235294117647</v>
       </c>
       <c r="K8" s="10">
         <f>IFERROR(D8/E8,0)</f>
-        <v>0.1925</v>
+        <v>0.13176470588235295</v>
       </c>
       <c r="L8" s="10" t="str">
         <f>LEFT(B8,3)</f>
@@ -3848,15 +5500,15 @@
       </c>
       <c r="N8">
         <f t="shared" si="1"/>
-        <v>15.399999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="O8">
         <f t="shared" si="2"/>
-        <v>3.08</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="P8">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q8">
         <f t="shared" si="4"/>
@@ -3868,7 +5520,7 @@
       </c>
       <c r="S8">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -3879,16 +5531,16 @@
         <v>59</v>
       </c>
       <c r="C9">
-        <v>-45.8</v>
+        <v>-44.3</v>
       </c>
       <c r="D9">
-        <v>-9.16</v>
+        <v>-8.86</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3898,15 +5550,15 @@
       </c>
       <c r="I9" s="7">
         <f>IFERROR((F9/E9)*100,0)</f>
-        <v>30.76923076923077</v>
+        <v>35.714285714285715</v>
       </c>
       <c r="J9" s="10">
         <f>IFERROR(C9/E9,0)</f>
-        <v>-3.523076923076923</v>
+        <v>-3.1642857142857141</v>
       </c>
       <c r="K9" s="10">
         <f>IFERROR(D9/E9,0)</f>
-        <v>-0.70461538461538464</v>
+        <v>-0.63285714285714278</v>
       </c>
       <c r="L9" s="10" t="str">
         <f>LEFT(B9,3)</f>
@@ -3914,19 +5566,19 @@
       </c>
       <c r="N9">
         <f t="shared" si="1"/>
-        <v>-45.8</v>
+        <v>-44.3</v>
       </c>
       <c r="O9">
         <f t="shared" si="2"/>
-        <v>-9.16</v>
+        <v>-8.86</v>
       </c>
       <c r="P9">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q9">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <f t="shared" si="5"/>
@@ -3945,16 +5597,16 @@
         <v>60</v>
       </c>
       <c r="C10">
-        <v>7.7999999999999989</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="D10">
-        <v>1.5599999999999998</v>
+        <v>3.58</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3964,15 +5616,15 @@
       </c>
       <c r="I10" s="7">
         <f>IFERROR((F10/E10)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>71.428571428571431</v>
       </c>
       <c r="J10" s="10">
         <f>IFERROR(C10/E10,0)</f>
-        <v>0.64999999999999991</v>
+        <v>1.2785714285714285</v>
       </c>
       <c r="K10" s="10">
         <f>IFERROR(D10/E10,0)</f>
-        <v>0.12999999999999998</v>
+        <v>0.25571428571428573</v>
       </c>
       <c r="L10" s="10" t="str">
         <f>LEFT(B10,3)</f>
@@ -3980,19 +5632,19 @@
       </c>
       <c r="N10">
         <f t="shared" si="1"/>
-        <v>7.7999999999999989</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="O10">
         <f t="shared" si="2"/>
-        <v>1.5599999999999998</v>
+        <v>3.58</v>
       </c>
       <c r="P10">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q10">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <f t="shared" si="5"/>
@@ -4005,60 +5657,60 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C11">
-        <v>17.5</v>
+        <v>10.9</v>
       </c>
       <c r="D11">
-        <v>3.4999999999999996</v>
+        <v>2.1800000000000006</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7">
         <f>IFERROR((F11/E11)*100,0)</f>
-        <v>60</v>
+        <v>53.846153846153847</v>
       </c>
       <c r="J11" s="10">
         <f>IFERROR(C11/E11,0)</f>
-        <v>1.75</v>
+        <v>0.83846153846153848</v>
       </c>
       <c r="K11" s="10">
         <f>IFERROR(D11/E11,0)</f>
-        <v>0.35</v>
+        <v>0.16769230769230775</v>
       </c>
       <c r="L11" s="10" t="str">
         <f>LEFT(B11,3)</f>
-        <v>WEG</v>
+        <v>PEG</v>
       </c>
       <c r="N11">
         <f t="shared" si="1"/>
-        <v>17.5</v>
+        <v>10.9</v>
       </c>
       <c r="O11">
         <f t="shared" si="2"/>
-        <v>3.4999999999999996</v>
+        <v>2.1800000000000006</v>
       </c>
       <c r="P11">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q11">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <f t="shared" si="5"/>
@@ -4066,61 +5718,61 @@
       </c>
       <c r="S11">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C12">
-        <v>6.9</v>
+        <v>5.5999999999999988</v>
       </c>
       <c r="D12">
-        <v>1.3800000000000003</v>
+        <v>1.1199999999999997</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F12">
         <v>5</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" s="7">
         <f>IFERROR((F12/E12)*100,0)</f>
-        <v>50</v>
+        <v>41.666666666666671</v>
       </c>
       <c r="J12" s="10">
         <f>IFERROR(C12/E12,0)</f>
-        <v>0.69000000000000006</v>
+        <v>0.46666666666666656</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(D12/E12,0)</f>
-        <v>0.13800000000000004</v>
+        <v>9.333333333333331E-2</v>
       </c>
       <c r="L12" s="10" t="str">
         <f>LEFT(B12,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N12">
         <f t="shared" si="1"/>
-        <v>6.9</v>
+        <v>5.5999999999999988</v>
       </c>
       <c r="O12">
         <f t="shared" si="2"/>
-        <v>1.3800000000000003</v>
+        <v>1.1199999999999997</v>
       </c>
       <c r="P12">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q12">
         <f t="shared" si="4"/>
@@ -4128,11 +5780,11 @@
       </c>
       <c r="R12">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -4143,34 +5795,34 @@
         <v>73</v>
       </c>
       <c r="C13">
-        <v>0.50000000000000178</v>
+        <v>-0.89999999999999813</v>
       </c>
       <c r="D13">
-        <v>0.10000000000000009</v>
+        <v>-0.17999999999999988</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
         <f>IFERROR((F13/E13)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>36.363636363636367</v>
       </c>
       <c r="J13" s="10">
         <f>IFERROR(C13/E13,0)</f>
-        <v>5.5555555555555754E-2</v>
+        <v>-8.1818181818181651E-2</v>
       </c>
       <c r="K13" s="10">
         <f>IFERROR(D13/E13,0)</f>
-        <v>1.111111111111112E-2</v>
+        <v>-1.6363636363636355E-2</v>
       </c>
       <c r="L13" s="10" t="str">
         <f>LEFT(B13,3)</f>
@@ -4178,19 +5830,19 @@
       </c>
       <c r="N13">
         <f t="shared" si="1"/>
-        <v>0.50000000000000178</v>
+        <v>-0.89999999999999813</v>
       </c>
       <c r="O13">
         <f t="shared" si="2"/>
-        <v>0.10000000000000009</v>
+        <v>-0.17999999999999988</v>
       </c>
       <c r="P13">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q13">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R13">
         <f t="shared" si="5"/>
@@ -4198,65 +5850,65 @@
       </c>
       <c r="S13">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="C14">
-        <v>4.3999999999999986</v>
+        <v>17.5</v>
       </c>
       <c r="D14">
-        <v>0.87999999999999978</v>
+        <v>3.4999999999999996</v>
       </c>
       <c r="E14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14" s="7">
         <f>IFERROR((F14/E14)*100,0)</f>
-        <v>44.444444444444443</v>
+        <v>60</v>
       </c>
       <c r="J14" s="10">
         <f>IFERROR(C14/E14,0)</f>
-        <v>0.48888888888888871</v>
+        <v>1.75</v>
       </c>
       <c r="K14" s="10">
         <f>IFERROR(D14/E14,0)</f>
-        <v>9.7777777777777755E-2</v>
+        <v>0.35</v>
       </c>
       <c r="L14" s="10" t="str">
         <f>LEFT(B14,3)</f>
-        <v>UEG</v>
+        <v>WEG</v>
       </c>
       <c r="N14">
         <f t="shared" si="1"/>
-        <v>4.3999999999999986</v>
+        <v>17.5</v>
       </c>
       <c r="O14">
         <f t="shared" si="2"/>
-        <v>0.87999999999999978</v>
+        <v>3.4999999999999996</v>
       </c>
       <c r="P14">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <f t="shared" si="5"/>
@@ -4264,7 +5916,7 @@
       </c>
       <c r="S14">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
@@ -4401,19 +6053,19 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C17">
-        <v>-13</v>
+        <v>-9.4</v>
       </c>
       <c r="D17">
-        <v>-2.6000000000000005</v>
+        <v>-1.879999999999999</v>
       </c>
       <c r="E17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17">
         <v>3</v>
@@ -4422,35 +6074,35 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="7">
         <f>IFERROR((F17/E17)*100,0)</f>
-        <v>42.857142857142854</v>
+        <v>37.5</v>
       </c>
       <c r="J17" s="10">
         <f>IFERROR(C17/E17,0)</f>
-        <v>-1.8571428571428572</v>
+        <v>-1.175</v>
       </c>
       <c r="K17" s="10">
         <f>IFERROR(D17/E17,0)</f>
-        <v>-0.3714285714285715</v>
+        <v>-0.23499999999999988</v>
       </c>
       <c r="L17" s="10" t="str">
         <f>LEFT(B17,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N17">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>-9.4</v>
       </c>
       <c r="O17">
         <f t="shared" si="2"/>
-        <v>-2.6000000000000005</v>
+        <v>-1.879999999999999</v>
       </c>
       <c r="P17">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <f t="shared" si="4"/>
@@ -4462,57 +6114,57 @@
       </c>
       <c r="S17">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C18">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="D18">
-        <v>-1.9999999999999991</v>
+        <v>-2.6000000000000005</v>
       </c>
       <c r="E18">
         <v>7</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I18" s="7">
         <f>IFERROR((F18/E18)*100,0)</f>
-        <v>28.571428571428569</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="J18" s="10">
         <f>IFERROR(C18/E18,0)</f>
-        <v>-1.4285714285714286</v>
+        <v>-1.8571428571428572</v>
       </c>
       <c r="K18" s="10">
         <f>IFERROR(D18/E18,0)</f>
-        <v>-0.28571428571428559</v>
+        <v>-0.3714285714285715</v>
       </c>
       <c r="L18" s="10" t="str">
         <f>LEFT(B18,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N18">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="O18">
         <f t="shared" ref="O18:O65" si="7">D18+V18</f>
-        <v>-1.9999999999999991</v>
+        <v>-2.6000000000000005</v>
       </c>
       <c r="P18">
         <f t="shared" ref="P18:P65" si="8">E18+W18</f>
@@ -4520,7 +6172,7 @@
       </c>
       <c r="Q18">
         <f t="shared" ref="Q18:Q65" si="9">F18+X18</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R18">
         <f t="shared" ref="R18:R47" si="10">G18+Y18</f>
@@ -4528,45 +6180,45 @@
       </c>
       <c r="S18">
         <f t="shared" ref="S18:S47" si="11">H18+Z18</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C19">
-        <v>3.3000000000000003</v>
+        <v>1.1999999999999993</v>
       </c>
       <c r="D19">
-        <v>0.66000000000000014</v>
+        <v>0.23999999999999988</v>
       </c>
       <c r="E19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" s="7">
         <f>IFERROR((F19/E19)*100,0)</f>
-        <v>50</v>
+        <v>71.428571428571431</v>
       </c>
       <c r="J19" s="10">
         <f>IFERROR(C19/E19,0)</f>
-        <v>0.55000000000000004</v>
+        <v>0.17142857142857132</v>
       </c>
       <c r="K19" s="10">
         <f>IFERROR(D19/E19,0)</f>
-        <v>0.11000000000000003</v>
+        <v>3.4285714285714267E-2</v>
       </c>
       <c r="L19" s="10" t="str">
         <f>LEFT(B19,3)</f>
@@ -4574,19 +6226,19 @@
       </c>
       <c r="N19">
         <f t="shared" si="1"/>
-        <v>3.3000000000000003</v>
+        <v>1.1999999999999993</v>
       </c>
       <c r="O19">
         <f t="shared" si="7"/>
-        <v>0.66000000000000014</v>
+        <v>0.23999999999999988</v>
       </c>
       <c r="P19">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <f t="shared" si="10"/>
@@ -4594,45 +6246,45 @@
       </c>
       <c r="S19">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C20">
-        <v>5.6</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="D20">
-        <v>1.1199999999999999</v>
+        <v>0.66000000000000014</v>
       </c>
       <c r="E20">
         <v>6</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="7">
         <f>IFERROR((F20/E20)*100,0)</f>
-        <v>83.333333333333343</v>
+        <v>50</v>
       </c>
       <c r="J20" s="10">
         <f>IFERROR(C20/E20,0)</f>
-        <v>0.93333333333333324</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K20" s="10">
         <f>IFERROR(D20/E20,0)</f>
-        <v>0.18666666666666665</v>
+        <v>0.11000000000000003</v>
       </c>
       <c r="L20" s="10" t="str">
         <f>LEFT(B20,3)</f>
@@ -4640,11 +6292,11 @@
       </c>
       <c r="N20">
         <f t="shared" si="1"/>
-        <v>5.6</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="O20">
         <f t="shared" si="7"/>
-        <v>1.1199999999999999</v>
+        <v>0.66000000000000014</v>
       </c>
       <c r="P20">
         <f t="shared" si="8"/>
@@ -4652,7 +6304,7 @@
       </c>
       <c r="Q20">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R20">
         <f t="shared" si="10"/>
@@ -4660,7 +6312,7 @@
       </c>
       <c r="S20">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -5067,13 +6719,13 @@
         <v>76</v>
       </c>
       <c r="C27">
-        <v>-0.5</v>
+        <v>-7.5</v>
       </c>
       <c r="D27">
-        <v>-9.9999999999999978E-2</v>
+        <v>-1.5</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>2</v>
@@ -5082,19 +6734,19 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" s="7">
         <f>IFERROR((F27/E27)*100,0)</f>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J27" s="10">
         <f>IFERROR(C27/E27,0)</f>
-        <v>-0.125</v>
+        <v>-1.5</v>
       </c>
       <c r="K27" s="10">
         <f>IFERROR(D27/E27,0)</f>
-        <v>-2.4999999999999994E-2</v>
+        <v>-0.3</v>
       </c>
       <c r="L27" s="10" t="str">
         <f>LEFT(B27,3)</f>
@@ -5102,15 +6754,15 @@
       </c>
       <c r="N27">
         <f t="shared" si="1"/>
-        <v>-0.5</v>
+        <v>-7.5</v>
       </c>
       <c r="O27">
         <f t="shared" si="7"/>
-        <v>-9.9999999999999978E-2</v>
+        <v>-1.5</v>
       </c>
       <c r="P27">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <f t="shared" si="9"/>
@@ -5122,24 +6774,24 @@
       </c>
       <c r="S27">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>-5.6000000000000014</v>
       </c>
       <c r="D28">
-        <v>1.2</v>
+        <v>-1.1200000000000003</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -5148,19 +6800,19 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="7">
         <f>IFERROR((F28/E28)*100,0)</f>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J28" s="10">
         <f>IFERROR(C28/E28,0)</f>
-        <v>2</v>
+        <v>-1.4000000000000004</v>
       </c>
       <c r="K28" s="10">
         <f>IFERROR(D28/E28,0)</f>
-        <v>0.39999999999999997</v>
+        <v>-0.28000000000000008</v>
       </c>
       <c r="L28" s="10" t="str">
         <f>LEFT(B28,3)</f>
@@ -5168,15 +6820,15 @@
       </c>
       <c r="N28">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>-5.6000000000000014</v>
       </c>
       <c r="O28">
         <f t="shared" si="7"/>
-        <v>1.2</v>
+        <v>-1.1200000000000003</v>
       </c>
       <c r="P28">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q28">
         <f t="shared" si="9"/>
@@ -5188,45 +6840,45 @@
       </c>
       <c r="S28">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C29">
-        <v>-12</v>
+        <v>6</v>
       </c>
       <c r="D29">
-        <v>-2.4</v>
+        <v>1.2</v>
       </c>
       <c r="E29">
         <v>3</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="7">
         <f>IFERROR((F29/E29)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J29" s="10">
         <f>IFERROR(C29/E29,0)</f>
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="K29" s="10">
         <f>IFERROR(D29/E29,0)</f>
-        <v>-0.79999999999999993</v>
+        <v>0.39999999999999997</v>
       </c>
       <c r="L29" s="10" t="str">
         <f>LEFT(B29,3)</f>
@@ -5234,11 +6886,11 @@
       </c>
       <c r="N29">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <f t="shared" si="7"/>
-        <v>-2.4</v>
+        <v>1.2</v>
       </c>
       <c r="P29">
         <f t="shared" si="8"/>
@@ -5246,7 +6898,7 @@
       </c>
       <c r="Q29">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R29">
         <f t="shared" si="10"/>
@@ -5254,45 +6906,45 @@
       </c>
       <c r="S29">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C30">
-        <v>-8.0000000000000018</v>
+        <v>-12</v>
       </c>
       <c r="D30">
-        <v>-1.6000000000000003</v>
+        <v>-2.4</v>
       </c>
       <c r="E30">
         <v>3</v>
       </c>
       <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
         <v>2</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
       </c>
       <c r="I30" s="7">
         <f>IFERROR((F30/E30)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J30" s="10">
         <f>IFERROR(C30/E30,0)</f>
-        <v>-2.6666666666666674</v>
+        <v>-4</v>
       </c>
       <c r="K30" s="10">
         <f>IFERROR(D30/E30,0)</f>
-        <v>-0.53333333333333344</v>
+        <v>-0.79999999999999993</v>
       </c>
       <c r="L30" s="10" t="str">
         <f>LEFT(B30,3)</f>
@@ -5300,11 +6952,11 @@
       </c>
       <c r="N30">
         <f t="shared" si="1"/>
-        <v>-8.0000000000000018</v>
+        <v>-12</v>
       </c>
       <c r="O30">
         <f t="shared" si="7"/>
-        <v>-1.6000000000000003</v>
+        <v>-2.4</v>
       </c>
       <c r="P30">
         <f t="shared" si="8"/>
@@ -5312,7 +6964,7 @@
       </c>
       <c r="Q30">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30">
         <f t="shared" si="10"/>
@@ -5320,65 +6972,65 @@
       </c>
       <c r="S30">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C31">
-        <v>1.0000000000000002</v>
+        <v>16.2</v>
       </c>
       <c r="D31">
-        <v>0.2</v>
+        <v>3.2399999999999998</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="7">
         <f>IFERROR((F31/E31)*100,0)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J31" s="10">
         <f>IFERROR(C31/E31,0)</f>
-        <v>0.50000000000000011</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="K31" s="10">
         <f>IFERROR(D31/E31,0)</f>
-        <v>0.1</v>
+        <v>1.0799999999999998</v>
       </c>
       <c r="L31" s="10" t="str">
         <f>LEFT(B31,3)</f>
-        <v>UEG</v>
+        <v>SEG</v>
       </c>
       <c r="N31">
         <f t="shared" si="1"/>
-        <v>1.0000000000000002</v>
+        <v>16.2</v>
       </c>
       <c r="O31">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>3.2399999999999998</v>
       </c>
       <c r="P31">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R31">
         <f t="shared" si="10"/>
@@ -5386,24 +7038,24 @@
       </c>
       <c r="S31">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="D32">
-        <v>0.2</v>
+        <v>-3.999999999999998E-2</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -5412,35 +7064,35 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="7">
         <f>IFERROR((F32/E32)*100,0)</f>
-        <v>50</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J32" s="10">
         <f>IFERROR(C32/E32,0)</f>
-        <v>0.5</v>
+        <v>-6.6666666666666652E-2</v>
       </c>
       <c r="K32" s="10">
         <f>IFERROR(D32/E32,0)</f>
-        <v>0.1</v>
+        <v>-1.3333333333333327E-2</v>
       </c>
       <c r="L32" s="10" t="str">
         <f>LEFT(B32,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N32">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="O32">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>-3.999999999999998E-2</v>
       </c>
       <c r="P32">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32">
         <f t="shared" si="9"/>
@@ -5452,45 +7104,45 @@
       </c>
       <c r="S32">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="C33">
-        <v>-1.8</v>
+        <v>5.8</v>
       </c>
       <c r="D33">
-        <v>-0.36</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="E33">
+        <v>3</v>
+      </c>
+      <c r="F33">
         <v>2</v>
       </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" s="7">
         <f>IFERROR((F33/E33)*100,0)</f>
-        <v>0</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J33" s="10">
         <f>IFERROR(C33/E33,0)</f>
-        <v>-0.9</v>
+        <v>1.9333333333333333</v>
       </c>
       <c r="K33" s="10">
         <f>IFERROR(D33/E33,0)</f>
-        <v>-0.18</v>
+        <v>0.38666666666666666</v>
       </c>
       <c r="L33" s="10" t="str">
         <f>LEFT(B33,3)</f>
@@ -5498,19 +7150,19 @@
       </c>
       <c r="N33">
         <f t="shared" si="1"/>
-        <v>-1.8</v>
+        <v>5.8</v>
       </c>
       <c r="O33">
         <f t="shared" si="7"/>
-        <v>-0.36</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P33">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R33">
         <f t="shared" si="10"/>
@@ -5518,27 +7170,27 @@
       </c>
       <c r="S33">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C34">
-        <v>-1.9000000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="D34">
-        <v>-0.38</v>
+        <v>3.44</v>
       </c>
       <c r="E34">
+        <v>3</v>
+      </c>
+      <c r="F34">
         <v>2</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -5548,35 +7200,35 @@
       </c>
       <c r="I34" s="7">
         <f>IFERROR((F34/E34)*100,0)</f>
-        <v>50</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J34" s="10">
         <f>IFERROR(C34/E34,0)</f>
-        <v>-0.95000000000000007</v>
+        <v>5.7333333333333334</v>
       </c>
       <c r="K34" s="10">
         <f>IFERROR(D34/E34,0)</f>
-        <v>-0.19</v>
+        <v>1.1466666666666667</v>
       </c>
       <c r="L34" s="10" t="str">
         <f>LEFT(B34,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N34">
         <f t="shared" si="1"/>
-        <v>-1.9000000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="O34">
         <f t="shared" si="7"/>
-        <v>-0.38</v>
+        <v>3.44</v>
       </c>
       <c r="P34">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q34">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34">
         <f t="shared" si="10"/>
@@ -5589,19 +7241,19 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="C35">
-        <v>-12</v>
+        <v>-34.6</v>
       </c>
       <c r="D35">
-        <v>-2.4</v>
+        <v>-6.9200000000000008</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -5610,7 +7262,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" s="7">
         <f>IFERROR((F35/E35)*100,0)</f>
@@ -5618,27 +7270,27 @@
       </c>
       <c r="J35" s="10">
         <f>IFERROR(C35/E35,0)</f>
-        <v>-6</v>
+        <v>-11.533333333333333</v>
       </c>
       <c r="K35" s="10">
         <f>IFERROR(D35/E35,0)</f>
-        <v>-1.2</v>
+        <v>-2.3066666666666671</v>
       </c>
       <c r="L35" s="10" t="str">
         <f>LEFT(B35,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N35">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>-34.6</v>
       </c>
       <c r="O35">
         <f t="shared" si="7"/>
-        <v>-2.4</v>
+        <v>-6.9200000000000008</v>
       </c>
       <c r="P35">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q35">
         <f t="shared" si="9"/>
@@ -5650,57 +7302,57 @@
       </c>
       <c r="S35">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C36">
-        <v>14</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D36">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="7">
         <f>IFERROR((F36/E36)*100,0)</f>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J36" s="10">
         <f>IFERROR(C36/E36,0)</f>
-        <v>7</v>
+        <v>0.50000000000000011</v>
       </c>
       <c r="K36" s="10">
         <f>IFERROR(D36/E36,0)</f>
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="L36" s="10" t="str">
         <f>LEFT(B36,3)</f>
-        <v>SEG</v>
+        <v>UEG</v>
       </c>
       <c r="N36">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="O36">
         <f t="shared" si="7"/>
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="P36">
         <f t="shared" si="8"/>
@@ -5708,7 +7360,7 @@
       </c>
       <c r="Q36">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36">
         <f t="shared" si="10"/>
@@ -5716,21 +7368,21 @@
       </c>
       <c r="S36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="C37">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="E37">
         <v>2</v>
@@ -5750,23 +7402,23 @@
       </c>
       <c r="J37" s="10">
         <f>IFERROR(C37/E37,0)</f>
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="K37" s="10">
         <f>IFERROR(D37/E37,0)</f>
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="L37" s="10" t="str">
         <f>LEFT(B37,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N37">
         <f t="shared" si="1"/>
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="O37">
         <f t="shared" si="7"/>
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="P37">
         <f t="shared" si="8"/>
@@ -5787,40 +7439,40 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="C38">
-        <v>1.7000000000000002</v>
+        <v>-1.8</v>
       </c>
       <c r="D38">
-        <v>0.34000000000000008</v>
+        <v>-0.36</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="7">
         <f>IFERROR((F38/E38)*100,0)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J38" s="10">
         <f>IFERROR(C38/E38,0)</f>
-        <v>0.85000000000000009</v>
+        <v>-0.9</v>
       </c>
       <c r="K38" s="10">
         <f>IFERROR(D38/E38,0)</f>
-        <v>0.17000000000000004</v>
+        <v>-0.18</v>
       </c>
       <c r="L38" s="10" t="str">
         <f>LEFT(B38,3)</f>
@@ -5828,11 +7480,11 @@
       </c>
       <c r="N38">
         <f t="shared" si="1"/>
-        <v>1.7000000000000002</v>
+        <v>-1.8</v>
       </c>
       <c r="O38">
         <f t="shared" si="7"/>
-        <v>0.34000000000000008</v>
+        <v>-0.36</v>
       </c>
       <c r="P38">
         <f t="shared" si="8"/>
@@ -5840,7 +7492,7 @@
       </c>
       <c r="Q38">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38">
         <f t="shared" si="10"/>
@@ -5848,21 +7500,21 @@
       </c>
       <c r="S38">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C39">
-        <v>15.6</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="D39">
-        <v>3.12</v>
+        <v>-0.38</v>
       </c>
       <c r="E39">
         <v>2</v>
@@ -5882,23 +7534,23 @@
       </c>
       <c r="J39" s="10">
         <f>IFERROR(C39/E39,0)</f>
-        <v>7.8</v>
+        <v>-0.95000000000000007</v>
       </c>
       <c r="K39" s="10">
         <f>IFERROR(D39/E39,0)</f>
-        <v>1.56</v>
+        <v>-0.19</v>
       </c>
       <c r="L39" s="10" t="str">
         <f>LEFT(B39,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N39">
         <f t="shared" si="1"/>
-        <v>15.6</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="O39">
         <f t="shared" si="7"/>
-        <v>3.12</v>
+        <v>-0.38</v>
       </c>
       <c r="P39">
         <f t="shared" si="8"/>
@@ -5919,16 +7571,16 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="C40">
-        <v>-30.7</v>
+        <v>-12</v>
       </c>
       <c r="D40">
-        <v>-6.1400000000000006</v>
+        <v>-2.4</v>
       </c>
       <c r="E40">
         <v>2</v>
@@ -5948,23 +7600,23 @@
       </c>
       <c r="J40" s="10">
         <f>IFERROR(C40/E40,0)</f>
-        <v>-15.35</v>
+        <v>-6</v>
       </c>
       <c r="K40" s="10">
         <f>IFERROR(D40/E40,0)</f>
-        <v>-3.0700000000000003</v>
+        <v>-1.2</v>
       </c>
       <c r="L40" s="10" t="str">
         <f>LEFT(B40,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N40">
         <f t="shared" si="1"/>
-        <v>-30.7</v>
+        <v>-12</v>
       </c>
       <c r="O40">
         <f t="shared" si="7"/>
-        <v>-6.1400000000000006</v>
+        <v>-2.4</v>
       </c>
       <c r="P40">
         <f t="shared" si="8"/>
@@ -7643,8 +9295,8 @@
       <c r="B75" s="8"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L65">
-    <sortCondition descending="1" ref="E2:E65"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L75">
+    <sortCondition descending="1" ref="E2:E75"/>
   </sortState>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="dataBar" priority="10">
@@ -7882,7 +9534,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A53AFF8-0615-4AA5-B49F-FDA402810813}">
   <dimension ref="A1:AB66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7891,7 +9543,7 @@
     <col min="8" max="28" width="6.28515625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -7899,7 +9551,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" t="s">
         <v>120</v>
@@ -7923,7 +9575,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -7956,8 +9608,9 @@
       <c r="J3" s="18"/>
       <c r="K3" s="18"/>
       <c r="L3" s="18"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3" s="18"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>64</v>
       </c>
@@ -7989,7 +9642,7 @@
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -8021,7 +9674,7 @@
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -8052,7 +9705,7 @@
       <c r="H6" s="18"/>
       <c r="I6" s="17"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -8080,10 +9733,11 @@
         <f>COUNTIF(H7:AB7, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H7" s="17"/>
+      <c r="H7" s="18"/>
       <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J7" s="17"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -8112,9 +9766,9 @@
         <v>0</v>
       </c>
       <c r="H8" s="18"/>
-      <c r="I8" s="17"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>67</v>
       </c>
@@ -8143,9 +9797,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I9" s="19"/>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>59</v>
       </c>
@@ -8177,7 +9832,7 @@
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -8205,13 +9860,12 @@
         <f>COUNTIF(H11:AB11, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B12">
         <f>SUM(H12:AB12)</f>
@@ -8240,9 +9894,9 @@
       <c r="H12" s="18"/>
       <c r="I12" s="19"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="B13">
         <f>SUM(H13:AB13)</f>
@@ -8269,9 +9923,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="18"/>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I13" s="18"/>
+      <c r="J13" s="15"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -8300,12 +9955,12 @@
         <v>0</v>
       </c>
       <c r="H14" s="18"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="B15">
         <f>SUM(H15:AB15)</f>
@@ -8333,8 +9988,9 @@
       </c>
       <c r="H15" s="18"/>
       <c r="I15" s="15"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J15" s="15"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>119</v>
       </c>
@@ -8397,7 +10053,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B18">
         <f>SUM(H18:AB18)</f>
@@ -8424,12 +10080,12 @@
         <v>0</v>
       </c>
       <c r="H18" s="18"/>
-      <c r="I18" s="15"/>
+      <c r="I18" s="19"/>
       <c r="J18" s="15"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B19">
         <f>SUM(H19:AB19)</f>
@@ -8460,7 +10116,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B20">
         <f>SUM(H20:AB20)</f>
@@ -8490,7 +10146,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B21">
         <f>SUM(H21:AB21)</f>
@@ -8607,6 +10263,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -8637,7 +10294,6 @@
         <v>0</v>
       </c>
       <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -8727,7 +10383,7 @@
         <f>COUNTIF(H28:AB28, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H28" s="17"/>
+      <c r="H28" s="18"/>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
@@ -8735,7 +10391,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B29">
         <f>SUM(H29:AB29)</f>
@@ -8765,7 +10421,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B30">
         <f>SUM(H30:AB30)</f>
@@ -8795,7 +10451,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B31">
         <f>SUM(H31:AB31)</f>
@@ -8821,12 +10477,11 @@
         <f>COUNTIF(H31:AB31, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
+      <c r="H31" s="19"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B32">
         <f>SUM(H32:AB32)</f>
@@ -8852,10 +10507,12 @@
         <f>COUNTIF(H32:AB32, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="B33">
         <f>SUM(H33:AB33)</f>
@@ -8881,10 +10538,11 @@
         <f>COUNTIF(H33:AB33, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H33" s="17"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="B34">
         <f>SUM(H34:AB34)</f>
@@ -8910,11 +10568,11 @@
         <f>COUNTIF(H34:AB34, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H34" s="15"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B35">
         <f>SUM(H35:AB35)</f>
@@ -8940,10 +10598,11 @@
         <f>COUNTIF(H35:AB35, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H35" s="17"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="B36">
         <f>SUM(H36:AB36)</f>
@@ -8969,11 +10628,11 @@
         <f>COUNTIF(H36:AB36, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H36" s="15"/>
+      <c r="H36" s="19"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B37">
         <f>SUM(H37:AB37)</f>
@@ -9004,7 +10663,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="B38">
         <f>SUM(H38:AB38)</f>
@@ -9034,7 +10693,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="B39">
         <f>SUM(H39:AB39)</f>
@@ -9064,7 +10723,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B40">
         <f>SUM(H40:AB40)</f>
@@ -9094,7 +10753,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="B41">
         <f>SUM(H41:AB41)</f>
@@ -9215,7 +10874,7 @@
       <c r="H44" s="15"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B45">
@@ -9302,7 +10961,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="5" t="s">
         <v>104</v>
       </c>
       <c r="B48">
@@ -9331,7 +10990,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="5" t="s">
         <v>106</v>
       </c>
       <c r="B49">
@@ -9363,7 +11022,7 @@
       <c r="J49" s="15"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="5" t="s">
         <v>107</v>
       </c>
       <c r="B50">
@@ -9776,7 +11435,7 @@
       <c r="I63" s="15"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B64">
@@ -9805,7 +11464,7 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="A65" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B65">
@@ -9834,7 +11493,7 @@
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="5" t="s">
         <v>90</v>
       </c>
       <c r="B66">
@@ -9863,8 +11522,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB66">
-    <sortCondition descending="1" ref="D2:D66"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB66">
+    <sortCondition descending="1" ref="D3:D66"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4850DF-602C-41FA-AEB2-166B8692F6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292FA713-08CB-42F6-9AF0-9A1C90F879A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
@@ -595,7 +595,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -626,6 +626,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -660,6 +666,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Динамика доходов по типам роботов</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -735,10 +766,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$E$2</c:f>
+              <c:f>Динамика!$B$2:$F$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -751,15 +782,18 @@
                 <c:pt idx="3">
                   <c:v>46288</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>46290</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$3:$E$3</c:f>
+              <c:f>Динамика!$B$3:$F$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>-20.100000000000001</c:v>
                 </c:pt>
@@ -771,6 +805,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>-0.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28.400000000000013</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -822,10 +859,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$E$2</c:f>
+              <c:f>Динамика!$B$2:$F$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -838,15 +875,18 @@
                 <c:pt idx="3">
                   <c:v>46288</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>46290</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$4:$E$4</c:f>
+              <c:f>Динамика!$B$4:$F$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>19.7</c:v>
                 </c:pt>
@@ -858,6 +898,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>83.199999999999989</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -909,10 +952,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$E$2</c:f>
+              <c:f>Динамика!$B$2:$F$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -925,15 +968,18 @@
                 <c:pt idx="3">
                   <c:v>46288</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>46290</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$5:$E$5</c:f>
+              <c:f>Динамика!$B$5:$F$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1.9</c:v>
                 </c:pt>
@@ -945,6 +991,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20.299999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -996,10 +1045,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$E$2</c:f>
+              <c:f>Динамика!$B$2:$F$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1012,15 +1061,18 @@
                 <c:pt idx="3">
                   <c:v>46288</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>46290</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$6:$E$6</c:f>
+              <c:f>Динамика!$B$6:$F$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>-21</c:v>
                 </c:pt>
@@ -1032,6 +1084,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>-1.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-15.199999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1083,10 +1138,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$E$2</c:f>
+              <c:f>Динамика!$B$2:$F$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1099,15 +1154,18 @@
                 <c:pt idx="3">
                   <c:v>46288</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>46290</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$7:$E$7</c:f>
+              <c:f>Динамика!$B$7:$F$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>-18.100000000000001</c:v>
                 </c:pt>
@@ -1119,6 +1177,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>-22.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-22.700000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1170,10 +1231,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$E$2</c:f>
+              <c:f>Динамика!$B$2:$F$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1186,15 +1247,18 @@
                 <c:pt idx="3">
                   <c:v>46288</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>46290</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$8:$E$8</c:f>
+              <c:f>Динамика!$B$8:$F$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>44.5</c:v>
                 </c:pt>
@@ -1206,6 +1270,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>59.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>62.400000000000006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2004,64 +2071,6 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46287.786514004627" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="64" xr:uid="{1976E921-BE3A-4FF1-A5EF-18E3F04892B4}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:L65" sheet="Результаты"/>
-  </cacheSource>
-  <cacheFields count="12">
-    <cacheField name="Номер" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="64"/>
-    </cacheField>
-    <cacheField name="Стратегия" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Абс" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-45.8" maxValue="95.199999999999989"/>
-    </cacheField>
-    <cacheField name="Отн" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-9.16" maxValue="19.040000000000006"/>
-    </cacheField>
-    <cacheField name="Кол-во" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="38"/>
-    </cacheField>
-    <cacheField name="Прибыль" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="25"/>
-    </cacheField>
-    <cacheField name="Нейтрал" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="Убыток" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="15"/>
-    </cacheField>
-    <cacheField name="ПроцПД" numFmtId="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="100"/>
-    </cacheField>
-    <cacheField name="САП" numFmtId="2">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-15.35" maxValue="7.8"/>
-    </cacheField>
-    <cacheField name="СОП" numFmtId="2">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-3.0700000000000003" maxValue="1.56"/>
-    </cacheField>
-    <cacheField name="Тип" numFmtId="2">
-      <sharedItems count="6">
-        <s v="PEG"/>
-        <s v="WEG"/>
-        <s v="LEG"/>
-        <s v="VEG"/>
-        <s v="UEG"/>
-        <s v="SEG"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46288.785760416664" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="41" xr:uid="{93B0B297-F304-40FC-B21C-BCAAF0FA44CB}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:L42" sheet="Результаты"/>
@@ -2119,908 +2128,65 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="64">
-  <r>
-    <n v="1"/>
-    <s v="PEG17_PHOENIX"/>
-    <n v="95.199999999999989"/>
-    <n v="19.040000000000006"/>
-    <n v="38"/>
-    <n v="25"/>
-    <n v="0"/>
-    <n v="13"/>
-    <n v="65.789473684210535"/>
-    <n v="2.5052631578947366"/>
-    <n v="0.50105263157894753"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <s v="PEG11_KUSURUKEN"/>
-    <n v="37.9"/>
-    <n v="7.58"/>
-    <n v="33"/>
-    <n v="17"/>
-    <n v="1"/>
-    <n v="15"/>
-    <n v="51.515151515151516"/>
-    <n v="1.1484848484848484"/>
-    <n v="0.22969696969696971"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <s v="WEG3_BATYA"/>
-    <n v="27.6"/>
-    <n v="5.5200000000000005"/>
-    <n v="32"/>
-    <n v="19"/>
-    <n v="0"/>
-    <n v="13"/>
-    <n v="59.375"/>
-    <n v="0.86250000000000004"/>
-    <n v="0.17250000000000001"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <s v="LEG2_DRINKER"/>
-    <n v="9.5"/>
-    <n v="1.9000000000000008"/>
-    <n v="19"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="10"/>
-    <n v="47.368421052631575"/>
-    <n v="0.5"/>
-    <n v="0.10000000000000005"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <s v="VEG1_VENUS"/>
-    <n v="-18.100000000000001"/>
-    <n v="-3.6199999999999997"/>
-    <n v="18"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="9"/>
-    <n v="50"/>
-    <n v="-1.0055555555555555"/>
-    <n v="-0.2011111111111111"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <s v="LEG2_FENNEC"/>
-    <n v="22.4"/>
-    <n v="4.4800000000000004"/>
-    <n v="17"/>
-    <n v="12"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="70.588235294117652"/>
-    <n v="1.3176470588235294"/>
-    <n v="0.2635294117647059"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <s v="LEG1_PIN"/>
-    <n v="15.399999999999999"/>
-    <n v="3.08"/>
-    <n v="16"/>
-    <n v="7"/>
-    <n v="1"/>
-    <n v="8"/>
-    <n v="43.75"/>
-    <n v="0.96249999999999991"/>
-    <n v="0.1925"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <s v="PEG18_BLAZE"/>
-    <n v="-45.8"/>
-    <n v="-9.16"/>
-    <n v="13"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="8"/>
-    <n v="30.76923076923077"/>
-    <n v="-3.523076923076923"/>
-    <n v="-0.70461538461538464"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <s v="LEG2_LYNX"/>
-    <n v="7.7999999999999989"/>
-    <n v="1.5599999999999998"/>
-    <n v="12"/>
-    <n v="8"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="66.666666666666657"/>
-    <n v="0.64999999999999991"/>
-    <n v="0.12999999999999998"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <s v="WEG4_PUPPY"/>
-    <n v="17.5"/>
-    <n v="3.4999999999999996"/>
-    <n v="10"/>
-    <n v="6"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="60"/>
-    <n v="1.75"/>
-    <n v="0.35"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="11"/>
-    <s v="PEG4_UNIVERSAL"/>
-    <n v="6.9"/>
-    <n v="1.3800000000000003"/>
-    <n v="10"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="50"/>
-    <n v="0.69000000000000006"/>
-    <n v="0.13800000000000004"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="12"/>
-    <s v="UEG6_PIGEON"/>
-    <n v="0.50000000000000178"/>
-    <n v="0.10000000000000009"/>
-    <n v="9"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="6"/>
-    <n v="33.333333333333329"/>
-    <n v="5.5555555555555754E-2"/>
-    <n v="1.111111111111112E-2"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="13"/>
-    <s v="UEG6_ADVENTURE"/>
-    <n v="4.3999999999999986"/>
-    <n v="0.87999999999999978"/>
-    <n v="9"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="44.444444444444443"/>
-    <n v="0.48888888888888871"/>
-    <n v="9.7777777777777755E-2"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="14"/>
-    <s v="LEG1_CC2"/>
-    <n v="-8.8999999999999986"/>
-    <n v="-1.7799999999999998"/>
-    <n v="8"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="50"/>
-    <n v="-1.1124999999999998"/>
-    <n v="-0.22249999999999998"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="15"/>
-    <s v="UEG6_VULTURE"/>
-    <n v="-9.6999999999999993"/>
-    <n v="-1.9400000000000002"/>
-    <n v="8"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="37.5"/>
-    <n v="-1.2124999999999999"/>
-    <n v="-0.24250000000000002"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="16"/>
-    <s v="PEG18_UTER2"/>
-    <n v="-13"/>
-    <n v="-2.6000000000000005"/>
-    <n v="7"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="42.857142857142854"/>
-    <n v="-1.8571428571428572"/>
-    <n v="-0.3714285714285715"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="17"/>
-    <s v="LEG1_BIBI2"/>
-    <n v="-10"/>
-    <n v="-1.9999999999999991"/>
-    <n v="7"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="28.571428571428569"/>
-    <n v="-1.4285714285714286"/>
-    <n v="-0.28571428571428559"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="18"/>
-    <s v="PEG14_RENEGADE"/>
-    <n v="3.3000000000000003"/>
-    <n v="0.66000000000000014"/>
-    <n v="6"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="50"/>
-    <n v="0.55000000000000004"/>
-    <n v="0.11000000000000003"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="19"/>
-    <s v="PEG4_U3"/>
-    <n v="5.6"/>
-    <n v="1.1199999999999999"/>
-    <n v="6"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="83.333333333333343"/>
-    <n v="0.93333333333333324"/>
-    <n v="0.18666666666666665"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="20"/>
-    <s v="SEG3_FORCE"/>
-    <n v="1.9000000000000004"/>
-    <n v="0.37999999999999989"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="60"/>
-    <n v="0.38000000000000006"/>
-    <n v="7.5999999999999984E-2"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="21"/>
-    <s v="UEG4_PELICAN"/>
-    <n v="-2.9000000000000004"/>
-    <n v="-0.58000000000000007"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="60"/>
-    <n v="-0.58000000000000007"/>
-    <n v="-0.11600000000000002"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="22"/>
-    <s v="PEG19_ANUBARAK"/>
-    <n v="-3.8000000000000007"/>
-    <n v="-0.76000000000000023"/>
-    <n v="5"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="40"/>
-    <n v="-0.76000000000000012"/>
-    <n v="-0.15200000000000005"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="23"/>
-    <s v="PEG18_UTER"/>
-    <n v="-6.2"/>
-    <n v="-1.24"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="60"/>
-    <n v="-1.24"/>
-    <n v="-0.248"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="24"/>
-    <s v="LEG1_IRONANNY2"/>
-    <n v="-7.5"/>
-    <n v="-1.5"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="20"/>
-    <n v="-1.5"/>
-    <n v="-0.3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="25"/>
-    <s v="PEG18_DIABLO2"/>
-    <n v="-9.1"/>
-    <n v="-1.82"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="20"/>
-    <n v="-1.8199999999999998"/>
-    <n v="-0.36399999999999999"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="26"/>
-    <s v="PEG26_UNKNOWN"/>
-    <n v="-0.5"/>
-    <n v="-9.9999999999999978E-2"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="50"/>
-    <n v="-0.125"/>
-    <n v="-2.4999999999999994E-2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="27"/>
-    <s v="LEG1_LAKSAe"/>
-    <n v="6"/>
-    <n v="1.2"/>
-    <n v="3"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="2"/>
-    <n v="0.39999999999999997"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="28"/>
-    <s v="LEG2_DRG"/>
-    <n v="-12"/>
-    <n v="-2.4"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="33.333333333333329"/>
-    <n v="-4"/>
-    <n v="-0.79999999999999993"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="29"/>
-    <s v="LEG2_LOGAN"/>
-    <n v="-8.0000000000000018"/>
-    <n v="-1.6000000000000003"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="66.666666666666657"/>
-    <n v="-2.6666666666666674"/>
-    <n v="-0.53333333333333344"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="30"/>
-    <s v="UEG7_ADVENTURE"/>
-    <n v="1.0000000000000002"/>
-    <n v="0.2"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="0.50000000000000011"/>
-    <n v="0.1"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="31"/>
-    <s v="PEG13_DWDDCr"/>
-    <n v="1"/>
-    <n v="0.2"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="0.5"/>
-    <n v="0.1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="32"/>
-    <s v="LEG2_HOTS"/>
-    <n v="-1.8"/>
-    <n v="-0.36"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="-0.9"/>
-    <n v="-0.18"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="33"/>
-    <s v="PEG14_RANGER"/>
-    <n v="-1.9000000000000001"/>
-    <n v="-0.38"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="-0.95000000000000007"/>
-    <n v="-0.19"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="34"/>
-    <s v="UEG4_FALCON"/>
-    <n v="-12"/>
-    <n v="-2.4"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="-6"/>
-    <n v="-1.2"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="35"/>
-    <s v="SEG1_LITE"/>
-    <n v="14"/>
-    <n v="2.8"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="7"/>
-    <n v="1.4"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="36"/>
-    <s v="UEG7_PIGEON"/>
-    <n v="1.7"/>
-    <n v="0.34"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="0.85"/>
-    <n v="0.17"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="37"/>
-    <s v="LEG1_IGOGOSHA2"/>
-    <n v="1.7000000000000002"/>
-    <n v="0.34000000000000008"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="0.85000000000000009"/>
-    <n v="0.17000000000000004"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="38"/>
-    <s v="UEG6_SHERIFF"/>
-    <n v="15.6"/>
-    <n v="3.12"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="7.8"/>
-    <n v="1.56"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="39"/>
-    <s v="LEG2_ALKASH"/>
-    <n v="-30.7"/>
-    <n v="-6.1400000000000006"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="-15.35"/>
-    <n v="-3.0700000000000003"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="40"/>
-    <s v="PEG18_ANDUIN"/>
-    <n v="-1.3"/>
-    <n v="-0.26"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-1.3"/>
-    <n v="-0.26"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="41"/>
-    <s v="LEG1_PHOGA"/>
-    <n v="-6"/>
-    <n v="-1.2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-6"/>
-    <n v="-1.2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="42"/>
-    <s v="LEG1_BORSCH"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="43"/>
-    <s v="LEG1_OKROSHKA"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="44"/>
-    <s v="LEG1_PHOBO"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="45"/>
-    <s v="LEG2_MONSTER"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="46"/>
-    <s v="PEG14_RWDDCr"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="47"/>
-    <s v="PEG15_ANNA"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="48"/>
-    <s v="PEG15_SILVANA"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="49"/>
-    <s v="PEG18_REXXAR2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="50"/>
-    <s v="PEG18_VARIAN2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="51"/>
-    <s v="PEG2_SDDCr"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="52"/>
-    <s v="PEG20_HOGGER"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="53"/>
-    <s v="PEG8_DOBBY"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="54"/>
-    <s v="PEG8_LOBSTER"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="55"/>
-    <s v="UEG4_CANADIAN"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="56"/>
-    <s v="UEG6_DODO"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="57"/>
-    <s v="UEG6_DUELDODO"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="58"/>
-    <s v="UEG7_DODO"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="59"/>
-    <s v="UEG7_DUELDODO"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="60"/>
-    <s v="UEG7_SHERIFF"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="61"/>
-    <s v="UEG7_VULTURE"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="62"/>
-    <s v="UEG8_AVENGER"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="63"/>
-    <s v="WEG4_DOG"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="64"/>
-    <s v="WEG7_PARADOX"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-  </r>
-</pivotCacheRecords>
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46290.963686805553" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="64" xr:uid="{1976E921-BE3A-4FF1-A5EF-18E3F04892B4}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:L65" sheet="Результаты"/>
+  </cacheSource>
+  <cacheFields count="12">
+    <cacheField name="Номер" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="64"/>
+    </cacheField>
+    <cacheField name="Стратегия" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Абс" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-42.900000000000006" maxValue="119.69999999999999"/>
+    </cacheField>
+    <cacheField name="Отн" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-8.58" maxValue="23.940000000000005"/>
+    </cacheField>
+    <cacheField name="Кол-во" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="51"/>
+    </cacheField>
+    <cacheField name="Прибыль" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="34"/>
+    </cacheField>
+    <cacheField name="Нейтрал" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
+    </cacheField>
+    <cacheField name="Убыток" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="17"/>
+    </cacheField>
+    <cacheField name="ПроцПД" numFmtId="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="100"/>
+    </cacheField>
+    <cacheField name="САП" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-10.725000000000001" maxValue="4.5999999999999996"/>
+    </cacheField>
+    <cacheField name="СОП" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-2.145" maxValue="0.91999999999999993"/>
+    </cacheField>
+    <cacheField name="Тип" numFmtId="2">
+      <sharedItems count="6">
+        <s v="PEG"/>
+        <s v="WEG"/>
+        <s v="LEG"/>
+        <s v="VEG"/>
+        <s v="UEG"/>
+        <s v="SEG"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="41">
   <r>
     <n v="1"/>
@@ -3599,8 +2765,909 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="64">
+  <r>
+    <n v="1"/>
+    <s v="PEG17_PHOENIX"/>
+    <n v="119.69999999999999"/>
+    <n v="23.940000000000005"/>
+    <n v="51"/>
+    <n v="34"/>
+    <n v="0"/>
+    <n v="17"/>
+    <n v="66.666666666666657"/>
+    <n v="2.3470588235294114"/>
+    <n v="0.46941176470588247"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <s v="PEG11_KUSURUKEN"/>
+    <n v="30.099999999999998"/>
+    <n v="6.0200000000000005"/>
+    <n v="36"/>
+    <n v="18"/>
+    <n v="1"/>
+    <n v="17"/>
+    <n v="50"/>
+    <n v="0.83611111111111103"/>
+    <n v="0.16722222222222224"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <s v="WEG3_BATYA"/>
+    <n v="44.900000000000006"/>
+    <n v="8.98"/>
+    <n v="34"/>
+    <n v="21"/>
+    <n v="0"/>
+    <n v="13"/>
+    <n v="61.764705882352942"/>
+    <n v="1.3205882352941178"/>
+    <n v="0.26411764705882357"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <s v="LEG2_FENNEC"/>
+    <n v="46.8"/>
+    <n v="9.3600000000000012"/>
+    <n v="22"/>
+    <n v="16"/>
+    <n v="0"/>
+    <n v="6"/>
+    <n v="72.727272727272734"/>
+    <n v="2.127272727272727"/>
+    <n v="0.42545454545454553"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <s v="LEG2_DRINKER"/>
+    <n v="13.3"/>
+    <n v="2.660000000000001"/>
+    <n v="21"/>
+    <n v="11"/>
+    <n v="0"/>
+    <n v="10"/>
+    <n v="52.380952380952387"/>
+    <n v="0.63333333333333341"/>
+    <n v="0.12666666666666671"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <s v="VEG1_VENUS"/>
+    <n v="-22.700000000000003"/>
+    <n v="-4.5399999999999991"/>
+    <n v="19"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="10"/>
+    <n v="47.368421052631575"/>
+    <n v="-1.1947368421052633"/>
+    <n v="-0.23894736842105258"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <s v="LEG1_PIN"/>
+    <n v="14.5"/>
+    <n v="2.9000000000000004"/>
+    <n v="18"/>
+    <n v="8"/>
+    <n v="1"/>
+    <n v="9"/>
+    <n v="44.444444444444443"/>
+    <n v="0.80555555555555558"/>
+    <n v="0.16111111111111112"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <s v="PEG4_UNIVERSAL"/>
+    <n v="11.5"/>
+    <n v="2.3000000000000007"/>
+    <n v="17"/>
+    <n v="10"/>
+    <n v="1"/>
+    <n v="6"/>
+    <n v="58.82352941176471"/>
+    <n v="0.67647058823529416"/>
+    <n v="0.13529411764705887"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <s v="LEG2_LYNX"/>
+    <n v="27.9"/>
+    <n v="5.58"/>
+    <n v="16"/>
+    <n v="12"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="75"/>
+    <n v="1.7437499999999999"/>
+    <n v="0.34875"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <s v="PEG18_BLAZE"/>
+    <n v="-40.799999999999997"/>
+    <n v="-8.16"/>
+    <n v="15"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="8"/>
+    <n v="40"/>
+    <n v="-2.7199999999999998"/>
+    <n v="-0.54400000000000004"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <s v="UEG6_ADVENTURE"/>
+    <n v="2.4999999999999982"/>
+    <n v="0.49999999999999956"/>
+    <n v="15"/>
+    <n v="6"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="40"/>
+    <n v="0.16666666666666655"/>
+    <n v="3.3333333333333305E-2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <s v="UEG6_PIGEON"/>
+    <n v="-3.0999999999999983"/>
+    <n v="-0.61999999999999988"/>
+    <n v="13"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="8"/>
+    <n v="38.461538461538467"/>
+    <n v="-0.23846153846153834"/>
+    <n v="-4.7692307692307687E-2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <s v="WEG4_PUPPY"/>
+    <n v="17.5"/>
+    <n v="3.4999999999999996"/>
+    <n v="10"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="60"/>
+    <n v="1.75"/>
+    <n v="0.35"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <s v="LEG1_BIBI2"/>
+    <n v="-8.7000000000000011"/>
+    <n v="-1.7399999999999991"/>
+    <n v="9"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="44.444444444444443"/>
+    <n v="-0.96666666666666679"/>
+    <n v="-0.19333333333333325"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <s v="LEG1_CC2"/>
+    <n v="-8.8999999999999986"/>
+    <n v="-1.7799999999999998"/>
+    <n v="8"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="50"/>
+    <n v="-1.1124999999999998"/>
+    <n v="-0.22249999999999998"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <s v="UEG6_VULTURE"/>
+    <n v="-9.6999999999999993"/>
+    <n v="-1.9400000000000002"/>
+    <n v="8"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="37.5"/>
+    <n v="-1.2124999999999999"/>
+    <n v="-0.24250000000000002"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <s v="PEG4_U3"/>
+    <n v="1.1999999999999993"/>
+    <n v="0.23999999999999988"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="62.5"/>
+    <n v="0.14999999999999991"/>
+    <n v="2.9999999999999985E-2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <s v="PEG18_UTER2"/>
+    <n v="-13"/>
+    <n v="-2.6000000000000005"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="42.857142857142854"/>
+    <n v="-1.8571428571428572"/>
+    <n v="-0.3714285714285715"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <s v="PEG14_RENEGADE"/>
+    <n v="3.3000000000000003"/>
+    <n v="0.66000000000000014"/>
+    <n v="6"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="50"/>
+    <n v="0.55000000000000004"/>
+    <n v="0.11000000000000003"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <s v="SEG3_FORCE"/>
+    <n v="1.9000000000000004"/>
+    <n v="0.37999999999999989"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="60"/>
+    <n v="0.38000000000000006"/>
+    <n v="7.5999999999999984E-2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <s v="UEG4_PELICAN"/>
+    <n v="-2.9000000000000004"/>
+    <n v="-0.58000000000000007"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="60"/>
+    <n v="-0.58000000000000007"/>
+    <n v="-0.11600000000000002"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <s v="PEG19_ANUBARAK"/>
+    <n v="-3.8000000000000007"/>
+    <n v="-0.76000000000000023"/>
+    <n v="5"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="40"/>
+    <n v="-0.76000000000000012"/>
+    <n v="-0.15200000000000005"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <s v="PEG18_UTER"/>
+    <n v="-6.2"/>
+    <n v="-1.24"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="60"/>
+    <n v="-1.24"/>
+    <n v="-0.248"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <s v="LEG1_IRONANNY2"/>
+    <n v="-7.5"/>
+    <n v="-1.5"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="-1.5"/>
+    <n v="-0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <s v="PEG18_DIABLO2"/>
+    <n v="-9.1"/>
+    <n v="-1.82"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="-1.8199999999999998"/>
+    <n v="-0.36399999999999999"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <s v="PEG26_UNKNOWN"/>
+    <n v="-7.5"/>
+    <n v="-1.5"/>
+    <n v="5"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="40"/>
+    <n v="-1.5"/>
+    <n v="-0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <s v="LEG2_LOGAN"/>
+    <n v="-2.6000000000000014"/>
+    <n v="-0.52000000000000035"/>
+    <n v="5"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="80"/>
+    <n v="-0.52000000000000024"/>
+    <n v="-0.10400000000000006"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <s v="SEG1_LITE"/>
+    <n v="18.399999999999999"/>
+    <n v="3.6799999999999997"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="4.5999999999999996"/>
+    <n v="0.91999999999999993"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <s v="UEG7_PIGEON"/>
+    <n v="-3.0999999999999996"/>
+    <n v="-0.61999999999999988"/>
+    <n v="4"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="25"/>
+    <n v="-0.77499999999999991"/>
+    <n v="-0.15499999999999997"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <s v="LEG1_IGOGOSHA2"/>
+    <n v="11.899999999999999"/>
+    <n v="2.38"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="75"/>
+    <n v="2.9749999999999996"/>
+    <n v="0.59499999999999997"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <s v="UEG6_SHERIFF"/>
+    <n v="12.1"/>
+    <n v="2.42"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="50"/>
+    <n v="3.0249999999999999"/>
+    <n v="0.60499999999999998"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <s v="LEG2_ALKASH"/>
+    <n v="-42.900000000000006"/>
+    <n v="-8.58"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="-10.725000000000001"/>
+    <n v="-2.145"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <s v="LEG1_LAKSAe"/>
+    <n v="6"/>
+    <n v="1.2"/>
+    <n v="3"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="2"/>
+    <n v="0.39999999999999997"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <s v="LEG2_DRG"/>
+    <n v="-12"/>
+    <n v="-2.4"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="33.333333333333329"/>
+    <n v="-4"/>
+    <n v="-0.79999999999999993"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <s v="UEG7_ADVENTURE"/>
+    <n v="1.0000000000000002"/>
+    <n v="0.2"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="0.50000000000000011"/>
+    <n v="0.1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <s v="PEG13_DWDDCr"/>
+    <n v="1"/>
+    <n v="0.2"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="0.5"/>
+    <n v="0.1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <s v="LEG2_HOTS"/>
+    <n v="-1.8"/>
+    <n v="-0.36"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="-0.9"/>
+    <n v="-0.18"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <s v="PEG14_RANGER"/>
+    <n v="-1.9000000000000001"/>
+    <n v="-0.38"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="-0.95000000000000007"/>
+    <n v="-0.19"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <s v="UEG4_FALCON"/>
+    <n v="-12"/>
+    <n v="-2.4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="-6"/>
+    <n v="-1.2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <s v="PEG18_ANDUIN"/>
+    <n v="-1.3"/>
+    <n v="-0.26"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="-1.3"/>
+    <n v="-0.26"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="41"/>
+    <s v="LEG1_PHOGA"/>
+    <n v="-6"/>
+    <n v="-1.2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="-6"/>
+    <n v="-1.2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="42"/>
+    <s v="LEG1_OKROSHKA"/>
+    <n v="-1.6"/>
+    <n v="-0.32"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="-1.6"/>
+    <n v="-0.32"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="43"/>
+    <s v="LEG1_BORSCH"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="44"/>
+    <s v="LEG1_PHOBO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="45"/>
+    <s v="LEG2_MONSTER"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="46"/>
+    <s v="PEG14_RWDDCr"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="47"/>
+    <s v="PEG15_ANNA"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="48"/>
+    <s v="PEG15_SILVANA"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="49"/>
+    <s v="PEG18_REXXAR2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="50"/>
+    <s v="PEG18_VARIAN2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="51"/>
+    <s v="PEG2_SDDCr"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="52"/>
+    <s v="PEG20_HOGGER"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="53"/>
+    <s v="PEG8_DOBBY"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="54"/>
+    <s v="PEG8_LOBSTER"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="55"/>
+    <s v="UEG4_CANADIAN"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="56"/>
+    <s v="UEG6_DODO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="57"/>
+    <s v="UEG6_DUELDODO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="58"/>
+    <s v="UEG7_DODO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="59"/>
+    <s v="UEG7_DUELDODO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="60"/>
+    <s v="UEG7_SHERIFF"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="61"/>
+    <s v="UEG7_VULTURE"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="62"/>
+    <s v="UEG8_AVENGER"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="63"/>
+    <s v="WEG4_DOG"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="64"/>
+    <s v="WEG7_PARADOX"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C4CB1275-447E-4587-B9C3-BDD7EB80BE41}" name="Сводная таблица2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C4CB1275-447E-4587-B9C3-BDD7EB80BE41}" name="Сводная таблица2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A12:G19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -3696,7 +3763,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5C6C209-71EC-45CD-876E-D40B4E36B838}" name="Сводная таблица1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5C6C209-71EC-45CD-876E-D40B4E36B838}" name="Сводная таблица1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:G10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -4298,7 +4365,7 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
-        <v>46287</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4329,22 +4396,22 @@
         <v>136</v>
       </c>
       <c r="B4" s="12">
-        <v>-22.100000000000005</v>
+        <v>28.400000000000013</v>
       </c>
       <c r="C4" s="12">
-        <v>-4.4199999999999982</v>
+        <v>5.6800000000000015</v>
       </c>
       <c r="D4" s="12">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E4" s="12">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F4" s="12">
         <v>1</v>
       </c>
       <c r="G4" s="12">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4352,22 +4419,22 @@
         <v>137</v>
       </c>
       <c r="B5" s="12">
-        <v>68.3</v>
+        <v>83.199999999999989</v>
       </c>
       <c r="C5" s="12">
-        <v>13.660000000000002</v>
+        <v>16.64</v>
       </c>
       <c r="D5" s="12">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="E5" s="12">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="F5" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="12">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4375,16 +4442,16 @@
         <v>138</v>
       </c>
       <c r="B6" s="12">
-        <v>15.9</v>
+        <v>20.299999999999997</v>
       </c>
       <c r="C6" s="12">
-        <v>3.1799999999999997</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="D6" s="12">
+        <v>9</v>
+      </c>
+      <c r="E6" s="12">
         <v>7</v>
-      </c>
-      <c r="E6" s="12">
-        <v>5</v>
       </c>
       <c r="F6" s="12">
         <v>0</v>
@@ -4398,22 +4465,22 @@
         <v>139</v>
       </c>
       <c r="B7" s="12">
-        <v>-1.4000000000000004</v>
+        <v>-15.199999999999998</v>
       </c>
       <c r="C7" s="12">
-        <v>-0.28000000000000025</v>
+        <v>-3.0400000000000009</v>
       </c>
       <c r="D7" s="12">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="E7" s="12">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F7" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="12">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4421,13 +4488,13 @@
         <v>140</v>
       </c>
       <c r="B8" s="12">
-        <v>-18.100000000000001</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="C8" s="12">
-        <v>-3.6199999999999997</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="D8" s="12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="12">
         <v>9</v>
@@ -4436,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4444,16 +4511,16 @@
         <v>141</v>
       </c>
       <c r="B9" s="12">
-        <v>45.1</v>
+        <v>62.400000000000006</v>
       </c>
       <c r="C9" s="12">
-        <v>9.02</v>
+        <v>12.48</v>
       </c>
       <c r="D9" s="12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9" s="12">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" s="12">
         <v>1</v>
@@ -4467,22 +4534,22 @@
         <v>134</v>
       </c>
       <c r="B10" s="12">
-        <v>87.699999999999989</v>
+        <v>156.39999999999998</v>
       </c>
       <c r="C10" s="12">
-        <v>17.540000000000006</v>
+        <v>31.279999999999998</v>
       </c>
       <c r="D10" s="12">
-        <v>343</v>
+        <v>412</v>
       </c>
       <c r="E10" s="12">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="F10" s="12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G10" s="12">
-        <v>159</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4700,8 +4767,9 @@
       <c r="E2" s="16">
         <v>46288</v>
       </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="F2" s="16">
+        <v>46290</v>
+      </c>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="16"/>
@@ -4736,6 +4804,9 @@
       <c r="E3">
         <v>-0.9</v>
       </c>
+      <c r="F3">
+        <v>28.400000000000013</v>
+      </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -4753,6 +4824,9 @@
       <c r="E4">
         <v>83</v>
       </c>
+      <c r="F4">
+        <v>83.199999999999989</v>
+      </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -4770,6 +4844,9 @@
       <c r="E5">
         <v>18.100000000000001</v>
       </c>
+      <c r="F5">
+        <v>20.299999999999997</v>
+      </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -4787,6 +4864,9 @@
       <c r="E6">
         <v>-1.9</v>
       </c>
+      <c r="F6">
+        <v>-15.199999999999998</v>
+      </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -4804,6 +4884,9 @@
       <c r="E7">
         <v>-22.7</v>
       </c>
+      <c r="F7">
+        <v>-22.700000000000003</v>
+      </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -4820,6 +4903,9 @@
       </c>
       <c r="E8">
         <v>59.4</v>
+      </c>
+      <c r="F8">
+        <v>62.400000000000006</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -4839,6 +4925,9 @@
         <f t="shared" si="0"/>
         <v>46288</v>
       </c>
+      <c r="F10" s="16">
+        <v>46290</v>
+      </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -4853,13 +4942,17 @@
         <v>-19.799999999999997</v>
       </c>
       <c r="D11">
-        <f t="shared" ref="D11:E11" si="1">D3-C3</f>
+        <f t="shared" ref="D11:F11" si="1">D3-C3</f>
         <v>17.799999999999997</v>
       </c>
       <c r="E11">
         <f t="shared" si="1"/>
         <v>21.200000000000003</v>
       </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>29.300000000000011</v>
+      </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -4870,7 +4963,7 @@
         <v>19.7</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C12:E16" si="3">C4-B4</f>
+        <f t="shared" ref="C12:F16" si="3">C4-B4</f>
         <v>31.000000000000004</v>
       </c>
       <c r="D12">
@@ -4881,6 +4974,10 @@
         <f t="shared" si="3"/>
         <v>14.700000000000003</v>
       </c>
+      <c r="F12">
+        <f t="shared" si="3"/>
+        <v>0.19999999999998863</v>
+      </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -4902,6 +4999,10 @@
         <f t="shared" si="3"/>
         <v>2.2000000000000011</v>
       </c>
+      <c r="F13">
+        <f t="shared" si="3"/>
+        <v>2.1999999999999957</v>
+      </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -4923,6 +5024,10 @@
         <f t="shared" si="3"/>
         <v>-0.5</v>
       </c>
+      <c r="F14">
+        <f t="shared" si="3"/>
+        <v>-13.299999999999997</v>
+      </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -4944,6 +5049,10 @@
         <f t="shared" si="3"/>
         <v>-4.5999999999999979</v>
       </c>
+      <c r="F15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -4964,6 +5073,10 @@
       <c r="E16">
         <f t="shared" si="3"/>
         <v>14.299999999999997</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="3"/>
+        <v>3.0000000000000071</v>
       </c>
     </row>
   </sheetData>
@@ -5069,34 +5182,34 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>111.79999999999998</v>
+        <v>119.69999999999999</v>
       </c>
       <c r="D2">
-        <v>22.360000000000007</v>
+        <v>23.940000000000005</v>
       </c>
       <c r="E2">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I2" s="7">
         <f>IFERROR((F2/E2)*100,0)</f>
-        <v>68.181818181818173</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J2" s="10">
         <f>IFERROR(C2/E2,0)</f>
-        <v>2.5409090909090906</v>
+        <v>2.3470588235294114</v>
       </c>
       <c r="K2" s="10">
         <f>IFERROR(D2/E2,0)</f>
-        <v>0.50818181818181829</v>
+        <v>0.46941176470588247</v>
       </c>
       <c r="L2" s="10" t="str">
         <f>LEFT(B2,3)</f>
@@ -5104,19 +5217,19 @@
       </c>
       <c r="N2">
         <f t="shared" ref="N2:S2" si="0">C2+U2</f>
-        <v>111.79999999999998</v>
+        <v>119.69999999999999</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>22.360000000000007</v>
+        <v>23.940000000000005</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
@@ -5124,7 +5237,7 @@
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -5135,13 +5248,13 @@
         <v>64</v>
       </c>
       <c r="C3">
-        <v>41.9</v>
+        <v>30.099999999999998</v>
       </c>
       <c r="D3">
-        <v>8.3800000000000008</v>
+        <v>6.0200000000000005</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>18</v>
@@ -5150,19 +5263,19 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3" s="7">
         <f>IFERROR((F3/E3)*100,0)</f>
-        <v>52.941176470588239</v>
+        <v>50</v>
       </c>
       <c r="J3" s="10">
         <f>IFERROR(C3/E3,0)</f>
-        <v>1.2323529411764707</v>
+        <v>0.83611111111111103</v>
       </c>
       <c r="K3" s="10">
         <f>IFERROR(D3/E3,0)</f>
-        <v>0.24647058823529414</v>
+        <v>0.16722222222222224</v>
       </c>
       <c r="L3" s="10" t="str">
         <f>LEFT(B3,3)</f>
@@ -5170,15 +5283,15 @@
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N64" si="1">C3+U3</f>
-        <v>41.9</v>
+        <v>30.099999999999998</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O17" si="2">D3+V3</f>
-        <v>8.3800000000000008</v>
+        <v>6.0200000000000005</v>
       </c>
       <c r="P3">
         <f t="shared" ref="P3:P17" si="3">E3+W3</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q17" si="4">F3+X3</f>
@@ -5190,7 +5303,7 @@
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S17" si="6">H3+Z3</f>
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -5201,16 +5314,16 @@
         <v>56</v>
       </c>
       <c r="C4">
-        <v>41.900000000000006</v>
+        <v>44.900000000000006</v>
       </c>
       <c r="D4">
-        <v>8.3800000000000008</v>
+        <v>8.98</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -5220,15 +5333,15 @@
       </c>
       <c r="I4" s="7">
         <f>IFERROR((F4/E4)*100,0)</f>
-        <v>60.606060606060609</v>
+        <v>61.764705882352942</v>
       </c>
       <c r="J4" s="10">
         <f>IFERROR(C4/E4,0)</f>
-        <v>1.2696969696969698</v>
+        <v>1.3205882352941178</v>
       </c>
       <c r="K4" s="10">
         <f>IFERROR(D4/E4,0)</f>
-        <v>0.25393939393939396</v>
+        <v>0.26411764705882357</v>
       </c>
       <c r="L4" s="10" t="str">
         <f>LEFT(B4,3)</f>
@@ -5236,19 +5349,19 @@
       </c>
       <c r="N4">
         <f t="shared" si="1"/>
-        <v>41.900000000000006</v>
+        <v>44.900000000000006</v>
       </c>
       <c r="O4">
         <f t="shared" si="2"/>
-        <v>8.3800000000000008</v>
+        <v>8.98</v>
       </c>
       <c r="P4">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q4">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R4">
         <f t="shared" si="5"/>
@@ -5264,37 +5377,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>46.8</v>
       </c>
       <c r="D5">
-        <v>2.0000000000000009</v>
+        <v>9.3600000000000012</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7">
         <f>IFERROR((F5/E5)*100,0)</f>
-        <v>50</v>
+        <v>72.727272727272734</v>
       </c>
       <c r="J5" s="10">
         <f>IFERROR(C5/E5,0)</f>
-        <v>0.5</v>
+        <v>2.127272727272727</v>
       </c>
       <c r="K5" s="10">
         <f>IFERROR(D5/E5,0)</f>
-        <v>0.10000000000000005</v>
+        <v>0.42545454545454553</v>
       </c>
       <c r="L5" s="10" t="str">
         <f>LEFT(B5,3)</f>
@@ -5302,19 +5415,19 @@
       </c>
       <c r="N5">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>46.8</v>
       </c>
       <c r="O5">
         <f t="shared" si="2"/>
-        <v>2.0000000000000009</v>
+        <v>9.3600000000000012</v>
       </c>
       <c r="P5">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q5">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R5">
         <f t="shared" si="5"/>
@@ -5322,7 +5435,7 @@
       </c>
       <c r="S5">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -5330,19 +5443,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C6">
-        <v>-22.700000000000003</v>
+        <v>13.3</v>
       </c>
       <c r="D6">
-        <v>-4.5399999999999991</v>
+        <v>2.660000000000001</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -5352,35 +5465,35 @@
       </c>
       <c r="I6" s="7">
         <f>IFERROR((F6/E6)*100,0)</f>
-        <v>47.368421052631575</v>
+        <v>52.380952380952387</v>
       </c>
       <c r="J6" s="10">
         <f>IFERROR(C6/E6,0)</f>
-        <v>-1.1947368421052633</v>
+        <v>0.63333333333333341</v>
       </c>
       <c r="K6" s="10">
         <f>IFERROR(D6/E6,0)</f>
-        <v>-0.23894736842105258</v>
+        <v>0.12666666666666671</v>
       </c>
       <c r="L6" s="10" t="str">
         <f>LEFT(B6,3)</f>
-        <v>VEG</v>
+        <v>LEG</v>
       </c>
       <c r="N6">
         <f t="shared" si="1"/>
-        <v>-22.700000000000003</v>
+        <v>13.3</v>
       </c>
       <c r="O6">
         <f t="shared" si="2"/>
-        <v>-4.5399999999999991</v>
+        <v>2.660000000000001</v>
       </c>
       <c r="P6">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q6">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R6">
         <f t="shared" si="5"/>
@@ -5396,49 +5509,49 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C7">
-        <v>34</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="D7">
-        <v>6.8000000000000007</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="E7">
         <v>19</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I7" s="7">
         <f>IFERROR((F7/E7)*100,0)</f>
-        <v>73.68421052631578</v>
+        <v>47.368421052631575</v>
       </c>
       <c r="J7" s="10">
         <f>IFERROR(C7/E7,0)</f>
-        <v>1.7894736842105263</v>
+        <v>-1.1947368421052633</v>
       </c>
       <c r="K7" s="10">
         <f>IFERROR(D7/E7,0)</f>
-        <v>0.35789473684210532</v>
+        <v>-0.23894736842105258</v>
       </c>
       <c r="L7" s="10" t="str">
         <f>LEFT(B7,3)</f>
-        <v>LEG</v>
+        <v>VEG</v>
       </c>
       <c r="N7">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="O7">
         <f t="shared" si="2"/>
-        <v>6.8000000000000007</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="P7">
         <f t="shared" si="3"/>
@@ -5446,7 +5559,7 @@
       </c>
       <c r="Q7">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <f t="shared" si="5"/>
@@ -5454,7 +5567,7 @@
       </c>
       <c r="S7">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -5465,16 +5578,16 @@
         <v>67</v>
       </c>
       <c r="C8">
-        <v>11.2</v>
+        <v>14.5</v>
       </c>
       <c r="D8">
-        <v>2.2400000000000002</v>
+        <v>2.9000000000000004</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -5484,15 +5597,15 @@
       </c>
       <c r="I8" s="7">
         <f>IFERROR((F8/E8)*100,0)</f>
-        <v>41.17647058823529</v>
+        <v>44.444444444444443</v>
       </c>
       <c r="J8" s="10">
         <f>IFERROR(C8/E8,0)</f>
-        <v>0.6588235294117647</v>
+        <v>0.80555555555555558</v>
       </c>
       <c r="K8" s="10">
         <f>IFERROR(D8/E8,0)</f>
-        <v>0.13176470588235295</v>
+        <v>0.16111111111111112</v>
       </c>
       <c r="L8" s="10" t="str">
         <f>LEFT(B8,3)</f>
@@ -5500,19 +5613,19 @@
       </c>
       <c r="N8">
         <f t="shared" si="1"/>
-        <v>11.2</v>
+        <v>14.5</v>
       </c>
       <c r="O8">
         <f t="shared" si="2"/>
-        <v>2.2400000000000002</v>
+        <v>2.9000000000000004</v>
       </c>
       <c r="P8">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <f t="shared" si="5"/>
@@ -5528,37 +5641,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C9">
-        <v>-44.3</v>
+        <v>11.5</v>
       </c>
       <c r="D9">
-        <v>-8.86</v>
+        <v>2.3000000000000007</v>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
         <f>IFERROR((F9/E9)*100,0)</f>
-        <v>35.714285714285715</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="J9" s="10">
         <f>IFERROR(C9/E9,0)</f>
-        <v>-3.1642857142857141</v>
+        <v>0.67647058823529416</v>
       </c>
       <c r="K9" s="10">
         <f>IFERROR(D9/E9,0)</f>
-        <v>-0.63285714285714278</v>
+        <v>0.13529411764705887</v>
       </c>
       <c r="L9" s="10" t="str">
         <f>LEFT(B9,3)</f>
@@ -5566,19 +5679,19 @@
       </c>
       <c r="N9">
         <f t="shared" si="1"/>
-        <v>-44.3</v>
+        <v>11.5</v>
       </c>
       <c r="O9">
         <f t="shared" si="2"/>
-        <v>-8.86</v>
+        <v>2.3000000000000007</v>
       </c>
       <c r="P9">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q9">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <f t="shared" si="5"/>
@@ -5586,7 +5699,7 @@
       </c>
       <c r="S9">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -5597,16 +5710,16 @@
         <v>60</v>
       </c>
       <c r="C10">
-        <v>17.899999999999999</v>
+        <v>27.9</v>
       </c>
       <c r="D10">
-        <v>3.58</v>
+        <v>5.58</v>
       </c>
       <c r="E10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -5616,15 +5729,15 @@
       </c>
       <c r="I10" s="7">
         <f>IFERROR((F10/E10)*100,0)</f>
-        <v>71.428571428571431</v>
+        <v>75</v>
       </c>
       <c r="J10" s="10">
         <f>IFERROR(C10/E10,0)</f>
-        <v>1.2785714285714285</v>
+        <v>1.7437499999999999</v>
       </c>
       <c r="K10" s="10">
         <f>IFERROR(D10/E10,0)</f>
-        <v>0.25571428571428573</v>
+        <v>0.34875</v>
       </c>
       <c r="L10" s="10" t="str">
         <f>LEFT(B10,3)</f>
@@ -5632,19 +5745,19 @@
       </c>
       <c r="N10">
         <f t="shared" si="1"/>
-        <v>17.899999999999999</v>
+        <v>27.9</v>
       </c>
       <c r="O10">
         <f t="shared" si="2"/>
-        <v>3.58</v>
+        <v>5.58</v>
       </c>
       <c r="P10">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q10">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R10">
         <f t="shared" si="5"/>
@@ -5660,37 +5773,37 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C11">
-        <v>10.9</v>
+        <v>-40.799999999999997</v>
       </c>
       <c r="D11">
-        <v>2.1800000000000006</v>
+        <v>-8.16</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I11" s="7">
         <f>IFERROR((F11/E11)*100,0)</f>
-        <v>53.846153846153847</v>
+        <v>40</v>
       </c>
       <c r="J11" s="10">
         <f>IFERROR(C11/E11,0)</f>
-        <v>0.83846153846153848</v>
+        <v>-2.7199999999999998</v>
       </c>
       <c r="K11" s="10">
         <f>IFERROR(D11/E11,0)</f>
-        <v>0.16769230769230775</v>
+        <v>-0.54400000000000004</v>
       </c>
       <c r="L11" s="10" t="str">
         <f>LEFT(B11,3)</f>
@@ -5698,19 +5811,19 @@
       </c>
       <c r="N11">
         <f t="shared" si="1"/>
-        <v>10.9</v>
+        <v>-40.799999999999997</v>
       </c>
       <c r="O11">
         <f t="shared" si="2"/>
-        <v>2.1800000000000006</v>
+        <v>-8.16</v>
       </c>
       <c r="P11">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q11">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R11">
         <f t="shared" si="5"/>
@@ -5718,7 +5831,7 @@
       </c>
       <c r="S11">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -5729,34 +5842,34 @@
         <v>92</v>
       </c>
       <c r="C12">
-        <v>5.5999999999999988</v>
+        <v>2.4999999999999982</v>
       </c>
       <c r="D12">
-        <v>1.1199999999999997</v>
+        <v>0.49999999999999956</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="H12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
         <f>IFERROR((F12/E12)*100,0)</f>
-        <v>41.666666666666671</v>
+        <v>40</v>
       </c>
       <c r="J12" s="10">
         <f>IFERROR(C12/E12,0)</f>
-        <v>0.46666666666666656</v>
+        <v>0.16666666666666655</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(D12/E12,0)</f>
-        <v>9.333333333333331E-2</v>
+        <v>3.3333333333333305E-2</v>
       </c>
       <c r="L12" s="10" t="str">
         <f>LEFT(B12,3)</f>
@@ -5764,19 +5877,19 @@
       </c>
       <c r="N12">
         <f t="shared" si="1"/>
-        <v>5.5999999999999988</v>
+        <v>2.4999999999999982</v>
       </c>
       <c r="O12">
         <f t="shared" si="2"/>
-        <v>1.1199999999999997</v>
+        <v>0.49999999999999956</v>
       </c>
       <c r="P12">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q12">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <f t="shared" si="5"/>
@@ -5784,7 +5897,7 @@
       </c>
       <c r="S12">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -5795,34 +5908,34 @@
         <v>73</v>
       </c>
       <c r="C13">
-        <v>-0.89999999999999813</v>
+        <v>-3.0999999999999983</v>
       </c>
       <c r="D13">
-        <v>-0.17999999999999988</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="E13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="7">
         <f>IFERROR((F13/E13)*100,0)</f>
-        <v>36.363636363636367</v>
+        <v>38.461538461538467</v>
       </c>
       <c r="J13" s="10">
         <f>IFERROR(C13/E13,0)</f>
-        <v>-8.1818181818181651E-2</v>
+        <v>-0.23846153846153834</v>
       </c>
       <c r="K13" s="10">
         <f>IFERROR(D13/E13,0)</f>
-        <v>-1.6363636363636355E-2</v>
+        <v>-4.7692307692307687E-2</v>
       </c>
       <c r="L13" s="10" t="str">
         <f>LEFT(B13,3)</f>
@@ -5830,19 +5943,19 @@
       </c>
       <c r="N13">
         <f t="shared" si="1"/>
-        <v>-0.89999999999999813</v>
+        <v>-3.0999999999999983</v>
       </c>
       <c r="O13">
         <f t="shared" si="2"/>
-        <v>-0.17999999999999988</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="P13">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q13">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R13">
         <f t="shared" si="5"/>
@@ -5850,7 +5963,7 @@
       </c>
       <c r="S13">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
@@ -5924,16 +6037,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C15">
-        <v>-8.8999999999999986</v>
+        <v>-8.7000000000000011</v>
       </c>
       <c r="D15">
-        <v>-1.7799999999999998</v>
+        <v>-1.7399999999999991</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15">
         <v>4</v>
@@ -5942,19 +6055,19 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" s="7">
         <f>IFERROR((F15/E15)*100,0)</f>
-        <v>50</v>
+        <v>44.444444444444443</v>
       </c>
       <c r="J15" s="10">
         <f>IFERROR(C15/E15,0)</f>
-        <v>-1.1124999999999998</v>
+        <v>-0.96666666666666679</v>
       </c>
       <c r="K15" s="10">
         <f>IFERROR(D15/E15,0)</f>
-        <v>-0.22249999999999998</v>
+        <v>-0.19333333333333325</v>
       </c>
       <c r="L15" s="10" t="str">
         <f>LEFT(B15,3)</f>
@@ -5962,15 +6075,15 @@
       </c>
       <c r="N15">
         <f t="shared" si="1"/>
-        <v>-8.8999999999999986</v>
+        <v>-8.7000000000000011</v>
       </c>
       <c r="O15">
         <f t="shared" si="2"/>
-        <v>-1.7799999999999998</v>
+        <v>-1.7399999999999991</v>
       </c>
       <c r="P15">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <f t="shared" si="4"/>
@@ -5982,7 +6095,7 @@
       </c>
       <c r="S15">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -5990,49 +6103,49 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C16">
-        <v>-9.6999999999999993</v>
+        <v>-8.8999999999999986</v>
       </c>
       <c r="D16">
-        <v>-1.9400000000000002</v>
+        <v>-1.7799999999999998</v>
       </c>
       <c r="E16">
         <v>8</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I16" s="7">
         <f>IFERROR((F16/E16)*100,0)</f>
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="J16" s="10">
         <f>IFERROR(C16/E16,0)</f>
-        <v>-1.2124999999999999</v>
+        <v>-1.1124999999999998</v>
       </c>
       <c r="K16" s="10">
         <f>IFERROR(D16/E16,0)</f>
-        <v>-0.24250000000000002</v>
+        <v>-0.22249999999999998</v>
       </c>
       <c r="L16" s="10" t="str">
         <f>LEFT(B16,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N16">
         <f t="shared" si="1"/>
-        <v>-9.6999999999999993</v>
+        <v>-8.8999999999999986</v>
       </c>
       <c r="O16">
         <f t="shared" si="2"/>
-        <v>-1.9400000000000002</v>
+        <v>-1.7799999999999998</v>
       </c>
       <c r="P16">
         <f t="shared" si="3"/>
@@ -6040,7 +6153,7 @@
       </c>
       <c r="Q16">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16">
         <f t="shared" si="5"/>
@@ -6048,7 +6161,7 @@
       </c>
       <c r="S16">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -6056,13 +6169,13 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="C17">
-        <v>-9.4</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="D17">
-        <v>-1.879999999999999</v>
+        <v>-1.9400000000000002</v>
       </c>
       <c r="E17">
         <v>8</v>
@@ -6082,23 +6195,23 @@
       </c>
       <c r="J17" s="10">
         <f>IFERROR(C17/E17,0)</f>
-        <v>-1.175</v>
+        <v>-1.2124999999999999</v>
       </c>
       <c r="K17" s="10">
         <f>IFERROR(D17/E17,0)</f>
-        <v>-0.23499999999999988</v>
+        <v>-0.24250000000000002</v>
       </c>
       <c r="L17" s="10" t="str">
         <f>LEFT(B17,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N17">
         <f t="shared" si="1"/>
-        <v>-9.4</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="O17">
         <f t="shared" si="2"/>
-        <v>-1.879999999999999</v>
+        <v>-1.9400000000000002</v>
       </c>
       <c r="P17">
         <f t="shared" si="3"/>
@@ -6122,37 +6235,37 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="C18">
-        <v>-13</v>
+        <v>1.1999999999999993</v>
       </c>
       <c r="D18">
-        <v>-2.6000000000000005</v>
+        <v>0.23999999999999988</v>
       </c>
       <c r="E18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18" s="7">
         <f>IFERROR((F18/E18)*100,0)</f>
-        <v>42.857142857142854</v>
+        <v>62.5</v>
       </c>
       <c r="J18" s="10">
         <f>IFERROR(C18/E18,0)</f>
-        <v>-1.8571428571428572</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="K18" s="10">
         <f>IFERROR(D18/E18,0)</f>
-        <v>-0.3714285714285715</v>
+        <v>2.9999999999999985E-2</v>
       </c>
       <c r="L18" s="10" t="str">
         <f>LEFT(B18,3)</f>
@@ -6160,27 +6273,27 @@
       </c>
       <c r="N18">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>1.1999999999999993</v>
       </c>
       <c r="O18">
         <f t="shared" ref="O18:O65" si="7">D18+V18</f>
-        <v>-2.6000000000000005</v>
+        <v>0.23999999999999988</v>
       </c>
       <c r="P18">
         <f t="shared" ref="P18:P65" si="8">E18+W18</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <f t="shared" ref="Q18:Q65" si="9">F18+X18</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <f t="shared" ref="R18:R47" si="10">G18+Y18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18">
         <f t="shared" ref="S18:S47" si="11">H18+Z18</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -6188,37 +6301,37 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="C19">
-        <v>1.1999999999999993</v>
+        <v>-13</v>
       </c>
       <c r="D19">
-        <v>0.23999999999999988</v>
+        <v>-2.6000000000000005</v>
       </c>
       <c r="E19">
         <v>7</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7">
         <f>IFERROR((F19/E19)*100,0)</f>
-        <v>71.428571428571431</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="J19" s="10">
         <f>IFERROR(C19/E19,0)</f>
-        <v>0.17142857142857132</v>
+        <v>-1.8571428571428572</v>
       </c>
       <c r="K19" s="10">
         <f>IFERROR(D19/E19,0)</f>
-        <v>3.4285714285714267E-2</v>
+        <v>-0.3714285714285715</v>
       </c>
       <c r="L19" s="10" t="str">
         <f>LEFT(B19,3)</f>
@@ -6226,11 +6339,11 @@
       </c>
       <c r="N19">
         <f t="shared" si="1"/>
-        <v>1.1999999999999993</v>
+        <v>-13</v>
       </c>
       <c r="O19">
         <f t="shared" si="7"/>
-        <v>0.23999999999999988</v>
+        <v>-2.6000000000000005</v>
       </c>
       <c r="P19">
         <f t="shared" si="8"/>
@@ -6238,7 +6351,7 @@
       </c>
       <c r="Q19">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R19">
         <f t="shared" si="10"/>
@@ -6246,7 +6359,7 @@
       </c>
       <c r="S19">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -6785,16 +6898,16 @@
         <v>82</v>
       </c>
       <c r="C28">
-        <v>-5.6000000000000014</v>
+        <v>-2.6000000000000014</v>
       </c>
       <c r="D28">
-        <v>-1.1200000000000003</v>
+        <v>-0.52000000000000035</v>
       </c>
       <c r="E28">
+        <v>5</v>
+      </c>
+      <c r="F28">
         <v>4</v>
-      </c>
-      <c r="F28">
-        <v>3</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6804,15 +6917,15 @@
       </c>
       <c r="I28" s="7">
         <f>IFERROR((F28/E28)*100,0)</f>
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J28" s="10">
         <f>IFERROR(C28/E28,0)</f>
-        <v>-1.4000000000000004</v>
+        <v>-0.52000000000000024</v>
       </c>
       <c r="K28" s="10">
         <f>IFERROR(D28/E28,0)</f>
-        <v>-0.28000000000000008</v>
+        <v>-0.10400000000000006</v>
       </c>
       <c r="L28" s="10" t="str">
         <f>LEFT(B28,3)</f>
@@ -6820,19 +6933,19 @@
       </c>
       <c r="N28">
         <f t="shared" si="1"/>
-        <v>-5.6000000000000014</v>
+        <v>-2.6000000000000014</v>
       </c>
       <c r="O28">
         <f t="shared" si="7"/>
-        <v>-1.1200000000000003</v>
+        <v>-0.52000000000000035</v>
       </c>
       <c r="P28">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R28">
         <f t="shared" si="10"/>
@@ -6848,19 +6961,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="D29">
-        <v>1.2</v>
+        <v>3.6799999999999997</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6874,31 +6987,31 @@
       </c>
       <c r="J29" s="10">
         <f>IFERROR(C29/E29,0)</f>
-        <v>2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="K29" s="10">
         <f>IFERROR(D29/E29,0)</f>
-        <v>0.39999999999999997</v>
+        <v>0.91999999999999993</v>
       </c>
       <c r="L29" s="10" t="str">
         <f>LEFT(B29,3)</f>
-        <v>LEG</v>
+        <v>SEG</v>
       </c>
       <c r="N29">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="O29">
         <f t="shared" si="7"/>
-        <v>1.2</v>
+        <v>3.6799999999999997</v>
       </c>
       <c r="P29">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q29">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R29">
         <f t="shared" si="10"/>
@@ -6914,16 +7027,16 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C30">
-        <v>-12</v>
+        <v>-3.0999999999999996</v>
       </c>
       <c r="D30">
-        <v>-2.4</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -6932,35 +7045,35 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="7">
         <f>IFERROR((F30/E30)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>25</v>
       </c>
       <c r="J30" s="10">
         <f>IFERROR(C30/E30,0)</f>
-        <v>-4</v>
+        <v>-0.77499999999999991</v>
       </c>
       <c r="K30" s="10">
         <f>IFERROR(D30/E30,0)</f>
-        <v>-0.79999999999999993</v>
+        <v>-0.15499999999999997</v>
       </c>
       <c r="L30" s="10" t="str">
         <f>LEFT(B30,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N30">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>-3.0999999999999996</v>
       </c>
       <c r="O30">
         <f t="shared" si="7"/>
-        <v>-2.4</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="P30">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q30">
         <f t="shared" si="9"/>
@@ -6972,7 +7085,7 @@
       </c>
       <c r="S30">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
@@ -6980,16 +7093,16 @@
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C31">
-        <v>16.2</v>
+        <v>11.899999999999999</v>
       </c>
       <c r="D31">
-        <v>3.2399999999999998</v>
+        <v>2.38</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31">
         <v>3</v>
@@ -6998,35 +7111,35 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="7">
         <f>IFERROR((F31/E31)*100,0)</f>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J31" s="10">
         <f>IFERROR(C31/E31,0)</f>
-        <v>5.3999999999999995</v>
+        <v>2.9749999999999996</v>
       </c>
       <c r="K31" s="10">
         <f>IFERROR(D31/E31,0)</f>
-        <v>1.0799999999999998</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="L31" s="10" t="str">
         <f>LEFT(B31,3)</f>
-        <v>SEG</v>
+        <v>LEG</v>
       </c>
       <c r="N31">
         <f t="shared" si="1"/>
-        <v>16.2</v>
+        <v>11.899999999999999</v>
       </c>
       <c r="O31">
         <f t="shared" si="7"/>
-        <v>3.2399999999999998</v>
+        <v>2.38</v>
       </c>
       <c r="P31">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q31">
         <f t="shared" si="9"/>
@@ -7038,7 +7151,7 @@
       </c>
       <c r="S31">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
@@ -7046,19 +7159,19 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C32">
-        <v>-0.19999999999999996</v>
+        <v>12.1</v>
       </c>
       <c r="D32">
-        <v>-3.999999999999998E-2</v>
+        <v>2.42</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -7068,15 +7181,15 @@
       </c>
       <c r="I32" s="7">
         <f>IFERROR((F32/E32)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>50</v>
       </c>
       <c r="J32" s="10">
         <f>IFERROR(C32/E32,0)</f>
-        <v>-6.6666666666666652E-2</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="K32" s="10">
         <f>IFERROR(D32/E32,0)</f>
-        <v>-1.3333333333333327E-2</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="L32" s="10" t="str">
         <f>LEFT(B32,3)</f>
@@ -7084,19 +7197,19 @@
       </c>
       <c r="N32">
         <f t="shared" si="1"/>
-        <v>-0.19999999999999996</v>
+        <v>12.1</v>
       </c>
       <c r="O32">
         <f t="shared" si="7"/>
-        <v>-3.999999999999998E-2</v>
+        <v>2.42</v>
       </c>
       <c r="P32">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q32">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32">
         <f t="shared" si="10"/>
@@ -7112,37 +7225,37 @@
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C33">
-        <v>5.8</v>
+        <v>-42.900000000000006</v>
       </c>
       <c r="D33">
-        <v>1.1599999999999999</v>
+        <v>-8.58</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I33" s="7">
         <f>IFERROR((F33/E33)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>0</v>
       </c>
       <c r="J33" s="10">
         <f>IFERROR(C33/E33,0)</f>
-        <v>1.9333333333333333</v>
+        <v>-10.725000000000001</v>
       </c>
       <c r="K33" s="10">
         <f>IFERROR(D33/E33,0)</f>
-        <v>0.38666666666666666</v>
+        <v>-2.145</v>
       </c>
       <c r="L33" s="10" t="str">
         <f>LEFT(B33,3)</f>
@@ -7150,19 +7263,19 @@
       </c>
       <c r="N33">
         <f t="shared" si="1"/>
-        <v>5.8</v>
+        <v>-42.900000000000006</v>
       </c>
       <c r="O33">
         <f t="shared" si="7"/>
-        <v>1.1599999999999999</v>
+        <v>-8.58</v>
       </c>
       <c r="P33">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q33">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R33">
         <f t="shared" si="10"/>
@@ -7170,7 +7283,7 @@
       </c>
       <c r="S33">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
@@ -7178,49 +7291,49 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="C34">
-        <v>17.2</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>3.44</v>
+        <v>1.2</v>
       </c>
       <c r="E34">
         <v>3</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="7">
         <f>IFERROR((F34/E34)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>100</v>
       </c>
       <c r="J34" s="10">
         <f>IFERROR(C34/E34,0)</f>
-        <v>5.7333333333333334</v>
+        <v>2</v>
       </c>
       <c r="K34" s="10">
         <f>IFERROR(D34/E34,0)</f>
-        <v>1.1466666666666667</v>
+        <v>0.39999999999999997</v>
       </c>
       <c r="L34" s="10" t="str">
         <f>LEFT(B34,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N34">
         <f t="shared" si="1"/>
-        <v>17.2</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <f t="shared" si="7"/>
-        <v>3.44</v>
+        <v>1.2</v>
       </c>
       <c r="P34">
         <f t="shared" si="8"/>
@@ -7228,7 +7341,7 @@
       </c>
       <c r="Q34">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R34">
         <f t="shared" si="10"/>
@@ -7236,7 +7349,7 @@
       </c>
       <c r="S34">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
@@ -7244,37 +7357,37 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C35">
-        <v>-34.6</v>
+        <v>-12</v>
       </c>
       <c r="D35">
-        <v>-6.9200000000000008</v>
+        <v>-2.4</v>
       </c>
       <c r="E35">
         <v>3</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" s="7">
         <f>IFERROR((F35/E35)*100,0)</f>
-        <v>0</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J35" s="10">
         <f>IFERROR(C35/E35,0)</f>
-        <v>-11.533333333333333</v>
+        <v>-4</v>
       </c>
       <c r="K35" s="10">
         <f>IFERROR(D35/E35,0)</f>
-        <v>-2.3066666666666671</v>
+        <v>-0.79999999999999993</v>
       </c>
       <c r="L35" s="10" t="str">
         <f>LEFT(B35,3)</f>
@@ -7282,11 +7395,11 @@
       </c>
       <c r="N35">
         <f t="shared" si="1"/>
-        <v>-34.6</v>
+        <v>-12</v>
       </c>
       <c r="O35">
         <f t="shared" si="7"/>
-        <v>-6.9200000000000008</v>
+        <v>-2.4</v>
       </c>
       <c r="P35">
         <f t="shared" si="8"/>
@@ -7294,7 +7407,7 @@
       </c>
       <c r="Q35">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35">
         <f t="shared" si="10"/>
@@ -7302,7 +7415,7 @@
       </c>
       <c r="S35">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
@@ -7771,17 +7884,17 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
-        <v>86</v>
+      <c r="B43" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -7790,7 +7903,7 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="7">
         <f>IFERROR((F43/E43)*100,0)</f>
@@ -7798,11 +7911,11 @@
       </c>
       <c r="J43" s="10">
         <f>IFERROR(C43/E43,0)</f>
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="K43" s="10">
         <f>IFERROR(D43/E43,0)</f>
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="L43" s="10" t="str">
         <f>LEFT(B43,3)</f>
@@ -7810,15 +7923,15 @@
       </c>
       <c r="N43">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="O43">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="P43">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43">
         <f t="shared" si="9"/>
@@ -7830,15 +7943,15 @@
       </c>
       <c r="S43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>85</v>
+      <c r="B44" t="s">
+        <v>86</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -9295,8 +9408,8 @@
       <c r="B75" s="8"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L75">
-    <sortCondition descending="1" ref="E2:E75"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L65">
+    <sortCondition descending="1" ref="E2:E65"/>
   </sortState>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="dataBar" priority="10">
@@ -9543,7 +9656,7 @@
     <col min="8" max="28" width="6.28515625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -9551,7 +9664,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" t="s">
         <v>120</v>
@@ -9575,25 +9688,25 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
       <c r="B3">
         <f>SUM(H3:AB3)</f>
-        <v>0</v>
+        <v>7.8999999999999986</v>
       </c>
       <c r="C3">
         <f>(B3/$C$1)*100</f>
-        <v>0</v>
+        <v>1.5799999999999998</v>
       </c>
       <c r="D3">
         <f>COUNTA(H3:AB3)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <f>COUNTIF(H3:AB3, "&gt;0")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <f>COUNTIF(H3:AB3, "=0")</f>
@@ -9601,34 +9714,49 @@
       </c>
       <c r="G3">
         <f>COUNTIF(H3:AB3, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="H3" s="20">
+        <v>3.4</v>
+      </c>
+      <c r="I3" s="20">
+        <v>5.3</v>
+      </c>
+      <c r="J3" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="K3" s="20">
+        <v>-0.6</v>
+      </c>
+      <c r="L3" s="20">
+        <v>-2.7</v>
+      </c>
+      <c r="M3" s="20">
+        <v>-3.3</v>
+      </c>
+      <c r="N3" s="20">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B4">
         <f>SUM(H4:AB4)</f>
-        <v>0</v>
+        <v>0.59999999999999964</v>
       </c>
       <c r="C4">
         <f>(B4/$C$1)*100</f>
-        <v>0</v>
+        <v>0.11999999999999993</v>
       </c>
       <c r="D4">
         <f>COUNTA(H4:AB4)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <f>COUNTIF(H4:AB4, "&gt;0")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <f>COUNTIF(H4:AB4, "=0")</f>
@@ -9636,31 +9764,40 @@
       </c>
       <c r="G4">
         <f>COUNTIF(H4:AB4, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H4" s="20">
+        <v>9.6</v>
+      </c>
+      <c r="I4" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="J4" s="21">
+        <v>0.4</v>
+      </c>
+      <c r="K4" s="21">
+        <v>-10.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B5">
         <f>SUM(H5:AB5)</f>
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="C5">
         <f>(B5/$C$1)*100</f>
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="D5">
         <f>COUNTA(H5:AB5)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <f>COUNTIF(H5:AB5, "&gt;0")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <f>COUNTIF(H5:AB5, "=0")</f>
@@ -9668,31 +9805,37 @@
       </c>
       <c r="G5">
         <f>COUNTIF(H5:AB5, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H5" s="20">
+        <v>-0.4</v>
+      </c>
+      <c r="I5" s="21">
+        <v>7.4</v>
+      </c>
+      <c r="J5" s="21">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="B6">
         <f>SUM(H6:AB6)</f>
-        <v>0</v>
+        <v>-3.1000000000000005</v>
       </c>
       <c r="C6">
         <f>(B6/$C$1)*100</f>
-        <v>0</v>
+        <v>-0.62000000000000011</v>
       </c>
       <c r="D6">
         <f>COUNTA(H6:AB6)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <f>COUNTIF(H6:AB6, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <f>COUNTIF(H6:AB6, "=0")</f>
@@ -9700,26 +9843,33 @@
       </c>
       <c r="G6">
         <f>COUNTIF(H6:AB6, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="17"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H6" s="20">
+        <v>4.5</v>
+      </c>
+      <c r="I6" s="21">
+        <v>-2.7</v>
+      </c>
+      <c r="J6" s="21">
+        <v>-4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <f>SUM(H7:AB7)</f>
-        <v>0</v>
+        <v>-11.8</v>
       </c>
       <c r="C7">
         <f>(B7/$C$1)*100</f>
-        <v>0</v>
+        <v>-2.3600000000000003</v>
       </c>
       <c r="D7">
         <f>COUNTA(H7:AB7)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7">
         <f>COUNTIF(H7:AB7, "&gt;0")</f>
@@ -9731,31 +9881,35 @@
       </c>
       <c r="G7">
         <f>COUNTIF(H7:AB7, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="17"/>
+        <v>2</v>
+      </c>
+      <c r="H7" s="20">
+        <v>-4.5999999999999996</v>
+      </c>
+      <c r="I7" s="21">
+        <v>-7.2</v>
+      </c>
       <c r="J7" s="17"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B8">
         <f>SUM(H8:AB8)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C8">
         <f>(B8/$C$1)*100</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <f>COUNTA(H8:AB8)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <f>COUNTIF(H8:AB8, "&gt;0")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <f>COUNTIF(H8:AB8, "=0")</f>
@@ -9765,28 +9919,33 @@
         <f>COUNTIF(H8:AB8, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H8" s="20">
+        <v>4.5</v>
+      </c>
+      <c r="I8" s="20">
+        <v>5.5</v>
+      </c>
+      <c r="J8" s="15"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B9">
         <f>SUM(H9:AB9)</f>
-        <v>0</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="C9">
         <f>(B9/$C$1)*100</f>
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="D9">
         <f>COUNTA(H9:AB9)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <f>COUNTIF(H9:AB9, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <f>COUNTIF(H9:AB9, "=0")</f>
@@ -9794,31 +9953,35 @@
       </c>
       <c r="G9">
         <f>COUNTIF(H9:AB9, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="H9" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="20">
+        <v>-2.7</v>
+      </c>
       <c r="J9" s="17"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B10">
         <f>SUM(H10:AB10)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10">
         <f>(B10/$C$1)*100</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D10">
         <f>COUNTA(H10:AB10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <f>COUNTIF(H10:AB10, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <f>COUNTIF(H10:AB10, "=0")</f>
@@ -9828,29 +9991,31 @@
         <f>COUNTIF(H10:AB10, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H10" s="18"/>
+      <c r="H10" s="20">
+        <v>3</v>
+      </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <f>SUM(H11:AB11)</f>
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="C11">
         <f>(B11/$C$1)*100</f>
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="D11">
         <f>COUNTA(H11:AB11)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <f>COUNTIF(H11:AB11, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <f>COUNTIF(H11:AB11, "=0")</f>
@@ -9860,28 +10025,30 @@
         <f>COUNTIF(H11:AB11, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H11" s="18"/>
+      <c r="H11" s="20">
+        <v>3.3</v>
+      </c>
       <c r="I11" s="19"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B12">
         <f>SUM(H12:AB12)</f>
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="C12">
         <f>(B12/$C$1)*100</f>
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="D12">
         <f>COUNTA(H12:AB12)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <f>COUNTIF(H12:AB12, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <f>COUNTIF(H12:AB12, "=0")</f>
@@ -9891,28 +10058,32 @@
         <f>COUNTIF(H12:AB12, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H12" s="18"/>
+      <c r="H12" s="20">
+        <v>3.3</v>
+      </c>
       <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J12" s="19"/>
+      <c r="K12" s="15"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="B13">
         <f>SUM(H13:AB13)</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C13">
         <f>(B13/$C$1)*100</f>
-        <v>0</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="D13">
         <f>COUNTA(H13:AB13)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <f>COUNTIF(H13:AB13, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <f>COUNTIF(H13:AB13, "=0")</f>
@@ -9922,29 +10093,31 @@
         <f>COUNTIF(H13:AB13, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="15"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H13" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="B14">
         <f>SUM(H14:AB14)</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C14">
         <f>(B14/$C$1)*100</f>
-        <v>0</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="D14">
         <f>COUNTA(H14:AB14)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <f>COUNTIF(H14:AB14, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <f>COUNTIF(H14:AB14, "=0")</f>
@@ -9954,13 +10127,15 @@
         <f>COUNTIF(H14:AB14, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H14" s="18"/>
+      <c r="H14" s="20">
+        <v>0.7</v>
+      </c>
       <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J14" s="15"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B15">
         <f>SUM(H15:AB15)</f>
@@ -9972,7 +10147,7 @@
       </c>
       <c r="D15">
         <f>COUNTA(H15:AB15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <f>COUNTIF(H15:AB15, "&gt;0")</f>
@@ -9980,35 +10155,37 @@
       </c>
       <c r="F15">
         <f>COUNTIF(H15:AB15, "=0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <f>COUNTIF(H15:AB15, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H15" s="18"/>
+      <c r="H15" s="20">
+        <v>0</v>
+      </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="B16">
         <f>SUM(H16:AB16)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <f>(B16/$C$1)*100</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D16">
         <f>COUNTA(H16:AB16)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
         <f>COUNTIF(H16:AB16, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <f>COUNTIF(H16:AB16, "=0")</f>
@@ -10018,28 +10195,30 @@
         <f>COUNTIF(H16:AB16, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H16" s="18"/>
+      <c r="H16" s="20">
+        <v>3</v>
+      </c>
       <c r="I16" s="15"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="B17">
         <f>SUM(H17:AB17)</f>
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="C17">
         <f>(B17/$C$1)*100</f>
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="D17">
         <f>COUNTA(H17:AB17)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <f>COUNTIF(H17:AB17, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
         <f>COUNTIF(H17:AB17, "=0")</f>
@@ -10049,23 +10228,26 @@
         <f>COUNTIF(H17:AB17, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H17" s="17"/>
+      <c r="H17" s="21">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I17" s="17"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="B18">
         <f>SUM(H18:AB18)</f>
-        <v>0</v>
+        <v>-2.9</v>
       </c>
       <c r="C18">
         <f>(B18/$C$1)*100</f>
-        <v>0</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="D18">
         <f>COUNTA(H18:AB18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <f>COUNTIF(H18:AB18, "&gt;0")</f>
@@ -10077,31 +10259,33 @@
       </c>
       <c r="G18">
         <f>COUNTIF(H18:AB18, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="H18" s="20">
+        <v>-2.9</v>
+      </c>
+      <c r="I18" s="15"/>
       <c r="J18" s="15"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B19">
         <f>SUM(H19:AB19)</f>
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="C19">
         <f>(B19/$C$1)*100</f>
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="D19">
         <f>COUNTA(H19:AB19)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <f>COUNTIF(H19:AB19, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <f>COUNTIF(H19:AB19, "=0")</f>
@@ -10111,24 +10295,26 @@
         <f>COUNTIF(H19:AB19, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H19" s="18"/>
+      <c r="H19" s="20">
+        <v>6.1</v>
+      </c>
       <c r="I19" s="15"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="B20">
         <f>SUM(H20:AB20)</f>
-        <v>0</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="C20">
         <f>(B20/$C$1)*100</f>
-        <v>0</v>
+        <v>-1.0199999999999998</v>
       </c>
       <c r="D20">
         <f>COUNTA(H20:AB20)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <f>COUNTIF(H20:AB20, "&gt;0")</f>
@@ -10140,25 +10326,27 @@
       </c>
       <c r="G20">
         <f>COUNTIF(H20:AB20, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="H20" s="20">
+        <v>-5.0999999999999996</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="B21">
         <f>SUM(H21:AB21)</f>
-        <v>0</v>
+        <v>-8.3000000000000007</v>
       </c>
       <c r="C21">
         <f>(B21/$C$1)*100</f>
-        <v>0</v>
+        <v>-1.66</v>
       </c>
       <c r="D21">
         <f>COUNTA(H21:AB21)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <f>COUNTIF(H21:AB21, "&gt;0")</f>
@@ -10170,25 +10358,27 @@
       </c>
       <c r="G21">
         <f>COUNTIF(H21:AB21, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="H21" s="20">
+        <v>-8.3000000000000007</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>74</v>
+      <c r="A22" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="B22">
         <f>SUM(H22:AB22)</f>
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="C22">
         <f>(B22/$C$1)*100</f>
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="D22">
         <f>COUNTA(H22:AB22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <f>COUNTIF(H22:AB22, "&gt;0")</f>
@@ -10200,13 +10390,15 @@
       </c>
       <c r="G22">
         <f>COUNTIF(H22:AB22, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="H22" s="21">
+        <v>-1.6</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B23">
         <f>SUM(H23:AB23)</f>
@@ -10233,10 +10425,12 @@
         <v>0</v>
       </c>
       <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="B24">
         <f>SUM(H24:AB24)</f>
@@ -10263,11 +10457,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B25">
         <f>SUM(H25:AB25)</f>
@@ -10297,7 +10490,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="B26">
         <f>SUM(H26:AB26)</f>
@@ -10327,7 +10520,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B27">
         <f>SUM(H27:AB27)</f>
@@ -10357,7 +10550,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="B28">
         <f>SUM(H28:AB28)</f>
@@ -10391,7 +10584,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B29">
         <f>SUM(H29:AB29)</f>
@@ -10421,7 +10614,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30">
         <f>SUM(H30:AB30)</f>
@@ -10451,7 +10644,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="B31">
         <f>SUM(H31:AB31)</f>
@@ -10478,10 +10671,11 @@
         <v>0</v>
       </c>
       <c r="H31" s="19"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B32">
         <f>SUM(H32:AB32)</f>
@@ -10507,12 +10701,11 @@
         <f>COUNTIF(H32:AB32, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
+      <c r="H32" s="19"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="B33">
         <f>SUM(H33:AB33)</f>
@@ -10538,11 +10731,11 @@
         <f>COUNTIF(H33:AB33, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H33" s="17"/>
+      <c r="H33" s="19"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B34">
         <f>SUM(H34:AB34)</f>
@@ -10572,7 +10765,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B35">
         <f>SUM(H35:AB35)</f>
@@ -10598,11 +10791,11 @@
         <f>COUNTIF(H35:AB35, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H35" s="17"/>
+      <c r="H35" s="18"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="B36">
         <f>SUM(H36:AB36)</f>
@@ -10632,7 +10825,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B37">
         <f>SUM(H37:AB37)</f>
@@ -10658,12 +10851,12 @@
         <f>COUNTIF(H37:AB37, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H37" s="15"/>
+      <c r="H37" s="19"/>
       <c r="I37" s="15"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="B38">
         <f>SUM(H38:AB38)</f>
@@ -10693,7 +10886,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B39">
         <f>SUM(H39:AB39)</f>
@@ -10723,7 +10916,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="B40">
         <f>SUM(H40:AB40)</f>
@@ -10753,7 +10946,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="B41">
         <f>SUM(H41:AB41)</f>
@@ -10785,7 +10978,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="B42">
         <f>SUM(H42:AB42)</f>
@@ -10815,7 +11008,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="B43">
         <f>SUM(H43:AB43)</f>
@@ -10845,7 +11038,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B44">
         <f>SUM(H44:AB44)</f>
@@ -10874,8 +11067,8 @@
       <c r="H44" s="15"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>85</v>
+      <c r="A45" t="s">
+        <v>86</v>
       </c>
       <c r="B45">
         <f>SUM(H45:AB45)</f>
@@ -10901,6 +11094,7 @@
         <f>COUNTIF(H45:AB45, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H45" s="15"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292FA713-08CB-42F6-9AF0-9A1C90F879A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1FA3C71-F238-4170-9A7C-129BF3B2FEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="1" r:id="rId6"/>
-    <pivotCache cacheId="4" r:id="rId7"/>
+    <pivotCache cacheId="11" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="157">
   <si>
     <t>AQUA</t>
   </si>
@@ -486,12 +486,42 @@
   </si>
   <si>
     <t>UEG4_CANADIAN</t>
+  </si>
+  <si>
+    <t>UEG7_CARRIER</t>
+  </si>
+  <si>
+    <t>UEG7_CELEBRITY</t>
+  </si>
+  <si>
+    <t>VEG1_MOON</t>
+  </si>
+  <si>
+    <t>UEG4_PELICAN2</t>
+  </si>
+  <si>
+    <t>UEG8_SOLDIER</t>
+  </si>
+  <si>
+    <t>UEG9_GRAVY2</t>
+  </si>
+  <si>
+    <t>UEG7_CANNIBAL</t>
+  </si>
+  <si>
+    <t>UEG7_LOVERGOOSE</t>
+  </si>
+  <si>
+    <t>UEG9_BIRDWATCHER2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.0"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -595,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -632,6 +662,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2071,64 +2107,6 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46288.785760416664" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="41" xr:uid="{93B0B297-F304-40FC-B21C-BCAAF0FA44CB}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:L42" sheet="Результаты"/>
-  </cacheSource>
-  <cacheFields count="12">
-    <cacheField name="Номер" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="41"/>
-    </cacheField>
-    <cacheField name="Стратегия" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Абс" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-44.3" maxValue="111.79999999999998"/>
-    </cacheField>
-    <cacheField name="Отн" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-8.86" maxValue="22.360000000000007"/>
-    </cacheField>
-    <cacheField name="Кол-во" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="44"/>
-    </cacheField>
-    <cacheField name="Прибыль" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="30"/>
-    </cacheField>
-    <cacheField name="Нейтрал" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
-    </cacheField>
-    <cacheField name="Убыток" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="15"/>
-    </cacheField>
-    <cacheField name="ПроцПД" numFmtId="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="100"/>
-    </cacheField>
-    <cacheField name="САП" numFmtId="2">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-11.533333333333333" maxValue="5.7333333333333334"/>
-    </cacheField>
-    <cacheField name="СОП" numFmtId="2">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-2.3066666666666671" maxValue="1.1466666666666667"/>
-    </cacheField>
-    <cacheField name="Тип" numFmtId="2">
-      <sharedItems count="6">
-        <s v="PEG"/>
-        <s v="WEG"/>
-        <s v="LEG"/>
-        <s v="VEG"/>
-        <s v="UEG"/>
-        <s v="SEG"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46290.963686805553" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="64" xr:uid="{1976E921-BE3A-4FF1-A5EF-18E3F04892B4}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:L65" sheet="Результаты"/>
@@ -2186,66 +2164,139 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46293.962728356484" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="76" xr:uid="{3D6F248A-0360-4477-B017-E96CAA4B0EB4}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:L1048576" sheet="Результаты"/>
+  </cacheSource>
+  <cacheFields count="12">
+    <cacheField name="Номер" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="64"/>
+    </cacheField>
+    <cacheField name="Стратегия" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Абс" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-42.900000000000006" maxValue="130.29999999999998"/>
+    </cacheField>
+    <cacheField name="Отн" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-8.58" maxValue="26.060000000000006"/>
+    </cacheField>
+    <cacheField name="Кол-во" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="54"/>
+    </cacheField>
+    <cacheField name="Прибыль" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="37"/>
+    </cacheField>
+    <cacheField name="Нейтрал" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
+    </cacheField>
+    <cacheField name="Убыток" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="17"/>
+    </cacheField>
+    <cacheField name="ПроцПД" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="100"/>
+    </cacheField>
+    <cacheField name="САП" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-19.5" maxValue="5.22"/>
+    </cacheField>
+    <cacheField name="СОП" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-3.9" maxValue="1.044"/>
+    </cacheField>
+    <cacheField name="Тип" numFmtId="0">
+      <sharedItems containsBlank="1" count="7">
+        <s v="PEG"/>
+        <s v="WEG"/>
+        <s v="LEG"/>
+        <s v="VEG"/>
+        <s v="UEG"/>
+        <s v="SEG"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="41">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="64">
   <r>
     <n v="1"/>
     <s v="PEG17_PHOENIX"/>
-    <n v="111.79999999999998"/>
-    <n v="22.360000000000007"/>
-    <n v="44"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="14"/>
-    <n v="68.181818181818173"/>
-    <n v="2.5409090909090906"/>
-    <n v="0.50818181818181829"/>
+    <n v="119.69999999999999"/>
+    <n v="23.940000000000005"/>
+    <n v="51"/>
+    <n v="34"/>
+    <n v="0"/>
+    <n v="17"/>
+    <n v="66.666666666666657"/>
+    <n v="2.3470588235294114"/>
+    <n v="0.46941176470588247"/>
     <x v="0"/>
   </r>
   <r>
     <n v="2"/>
     <s v="PEG11_KUSURUKEN"/>
-    <n v="41.9"/>
-    <n v="8.3800000000000008"/>
-    <n v="34"/>
+    <n v="30.099999999999998"/>
+    <n v="6.0200000000000005"/>
+    <n v="36"/>
     <n v="18"/>
     <n v="1"/>
-    <n v="15"/>
-    <n v="52.941176470588239"/>
-    <n v="1.2323529411764707"/>
-    <n v="0.24647058823529414"/>
+    <n v="17"/>
+    <n v="50"/>
+    <n v="0.83611111111111103"/>
+    <n v="0.16722222222222224"/>
     <x v="0"/>
   </r>
   <r>
     <n v="3"/>
     <s v="WEG3_BATYA"/>
-    <n v="41.900000000000006"/>
-    <n v="8.3800000000000008"/>
-    <n v="33"/>
-    <n v="20"/>
+    <n v="44.900000000000006"/>
+    <n v="8.98"/>
+    <n v="34"/>
+    <n v="21"/>
     <n v="0"/>
     <n v="13"/>
-    <n v="60.606060606060609"/>
-    <n v="1.2696969696969698"/>
-    <n v="0.25393939393939396"/>
+    <n v="61.764705882352942"/>
+    <n v="1.3205882352941178"/>
+    <n v="0.26411764705882357"/>
     <x v="1"/>
   </r>
   <r>
     <n v="4"/>
+    <s v="LEG2_FENNEC"/>
+    <n v="46.8"/>
+    <n v="9.3600000000000012"/>
+    <n v="22"/>
+    <n v="16"/>
+    <n v="0"/>
+    <n v="6"/>
+    <n v="72.727272727272734"/>
+    <n v="2.127272727272727"/>
+    <n v="0.42545454545454553"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="5"/>
     <s v="LEG2_DRINKER"/>
+    <n v="13.3"/>
+    <n v="2.660000000000001"/>
+    <n v="21"/>
+    <n v="11"/>
+    <n v="0"/>
     <n v="10"/>
-    <n v="2.0000000000000009"/>
-    <n v="20"/>
-    <n v="10"/>
-    <n v="0"/>
-    <n v="10"/>
-    <n v="50"/>
-    <n v="0.5"/>
-    <n v="0.10000000000000005"/>
+    <n v="52.380952380952387"/>
+    <n v="0.63333333333333341"/>
+    <n v="0.12666666666666671"/>
     <x v="2"/>
   </r>
   <r>
-    <n v="5"/>
+    <n v="6"/>
     <s v="VEG1_VENUS"/>
     <n v="-22.700000000000003"/>
     <n v="-4.5399999999999991"/>
@@ -2259,101 +2310,87 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="6"/>
-    <s v="LEG2_FENNEC"/>
-    <n v="34"/>
-    <n v="6.8000000000000007"/>
-    <n v="19"/>
-    <n v="14"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="73.68421052631578"/>
-    <n v="1.7894736842105263"/>
-    <n v="0.35789473684210532"/>
-    <x v="2"/>
-  </r>
-  <r>
     <n v="7"/>
     <s v="LEG1_PIN"/>
-    <n v="11.2"/>
-    <n v="2.2400000000000002"/>
-    <n v="17"/>
-    <n v="7"/>
+    <n v="14.5"/>
+    <n v="2.9000000000000004"/>
+    <n v="18"/>
+    <n v="8"/>
     <n v="1"/>
     <n v="9"/>
-    <n v="41.17647058823529"/>
-    <n v="0.6588235294117647"/>
-    <n v="0.13176470588235295"/>
+    <n v="44.444444444444443"/>
+    <n v="0.80555555555555558"/>
+    <n v="0.16111111111111112"/>
     <x v="2"/>
   </r>
   <r>
     <n v="8"/>
+    <s v="PEG4_UNIVERSAL"/>
+    <n v="11.5"/>
+    <n v="2.3000000000000007"/>
+    <n v="17"/>
+    <n v="10"/>
+    <n v="1"/>
+    <n v="6"/>
+    <n v="58.82352941176471"/>
+    <n v="0.67647058823529416"/>
+    <n v="0.13529411764705887"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <s v="LEG2_LYNX"/>
+    <n v="27.9"/>
+    <n v="5.58"/>
+    <n v="16"/>
+    <n v="12"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="75"/>
+    <n v="1.7437499999999999"/>
+    <n v="0.34875"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="11"/>
     <s v="PEG18_BLAZE"/>
-    <n v="-44.3"/>
-    <n v="-8.86"/>
-    <n v="14"/>
-    <n v="5"/>
+    <n v="-40.799999999999997"/>
+    <n v="-8.16"/>
+    <n v="15"/>
+    <n v="6"/>
     <n v="1"/>
     <n v="8"/>
-    <n v="35.714285714285715"/>
-    <n v="-3.1642857142857141"/>
-    <n v="-0.63285714285714278"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <s v="LEG2_LYNX"/>
-    <n v="17.899999999999999"/>
-    <n v="3.58"/>
-    <n v="14"/>
-    <n v="10"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="71.428571428571431"/>
-    <n v="1.2785714285714285"/>
-    <n v="0.25571428571428573"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="11"/>
-    <s v="PEG4_UNIVERSAL"/>
-    <n v="10.9"/>
-    <n v="2.1800000000000006"/>
-    <n v="13"/>
-    <n v="7"/>
-    <n v="1"/>
-    <n v="5"/>
-    <n v="53.846153846153847"/>
-    <n v="0.83846153846153848"/>
-    <n v="0.16769230769230775"/>
+    <n v="40"/>
+    <n v="-2.7199999999999998"/>
+    <n v="-0.54400000000000004"/>
     <x v="0"/>
   </r>
   <r>
     <n v="13"/>
     <s v="UEG6_ADVENTURE"/>
-    <n v="5.5999999999999988"/>
-    <n v="1.1199999999999997"/>
-    <n v="12"/>
-    <n v="5"/>
+    <n v="2.4999999999999982"/>
+    <n v="0.49999999999999956"/>
+    <n v="15"/>
+    <n v="6"/>
     <n v="2"/>
-    <n v="5"/>
-    <n v="41.666666666666671"/>
-    <n v="0.46666666666666656"/>
-    <n v="9.333333333333331E-2"/>
+    <n v="7"/>
+    <n v="40"/>
+    <n v="0.16666666666666655"/>
+    <n v="3.3333333333333305E-2"/>
     <x v="4"/>
   </r>
   <r>
     <n v="12"/>
     <s v="UEG6_PIGEON"/>
-    <n v="-0.89999999999999813"/>
-    <n v="-0.17999999999999988"/>
-    <n v="11"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="7"/>
-    <n v="36.363636363636367"/>
-    <n v="-8.1818181818181651E-2"/>
-    <n v="-1.6363636363636355E-2"/>
+    <n v="-3.0999999999999983"/>
+    <n v="-0.61999999999999988"/>
+    <n v="13"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="8"/>
+    <n v="38.461538461538467"/>
+    <n v="-0.23846153846153834"/>
+    <n v="-4.7692307692307687E-2"/>
     <x v="4"/>
   </r>
   <r>
@@ -2372,6 +2409,20 @@
   </r>
   <r>
     <n v="14"/>
+    <s v="LEG1_BIBI2"/>
+    <n v="-8.7000000000000011"/>
+    <n v="-1.7399999999999991"/>
+    <n v="9"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="44.444444444444443"/>
+    <n v="-0.96666666666666679"/>
+    <n v="-0.19333333333333325"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="15"/>
     <s v="LEG1_CC2"/>
     <n v="-8.8999999999999986"/>
     <n v="-1.7799999999999998"/>
@@ -2385,7 +2436,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="15"/>
+    <n v="17"/>
     <s v="UEG6_VULTURE"/>
     <n v="-9.6999999999999993"/>
     <n v="-1.9400000000000002"/>
@@ -2399,21 +2450,21 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="17"/>
-    <s v="LEG1_BIBI2"/>
-    <n v="-9.4"/>
-    <n v="-1.879999999999999"/>
+    <n v="16"/>
+    <s v="PEG4_U3"/>
+    <n v="1.1999999999999993"/>
+    <n v="0.23999999999999988"/>
     <n v="8"/>
-    <n v="3"/>
-    <n v="0"/>
     <n v="5"/>
-    <n v="37.5"/>
-    <n v="-1.175"/>
-    <n v="-0.23499999999999988"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="16"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="62.5"/>
+    <n v="0.14999999999999991"/>
+    <n v="2.9999999999999985E-2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="19"/>
     <s v="PEG18_UTER2"/>
     <n v="-13"/>
     <n v="-2.6000000000000005"/>
@@ -2424,20 +2475,6 @@
     <n v="42.857142857142854"/>
     <n v="-1.8571428571428572"/>
     <n v="-0.3714285714285715"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="19"/>
-    <s v="PEG4_U3"/>
-    <n v="1.1999999999999993"/>
-    <n v="0.23999999999999988"/>
-    <n v="7"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="71.428571428571431"/>
-    <n v="0.17142857142857132"/>
-    <n v="3.4285714285714267E-2"/>
     <x v="0"/>
   </r>
   <r>
@@ -2555,19 +2592,89 @@
   <r>
     <n v="29"/>
     <s v="LEG2_LOGAN"/>
-    <n v="-5.6000000000000014"/>
-    <n v="-1.1200000000000003"/>
+    <n v="-2.6000000000000014"/>
+    <n v="-0.52000000000000035"/>
+    <n v="5"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="80"/>
+    <n v="-0.52000000000000024"/>
+    <n v="-0.10400000000000006"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <s v="SEG1_LITE"/>
+    <n v="18.399999999999999"/>
+    <n v="3.6799999999999997"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="4.5999999999999996"/>
+    <n v="0.91999999999999993"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <s v="UEG7_PIGEON"/>
+    <n v="-3.0999999999999996"/>
+    <n v="-0.61999999999999988"/>
+    <n v="4"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="25"/>
+    <n v="-0.77499999999999991"/>
+    <n v="-0.15499999999999997"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <s v="LEG1_IGOGOSHA2"/>
+    <n v="11.899999999999999"/>
+    <n v="2.38"/>
     <n v="4"/>
     <n v="3"/>
     <n v="0"/>
     <n v="1"/>
     <n v="75"/>
-    <n v="-1.4000000000000004"/>
-    <n v="-0.28000000000000008"/>
+    <n v="2.9749999999999996"/>
+    <n v="0.59499999999999997"/>
     <x v="2"/>
   </r>
   <r>
-    <n v="27"/>
+    <n v="36"/>
+    <s v="UEG6_SHERIFF"/>
+    <n v="12.1"/>
+    <n v="2.42"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="50"/>
+    <n v="3.0249999999999999"/>
+    <n v="0.60499999999999998"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <s v="LEG2_ALKASH"/>
+    <n v="-42.900000000000006"/>
+    <n v="-8.58"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="-10.725000000000001"/>
+    <n v="-2.145"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="38"/>
     <s v="LEG1_LAKSAe"/>
     <n v="6"/>
     <n v="1.2"/>
@@ -2581,7 +2688,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="28"/>
+    <n v="39"/>
     <s v="LEG2_DRG"/>
     <n v="-12"/>
     <n v="-2.4"/>
@@ -2592,76 +2699,6 @@
     <n v="33.333333333333329"/>
     <n v="-4"/>
     <n v="-0.79999999999999993"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="35"/>
-    <s v="SEG1_LITE"/>
-    <n v="16.2"/>
-    <n v="3.2399999999999998"/>
-    <n v="3"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="5.3999999999999995"/>
-    <n v="1.0799999999999998"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="36"/>
-    <s v="UEG7_PIGEON"/>
-    <n v="-0.19999999999999996"/>
-    <n v="-3.999999999999998E-2"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="33.333333333333329"/>
-    <n v="-6.6666666666666652E-2"/>
-    <n v="-1.3333333333333327E-2"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="37"/>
-    <s v="LEG1_IGOGOSHA2"/>
-    <n v="5.8"/>
-    <n v="1.1599999999999999"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="66.666666666666657"/>
-    <n v="1.9333333333333333"/>
-    <n v="0.38666666666666666"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="38"/>
-    <s v="UEG6_SHERIFF"/>
-    <n v="17.2"/>
-    <n v="3.44"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="66.666666666666657"/>
-    <n v="5.7333333333333334"/>
-    <n v="1.1466666666666667"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="39"/>
-    <s v="LEG2_ALKASH"/>
-    <n v="-34.6"/>
-    <n v="-6.9200000000000008"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-11.533333333333333"/>
-    <n v="-2.3066666666666671"/>
     <x v="2"/>
   </r>
   <r>
@@ -2762,27 +2799,363 @@
     <n v="-1.2"/>
     <x v="2"/>
   </r>
+  <r>
+    <n v="42"/>
+    <s v="LEG1_OKROSHKA"/>
+    <n v="-1.6"/>
+    <n v="-0.32"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="-1.6"/>
+    <n v="-0.32"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="43"/>
+    <s v="LEG1_BORSCH"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="44"/>
+    <s v="LEG1_PHOBO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="45"/>
+    <s v="LEG2_MONSTER"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="46"/>
+    <s v="PEG14_RWDDCr"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="47"/>
+    <s v="PEG15_ANNA"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="48"/>
+    <s v="PEG15_SILVANA"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="49"/>
+    <s v="PEG18_REXXAR2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="50"/>
+    <s v="PEG18_VARIAN2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="51"/>
+    <s v="PEG2_SDDCr"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="52"/>
+    <s v="PEG20_HOGGER"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="53"/>
+    <s v="PEG8_DOBBY"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="54"/>
+    <s v="PEG8_LOBSTER"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="55"/>
+    <s v="UEG4_CANADIAN"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="56"/>
+    <s v="UEG6_DODO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="57"/>
+    <s v="UEG6_DUELDODO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="58"/>
+    <s v="UEG7_DODO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="59"/>
+    <s v="UEG7_DUELDODO"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="60"/>
+    <s v="UEG7_SHERIFF"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="61"/>
+    <s v="UEG7_VULTURE"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="62"/>
+    <s v="UEG8_AVENGER"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="63"/>
+    <s v="WEG4_DOG"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="64"/>
+    <s v="WEG7_PARADOX"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="64">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="76">
   <r>
     <n v="1"/>
     <s v="PEG17_PHOENIX"/>
-    <n v="119.69999999999999"/>
-    <n v="23.940000000000005"/>
-    <n v="51"/>
-    <n v="34"/>
+    <n v="130.29999999999998"/>
+    <n v="26.060000000000006"/>
+    <n v="54"/>
+    <n v="37"/>
     <n v="0"/>
     <n v="17"/>
-    <n v="66.666666666666657"/>
-    <n v="2.3470588235294114"/>
-    <n v="0.46941176470588247"/>
+    <n v="68.518518518518519"/>
+    <n v="2.4129629629629625"/>
+    <n v="0.48259259259259268"/>
     <x v="0"/>
   </r>
   <r>
     <n v="2"/>
+    <s v="WEG3_BATYA"/>
+    <n v="55.500000000000007"/>
+    <n v="11.100000000000001"/>
+    <n v="38"/>
+    <n v="23"/>
+    <n v="0"/>
+    <n v="15"/>
+    <n v="60.526315789473685"/>
+    <n v="1.4605263157894739"/>
+    <n v="0.29210526315789476"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="3"/>
     <s v="PEG11_KUSURUKEN"/>
     <n v="30.099999999999998"/>
     <n v="6.0200000000000005"/>
@@ -2796,20 +3169,6 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="3"/>
-    <s v="WEG3_BATYA"/>
-    <n v="44.900000000000006"/>
-    <n v="8.98"/>
-    <n v="34"/>
-    <n v="21"/>
-    <n v="0"/>
-    <n v="13"/>
-    <n v="61.764705882352942"/>
-    <n v="1.3205882352941178"/>
-    <n v="0.26411764705882357"/>
-    <x v="1"/>
-  </r>
-  <r>
     <n v="4"/>
     <s v="LEG2_FENNEC"/>
     <n v="46.8"/>
@@ -2826,19 +3185,33 @@
   <r>
     <n v="5"/>
     <s v="LEG2_DRINKER"/>
-    <n v="13.3"/>
-    <n v="2.660000000000001"/>
-    <n v="21"/>
+    <n v="9.6000000000000014"/>
+    <n v="1.920000000000001"/>
+    <n v="22"/>
     <n v="11"/>
     <n v="0"/>
-    <n v="10"/>
-    <n v="52.380952380952387"/>
-    <n v="0.63333333333333341"/>
-    <n v="0.12666666666666671"/>
+    <n v="11"/>
+    <n v="50"/>
+    <n v="0.43636363636363645"/>
+    <n v="8.7272727272727321E-2"/>
     <x v="2"/>
   </r>
   <r>
     <n v="6"/>
+    <s v="PEG4_UNIVERSAL"/>
+    <n v="3.4000000000000004"/>
+    <n v="0.68000000000000083"/>
+    <n v="20"/>
+    <n v="11"/>
+    <n v="1"/>
+    <n v="8"/>
+    <n v="55.000000000000007"/>
+    <n v="0.17"/>
+    <n v="3.4000000000000044E-2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
     <s v="VEG1_VENUS"/>
     <n v="-22.700000000000003"/>
     <n v="-4.5399999999999991"/>
@@ -2852,49 +3225,49 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="7"/>
+    <n v="8"/>
     <s v="LEG1_PIN"/>
-    <n v="14.5"/>
-    <n v="2.9000000000000004"/>
-    <n v="18"/>
-    <n v="8"/>
+    <n v="16.3"/>
+    <n v="3.2600000000000002"/>
+    <n v="19"/>
+    <n v="9"/>
     <n v="1"/>
     <n v="9"/>
-    <n v="44.444444444444443"/>
-    <n v="0.80555555555555558"/>
-    <n v="0.16111111111111112"/>
+    <n v="47.368421052631575"/>
+    <n v="0.85789473684210527"/>
+    <n v="0.17157894736842105"/>
     <x v="2"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <s v="PEG4_UNIVERSAL"/>
-    <n v="11.5"/>
-    <n v="2.3000000000000007"/>
-    <n v="17"/>
-    <n v="10"/>
-    <n v="1"/>
-    <n v="6"/>
-    <n v="58.82352941176471"/>
-    <n v="0.67647058823529416"/>
-    <n v="0.13529411764705887"/>
-    <x v="0"/>
   </r>
   <r>
     <n v="9"/>
     <s v="LEG2_LYNX"/>
-    <n v="27.9"/>
-    <n v="5.58"/>
-    <n v="16"/>
-    <n v="12"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="75"/>
-    <n v="1.7437499999999999"/>
-    <n v="0.34875"/>
+    <n v="32.099999999999994"/>
+    <n v="6.42"/>
+    <n v="19"/>
+    <n v="14"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="73.68421052631578"/>
+    <n v="1.689473684210526"/>
+    <n v="0.33789473684210525"/>
     <x v="2"/>
   </r>
   <r>
     <n v="11"/>
+    <s v="UEG6_ADVENTURE"/>
+    <n v="22.6"/>
+    <n v="4.5199999999999996"/>
+    <n v="17"/>
+    <n v="8"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="47.058823529411761"/>
+    <n v="1.3294117647058825"/>
+    <n v="0.26588235294117646"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="13"/>
     <s v="PEG18_BLAZE"/>
     <n v="-40.799999999999997"/>
     <n v="-8.16"/>
@@ -2906,20 +3279,6 @@
     <n v="-2.7199999999999998"/>
     <n v="-0.54400000000000004"/>
     <x v="0"/>
-  </r>
-  <r>
-    <n v="13"/>
-    <s v="UEG6_ADVENTURE"/>
-    <n v="2.4999999999999982"/>
-    <n v="0.49999999999999956"/>
-    <n v="15"/>
-    <n v="6"/>
-    <n v="2"/>
-    <n v="7"/>
-    <n v="40"/>
-    <n v="0.16666666666666655"/>
-    <n v="3.3333333333333305E-2"/>
-    <x v="4"/>
   </r>
   <r>
     <n v="12"/>
@@ -2952,15 +3311,15 @@
   <r>
     <n v="14"/>
     <s v="LEG1_BIBI2"/>
-    <n v="-8.7000000000000011"/>
-    <n v="-1.7399999999999991"/>
-    <n v="9"/>
-    <n v="4"/>
-    <n v="0"/>
+    <n v="1.0999999999999996"/>
+    <n v="0.22000000000000108"/>
+    <n v="10"/>
     <n v="5"/>
-    <n v="44.444444444444443"/>
-    <n v="-0.96666666666666679"/>
-    <n v="-0.19333333333333325"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="50"/>
+    <n v="0.10999999999999996"/>
+    <n v="2.200000000000011E-2"/>
     <x v="2"/>
   </r>
   <r>
@@ -3035,6 +3394,20 @@
   </r>
   <r>
     <n v="20"/>
+    <s v="LEG2_LOGAN"/>
+    <n v="-0.90000000000000147"/>
+    <n v="-0.18000000000000038"/>
+    <n v="6"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="83.333333333333343"/>
+    <n v="-0.15000000000000024"/>
+    <n v="-3.0000000000000065E-2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="21"/>
     <s v="SEG3_FORCE"/>
     <n v="1.9000000000000004"/>
     <n v="0.37999999999999989"/>
@@ -3048,7 +3421,7 @@
     <x v="5"/>
   </r>
   <r>
-    <n v="21"/>
+    <n v="22"/>
     <s v="UEG4_PELICAN"/>
     <n v="-2.9000000000000004"/>
     <n v="-0.58000000000000007"/>
@@ -3062,7 +3435,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="22"/>
+    <n v="23"/>
     <s v="PEG19_ANUBARAK"/>
     <n v="-3.8000000000000007"/>
     <n v="-0.76000000000000023"/>
@@ -3076,7 +3449,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="23"/>
+    <n v="24"/>
     <s v="PEG18_UTER"/>
     <n v="-6.2"/>
     <n v="-1.24"/>
@@ -3090,7 +3463,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="24"/>
+    <n v="25"/>
     <s v="LEG1_IRONANNY2"/>
     <n v="-7.5"/>
     <n v="-1.5"/>
@@ -3104,7 +3477,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="25"/>
+    <n v="26"/>
     <s v="PEG18_DIABLO2"/>
     <n v="-9.1"/>
     <n v="-1.82"/>
@@ -3118,7 +3491,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="26"/>
+    <n v="29"/>
     <s v="PEG26_UNKNOWN"/>
     <n v="-7.5"/>
     <n v="-1.5"/>
@@ -3132,31 +3505,17 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="29"/>
-    <s v="LEG2_LOGAN"/>
-    <n v="-2.6000000000000014"/>
-    <n v="-0.52000000000000035"/>
-    <n v="5"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="80"/>
-    <n v="-0.52000000000000024"/>
-    <n v="-0.10400000000000006"/>
-    <x v="2"/>
-  </r>
-  <r>
     <n v="27"/>
     <s v="SEG1_LITE"/>
-    <n v="18.399999999999999"/>
-    <n v="3.6799999999999997"/>
-    <n v="4"/>
-    <n v="4"/>
+    <n v="26.099999999999998"/>
+    <n v="5.22"/>
+    <n v="5"/>
+    <n v="5"/>
     <n v="0"/>
     <n v="0"/>
     <n v="100"/>
-    <n v="4.5999999999999996"/>
-    <n v="0.91999999999999993"/>
+    <n v="5.22"/>
+    <n v="1.044"/>
     <x v="5"/>
   </r>
   <r>
@@ -3217,6 +3576,20 @@
   </r>
   <r>
     <n v="38"/>
+    <s v="LEG2_DRG"/>
+    <n v="-12.2"/>
+    <n v="-2.44"/>
+    <n v="4"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="25"/>
+    <n v="-3.05"/>
+    <n v="-0.61"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="39"/>
     <s v="LEG1_LAKSAe"/>
     <n v="6"/>
     <n v="1.2"/>
@@ -3230,21 +3603,35 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="39"/>
-    <s v="LEG2_DRG"/>
-    <n v="-12"/>
-    <n v="-2.4"/>
+    <n v="30"/>
+    <s v="UEG8_SOLDIER"/>
+    <n v="-1.7000000000000002"/>
+    <n v="-0.34"/>
     <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
     <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="33.333333333333329"/>
-    <n v="-4"/>
-    <n v="-0.79999999999999993"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="30"/>
+    <n v="66.666666666666657"/>
+    <n v="-0.56666666666666676"/>
+    <n v="-0.11333333333333334"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <s v="UEG9_GRAVY2"/>
+    <n v="-13.799999999999999"/>
+    <n v="-2.76"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="-4.5999999999999996"/>
+    <n v="-0.91999999999999993"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="32"/>
     <s v="UEG7_ADVENTURE"/>
     <n v="1.0000000000000002"/>
     <n v="0.2"/>
@@ -3258,7 +3645,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="31"/>
+    <n v="33"/>
     <s v="PEG13_DWDDCr"/>
     <n v="1"/>
     <n v="0.2"/>
@@ -3272,7 +3659,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="32"/>
+    <n v="34"/>
     <s v="LEG2_HOTS"/>
     <n v="-1.8"/>
     <n v="-0.36"/>
@@ -3286,7 +3673,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="33"/>
+    <n v="40"/>
     <s v="PEG14_RANGER"/>
     <n v="-1.9000000000000001"/>
     <n v="-0.38"/>
@@ -3300,7 +3687,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="34"/>
+    <n v="41"/>
     <s v="UEG4_FALCON"/>
     <n v="-12"/>
     <n v="-2.4"/>
@@ -3314,7 +3701,35 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="40"/>
+    <n v="42"/>
+    <s v="UEG7_CELEBRITY"/>
+    <n v="-5.2"/>
+    <n v="-1.04"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="-2.6"/>
+    <n v="-0.52"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="43"/>
+    <s v="VEG1_MOON"/>
+    <n v="-14.8"/>
+    <n v="-2.96"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="-7.4"/>
+    <n v="-1.48"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="44"/>
     <s v="PEG18_ANDUIN"/>
     <n v="-1.3"/>
     <n v="-0.26"/>
@@ -3328,7 +3743,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="41"/>
+    <n v="45"/>
     <s v="LEG1_PHOGA"/>
     <n v="-6"/>
     <n v="-1.2"/>
@@ -3342,7 +3757,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="42"/>
+    <n v="46"/>
     <s v="LEG1_OKROSHKA"/>
     <n v="-1.6"/>
     <n v="-0.32"/>
@@ -3356,7 +3771,91 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="43"/>
+    <n v="47"/>
+    <s v="WEG7_PARADOX"/>
+    <n v="4.3"/>
+    <n v="0.86"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="4.3"/>
+    <n v="0.86"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="48"/>
+    <s v="UEG7_CARRIER"/>
+    <n v="-1.3"/>
+    <n v="-0.26"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="-1.3"/>
+    <n v="-0.26"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="49"/>
+    <s v="UEG4_PELICAN2"/>
+    <n v="-11.4"/>
+    <n v="-2.2800000000000002"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="-11.4"/>
+    <n v="-2.2800000000000002"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="50"/>
+    <s v="UEG7_CANNIBAL"/>
+    <n v="-4"/>
+    <n v="-0.8"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="-4"/>
+    <n v="-0.8"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="51"/>
+    <s v="UEG7_LOVERGOOSE"/>
+    <n v="0.5"/>
+    <n v="0.1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="0.5"/>
+    <n v="0.1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="52"/>
+    <s v="UEG9_BIRDWATCHER2"/>
+    <n v="-19.5"/>
+    <n v="-3.9"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="-19.5"/>
+    <n v="-3.9"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="53"/>
     <s v="LEG1_BORSCH"/>
     <n v="0"/>
     <n v="0"/>
@@ -3370,7 +3869,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="44"/>
+    <n v="54"/>
     <s v="LEG1_PHOBO"/>
     <n v="0"/>
     <n v="0"/>
@@ -3384,7 +3883,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="45"/>
+    <n v="55"/>
     <s v="LEG2_MONSTER"/>
     <n v="0"/>
     <n v="0"/>
@@ -3398,7 +3897,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="46"/>
+    <n v="56"/>
     <s v="PEG14_RWDDCr"/>
     <n v="0"/>
     <n v="0"/>
@@ -3412,7 +3911,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="47"/>
+    <n v="57"/>
     <s v="PEG15_ANNA"/>
     <n v="0"/>
     <n v="0"/>
@@ -3426,7 +3925,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="48"/>
+    <n v="58"/>
     <s v="PEG15_SILVANA"/>
     <n v="0"/>
     <n v="0"/>
@@ -3440,7 +3939,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="49"/>
+    <n v="59"/>
     <s v="PEG18_REXXAR2"/>
     <n v="0"/>
     <n v="0"/>
@@ -3454,7 +3953,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="50"/>
+    <n v="60"/>
     <s v="PEG18_VARIAN2"/>
     <n v="0"/>
     <n v="0"/>
@@ -3468,7 +3967,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="51"/>
+    <n v="61"/>
     <s v="PEG2_SDDCr"/>
     <n v="0"/>
     <n v="0"/>
@@ -3482,7 +3981,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="52"/>
+    <n v="62"/>
     <s v="PEG20_HOGGER"/>
     <n v="0"/>
     <n v="0"/>
@@ -3496,7 +3995,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="53"/>
+    <n v="63"/>
     <s v="PEG8_DOBBY"/>
     <n v="0"/>
     <n v="0"/>
@@ -3510,7 +4009,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="54"/>
+    <n v="64"/>
     <s v="PEG8_LOBSTER"/>
     <n v="0"/>
     <n v="0"/>
@@ -3524,7 +4023,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="55"/>
+    <m/>
     <s v="UEG4_CANADIAN"/>
     <n v="0"/>
     <n v="0"/>
@@ -3538,7 +4037,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="56"/>
+    <m/>
     <s v="UEG6_DODO"/>
     <n v="0"/>
     <n v="0"/>
@@ -3552,7 +4051,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="57"/>
+    <m/>
     <s v="UEG6_DUELDODO"/>
     <n v="0"/>
     <n v="0"/>
@@ -3566,7 +4065,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="58"/>
+    <m/>
     <s v="UEG7_DODO"/>
     <n v="0"/>
     <n v="0"/>
@@ -3580,7 +4079,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="59"/>
+    <m/>
     <s v="UEG7_DUELDODO"/>
     <n v="0"/>
     <n v="0"/>
@@ -3594,7 +4093,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="60"/>
+    <m/>
     <s v="UEG7_SHERIFF"/>
     <n v="0"/>
     <n v="0"/>
@@ -3608,7 +4107,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="61"/>
+    <m/>
     <s v="UEG7_VULTURE"/>
     <n v="0"/>
     <n v="0"/>
@@ -3622,7 +4121,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="62"/>
+    <m/>
     <s v="UEG8_AVENGER"/>
     <n v="0"/>
     <n v="0"/>
@@ -3636,7 +4135,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="63"/>
+    <m/>
     <s v="WEG4_DOG"/>
     <n v="0"/>
     <n v="0"/>
@@ -3650,24 +4149,52 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="64"/>
-    <s v="WEG7_PARADOX"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="6"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="6"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="6"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C4CB1275-447E-4587-B9C3-BDD7EB80BE41}" name="Сводная таблица2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{08A3FD17-FFE6-464D-A72F-02ADC3CE221B}" name="Сводная таблица3" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A12:G19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -3678,17 +4205,18 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="7">
+      <items count="8">
         <item x="2"/>
         <item x="0"/>
         <item x="5"/>
         <item x="4"/>
         <item x="3"/>
         <item x="1"/>
+        <item h="1" x="6"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3763,7 +4291,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5C6C209-71EC-45CD-876E-D40B4E36B838}" name="Сводная таблица1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E5C6C209-71EC-45CD-876E-D40B4E36B838}" name="Сводная таблица1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:G10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -4554,7 +5082,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
-        <v>46288</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4585,22 +5113,22 @@
         <v>136</v>
       </c>
       <c r="B13" s="12">
-        <v>-0.90000000000001545</v>
+        <v>41.999999999999993</v>
       </c>
       <c r="C13" s="12">
-        <v>-0.17999999999999994</v>
+        <v>8.4000000000000021</v>
       </c>
       <c r="D13" s="12">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="E13" s="12">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="F13" s="12">
         <v>1</v>
       </c>
       <c r="G13" s="12">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -4608,22 +5136,22 @@
         <v>137</v>
       </c>
       <c r="B14" s="12">
-        <v>83</v>
+        <v>85.699999999999989</v>
       </c>
       <c r="C14" s="12">
-        <v>16.600000000000005</v>
+        <v>17.14</v>
       </c>
       <c r="D14" s="12">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="E14" s="12">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F14" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="12">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -4631,16 +5159,16 @@
         <v>138</v>
       </c>
       <c r="B15" s="12">
-        <v>18.100000000000001</v>
+        <v>28</v>
       </c>
       <c r="C15" s="12">
-        <v>3.6199999999999997</v>
+        <v>5.6</v>
       </c>
       <c r="D15" s="12">
+        <v>10</v>
+      </c>
+      <c r="E15" s="12">
         <v>8</v>
-      </c>
-      <c r="E15" s="12">
-        <v>6</v>
       </c>
       <c r="F15" s="12">
         <v>0</v>
@@ -4654,22 +5182,22 @@
         <v>139</v>
       </c>
       <c r="B16" s="12">
-        <v>-1.8999999999999986</v>
+        <v>-51.5</v>
       </c>
       <c r="C16" s="12">
-        <v>-0.38000000000000034</v>
+        <v>-10.3</v>
       </c>
       <c r="D16" s="12">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E16" s="12">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F16" s="12">
         <v>2</v>
       </c>
       <c r="G16" s="12">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -4677,13 +5205,13 @@
         <v>140</v>
       </c>
       <c r="B17" s="12">
-        <v>-22.700000000000003</v>
+        <v>-37.5</v>
       </c>
       <c r="C17" s="12">
-        <v>-4.5399999999999991</v>
+        <v>-7.4999999999999991</v>
       </c>
       <c r="D17" s="12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E17" s="12">
         <v>9</v>
@@ -4692,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="12">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4700,22 +5228,22 @@
         <v>141</v>
       </c>
       <c r="B18" s="12">
-        <v>59.400000000000006</v>
+        <v>77.3</v>
       </c>
       <c r="C18" s="12">
-        <v>11.88</v>
+        <v>15.46</v>
       </c>
       <c r="D18" s="12">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E18" s="12">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F18" s="12">
         <v>1</v>
       </c>
       <c r="G18" s="12">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -4723,22 +5251,22 @@
         <v>134</v>
       </c>
       <c r="B19" s="12">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C19" s="12">
-        <v>27.000000000000007</v>
+        <v>28.8</v>
       </c>
       <c r="D19" s="12">
-        <v>376</v>
+        <v>449</v>
       </c>
       <c r="E19" s="12">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="F19" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G19" s="12">
-        <v>169</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -4769,6 +5297,9 @@
       </c>
       <c r="F2" s="16">
         <v>46290</v>
+      </c>
+      <c r="G2" s="16">
+        <v>46293</v>
       </c>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
@@ -4807,6 +5338,9 @@
       <c r="F3">
         <v>28.400000000000013</v>
       </c>
+      <c r="G3">
+        <v>41.999999999999993</v>
+      </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -4827,6 +5361,9 @@
       <c r="F4">
         <v>83.199999999999989</v>
       </c>
+      <c r="G4">
+        <v>85.699999999999989</v>
+      </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -4847,6 +5384,9 @@
       <c r="F5">
         <v>20.299999999999997</v>
       </c>
+      <c r="G5">
+        <v>28</v>
+      </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -4867,6 +5407,9 @@
       <c r="F6">
         <v>-15.199999999999998</v>
       </c>
+      <c r="G6">
+        <v>-51.5</v>
+      </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -4887,6 +5430,9 @@
       <c r="F7">
         <v>-22.700000000000003</v>
       </c>
+      <c r="G7">
+        <v>-37.5</v>
+      </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -4906,6 +5452,9 @@
       </c>
       <c r="F8">
         <v>62.400000000000006</v>
+      </c>
+      <c r="G8">
+        <v>77.3</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -4914,7 +5463,7 @@
         <v>46285</v>
       </c>
       <c r="C10" s="16">
-        <f t="shared" ref="C10:E10" si="0">C2</f>
+        <f t="shared" ref="C10:G10" si="0">C2</f>
         <v>46286</v>
       </c>
       <c r="D10" s="16">
@@ -4926,7 +5475,12 @@
         <v>46288</v>
       </c>
       <c r="F10" s="16">
+        <f t="shared" si="0"/>
         <v>46290</v>
+      </c>
+      <c r="G10" s="16">
+        <f t="shared" si="0"/>
+        <v>46293</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -4942,7 +5496,7 @@
         <v>-19.799999999999997</v>
       </c>
       <c r="D11">
-        <f t="shared" ref="D11:F11" si="1">D3-C3</f>
+        <f t="shared" ref="D11:G11" si="1">D3-C3</f>
         <v>17.799999999999997</v>
       </c>
       <c r="E11">
@@ -4953,6 +5507,10 @@
         <f t="shared" si="1"/>
         <v>29.300000000000011</v>
       </c>
+      <c r="G11">
+        <f t="shared" si="1"/>
+        <v>13.59999999999998</v>
+      </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -4963,7 +5521,7 @@
         <v>19.7</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C12:F16" si="3">C4-B4</f>
+        <f t="shared" ref="C12:G16" si="3">C4-B4</f>
         <v>31.000000000000004</v>
       </c>
       <c r="D12">
@@ -4978,6 +5536,10 @@
         <f t="shared" si="3"/>
         <v>0.19999999999998863</v>
       </c>
+      <c r="G12">
+        <f t="shared" si="3"/>
+        <v>2.5</v>
+      </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -5003,6 +5565,10 @@
         <f t="shared" si="3"/>
         <v>2.1999999999999957</v>
       </c>
+      <c r="G13">
+        <f t="shared" si="3"/>
+        <v>7.7000000000000028</v>
+      </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -5028,6 +5594,10 @@
         <f t="shared" si="3"/>
         <v>-13.299999999999997</v>
       </c>
+      <c r="G14">
+        <f t="shared" si="3"/>
+        <v>-36.300000000000004</v>
+      </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -5053,6 +5623,10 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="G15">
+        <f t="shared" si="3"/>
+        <v>-14.799999999999997</v>
+      </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -5077,6 +5651,10 @@
       <c r="F16">
         <f t="shared" si="3"/>
         <v>3.0000000000000071</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="3"/>
+        <v>14.899999999999991</v>
       </c>
     </row>
   </sheetData>
@@ -5182,16 +5760,16 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>119.69999999999999</v>
+        <v>130.29999999999998</v>
       </c>
       <c r="D2">
-        <v>23.940000000000005</v>
+        <v>26.060000000000006</v>
       </c>
       <c r="E2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -5201,15 +5779,15 @@
       </c>
       <c r="I2" s="7">
         <f>IFERROR((F2/E2)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>68.518518518518519</v>
       </c>
       <c r="J2" s="10">
         <f>IFERROR(C2/E2,0)</f>
-        <v>2.3470588235294114</v>
+        <v>2.4129629629629625</v>
       </c>
       <c r="K2" s="10">
         <f>IFERROR(D2/E2,0)</f>
-        <v>0.46941176470588247</v>
+        <v>0.48259259259259268</v>
       </c>
       <c r="L2" s="10" t="str">
         <f>LEFT(B2,3)</f>
@@ -5217,19 +5795,19 @@
       </c>
       <c r="N2">
         <f t="shared" ref="N2:S2" si="0">C2+U2</f>
-        <v>119.69999999999999</v>
+        <v>130.29999999999998</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>23.940000000000005</v>
+        <v>26.060000000000006</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
@@ -5245,65 +5823,65 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C3">
-        <v>30.099999999999998</v>
+        <v>55.500000000000007</v>
       </c>
       <c r="D3">
-        <v>6.0200000000000005</v>
+        <v>11.100000000000001</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I3" s="7">
         <f>IFERROR((F3/E3)*100,0)</f>
-        <v>50</v>
+        <v>60.526315789473685</v>
       </c>
       <c r="J3" s="10">
         <f>IFERROR(C3/E3,0)</f>
-        <v>0.83611111111111103</v>
+        <v>1.4605263157894739</v>
       </c>
       <c r="K3" s="10">
         <f>IFERROR(D3/E3,0)</f>
-        <v>0.16722222222222224</v>
+        <v>0.29210526315789476</v>
       </c>
       <c r="L3" s="10" t="str">
         <f>LEFT(B3,3)</f>
-        <v>PEG</v>
+        <v>WEG</v>
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N64" si="1">C3+U3</f>
-        <v>30.099999999999998</v>
+        <v>55.500000000000007</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O17" si="2">D3+V3</f>
-        <v>6.0200000000000005</v>
+        <v>11.100000000000001</v>
       </c>
       <c r="P3">
         <f t="shared" ref="P3:P17" si="3">E3+W3</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q17" si="4">F3+X3</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R17" si="5">G3+Y3</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S17" si="6">H3+Z3</f>
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -5311,65 +5889,65 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C4">
-        <v>44.900000000000006</v>
+        <v>30.099999999999998</v>
       </c>
       <c r="D4">
-        <v>8.98</v>
+        <v>6.0200000000000005</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I4" s="7">
         <f>IFERROR((F4/E4)*100,0)</f>
-        <v>61.764705882352942</v>
+        <v>50</v>
       </c>
       <c r="J4" s="10">
         <f>IFERROR(C4/E4,0)</f>
-        <v>1.3205882352941178</v>
+        <v>0.83611111111111103</v>
       </c>
       <c r="K4" s="10">
         <f>IFERROR(D4/E4,0)</f>
-        <v>0.26411764705882357</v>
+        <v>0.16722222222222224</v>
       </c>
       <c r="L4" s="10" t="str">
         <f>LEFT(B4,3)</f>
-        <v>WEG</v>
+        <v>PEG</v>
       </c>
       <c r="N4">
         <f t="shared" si="1"/>
-        <v>44.900000000000006</v>
+        <v>30.099999999999998</v>
       </c>
       <c r="O4">
         <f t="shared" si="2"/>
-        <v>8.98</v>
+        <v>6.0200000000000005</v>
       </c>
       <c r="P4">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q4">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -5446,13 +6024,13 @@
         <v>55</v>
       </c>
       <c r="C6">
-        <v>13.3</v>
+        <v>9.6000000000000014</v>
       </c>
       <c r="D6">
-        <v>2.660000000000001</v>
+        <v>1.920000000000001</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <v>11</v>
@@ -5461,19 +6039,19 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="7">
         <f>IFERROR((F6/E6)*100,0)</f>
-        <v>52.380952380952387</v>
+        <v>50</v>
       </c>
       <c r="J6" s="10">
         <f>IFERROR(C6/E6,0)</f>
-        <v>0.63333333333333341</v>
+        <v>0.43636363636363645</v>
       </c>
       <c r="K6" s="10">
         <f>IFERROR(D6/E6,0)</f>
-        <v>0.12666666666666671</v>
+        <v>8.7272727272727321E-2</v>
       </c>
       <c r="L6" s="10" t="str">
         <f>LEFT(B6,3)</f>
@@ -5481,15 +6059,15 @@
       </c>
       <c r="N6">
         <f t="shared" si="1"/>
-        <v>13.3</v>
+        <v>9.6000000000000014</v>
       </c>
       <c r="O6">
         <f t="shared" si="2"/>
-        <v>2.660000000000001</v>
+        <v>1.920000000000001</v>
       </c>
       <c r="P6">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q6">
         <f t="shared" si="4"/>
@@ -5501,7 +6079,7 @@
       </c>
       <c r="S6">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -5509,65 +6087,65 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C7">
-        <v>-22.700000000000003</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="D7">
-        <v>-4.5399999999999991</v>
+        <v>0.68000000000000083</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I7" s="7">
         <f>IFERROR((F7/E7)*100,0)</f>
-        <v>47.368421052631575</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J7" s="10">
         <f>IFERROR(C7/E7,0)</f>
-        <v>-1.1947368421052633</v>
+        <v>0.17</v>
       </c>
       <c r="K7" s="10">
         <f>IFERROR(D7/E7,0)</f>
-        <v>-0.23894736842105258</v>
+        <v>3.4000000000000044E-2</v>
       </c>
       <c r="L7" s="10" t="str">
         <f>LEFT(B7,3)</f>
-        <v>VEG</v>
+        <v>PEG</v>
       </c>
       <c r="N7">
         <f t="shared" si="1"/>
-        <v>-22.700000000000003</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="O7">
         <f t="shared" si="2"/>
-        <v>-4.5399999999999991</v>
+        <v>0.68000000000000083</v>
       </c>
       <c r="P7">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q7">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -5575,65 +6153,65 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C8">
-        <v>14.5</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="D8">
-        <v>2.9000000000000004</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I8" s="7">
         <f>IFERROR((F8/E8)*100,0)</f>
-        <v>44.444444444444443</v>
+        <v>47.368421052631575</v>
       </c>
       <c r="J8" s="10">
         <f>IFERROR(C8/E8,0)</f>
-        <v>0.80555555555555558</v>
+        <v>-1.1947368421052633</v>
       </c>
       <c r="K8" s="10">
         <f>IFERROR(D8/E8,0)</f>
-        <v>0.16111111111111112</v>
+        <v>-0.23894736842105258</v>
       </c>
       <c r="L8" s="10" t="str">
         <f>LEFT(B8,3)</f>
-        <v>LEG</v>
+        <v>VEG</v>
       </c>
       <c r="N8">
         <f t="shared" si="1"/>
-        <v>14.5</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="O8">
         <f t="shared" si="2"/>
-        <v>2.9000000000000004</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="P8">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -5641,57 +6219,57 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C9">
-        <v>11.5</v>
+        <v>16.3</v>
       </c>
       <c r="D9">
-        <v>2.3000000000000007</v>
+        <v>3.2600000000000002</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7">
         <f>IFERROR((F9/E9)*100,0)</f>
-        <v>58.82352941176471</v>
+        <v>47.368421052631575</v>
       </c>
       <c r="J9" s="10">
         <f>IFERROR(C9/E9,0)</f>
-        <v>0.67647058823529416</v>
+        <v>0.85789473684210527</v>
       </c>
       <c r="K9" s="10">
         <f>IFERROR(D9/E9,0)</f>
-        <v>0.13529411764705887</v>
+        <v>0.17157894736842105</v>
       </c>
       <c r="L9" s="10" t="str">
         <f>LEFT(B9,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N9">
         <f t="shared" si="1"/>
-        <v>11.5</v>
+        <v>16.3</v>
       </c>
       <c r="O9">
         <f t="shared" si="2"/>
-        <v>2.3000000000000007</v>
+        <v>3.2600000000000002</v>
       </c>
       <c r="P9">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q9">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <f t="shared" si="5"/>
@@ -5699,7 +6277,7 @@
       </c>
       <c r="S9">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -5710,34 +6288,34 @@
         <v>60</v>
       </c>
       <c r="C10">
-        <v>27.9</v>
+        <v>32.099999999999994</v>
       </c>
       <c r="D10">
-        <v>5.58</v>
+        <v>6.42</v>
       </c>
       <c r="E10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="7">
         <f>IFERROR((F10/E10)*100,0)</f>
-        <v>75</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="J10" s="10">
         <f>IFERROR(C10/E10,0)</f>
-        <v>1.7437499999999999</v>
+        <v>1.689473684210526</v>
       </c>
       <c r="K10" s="10">
         <f>IFERROR(D10/E10,0)</f>
-        <v>0.34875</v>
+        <v>0.33789473684210525</v>
       </c>
       <c r="L10" s="10" t="str">
         <f>LEFT(B10,3)</f>
@@ -5745,19 +6323,19 @@
       </c>
       <c r="N10">
         <f t="shared" si="1"/>
-        <v>27.9</v>
+        <v>32.099999999999994</v>
       </c>
       <c r="O10">
         <f t="shared" si="2"/>
-        <v>5.58</v>
+        <v>6.42</v>
       </c>
       <c r="P10">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q10">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R10">
         <f t="shared" si="5"/>
@@ -5765,7 +6343,7 @@
       </c>
       <c r="S10">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -5773,65 +6351,65 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C11">
-        <v>-40.799999999999997</v>
+        <v>22.6</v>
       </c>
       <c r="D11">
-        <v>-8.16</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7">
         <f>IFERROR((F11/E11)*100,0)</f>
-        <v>40</v>
+        <v>47.058823529411761</v>
       </c>
       <c r="J11" s="10">
         <f>IFERROR(C11/E11,0)</f>
-        <v>-2.7199999999999998</v>
+        <v>1.3294117647058825</v>
       </c>
       <c r="K11" s="10">
         <f>IFERROR(D11/E11,0)</f>
-        <v>-0.54400000000000004</v>
+        <v>0.26588235294117646</v>
       </c>
       <c r="L11" s="10" t="str">
         <f>LEFT(B11,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N11">
         <f t="shared" si="1"/>
-        <v>-40.799999999999997</v>
+        <v>22.6</v>
       </c>
       <c r="O11">
         <f t="shared" si="2"/>
-        <v>-8.16</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="P11">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q11">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S11">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -5839,13 +6417,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="C12">
-        <v>2.4999999999999982</v>
+        <v>-40.799999999999997</v>
       </c>
       <c r="D12">
-        <v>0.49999999999999956</v>
+        <v>-8.16</v>
       </c>
       <c r="E12">
         <v>15</v>
@@ -5854,10 +6432,10 @@
         <v>6</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I12" s="7">
         <f>IFERROR((F12/E12)*100,0)</f>
@@ -5865,23 +6443,23 @@
       </c>
       <c r="J12" s="10">
         <f>IFERROR(C12/E12,0)</f>
-        <v>0.16666666666666655</v>
+        <v>-2.7199999999999998</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(D12/E12,0)</f>
-        <v>3.3333333333333305E-2</v>
+        <v>-0.54400000000000004</v>
       </c>
       <c r="L12" s="10" t="str">
         <f>LEFT(B12,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N12">
         <f t="shared" si="1"/>
-        <v>2.4999999999999982</v>
+        <v>-40.799999999999997</v>
       </c>
       <c r="O12">
         <f t="shared" si="2"/>
-        <v>0.49999999999999956</v>
+        <v>-8.16</v>
       </c>
       <c r="P12">
         <f t="shared" si="3"/>
@@ -5893,11 +6471,11 @@
       </c>
       <c r="R12">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S12">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -6040,16 +6618,16 @@
         <v>116</v>
       </c>
       <c r="C15">
-        <v>-8.7000000000000011</v>
+        <v>1.0999999999999996</v>
       </c>
       <c r="D15">
-        <v>-1.7399999999999991</v>
+        <v>0.22000000000000108</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -6059,15 +6637,15 @@
       </c>
       <c r="I15" s="7">
         <f>IFERROR((F15/E15)*100,0)</f>
-        <v>44.444444444444443</v>
+        <v>50</v>
       </c>
       <c r="J15" s="10">
         <f>IFERROR(C15/E15,0)</f>
-        <v>-0.96666666666666679</v>
+        <v>0.10999999999999996</v>
       </c>
       <c r="K15" s="10">
         <f>IFERROR(D15/E15,0)</f>
-        <v>-0.19333333333333325</v>
+        <v>2.200000000000011E-2</v>
       </c>
       <c r="L15" s="10" t="str">
         <f>LEFT(B15,3)</f>
@@ -6075,19 +6653,19 @@
       </c>
       <c r="N15">
         <f t="shared" si="1"/>
-        <v>-8.7000000000000011</v>
+        <v>1.0999999999999996</v>
       </c>
       <c r="O15">
         <f t="shared" si="2"/>
-        <v>-1.7399999999999991</v>
+        <v>0.22000000000000108</v>
       </c>
       <c r="P15">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R15">
         <f t="shared" si="5"/>
@@ -6433,57 +7011,57 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C21">
-        <v>1.9000000000000004</v>
+        <v>-0.90000000000000147</v>
       </c>
       <c r="D21">
-        <v>0.37999999999999989</v>
+        <v>-0.18000000000000038</v>
       </c>
       <c r="E21">
+        <v>6</v>
+      </c>
+      <c r="F21">
         <v>5</v>
       </c>
-      <c r="F21">
-        <v>3</v>
-      </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="7">
         <f>IFERROR((F21/E21)*100,0)</f>
-        <v>60</v>
+        <v>83.333333333333343</v>
       </c>
       <c r="J21" s="10">
         <f>IFERROR(C21/E21,0)</f>
-        <v>0.38000000000000006</v>
+        <v>-0.15000000000000024</v>
       </c>
       <c r="K21" s="10">
         <f>IFERROR(D21/E21,0)</f>
-        <v>7.5999999999999984E-2</v>
+        <v>-3.0000000000000065E-2</v>
       </c>
       <c r="L21" s="10" t="str">
         <f>LEFT(B21,3)</f>
-        <v>SEG</v>
+        <v>LEG</v>
       </c>
       <c r="N21">
         <f t="shared" si="1"/>
-        <v>1.9000000000000004</v>
+        <v>-0.90000000000000147</v>
       </c>
       <c r="O21">
         <f t="shared" si="7"/>
-        <v>0.37999999999999989</v>
+        <v>-0.18000000000000038</v>
       </c>
       <c r="P21">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <f t="shared" si="10"/>
@@ -6491,7 +7069,7 @@
       </c>
       <c r="S21">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -6499,13 +7077,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C22">
-        <v>-2.9000000000000004</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="D22">
-        <v>-0.58000000000000007</v>
+        <v>0.37999999999999989</v>
       </c>
       <c r="E22">
         <v>5</v>
@@ -6525,23 +7103,23 @@
       </c>
       <c r="J22" s="10">
         <f>IFERROR(C22/E22,0)</f>
-        <v>-0.58000000000000007</v>
+        <v>0.38000000000000006</v>
       </c>
       <c r="K22" s="10">
         <f>IFERROR(D22/E22,0)</f>
-        <v>-0.11600000000000002</v>
+        <v>7.5999999999999984E-2</v>
       </c>
       <c r="L22" s="10" t="str">
         <f>LEFT(B22,3)</f>
-        <v>UEG</v>
+        <v>SEG</v>
       </c>
       <c r="N22">
         <f t="shared" si="1"/>
-        <v>-2.9000000000000004</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="O22">
         <f t="shared" si="7"/>
-        <v>-0.58000000000000007</v>
+        <v>0.37999999999999989</v>
       </c>
       <c r="P22">
         <f t="shared" si="8"/>
@@ -6565,49 +7143,49 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="C23">
-        <v>-3.8000000000000007</v>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="D23">
-        <v>-0.76000000000000023</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="E23">
         <v>5</v>
       </c>
       <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>2</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>3</v>
       </c>
       <c r="I23" s="7">
         <f>IFERROR((F23/E23)*100,0)</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J23" s="10">
         <f>IFERROR(C23/E23,0)</f>
-        <v>-0.76000000000000012</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="K23" s="10">
         <f>IFERROR(D23/E23,0)</f>
-        <v>-0.15200000000000005</v>
+        <v>-0.11600000000000002</v>
       </c>
       <c r="L23" s="10" t="str">
         <f>LEFT(B23,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N23">
         <f t="shared" si="1"/>
-        <v>-3.8000000000000007</v>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="O23">
         <f t="shared" si="7"/>
-        <v>-0.76000000000000023</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="P23">
         <f t="shared" si="8"/>
@@ -6615,7 +7193,7 @@
       </c>
       <c r="Q23">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R23">
         <f t="shared" si="10"/>
@@ -6623,7 +7201,7 @@
       </c>
       <c r="S23">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -6631,37 +7209,37 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C24">
-        <v>-6.2</v>
+        <v>-3.8000000000000007</v>
       </c>
       <c r="D24">
-        <v>-1.24</v>
+        <v>-0.76000000000000023</v>
       </c>
       <c r="E24">
         <v>5</v>
       </c>
       <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
         <v>3</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
       </c>
       <c r="I24" s="7">
         <f>IFERROR((F24/E24)*100,0)</f>
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J24" s="10">
         <f>IFERROR(C24/E24,0)</f>
-        <v>-1.24</v>
+        <v>-0.76000000000000012</v>
       </c>
       <c r="K24" s="10">
         <f>IFERROR(D24/E24,0)</f>
-        <v>-0.248</v>
+        <v>-0.15200000000000005</v>
       </c>
       <c r="L24" s="10" t="str">
         <f>LEFT(B24,3)</f>
@@ -6669,11 +7247,11 @@
       </c>
       <c r="N24">
         <f t="shared" si="1"/>
-        <v>-6.2</v>
+        <v>-3.8000000000000007</v>
       </c>
       <c r="O24">
         <f t="shared" si="7"/>
-        <v>-1.24</v>
+        <v>-0.76000000000000023</v>
       </c>
       <c r="P24">
         <f t="shared" si="8"/>
@@ -6681,15 +7259,15 @@
       </c>
       <c r="Q24">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R24">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -6697,49 +7275,49 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C25">
-        <v>-7.5</v>
+        <v>-6.2</v>
       </c>
       <c r="D25">
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="E25">
         <v>5</v>
       </c>
       <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
         <v>1</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
       <c r="H25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I25" s="7">
         <f>IFERROR((F25/E25)*100,0)</f>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J25" s="10">
         <f>IFERROR(C25/E25,0)</f>
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="K25" s="10">
         <f>IFERROR(D25/E25,0)</f>
-        <v>-0.3</v>
+        <v>-0.248</v>
       </c>
       <c r="L25" s="10" t="str">
         <f>LEFT(B25,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N25">
         <f t="shared" si="1"/>
-        <v>-7.5</v>
+        <v>-6.2</v>
       </c>
       <c r="O25">
         <f t="shared" si="7"/>
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="P25">
         <f t="shared" si="8"/>
@@ -6747,15 +7325,15 @@
       </c>
       <c r="Q25">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R25">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
@@ -6763,13 +7341,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C26">
-        <v>-9.1</v>
+        <v>-7.5</v>
       </c>
       <c r="D26">
-        <v>-1.82</v>
+        <v>-1.5</v>
       </c>
       <c r="E26">
         <v>5</v>
@@ -6789,23 +7367,23 @@
       </c>
       <c r="J26" s="10">
         <f>IFERROR(C26/E26,0)</f>
-        <v>-1.8199999999999998</v>
+        <v>-1.5</v>
       </c>
       <c r="K26" s="10">
         <f>IFERROR(D26/E26,0)</f>
-        <v>-0.36399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="L26" s="10" t="str">
         <f>LEFT(B26,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N26">
         <f t="shared" si="1"/>
-        <v>-9.1</v>
+        <v>-7.5</v>
       </c>
       <c r="O26">
         <f t="shared" si="7"/>
-        <v>-1.82</v>
+        <v>-1.5</v>
       </c>
       <c r="P26">
         <f t="shared" si="8"/>
@@ -6829,37 +7407,37 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C27">
-        <v>-7.5</v>
+        <v>-9.1</v>
       </c>
       <c r="D27">
-        <v>-1.5</v>
+        <v>-1.82</v>
       </c>
       <c r="E27">
         <v>5</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="7">
         <f>IFERROR((F27/E27)*100,0)</f>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J27" s="10">
         <f>IFERROR(C27/E27,0)</f>
-        <v>-1.5</v>
+        <v>-1.8199999999999998</v>
       </c>
       <c r="K27" s="10">
         <f>IFERROR(D27/E27,0)</f>
-        <v>-0.3</v>
+        <v>-0.36399999999999999</v>
       </c>
       <c r="L27" s="10" t="str">
         <f>LEFT(B27,3)</f>
@@ -6867,11 +7445,11 @@
       </c>
       <c r="N27">
         <f t="shared" si="1"/>
-        <v>-7.5</v>
+        <v>-9.1</v>
       </c>
       <c r="O27">
         <f t="shared" si="7"/>
-        <v>-1.5</v>
+        <v>-1.82</v>
       </c>
       <c r="P27">
         <f t="shared" si="8"/>
@@ -6879,7 +7457,7 @@
       </c>
       <c r="Q27">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27">
         <f t="shared" si="10"/>
@@ -6887,7 +7465,7 @@
       </c>
       <c r="S27">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -6895,49 +7473,49 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C28">
-        <v>-2.6000000000000014</v>
+        <v>-7.5</v>
       </c>
       <c r="D28">
-        <v>-0.52000000000000035</v>
+        <v>-1.5</v>
       </c>
       <c r="E28">
         <v>5</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28" s="7">
         <f>IFERROR((F28/E28)*100,0)</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J28" s="10">
         <f>IFERROR(C28/E28,0)</f>
-        <v>-0.52000000000000024</v>
+        <v>-1.5</v>
       </c>
       <c r="K28" s="10">
         <f>IFERROR(D28/E28,0)</f>
-        <v>-0.10400000000000006</v>
+        <v>-0.3</v>
       </c>
       <c r="L28" s="10" t="str">
         <f>LEFT(B28,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N28">
         <f t="shared" si="1"/>
-        <v>-2.6000000000000014</v>
+        <v>-7.5</v>
       </c>
       <c r="O28">
         <f t="shared" si="7"/>
-        <v>-0.52000000000000035</v>
+        <v>-1.5</v>
       </c>
       <c r="P28">
         <f t="shared" si="8"/>
@@ -6945,7 +7523,7 @@
       </c>
       <c r="Q28">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R28">
         <f t="shared" si="10"/>
@@ -6953,7 +7531,7 @@
       </c>
       <c r="S28">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -6964,16 +7542,16 @@
         <v>109</v>
       </c>
       <c r="C29">
-        <v>18.399999999999999</v>
+        <v>26.099999999999998</v>
       </c>
       <c r="D29">
-        <v>3.6799999999999997</v>
+        <v>5.22</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6987,11 +7565,11 @@
       </c>
       <c r="J29" s="10">
         <f>IFERROR(C29/E29,0)</f>
-        <v>4.5999999999999996</v>
+        <v>5.22</v>
       </c>
       <c r="K29" s="10">
         <f>IFERROR(D29/E29,0)</f>
-        <v>0.91999999999999993</v>
+        <v>1.044</v>
       </c>
       <c r="L29" s="10" t="str">
         <f>LEFT(B29,3)</f>
@@ -6999,19 +7577,19 @@
       </c>
       <c r="N29">
         <f t="shared" si="1"/>
-        <v>18.399999999999999</v>
+        <v>26.099999999999998</v>
       </c>
       <c r="O29">
         <f t="shared" si="7"/>
-        <v>3.6799999999999997</v>
+        <v>5.22</v>
       </c>
       <c r="P29">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <f t="shared" si="10"/>
@@ -7291,37 +7869,37 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>-12.2</v>
       </c>
       <c r="D34">
-        <v>1.2</v>
+        <v>-2.44</v>
       </c>
       <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <v>3</v>
-      </c>
-      <c r="F34">
-        <v>3</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
       </c>
       <c r="I34" s="7">
         <f>IFERROR((F34/E34)*100,0)</f>
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="J34" s="10">
         <f>IFERROR(C34/E34,0)</f>
-        <v>2</v>
+        <v>-3.05</v>
       </c>
       <c r="K34" s="10">
         <f>IFERROR(D34/E34,0)</f>
-        <v>0.39999999999999997</v>
+        <v>-0.61</v>
       </c>
       <c r="L34" s="10" t="str">
         <f>LEFT(B34,3)</f>
@@ -7329,19 +7907,19 @@
       </c>
       <c r="N34">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>-12.2</v>
       </c>
       <c r="O34">
         <f t="shared" si="7"/>
-        <v>1.2</v>
+        <v>-2.44</v>
       </c>
       <c r="P34">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q34">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R34">
         <f t="shared" si="10"/>
@@ -7349,7 +7927,7 @@
       </c>
       <c r="S34">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
@@ -7357,37 +7935,37 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C35">
-        <v>-12</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>-2.4</v>
+        <v>1.2</v>
       </c>
       <c r="E35">
         <v>3</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35" s="7">
         <f>IFERROR((F35/E35)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="J35" s="10">
         <f>IFERROR(C35/E35,0)</f>
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="K35" s="10">
         <f>IFERROR(D35/E35,0)</f>
-        <v>-0.79999999999999993</v>
+        <v>0.39999999999999997</v>
       </c>
       <c r="L35" s="10" t="str">
         <f>LEFT(B35,3)</f>
@@ -7395,11 +7973,11 @@
       </c>
       <c r="N35">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <f t="shared" si="7"/>
-        <v>-2.4</v>
+        <v>1.2</v>
       </c>
       <c r="P35">
         <f t="shared" si="8"/>
@@ -7407,7 +7985,7 @@
       </c>
       <c r="Q35">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R35">
         <f t="shared" si="10"/>
@@ -7415,7 +7993,7 @@
       </c>
       <c r="S35">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
@@ -7423,19 +8001,19 @@
         <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="C36">
-        <v>1.0000000000000002</v>
+        <v>-1.7000000000000002</v>
       </c>
       <c r="D36">
-        <v>0.2</v>
+        <v>-0.34</v>
       </c>
       <c r="E36">
+        <v>3</v>
+      </c>
+      <c r="F36">
         <v>2</v>
-      </c>
-      <c r="F36">
-        <v>1</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -7445,15 +8023,15 @@
       </c>
       <c r="I36" s="7">
         <f>IFERROR((F36/E36)*100,0)</f>
-        <v>50</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J36" s="10">
         <f>IFERROR(C36/E36,0)</f>
-        <v>0.50000000000000011</v>
+        <v>-0.56666666666666676</v>
       </c>
       <c r="K36" s="10">
         <f>IFERROR(D36/E36,0)</f>
-        <v>0.1</v>
+        <v>-0.11333333333333334</v>
       </c>
       <c r="L36" s="10" t="str">
         <f>LEFT(B36,3)</f>
@@ -7461,19 +8039,19 @@
       </c>
       <c r="N36">
         <f t="shared" si="1"/>
-        <v>1.0000000000000002</v>
+        <v>-1.7000000000000002</v>
       </c>
       <c r="O36">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>-0.34</v>
       </c>
       <c r="P36">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q36">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36">
         <f t="shared" si="10"/>
@@ -7489,57 +8067,57 @@
         <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>-13.799999999999999</v>
       </c>
       <c r="D37">
-        <v>0.2</v>
+        <v>-2.76</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" s="7">
         <f>IFERROR((F37/E37)*100,0)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J37" s="10">
         <f>IFERROR(C37/E37,0)</f>
-        <v>0.5</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="K37" s="10">
         <f>IFERROR(D37/E37,0)</f>
-        <v>0.1</v>
+        <v>-0.91999999999999993</v>
       </c>
       <c r="L37" s="10" t="str">
         <f>LEFT(B37,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N37">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>-13.799999999999999</v>
       </c>
       <c r="O37">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>-2.76</v>
       </c>
       <c r="P37">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q37">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37">
         <f t="shared" si="10"/>
@@ -7547,7 +8125,7 @@
       </c>
       <c r="S37">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
@@ -7555,49 +8133,49 @@
         <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C38">
-        <v>-1.8</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D38">
-        <v>-0.36</v>
+        <v>0.2</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="7">
         <f>IFERROR((F38/E38)*100,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J38" s="10">
         <f>IFERROR(C38/E38,0)</f>
-        <v>-0.9</v>
+        <v>0.50000000000000011</v>
       </c>
       <c r="K38" s="10">
         <f>IFERROR(D38/E38,0)</f>
-        <v>-0.18</v>
+        <v>0.1</v>
       </c>
       <c r="L38" s="10" t="str">
         <f>LEFT(B38,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N38">
         <f t="shared" si="1"/>
-        <v>-1.8</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="O38">
         <f t="shared" si="7"/>
-        <v>-0.36</v>
+        <v>0.2</v>
       </c>
       <c r="P38">
         <f t="shared" si="8"/>
@@ -7605,7 +8183,7 @@
       </c>
       <c r="Q38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38">
         <f t="shared" si="10"/>
@@ -7613,7 +8191,7 @@
       </c>
       <c r="S38">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
@@ -7621,13 +8199,13 @@
         <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="C39">
-        <v>-1.9000000000000001</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>-0.38</v>
+        <v>0.2</v>
       </c>
       <c r="E39">
         <v>2</v>
@@ -7647,11 +8225,11 @@
       </c>
       <c r="J39" s="10">
         <f>IFERROR(C39/E39,0)</f>
-        <v>-0.95000000000000007</v>
+        <v>0.5</v>
       </c>
       <c r="K39" s="10">
         <f>IFERROR(D39/E39,0)</f>
-        <v>-0.19</v>
+        <v>0.1</v>
       </c>
       <c r="L39" s="10" t="str">
         <f>LEFT(B39,3)</f>
@@ -7659,11 +8237,11 @@
       </c>
       <c r="N39">
         <f t="shared" si="1"/>
-        <v>-1.9000000000000001</v>
+        <v>1</v>
       </c>
       <c r="O39">
         <f t="shared" si="7"/>
-        <v>-0.38</v>
+        <v>0.2</v>
       </c>
       <c r="P39">
         <f t="shared" si="8"/>
@@ -7687,13 +8265,13 @@
         <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C40">
-        <v>-12</v>
+        <v>-1.8</v>
       </c>
       <c r="D40">
-        <v>-2.4</v>
+        <v>-0.36</v>
       </c>
       <c r="E40">
         <v>2</v>
@@ -7713,23 +8291,23 @@
       </c>
       <c r="J40" s="10">
         <f>IFERROR(C40/E40,0)</f>
-        <v>-6</v>
+        <v>-0.9</v>
       </c>
       <c r="K40" s="10">
         <f>IFERROR(D40/E40,0)</f>
-        <v>-1.2</v>
+        <v>-0.18</v>
       </c>
       <c r="L40" s="10" t="str">
         <f>LEFT(B40,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N40">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>-1.8</v>
       </c>
       <c r="O40">
         <f t="shared" si="7"/>
-        <v>-2.4</v>
+        <v>-0.36</v>
       </c>
       <c r="P40">
         <f t="shared" si="8"/>
@@ -7753,19 +8331,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C41">
-        <v>-1.3</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="D41">
-        <v>-0.26</v>
+        <v>-0.38</v>
       </c>
       <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="F41">
         <v>1</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -7775,15 +8353,15 @@
       </c>
       <c r="I41" s="7">
         <f>IFERROR((F41/E41)*100,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J41" s="10">
         <f>IFERROR(C41/E41,0)</f>
-        <v>-1.3</v>
+        <v>-0.95000000000000007</v>
       </c>
       <c r="K41" s="10">
         <f>IFERROR(D41/E41,0)</f>
-        <v>-0.26</v>
+        <v>-0.19</v>
       </c>
       <c r="L41" s="10" t="str">
         <f>LEFT(B41,3)</f>
@@ -7791,19 +8369,19 @@
       </c>
       <c r="N41">
         <f t="shared" si="1"/>
-        <v>-1.3</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="O41">
         <f t="shared" si="7"/>
-        <v>-0.26</v>
+        <v>-0.38</v>
       </c>
       <c r="P41">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q41">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41">
         <f t="shared" si="10"/>
@@ -7819,16 +8397,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C42">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="D42">
-        <v>-1.2</v>
+        <v>-2.4</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -7837,7 +8415,7 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" s="7">
         <f>IFERROR((F42/E42)*100,0)</f>
@@ -7853,19 +8431,19 @@
       </c>
       <c r="L42" s="10" t="str">
         <f>LEFT(B42,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N42">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="O42">
         <f t="shared" si="7"/>
-        <v>-1.2</v>
+        <v>-2.4</v>
       </c>
       <c r="P42">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q42">
         <f t="shared" si="9"/>
@@ -7877,24 +8455,24 @@
       </c>
       <c r="S42">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>85</v>
+      <c r="B43" t="s">
+        <v>149</v>
       </c>
       <c r="C43">
-        <v>-1.6</v>
+        <v>-5.2</v>
       </c>
       <c r="D43">
-        <v>-0.32</v>
+        <v>-1.04</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -7903,7 +8481,7 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="7">
         <f>IFERROR((F43/E43)*100,0)</f>
@@ -7911,27 +8489,27 @@
       </c>
       <c r="J43" s="10">
         <f>IFERROR(C43/E43,0)</f>
-        <v>-1.6</v>
+        <v>-2.6</v>
       </c>
       <c r="K43" s="10">
         <f>IFERROR(D43/E43,0)</f>
-        <v>-0.32</v>
+        <v>-0.52</v>
       </c>
       <c r="L43" s="10" t="str">
         <f>LEFT(B43,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N43">
         <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>-5.2</v>
       </c>
       <c r="O43">
         <f t="shared" si="7"/>
-        <v>-0.32</v>
+        <v>-1.04</v>
       </c>
       <c r="P43">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q43">
         <f t="shared" si="9"/>
@@ -7943,7 +8521,7 @@
       </c>
       <c r="S43">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
@@ -7951,16 +8529,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>-14.8</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>-2.96</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -7969,7 +8547,7 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" s="7">
         <f>IFERROR((F44/E44)*100,0)</f>
@@ -7977,27 +8555,27 @@
       </c>
       <c r="J44" s="10">
         <f>IFERROR(C44/E44,0)</f>
-        <v>0</v>
+        <v>-7.4</v>
       </c>
       <c r="K44" s="10">
         <f>IFERROR(D44/E44,0)</f>
-        <v>0</v>
+        <v>-1.48</v>
       </c>
       <c r="L44" s="10" t="str">
         <f>LEFT(B44,3)</f>
-        <v>LEG</v>
+        <v>VEG</v>
       </c>
       <c r="N44">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-14.8</v>
       </c>
       <c r="O44">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2.96</v>
       </c>
       <c r="P44">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q44">
         <f t="shared" si="9"/>
@@ -8009,7 +8587,7 @@
       </c>
       <c r="S44">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
@@ -8017,16 +8595,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -8035,7 +8613,7 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="7">
         <f>IFERROR((F45/E45)*100,0)</f>
@@ -8043,27 +8621,27 @@
       </c>
       <c r="J45" s="10">
         <f>IFERROR(C45/E45,0)</f>
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="K45" s="10">
         <f>IFERROR(D45/E45,0)</f>
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="L45" s="10" t="str">
         <f>LEFT(B45,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N45">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="O45">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="P45">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45">
         <f t="shared" si="9"/>
@@ -8075,7 +8653,7 @@
       </c>
       <c r="S45">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -8083,16 +8661,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -8101,7 +8679,7 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="7">
         <f>IFERROR((F46/E46)*100,0)</f>
@@ -8109,11 +8687,11 @@
       </c>
       <c r="J46" s="10">
         <f>IFERROR(C46/E46,0)</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="K46" s="10">
         <f>IFERROR(D46/E46,0)</f>
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="L46" s="10" t="str">
         <f>LEFT(B46,3)</f>
@@ -8121,15 +8699,15 @@
       </c>
       <c r="N46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="O46">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="P46">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46">
         <f t="shared" si="9"/>
@@ -8141,24 +8719,24 @@
       </c>
       <c r="S46">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>104</v>
+      <c r="B47" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -8167,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="7">
         <f>IFERROR((F47/E47)*100,0)</f>
@@ -8175,27 +8753,27 @@
       </c>
       <c r="J47" s="10">
         <f>IFERROR(C47/E47,0)</f>
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="K47" s="10">
         <f>IFERROR(D47/E47,0)</f>
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="L47" s="10" t="str">
         <f>LEFT(B47,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N47">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="O47">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="P47">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47">
         <f t="shared" si="9"/>
@@ -8207,7 +8785,7 @@
       </c>
       <c r="S47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
@@ -8215,19 +8793,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -8237,35 +8815,35 @@
       </c>
       <c r="I48" s="7">
         <f>IFERROR((F48/E48)*100,0)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J48" s="10">
         <f>IFERROR(C48/E48,0)</f>
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="K48" s="10">
         <f>IFERROR(D48/E48,0)</f>
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="L48" s="10" t="str">
         <f>LEFT(B48,3)</f>
-        <v>PEG</v>
+        <v>WEG</v>
       </c>
       <c r="N48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O48">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="P48">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48">
         <f t="shared" ref="R48:R65" si="12">G48+Y48</f>
@@ -8280,17 +8858,17 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>107</v>
+      <c r="B49" t="s">
+        <v>148</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -8299,7 +8877,7 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="7">
         <f>IFERROR((F49/E49)*100,0)</f>
@@ -8307,27 +8885,27 @@
       </c>
       <c r="J49" s="10">
         <f>IFERROR(C49/E49,0)</f>
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="K49" s="10">
         <f>IFERROR(D49/E49,0)</f>
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="L49" s="10" t="str">
         <f>LEFT(B49,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="O49">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="P49">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49">
         <f t="shared" si="9"/>
@@ -8339,7 +8917,7 @@
       </c>
       <c r="S49">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
@@ -8347,16 +8925,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>-11.4</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -8365,7 +8943,7 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="7">
         <f>IFERROR((F50/E50)*100,0)</f>
@@ -8373,27 +8951,27 @@
       </c>
       <c r="J50" s="10">
         <f>IFERROR(C50/E50,0)</f>
-        <v>0</v>
+        <v>-11.4</v>
       </c>
       <c r="K50" s="10">
         <f>IFERROR(D50/E50,0)</f>
-        <v>0</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="L50" s="10" t="str">
         <f>LEFT(B50,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N50">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-11.4</v>
       </c>
       <c r="O50">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="P50">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50">
         <f t="shared" si="9"/>
@@ -8405,7 +8983,7 @@
       </c>
       <c r="S50">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
@@ -8413,16 +8991,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -8431,7 +9009,7 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" s="7">
         <f>IFERROR((F51/E51)*100,0)</f>
@@ -8439,27 +9017,27 @@
       </c>
       <c r="J51" s="10">
         <f>IFERROR(C51/E51,0)</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K51" s="10">
         <f>IFERROR(D51/E51,0)</f>
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="L51" s="10" t="str">
         <f>LEFT(B51,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N51">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="O51">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="P51">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51">
         <f t="shared" si="9"/>
@@ -8471,27 +9049,27 @@
       </c>
       <c r="S51">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
-        <v>101</v>
+      <c r="B52" s="8" t="s">
+        <v>155</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -8501,35 +9079,35 @@
       </c>
       <c r="I52" s="7">
         <f>IFERROR((F52/E52)*100,0)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J52" s="10">
         <f>IFERROR(C52/E52,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K52" s="10">
         <f>IFERROR(D52/E52,0)</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L52" s="10" t="str">
         <f>LEFT(B52,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N52">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O52">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P52">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52">
         <f t="shared" si="12"/>
@@ -8544,17 +9122,17 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
-        <v>84</v>
+      <c r="B53" s="8" t="s">
+        <v>156</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>-19.5</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>-3.9</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -8563,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="7">
         <f>IFERROR((F53/E53)*100,0)</f>
@@ -8571,27 +9149,27 @@
       </c>
       <c r="J53" s="10">
         <f>IFERROR(C53/E53,0)</f>
-        <v>0</v>
+        <v>-19.5</v>
       </c>
       <c r="K53" s="10">
         <f>IFERROR(D53/E53,0)</f>
-        <v>0</v>
+        <v>-3.9</v>
       </c>
       <c r="L53" s="10" t="str">
         <f>LEFT(B53,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N53">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-19.5</v>
       </c>
       <c r="O53">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3.9</v>
       </c>
       <c r="P53">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53">
         <f t="shared" si="9"/>
@@ -8603,7 +9181,7 @@
       </c>
       <c r="S53">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
@@ -8611,7 +9189,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -8645,7 +9223,7 @@
       </c>
       <c r="L54" s="10" t="str">
         <f>LEFT(B54,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N54">
         <f t="shared" si="1"/>
@@ -8677,7 +9255,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -8711,7 +9289,7 @@
       </c>
       <c r="L55" s="10" t="str">
         <f>LEFT(B55,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N55">
         <f t="shared" si="1"/>
@@ -8743,7 +9321,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -8777,7 +9355,7 @@
       </c>
       <c r="L56" s="10" t="str">
         <f>LEFT(B56,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N56">
         <f t="shared" si="1"/>
@@ -8808,8 +9386,8 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
-        <v>66</v>
+      <c r="B57" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -8843,7 +9421,7 @@
       </c>
       <c r="L57" s="10" t="str">
         <f>LEFT(B57,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N57">
         <f t="shared" si="1"/>
@@ -8874,8 +9452,8 @@
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
-        <v>91</v>
+      <c r="B58" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -8909,7 +9487,7 @@
       </c>
       <c r="L58" s="10" t="str">
         <f>LEFT(B58,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N58">
         <f t="shared" si="1"/>
@@ -8940,8 +9518,8 @@
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
-        <v>94</v>
+      <c r="B59" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -8975,7 +9553,7 @@
       </c>
       <c r="L59" s="10" t="str">
         <f>LEFT(B59,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N59">
         <f t="shared" si="1"/>
@@ -9007,7 +9585,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -9041,7 +9619,7 @@
       </c>
       <c r="L60" s="10" t="str">
         <f>LEFT(B60,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N60">
         <f t="shared" si="1"/>
@@ -9073,7 +9651,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -9107,7 +9685,7 @@
       </c>
       <c r="L61" s="10" t="str">
         <f>LEFT(B61,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N61">
         <f t="shared" si="1"/>
@@ -9139,7 +9717,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -9173,7 +9751,7 @@
       </c>
       <c r="L62" s="10" t="str">
         <f>LEFT(B62,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N62">
         <f t="shared" si="1"/>
@@ -9204,8 +9782,8 @@
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>100</v>
+      <c r="B63" t="s">
+        <v>84</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -9239,7 +9817,7 @@
       </c>
       <c r="L63" s="10" t="str">
         <f>LEFT(B63,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N63">
         <f t="shared" si="1"/>
@@ -9270,8 +9848,8 @@
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>83</v>
+      <c r="B64" t="s">
+        <v>102</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -9305,7 +9883,7 @@
       </c>
       <c r="L64" s="10" t="str">
         <f>LEFT(B64,3)</f>
-        <v>WEG</v>
+        <v>PEG</v>
       </c>
       <c r="N64">
         <f t="shared" si="1"/>
@@ -9336,8 +9914,8 @@
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>90</v>
+      <c r="B65" t="s">
+        <v>103</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -9371,7 +9949,7 @@
       </c>
       <c r="L65" s="10" t="str">
         <f>LEFT(B65,3)</f>
-        <v>WEG</v>
+        <v>PEG</v>
       </c>
       <c r="N65">
         <f t="shared" ref="N65" si="14">C65+U65</f>
@@ -9398,18 +9976,579 @@
         <v>0</v>
       </c>
     </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>147</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66" s="7">
+        <f>IFERROR((F66/E66)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="10">
+        <f>IFERROR(C66/E66,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K66" s="10">
+        <f>IFERROR(D66/E66,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L66" s="10" t="str">
+        <f>LEFT(B66,3)</f>
+        <v>UEG</v>
+      </c>
+      <c r="N66">
+        <f t="shared" ref="N66:N74" si="15">C66+U66</f>
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <f t="shared" ref="O66:O74" si="16">D66+V66</f>
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <f t="shared" ref="P66:P74" si="17">E66+W66</f>
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <f t="shared" ref="Q66:Q74" si="18">F66+X66</f>
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <f t="shared" ref="R66:R74" si="19">G66+Y66</f>
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <f t="shared" ref="S66:S74" si="20">H66+Z66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>66</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67" s="7">
+        <f>IFERROR((F67/E67)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="10">
+        <f>IFERROR(C67/E67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K67" s="10">
+        <f>IFERROR(D67/E67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L67" s="10" t="str">
+        <f>LEFT(B67,3)</f>
+        <v>UEG</v>
+      </c>
+      <c r="N67">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>91</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68" s="7">
+        <f>IFERROR((F68/E68)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J68" s="10">
+        <f>IFERROR(C68/E68,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K68" s="10">
+        <f>IFERROR(D68/E68,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L68" s="10" t="str">
+        <f>LEFT(B68,3)</f>
+        <v>UEG</v>
+      </c>
+      <c r="N68">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>94</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69" s="7">
+        <f>IFERROR((F69/E69)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J69" s="10">
+        <f>IFERROR(C69/E69,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K69" s="10">
+        <f>IFERROR(D69/E69,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L69" s="10" t="str">
+        <f>LEFT(B69,3)</f>
+        <v>UEG</v>
+      </c>
+      <c r="N69">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>95</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70" s="7">
+        <f>IFERROR((F70/E70)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="10">
+        <f>IFERROR(C70/E70,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K70" s="10">
+        <f>IFERROR(D70/E70,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L70" s="10" t="str">
+        <f>LEFT(B70,3)</f>
+        <v>UEG</v>
+      </c>
+      <c r="N70">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>99</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71" s="7">
+        <f>IFERROR((F71/E71)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J71" s="10">
+        <f>IFERROR(C71/E71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K71" s="10">
+        <f>IFERROR(D71/E71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L71" s="10" t="str">
+        <f>LEFT(B71,3)</f>
+        <v>UEG</v>
+      </c>
+      <c r="N71">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>96</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72" s="7">
+        <f>IFERROR((F72/E72)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="10">
+        <f>IFERROR(C72/E72,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K72" s="10">
+        <f>IFERROR(D72/E72,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L72" s="10" t="str">
+        <f>LEFT(B72,3)</f>
+        <v>UEG</v>
+      </c>
+      <c r="N72">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="8"/>
+      <c r="B73" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73" s="7">
+        <f>IFERROR((F73/E73)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J73" s="10">
+        <f>IFERROR(C73/E73,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K73" s="10">
+        <f>IFERROR(D73/E73,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L73" s="10" t="str">
+        <f>LEFT(B73,3)</f>
+        <v>UEG</v>
+      </c>
+      <c r="N73">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="8"/>
+      <c r="B74" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74" s="7">
+        <f>IFERROR((F74/E74)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J74" s="10">
+        <f>IFERROR(C74/E74,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K74" s="10">
+        <f>IFERROR(D74/E74,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L74" s="10" t="str">
+        <f>LEFT(B74,3)</f>
+        <v>WEG</v>
+      </c>
+      <c r="N74">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B75" s="8"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L65">
-    <sortCondition descending="1" ref="E2:E65"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L75">
+    <sortCondition descending="1" ref="E2:E75"/>
   </sortState>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="dataBar" priority="10">
@@ -9649,11 +10788,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A53AFF8-0615-4AA5-B49F-FDA402810813}">
-  <dimension ref="A1:AB66"/>
+  <dimension ref="A1:AB75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
-    <col min="8" max="28" width="6.28515625" style="11" customWidth="1"/>
+    <col min="8" max="28" width="8.42578125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -9690,23 +10829,23 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B3">
         <f>SUM(H3:AB3)</f>
-        <v>7.8999999999999986</v>
+        <v>10.6</v>
       </c>
       <c r="C3">
         <f>(B3/$C$1)*100</f>
-        <v>1.5799999999999998</v>
+        <v>2.12</v>
       </c>
       <c r="D3">
         <f>COUNTA(H3:AB3)</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <f>COUNTIF(H3:AB3, "&gt;0")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <f>COUNTIF(H3:AB3, "=0")</f>
@@ -9714,45 +10853,39 @@
       </c>
       <c r="G3">
         <f>COUNTIF(H3:AB3, "&lt;0")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" s="20">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="I3" s="20">
-        <v>5.3</v>
+        <v>-0.9</v>
       </c>
       <c r="J3" s="20">
-        <v>0.2</v>
+        <v>13.1</v>
       </c>
       <c r="K3" s="20">
-        <v>-0.6</v>
-      </c>
-      <c r="L3" s="20">
-        <v>-2.7</v>
-      </c>
-      <c r="M3" s="20">
-        <v>-3.3</v>
-      </c>
-      <c r="N3" s="20">
-        <v>5.6</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B4">
         <f>SUM(H4:AB4)</f>
-        <v>0.59999999999999964</v>
+        <v>10.6</v>
       </c>
       <c r="C4">
         <f>(B4/$C$1)*100</f>
-        <v>0.11999999999999993</v>
+        <v>2.12</v>
       </c>
       <c r="D4">
         <f>COUNTA(H4:AB4)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <f>COUNTIF(H4:AB4, "&gt;0")</f>
@@ -9764,32 +10897,33 @@
       </c>
       <c r="G4">
         <f>COUNTIF(H4:AB4, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="20">
-        <v>9.6</v>
+        <v>5.3</v>
       </c>
       <c r="I4" s="20">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J4" s="21">
-        <v>0.4</v>
-      </c>
-      <c r="K4" s="21">
-        <v>-10.3</v>
-      </c>
+        <v>3.8</v>
+      </c>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B5">
         <f>SUM(H5:AB5)</f>
-        <v>12.8</v>
+        <v>-8.1</v>
       </c>
       <c r="C5">
         <f>(B5/$C$1)*100</f>
-        <v>2.56</v>
+        <v>-1.6199999999999999</v>
       </c>
       <c r="D5">
         <f>COUNTA(H5:AB5)</f>
@@ -9797,7 +10931,7 @@
       </c>
       <c r="E5">
         <f>COUNTIF(H5:AB5, "&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <f>COUNTIF(H5:AB5, "=0")</f>
@@ -9805,29 +10939,30 @@
       </c>
       <c r="G5">
         <f>COUNTIF(H5:AB5, "&lt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="20">
-        <v>-0.4</v>
-      </c>
-      <c r="I5" s="21">
-        <v>7.4</v>
-      </c>
-      <c r="J5" s="21">
-        <v>5.8</v>
-      </c>
+        <v>-5.2</v>
+      </c>
+      <c r="I5" s="20">
+        <v>3.2</v>
+      </c>
+      <c r="J5" s="20">
+        <v>-6.1</v>
+      </c>
+      <c r="K5" s="15"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="B6">
         <f>SUM(H6:AB6)</f>
-        <v>-3.1000000000000005</v>
+        <v>4.1999999999999993</v>
       </c>
       <c r="C6">
         <f>(B6/$C$1)*100</f>
-        <v>-0.62000000000000011</v>
+        <v>0.83999999999999975</v>
       </c>
       <c r="D6">
         <f>COUNTA(H6:AB6)</f>
@@ -9835,7 +10970,7 @@
       </c>
       <c r="E6">
         <f>COUNTIF(H6:AB6, "&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <f>COUNTIF(H6:AB6, "=0")</f>
@@ -9843,37 +10978,37 @@
       </c>
       <c r="G6">
         <f>COUNTIF(H6:AB6, "&lt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="20">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="I6" s="21">
-        <v>-2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J6" s="21">
-        <v>-4.9000000000000004</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="B7">
         <f>SUM(H7:AB7)</f>
-        <v>-11.8</v>
+        <v>-1.7000000000000002</v>
       </c>
       <c r="C7">
         <f>(B7/$C$1)*100</f>
-        <v>-2.3600000000000003</v>
+        <v>-0.34</v>
       </c>
       <c r="D7">
         <f>COUNTA(H7:AB7)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <f>COUNTIF(H7:AB7, "&gt;0")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <f>COUNTIF(H7:AB7, "=0")</f>
@@ -9881,35 +11016,37 @@
       </c>
       <c r="G7">
         <f>COUNTIF(H7:AB7, "&lt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="20">
-        <v>-4.5999999999999996</v>
+        <v>1.6</v>
       </c>
       <c r="I7" s="21">
-        <v>-7.2</v>
-      </c>
-      <c r="J7" s="17"/>
+        <v>1.6</v>
+      </c>
+      <c r="J7" s="21">
+        <v>-4.9000000000000004</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="B8">
         <f>SUM(H8:AB8)</f>
-        <v>10</v>
+        <v>-13.799999999999999</v>
       </c>
       <c r="C8">
         <f>(B8/$C$1)*100</f>
-        <v>2</v>
+        <v>-2.76</v>
       </c>
       <c r="D8">
         <f>COUNTA(H8:AB8)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8">
         <f>COUNTIF(H8:AB8, "&gt;0")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <f>COUNTIF(H8:AB8, "=0")</f>
@@ -9917,27 +11054,29 @@
       </c>
       <c r="G8">
         <f>COUNTIF(H8:AB8, "&lt;0")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" s="20">
-        <v>4.5</v>
+        <v>-6.1</v>
       </c>
       <c r="I8" s="20">
-        <v>5.5</v>
-      </c>
-      <c r="J8" s="15"/>
+        <v>-6.8</v>
+      </c>
+      <c r="J8" s="20">
+        <v>-0.9</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B9">
         <f>SUM(H9:AB9)</f>
-        <v>-2.2000000000000002</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="C9">
         <f>(B9/$C$1)*100</f>
-        <v>-0.44</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="D9">
         <f>COUNTA(H9:AB9)</f>
@@ -9945,7 +11084,7 @@
       </c>
       <c r="E9">
         <f>COUNTIF(H9:AB9, "&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <f>COUNTIF(H9:AB9, "=0")</f>
@@ -9953,35 +11092,35 @@
       </c>
       <c r="G9">
         <f>COUNTIF(H9:AB9, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="20">
-        <v>0.5</v>
+        <v>9.9</v>
       </c>
       <c r="I9" s="20">
-        <v>-2.7</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="J9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="B10">
         <f>SUM(H10:AB10)</f>
-        <v>3</v>
+        <v>-5.2</v>
       </c>
       <c r="C10">
         <f>(B10/$C$1)*100</f>
-        <v>0.6</v>
+        <v>-1.04</v>
       </c>
       <c r="D10">
         <f>COUNTA(H10:AB10)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <f>COUNTIF(H10:AB10, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <f>COUNTIF(H10:AB10, "=0")</f>
@@ -9989,33 +11128,35 @@
       </c>
       <c r="G10">
         <f>COUNTIF(H10:AB10, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="20">
-        <v>3</v>
-      </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
+        <v>2</v>
+      </c>
+      <c r="H10" s="15">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="I10" s="20">
+        <v>-3</v>
+      </c>
+      <c r="J10" s="15"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="B11">
         <f>SUM(H11:AB11)</f>
-        <v>3.3</v>
+        <v>-14.8</v>
       </c>
       <c r="C11">
         <f>(B11/$C$1)*100</f>
-        <v>0.66</v>
+        <v>-2.96</v>
       </c>
       <c r="D11">
         <f>COUNTA(H11:AB11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11">
         <f>COUNTIF(H11:AB11, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <f>COUNTIF(H11:AB11, "=0")</f>
@@ -10023,24 +11164,27 @@
       </c>
       <c r="G11">
         <f>COUNTIF(H11:AB11, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="20">
-        <v>3.3</v>
-      </c>
-      <c r="I11" s="19"/>
+        <v>2</v>
+      </c>
+      <c r="H11" s="15">
+        <v>-10.1</v>
+      </c>
+      <c r="I11" s="20">
+        <v>-4.7</v>
+      </c>
+      <c r="J11" s="15"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B12">
         <f>SUM(H12:AB12)</f>
-        <v>3.3</v>
+        <v>-3.7</v>
       </c>
       <c r="C12">
         <f>(B12/$C$1)*100</f>
-        <v>0.66</v>
+        <v>-0.74</v>
       </c>
       <c r="D12">
         <f>COUNTA(H12:AB12)</f>
@@ -10048,7 +11192,7 @@
       </c>
       <c r="E12">
         <f>COUNTIF(H12:AB12, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <f>COUNTIF(H12:AB12, "=0")</f>
@@ -10056,26 +11200,26 @@
       </c>
       <c r="G12">
         <f>COUNTIF(H12:AB12, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="20">
-        <v>3.3</v>
-      </c>
-      <c r="I12" s="19"/>
+        <v>-3.7</v>
+      </c>
+      <c r="I12" s="22"/>
       <c r="J12" s="19"/>
       <c r="K12" s="15"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B13">
         <f>SUM(H13:AB13)</f>
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="C13">
         <f>(B13/$C$1)*100</f>
-        <v>0.70000000000000007</v>
+        <v>0.36</v>
       </c>
       <c r="D13">
         <f>COUNTA(H13:AB13)</f>
@@ -10094,9 +11238,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="20">
-        <v>3.5</v>
-      </c>
-      <c r="I13" s="19"/>
+        <v>1.8</v>
+      </c>
+      <c r="I13" s="20"/>
       <c r="J13" s="19"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -10105,11 +11249,11 @@
       </c>
       <c r="B14">
         <f>SUM(H14:AB14)</f>
-        <v>0.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="C14">
         <f>(B14/$C$1)*100</f>
-        <v>0.13999999999999999</v>
+        <v>1.9600000000000002</v>
       </c>
       <c r="D14">
         <f>COUNTA(H14:AB14)</f>
@@ -10128,22 +11272,22 @@
         <v>0</v>
       </c>
       <c r="H14" s="20">
-        <v>0.7</v>
-      </c>
-      <c r="I14" s="19"/>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I14" s="15"/>
       <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B15">
         <f>SUM(H15:AB15)</f>
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="C15">
         <f>(B15/$C$1)*100</f>
-        <v>0</v>
+        <v>0.33999999999999997</v>
       </c>
       <c r="D15">
         <f>COUNTA(H15:AB15)</f>
@@ -10151,33 +11295,33 @@
       </c>
       <c r="E15">
         <f>COUNTIF(H15:AB15, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <f>COUNTIF(H15:AB15, "=0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <f>COUNTIF(H15:AB15, "&lt;0")</f>
         <v>0</v>
       </c>
       <c r="H15" s="20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="B16">
         <f>SUM(H16:AB16)</f>
-        <v>3</v>
+        <v>7.7</v>
       </c>
       <c r="C16">
         <f>(B16/$C$1)*100</f>
-        <v>0.6</v>
+        <v>1.54</v>
       </c>
       <c r="D16">
         <f>COUNTA(H16:AB16)</f>
@@ -10196,21 +11340,21 @@
         <v>0</v>
       </c>
       <c r="H16" s="20">
-        <v>3</v>
+        <v>7.7</v>
       </c>
       <c r="I16" s="15"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="B17">
         <f>SUM(H17:AB17)</f>
-        <v>2.2000000000000002</v>
+        <v>-0.2</v>
       </c>
       <c r="C17">
         <f>(B17/$C$1)*100</f>
-        <v>0.44</v>
+        <v>-0.04</v>
       </c>
       <c r="D17">
         <f>COUNTA(H17:AB17)</f>
@@ -10218,7 +11362,7 @@
       </c>
       <c r="E17">
         <f>COUNTIF(H17:AB17, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <f>COUNTIF(H17:AB17, "=0")</f>
@@ -10226,24 +11370,23 @@
       </c>
       <c r="G17">
         <f>COUNTIF(H17:AB17, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="21">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="I17" s="17"/>
+        <v>-0.2</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>97</v>
+      <c r="A18" s="5" t="s">
+        <v>90</v>
       </c>
       <c r="B18">
         <f>SUM(H18:AB18)</f>
-        <v>-2.9</v>
+        <v>4.3</v>
       </c>
       <c r="C18">
         <f>(B18/$C$1)*100</f>
-        <v>-0.57999999999999996</v>
+        <v>0.86</v>
       </c>
       <c r="D18">
         <f>COUNTA(H18:AB18)</f>
@@ -10251,7 +11394,7 @@
       </c>
       <c r="E18">
         <f>COUNTIF(H18:AB18, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <f>COUNTIF(H18:AB18, "=0")</f>
@@ -10259,25 +11402,25 @@
       </c>
       <c r="G18">
         <f>COUNTIF(H18:AB18, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="20">
-        <v>-2.9</v>
+        <v>4.3</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B19">
         <f>SUM(H19:AB19)</f>
-        <v>6.1</v>
+        <v>-1.3</v>
       </c>
       <c r="C19">
         <f>(B19/$C$1)*100</f>
-        <v>1.22</v>
+        <v>-0.26</v>
       </c>
       <c r="D19">
         <f>COUNTA(H19:AB19)</f>
@@ -10285,7 +11428,7 @@
       </c>
       <c r="E19">
         <f>COUNTIF(H19:AB19, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <f>COUNTIF(H19:AB19, "=0")</f>
@@ -10293,24 +11436,24 @@
       </c>
       <c r="G19">
         <f>COUNTIF(H19:AB19, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="20">
-        <v>6.1</v>
+        <v>-1.3</v>
       </c>
       <c r="I19" s="15"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="B20">
         <f>SUM(H20:AB20)</f>
-        <v>-5.0999999999999996</v>
+        <v>-11.4</v>
       </c>
       <c r="C20">
         <f>(B20/$C$1)*100</f>
-        <v>-1.0199999999999998</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="D20">
         <f>COUNTA(H20:AB20)</f>
@@ -10328,21 +11471,21 @@
         <f>COUNTIF(H20:AB20, "&lt;0")</f>
         <v>1</v>
       </c>
-      <c r="H20" s="20">
-        <v>-5.0999999999999996</v>
+      <c r="H20" s="15">
+        <v>-11.4</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>154</v>
       </c>
       <c r="B21">
         <f>SUM(H21:AB21)</f>
-        <v>-8.3000000000000007</v>
+        <v>-4</v>
       </c>
       <c r="C21">
         <f>(B21/$C$1)*100</f>
-        <v>-1.66</v>
+        <v>-0.8</v>
       </c>
       <c r="D21">
         <f>COUNTA(H21:AB21)</f>
@@ -10360,21 +11503,21 @@
         <f>COUNTIF(H21:AB21, "&lt;0")</f>
         <v>1</v>
       </c>
-      <c r="H21" s="20">
-        <v>-8.3000000000000007</v>
+      <c r="H21" s="15">
+        <v>-4</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>85</v>
+      <c r="A22" t="s">
+        <v>155</v>
       </c>
       <c r="B22">
         <f>SUM(H22:AB22)</f>
-        <v>-1.6</v>
+        <v>0.5</v>
       </c>
       <c r="C22">
         <f>(B22/$C$1)*100</f>
-        <v>-0.32</v>
+        <v>0.1</v>
       </c>
       <c r="D22">
         <f>COUNTA(H22:AB22)</f>
@@ -10382,7 +11525,7 @@
       </c>
       <c r="E22">
         <f>COUNTIF(H22:AB22, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
         <f>COUNTIF(H22:AB22, "=0")</f>
@@ -10390,27 +11533,27 @@
       </c>
       <c r="G22">
         <f>COUNTIF(H22:AB22, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="21">
-        <v>-1.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="B23">
         <f>SUM(H23:AB23)</f>
-        <v>0</v>
+        <v>-19.5</v>
       </c>
       <c r="C23">
         <f>(B23/$C$1)*100</f>
-        <v>0</v>
+        <v>-3.9</v>
       </c>
       <c r="D23">
         <f>COUNTA(H23:AB23)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <f>COUNTIF(H23:AB23, "&gt;0")</f>
@@ -10422,15 +11565,15 @@
       </c>
       <c r="G23">
         <f>COUNTIF(H23:AB23, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="H23" s="23">
+        <v>-19.5</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B24">
         <f>SUM(H24:AB24)</f>
@@ -10456,11 +11599,14 @@
         <f>COUNTIF(H24:AB24, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H24" s="17"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>62</v>
       </c>
       <c r="B25">
         <f>SUM(H25:AB25)</f>
@@ -10486,11 +11632,13 @@
         <f>COUNTIF(H25:AB25, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="17"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B26">
         <f>SUM(H26:AB26)</f>
@@ -10516,11 +11664,12 @@
         <f>COUNTIF(H26:AB26, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H26" s="17"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="B27">
         <f>SUM(H27:AB27)</f>
@@ -10546,11 +11695,13 @@
         <f>COUNTIF(H27:AB27, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H27" s="17"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B28">
         <f>SUM(H28:AB28)</f>
@@ -10576,15 +11727,15 @@
         <f>COUNTIF(H28:AB28, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H28" s="18"/>
-      <c r="I28" s="15"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="19"/>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
       <c r="L28" s="15"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B29">
         <f>SUM(H29:AB29)</f>
@@ -10610,11 +11761,11 @@
         <f>COUNTIF(H29:AB29, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H29" s="19"/>
+      <c r="H29" s="20"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="B30">
         <f>SUM(H30:AB30)</f>
@@ -10640,11 +11791,12 @@
         <f>COUNTIF(H30:AB30, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H30" s="19"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="17"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="B31">
         <f>SUM(H31:AB31)</f>
@@ -10670,12 +11822,11 @@
         <f>COUNTIF(H31:AB31, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H31" s="19"/>
-      <c r="I31" s="17"/>
+      <c r="H31" s="20"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="B32">
         <f>SUM(H32:AB32)</f>
@@ -10701,11 +11852,11 @@
         <f>COUNTIF(H32:AB32, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H32" s="19"/>
+      <c r="H32" s="20"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B33">
         <f>SUM(H33:AB33)</f>
@@ -10731,11 +11882,11 @@
         <f>COUNTIF(H33:AB33, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H33" s="19"/>
+      <c r="H33" s="20"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="B34">
         <f>SUM(H34:AB34)</f>
@@ -10761,11 +11912,11 @@
         <f>COUNTIF(H34:AB34, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H34" s="19"/>
+      <c r="H34" s="20"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>76</v>
+      <c r="A35" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="B35">
         <f>SUM(H35:AB35)</f>
@@ -10791,11 +11942,11 @@
         <f>COUNTIF(H35:AB35, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H35" s="18"/>
+      <c r="H35" s="22"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B36">
         <f>SUM(H36:AB36)</f>
@@ -10822,10 +11973,12 @@
         <v>0</v>
       </c>
       <c r="H36" s="19"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="B37">
         <f>SUM(H37:AB37)</f>
@@ -10856,7 +12009,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B38">
         <f>SUM(H38:AB38)</f>
@@ -10882,11 +12035,11 @@
         <f>COUNTIF(H38:AB38, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H38" s="15"/>
+      <c r="H38" s="19"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="B39">
         <f>SUM(H39:AB39)</f>
@@ -10912,11 +12065,11 @@
         <f>COUNTIF(H39:AB39, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H39" s="15"/>
+      <c r="H39" s="19"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="B40">
         <f>SUM(H40:AB40)</f>
@@ -10942,11 +12095,11 @@
         <f>COUNTIF(H40:AB40, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H40" s="15"/>
+      <c r="H40" s="19"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="B41">
         <f>SUM(H41:AB41)</f>
@@ -10972,13 +12125,13 @@
         <f>COUNTIF(H41:AB41, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H41" s="15"/>
+      <c r="H41" s="18"/>
       <c r="I41" s="15"/>
       <c r="J41" s="15"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="B42">
         <f>SUM(H42:AB42)</f>
@@ -11004,11 +12157,12 @@
         <f>COUNTIF(H42:AB42, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H42" s="15"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="17"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B43">
         <f>SUM(H43:AB43)</f>
@@ -11034,11 +12188,11 @@
         <f>COUNTIF(H43:AB43, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H43" s="15"/>
+      <c r="H43" s="19"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B44">
         <f>SUM(H44:AB44)</f>
@@ -11064,11 +12218,11 @@
         <f>COUNTIF(H44:AB44, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H44" s="15"/>
+      <c r="H44" s="19"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B45">
         <f>SUM(H45:AB45)</f>
@@ -11094,11 +12248,11 @@
         <f>COUNTIF(H45:AB45, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H45" s="15"/>
+      <c r="H45" s="19"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="B46">
         <f>SUM(H46:AB46)</f>
@@ -11124,10 +12278,11 @@
         <f>COUNTIF(H46:AB46, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H46" s="17"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B47">
         <f>SUM(H47:AB47)</f>
@@ -11153,10 +12308,11 @@
         <f>COUNTIF(H47:AB47, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H47" s="17"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>104</v>
+      <c r="A48" t="s">
+        <v>75</v>
       </c>
       <c r="B48">
         <f>SUM(H48:AB48)</f>
@@ -11184,8 +12340,8 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>106</v>
+      <c r="A49" t="s">
+        <v>81</v>
       </c>
       <c r="B49">
         <f>SUM(H49:AB49)</f>
@@ -11216,8 +12372,8 @@
       <c r="J49" s="15"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>107</v>
+      <c r="A50" t="s">
+        <v>105</v>
       </c>
       <c r="B50">
         <f>SUM(H50:AB50)</f>
@@ -11246,7 +12402,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="B51">
         <f>SUM(H51:AB51)</f>
@@ -11275,7 +12431,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B52">
         <f>SUM(H52:AB52)</f>
@@ -11306,7 +12462,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="B53">
         <f>SUM(H53:AB53)</f>
@@ -11336,7 +12492,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B54">
         <f>SUM(H54:AB54)</f>
@@ -11366,7 +12522,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="B55">
         <f>SUM(H55:AB55)</f>
@@ -11395,7 +12551,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B56">
         <f>SUM(H56:AB56)</f>
@@ -11424,7 +12580,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="B57">
         <f>SUM(H57:AB57)</f>
@@ -11452,8 +12608,8 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>66</v>
+      <c r="A58" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B58">
         <f>SUM(H58:AB58)</f>
@@ -11482,8 +12638,8 @@
       <c r="H58" s="15"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>91</v>
+      <c r="A59" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B59">
         <f>SUM(H59:AB59)</f>
@@ -11511,8 +12667,8 @@
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>94</v>
+      <c r="A60" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B60">
         <f>SUM(H60:AB60)</f>
@@ -11541,7 +12697,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B61">
         <f>SUM(H61:AB61)</f>
@@ -11570,7 +12726,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B62">
         <f>SUM(H62:AB62)</f>
@@ -11599,7 +12755,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B63">
         <f>SUM(H63:AB63)</f>
@@ -11629,8 +12785,8 @@
       <c r="I63" s="15"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
-        <v>100</v>
+      <c r="A64" t="s">
+        <v>84</v>
       </c>
       <c r="B64">
         <f>SUM(H64:AB64)</f>
@@ -11657,9 +12813,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
-        <v>83</v>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>102</v>
       </c>
       <c r="B65">
         <f>SUM(H65:AB65)</f>
@@ -11686,9 +12842,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
-        <v>90</v>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>103</v>
       </c>
       <c r="B66">
         <f>SUM(H66:AB66)</f>
@@ -11714,10 +12870,283 @@
         <f>COUNTIF(H66:AB66, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H66" s="15"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>147</v>
+      </c>
+      <c r="B67">
+        <f>SUM(H67:AB67)</f>
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <f>(B67/$C$1)*100</f>
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <f>COUNTA(H67:AB67)</f>
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <f>COUNTIF(H67:AB67, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <f>COUNTIF(H67:AB67, "=0")</f>
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <f>COUNTIF(H67:AB67, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="H67" s="15"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <f>SUM(H68:AB68)</f>
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <f>(B68/$C$1)*100</f>
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <f>COUNTA(H68:AB68)</f>
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <f>COUNTIF(H68:AB68, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <f>COUNTIF(H68:AB68, "=0")</f>
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <f>COUNTIF(H68:AB68, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="I68" s="15"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>91</v>
+      </c>
+      <c r="B69">
+        <f>SUM(H69:AB69)</f>
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <f>(B69/$C$1)*100</f>
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <f>COUNTA(H69:AB69)</f>
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <f>COUNTIF(H69:AB69, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <f>COUNTIF(H69:AB69, "=0")</f>
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <f>COUNTIF(H69:AB69, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="I69" s="15"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>94</v>
+      </c>
+      <c r="B70">
+        <f>SUM(H70:AB70)</f>
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <f>(B70/$C$1)*100</f>
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <f>COUNTA(H70:AB70)</f>
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <f>COUNTIF(H70:AB70, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <f>COUNTIF(H70:AB70, "=0")</f>
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <f>COUNTIF(H70:AB70, "&lt;0")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>95</v>
+      </c>
+      <c r="B71">
+        <f>SUM(H71:AB71)</f>
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <f>(B71/$C$1)*100</f>
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <f>COUNTA(H71:AB71)</f>
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <f>COUNTIF(H71:AB71, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <f>COUNTIF(H71:AB71, "=0")</f>
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <f>COUNTIF(H71:AB71, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72">
+        <f>SUM(H72:AB72)</f>
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <f>(B72/$C$1)*100</f>
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <f>COUNTA(H72:AB72)</f>
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <f>COUNTIF(H72:AB72, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <f>COUNTIF(H72:AB72, "=0")</f>
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <f>COUNTIF(H72:AB72, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>96</v>
+      </c>
+      <c r="B73">
+        <f>SUM(H73:AB73)</f>
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <f>(B73/$C$1)*100</f>
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <f>COUNTA(H73:AB73)</f>
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <f>COUNTIF(H73:AB73, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <f>COUNTIF(H73:AB73, "=0")</f>
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <f>COUNTIF(H73:AB73, "&lt;0")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B74">
+        <f>SUM(H74:AB74)</f>
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <f>(B74/$C$1)*100</f>
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <f>COUNTA(H74:AB74)</f>
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <f>COUNTIF(H74:AB74, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <f>COUNTIF(H74:AB74, "=0")</f>
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <f>COUNTIF(H74:AB74, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="H74" s="15"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75">
+        <f>SUM(H75:AB75)</f>
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <f>(B75/$C$1)*100</f>
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <f>COUNTA(H75:AB75)</f>
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <f>COUNTIF(H75:AB75, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <f>COUNTIF(H75:AB75, "=0")</f>
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <f>COUNTIF(H75:AB75, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="H75" s="15"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB66">
-    <sortCondition descending="1" ref="D3:D66"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:W75">
+    <sortCondition descending="1" ref="D3:D75"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF19EFE2-F131-44C1-8D97-97C3B124E3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E1229F-2CAC-4E5C-AD96-20E97B682656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
     <sheet name="СтатПоТипу" sheetId="6" r:id="rId2"/>
     <sheet name="Динамика" sheetId="7" r:id="rId3"/>
-    <sheet name="Результаты" sheetId="4" r:id="rId4"/>
-    <sheet name="СумматорСегодня" sheetId="5" r:id="rId5"/>
+    <sheet name="ГрафикДинамики" sheetId="8" r:id="rId4"/>
+    <sheet name="Результаты" sheetId="4" r:id="rId5"/>
+    <sheet name="СумматорСегодня" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId6"/>
+    <pivotCache cacheId="3" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="140">
   <si>
     <t>AQUA</t>
   </si>
@@ -449,15 +450,24 @@
   </si>
   <si>
     <t>UEG9_BIRDWATCHER2</t>
+  </si>
+  <si>
+    <t>VEG1_EARTH</t>
+  </si>
+  <si>
+    <t>UEG7_DETECTIVE</t>
+  </si>
+  <si>
+    <t>WEG4_DOG</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -561,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -598,9 +608,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -735,10 +742,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$H$2</c:f>
+              <c:f>Динамика!$B$2:$I$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -759,16 +766,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>46294</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$3:$H$3</c:f>
+              <c:f>Динамика!$B$3:$I$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>-20.100000000000001</c:v>
                 </c:pt>
@@ -789,6 +799,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-17.000000000000021</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.4999999999999858</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -796,7 +809,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C8F5-4770-9D74-C7A222ED5A91}"/>
+              <c16:uniqueId val="{00000000-2937-46B9-9566-F06989B964D6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -840,10 +853,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$H$2</c:f>
+              <c:f>Динамика!$B$2:$I$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -864,16 +877,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>46294</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$4:$H$4</c:f>
+              <c:f>Динамика!$B$4:$I$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>19.7</c:v>
                 </c:pt>
@@ -894,6 +910,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>70.199999999999989</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>85.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -901,7 +920,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C8F5-4770-9D74-C7A222ED5A91}"/>
+              <c16:uniqueId val="{00000001-2937-46B9-9566-F06989B964D6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -945,10 +964,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$H$2</c:f>
+              <c:f>Динамика!$B$2:$I$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -969,16 +988,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>46294</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$5:$H$5</c:f>
+              <c:f>Динамика!$B$5:$I$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1.9</c:v>
                 </c:pt>
@@ -999,6 +1021,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>17.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12.699999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,7 +1031,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C8F5-4770-9D74-C7A222ED5A91}"/>
+              <c16:uniqueId val="{00000002-2937-46B9-9566-F06989B964D6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1050,10 +1075,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$H$2</c:f>
+              <c:f>Динамика!$B$2:$I$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1074,16 +1099,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>46294</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$6:$H$6</c:f>
+              <c:f>Динамика!$B$6:$I$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>-21</c:v>
                 </c:pt>
@@ -1104,6 +1132,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-55.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-23.799999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1111,7 +1142,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C8F5-4770-9D74-C7A222ED5A91}"/>
+              <c16:uniqueId val="{00000003-2937-46B9-9566-F06989B964D6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1155,10 +1186,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$H$2</c:f>
+              <c:f>Динамика!$B$2:$I$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1179,16 +1210,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>46294</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$7:$H$7</c:f>
+              <c:f>Динамика!$B$7:$I$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>-18.100000000000001</c:v>
                 </c:pt>
@@ -1209,6 +1243,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-37.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-47.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1216,7 +1253,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-C8F5-4770-9D74-C7A222ED5A91}"/>
+              <c16:uniqueId val="{00000004-2937-46B9-9566-F06989B964D6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1260,10 +1297,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$H$2</c:f>
+              <c:f>Динамика!$B$2:$I$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1284,16 +1321,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>46294</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$8:$H$8</c:f>
+              <c:f>Динамика!$B$8:$I$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>44.5</c:v>
                 </c:pt>
@@ -1314,6 +1354,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>74.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>73</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1321,7 +1364,124 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-C8F5-4770-9D74-C7A222ED5A91}"/>
+              <c16:uniqueId val="{00000005-2937-46B9-9566-F06989B964D6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Динамика!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Динамика!$B$2:$I$2</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>46285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46287</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46288</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46290</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46293</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46294</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46295</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Динамика!$B$9:$I$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>6.8999999999999915</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>87.699999999999989</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>134.99999999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>156.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>52.399999999999977</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>106.79999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-2937-46B9-9566-F06989B964D6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2074,27 +2234,29 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>142874</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>109537</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>476249</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Диаграмма 3">
+        <xdr:cNvPr id="2" name="Диаграмма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C4DE348-C853-4C12-8B37-B46EB6F1F415}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50ACC054-380D-4AFE-9C8A-E3EBB25684A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2112,43 +2274,43 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46295.003215856479" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="76" xr:uid="{3D6F248A-0360-4477-B017-E96CAA4B0EB4}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46295.963663541668" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="75" xr:uid="{3D6F248A-0360-4477-B017-E96CAA4B0EB4}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:L1048576" sheet="Результаты"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="Номер" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="52"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="55"/>
     </cacheField>
     <cacheField name="Стратегия" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Абс" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-42.900000000000006" maxValue="113.09999999999998"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-42.900000000000006" maxValue="123.69999999999997"/>
     </cacheField>
     <cacheField name="Отн" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-8.58" maxValue="22.620000000000005"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-8.58" maxValue="24.740000000000006"/>
     </cacheField>
     <cacheField name="Кол-во" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="59"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="64"/>
     </cacheField>
     <cacheField name="Прибыль" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="40"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="44"/>
     </cacheField>
     <cacheField name="Нейтрал" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
     </cacheField>
     <cacheField name="Убыток" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="19"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="20"/>
     </cacheField>
     <cacheField name="ПроцПД" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="100"/>
     </cacheField>
     <cacheField name="САП" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-19.5" maxValue="3.05"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-19.5" maxValue="5.2"/>
     </cacheField>
     <cacheField name="СОП" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-3.9" maxValue="0.61"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-3.9" maxValue="1.04"/>
     </cacheField>
     <cacheField name="Тип" numFmtId="0">
       <sharedItems containsBlank="1" count="7">
@@ -2171,47 +2333,47 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="76">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="75">
   <r>
     <n v="1"/>
     <s v="PEG17_PHOENIX"/>
-    <n v="113.09999999999998"/>
-    <n v="22.620000000000005"/>
-    <n v="59"/>
-    <n v="40"/>
+    <n v="123.69999999999997"/>
+    <n v="24.740000000000006"/>
+    <n v="64"/>
+    <n v="44"/>
     <n v="0"/>
-    <n v="19"/>
-    <n v="67.796610169491515"/>
-    <n v="1.9169491525423725"/>
-    <n v="0.38338983050847464"/>
+    <n v="20"/>
+    <n v="68.75"/>
+    <n v="1.9328124999999996"/>
+    <n v="0.38656250000000009"/>
     <x v="0"/>
   </r>
   <r>
     <n v="2"/>
     <s v="WEG3_BATYA"/>
-    <n v="50.000000000000007"/>
-    <n v="10.000000000000002"/>
-    <n v="43"/>
-    <n v="26"/>
-    <n v="0"/>
-    <n v="17"/>
-    <n v="60.465116279069761"/>
-    <n v="1.1627906976744187"/>
-    <n v="0.23255813953488377"/>
+    <n v="49.300000000000004"/>
+    <n v="9.8600000000000012"/>
+    <n v="47"/>
+    <n v="28"/>
+    <n v="1"/>
+    <n v="18"/>
+    <n v="59.574468085106382"/>
+    <n v="1.048936170212766"/>
+    <n v="0.20978723404255323"/>
     <x v="1"/>
   </r>
   <r>
     <n v="3"/>
     <s v="PEG11_KUSURUKEN"/>
-    <n v="30.9"/>
-    <n v="6.1800000000000006"/>
-    <n v="38"/>
+    <n v="29.799999999999997"/>
+    <n v="5.9600000000000009"/>
+    <n v="39"/>
     <n v="19"/>
     <n v="1"/>
-    <n v="18"/>
-    <n v="50"/>
-    <n v="0.81315789473684208"/>
-    <n v="0.16263157894736843"/>
+    <n v="19"/>
+    <n v="48.717948717948715"/>
+    <n v="0.76410256410256405"/>
+    <n v="0.15282051282051284"/>
     <x v="0"/>
   </r>
   <r>
@@ -2231,15 +2393,15 @@
   <r>
     <n v="5"/>
     <s v="LEG2_LYNX"/>
-    <n v="-1.0000000000000071"/>
-    <n v="-0.20000000000000107"/>
-    <n v="23"/>
-    <n v="14"/>
+    <n v="8.0999999999999925"/>
+    <n v="1.619999999999999"/>
+    <n v="24"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="9"/>
-    <n v="60.869565217391312"/>
-    <n v="-4.3478260869565528E-2"/>
-    <n v="-8.6956521739130904E-3"/>
+    <n v="62.5"/>
+    <n v="0.33749999999999969"/>
+    <n v="6.7499999999999963E-2"/>
     <x v="2"/>
   </r>
   <r>
@@ -2273,15 +2435,15 @@
   <r>
     <n v="8"/>
     <s v="LEG1_PIN"/>
-    <n v="4.9000000000000004"/>
-    <n v="0.98"/>
-    <n v="20"/>
-    <n v="9"/>
+    <n v="5.8000000000000007"/>
+    <n v="1.1599999999999999"/>
+    <n v="21"/>
+    <n v="10"/>
     <n v="1"/>
     <n v="10"/>
-    <n v="45"/>
-    <n v="0.24500000000000002"/>
-    <n v="4.9000000000000002E-2"/>
+    <n v="47.619047619047613"/>
+    <n v="0.27619047619047621"/>
+    <n v="5.5238095238095232E-2"/>
     <x v="2"/>
   </r>
   <r>
@@ -2315,15 +2477,15 @@
   <r>
     <n v="13"/>
     <s v="PEG18_BLAZE"/>
-    <n v="-40.799999999999997"/>
-    <n v="-8.16"/>
-    <n v="15"/>
-    <n v="6"/>
+    <n v="-39.199999999999996"/>
+    <n v="-7.84"/>
+    <n v="16"/>
+    <n v="7"/>
     <n v="1"/>
     <n v="8"/>
-    <n v="40"/>
-    <n v="-2.7199999999999998"/>
-    <n v="-0.54400000000000004"/>
+    <n v="43.75"/>
+    <n v="-2.4499999999999997"/>
+    <n v="-0.49"/>
     <x v="0"/>
   </r>
   <r>
@@ -2342,34 +2504,62 @@
   </r>
   <r>
     <n v="10"/>
+    <s v="LEG1_BIBI2"/>
+    <n v="14.5"/>
+    <n v="2.9000000000000008"/>
+    <n v="13"/>
+    <n v="7"/>
+    <n v="0"/>
+    <n v="6"/>
+    <n v="53.846153846153847"/>
+    <n v="1.1153846153846154"/>
+    <n v="0.22307692307692314"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="14"/>
     <s v="WEG4_PUPPY"/>
-    <n v="18.3"/>
-    <n v="3.6599999999999997"/>
-    <n v="11"/>
+    <n v="10.4"/>
+    <n v="2.0799999999999996"/>
+    <n v="12"/>
     <n v="7"/>
     <n v="1"/>
-    <n v="3"/>
-    <n v="63.636363636363633"/>
-    <n v="1.6636363636363638"/>
-    <n v="0.3327272727272727"/>
+    <n v="4"/>
+    <n v="58.333333333333336"/>
+    <n v="0.8666666666666667"/>
+    <n v="0.17333333333333331"/>
     <x v="1"/>
   </r>
   <r>
-    <n v="14"/>
-    <s v="LEG1_BIBI2"/>
-    <n v="14.7"/>
-    <n v="2.9400000000000008"/>
-    <n v="11"/>
-    <n v="6"/>
+    <n v="15"/>
+    <s v="LEG2_LOGAN"/>
+    <n v="6.3999999999999986"/>
+    <n v="1.2799999999999996"/>
+    <n v="9"/>
+    <n v="8"/>
     <n v="0"/>
-    <n v="5"/>
-    <n v="54.54545454545454"/>
-    <n v="1.3363636363636362"/>
-    <n v="0.26727272727272733"/>
+    <n v="1"/>
+    <n v="88.888888888888886"/>
+    <n v="0.71111111111111092"/>
+    <n v="0.14222222222222217"/>
     <x v="2"/>
   </r>
   <r>
-    <n v="15"/>
+    <n v="17"/>
+    <s v="SEG1_LITE"/>
+    <n v="10.799999999999997"/>
+    <n v="2.1599999999999997"/>
+    <n v="9"/>
+    <n v="6"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="66.666666666666657"/>
+    <n v="1.1999999999999997"/>
+    <n v="0.23999999999999996"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="16"/>
     <s v="LEG1_CC2"/>
     <n v="-8.8999999999999986"/>
     <n v="-1.7799999999999998"/>
@@ -2383,7 +2573,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="17"/>
+    <n v="19"/>
     <s v="UEG6_VULTURE"/>
     <n v="-9.6999999999999993"/>
     <n v="-1.9400000000000002"/>
@@ -2397,7 +2587,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="16"/>
+    <n v="18"/>
     <s v="PEG4_U3"/>
     <n v="1.1999999999999993"/>
     <n v="0.23999999999999988"/>
@@ -2411,7 +2601,35 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="19"/>
+    <n v="20"/>
+    <s v="PEG14_RENEGADE"/>
+    <n v="20.5"/>
+    <n v="4.1000000000000005"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="62.5"/>
+    <n v="2.5625"/>
+    <n v="0.51250000000000007"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <s v="PEG19_ANUBARAK"/>
+    <n v="-10.4"/>
+    <n v="-2.08"/>
+    <n v="8"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="37.5"/>
+    <n v="-1.3"/>
+    <n v="-0.26"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="22"/>
     <s v="PEG18_UTER2"/>
     <n v="-13"/>
     <n v="-2.6000000000000005"/>
@@ -2425,63 +2643,21 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="18"/>
-    <s v="PEG14_RENEGADE"/>
-    <n v="19.8"/>
-    <n v="3.9600000000000004"/>
-    <n v="7"/>
+    <n v="23"/>
+    <s v="UEG9_GRAVY2"/>
+    <n v="-1.9999999999999982"/>
+    <n v="-0.39999999999999947"/>
+    <n v="6"/>
+    <n v="2"/>
+    <n v="0"/>
     <n v="4"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="57.142857142857139"/>
-    <n v="2.8285714285714287"/>
-    <n v="0.56571428571428573"/>
-    <x v="0"/>
+    <n v="33.333333333333329"/>
+    <n v="-0.33333333333333304"/>
+    <n v="-6.6666666666666582E-2"/>
+    <x v="4"/>
   </r>
   <r>
-    <n v="20"/>
-    <s v="LEG2_LOGAN"/>
-    <n v="0.59999999999999853"/>
-    <n v="0.11999999999999961"/>
-    <n v="7"/>
-    <n v="6"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="85.714285714285708"/>
-    <n v="8.5714285714285507E-2"/>
-    <n v="1.7142857142857088E-2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="21"/>
-    <s v="PEG19_ANUBARAK"/>
-    <n v="-15.3"/>
-    <n v="-3.06"/>
-    <n v="7"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="28.571428571428569"/>
-    <n v="-2.1857142857142859"/>
-    <n v="-0.43714285714285717"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="22"/>
-    <s v="SEG1_LITE"/>
-    <n v="15.999999999999998"/>
-    <n v="3.1999999999999997"/>
-    <n v="7"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="71.428571428571431"/>
-    <n v="2.2857142857142856"/>
-    <n v="0.45714285714285713"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="23"/>
+    <n v="24"/>
     <s v="SEG3_FORCE"/>
     <n v="1.9000000000000004"/>
     <n v="0.37999999999999989"/>
@@ -2495,7 +2671,7 @@
     <x v="5"/>
   </r>
   <r>
-    <n v="24"/>
+    <n v="25"/>
     <s v="UEG4_PELICAN"/>
     <n v="-2.9000000000000004"/>
     <n v="-0.58000000000000007"/>
@@ -2509,7 +2685,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="25"/>
+    <n v="26"/>
     <s v="PEG18_UTER"/>
     <n v="-6.2"/>
     <n v="-1.24"/>
@@ -2523,7 +2699,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="26"/>
+    <n v="29"/>
     <s v="LEG1_IRONANNY2"/>
     <n v="-7.5"/>
     <n v="-1.5"/>
@@ -2537,7 +2713,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="29"/>
+    <n v="27"/>
     <s v="PEG18_DIABLO2"/>
     <n v="-9.1"/>
     <n v="-1.82"/>
@@ -2551,7 +2727,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="27"/>
+    <n v="28"/>
     <s v="PEG26_UNKNOWN"/>
     <n v="-7.5"/>
     <n v="-1.5"/>
@@ -2565,7 +2741,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="28"/>
+    <n v="35"/>
     <s v="LEG2_DRG"/>
     <n v="-12"/>
     <n v="-2.4"/>
@@ -2579,21 +2755,35 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="35"/>
-    <s v="UEG9_GRAVY2"/>
-    <n v="-12.599999999999998"/>
-    <n v="-2.5199999999999996"/>
+    <n v="36"/>
+    <s v="UEG6_SHERIFF"/>
+    <n v="13.4"/>
+    <n v="2.6799999999999997"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="60"/>
+    <n v="2.68"/>
+    <n v="0.53599999999999992"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <s v="VEG1_MOON"/>
+    <n v="-18"/>
+    <n v="-3.6"/>
     <n v="5"/>
     <n v="1"/>
     <n v="0"/>
     <n v="4"/>
     <n v="20"/>
-    <n v="-2.5199999999999996"/>
-    <n v="-0.50399999999999989"/>
-    <x v="4"/>
+    <n v="-3.6"/>
+    <n v="-0.72"/>
+    <x v="3"/>
   </r>
   <r>
-    <n v="36"/>
+    <n v="38"/>
     <s v="UEG7_PIGEON"/>
     <n v="-3.0999999999999996"/>
     <n v="-0.61999999999999988"/>
@@ -2607,7 +2797,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="37"/>
+    <n v="39"/>
     <s v="LEG1_IGOGOSHA2"/>
     <n v="11.899999999999999"/>
     <n v="2.38"/>
@@ -2621,21 +2811,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="38"/>
-    <s v="UEG6_SHERIFF"/>
-    <n v="12.1"/>
-    <n v="2.42"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="50"/>
-    <n v="3.0249999999999999"/>
-    <n v="0.60499999999999998"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="39"/>
+    <n v="30"/>
     <s v="LEG2_ALKASH"/>
     <n v="-42.900000000000006"/>
     <n v="-8.58"/>
@@ -2649,7 +2825,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="30"/>
+    <n v="31"/>
     <s v="UEG7_CELEBRITY"/>
     <n v="-10.199999999999999"/>
     <n v="-2.04"/>
@@ -2663,35 +2839,49 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="31"/>
+    <n v="32"/>
     <s v="LEG1_LAKSAe"/>
-    <n v="6"/>
-    <n v="1.2"/>
-    <n v="3"/>
-    <n v="3"/>
+    <n v="13.9"/>
+    <n v="2.7800000000000002"/>
+    <n v="4"/>
+    <n v="4"/>
     <n v="0"/>
     <n v="0"/>
     <n v="100"/>
-    <n v="2"/>
-    <n v="0.39999999999999997"/>
+    <n v="3.4750000000000001"/>
+    <n v="0.69500000000000006"/>
     <x v="2"/>
   </r>
   <r>
-    <n v="32"/>
+    <n v="33"/>
     <s v="UEG8_SOLDIER"/>
-    <n v="-1.7000000000000002"/>
-    <n v="-0.34"/>
+    <n v="6.7"/>
+    <n v="1.34"/>
+    <n v="4"/>
     <n v="3"/>
-    <n v="2"/>
     <n v="0"/>
     <n v="1"/>
-    <n v="66.666666666666657"/>
-    <n v="-0.56666666666666676"/>
-    <n v="-0.11333333333333334"/>
+    <n v="75"/>
+    <n v="1.675"/>
+    <n v="0.33500000000000002"/>
     <x v="4"/>
   </r>
   <r>
-    <n v="33"/>
+    <n v="34"/>
+    <s v="UEG7_CANNIBAL"/>
+    <n v="9.6"/>
+    <n v="1.92"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="75"/>
+    <n v="2.4"/>
+    <n v="0.48"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="40"/>
     <s v="LEG2_HOTS"/>
     <n v="-13.9"/>
     <n v="-2.78"/>
@@ -2705,7 +2895,63 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="34"/>
+    <n v="41"/>
+    <s v="WEG7_PARADOX"/>
+    <n v="8.1"/>
+    <n v="1.62"/>
+    <n v="3"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="2.6999999999999997"/>
+    <n v="0.54"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="42"/>
+    <s v="UEG7_LOVERGOOSE"/>
+    <n v="4.7"/>
+    <n v="0.94000000000000006"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="66.666666666666657"/>
+    <n v="1.5666666666666667"/>
+    <n v="0.31333333333333335"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="43"/>
+    <s v="PEG18_ANDUIN"/>
+    <n v="-2.7"/>
+    <n v="-0.54"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="33.333333333333329"/>
+    <n v="-0.9"/>
+    <n v="-0.18000000000000002"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="44"/>
+    <s v="VEG1_EARTH"/>
+    <n v="-6.4"/>
+    <n v="-1.28"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="33.333333333333329"/>
+    <n v="-2.1333333333333333"/>
+    <n v="-0.42666666666666669"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="45"/>
     <s v="UEG7_ADVENTURE"/>
     <n v="1.0000000000000002"/>
     <n v="0.2"/>
@@ -2719,7 +2965,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="40"/>
+    <n v="46"/>
     <s v="PEG13_DWDDCr"/>
     <n v="1"/>
     <n v="0.2"/>
@@ -2733,7 +2979,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="41"/>
+    <n v="47"/>
     <s v="PEG14_RANGER"/>
     <n v="-1.9000000000000001"/>
     <n v="-0.38"/>
@@ -2747,7 +2993,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="42"/>
+    <n v="48"/>
     <s v="UEG4_FALCON"/>
     <n v="-12"/>
     <n v="-2.4"/>
@@ -2761,77 +3007,21 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="43"/>
-    <s v="VEG1_MOON"/>
-    <n v="-14.8"/>
-    <n v="-2.96"/>
+    <n v="49"/>
+    <s v="UEG7_CARRIER"/>
+    <n v="-3.3"/>
+    <n v="-0.66"/>
     <n v="2"/>
     <n v="0"/>
     <n v="0"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="-7.4"/>
-    <n v="-1.48"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="44"/>
-    <s v="WEG7_PARADOX"/>
-    <n v="6.1"/>
-    <n v="1.22"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="3.05"/>
-    <n v="0.61"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="45"/>
-    <s v="UEG7_CANNIBAL"/>
-    <n v="2.5"/>
-    <n v="0.5"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="1.25"/>
-    <n v="0.25"/>
+    <n v="-1.65"/>
+    <n v="-0.33"/>
     <x v="4"/>
   </r>
   <r>
-    <n v="46"/>
-    <s v="UEG7_LOVERGOOSE"/>
-    <n v="0.3"/>
-    <n v="6.0000000000000005E-2"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
     <n v="50"/>
-    <n v="0.15"/>
-    <n v="3.0000000000000002E-2"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="47"/>
-    <s v="PEG18_ANDUIN"/>
-    <n v="-1.3"/>
-    <n v="-0.26"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-1.3"/>
-    <n v="-0.26"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="48"/>
     <s v="LEG1_PHOGA"/>
     <n v="-6"/>
     <n v="-1.2"/>
@@ -2845,7 +3035,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="49"/>
+    <n v="51"/>
     <s v="LEG1_OKROSHKA"/>
     <n v="-1.6"/>
     <n v="-0.32"/>
@@ -2859,21 +3049,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="50"/>
-    <s v="UEG7_CARRIER"/>
-    <n v="-1.3"/>
-    <n v="-0.26"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-1.3"/>
-    <n v="-0.26"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="51"/>
+    <n v="52"/>
     <s v="UEG4_PELICAN2"/>
     <n v="-11.4"/>
     <n v="-2.2800000000000002"/>
@@ -2887,7 +3063,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="52"/>
+    <n v="53"/>
     <s v="UEG9_BIRDWATCHER2"/>
     <n v="-19.5"/>
     <n v="-3.9"/>
@@ -2901,60 +3077,32 @@
     <x v="4"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="6"/>
+    <n v="54"/>
+    <s v="UEG7_DETECTIVE"/>
+    <n v="2"/>
+    <n v="0.4"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="2"/>
+    <n v="0.4"/>
+    <x v="4"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="6"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="6"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="6"/>
+    <n v="55"/>
+    <s v="WEG4_DOG"/>
+    <n v="5.2"/>
+    <n v="1.04"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="5.2"/>
+    <n v="1.04"/>
+    <x v="1"/>
   </r>
   <r>
     <m/>
@@ -3240,7 +3388,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{08A3FD17-FFE6-464D-A72F-02ADC3CE221B}" name="Сводная таблица3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{08A3FD17-FFE6-464D-A72F-02ADC3CE221B}" name="Сводная таблица3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:G10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -3843,7 +3991,7 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3874,22 +4022,22 @@
         <v>116</v>
       </c>
       <c r="B4" s="12">
-        <v>-17.000000000000021</v>
+        <v>6.4999999999999858</v>
       </c>
       <c r="C4" s="12">
-        <v>-3.3999999999999986</v>
+        <v>1.3000000000000025</v>
       </c>
       <c r="D4" s="12">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E4" s="12">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F4" s="12">
         <v>1</v>
       </c>
       <c r="G4" s="12">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3897,22 +4045,22 @@
         <v>117</v>
       </c>
       <c r="B5" s="12">
-        <v>70.199999999999989</v>
+        <v>85.5</v>
       </c>
       <c r="C5" s="12">
-        <v>14.040000000000003</v>
+        <v>17.100000000000005</v>
       </c>
       <c r="D5" s="12">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="E5" s="12">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F5" s="12">
         <v>5</v>
       </c>
       <c r="G5" s="12">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3920,22 +4068,22 @@
         <v>118</v>
       </c>
       <c r="B6" s="12">
-        <v>17.899999999999999</v>
+        <v>12.699999999999998</v>
       </c>
       <c r="C6" s="12">
-        <v>3.5799999999999996</v>
+        <v>2.5399999999999996</v>
       </c>
       <c r="D6" s="12">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="12">
         <v>0</v>
       </c>
       <c r="G6" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -3943,22 +4091,22 @@
         <v>119</v>
       </c>
       <c r="B7" s="12">
-        <v>-55.599999999999994</v>
+        <v>-23.799999999999994</v>
       </c>
       <c r="C7" s="12">
-        <v>-11.120000000000001</v>
+        <v>-4.7600000000000007</v>
       </c>
       <c r="D7" s="12">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E7" s="12">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F7" s="12">
         <v>2</v>
       </c>
       <c r="G7" s="12">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3966,22 +4114,22 @@
         <v>120</v>
       </c>
       <c r="B8" s="12">
-        <v>-37.5</v>
+        <v>-47.1</v>
       </c>
       <c r="C8" s="12">
-        <v>-7.4999999999999991</v>
+        <v>-9.4199999999999982</v>
       </c>
       <c r="D8" s="12">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E8" s="12">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8" s="12">
         <v>0</v>
       </c>
       <c r="G8" s="12">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3989,22 +4137,22 @@
         <v>121</v>
       </c>
       <c r="B9" s="12">
-        <v>74.400000000000006</v>
+        <v>73</v>
       </c>
       <c r="C9" s="12">
-        <v>14.880000000000003</v>
+        <v>14.600000000000001</v>
       </c>
       <c r="D9" s="12">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E9" s="12">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F9" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="12">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4012,22 +4160,22 @@
         <v>114</v>
       </c>
       <c r="B10" s="12">
-        <v>52.399999999999977</v>
+        <v>106.79999999999998</v>
       </c>
       <c r="C10" s="12">
-        <v>10.480000000000008</v>
+        <v>21.360000000000007</v>
       </c>
       <c r="D10" s="12">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="E10" s="12">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="F10" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="12">
-        <v>225</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -4037,13 +4185,375 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8DFA0FD-4A38-4441-810F-67EAE4BA7EB9}">
-  <dimension ref="A2:X16"/>
+  <dimension ref="A1:DQ18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="24" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+      <c r="N1">
+        <v>13</v>
+      </c>
+      <c r="O1">
+        <v>14</v>
+      </c>
+      <c r="P1">
+        <v>15</v>
+      </c>
+      <c r="Q1">
+        <v>16</v>
+      </c>
+      <c r="R1">
+        <v>17</v>
+      </c>
+      <c r="S1">
+        <v>18</v>
+      </c>
+      <c r="T1">
+        <v>19</v>
+      </c>
+      <c r="U1">
+        <v>20</v>
+      </c>
+      <c r="V1">
+        <v>21</v>
+      </c>
+      <c r="W1">
+        <v>22</v>
+      </c>
+      <c r="X1">
+        <v>23</v>
+      </c>
+      <c r="Y1">
+        <v>24</v>
+      </c>
+      <c r="Z1">
+        <v>25</v>
+      </c>
+      <c r="AA1">
+        <v>26</v>
+      </c>
+      <c r="AB1">
+        <v>27</v>
+      </c>
+      <c r="AC1">
+        <v>28</v>
+      </c>
+      <c r="AD1">
+        <v>29</v>
+      </c>
+      <c r="AE1">
+        <v>30</v>
+      </c>
+      <c r="AF1">
+        <v>31</v>
+      </c>
+      <c r="AG1">
+        <v>32</v>
+      </c>
+      <c r="AH1">
+        <v>33</v>
+      </c>
+      <c r="AI1">
+        <v>34</v>
+      </c>
+      <c r="AJ1">
+        <v>35</v>
+      </c>
+      <c r="AK1">
+        <v>36</v>
+      </c>
+      <c r="AL1">
+        <v>37</v>
+      </c>
+      <c r="AM1">
+        <v>38</v>
+      </c>
+      <c r="AN1">
+        <v>39</v>
+      </c>
+      <c r="AO1">
+        <v>40</v>
+      </c>
+      <c r="AP1">
+        <v>41</v>
+      </c>
+      <c r="AQ1">
+        <v>42</v>
+      </c>
+      <c r="AR1">
+        <v>43</v>
+      </c>
+      <c r="AS1">
+        <v>44</v>
+      </c>
+      <c r="AT1">
+        <v>45</v>
+      </c>
+      <c r="AU1">
+        <v>46</v>
+      </c>
+      <c r="AV1">
+        <v>47</v>
+      </c>
+      <c r="AW1">
+        <v>48</v>
+      </c>
+      <c r="AX1">
+        <v>49</v>
+      </c>
+      <c r="AY1">
+        <v>50</v>
+      </c>
+      <c r="AZ1">
+        <v>51</v>
+      </c>
+      <c r="BA1">
+        <v>52</v>
+      </c>
+      <c r="BB1">
+        <v>53</v>
+      </c>
+      <c r="BC1">
+        <v>54</v>
+      </c>
+      <c r="BD1">
+        <v>55</v>
+      </c>
+      <c r="BE1">
+        <v>56</v>
+      </c>
+      <c r="BF1">
+        <v>57</v>
+      </c>
+      <c r="BG1">
+        <v>58</v>
+      </c>
+      <c r="BH1">
+        <v>59</v>
+      </c>
+      <c r="BI1">
+        <v>60</v>
+      </c>
+      <c r="BJ1">
+        <v>61</v>
+      </c>
+      <c r="BK1">
+        <v>62</v>
+      </c>
+      <c r="BL1">
+        <v>63</v>
+      </c>
+      <c r="BM1">
+        <v>64</v>
+      </c>
+      <c r="BN1">
+        <v>65</v>
+      </c>
+      <c r="BO1">
+        <v>66</v>
+      </c>
+      <c r="BP1">
+        <v>67</v>
+      </c>
+      <c r="BQ1">
+        <v>68</v>
+      </c>
+      <c r="BR1">
+        <v>69</v>
+      </c>
+      <c r="BS1">
+        <v>70</v>
+      </c>
+      <c r="BT1">
+        <v>71</v>
+      </c>
+      <c r="BU1">
+        <v>72</v>
+      </c>
+      <c r="BV1">
+        <v>73</v>
+      </c>
+      <c r="BW1">
+        <v>74</v>
+      </c>
+      <c r="BX1">
+        <v>75</v>
+      </c>
+      <c r="BY1">
+        <v>76</v>
+      </c>
+      <c r="BZ1">
+        <v>77</v>
+      </c>
+      <c r="CA1">
+        <v>78</v>
+      </c>
+      <c r="CB1">
+        <v>79</v>
+      </c>
+      <c r="CC1">
+        <v>80</v>
+      </c>
+      <c r="CD1">
+        <v>81</v>
+      </c>
+      <c r="CE1">
+        <v>82</v>
+      </c>
+      <c r="CF1">
+        <v>83</v>
+      </c>
+      <c r="CG1">
+        <v>84</v>
+      </c>
+      <c r="CH1">
+        <v>85</v>
+      </c>
+      <c r="CI1">
+        <v>86</v>
+      </c>
+      <c r="CJ1">
+        <v>87</v>
+      </c>
+      <c r="CK1">
+        <v>88</v>
+      </c>
+      <c r="CL1">
+        <v>89</v>
+      </c>
+      <c r="CM1">
+        <v>90</v>
+      </c>
+      <c r="CN1">
+        <v>91</v>
+      </c>
+      <c r="CO1">
+        <v>92</v>
+      </c>
+      <c r="CP1">
+        <v>93</v>
+      </c>
+      <c r="CQ1">
+        <v>94</v>
+      </c>
+      <c r="CR1">
+        <v>95</v>
+      </c>
+      <c r="CS1">
+        <v>96</v>
+      </c>
+      <c r="CT1">
+        <v>97</v>
+      </c>
+      <c r="CU1">
+        <v>98</v>
+      </c>
+      <c r="CV1">
+        <v>99</v>
+      </c>
+      <c r="CW1">
+        <v>100</v>
+      </c>
+      <c r="CX1">
+        <v>101</v>
+      </c>
+      <c r="CY1">
+        <v>102</v>
+      </c>
+      <c r="CZ1">
+        <v>103</v>
+      </c>
+      <c r="DA1">
+        <v>104</v>
+      </c>
+      <c r="DB1">
+        <v>105</v>
+      </c>
+      <c r="DC1">
+        <v>106</v>
+      </c>
+      <c r="DD1">
+        <v>107</v>
+      </c>
+      <c r="DE1">
+        <v>108</v>
+      </c>
+      <c r="DF1">
+        <v>109</v>
+      </c>
+      <c r="DG1">
+        <v>110</v>
+      </c>
+      <c r="DH1">
+        <v>111</v>
+      </c>
+      <c r="DI1">
+        <v>112</v>
+      </c>
+      <c r="DJ1">
+        <v>113</v>
+      </c>
+      <c r="DK1">
+        <v>114</v>
+      </c>
+      <c r="DL1">
+        <v>115</v>
+      </c>
+      <c r="DM1">
+        <v>116</v>
+      </c>
+      <c r="DN1">
+        <v>117</v>
+      </c>
+      <c r="DO1">
+        <v>118</v>
+      </c>
+      <c r="DP1">
+        <v>119</v>
+      </c>
+      <c r="DQ1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:121" x14ac:dyDescent="0.25">
       <c r="B2" s="16">
         <v>46285</v>
       </c>
@@ -4065,7 +4575,9 @@
       <c r="H2" s="16">
         <v>46294</v>
       </c>
-      <c r="I2" s="16"/>
+      <c r="I2" s="16">
+        <v>46295</v>
+      </c>
       <c r="J2" s="16"/>
       <c r="K2" s="16"/>
       <c r="L2" s="16"/>
@@ -4082,7 +4594,7 @@
       <c r="W2" s="16"/>
       <c r="X2" s="16"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>116</v>
       </c>
@@ -4107,8 +4619,11 @@
       <c r="H3">
         <v>-17.000000000000021</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <v>6.4999999999999858</v>
+      </c>
+    </row>
+    <row r="4" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>117</v>
       </c>
@@ -4133,8 +4648,11 @@
       <c r="H4">
         <v>70.199999999999989</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -4159,8 +4677,11 @@
       <c r="H5">
         <v>17.899999999999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <v>12.699999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>119</v>
       </c>
@@ -4185,8 +4706,11 @@
       <c r="H6">
         <v>-55.599999999999994</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <v>-23.799999999999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>120</v>
       </c>
@@ -4211,8 +4735,11 @@
       <c r="H7">
         <v>-37.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="I7">
+        <v>-47.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>121</v>
       </c>
@@ -4237,242 +4764,356 @@
       <c r="H8">
         <v>74.400000000000006</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B10" s="16">
+      <c r="I8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B9">
+        <f>SUM(B3:B8)</f>
+        <v>6.8999999999999915</v>
+      </c>
+      <c r="C9">
+        <f t="shared" ref="C9:I9" si="0">SUM(C3:C8)</f>
+        <v>5.7000000000000028</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>87.699999999999989</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>134.99999999999997</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>156.39999999999998</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>144</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>52.399999999999977</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>106.79999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="B11" s="16">
         <f>B2</f>
         <v>46285</v>
       </c>
-      <c r="C10" s="16">
-        <f t="shared" ref="C10:H10" si="0">C2</f>
+      <c r="C11" s="16">
+        <f t="shared" ref="C11:I11" si="1">C2</f>
         <v>46286</v>
       </c>
-      <c r="D10" s="16">
-        <f t="shared" si="0"/>
+      <c r="D11" s="16">
+        <f t="shared" si="1"/>
         <v>46287</v>
       </c>
-      <c r="E10" s="16">
-        <f t="shared" si="0"/>
+      <c r="E11" s="16">
+        <f t="shared" si="1"/>
         <v>46288</v>
       </c>
-      <c r="F10" s="16">
-        <f t="shared" si="0"/>
+      <c r="F11" s="16">
+        <f t="shared" si="1"/>
         <v>46290</v>
       </c>
-      <c r="G10" s="16">
-        <f t="shared" si="0"/>
+      <c r="G11" s="16">
+        <f t="shared" si="1"/>
         <v>46293</v>
       </c>
-      <c r="H10" s="16">
-        <f t="shared" si="0"/>
+      <c r="H11" s="16">
+        <f t="shared" si="1"/>
         <v>46294</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="I11" s="16">
+        <f t="shared" si="1"/>
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="12" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>116</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <f>B3</f>
         <v>-20.100000000000001</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <f>C3-B3</f>
         <v>-19.799999999999997</v>
       </c>
-      <c r="D11">
-        <f t="shared" ref="D11:H11" si="1">D3-C3</f>
+      <c r="D12">
+        <f t="shared" ref="D12:I12" si="2">D3-C3</f>
         <v>17.799999999999997</v>
       </c>
-      <c r="E11">
-        <f t="shared" si="1"/>
+      <c r="E12">
+        <f t="shared" si="2"/>
         <v>21.200000000000003</v>
       </c>
-      <c r="F11">
-        <f t="shared" si="1"/>
+      <c r="F12">
+        <f t="shared" si="2"/>
         <v>29.300000000000011</v>
       </c>
-      <c r="G11">
-        <f t="shared" si="1"/>
+      <c r="G12">
+        <f t="shared" si="2"/>
         <v>13.59999999999998</v>
       </c>
-      <c r="H11">
-        <f t="shared" si="1"/>
+      <c r="H12">
+        <f t="shared" si="2"/>
         <v>-59.000000000000014</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="I12">
+        <f t="shared" si="2"/>
+        <v>23.500000000000007</v>
+      </c>
+    </row>
+    <row r="13" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>117</v>
       </c>
-      <c r="B12">
-        <f t="shared" ref="B12:B16" si="2">B4</f>
+      <c r="B13">
+        <f t="shared" ref="B13:B17" si="3">B4</f>
         <v>19.7</v>
       </c>
-      <c r="C12">
-        <f t="shared" ref="C12:H16" si="3">C4-B4</f>
+      <c r="C13">
+        <f t="shared" ref="C13:I17" si="4">C4-B4</f>
         <v>31.000000000000004</v>
       </c>
-      <c r="D12">
+      <c r="D13">
+        <f t="shared" si="4"/>
+        <v>17.599999999999994</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="4"/>
+        <v>14.700000000000003</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="4"/>
+        <v>0.19999999999998863</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="4"/>
+        <v>2.5</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="4"/>
+        <v>-15.5</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="4"/>
+        <v>15.300000000000011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14">
         <f t="shared" si="3"/>
-        <v>17.599999999999994</v>
-      </c>
-      <c r="E12">
+        <v>1.9</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="4"/>
+        <v>2.2000000000000011</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="4"/>
+        <v>2.1999999999999957</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="4"/>
+        <v>7.7000000000000028</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="4"/>
+        <v>-10.100000000000001</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="4"/>
+        <v>-5.2000000000000011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15">
         <f t="shared" si="3"/>
-        <v>14.700000000000003</v>
-      </c>
-      <c r="F12">
+        <v>-21</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="4"/>
+        <v>-20</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="4"/>
+        <v>39.6</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="4"/>
+        <v>-0.5</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="4"/>
+        <v>-13.299999999999997</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="4"/>
+        <v>-36.300000000000004</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="4"/>
+        <v>-4.0999999999999943</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="4"/>
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16">
         <f t="shared" si="3"/>
-        <v>0.19999999999998863</v>
-      </c>
-      <c r="G12">
+        <v>-18.100000000000001</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="4"/>
+        <v>-4.5999999999999979</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="4"/>
+        <v>-14.799999999999997</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="4"/>
+        <v>-9.6000000000000014</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="3"/>
-        <v>-15.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B13">
-        <f t="shared" si="2"/>
-        <v>1.9</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="3"/>
-        <v>2.2000000000000011</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="3"/>
-        <v>2.1999999999999957</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="3"/>
-        <v>7.7000000000000028</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="3"/>
-        <v>-10.100000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>119</v>
-      </c>
-      <c r="B14">
-        <f t="shared" si="2"/>
-        <v>-21</v>
-      </c>
-      <c r="C14">
-        <f t="shared" si="3"/>
-        <v>-20</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="3"/>
-        <v>39.6</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="3"/>
-        <v>-0.5</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="3"/>
-        <v>-13.299999999999997</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="3"/>
-        <v>-36.300000000000004</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="3"/>
-        <v>-4.0999999999999943</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B15">
-        <f t="shared" si="2"/>
-        <v>-18.100000000000001</v>
-      </c>
-      <c r="C15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="3"/>
-        <v>-4.5999999999999979</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="3"/>
-        <v>-14.799999999999997</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>121</v>
-      </c>
-      <c r="B16">
-        <f t="shared" si="2"/>
         <v>44.5</v>
       </c>
-      <c r="C16">
-        <f t="shared" si="3"/>
+      <c r="C17">
+        <f t="shared" si="4"/>
         <v>-0.39999999999999858</v>
       </c>
-      <c r="D16">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="3"/>
+      <c r="D17">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="4"/>
         <v>14.299999999999997</v>
       </c>
-      <c r="F16">
-        <f t="shared" si="3"/>
+      <c r="F17">
+        <f t="shared" si="4"/>
         <v>3.0000000000000071</v>
       </c>
-      <c r="G16">
-        <f t="shared" si="3"/>
+      <c r="G17">
+        <f t="shared" si="4"/>
         <v>14.899999999999991</v>
       </c>
-      <c r="H16">
-        <f t="shared" si="3"/>
+      <c r="H17">
+        <f t="shared" si="4"/>
         <v>-2.8999999999999915</v>
       </c>
+      <c r="I17">
+        <f t="shared" si="4"/>
+        <v>-1.4000000000000057</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18">
+        <f>SUM(B12:B17)</f>
+        <v>6.8999999999999915</v>
+      </c>
+      <c r="C18">
+        <f t="shared" ref="C18" si="5">SUM(C12:C17)</f>
+        <v>-1.1999999999999922</v>
+      </c>
+      <c r="D18">
+        <f t="shared" ref="D18" si="6">SUM(D12:D17)</f>
+        <v>82</v>
+      </c>
+      <c r="E18">
+        <f t="shared" ref="E18" si="7">SUM(E12:E17)</f>
+        <v>47.300000000000011</v>
+      </c>
+      <c r="F18">
+        <f t="shared" ref="F18" si="8">SUM(F12:F17)</f>
+        <v>21.400000000000006</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ref="G18" si="9">SUM(G12:G17)</f>
+        <v>-12.400000000000027</v>
+      </c>
+      <c r="H18">
+        <f t="shared" ref="H18" si="10">SUM(H12:H17)</f>
+        <v>-91.600000000000009</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ref="I18" si="11">SUM(I12:I17)</f>
+        <v>54.400000000000013</v>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56BC7F9C-72F9-414E-BDDC-ADB9C988A492}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8FFDFC-F0D8-484F-BD9F-73CE26658A10}">
   <dimension ref="A1:Z75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4569,34 +5210,34 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>113.09999999999998</v>
+        <v>123.69999999999997</v>
       </c>
       <c r="D2">
-        <v>22.620000000000005</v>
+        <v>24.740000000000006</v>
       </c>
       <c r="E2">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" s="7">
         <f>IFERROR((F2/E2)*100,0)</f>
-        <v>67.796610169491515</v>
+        <v>68.75</v>
       </c>
       <c r="J2" s="10">
         <f>IFERROR(C2/E2,0)</f>
-        <v>1.9169491525423725</v>
+        <v>1.9328124999999996</v>
       </c>
       <c r="K2" s="10">
         <f>IFERROR(D2/E2,0)</f>
-        <v>0.38338983050847464</v>
+        <v>0.38656250000000009</v>
       </c>
       <c r="L2" s="10" t="str">
         <f>LEFT(B2,3)</f>
@@ -4604,19 +5245,19 @@
       </c>
       <c r="N2">
         <f t="shared" ref="N2:S2" si="0">C2+U2</f>
-        <v>113.09999999999998</v>
+        <v>123.69999999999997</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>22.620000000000005</v>
+        <v>24.740000000000006</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
@@ -4624,7 +5265,7 @@
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -4635,62 +5276,62 @@
         <v>56</v>
       </c>
       <c r="C3">
-        <v>50.000000000000007</v>
+        <v>49.300000000000004</v>
       </c>
       <c r="D3">
-        <v>10.000000000000002</v>
+        <v>9.8600000000000012</v>
       </c>
       <c r="E3">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" s="7">
         <f>IFERROR((F3/E3)*100,0)</f>
-        <v>60.465116279069761</v>
+        <v>59.574468085106382</v>
       </c>
       <c r="J3" s="10">
         <f>IFERROR(C3/E3,0)</f>
-        <v>1.1627906976744187</v>
+        <v>1.048936170212766</v>
       </c>
       <c r="K3" s="10">
         <f>IFERROR(D3/E3,0)</f>
-        <v>0.23255813953488377</v>
+        <v>0.20978723404255323</v>
       </c>
       <c r="L3" s="10" t="str">
         <f>LEFT(B3,3)</f>
         <v>WEG</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N64" si="1">C3+U3</f>
-        <v>50.000000000000007</v>
+        <f t="shared" ref="N3:N53" si="1">C3+U3</f>
+        <v>49.300000000000004</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O17" si="2">D3+V3</f>
-        <v>10.000000000000002</v>
+        <v>9.8600000000000012</v>
       </c>
       <c r="P3">
         <f t="shared" ref="P3:P17" si="3">E3+W3</f>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q17" si="4">F3+X3</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R17" si="5">G3+Y3</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S17" si="6">H3+Z3</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -4701,13 +5342,13 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>30.9</v>
+        <v>29.799999999999997</v>
       </c>
       <c r="D4">
-        <v>6.1800000000000006</v>
+        <v>5.9600000000000009</v>
       </c>
       <c r="E4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -4716,19 +5357,19 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I4" s="7">
         <f>IFERROR((F4/E4)*100,0)</f>
-        <v>50</v>
+        <v>48.717948717948715</v>
       </c>
       <c r="J4" s="10">
         <f>IFERROR(C4/E4,0)</f>
-        <v>0.81315789473684208</v>
+        <v>0.76410256410256405</v>
       </c>
       <c r="K4" s="10">
         <f>IFERROR(D4/E4,0)</f>
-        <v>0.16263157894736843</v>
+        <v>0.15282051282051284</v>
       </c>
       <c r="L4" s="10" t="str">
         <f>LEFT(B4,3)</f>
@@ -4736,15 +5377,15 @@
       </c>
       <c r="N4">
         <f t="shared" si="1"/>
-        <v>30.9</v>
+        <v>29.799999999999997</v>
       </c>
       <c r="O4">
         <f t="shared" si="2"/>
-        <v>6.1800000000000006</v>
+        <v>5.9600000000000009</v>
       </c>
       <c r="P4">
         <f t="shared" si="3"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q4">
         <f t="shared" si="4"/>
@@ -4756,7 +5397,7 @@
       </c>
       <c r="S4">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -4833,16 +5474,16 @@
         <v>60</v>
       </c>
       <c r="C6">
-        <v>-1.0000000000000071</v>
+        <v>8.0999999999999925</v>
       </c>
       <c r="D6">
-        <v>-0.20000000000000107</v>
+        <v>1.619999999999999</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -4852,15 +5493,15 @@
       </c>
       <c r="I6" s="7">
         <f>IFERROR((F6/E6)*100,0)</f>
-        <v>60.869565217391312</v>
+        <v>62.5</v>
       </c>
       <c r="J6" s="10">
         <f>IFERROR(C6/E6,0)</f>
-        <v>-4.3478260869565528E-2</v>
+        <v>0.33749999999999969</v>
       </c>
       <c r="K6" s="10">
         <f>IFERROR(D6/E6,0)</f>
-        <v>-8.6956521739130904E-3</v>
+        <v>6.7499999999999963E-2</v>
       </c>
       <c r="L6" s="10" t="str">
         <f>LEFT(B6,3)</f>
@@ -4868,19 +5509,19 @@
       </c>
       <c r="N6">
         <f t="shared" si="1"/>
-        <v>-1.0000000000000071</v>
+        <v>8.0999999999999925</v>
       </c>
       <c r="O6">
         <f t="shared" si="2"/>
-        <v>-0.20000000000000107</v>
+        <v>1.619999999999999</v>
       </c>
       <c r="P6">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q6">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R6">
         <f t="shared" si="5"/>
@@ -5031,16 +5672,16 @@
         <v>66</v>
       </c>
       <c r="C9">
-        <v>4.9000000000000004</v>
+        <v>5.8000000000000007</v>
       </c>
       <c r="D9">
-        <v>0.98</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -5050,15 +5691,15 @@
       </c>
       <c r="I9" s="7">
         <f>IFERROR((F9/E9)*100,0)</f>
-        <v>45</v>
+        <v>47.619047619047613</v>
       </c>
       <c r="J9" s="10">
         <f>IFERROR(C9/E9,0)</f>
-        <v>0.24500000000000002</v>
+        <v>0.27619047619047621</v>
       </c>
       <c r="K9" s="10">
         <f>IFERROR(D9/E9,0)</f>
-        <v>4.9000000000000002E-2</v>
+        <v>5.5238095238095232E-2</v>
       </c>
       <c r="L9" s="10" t="str">
         <f>LEFT(B9,3)</f>
@@ -5066,19 +5707,19 @@
       </c>
       <c r="N9">
         <f t="shared" si="1"/>
-        <v>4.9000000000000004</v>
+        <v>5.8000000000000007</v>
       </c>
       <c r="O9">
         <f t="shared" si="2"/>
-        <v>0.98</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P9">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q9">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <f t="shared" si="5"/>
@@ -5229,16 +5870,16 @@
         <v>59</v>
       </c>
       <c r="C12">
-        <v>-40.799999999999997</v>
+        <v>-39.199999999999996</v>
       </c>
       <c r="D12">
-        <v>-8.16</v>
+        <v>-7.84</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -5248,15 +5889,15 @@
       </c>
       <c r="I12" s="7">
         <f>IFERROR((F12/E12)*100,0)</f>
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="J12" s="10">
         <f>IFERROR(C12/E12,0)</f>
-        <v>-2.7199999999999998</v>
+        <v>-2.4499999999999997</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(D12/E12,0)</f>
-        <v>-0.54400000000000004</v>
+        <v>-0.49</v>
       </c>
       <c r="L12" s="10" t="str">
         <f>LEFT(B12,3)</f>
@@ -5264,19 +5905,19 @@
       </c>
       <c r="N12">
         <f t="shared" si="1"/>
-        <v>-40.799999999999997</v>
+        <v>-39.199999999999996</v>
       </c>
       <c r="O12">
         <f t="shared" si="2"/>
-        <v>-8.16</v>
+        <v>-7.84</v>
       </c>
       <c r="P12">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q12">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <f t="shared" si="5"/>
@@ -5358,53 +5999,53 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="C14">
-        <v>18.3</v>
+        <v>14.5</v>
       </c>
       <c r="D14">
-        <v>3.6599999999999997</v>
+        <v>2.9000000000000008</v>
       </c>
       <c r="E14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F14">
         <v>7</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I14" s="7">
         <f>IFERROR((F14/E14)*100,0)</f>
-        <v>63.636363636363633</v>
+        <v>53.846153846153847</v>
       </c>
       <c r="J14" s="10">
         <f>IFERROR(C14/E14,0)</f>
-        <v>1.6636363636363638</v>
+        <v>1.1153846153846154</v>
       </c>
       <c r="K14" s="10">
         <f>IFERROR(D14/E14,0)</f>
-        <v>0.3327272727272727</v>
+        <v>0.22307692307692314</v>
       </c>
       <c r="L14" s="10" t="str">
         <f>LEFT(B14,3)</f>
-        <v>WEG</v>
+        <v>LEG</v>
       </c>
       <c r="N14">
         <f t="shared" si="1"/>
-        <v>18.3</v>
+        <v>14.5</v>
       </c>
       <c r="O14">
         <f t="shared" si="2"/>
-        <v>3.6599999999999997</v>
+        <v>2.9000000000000008</v>
       </c>
       <c r="P14">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q14">
         <f t="shared" si="4"/>
@@ -5412,11 +6053,11 @@
       </c>
       <c r="R14">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
@@ -5424,65 +6065,65 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="C15">
-        <v>14.7</v>
+        <v>10.4</v>
       </c>
       <c r="D15">
-        <v>2.9400000000000008</v>
+        <v>2.0799999999999996</v>
       </c>
       <c r="E15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I15" s="7">
         <f>IFERROR((F15/E15)*100,0)</f>
-        <v>54.54545454545454</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="J15" s="10">
         <f>IFERROR(C15/E15,0)</f>
-        <v>1.3363636363636362</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="K15" s="10">
         <f>IFERROR(D15/E15,0)</f>
-        <v>0.26727272727272733</v>
+        <v>0.17333333333333331</v>
       </c>
       <c r="L15" s="10" t="str">
         <f>LEFT(B15,3)</f>
-        <v>LEG</v>
+        <v>WEG</v>
       </c>
       <c r="N15">
         <f t="shared" si="1"/>
-        <v>14.7</v>
+        <v>10.4</v>
       </c>
       <c r="O15">
         <f t="shared" si="2"/>
-        <v>2.9400000000000008</v>
+        <v>2.0799999999999996</v>
       </c>
       <c r="P15">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q15">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -5490,37 +6131,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C16">
-        <v>-8.8999999999999986</v>
+        <v>6.3999999999999986</v>
       </c>
       <c r="D16">
-        <v>-1.7799999999999998</v>
+        <v>1.2799999999999996</v>
       </c>
       <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="F16">
         <v>8</v>
       </c>
-      <c r="F16">
-        <v>4</v>
-      </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" s="7">
         <f>IFERROR((F16/E16)*100,0)</f>
-        <v>50</v>
+        <v>88.888888888888886</v>
       </c>
       <c r="J16" s="10">
         <f>IFERROR(C16/E16,0)</f>
-        <v>-1.1124999999999998</v>
+        <v>0.71111111111111092</v>
       </c>
       <c r="K16" s="10">
         <f>IFERROR(D16/E16,0)</f>
-        <v>-0.22249999999999998</v>
+        <v>0.14222222222222217</v>
       </c>
       <c r="L16" s="10" t="str">
         <f>LEFT(B16,3)</f>
@@ -5528,19 +6169,19 @@
       </c>
       <c r="N16">
         <f t="shared" si="1"/>
-        <v>-8.8999999999999986</v>
+        <v>6.3999999999999986</v>
       </c>
       <c r="O16">
         <f t="shared" si="2"/>
-        <v>-1.7799999999999998</v>
+        <v>1.2799999999999996</v>
       </c>
       <c r="P16">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <f t="shared" si="5"/>
@@ -5548,7 +6189,7 @@
       </c>
       <c r="S16">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -5556,57 +6197,57 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C17">
-        <v>-9.6999999999999993</v>
+        <v>10.799999999999997</v>
       </c>
       <c r="D17">
-        <v>-1.9400000000000002</v>
+        <v>2.1599999999999997</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17">
+        <v>6</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>3</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>5</v>
       </c>
       <c r="I17" s="7">
         <f>IFERROR((F17/E17)*100,0)</f>
-        <v>37.5</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J17" s="10">
         <f>IFERROR(C17/E17,0)</f>
-        <v>-1.2124999999999999</v>
+        <v>1.1999999999999997</v>
       </c>
       <c r="K17" s="10">
         <f>IFERROR(D17/E17,0)</f>
-        <v>-0.24250000000000002</v>
+        <v>0.23999999999999996</v>
       </c>
       <c r="L17" s="10" t="str">
         <f>LEFT(B17,3)</f>
-        <v>UEG</v>
+        <v>SEG</v>
       </c>
       <c r="N17">
         <f t="shared" si="1"/>
-        <v>-9.6999999999999993</v>
+        <v>10.799999999999997</v>
       </c>
       <c r="O17">
         <f t="shared" si="2"/>
-        <v>-1.9400000000000002</v>
+        <v>2.1599999999999997</v>
       </c>
       <c r="P17">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <f t="shared" si="5"/>
@@ -5614,7 +6255,7 @@
       </c>
       <c r="S17">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -5622,65 +6263,65 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="C18">
-        <v>1.1999999999999993</v>
+        <v>-8.8999999999999986</v>
       </c>
       <c r="D18">
-        <v>0.23999999999999988</v>
+        <v>-1.7799999999999998</v>
       </c>
       <c r="E18">
         <v>8</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I18" s="7">
         <f>IFERROR((F18/E18)*100,0)</f>
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J18" s="10">
         <f>IFERROR(C18/E18,0)</f>
-        <v>0.14999999999999991</v>
+        <v>-1.1124999999999998</v>
       </c>
       <c r="K18" s="10">
         <f>IFERROR(D18/E18,0)</f>
-        <v>2.9999999999999985E-2</v>
+        <v>-0.22249999999999998</v>
       </c>
       <c r="L18" s="10" t="str">
         <f>LEFT(B18,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N18">
         <f t="shared" si="1"/>
-        <v>1.1999999999999993</v>
+        <v>-8.8999999999999986</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:O65" si="7">D18+V18</f>
-        <v>0.23999999999999988</v>
+        <f t="shared" ref="O18:O53" si="7">D18+V18</f>
+        <v>-1.7799999999999998</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18:P65" si="8">E18+W18</f>
+        <f t="shared" ref="P18:P53" si="8">E18+W18</f>
         <v>8</v>
       </c>
       <c r="Q18">
-        <f t="shared" ref="Q18:Q65" si="9">F18+X18</f>
-        <v>5</v>
+        <f t="shared" ref="Q18:Q53" si="9">F18+X18</f>
+        <v>4</v>
       </c>
       <c r="R18">
         <f t="shared" ref="R18:R47" si="10">G18+Y18</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <f t="shared" ref="S18:S47" si="11">H18+Z18</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -5688,16 +6329,16 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="C19">
-        <v>-13</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="D19">
-        <v>-2.6000000000000005</v>
+        <v>-1.9400000000000002</v>
       </c>
       <c r="E19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19">
         <v>3</v>
@@ -5706,35 +6347,35 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7">
         <f>IFERROR((F19/E19)*100,0)</f>
-        <v>42.857142857142854</v>
+        <v>37.5</v>
       </c>
       <c r="J19" s="10">
         <f>IFERROR(C19/E19,0)</f>
-        <v>-1.8571428571428572</v>
+        <v>-1.2124999999999999</v>
       </c>
       <c r="K19" s="10">
         <f>IFERROR(D19/E19,0)</f>
-        <v>-0.3714285714285715</v>
+        <v>-0.24250000000000002</v>
       </c>
       <c r="L19" s="10" t="str">
         <f>LEFT(B19,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N19">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="O19">
         <f t="shared" si="7"/>
-        <v>-2.6000000000000005</v>
+        <v>-1.9400000000000002</v>
       </c>
       <c r="P19">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <f t="shared" si="9"/>
@@ -5746,7 +6387,7 @@
       </c>
       <c r="S19">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -5754,37 +6395,37 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C20">
-        <v>19.8</v>
+        <v>1.1999999999999993</v>
       </c>
       <c r="D20">
-        <v>3.9600000000000004</v>
+        <v>0.23999999999999988</v>
       </c>
       <c r="E20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" s="7">
         <f>IFERROR((F20/E20)*100,0)</f>
-        <v>57.142857142857139</v>
+        <v>62.5</v>
       </c>
       <c r="J20" s="10">
         <f>IFERROR(C20/E20,0)</f>
-        <v>2.8285714285714287</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="K20" s="10">
         <f>IFERROR(D20/E20,0)</f>
-        <v>0.56571428571428573</v>
+        <v>2.9999999999999985E-2</v>
       </c>
       <c r="L20" s="10" t="str">
         <f>LEFT(B20,3)</f>
@@ -5792,27 +6433,27 @@
       </c>
       <c r="N20">
         <f t="shared" si="1"/>
-        <v>19.8</v>
+        <v>1.1999999999999993</v>
       </c>
       <c r="O20">
         <f t="shared" si="7"/>
-        <v>3.9600000000000004</v>
+        <v>0.23999999999999988</v>
       </c>
       <c r="P20">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R20">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -5820,57 +6461,57 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="C21">
-        <v>0.59999999999999853</v>
+        <v>20.5</v>
       </c>
       <c r="D21">
-        <v>0.11999999999999961</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="E21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" s="7">
         <f>IFERROR((F21/E21)*100,0)</f>
-        <v>85.714285714285708</v>
+        <v>62.5</v>
       </c>
       <c r="J21" s="10">
         <f>IFERROR(C21/E21,0)</f>
-        <v>8.5714285714285507E-2</v>
+        <v>2.5625</v>
       </c>
       <c r="K21" s="10">
         <f>IFERROR(D21/E21,0)</f>
-        <v>1.7142857142857088E-2</v>
+        <v>0.51250000000000007</v>
       </c>
       <c r="L21" s="10" t="str">
         <f>LEFT(B21,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N21">
         <f t="shared" si="1"/>
-        <v>0.59999999999999853</v>
+        <v>20.5</v>
       </c>
       <c r="O21">
         <f t="shared" si="7"/>
-        <v>0.11999999999999961</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="P21">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <f t="shared" si="10"/>
@@ -5878,7 +6519,7 @@
       </c>
       <c r="S21">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -5889,16 +6530,16 @@
         <v>95</v>
       </c>
       <c r="C22">
-        <v>-15.3</v>
+        <v>-10.4</v>
       </c>
       <c r="D22">
-        <v>-3.06</v>
+        <v>-2.08</v>
       </c>
       <c r="E22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -5908,15 +6549,15 @@
       </c>
       <c r="I22" s="7">
         <f>IFERROR((F22/E22)*100,0)</f>
-        <v>28.571428571428569</v>
+        <v>37.5</v>
       </c>
       <c r="J22" s="10">
         <f>IFERROR(C22/E22,0)</f>
-        <v>-2.1857142857142859</v>
+        <v>-1.3</v>
       </c>
       <c r="K22" s="10">
         <f>IFERROR(D22/E22,0)</f>
-        <v>-0.43714285714285717</v>
+        <v>-0.26</v>
       </c>
       <c r="L22" s="10" t="str">
         <f>LEFT(B22,3)</f>
@@ -5924,19 +6565,19 @@
       </c>
       <c r="N22">
         <f t="shared" si="1"/>
-        <v>-15.3</v>
+        <v>-10.4</v>
       </c>
       <c r="O22">
         <f t="shared" si="7"/>
-        <v>-3.06</v>
+        <v>-2.08</v>
       </c>
       <c r="P22">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R22">
         <f t="shared" si="10"/>
@@ -5952,49 +6593,49 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23">
-        <v>15.999999999999998</v>
+        <v>-13</v>
       </c>
       <c r="D23">
-        <v>3.1999999999999997</v>
+        <v>-2.6000000000000005</v>
       </c>
       <c r="E23">
         <v>7</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I23" s="7">
         <f>IFERROR((F23/E23)*100,0)</f>
-        <v>71.428571428571431</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="J23" s="10">
         <f>IFERROR(C23/E23,0)</f>
-        <v>2.2857142857142856</v>
+        <v>-1.8571428571428572</v>
       </c>
       <c r="K23" s="10">
         <f>IFERROR(D23/E23,0)</f>
-        <v>0.45714285714285713</v>
+        <v>-0.3714285714285715</v>
       </c>
       <c r="L23" s="10" t="str">
         <f>LEFT(B23,3)</f>
-        <v>SEG</v>
+        <v>PEG</v>
       </c>
       <c r="N23">
         <f t="shared" si="1"/>
-        <v>15.999999999999998</v>
+        <v>-13</v>
       </c>
       <c r="O23">
         <f t="shared" si="7"/>
-        <v>3.1999999999999997</v>
+        <v>-2.6000000000000005</v>
       </c>
       <c r="P23">
         <f t="shared" si="8"/>
@@ -6002,7 +6643,7 @@
       </c>
       <c r="Q23">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R23">
         <f t="shared" si="10"/>
@@ -6010,65 +6651,65 @@
       </c>
       <c r="S23">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>73</v>
+      <c r="B24" s="8" t="s">
+        <v>132</v>
       </c>
       <c r="C24">
-        <v>1.9000000000000004</v>
+        <v>-1.9999999999999982</v>
       </c>
       <c r="D24">
-        <v>0.37999999999999989</v>
+        <v>-0.39999999999999947</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24" s="7">
         <f>IFERROR((F24/E24)*100,0)</f>
-        <v>60</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J24" s="10">
         <f>IFERROR(C24/E24,0)</f>
-        <v>0.38000000000000006</v>
+        <v>-0.33333333333333304</v>
       </c>
       <c r="K24" s="10">
         <f>IFERROR(D24/E24,0)</f>
-        <v>7.5999999999999984E-2</v>
+        <v>-6.6666666666666582E-2</v>
       </c>
       <c r="L24" s="10" t="str">
         <f>LEFT(B24,3)</f>
-        <v>SEG</v>
+        <v>UEG</v>
       </c>
       <c r="N24">
         <f t="shared" si="1"/>
-        <v>1.9000000000000004</v>
+        <v>-1.9999999999999982</v>
       </c>
       <c r="O24">
         <f t="shared" si="7"/>
-        <v>0.37999999999999989</v>
+        <v>-0.39999999999999947</v>
       </c>
       <c r="P24">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R24">
         <f t="shared" si="10"/>
@@ -6076,7 +6717,7 @@
       </c>
       <c r="S24">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -6084,13 +6725,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C25">
-        <v>-2.9000000000000004</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="D25">
-        <v>-0.58000000000000007</v>
+        <v>0.37999999999999989</v>
       </c>
       <c r="E25">
         <v>5</v>
@@ -6110,23 +6751,23 @@
       </c>
       <c r="J25" s="10">
         <f>IFERROR(C25/E25,0)</f>
-        <v>-0.58000000000000007</v>
+        <v>0.38000000000000006</v>
       </c>
       <c r="K25" s="10">
         <f>IFERROR(D25/E25,0)</f>
-        <v>-0.11600000000000002</v>
+        <v>7.5999999999999984E-2</v>
       </c>
       <c r="L25" s="10" t="str">
         <f>LEFT(B25,3)</f>
-        <v>UEG</v>
+        <v>SEG</v>
       </c>
       <c r="N25">
         <f t="shared" si="1"/>
-        <v>-2.9000000000000004</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="O25">
         <f t="shared" si="7"/>
-        <v>-0.58000000000000007</v>
+        <v>0.37999999999999989</v>
       </c>
       <c r="P25">
         <f t="shared" si="8"/>
@@ -6150,13 +6791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C26">
-        <v>-6.2</v>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="D26">
-        <v>-1.24</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="E26">
         <v>5</v>
@@ -6165,10 +6806,10 @@
         <v>3</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="7">
         <f>IFERROR((F26/E26)*100,0)</f>
@@ -6176,23 +6817,23 @@
       </c>
       <c r="J26" s="10">
         <f>IFERROR(C26/E26,0)</f>
-        <v>-1.24</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="K26" s="10">
         <f>IFERROR(D26/E26,0)</f>
-        <v>-0.248</v>
+        <v>-0.11600000000000002</v>
       </c>
       <c r="L26" s="10" t="str">
         <f>LEFT(B26,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N26">
         <f t="shared" si="1"/>
-        <v>-6.2</v>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="O26">
         <f t="shared" si="7"/>
-        <v>-1.24</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="P26">
         <f t="shared" si="8"/>
@@ -6204,11 +6845,11 @@
       </c>
       <c r="R26">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -6216,49 +6857,49 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C27">
-        <v>-7.5</v>
+        <v>-6.2</v>
       </c>
       <c r="D27">
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="E27">
         <v>5</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I27" s="7">
         <f>IFERROR((F27/E27)*100,0)</f>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J27" s="10">
         <f>IFERROR(C27/E27,0)</f>
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="K27" s="10">
         <f>IFERROR(D27/E27,0)</f>
-        <v>-0.3</v>
+        <v>-0.248</v>
       </c>
       <c r="L27" s="10" t="str">
         <f>LEFT(B27,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N27">
         <f t="shared" si="1"/>
-        <v>-7.5</v>
+        <v>-6.2</v>
       </c>
       <c r="O27">
         <f t="shared" si="7"/>
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="P27">
         <f t="shared" si="8"/>
@@ -6266,15 +6907,15 @@
       </c>
       <c r="Q27">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -6282,13 +6923,13 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C28">
-        <v>-9.1</v>
+        <v>-7.5</v>
       </c>
       <c r="D28">
-        <v>-1.82</v>
+        <v>-1.5</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -6308,23 +6949,23 @@
       </c>
       <c r="J28" s="10">
         <f>IFERROR(C28/E28,0)</f>
-        <v>-1.8199999999999998</v>
+        <v>-1.5</v>
       </c>
       <c r="K28" s="10">
         <f>IFERROR(D28/E28,0)</f>
-        <v>-0.36399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="L28" s="10" t="str">
         <f>LEFT(B28,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N28">
         <f t="shared" si="1"/>
-        <v>-9.1</v>
+        <v>-7.5</v>
       </c>
       <c r="O28">
         <f t="shared" si="7"/>
-        <v>-1.82</v>
+        <v>-1.5</v>
       </c>
       <c r="P28">
         <f t="shared" si="8"/>
@@ -6348,37 +6989,37 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C29">
-        <v>-7.5</v>
+        <v>-9.1</v>
       </c>
       <c r="D29">
-        <v>-1.5</v>
+        <v>-1.82</v>
       </c>
       <c r="E29">
         <v>5</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="7">
         <f>IFERROR((F29/E29)*100,0)</f>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J29" s="10">
         <f>IFERROR(C29/E29,0)</f>
-        <v>-1.5</v>
+        <v>-1.8199999999999998</v>
       </c>
       <c r="K29" s="10">
         <f>IFERROR(D29/E29,0)</f>
-        <v>-0.3</v>
+        <v>-0.36399999999999999</v>
       </c>
       <c r="L29" s="10" t="str">
         <f>LEFT(B29,3)</f>
@@ -6386,11 +7027,11 @@
       </c>
       <c r="N29">
         <f t="shared" si="1"/>
-        <v>-7.5</v>
+        <v>-9.1</v>
       </c>
       <c r="O29">
         <f t="shared" si="7"/>
-        <v>-1.5</v>
+        <v>-1.82</v>
       </c>
       <c r="P29">
         <f t="shared" si="8"/>
@@ -6398,7 +7039,7 @@
       </c>
       <c r="Q29">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <f t="shared" si="10"/>
@@ -6406,21 +7047,21 @@
       </c>
       <c r="S29">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>70</v>
+      <c r="B30" t="s">
+        <v>75</v>
       </c>
       <c r="C30">
-        <v>-12</v>
+        <v>-7.5</v>
       </c>
       <c r="D30">
-        <v>-2.4</v>
+        <v>-1.5</v>
       </c>
       <c r="E30">
         <v>5</v>
@@ -6440,23 +7081,23 @@
       </c>
       <c r="J30" s="10">
         <f>IFERROR(C30/E30,0)</f>
-        <v>-2.4</v>
+        <v>-1.5</v>
       </c>
       <c r="K30" s="10">
         <f>IFERROR(D30/E30,0)</f>
-        <v>-0.48</v>
+        <v>-0.3</v>
       </c>
       <c r="L30" s="10" t="str">
         <f>LEFT(B30,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N30">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>-7.5</v>
       </c>
       <c r="O30">
         <f t="shared" si="7"/>
-        <v>-2.4</v>
+        <v>-1.5</v>
       </c>
       <c r="P30">
         <f t="shared" si="8"/>
@@ -6480,49 +7121,49 @@
         <v>35</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="C31">
-        <v>-12.599999999999998</v>
+        <v>-12</v>
       </c>
       <c r="D31">
-        <v>-2.5199999999999996</v>
+        <v>-2.4</v>
       </c>
       <c r="E31">
         <v>5</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I31" s="7">
         <f>IFERROR((F31/E31)*100,0)</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J31" s="10">
         <f>IFERROR(C31/E31,0)</f>
-        <v>-2.5199999999999996</v>
+        <v>-2.4</v>
       </c>
       <c r="K31" s="10">
         <f>IFERROR(D31/E31,0)</f>
-        <v>-0.50399999999999989</v>
+        <v>-0.48</v>
       </c>
       <c r="L31" s="10" t="str">
         <f>LEFT(B31,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N31">
         <f t="shared" si="1"/>
-        <v>-12.599999999999998</v>
+        <v>-12</v>
       </c>
       <c r="O31">
         <f t="shared" si="7"/>
-        <v>-2.5199999999999996</v>
+        <v>-2.4</v>
       </c>
       <c r="P31">
         <f t="shared" si="8"/>
@@ -6530,7 +7171,7 @@
       </c>
       <c r="Q31">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31">
         <f t="shared" si="10"/>
@@ -6538,7 +7179,7 @@
       </c>
       <c r="S31">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
@@ -6546,37 +7187,37 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C32">
-        <v>-3.0999999999999996</v>
+        <v>13.4</v>
       </c>
       <c r="D32">
-        <v>-0.61999999999999988</v>
+        <v>2.6799999999999997</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32" s="7">
         <f>IFERROR((F32/E32)*100,0)</f>
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="J32" s="10">
         <f>IFERROR(C32/E32,0)</f>
-        <v>-0.77499999999999991</v>
+        <v>2.68</v>
       </c>
       <c r="K32" s="10">
         <f>IFERROR(D32/E32,0)</f>
-        <v>-0.15499999999999997</v>
+        <v>0.53599999999999992</v>
       </c>
       <c r="L32" s="10" t="str">
         <f>LEFT(B32,3)</f>
@@ -6584,19 +7225,19 @@
       </c>
       <c r="N32">
         <f t="shared" si="1"/>
-        <v>-3.0999999999999996</v>
+        <v>13.4</v>
       </c>
       <c r="O32">
         <f t="shared" si="7"/>
-        <v>-0.61999999999999988</v>
+        <v>2.6799999999999997</v>
       </c>
       <c r="P32">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q32">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R32">
         <f t="shared" si="10"/>
@@ -6604,65 +7245,65 @@
       </c>
       <c r="S32">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>37</v>
       </c>
-      <c r="B33" t="s">
-        <v>97</v>
+      <c r="B33" s="8" t="s">
+        <v>129</v>
       </c>
       <c r="C33">
-        <v>11.899999999999999</v>
+        <v>-18</v>
       </c>
       <c r="D33">
-        <v>2.38</v>
+        <v>-3.6</v>
       </c>
       <c r="E33">
+        <v>5</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>4</v>
-      </c>
-      <c r="F33">
-        <v>3</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
       </c>
       <c r="I33" s="7">
         <f>IFERROR((F33/E33)*100,0)</f>
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="J33" s="10">
         <f>IFERROR(C33/E33,0)</f>
-        <v>2.9749999999999996</v>
+        <v>-3.6</v>
       </c>
       <c r="K33" s="10">
         <f>IFERROR(D33/E33,0)</f>
-        <v>0.59499999999999997</v>
+        <v>-0.72</v>
       </c>
       <c r="L33" s="10" t="str">
         <f>LEFT(B33,3)</f>
-        <v>LEG</v>
+        <v>VEG</v>
       </c>
       <c r="N33">
         <f t="shared" si="1"/>
-        <v>11.899999999999999</v>
+        <v>-18</v>
       </c>
       <c r="O33">
         <f t="shared" si="7"/>
-        <v>2.38</v>
+        <v>-3.6</v>
       </c>
       <c r="P33">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q33">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R33">
         <f t="shared" si="10"/>
@@ -6670,7 +7311,7 @@
       </c>
       <c r="S33">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
@@ -6678,37 +7319,37 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C34">
-        <v>12.1</v>
+        <v>-3.0999999999999996</v>
       </c>
       <c r="D34">
-        <v>2.42</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="E34">
         <v>4</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" s="7">
         <f>IFERROR((F34/E34)*100,0)</f>
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J34" s="10">
         <f>IFERROR(C34/E34,0)</f>
-        <v>3.0249999999999999</v>
+        <v>-0.77499999999999991</v>
       </c>
       <c r="K34" s="10">
         <f>IFERROR(D34/E34,0)</f>
-        <v>0.60499999999999998</v>
+        <v>-0.15499999999999997</v>
       </c>
       <c r="L34" s="10" t="str">
         <f>LEFT(B34,3)</f>
@@ -6716,11 +7357,11 @@
       </c>
       <c r="N34">
         <f t="shared" si="1"/>
-        <v>12.1</v>
+        <v>-3.0999999999999996</v>
       </c>
       <c r="O34">
         <f t="shared" si="7"/>
-        <v>2.42</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="P34">
         <f t="shared" si="8"/>
@@ -6728,7 +7369,7 @@
       </c>
       <c r="Q34">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34">
         <f t="shared" si="10"/>
@@ -6736,7 +7377,7 @@
       </c>
       <c r="S34">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
@@ -6744,37 +7385,37 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C35">
-        <v>-42.900000000000006</v>
+        <v>11.899999999999999</v>
       </c>
       <c r="D35">
-        <v>-8.58</v>
+        <v>2.38</v>
       </c>
       <c r="E35">
         <v>4</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I35" s="7">
         <f>IFERROR((F35/E35)*100,0)</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J35" s="10">
         <f>IFERROR(C35/E35,0)</f>
-        <v>-10.725000000000001</v>
+        <v>2.9749999999999996</v>
       </c>
       <c r="K35" s="10">
         <f>IFERROR(D35/E35,0)</f>
-        <v>-2.145</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="L35" s="10" t="str">
         <f>LEFT(B35,3)</f>
@@ -6782,11 +7423,11 @@
       </c>
       <c r="N35">
         <f t="shared" si="1"/>
-        <v>-42.900000000000006</v>
+        <v>11.899999999999999</v>
       </c>
       <c r="O35">
         <f t="shared" si="7"/>
-        <v>-8.58</v>
+        <v>2.38</v>
       </c>
       <c r="P35">
         <f t="shared" si="8"/>
@@ -6794,7 +7435,7 @@
       </c>
       <c r="Q35">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R35">
         <f t="shared" si="10"/>
@@ -6802,21 +7443,21 @@
       </c>
       <c r="S35">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>30</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>128</v>
+      <c r="B36" t="s">
+        <v>83</v>
       </c>
       <c r="C36">
-        <v>-10.199999999999999</v>
+        <v>-42.900000000000006</v>
       </c>
       <c r="D36">
-        <v>-2.04</v>
+        <v>-8.58</v>
       </c>
       <c r="E36">
         <v>4</v>
@@ -6836,23 +7477,23 @@
       </c>
       <c r="J36" s="10">
         <f>IFERROR(C36/E36,0)</f>
-        <v>-2.5499999999999998</v>
+        <v>-10.725000000000001</v>
       </c>
       <c r="K36" s="10">
         <f>IFERROR(D36/E36,0)</f>
-        <v>-0.51</v>
+        <v>-2.145</v>
       </c>
       <c r="L36" s="10" t="str">
         <f>LEFT(B36,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N36">
         <f t="shared" si="1"/>
-        <v>-10.199999999999999</v>
+        <v>-42.900000000000006</v>
       </c>
       <c r="O36">
         <f t="shared" si="7"/>
-        <v>-2.04</v>
+        <v>-8.58</v>
       </c>
       <c r="P36">
         <f t="shared" si="8"/>
@@ -6876,57 +7517,57 @@
         <v>31</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>-10.199999999999999</v>
       </c>
       <c r="D37">
-        <v>1.2</v>
+        <v>-2.04</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I37" s="7">
         <f>IFERROR((F37/E37)*100,0)</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J37" s="10">
         <f>IFERROR(C37/E37,0)</f>
-        <v>2</v>
+        <v>-2.5499999999999998</v>
       </c>
       <c r="K37" s="10">
         <f>IFERROR(D37/E37,0)</f>
-        <v>0.39999999999999997</v>
+        <v>-0.51</v>
       </c>
       <c r="L37" s="10" t="str">
         <f>LEFT(B37,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N37">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>-10.199999999999999</v>
       </c>
       <c r="O37">
         <f t="shared" si="7"/>
-        <v>1.2</v>
+        <v>-2.04</v>
       </c>
       <c r="P37">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q37">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R37">
         <f t="shared" si="10"/>
@@ -6934,7 +7575,7 @@
       </c>
       <c r="S37">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
@@ -6942,57 +7583,57 @@
         <v>32</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="C38">
-        <v>-1.7000000000000002</v>
+        <v>13.9</v>
       </c>
       <c r="D38">
-        <v>-0.34</v>
+        <v>2.7800000000000002</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="7">
         <f>IFERROR((F38/E38)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>100</v>
       </c>
       <c r="J38" s="10">
         <f>IFERROR(C38/E38,0)</f>
-        <v>-0.56666666666666676</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="K38" s="10">
         <f>IFERROR(D38/E38,0)</f>
-        <v>-0.11333333333333334</v>
+        <v>0.69500000000000006</v>
       </c>
       <c r="L38" s="10" t="str">
         <f>LEFT(B38,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N38">
         <f t="shared" si="1"/>
-        <v>-1.7000000000000002</v>
+        <v>13.9</v>
       </c>
       <c r="O38">
         <f t="shared" si="7"/>
-        <v>-0.34</v>
+        <v>2.7800000000000002</v>
       </c>
       <c r="P38">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q38">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R38">
         <f t="shared" si="10"/>
@@ -7000,7 +7641,7 @@
       </c>
       <c r="S38">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
@@ -7008,57 +7649,57 @@
         <v>33</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="C39">
-        <v>-13.9</v>
+        <v>6.7</v>
       </c>
       <c r="D39">
-        <v>-2.78</v>
+        <v>1.34</v>
       </c>
       <c r="E39">
+        <v>4</v>
+      </c>
+      <c r="F39">
         <v>3</v>
       </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39" s="7">
         <f>IFERROR((F39/E39)*100,0)</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J39" s="10">
         <f>IFERROR(C39/E39,0)</f>
-        <v>-4.6333333333333337</v>
+        <v>1.675</v>
       </c>
       <c r="K39" s="10">
         <f>IFERROR(D39/E39,0)</f>
-        <v>-0.92666666666666664</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="L39" s="10" t="str">
         <f>LEFT(B39,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N39">
         <f t="shared" si="1"/>
-        <v>-13.9</v>
+        <v>6.7</v>
       </c>
       <c r="O39">
         <f t="shared" si="7"/>
-        <v>-2.78</v>
+        <v>1.34</v>
       </c>
       <c r="P39">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q39">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R39">
         <f t="shared" si="10"/>
@@ -7066,7 +7707,7 @@
       </c>
       <c r="S39">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
@@ -7074,19 +7715,19 @@
         <v>34</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="C40">
-        <v>1.0000000000000002</v>
+        <v>9.6</v>
       </c>
       <c r="D40">
-        <v>0.2</v>
+        <v>1.92</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -7096,15 +7737,15 @@
       </c>
       <c r="I40" s="7">
         <f>IFERROR((F40/E40)*100,0)</f>
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J40" s="10">
         <f>IFERROR(C40/E40,0)</f>
-        <v>0.50000000000000011</v>
+        <v>2.4</v>
       </c>
       <c r="K40" s="10">
         <f>IFERROR(D40/E40,0)</f>
-        <v>0.1</v>
+        <v>0.48</v>
       </c>
       <c r="L40" s="10" t="str">
         <f>LEFT(B40,3)</f>
@@ -7112,19 +7753,19 @@
       </c>
       <c r="N40">
         <f t="shared" si="1"/>
-        <v>1.0000000000000002</v>
+        <v>9.6</v>
       </c>
       <c r="O40">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>1.92</v>
       </c>
       <c r="P40">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q40">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R40">
         <f t="shared" si="10"/>
@@ -7140,57 +7781,57 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>-13.9</v>
       </c>
       <c r="D41">
-        <v>0.2</v>
+        <v>-2.78</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41" s="7">
         <f>IFERROR((F41/E41)*100,0)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J41" s="10">
         <f>IFERROR(C41/E41,0)</f>
-        <v>0.5</v>
+        <v>-4.6333333333333337</v>
       </c>
       <c r="K41" s="10">
         <f>IFERROR(D41/E41,0)</f>
-        <v>0.1</v>
+        <v>-0.92666666666666664</v>
       </c>
       <c r="L41" s="10" t="str">
         <f>LEFT(B41,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N41">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>-13.9</v>
       </c>
       <c r="O41">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>-2.78</v>
       </c>
       <c r="P41">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q41">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41">
         <f t="shared" si="10"/>
@@ -7198,7 +7839,7 @@
       </c>
       <c r="S41">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
@@ -7206,57 +7847,57 @@
         <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C42">
-        <v>-1.9000000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="D42">
-        <v>-0.38</v>
+        <v>1.62</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="7">
         <f>IFERROR((F42/E42)*100,0)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J42" s="10">
         <f>IFERROR(C42/E42,0)</f>
-        <v>-0.95000000000000007</v>
+        <v>2.6999999999999997</v>
       </c>
       <c r="K42" s="10">
         <f>IFERROR(D42/E42,0)</f>
-        <v>-0.19</v>
+        <v>0.54</v>
       </c>
       <c r="L42" s="10" t="str">
         <f>LEFT(B42,3)</f>
-        <v>PEG</v>
+        <v>WEG</v>
       </c>
       <c r="N42">
         <f t="shared" si="1"/>
-        <v>-1.9000000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="O42">
         <f t="shared" si="7"/>
-        <v>-0.38</v>
+        <v>1.62</v>
       </c>
       <c r="P42">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R42">
         <f t="shared" si="10"/>
@@ -7264,7 +7905,7 @@
       </c>
       <c r="S42">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
@@ -7272,37 +7913,37 @@
         <v>42</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="C43">
-        <v>-12</v>
+        <v>4.7</v>
       </c>
       <c r="D43">
-        <v>-2.4</v>
+        <v>0.94000000000000006</v>
       </c>
       <c r="E43">
+        <v>3</v>
+      </c>
+      <c r="F43">
         <v>2</v>
       </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="7">
         <f>IFERROR((F43/E43)*100,0)</f>
-        <v>0</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J43" s="10">
         <f>IFERROR(C43/E43,0)</f>
-        <v>-6</v>
+        <v>1.5666666666666667</v>
       </c>
       <c r="K43" s="10">
         <f>IFERROR(D43/E43,0)</f>
-        <v>-1.2</v>
+        <v>0.31333333333333335</v>
       </c>
       <c r="L43" s="10" t="str">
         <f>LEFT(B43,3)</f>
@@ -7310,19 +7951,19 @@
       </c>
       <c r="N43">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>4.7</v>
       </c>
       <c r="O43">
         <f t="shared" si="7"/>
-        <v>-2.4</v>
+        <v>0.94000000000000006</v>
       </c>
       <c r="P43">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q43">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R43">
         <f t="shared" si="10"/>
@@ -7330,7 +7971,7 @@
       </c>
       <c r="S43">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
@@ -7338,19 +7979,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C44">
-        <v>-14.8</v>
+        <v>-2.7</v>
       </c>
       <c r="D44">
-        <v>-2.96</v>
+        <v>-0.54</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -7360,35 +8001,35 @@
       </c>
       <c r="I44" s="7">
         <f>IFERROR((F44/E44)*100,0)</f>
-        <v>0</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J44" s="10">
         <f>IFERROR(C44/E44,0)</f>
-        <v>-7.4</v>
+        <v>-0.9</v>
       </c>
       <c r="K44" s="10">
         <f>IFERROR(D44/E44,0)</f>
-        <v>-1.48</v>
+        <v>-0.18000000000000002</v>
       </c>
       <c r="L44" s="10" t="str">
         <f>LEFT(B44,3)</f>
-        <v>VEG</v>
+        <v>PEG</v>
       </c>
       <c r="N44">
         <f t="shared" si="1"/>
-        <v>-14.8</v>
+        <v>-2.7</v>
       </c>
       <c r="O44">
         <f t="shared" si="7"/>
-        <v>-2.96</v>
+        <v>-0.54</v>
       </c>
       <c r="P44">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q44">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44">
         <f t="shared" si="10"/>
@@ -7403,58 +8044,58 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>84</v>
+      <c r="B45" t="s">
+        <v>136</v>
       </c>
       <c r="C45">
-        <v>6.1</v>
+        <v>-6.4</v>
       </c>
       <c r="D45">
-        <v>1.22</v>
+        <v>-1.28</v>
       </c>
       <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
         <v>2</v>
-      </c>
-      <c r="F45">
-        <v>2</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
       </c>
       <c r="I45" s="7">
         <f>IFERROR((F45/E45)*100,0)</f>
-        <v>100</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J45" s="10">
         <f>IFERROR(C45/E45,0)</f>
-        <v>3.05</v>
+        <v>-2.1333333333333333</v>
       </c>
       <c r="K45" s="10">
         <f>IFERROR(D45/E45,0)</f>
-        <v>0.61</v>
+        <v>-0.42666666666666669</v>
       </c>
       <c r="L45" s="10" t="str">
         <f>LEFT(B45,3)</f>
-        <v>WEG</v>
+        <v>VEG</v>
       </c>
       <c r="N45">
         <f t="shared" si="1"/>
-        <v>6.1</v>
+        <v>-6.4</v>
       </c>
       <c r="O45">
         <f t="shared" si="7"/>
-        <v>1.22</v>
+        <v>-1.28</v>
       </c>
       <c r="P45">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45">
         <f t="shared" si="10"/>
@@ -7462,7 +8103,7 @@
       </c>
       <c r="S45">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -7470,13 +8111,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="C46">
-        <v>2.5</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D46">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -7496,11 +8137,11 @@
       </c>
       <c r="J46" s="10">
         <f>IFERROR(C46/E46,0)</f>
-        <v>1.25</v>
+        <v>0.50000000000000011</v>
       </c>
       <c r="K46" s="10">
         <f>IFERROR(D46/E46,0)</f>
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="10" t="str">
         <f>LEFT(B46,3)</f>
@@ -7508,11 +8149,11 @@
       </c>
       <c r="N46">
         <f t="shared" si="1"/>
-        <v>2.5</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="O46">
         <f t="shared" si="7"/>
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="P46">
         <f t="shared" si="8"/>
@@ -7536,13 +8177,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="C47">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>6.0000000000000005E-2</v>
+        <v>0.2</v>
       </c>
       <c r="E47">
         <v>2</v>
@@ -7562,23 +8203,23 @@
       </c>
       <c r="J47" s="10">
         <f>IFERROR(C47/E47,0)</f>
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="K47" s="10">
         <f>IFERROR(D47/E47,0)</f>
-        <v>3.0000000000000002E-2</v>
+        <v>0.1</v>
       </c>
       <c r="L47" s="10" t="str">
         <f>LEFT(B47,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N47">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="O47">
         <f t="shared" si="7"/>
-        <v>6.0000000000000005E-2</v>
+        <v>0.2</v>
       </c>
       <c r="P47">
         <f t="shared" si="8"/>
@@ -7602,19 +8243,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C48">
-        <v>-1.3</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="D48">
-        <v>-0.26</v>
+        <v>-0.38</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -7624,15 +8265,15 @@
       </c>
       <c r="I48" s="7">
         <f>IFERROR((F48/E48)*100,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J48" s="10">
         <f>IFERROR(C48/E48,0)</f>
-        <v>-1.3</v>
+        <v>-0.95000000000000007</v>
       </c>
       <c r="K48" s="10">
         <f>IFERROR(D48/E48,0)</f>
-        <v>-0.26</v>
+        <v>-0.19</v>
       </c>
       <c r="L48" s="10" t="str">
         <f>LEFT(B48,3)</f>
@@ -7640,26 +8281,26 @@
       </c>
       <c r="N48">
         <f t="shared" si="1"/>
-        <v>-1.3</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="O48">
         <f t="shared" si="7"/>
-        <v>-0.26</v>
+        <v>-0.38</v>
       </c>
       <c r="P48">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48">
-        <f t="shared" ref="R48:R65" si="12">G48+Y48</f>
+        <f t="shared" ref="R48:R53" si="12">G48+Y48</f>
         <v>0</v>
       </c>
       <c r="S48">
-        <f t="shared" ref="S48:S65" si="13">H48+Z48</f>
+        <f t="shared" ref="S48:S53" si="13">H48+Z48</f>
         <v>1</v>
       </c>
     </row>
@@ -7668,16 +8309,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="C49">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="D49">
-        <v>-1.2</v>
+        <v>-2.4</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -7686,7 +8327,7 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="7">
         <f>IFERROR((F49/E49)*100,0)</f>
@@ -7702,19 +8343,19 @@
       </c>
       <c r="L49" s="10" t="str">
         <f>LEFT(B49,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N49">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="O49">
         <f t="shared" si="7"/>
-        <v>-1.2</v>
+        <v>-2.4</v>
       </c>
       <c r="P49">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q49">
         <f t="shared" si="9"/>
@@ -7726,7 +8367,7 @@
       </c>
       <c r="S49">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
@@ -7734,16 +8375,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="C50">
-        <v>-1.6</v>
+        <v>-3.3</v>
       </c>
       <c r="D50">
-        <v>-0.32</v>
+        <v>-0.66</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -7752,7 +8393,7 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" s="7">
         <f>IFERROR((F50/E50)*100,0)</f>
@@ -7760,27 +8401,27 @@
       </c>
       <c r="J50" s="10">
         <f>IFERROR(C50/E50,0)</f>
-        <v>-1.6</v>
+        <v>-1.65</v>
       </c>
       <c r="K50" s="10">
         <f>IFERROR(D50/E50,0)</f>
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="L50" s="10" t="str">
         <f>LEFT(B50,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N50">
         <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>-3.3</v>
       </c>
       <c r="O50">
         <f t="shared" si="7"/>
-        <v>-0.32</v>
+        <v>-0.66</v>
       </c>
       <c r="P50">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q50">
         <f t="shared" si="9"/>
@@ -7792,7 +8433,7 @@
       </c>
       <c r="S50">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
@@ -7800,13 +8441,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="C51">
-        <v>-1.3</v>
+        <v>-6</v>
       </c>
       <c r="D51">
-        <v>-0.26</v>
+        <v>-1.2</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -7826,23 +8467,23 @@
       </c>
       <c r="J51" s="10">
         <f>IFERROR(C51/E51,0)</f>
-        <v>-1.3</v>
+        <v>-6</v>
       </c>
       <c r="K51" s="10">
         <f>IFERROR(D51/E51,0)</f>
-        <v>-0.26</v>
+        <v>-1.2</v>
       </c>
       <c r="L51" s="10" t="str">
         <f>LEFT(B51,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N51">
         <f t="shared" si="1"/>
-        <v>-1.3</v>
+        <v>-6</v>
       </c>
       <c r="O51">
         <f t="shared" si="7"/>
-        <v>-0.26</v>
+        <v>-1.2</v>
       </c>
       <c r="P51">
         <f t="shared" si="8"/>
@@ -7866,13 +8507,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="C52">
-        <v>-11.4</v>
+        <v>-1.6</v>
       </c>
       <c r="D52">
-        <v>-2.2800000000000002</v>
+        <v>-0.32</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -7892,23 +8533,23 @@
       </c>
       <c r="J52" s="10">
         <f>IFERROR(C52/E52,0)</f>
-        <v>-11.4</v>
+        <v>-1.6</v>
       </c>
       <c r="K52" s="10">
         <f>IFERROR(D52/E52,0)</f>
-        <v>-2.2800000000000002</v>
+        <v>-0.32</v>
       </c>
       <c r="L52" s="10" t="str">
         <f>LEFT(B52,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N52">
         <f t="shared" si="1"/>
-        <v>-11.4</v>
+        <v>-1.6</v>
       </c>
       <c r="O52">
         <f t="shared" si="7"/>
-        <v>-2.2800000000000002</v>
+        <v>-0.32</v>
       </c>
       <c r="P52">
         <f t="shared" si="8"/>
@@ -7932,13 +8573,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C53">
-        <v>-19.5</v>
+        <v>-11.4</v>
       </c>
       <c r="D53">
-        <v>-3.9</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -7958,11 +8599,11 @@
       </c>
       <c r="J53" s="10">
         <f>IFERROR(C53/E53,0)</f>
-        <v>-19.5</v>
+        <v>-11.4</v>
       </c>
       <c r="K53" s="10">
         <f>IFERROR(D53/E53,0)</f>
-        <v>-3.9</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="L53" s="10" t="str">
         <f>LEFT(B53,3)</f>
@@ -7970,11 +8611,11 @@
       </c>
       <c r="N53">
         <f t="shared" si="1"/>
-        <v>-19.5</v>
+        <v>-11.4</v>
       </c>
       <c r="O53">
         <f t="shared" si="7"/>
-        <v>-3.9</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="P53">
         <f t="shared" si="8"/>
@@ -7994,22 +8635,202 @@
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="I54" s="7"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54">
+        <v>-19.5</v>
+      </c>
+      <c r="D54">
+        <v>-3.9</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54" s="7">
+        <f>IFERROR((F54/E54)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="10">
+        <f>IFERROR(C54/E54,0)</f>
+        <v>-19.5</v>
+      </c>
+      <c r="K54" s="10">
+        <f>IFERROR(D54/E54,0)</f>
+        <v>-3.9</v>
+      </c>
+      <c r="L54" s="10" t="str">
+        <f>LEFT(B54,3)</f>
+        <v>UEG</v>
+      </c>
+      <c r="N54">
+        <f t="shared" ref="N54:N56" si="14">C54+U54</f>
+        <v>-19.5</v>
+      </c>
+      <c r="O54">
+        <f t="shared" ref="O54:O56" si="15">D54+V54</f>
+        <v>-3.9</v>
+      </c>
+      <c r="P54">
+        <f t="shared" ref="P54:P56" si="16">E54+W54</f>
+        <v>1</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" ref="Q54:Q56" si="17">F54+X54</f>
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <f t="shared" ref="R54:R56" si="18">G54+Y54</f>
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <f t="shared" ref="S54:S56" si="19">H54+Z54</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="I55" s="7"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>137</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55">
+        <v>0.4</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55" s="7">
+        <f>IFERROR((F55/E55)*100,0)</f>
+        <v>100</v>
+      </c>
+      <c r="J55" s="10">
+        <f>IFERROR(C55/E55,0)</f>
+        <v>2</v>
+      </c>
+      <c r="K55" s="10">
+        <f>IFERROR(D55/E55,0)</f>
+        <v>0.4</v>
+      </c>
+      <c r="L55" s="10" t="str">
+        <f>LEFT(B55,3)</f>
+        <v>UEG</v>
+      </c>
+      <c r="N55">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="15"/>
+        <v>0.4</v>
+      </c>
+      <c r="P55">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="R55">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="I56" s="7"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56">
+        <v>5.2</v>
+      </c>
+      <c r="D56">
+        <v>1.04</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56" s="7">
+        <f>IFERROR((F56/E56)*100,0)</f>
+        <v>100</v>
+      </c>
+      <c r="J56" s="10">
+        <f>IFERROR(C56/E56,0)</f>
+        <v>5.2</v>
+      </c>
+      <c r="K56" s="10">
+        <f>IFERROR(D56/E56,0)</f>
+        <v>1.04</v>
+      </c>
+      <c r="L56" s="10" t="str">
+        <f>LEFT(B56,3)</f>
+        <v>WEG</v>
+      </c>
+      <c r="N56">
+        <f t="shared" si="14"/>
+        <v>5.2</v>
+      </c>
+      <c r="O56">
+        <f t="shared" si="15"/>
+        <v>1.04</v>
+      </c>
+      <c r="P56">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q56">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="R56">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B57" s="8"/>
@@ -8380,7 +9201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A53AFF8-0615-4AA5-B49F-FDA402810813}">
   <dimension ref="A1:AB75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8389,7 +9210,7 @@
     <col min="8" max="28" width="8.42578125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>104</v>
       </c>
@@ -8397,7 +9218,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" t="s">
         <v>100</v>
@@ -8421,17 +9242,17 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
       <c r="B3">
         <f>SUM(H3:AB3)</f>
-        <v>-17.2</v>
+        <v>10.6</v>
       </c>
       <c r="C3">
         <f>(B3/$C$1)*100</f>
-        <v>-3.44</v>
+        <v>2.12</v>
       </c>
       <c r="D3">
         <f>COUNTA(H3:AB3)</f>
@@ -8439,7 +9260,7 @@
       </c>
       <c r="E3">
         <f>COUNTIF(H3:AB3, "&gt;0")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <f>COUNTIF(H3:AB3, "=0")</f>
@@ -8447,91 +9268,84 @@
       </c>
       <c r="G3">
         <f>COUNTIF(H3:AB3, "&lt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" s="20">
-        <v>-15.7</v>
+        <v>1.4</v>
       </c>
       <c r="I3" s="20">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J3" s="20">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="K3" s="20">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="L3" s="20">
-        <v>-10.7</v>
-      </c>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>56</v>
       </c>
       <c r="B4">
         <f>SUM(H4:AB4)</f>
-        <v>-5.5000000000000009</v>
+        <v>-0.69999999999999973</v>
       </c>
       <c r="C4">
         <f>(B4/$C$1)*100</f>
-        <v>-1.1000000000000001</v>
+        <v>-0.13999999999999996</v>
       </c>
       <c r="D4">
         <f>COUNTA(H4:AB4)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <f>COUNTIF(H4:AB4, "&gt;0")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <f>COUNTIF(H4:AB4, "=0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <f>COUNTIF(H4:AB4, "&lt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="20">
-        <v>-6.4</v>
+        <v>1.6</v>
       </c>
       <c r="I4" s="20">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="J4" s="20">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="K4" s="20">
-        <v>5</v>
-      </c>
-      <c r="L4" s="20">
-        <v>-9.4</v>
-      </c>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>60</v>
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>129</v>
       </c>
       <c r="B5">
         <f>SUM(H5:AB5)</f>
-        <v>-33.1</v>
+        <v>-3.2</v>
       </c>
       <c r="C5">
         <f>(B5/$C$1)*100</f>
-        <v>-6.620000000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="D5">
         <f>COUNTA(H5:AB5)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <f>COUNTIF(H5:AB5, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <f>COUNTIF(H5:AB5, "=0")</f>
@@ -8539,36 +9353,33 @@
       </c>
       <c r="G5">
         <f>COUNTIF(H5:AB5, "&lt;0")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5" s="20">
-        <v>-5.7</v>
-      </c>
-      <c r="I5" s="20">
-        <v>-17.2</v>
-      </c>
-      <c r="J5" s="20">
-        <v>-8.8000000000000007</v>
-      </c>
-      <c r="K5" s="20">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>64</v>
+        <v>0.9</v>
+      </c>
+      <c r="I5" s="21">
+        <v>-0.9</v>
+      </c>
+      <c r="J5" s="21">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="B6">
         <f>SUM(H6:AB6)</f>
-        <v>0.79999999999999982</v>
+        <v>-6.4</v>
       </c>
       <c r="C6">
         <f>(B6/$C$1)*100</f>
-        <v>0.15999999999999998</v>
+        <v>-1.28</v>
       </c>
       <c r="D6">
         <f>COUNTA(H6:AB6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <f>COUNTIF(H6:AB6, "&gt;0")</f>
@@ -8580,27 +9391,29 @@
       </c>
       <c r="G6">
         <f>COUNTIF(H6:AB6, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H6" s="20">
-        <v>6.3</v>
-      </c>
-      <c r="I6" s="20">
-        <v>-5.5</v>
-      </c>
-      <c r="J6" s="17"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H6" s="21">
+        <v>5.3</v>
+      </c>
+      <c r="I6" s="21">
+        <v>-2.6</v>
+      </c>
+      <c r="J6" s="21">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B7">
         <f>SUM(H7:AB7)</f>
-        <v>-17.7</v>
+        <v>-0.19999999999999973</v>
       </c>
       <c r="C7">
         <f>(B7/$C$1)*100</f>
-        <v>-3.54</v>
+        <v>-3.9999999999999945E-2</v>
       </c>
       <c r="D7">
         <f>COUNTA(H7:AB7)</f>
@@ -8608,7 +9421,7 @@
       </c>
       <c r="E7">
         <f>COUNTIF(H7:AB7, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <f>COUNTIF(H7:AB7, "=0")</f>
@@ -8616,27 +9429,26 @@
       </c>
       <c r="G7">
         <f>COUNTIF(H7:AB7, "&lt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="20">
-        <v>-8</v>
+        <v>3.1</v>
       </c>
       <c r="I7" s="21">
-        <v>-9.6999999999999993</v>
-      </c>
-      <c r="J7" s="17"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B8">
         <f>SUM(H8:AB8)</f>
-        <v>-4.0999999999999996</v>
+        <v>5.8</v>
       </c>
       <c r="C8">
         <f>(B8/$C$1)*100</f>
-        <v>-0.81999999999999984</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D8">
         <f>COUNTA(H8:AB8)</f>
@@ -8644,7 +9456,7 @@
       </c>
       <c r="E8">
         <f>COUNTIF(H8:AB8, "&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <f>COUNTIF(H8:AB8, "=0")</f>
@@ -8652,27 +9464,26 @@
       </c>
       <c r="G8">
         <f>COUNTIF(H8:AB8, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H8" s="20">
-        <v>6.4</v>
-      </c>
-      <c r="I8" s="20">
-        <v>-10.5</v>
-      </c>
-      <c r="J8" s="18"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21">
+        <v>5</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B9">
         <f>SUM(H9:AB9)</f>
-        <v>-6.6</v>
+        <v>-5.2</v>
       </c>
       <c r="C9">
         <f>(B9/$C$1)*100</f>
-        <v>-1.32</v>
+        <v>-1.04</v>
       </c>
       <c r="D9">
         <f>COUNTA(H9:AB9)</f>
@@ -8690,25 +9501,24 @@
         <f>COUNTIF(H9:AB9, "&lt;0")</f>
         <v>1</v>
       </c>
-      <c r="H9" s="20">
-        <v>2</v>
-      </c>
-      <c r="I9" s="20">
-        <v>-8.6</v>
-      </c>
-      <c r="J9" s="17"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>95</v>
+      <c r="H9" s="21">
+        <v>-5.8</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>133</v>
       </c>
       <c r="B10">
         <f>SUM(H10:AB10)</f>
-        <v>-11.5</v>
+        <v>7.1</v>
       </c>
       <c r="C10">
         <f>(B10/$C$1)*100</f>
-        <v>-2.2999999999999998</v>
+        <v>1.42</v>
       </c>
       <c r="D10">
         <f>COUNTA(H10:AB10)</f>
@@ -8716,7 +9526,7 @@
       </c>
       <c r="E10">
         <f>COUNTIF(H10:AB10, "&gt;0")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <f>COUNTIF(H10:AB10, "=0")</f>
@@ -8724,27 +9534,26 @@
       </c>
       <c r="G10">
         <f>COUNTIF(H10:AB10, "&lt;0")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="20">
-        <v>-9.9</v>
-      </c>
-      <c r="I10" s="20">
-        <v>-1.6</v>
-      </c>
-      <c r="J10" s="19"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>91</v>
+        <v>2.5</v>
+      </c>
+      <c r="I10" s="21">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="B11">
         <f>SUM(H11:AB11)</f>
-        <v>-10.1</v>
+        <v>-1.4000000000000001</v>
       </c>
       <c r="C11">
         <f>(B11/$C$1)*100</f>
-        <v>-2.02</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="D11">
         <f>COUNTA(H11:AB11)</f>
@@ -8752,7 +9561,7 @@
       </c>
       <c r="E11">
         <f>COUNTIF(H11:AB11, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <f>COUNTIF(H11:AB11, "=0")</f>
@@ -8760,36 +9569,34 @@
       </c>
       <c r="G11">
         <f>COUNTIF(H11:AB11, "&lt;0")</f>
-        <v>2</v>
-      </c>
-      <c r="H11" s="20">
-        <v>-2.5</v>
-      </c>
-      <c r="I11" s="20">
-        <v>-7.6</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>132</v>
+        <v>1</v>
+      </c>
+      <c r="H11" s="21">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="I11" s="21">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>64</v>
       </c>
       <c r="B12">
         <f>SUM(H12:AB12)</f>
-        <v>1.2000000000000002</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="C12">
         <f>(B12/$C$1)*100</f>
-        <v>0.24000000000000002</v>
+        <v>-0.22</v>
       </c>
       <c r="D12">
         <f>COUNTA(H12:AB12)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <f>COUNTIF(H12:AB12, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <f>COUNTIF(H12:AB12, "=0")</f>
@@ -8799,34 +9606,29 @@
         <f>COUNTIF(H12:AB12, "&lt;0")</f>
         <v>1</v>
       </c>
-      <c r="H12" s="20">
-        <v>-6.1</v>
-      </c>
-      <c r="I12" s="20">
-        <v>7.3</v>
-      </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>128</v>
+      <c r="H12" s="21">
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>60</v>
       </c>
       <c r="B13">
         <f>SUM(H13:AB13)</f>
-        <v>-5</v>
+        <v>9.1</v>
       </c>
       <c r="C13">
         <f>(B13/$C$1)*100</f>
-        <v>-1</v>
+        <v>1.82</v>
       </c>
       <c r="D13">
         <f>COUNTA(H13:AB13)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <f>COUNTIF(H13:AB13, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <f>COUNTIF(H13:AB13, "=0")</f>
@@ -8834,27 +9636,23 @@
       </c>
       <c r="G13">
         <f>COUNTIF(H13:AB13, "&lt;0")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" s="20">
-        <v>-1</v>
-      </c>
-      <c r="I13" s="20">
-        <v>-4</v>
-      </c>
-      <c r="J13" s="15"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>66</v>
       </c>
       <c r="B14">
         <f>SUM(H14:AB14)</f>
-        <v>-11.4</v>
+        <v>0.9</v>
       </c>
       <c r="C14">
         <f>(B14/$C$1)*100</f>
-        <v>-2.2800000000000002</v>
+        <v>0.18</v>
       </c>
       <c r="D14">
         <f>COUNTA(H14:AB14)</f>
@@ -8862,7 +9660,7 @@
       </c>
       <c r="E14">
         <f>COUNTIF(H14:AB14, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <f>COUNTIF(H14:AB14, "=0")</f>
@@ -8870,25 +9668,23 @@
       </c>
       <c r="G14">
         <f>COUNTIF(H14:AB14, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H14" s="20">
-        <v>-11.4</v>
-      </c>
-      <c r="I14" s="18"/>
-      <c r="J14" s="15"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15">
         <f>SUM(H15:AB15)</f>
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="C15">
         <f>(B15/$C$1)*100</f>
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="D15">
         <f>COUNTA(H15:AB15)</f>
@@ -8907,22 +9703,20 @@
         <v>0</v>
       </c>
       <c r="H15" s="20">
-        <v>0.8</v>
-      </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="B16">
         <f>SUM(H16:AB16)</f>
-        <v>13.6</v>
+        <v>-7.9</v>
       </c>
       <c r="C16">
         <f>(B16/$C$1)*100</f>
-        <v>2.7199999999999998</v>
+        <v>-1.58</v>
       </c>
       <c r="D16">
         <f>COUNTA(H16:AB16)</f>
@@ -8930,7 +9724,7 @@
       </c>
       <c r="E16">
         <f>COUNTIF(H16:AB16, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <f>COUNTIF(H16:AB16, "=0")</f>
@@ -8938,10 +9732,10 @@
       </c>
       <c r="G16">
         <f>COUNTIF(H16:AB16, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="20">
-        <v>13.6</v>
+        <v>-7.9</v>
       </c>
       <c r="I16" s="15"/>
     </row>
@@ -8951,11 +9745,11 @@
       </c>
       <c r="B17">
         <f>SUM(H17:AB17)</f>
-        <v>16.5</v>
+        <v>0.7</v>
       </c>
       <c r="C17">
         <f>(B17/$C$1)*100</f>
-        <v>3.3000000000000003</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="D17">
         <f>COUNTA(H17:AB17)</f>
@@ -8974,20 +9768,20 @@
         <v>0</v>
       </c>
       <c r="H17" s="21">
-        <v>16.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="B18">
         <f>SUM(H18:AB18)</f>
-        <v>1.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C18">
         <f>(B18/$C$1)*100</f>
-        <v>0.3</v>
+        <v>0.98000000000000009</v>
       </c>
       <c r="D18">
         <f>COUNTA(H18:AB18)</f>
@@ -9005,23 +9799,21 @@
         <f>COUNTIF(H18:AB18, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H18" s="20">
-        <v>1.5</v>
-      </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
+      <c r="H18" s="21">
+        <v>4.9000000000000004</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="B19">
         <f>SUM(H19:AB19)</f>
-        <v>0.2</v>
+        <v>10.6</v>
       </c>
       <c r="C19">
         <f>(B19/$C$1)*100</f>
-        <v>0.04</v>
+        <v>2.12</v>
       </c>
       <c r="D19">
         <f>COUNTA(H19:AB19)</f>
@@ -9039,22 +9831,21 @@
         <f>COUNTIF(H19:AB19, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H19" s="20">
-        <v>0.2</v>
-      </c>
-      <c r="I19" s="15"/>
+      <c r="H19" s="21">
+        <v>10.6</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>80</v>
+      <c r="A20" t="s">
+        <v>86</v>
       </c>
       <c r="B20">
         <f>SUM(H20:AB20)</f>
-        <v>-12.1</v>
+        <v>1.3</v>
       </c>
       <c r="C20">
         <f>(B20/$C$1)*100</f>
-        <v>-2.42</v>
+        <v>0.26</v>
       </c>
       <c r="D20">
         <f>COUNTA(H20:AB20)</f>
@@ -9062,7 +9853,7 @@
       </c>
       <c r="E20">
         <f>COUNTIF(H20:AB20, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
         <f>COUNTIF(H20:AB20, "=0")</f>
@@ -9070,23 +9861,25 @@
       </c>
       <c r="G20">
         <f>COUNTIF(H20:AB20, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H20" s="20">
-        <v>-12.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H20" s="21">
+        <v>1.3</v>
+      </c>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B21">
         <f>SUM(H21:AB21)</f>
-        <v>1.8</v>
+        <v>7.9</v>
       </c>
       <c r="C21">
         <f>(B21/$C$1)*100</f>
-        <v>0.36</v>
+        <v>1.58</v>
       </c>
       <c r="D21">
         <f>COUNTA(H21:AB21)</f>
@@ -9105,20 +9898,20 @@
         <v>0</v>
       </c>
       <c r="H21" s="20">
-        <v>1.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B22">
         <f>SUM(H22:AB22)</f>
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="C22">
         <f>(B22/$C$1)*100</f>
-        <v>1.3</v>
+        <v>1.6800000000000002</v>
       </c>
       <c r="D22">
         <f>COUNTA(H22:AB22)</f>
@@ -9137,20 +9930,21 @@
         <v>0</v>
       </c>
       <c r="H22" s="20">
-        <v>6.5</v>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="I22" s="15"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="B23">
         <f>SUM(H23:AB23)</f>
-        <v>-0.2</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <f>(B23/$C$1)*100</f>
-        <v>-0.04</v>
+        <v>0.4</v>
       </c>
       <c r="D23">
         <f>COUNTA(H23:AB23)</f>
@@ -9158,7 +9952,7 @@
       </c>
       <c r="E23">
         <f>COUNTIF(H23:AB23, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <f>COUNTIF(H23:AB23, "=0")</f>
@@ -9166,31 +9960,32 @@
       </c>
       <c r="G23">
         <f>COUNTIF(H23:AB23, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H23" s="21">
-        <v>-0.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H23" s="20">
+        <v>2</v>
+      </c>
+      <c r="I23" s="17"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>55</v>
+      <c r="A24" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="B24">
         <f>SUM(H24:AB24)</f>
-        <v>0</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="C24">
         <f>(B24/$C$1)*100</f>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="D24">
         <f>COUNTA(H24:AB24)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <f>COUNTIF(H24:AB24, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
         <f>COUNTIF(H24:AB24, "=0")</f>
@@ -9200,25 +9995,26 @@
         <f>COUNTIF(H24:AB24, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
+      <c r="H24" s="20">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I24" s="15"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>57</v>
+      <c r="A25" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="B25">
         <f>SUM(H25:AB25)</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C25">
         <f>(B25/$C$1)*100</f>
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D25">
         <f>COUNTA(H25:AB25)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
         <f>COUNTIF(H25:AB25, "&gt;0")</f>
@@ -9230,31 +10026,31 @@
       </c>
       <c r="G25">
         <f>COUNTIF(H25:AB25, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="H25" s="21">
+        <v>-2</v>
+      </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>59</v>
+      <c r="A26" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="B26">
         <f>SUM(H26:AB26)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C26">
         <f>(B26/$C$1)*100</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D26">
         <f>COUNTA(H26:AB26)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <f>COUNTIF(H26:AB26, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <f>COUNTIF(H26:AB26, "=0")</f>
@@ -9264,29 +10060,29 @@
         <f>COUNTIF(H26:AB26, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
+      <c r="H26" s="21">
+        <v>2</v>
+      </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>72</v>
+      <c r="A27" s="8" t="s">
+        <v>138</v>
       </c>
       <c r="B27">
         <f>SUM(H27:AB27)</f>
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="C27">
         <f>(B27/$C$1)*100</f>
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="D27">
         <f>COUNTA(H27:AB27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
         <f>COUNTIF(H27:AB27, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
         <f>COUNTIF(H27:AB27, "=0")</f>
@@ -9296,11 +10092,13 @@
         <f>COUNTIF(H27:AB27, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H27" s="17"/>
+      <c r="H27" s="21">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="B28">
         <f>SUM(H28:AB28)</f>
@@ -9326,7 +10124,7 @@
         <f>COUNTIF(H28:AB28, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H28" s="19"/>
+      <c r="H28" s="15"/>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
@@ -9334,7 +10132,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B29">
         <f>SUM(H29:AB29)</f>
@@ -9360,11 +10158,11 @@
         <f>COUNTIF(H29:AB29, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H29" s="18"/>
+      <c r="H29" s="15"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="B30">
         <f>SUM(H30:AB30)</f>
@@ -9390,12 +10188,12 @@
         <f>COUNTIF(H30:AB30, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H30" s="18"/>
+      <c r="H30" s="15"/>
       <c r="I30" s="15"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="B31">
         <f>SUM(H31:AB31)</f>
@@ -9425,7 +10223,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="B32">
         <f>SUM(H32:AB32)</f>
@@ -9451,11 +10249,11 @@
         <f>COUNTIF(H32:AB32, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H32" s="22"/>
+      <c r="H32" s="15"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B33">
         <f>SUM(H33:AB33)</f>
@@ -9481,14 +10279,11 @@
         <f>COUNTIF(H33:AB33, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H33" s="19"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
+      <c r="H33" s="15"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B34">
         <f>SUM(H34:AB34)</f>
@@ -9514,12 +10309,11 @@
         <f>COUNTIF(H34:AB34, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H34" s="19"/>
-      <c r="I34" s="17"/>
+      <c r="H34" s="15"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B35">
         <f>SUM(H35:AB35)</f>
@@ -9545,13 +10339,11 @@
         <f>COUNTIF(H35:AB35, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H35" s="19"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
+      <c r="H35" s="15"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="B36">
         <f>SUM(H36:AB36)</f>
@@ -9577,12 +10369,11 @@
         <f>COUNTIF(H36:AB36, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H36" s="18"/>
-      <c r="I36" s="17"/>
+      <c r="H36" s="15"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="B37">
         <f>SUM(H37:AB37)</f>
@@ -9608,12 +10399,12 @@
         <f>COUNTIF(H37:AB37, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H37" s="18"/>
+      <c r="H37" s="15"/>
       <c r="I37" s="15"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B38">
         <f>SUM(H38:AB38)</f>
@@ -9639,12 +10430,12 @@
         <f>COUNTIF(H38:AB38, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H38" s="18"/>
+      <c r="H38" s="15"/>
       <c r="I38" s="15"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="B39">
         <f>SUM(H39:AB39)</f>
@@ -9670,11 +10461,11 @@
         <f>COUNTIF(H39:AB39, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H39" s="18"/>
+      <c r="H39" s="15"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B40">
         <f>SUM(H40:AB40)</f>
@@ -9700,11 +10491,11 @@
         <f>COUNTIF(H40:AB40, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H40" s="18"/>
+      <c r="H40" s="15"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="B41">
         <f>SUM(H41:AB41)</f>
@@ -9730,13 +10521,13 @@
         <f>COUNTIF(H41:AB41, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H41" s="18"/>
+      <c r="H41" s="19"/>
       <c r="I41" s="15"/>
       <c r="J41" s="15"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
-        <v>68</v>
+      <c r="A42" t="s">
+        <v>93</v>
       </c>
       <c r="B42">
         <f>SUM(H42:AB42)</f>
@@ -9762,13 +10553,11 @@
         <f>COUNTIF(H42:AB42, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H42" s="19"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
+      <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
-        <v>131</v>
+      <c r="A43" t="s">
+        <v>75</v>
       </c>
       <c r="B43">
         <f>SUM(H43:AB43)</f>
@@ -9794,11 +10583,11 @@
         <f>COUNTIF(H43:AB43, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H43" s="19"/>
+      <c r="H43" s="18"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="B44">
         <f>SUM(H44:AB44)</f>
@@ -9824,12 +10613,12 @@
         <f>COUNTIF(H44:AB44, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H44" s="19"/>
+      <c r="H44" s="15"/>
       <c r="I44" s="15"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
-        <v>74</v>
+      <c r="A45" t="s">
+        <v>87</v>
       </c>
       <c r="B45">
         <f>SUM(H45:AB45)</f>
@@ -9856,10 +10645,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="17"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
-        <v>89</v>
+      <c r="A46" t="s">
+        <v>97</v>
       </c>
       <c r="B46">
         <f>SUM(H46:AB46)</f>
@@ -9885,12 +10677,12 @@
         <f>COUNTIF(H46:AB46, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H46" s="17"/>
+      <c r="H46" s="19"/>
       <c r="I46" s="17"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
-        <v>54</v>
+      <c r="A47" t="s">
+        <v>83</v>
       </c>
       <c r="B47">
         <f>SUM(H47:AB47)</f>
@@ -9916,11 +10708,12 @@
         <f>COUNTIF(H47:AB47, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H47" s="17"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="19"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B48">
         <f>SUM(H48:AB48)</f>
@@ -9946,11 +10739,11 @@
         <f>COUNTIF(H48:AB48, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H48" s="17"/>
+      <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B49">
         <f>SUM(H49:AB49)</f>
@@ -9976,13 +10769,13 @@
         <f>COUNTIF(H49:AB49, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H49" s="19"/>
+      <c r="H49" s="18"/>
       <c r="I49" s="15"/>
       <c r="J49" s="15"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B50">
         <f>SUM(H50:AB50)</f>
@@ -10012,7 +10805,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B51">
         <f>SUM(H51:AB51)</f>
@@ -10038,10 +10831,13 @@
         <f>COUNTIF(H51:AB51, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="B52">
         <f>SUM(H52:AB52)</f>
@@ -10067,12 +10863,12 @@
         <f>COUNTIF(H52:AB52, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H52" s="15"/>
+      <c r="H52" s="19"/>
       <c r="I52" s="15"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="B53">
         <f>SUM(H53:AB53)</f>
@@ -10098,11 +10894,11 @@
         <f>COUNTIF(H53:AB53, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H53" s="15"/>
+      <c r="H53" s="19"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="B54">
         <f>SUM(H54:AB54)</f>
@@ -10128,113 +10924,124 @@
         <f>COUNTIF(H54:AB54, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H54" s="15"/>
+      <c r="H54" s="19"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="8"/>
+      <c r="A55" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="B55">
-        <f t="shared" ref="B35:B66" si="0">SUM(H55:AB55)</f>
+        <f>SUM(H55:AB55)</f>
         <v>0</v>
       </c>
       <c r="C55">
-        <f t="shared" ref="C35:C66" si="1">(B55/$C$1)*100</f>
+        <f>(B55/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D55">
-        <f t="shared" ref="D35:D66" si="2">COUNTA(H55:AB55)</f>
+        <f>COUNTA(H55:AB55)</f>
         <v>0</v>
       </c>
       <c r="E55">
-        <f t="shared" ref="E35:E66" si="3">COUNTIF(H55:AB55, "&gt;0")</f>
+        <f>COUNTIF(H55:AB55, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F55">
-        <f t="shared" ref="F35:F66" si="4">COUNTIF(H55:AB55, "=0")</f>
+        <f>COUNTIF(H55:AB55, "=0")</f>
         <v>0</v>
       </c>
       <c r="G55">
-        <f t="shared" ref="G35:G66" si="5">COUNTIF(H55:AB55, "&lt;0")</f>
-        <v>0</v>
-      </c>
+        <f>COUNTIF(H55:AB55, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="8"/>
+      <c r="A56" s="8" t="s">
+        <v>130</v>
+      </c>
       <c r="B56">
-        <f t="shared" si="0"/>
+        <f>SUM(H56:AB56)</f>
         <v>0</v>
       </c>
       <c r="C56">
-        <f t="shared" si="1"/>
+        <f>(B56/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D56">
-        <f t="shared" si="2"/>
+        <f>COUNTA(H56:AB56)</f>
         <v>0</v>
       </c>
       <c r="E56">
-        <f t="shared" si="3"/>
+        <f>COUNTIF(H56:AB56, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F56">
-        <f t="shared" si="4"/>
+        <f>COUNTIF(H56:AB56, "=0")</f>
         <v>0</v>
       </c>
       <c r="G56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+        <f>COUNTIF(H56:AB56, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="H56" s="15"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="8"/>
+      <c r="A57" s="8" t="s">
+        <v>135</v>
+      </c>
       <c r="B57">
-        <f t="shared" si="0"/>
+        <f>SUM(H57:AB57)</f>
         <v>0</v>
       </c>
       <c r="C57">
-        <f t="shared" si="1"/>
+        <f>(B57/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D57">
-        <f t="shared" si="2"/>
+        <f>COUNTA(H57:AB57)</f>
         <v>0</v>
       </c>
       <c r="E57">
-        <f t="shared" si="3"/>
+        <f>COUNTIF(H57:AB57, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F57">
-        <f t="shared" si="4"/>
+        <f>COUNTIF(H57:AB57, "=0")</f>
         <v>0</v>
       </c>
       <c r="G57">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+        <f>COUNTIF(H57:AB57, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="H57" s="15"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="8"/>
       <c r="B58">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B55:B66" si="0">SUM(H58:AB58)</f>
         <v>0</v>
       </c>
       <c r="C58">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C55:C66" si="1">(B58/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D58">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D55:D66" si="2">COUNTA(H58:AB58)</f>
         <v>0</v>
       </c>
       <c r="E58">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E55:E66" si="3">COUNTIF(H58:AB58, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F58">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="F55:F66" si="4">COUNTIF(H58:AB58, "=0")</f>
         <v>0</v>
       </c>
       <c r="G58">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="G55:G66" si="5">COUNTIF(H58:AB58, "&lt;0")</f>
         <v>0</v>
       </c>
       <c r="H58" s="15"/>
@@ -10465,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:C98" si="7">(B67/$C$1)*100</f>
+        <f t="shared" ref="C67:C75" si="7">(B67/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D67">
@@ -10481,7 +11288,7 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <f t="shared" ref="G67:G98" si="11">COUNTIF(H67:AB67, "&lt;0")</f>
+        <f t="shared" ref="G67:G75" si="11">COUNTIF(H67:AB67, "&lt;0")</f>
         <v>0</v>
       </c>
       <c r="H67" s="15"/>
@@ -10713,8 +11520,8 @@
       <c r="H75" s="15"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB54">
-    <sortCondition descending="1" ref="D3:D54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB57">
+    <sortCondition descending="1" ref="D3:D57"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C46C4DE-A3BD-4DA6-BE00-394869A26579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1687CF6F-D478-4DF7-88B9-D61411E25716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId6"/>
+    <pivotCache cacheId="6" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="147">
   <si>
     <t>AQUA</t>
   </si>
@@ -476,6 +476,12 @@
   </si>
   <si>
     <t>PEG17_PROBIUS</t>
+  </si>
+  <si>
+    <t>PEG31_HYPERION</t>
+  </si>
+  <si>
+    <t>UEG4_CANADIAN</t>
   </si>
 </sst>
 </file>
@@ -619,7 +625,56 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="35">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -666,6 +721,104 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -923,10 +1076,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$K$2</c:f>
+              <c:f>Динамика!$B$2:$L$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -956,16 +1109,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46300</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$3:$K$3</c:f>
+              <c:f>Динамика!$B$3:$L$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>-20.100000000000001</c:v>
                 </c:pt>
@@ -995,6 +1151,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>-20.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-27.200000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1101,10 +1260,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$K$2</c:f>
+              <c:f>Динамика!$B$2:$L$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1134,16 +1293,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46300</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$4:$K$4</c:f>
+              <c:f>Динамика!$B$4:$L$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>19.7</c:v>
                 </c:pt>
@@ -1173,6 +1335,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>112.89999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>109.69999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1279,10 +1444,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$K$2</c:f>
+              <c:f>Динамика!$B$2:$L$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1312,16 +1477,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46300</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$5:$K$5</c:f>
+              <c:f>Динамика!$B$5:$L$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1.9</c:v>
                 </c:pt>
@@ -1350,6 +1518,9 @@
                   <c:v>14.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>14.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>14.799999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -1457,10 +1628,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$K$2</c:f>
+              <c:f>Динамика!$B$2:$L$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1490,16 +1661,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46300</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$6:$K$6</c:f>
+              <c:f>Динамика!$B$6:$L$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>-21</c:v>
                 </c:pt>
@@ -1529,6 +1703,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>-31.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-16.200000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1635,10 +1812,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$K$2</c:f>
+              <c:f>Динамика!$B$2:$L$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1668,16 +1845,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46300</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$7:$K$7</c:f>
+              <c:f>Динамика!$B$7:$L$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>-18.100000000000001</c:v>
                 </c:pt>
@@ -1707,6 +1887,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>-31.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-27.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1813,10 +1996,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$K$2</c:f>
+              <c:f>Динамика!$B$2:$L$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1846,16 +2029,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46300</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$8:$K$8</c:f>
+              <c:f>Динамика!$B$8:$L$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>44.5</c:v>
                 </c:pt>
@@ -1885,6 +2071,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>51.6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>63</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1994,10 +2183,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$K$2</c:f>
+              <c:f>Динамика!$B$2:$L$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -2027,16 +2216,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46300</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$9:$K$9</c:f>
+              <c:f>Динамика!$B$9:$L$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>6.8999999999999915</c:v>
                 </c:pt>
@@ -2066,6 +2258,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>95.999999999999972</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>116.99999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2824,43 +3019,43 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46300.967478240738" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="76" xr:uid="{3D6F248A-0360-4477-B017-E96CAA4B0EB4}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46301.967136342595" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="77" xr:uid="{3D6F248A-0360-4477-B017-E96CAA4B0EB4}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:L1048576" sheet="Результаты"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="Номер" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="60"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="62"/>
     </cacheField>
     <cacheField name="Стратегия" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Абс" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-42.900000000000006" maxValue="161.59999999999997"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-42.900000000000006" maxValue="163.89999999999998"/>
     </cacheField>
     <cacheField name="Отн" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-8.58" maxValue="32.320000000000007"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-8.58" maxValue="32.780000000000008"/>
     </cacheField>
     <cacheField name="Кол-во" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="73"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="78"/>
     </cacheField>
     <cacheField name="Прибыль" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="50"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="51"/>
     </cacheField>
     <cacheField name="Нейтрал" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
     </cacheField>
     <cacheField name="Убыток" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="23"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="27"/>
     </cacheField>
     <cacheField name="ПроцПД" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="100"/>
     </cacheField>
     <cacheField name="САП" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-19.5" maxValue="2.95"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-19.5" maxValue="2.7250000000000001"/>
     </cacheField>
     <cacheField name="СОП" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-3.9" maxValue="0.59000000000000008"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-3.9" maxValue="0.54500000000000004"/>
     </cacheField>
     <cacheField name="Тип" numFmtId="0">
       <sharedItems containsBlank="1" count="7">
@@ -2883,47 +3078,47 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="76">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="77">
   <r>
     <n v="1"/>
     <s v="PEG17_PHOENIX"/>
-    <n v="161.59999999999997"/>
-    <n v="32.320000000000007"/>
-    <n v="73"/>
-    <n v="50"/>
+    <n v="163.89999999999998"/>
+    <n v="32.780000000000008"/>
+    <n v="78"/>
+    <n v="51"/>
     <n v="0"/>
-    <n v="23"/>
-    <n v="68.493150684931507"/>
-    <n v="2.2136986301369856"/>
-    <n v="0.44273972602739736"/>
+    <n v="27"/>
+    <n v="65.384615384615387"/>
+    <n v="2.1012820512820509"/>
+    <n v="0.42025641025641036"/>
     <x v="0"/>
   </r>
   <r>
     <n v="2"/>
     <s v="WEG3_BATYA"/>
-    <n v="40.700000000000003"/>
-    <n v="8.1400000000000023"/>
-    <n v="54"/>
-    <n v="31"/>
+    <n v="45"/>
+    <n v="9.0000000000000018"/>
+    <n v="56"/>
+    <n v="33"/>
     <n v="1"/>
     <n v="22"/>
-    <n v="57.407407407407405"/>
-    <n v="0.75370370370370376"/>
-    <n v="0.15074074074074079"/>
+    <n v="58.928571428571431"/>
+    <n v="0.8035714285714286"/>
+    <n v="0.16071428571428575"/>
     <x v="1"/>
   </r>
   <r>
     <n v="3"/>
     <s v="PEG11_KUSURUKEN"/>
-    <n v="32.199999999999996"/>
-    <n v="6.4400000000000013"/>
-    <n v="41"/>
-    <n v="20"/>
+    <n v="35.099999999999994"/>
+    <n v="7.0200000000000014"/>
+    <n v="42"/>
+    <n v="21"/>
     <n v="1"/>
     <n v="20"/>
-    <n v="48.780487804878049"/>
-    <n v="0.78536585365853651"/>
-    <n v="0.15707317073170735"/>
+    <n v="50"/>
+    <n v="0.83571428571428563"/>
+    <n v="0.16714285714285718"/>
     <x v="0"/>
   </r>
   <r>
@@ -2942,20 +3137,48 @@
   </r>
   <r>
     <n v="5"/>
-    <s v="UEG8_SOLDIER"/>
-    <n v="17.5"/>
-    <n v="3.5000000000000004"/>
+    <s v="UEG9_GRAVY2"/>
+    <n v="18.700000000000003"/>
+    <n v="3.74"/>
+    <n v="12"/>
     <n v="8"/>
-    <n v="6"/>
     <n v="0"/>
-    <n v="2"/>
-    <n v="75"/>
-    <n v="2.1875"/>
-    <n v="0.43750000000000006"/>
+    <n v="4"/>
+    <n v="66.666666666666657"/>
+    <n v="1.5583333333333336"/>
+    <n v="0.3116666666666667"/>
     <x v="3"/>
   </r>
   <r>
     <n v="6"/>
+    <s v="LEG1_LAKSAe"/>
+    <n v="18.700000000000003"/>
+    <n v="3.74"/>
+    <n v="7"/>
+    <n v="6"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="85.714285714285708"/>
+    <n v="2.6714285714285717"/>
+    <n v="0.53428571428571436"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <s v="UEG8_SOLDIER"/>
+    <n v="16.700000000000003"/>
+    <n v="3.3400000000000007"/>
+    <n v="13"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="61.53846153846154"/>
+    <n v="1.2846153846153849"/>
+    <n v="0.25692307692307698"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="8"/>
     <s v="WEG4_PUPPY"/>
     <n v="16"/>
     <n v="3.1999999999999993"/>
@@ -2969,7 +3192,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="7"/>
+    <n v="9"/>
     <s v="UEG6_ADVENTURE"/>
     <n v="16"/>
     <n v="3.1999999999999993"/>
@@ -2983,7 +3206,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="8"/>
+    <n v="11"/>
     <s v="PEG14_RENEGADE"/>
     <n v="15.7"/>
     <n v="3.1400000000000006"/>
@@ -2995,34 +3218,6 @@
     <n v="1.5699999999999998"/>
     <n v="0.31400000000000006"/>
     <x v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <s v="LEG1_PIN"/>
-    <n v="13.900000000000002"/>
-    <n v="2.7800000000000002"/>
-    <n v="24"/>
-    <n v="12"/>
-    <n v="1"/>
-    <n v="11"/>
-    <n v="50"/>
-    <n v="0.57916666666666672"/>
-    <n v="0.11583333333333334"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="11"/>
-    <s v="LEG1_LAKSAe"/>
-    <n v="13.3"/>
-    <n v="2.66"/>
-    <n v="6"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="83.333333333333343"/>
-    <n v="2.2166666666666668"/>
-    <n v="0.44333333333333336"/>
-    <x v="2"/>
   </r>
   <r>
     <n v="13"/>
@@ -3040,6 +3235,34 @@
   </r>
   <r>
     <n v="12"/>
+    <s v="VEG1_EARTH"/>
+    <n v="12.200000000000001"/>
+    <n v="2.44"/>
+    <n v="7"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="57.142857142857139"/>
+    <n v="1.7428571428571431"/>
+    <n v="0.34857142857142859"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <s v="PEG30_ETC2"/>
+    <n v="10.9"/>
+    <n v="2.1800000000000002"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="2.7250000000000001"/>
+    <n v="0.54500000000000004"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="14"/>
     <s v="LEG1_IGOGOSHA2"/>
     <n v="9.9999999999999982"/>
     <n v="2"/>
@@ -3053,7 +3276,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="10"/>
+    <n v="15"/>
     <s v="LEG2_DRINKER"/>
     <n v="9.6000000000000014"/>
     <n v="1.920000000000001"/>
@@ -3067,21 +3290,49 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="14"/>
+    <n v="17"/>
+    <s v="WEG4_DOG"/>
+    <n v="9.5"/>
+    <n v="1.9"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="50"/>
+    <n v="2.375"/>
+    <n v="0.47499999999999998"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="16"/>
     <s v="PEG18_ANDUIN"/>
-    <n v="9.1"/>
-    <n v="1.8199999999999998"/>
-    <n v="7"/>
+    <n v="9.5"/>
+    <n v="1.9"/>
+    <n v="9"/>
+    <n v="5"/>
+    <n v="0"/>
     <n v="4"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="57.142857142857139"/>
-    <n v="1.3"/>
-    <n v="0.25999999999999995"/>
+    <n v="55.555555555555557"/>
+    <n v="1.0555555555555556"/>
+    <n v="0.21111111111111111"/>
     <x v="0"/>
   </r>
   <r>
-    <n v="15"/>
+    <n v="19"/>
+    <s v="LEG1_PIN"/>
+    <n v="9.2000000000000028"/>
+    <n v="1.8400000000000003"/>
+    <n v="25"/>
+    <n v="12"/>
+    <n v="1"/>
+    <n v="12"/>
+    <n v="48"/>
+    <n v="0.3680000000000001"/>
+    <n v="7.3600000000000013E-2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="18"/>
     <s v="UEG6_SHERIFF"/>
     <n v="9"/>
     <n v="1.7999999999999998"/>
@@ -3095,21 +3346,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="17"/>
-    <s v="VEG1_EARTH"/>
-    <n v="7.3000000000000007"/>
-    <n v="1.46"/>
-    <n v="6"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="50"/>
-    <n v="1.2166666666666668"/>
-    <n v="0.24333333333333332"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="16"/>
+    <n v="20"/>
     <s v="UEG7_LOVERGOOSE"/>
     <n v="7.0000000000000009"/>
     <n v="1.4"/>
@@ -3123,63 +3360,49 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="19"/>
+    <n v="21"/>
     <s v="LEG2_LYNX"/>
-    <n v="6.4999999999999929"/>
-    <n v="1.2999999999999989"/>
-    <n v="26"/>
+    <n v="3.599999999999993"/>
+    <n v="0.71999999999999897"/>
+    <n v="27"/>
     <n v="15"/>
     <n v="0"/>
-    <n v="11"/>
-    <n v="57.692307692307686"/>
-    <n v="0.24999999999999972"/>
-    <n v="4.9999999999999961E-2"/>
+    <n v="12"/>
+    <n v="55.555555555555557"/>
+    <n v="0.13333333333333308"/>
+    <n v="2.666666666666663E-2"/>
     <x v="2"/>
   </r>
   <r>
-    <n v="18"/>
-    <s v="PEG30_ETC2"/>
-    <n v="5.9"/>
-    <n v="1.1800000000000002"/>
+    <n v="22"/>
+    <s v="PEG17_TEMPLAR"/>
+    <n v="2.6000000000000005"/>
+    <n v="0.52000000000000013"/>
     <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="1.3000000000000003"/>
+    <n v="0.26000000000000006"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <s v="UEG4_CANADIAN"/>
     <n v="2"/>
+    <n v="0.4"/>
+    <n v="1"/>
+    <n v="1"/>
     <n v="0"/>
     <n v="0"/>
     <n v="100"/>
-    <n v="2.95"/>
-    <n v="0.59000000000000008"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="20"/>
-    <s v="UEG9_GRAVY2"/>
-    <n v="5.0000000000000018"/>
-    <n v="1.0000000000000007"/>
-    <n v="9"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="55.555555555555557"/>
-    <n v="0.5555555555555558"/>
-    <n v="0.11111111111111119"/>
+    <n v="2"/>
+    <n v="0.4"/>
     <x v="3"/>
   </r>
   <r>
-    <n v="21"/>
-    <s v="WEG4_DOG"/>
-    <n v="2.4000000000000004"/>
-    <n v="0.48000000000000004"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="33.333333333333329"/>
-    <n v="0.80000000000000016"/>
-    <n v="0.16"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="22"/>
+    <n v="24"/>
     <s v="SEG3_FORCE"/>
     <n v="1.9000000000000004"/>
     <n v="0.37999999999999989"/>
@@ -3193,7 +3416,7 @@
     <x v="4"/>
   </r>
   <r>
-    <n v="23"/>
+    <n v="25"/>
     <s v="PEG4_U3"/>
     <n v="1.1999999999999993"/>
     <n v="0.23999999999999988"/>
@@ -3207,7 +3430,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="24"/>
+    <n v="26"/>
     <s v="PEG13_DWDDCr"/>
     <n v="1"/>
     <n v="0.2"/>
@@ -3221,45 +3444,17 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="25"/>
-    <s v="PEG17_SELENDIS"/>
-    <n v="0.9"/>
-    <n v="0.18"/>
-    <n v="1"/>
-    <n v="1"/>
+    <n v="29"/>
+    <s v="UEG7_CANNIBAL"/>
+    <n v="0.5"/>
+    <n v="0.10000000000000026"/>
+    <n v="11"/>
+    <n v="6"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="0.9"/>
-    <n v="0.18"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="26"/>
-    <s v="PEG17_PROBIUS"/>
-    <n v="0.5"/>
-    <n v="0.1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="0.5"/>
-    <n v="0.1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="29"/>
-    <s v="UEG7_ADVENTURE"/>
-    <n v="0.40000000000000024"/>
-    <n v="8.0000000000000016E-2"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="33.333333333333329"/>
-    <n v="0.13333333333333341"/>
-    <n v="2.6666666666666672E-2"/>
+    <n v="5"/>
+    <n v="54.54545454545454"/>
+    <n v="4.5454545454545456E-2"/>
+    <n v="9.0909090909091148E-3"/>
     <x v="3"/>
   </r>
   <r>
@@ -3292,6 +3487,20 @@
   </r>
   <r>
     <n v="35"/>
+    <s v="UEG7_ADVENTURE"/>
+    <n v="-0.69999999999999984"/>
+    <n v="-0.13999999999999999"/>
+    <n v="4"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="25"/>
+    <n v="-0.17499999999999996"/>
+    <n v="-3.4999999999999996E-2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="36"/>
     <s v="LEG2_LOGAN"/>
     <n v="-0.70000000000000107"/>
     <n v="-0.14000000000000012"/>
@@ -3303,20 +3512,6 @@
     <n v="-5.8333333333333424E-2"/>
     <n v="-1.1666666666666678E-2"/>
     <x v="2"/>
-  </r>
-  <r>
-    <n v="36"/>
-    <s v="UEG7_CANNIBAL"/>
-    <n v="-1"/>
-    <n v="-0.19999999999999973"/>
-    <n v="9"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="55.555555555555557"/>
-    <n v="-0.1111111111111111"/>
-    <n v="-2.2222222222222192E-2"/>
-    <x v="3"/>
   </r>
   <r>
     <n v="37"/>
@@ -3362,6 +3557,20 @@
   </r>
   <r>
     <n v="30"/>
+    <s v="PEG17_PROBIUS"/>
+    <n v="-3"/>
+    <n v="-0.60000000000000009"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="-1.5"/>
+    <n v="-0.30000000000000004"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="31"/>
     <s v="UEG6_PIGEON"/>
     <n v="-3.0999999999999983"/>
     <n v="-0.61999999999999988"/>
@@ -3375,7 +3584,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="31"/>
+    <n v="32"/>
     <s v="UEG7_PIGEON"/>
     <n v="-3.0999999999999996"/>
     <n v="-0.61999999999999988"/>
@@ -3389,21 +3598,21 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="32"/>
-    <s v="PEG17_TEMPLAR"/>
-    <n v="-4.3"/>
-    <n v="-0.86"/>
+    <n v="33"/>
+    <s v="PEG17_SELENDIS"/>
+    <n v="-5.6"/>
+    <n v="-1.1200000000000001"/>
+    <n v="2"/>
     <n v="1"/>
     <n v="0"/>
-    <n v="0"/>
     <n v="1"/>
-    <n v="0"/>
-    <n v="-4.3"/>
-    <n v="-0.86"/>
+    <n v="50"/>
+    <n v="-2.8"/>
+    <n v="-0.56000000000000005"/>
     <x v="0"/>
   </r>
   <r>
-    <n v="33"/>
+    <n v="34"/>
     <s v="LEG1_PHOGA"/>
     <n v="-6"/>
     <n v="-1.2"/>
@@ -3417,7 +3626,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="34"/>
+    <n v="40"/>
     <s v="PEG18_UTER"/>
     <n v="-6.2"/>
     <n v="-1.24"/>
@@ -3431,7 +3640,21 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="40"/>
+    <n v="41"/>
+    <s v="PEG31_HYPERION"/>
+    <n v="-7.4999999999999991"/>
+    <n v="-1.4999999999999998"/>
+    <n v="8"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="50"/>
+    <n v="-0.93749999999999989"/>
+    <n v="-0.18749999999999997"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="42"/>
     <s v="PEG26_UNKNOWN"/>
     <n v="-7.5"/>
     <n v="-1.5"/>
@@ -3445,7 +3668,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="41"/>
+    <n v="43"/>
     <s v="LEG1_IRONANNY2"/>
     <n v="-7.5"/>
     <n v="-1.5"/>
@@ -3459,7 +3682,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="42"/>
+    <n v="44"/>
     <s v="WEG7_PARADOX"/>
     <n v="-7.5000000000000009"/>
     <n v="-1.5"/>
@@ -3473,21 +3696,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="43"/>
-    <s v="LEG1_CC2"/>
-    <n v="-8.8999999999999986"/>
-    <n v="-1.7799999999999998"/>
-    <n v="8"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="50"/>
-    <n v="-1.1124999999999998"/>
-    <n v="-0.22249999999999998"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="44"/>
+    <n v="45"/>
     <s v="PEG18_DIABLO2"/>
     <n v="-9.1"/>
     <n v="-1.82"/>
@@ -3501,7 +3710,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="45"/>
+    <n v="46"/>
     <s v="LEG1_BIBI2"/>
     <n v="-9.4000000000000021"/>
     <n v="-1.879999999999999"/>
@@ -3515,7 +3724,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="46"/>
+    <n v="47"/>
     <s v="UEG6_VULTURE"/>
     <n v="-9.6999999999999993"/>
     <n v="-1.9400000000000002"/>
@@ -3527,20 +3736,6 @@
     <n v="-1.2124999999999999"/>
     <n v="-0.24250000000000002"/>
     <x v="3"/>
-  </r>
-  <r>
-    <n v="47"/>
-    <s v="PEG19_ANUBARAK"/>
-    <n v="-9.6999999999999993"/>
-    <n v="-1.94"/>
-    <n v="10"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="6"/>
-    <n v="40"/>
-    <n v="-0.97"/>
-    <n v="-0.19400000000000001"/>
-    <x v="0"/>
   </r>
   <r>
     <n v="48"/>
@@ -3614,48 +3809,90 @@
   </r>
   <r>
     <n v="53"/>
+    <s v="LEG1_CC2"/>
+    <n v="-13.299999999999999"/>
+    <n v="-2.6599999999999997"/>
+    <n v="9"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="44.444444444444443"/>
+    <n v="-1.4777777777777776"/>
+    <n v="-0.29555555555555552"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="54"/>
     <s v="UEG7_CARRIER"/>
     <n v="-13.899999999999999"/>
     <n v="-2.7800000000000002"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="1"/>
     <n v="4"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-3.4749999999999996"/>
-    <n v="-0.69500000000000006"/>
+    <n v="-2.78"/>
+    <n v="-0.55600000000000005"/>
     <x v="3"/>
   </r>
   <r>
-    <n v="54"/>
+    <n v="55"/>
     <s v="LEG2_HOTS"/>
     <n v="-14"/>
     <n v="-2.8"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="1"/>
     <n v="4"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-3.5"/>
-    <n v="-0.7"/>
+    <n v="-2.8"/>
+    <n v="-0.55999999999999994"/>
     <x v="2"/>
   </r>
   <r>
-    <n v="55"/>
+    <n v="56"/>
     <s v="VEG1_MOON"/>
-    <n v="-15.8"/>
-    <n v="-3.16"/>
-    <n v="8"/>
+    <n v="-16.600000000000001"/>
+    <n v="-3.3200000000000003"/>
+    <n v="9"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="6"/>
-    <n v="25"/>
-    <n v="-1.9750000000000001"/>
-    <n v="-0.39500000000000002"/>
+    <n v="7"/>
+    <n v="22.222222222222221"/>
+    <n v="-1.8444444444444446"/>
+    <n v="-0.36888888888888893"/>
     <x v="5"/>
   </r>
   <r>
-    <n v="56"/>
+    <n v="57"/>
+    <s v="PEG19_ANUBARAK"/>
+    <n v="-17.299999999999997"/>
+    <n v="-3.46"/>
+    <n v="11"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="7"/>
+    <n v="36.363636363636367"/>
+    <n v="-1.5727272727272725"/>
+    <n v="-0.31454545454545452"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="58"/>
+    <s v="PEG17_ZEALOT"/>
+    <n v="-18.799999999999997"/>
+    <n v="-3.76"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="33.333333333333329"/>
+    <n v="-6.2666666666666657"/>
+    <n v="-1.2533333333333332"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="59"/>
     <s v="UEG9_BIRDWATCHER2"/>
     <n v="-19.5"/>
     <n v="-3.9"/>
@@ -3669,21 +3906,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="57"/>
-    <s v="PEG17_ZEALOT"/>
-    <n v="-20.099999999999998"/>
-    <n v="-4.0199999999999996"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="-10.049999999999999"/>
-    <n v="-2.0099999999999998"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="58"/>
+    <n v="60"/>
     <s v="VEG1_VENUS"/>
     <n v="-22.700000000000003"/>
     <n v="-4.5399999999999991"/>
@@ -3697,21 +3920,21 @@
     <x v="5"/>
   </r>
   <r>
-    <n v="59"/>
+    <n v="61"/>
     <s v="PEG18_BLAZE"/>
-    <n v="-42.699999999999996"/>
-    <n v="-8.5399999999999991"/>
-    <n v="17"/>
-    <n v="7"/>
+    <n v="-39.599999999999994"/>
+    <n v="-7.919999999999999"/>
+    <n v="18"/>
+    <n v="8"/>
     <n v="1"/>
     <n v="9"/>
-    <n v="41.17647058823529"/>
-    <n v="-2.5117647058823529"/>
-    <n v="-0.50235294117647056"/>
+    <n v="44.444444444444443"/>
+    <n v="-2.1999999999999997"/>
+    <n v="-0.43999999999999995"/>
     <x v="0"/>
   </r>
   <r>
-    <n v="60"/>
+    <n v="62"/>
     <s v="LEG2_ALKASH"/>
     <n v="-42.900000000000006"/>
     <n v="-8.58"/>
@@ -3934,25 +4157,11 @@
     <m/>
     <x v="6"/>
   </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="6"/>
-  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{08A3FD17-FFE6-464D-A72F-02ADC3CE221B}" name="Сводная таблица3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{08A3FD17-FFE6-464D-A72F-02ADC3CE221B}" name="Сводная таблица3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:G10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -4586,22 +4795,22 @@
         <v>116</v>
       </c>
       <c r="B4" s="12">
-        <v>-20.599999999999994</v>
+        <v>-27.200000000000003</v>
       </c>
       <c r="C4" s="12">
-        <v>-4.1199999999999948</v>
+        <v>-5.4399999999999968</v>
       </c>
       <c r="D4" s="12">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E4" s="12">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F4" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="12">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4609,22 +4818,22 @@
         <v>117</v>
       </c>
       <c r="B5" s="12">
-        <v>112.89999999999998</v>
+        <v>109.69999999999996</v>
       </c>
       <c r="C5" s="12">
-        <v>22.580000000000009</v>
+        <v>21.940000000000015</v>
       </c>
       <c r="D5" s="12">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="E5" s="12">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F5" s="12">
         <v>5</v>
       </c>
       <c r="G5" s="12">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4655,22 +4864,22 @@
         <v>119</v>
       </c>
       <c r="B7" s="12">
-        <v>-31.5</v>
+        <v>-16.200000000000003</v>
       </c>
       <c r="C7" s="12">
-        <v>-6.299999999999998</v>
+        <v>-3.2399999999999958</v>
       </c>
       <c r="D7" s="12">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E7" s="12">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F7" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="12">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4678,22 +4887,22 @@
         <v>120</v>
       </c>
       <c r="B8" s="12">
-        <v>-31.200000000000003</v>
+        <v>-27.1</v>
       </c>
       <c r="C8" s="12">
-        <v>-6.2399999999999993</v>
+        <v>-5.42</v>
       </c>
       <c r="D8" s="12">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8" s="12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" s="12">
         <v>0</v>
       </c>
       <c r="G8" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4701,16 +4910,16 @@
         <v>121</v>
       </c>
       <c r="B9" s="12">
-        <v>51.6</v>
+        <v>63</v>
       </c>
       <c r="C9" s="12">
-        <v>10.320000000000002</v>
+        <v>12.600000000000001</v>
       </c>
       <c r="D9" s="12">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E9" s="12">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F9" s="12">
         <v>2</v>
@@ -4724,22 +4933,22 @@
         <v>114</v>
       </c>
       <c r="B10" s="12">
-        <v>95.999999999999972</v>
+        <v>116.99999999999994</v>
       </c>
       <c r="C10" s="12">
-        <v>19.200000000000024</v>
+        <v>23.400000000000027</v>
       </c>
       <c r="D10" s="12">
-        <v>612</v>
+        <v>659</v>
       </c>
       <c r="E10" s="12">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="F10" s="12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10" s="12">
-        <v>282</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -5148,7 +5357,9 @@
       <c r="K2" s="16">
         <v>46300</v>
       </c>
-      <c r="L2" s="16"/>
+      <c r="L2" s="16">
+        <v>46301</v>
+      </c>
       <c r="M2" s="16"/>
       <c r="N2" s="16"/>
       <c r="O2" s="16"/>
@@ -5196,6 +5407,9 @@
       <c r="K3">
         <v>-20.599999999999994</v>
       </c>
+      <c r="L3" s="12">
+        <v>-27.200000000000003</v>
+      </c>
     </row>
     <row r="4" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -5231,6 +5445,9 @@
       <c r="K4">
         <v>112.89999999999998</v>
       </c>
+      <c r="L4" s="12">
+        <v>109.69999999999996</v>
+      </c>
     </row>
     <row r="5" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -5266,6 +5483,9 @@
       <c r="K5">
         <v>14.799999999999997</v>
       </c>
+      <c r="L5" s="12">
+        <v>14.799999999999997</v>
+      </c>
     </row>
     <row r="6" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -5301,6 +5521,9 @@
       <c r="K6">
         <v>-31.5</v>
       </c>
+      <c r="L6" s="12">
+        <v>-16.200000000000003</v>
+      </c>
     </row>
     <row r="7" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -5336,6 +5559,9 @@
       <c r="K7">
         <v>-31.200000000000003</v>
       </c>
+      <c r="L7" s="12">
+        <v>-27.1</v>
+      </c>
     </row>
     <row r="8" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -5371,6 +5597,9 @@
       <c r="K8">
         <v>51.6</v>
       </c>
+      <c r="L8" s="12">
+        <v>63</v>
+      </c>
     </row>
     <row r="9" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -5381,7 +5610,7 @@
         <v>6.8999999999999915</v>
       </c>
       <c r="C9">
-        <f t="shared" ref="C9:K9" si="0">SUM(C3:C8)</f>
+        <f t="shared" ref="C9:L9" si="0">SUM(C3:C8)</f>
         <v>5.7000000000000028</v>
       </c>
       <c r="D9">
@@ -5415,6 +5644,10 @@
       <c r="K9">
         <f t="shared" si="0"/>
         <v>95.999999999999972</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>116.99999999999994</v>
       </c>
     </row>
     <row r="11" spans="1:121" x14ac:dyDescent="0.25">
@@ -5455,8 +5688,12 @@
         <v>46297</v>
       </c>
       <c r="K11" s="16">
-        <f t="shared" ref="K11" si="2">K2</f>
+        <f t="shared" ref="K11:L11" si="2">K2</f>
         <v>46300</v>
+      </c>
+      <c r="L11" s="16">
+        <f t="shared" si="2"/>
+        <v>46301</v>
       </c>
     </row>
     <row r="12" spans="1:121" x14ac:dyDescent="0.25">
@@ -5472,7 +5709,7 @@
         <v>-19.799999999999997</v>
       </c>
       <c r="D12">
-        <f t="shared" ref="D12:K12" si="3">D3-C3</f>
+        <f t="shared" ref="D12:L12" si="3">D3-C3</f>
         <v>17.799999999999997</v>
       </c>
       <c r="E12">
@@ -5503,6 +5740,10 @@
         <f t="shared" si="3"/>
         <v>-32.299999999999976</v>
       </c>
+      <c r="L12">
+        <f t="shared" si="3"/>
+        <v>-6.6000000000000085</v>
+      </c>
     </row>
     <row r="13" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -5513,7 +5754,7 @@
         <v>19.7</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:K17" si="5">C4-B4</f>
+        <f t="shared" ref="C13:L17" si="5">C4-B4</f>
         <v>31.000000000000004</v>
       </c>
       <c r="D13">
@@ -5548,6 +5789,10 @@
         <f t="shared" si="5"/>
         <v>4.1999999999999602</v>
       </c>
+      <c r="L13">
+        <f t="shared" si="5"/>
+        <v>-3.2000000000000171</v>
+      </c>
     </row>
     <row r="14" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -5593,6 +5838,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="L14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -5638,6 +5887,10 @@
         <f t="shared" si="5"/>
         <v>-16.500000000000007</v>
       </c>
+      <c r="L15">
+        <f t="shared" si="5"/>
+        <v>15.299999999999997</v>
+      </c>
     </row>
     <row r="16" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -5683,8 +5936,12 @@
         <f t="shared" si="5"/>
         <v>23.6</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16">
+        <f t="shared" si="5"/>
+        <v>4.1000000000000014</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -5728,8 +5985,12 @@
         <f t="shared" si="5"/>
         <v>-14.500000000000007</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17">
+        <f t="shared" si="5"/>
+        <v>11.399999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>139</v>
       </c>
@@ -5770,8 +6031,12 @@
         <v>24.700000000000017</v>
       </c>
       <c r="K18">
-        <f t="shared" ref="K18" si="13">SUM(K12:K17)</f>
+        <f t="shared" ref="K18:L18" si="13">SUM(K12:K17)</f>
         <v>-35.500000000000028</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="13"/>
+        <v>20.999999999999972</v>
       </c>
     </row>
   </sheetData>
@@ -5878,34 +6143,34 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>161.59999999999997</v>
+        <v>163.89999999999998</v>
       </c>
       <c r="D2">
-        <v>32.320000000000007</v>
+        <v>32.780000000000008</v>
       </c>
       <c r="E2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I2" s="7">
         <f>IFERROR((F2/E2)*100,0)</f>
-        <v>68.493150684931507</v>
+        <v>65.384615384615387</v>
       </c>
       <c r="J2" s="10">
         <f>IFERROR(C2/E2,0)</f>
-        <v>2.2136986301369856</v>
+        <v>2.1012820512820509</v>
       </c>
       <c r="K2" s="10">
         <f>IFERROR(D2/E2,0)</f>
-        <v>0.44273972602739736</v>
+        <v>0.42025641025641036</v>
       </c>
       <c r="L2" s="10" t="str">
         <f>LEFT(B2,3)</f>
@@ -5913,19 +6178,19 @@
       </c>
       <c r="N2">
         <f t="shared" ref="N2:S2" si="0">C2+U2</f>
-        <v>161.59999999999997</v>
+        <v>163.89999999999998</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>32.320000000000007</v>
+        <v>32.780000000000008</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
@@ -5933,7 +6198,7 @@
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -5944,16 +6209,16 @@
         <v>56</v>
       </c>
       <c r="C3">
-        <v>40.700000000000003</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>8.1400000000000023</v>
+        <v>9.0000000000000018</v>
       </c>
       <c r="E3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -5963,15 +6228,15 @@
       </c>
       <c r="I3" s="7">
         <f>IFERROR((F3/E3)*100,0)</f>
-        <v>57.407407407407405</v>
+        <v>58.928571428571431</v>
       </c>
       <c r="J3" s="10">
         <f>IFERROR(C3/E3,0)</f>
-        <v>0.75370370370370376</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="K3" s="10">
         <f>IFERROR(D3/E3,0)</f>
-        <v>0.15074074074074079</v>
+        <v>0.16071428571428575</v>
       </c>
       <c r="L3" s="10" t="str">
         <f>LEFT(B3,3)</f>
@@ -5979,19 +6244,19 @@
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N53" si="1">C3+U3</f>
-        <v>40.700000000000003</v>
+        <v>45</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O17" si="2">D3+V3</f>
-        <v>8.1400000000000023</v>
+        <v>9.0000000000000018</v>
       </c>
       <c r="P3">
         <f t="shared" ref="P3:P17" si="3">E3+W3</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q17" si="4">F3+X3</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R17" si="5">G3+Y3</f>
@@ -6010,16 +6275,16 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>32.199999999999996</v>
+        <v>35.099999999999994</v>
       </c>
       <c r="D4">
-        <v>6.4400000000000013</v>
+        <v>7.0200000000000014</v>
       </c>
       <c r="E4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -6029,15 +6294,15 @@
       </c>
       <c r="I4" s="7">
         <f>IFERROR((F4/E4)*100,0)</f>
-        <v>48.780487804878049</v>
+        <v>50</v>
       </c>
       <c r="J4" s="10">
         <f>IFERROR(C4/E4,0)</f>
-        <v>0.78536585365853651</v>
+        <v>0.83571428571428563</v>
       </c>
       <c r="K4" s="10">
         <f>IFERROR(D4/E4,0)</f>
-        <v>0.15707317073170735</v>
+        <v>0.16714285714285718</v>
       </c>
       <c r="L4" s="10" t="str">
         <f>LEFT(B4,3)</f>
@@ -6045,19 +6310,19 @@
       </c>
       <c r="N4">
         <f t="shared" si="1"/>
-        <v>32.199999999999996</v>
+        <v>35.099999999999994</v>
       </c>
       <c r="O4">
         <f t="shared" si="2"/>
-        <v>6.4400000000000013</v>
+        <v>7.0200000000000014</v>
       </c>
       <c r="P4">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q4">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R4">
         <f t="shared" si="5"/>
@@ -6139,37 +6404,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C6">
-        <v>17.5</v>
+        <v>18.700000000000003</v>
       </c>
       <c r="D6">
-        <v>3.5000000000000004</v>
+        <v>3.74</v>
       </c>
       <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" s="7">
         <f>IFERROR((F6/E6)*100,0)</f>
-        <v>75</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J6" s="10">
         <f>IFERROR(C6/E6,0)</f>
-        <v>2.1875</v>
+        <v>1.5583333333333336</v>
       </c>
       <c r="K6" s="10">
         <f>IFERROR(D6/E6,0)</f>
-        <v>0.43750000000000006</v>
+        <v>0.3116666666666667</v>
       </c>
       <c r="L6" s="10" t="str">
         <f>LEFT(B6,3)</f>
@@ -6177,19 +6442,19 @@
       </c>
       <c r="N6">
         <f t="shared" si="1"/>
-        <v>17.5</v>
+        <v>18.700000000000003</v>
       </c>
       <c r="O6">
         <f t="shared" si="2"/>
-        <v>3.5000000000000004</v>
+        <v>3.74</v>
       </c>
       <c r="P6">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q6">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <f t="shared" si="5"/>
@@ -6197,111 +6462,111 @@
       </c>
       <c r="S6">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>58</v>
+      <c r="B7" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>18.700000000000003</v>
       </c>
       <c r="D7">
-        <v>3.1999999999999993</v>
+        <v>3.74</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>1</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
       </c>
       <c r="I7" s="7">
         <f>IFERROR((F7/E7)*100,0)</f>
-        <v>61.53846153846154</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="J7" s="10">
         <f>IFERROR(C7/E7,0)</f>
-        <v>1.2307692307692308</v>
+        <v>2.6714285714285717</v>
       </c>
       <c r="K7" s="10">
         <f>IFERROR(D7/E7,0)</f>
-        <v>0.24615384615384611</v>
+        <v>0.53428571428571436</v>
       </c>
       <c r="L7" s="10" t="str">
         <f>LEFT(B7,3)</f>
-        <v>WEG</v>
+        <v>LEG</v>
       </c>
       <c r="N7">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>18.700000000000003</v>
       </c>
       <c r="O7">
         <f t="shared" si="2"/>
-        <v>3.1999999999999993</v>
+        <v>3.74</v>
       </c>
       <c r="P7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R7">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>85</v>
+      <c r="B8" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="C8">
-        <v>16</v>
+        <v>16.700000000000003</v>
       </c>
       <c r="D8">
-        <v>3.1999999999999993</v>
+        <v>3.3400000000000007</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I8" s="7">
         <f>IFERROR((F8/E8)*100,0)</f>
-        <v>47.368421052631575</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="J8" s="10">
         <f>IFERROR(C8/E8,0)</f>
-        <v>0.84210526315789469</v>
+        <v>1.2846153846153849</v>
       </c>
       <c r="K8" s="10">
         <f>IFERROR(D8/E8,0)</f>
-        <v>0.16842105263157892</v>
+        <v>0.25692307692307698</v>
       </c>
       <c r="L8" s="10" t="str">
         <f>LEFT(B8,3)</f>
@@ -6309,27 +6574,27 @@
       </c>
       <c r="N8">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>16.700000000000003</v>
       </c>
       <c r="O8">
         <f t="shared" si="2"/>
-        <v>3.1999999999999993</v>
+        <v>3.3400000000000007</v>
       </c>
       <c r="P8">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -6337,65 +6602,65 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C9">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>3.1400000000000006</v>
+        <v>3.1999999999999993</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I9" s="7">
         <f>IFERROR((F9/E9)*100,0)</f>
-        <v>50</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="J9" s="10">
         <f>IFERROR(C9/E9,0)</f>
-        <v>1.5699999999999998</v>
+        <v>1.2307692307692308</v>
       </c>
       <c r="K9" s="10">
         <f>IFERROR(D9/E9,0)</f>
-        <v>0.31400000000000006</v>
+        <v>0.24615384615384611</v>
       </c>
       <c r="L9" s="10" t="str">
         <f>LEFT(B9,3)</f>
-        <v>PEG</v>
+        <v>WEG</v>
       </c>
       <c r="N9">
         <f t="shared" si="1"/>
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="O9">
         <f t="shared" si="2"/>
-        <v>3.1400000000000006</v>
+        <v>3.1999999999999993</v>
       </c>
       <c r="P9">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q9">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -6403,82 +6668,82 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C10">
-        <v>13.900000000000002</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>2.7800000000000002</v>
+        <v>3.1999999999999993</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I10" s="7">
         <f>IFERROR((F10/E10)*100,0)</f>
-        <v>50</v>
+        <v>47.368421052631575</v>
       </c>
       <c r="J10" s="10">
         <f>IFERROR(C10/E10,0)</f>
-        <v>0.57916666666666672</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="K10" s="10">
         <f>IFERROR(D10/E10,0)</f>
-        <v>0.11583333333333334</v>
+        <v>0.16842105263157892</v>
       </c>
       <c r="L10" s="10" t="str">
         <f>LEFT(B10,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N10">
         <f t="shared" si="1"/>
-        <v>13.900000000000002</v>
+        <v>16</v>
       </c>
       <c r="O10">
         <f t="shared" si="2"/>
-        <v>2.7800000000000002</v>
+        <v>3.1999999999999993</v>
       </c>
       <c r="P10">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q10">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S10">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>68</v>
+      <c r="B11" t="s">
+        <v>61</v>
       </c>
       <c r="C11">
-        <v>13.3</v>
+        <v>15.7</v>
       </c>
       <c r="D11">
-        <v>2.66</v>
+        <v>3.1400000000000006</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6487,35 +6752,35 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7">
         <f>IFERROR((F11/E11)*100,0)</f>
-        <v>83.333333333333343</v>
+        <v>50</v>
       </c>
       <c r="J11" s="10">
         <f>IFERROR(C11/E11,0)</f>
-        <v>2.2166666666666668</v>
+        <v>1.5699999999999998</v>
       </c>
       <c r="K11" s="10">
         <f>IFERROR(D11/E11,0)</f>
-        <v>0.44333333333333336</v>
+        <v>0.31400000000000006</v>
       </c>
       <c r="L11" s="10" t="str">
         <f>LEFT(B11,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N11">
         <f t="shared" si="1"/>
-        <v>13.3</v>
+        <v>15.7</v>
       </c>
       <c r="O11">
         <f t="shared" si="2"/>
-        <v>2.66</v>
+        <v>3.1400000000000006</v>
       </c>
       <c r="P11">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <f t="shared" si="4"/>
@@ -6527,7 +6792,7 @@
       </c>
       <c r="S11">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -6601,57 +6866,57 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="C13">
-        <v>9.9999999999999982</v>
+        <v>12.200000000000001</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>3</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>2</v>
       </c>
       <c r="I13" s="7">
         <f>IFERROR((F13/E13)*100,0)</f>
-        <v>60</v>
+        <v>57.142857142857139</v>
       </c>
       <c r="J13" s="10">
         <f>IFERROR(C13/E13,0)</f>
-        <v>1.9999999999999996</v>
+        <v>1.7428571428571431</v>
       </c>
       <c r="K13" s="10">
         <f>IFERROR(D13/E13,0)</f>
-        <v>0.4</v>
+        <v>0.34857142857142859</v>
       </c>
       <c r="L13" s="10" t="str">
         <f>LEFT(B13,3)</f>
-        <v>LEG</v>
+        <v>VEG</v>
       </c>
       <c r="N13">
         <f t="shared" si="1"/>
-        <v>9.9999999999999982</v>
+        <v>12.200000000000001</v>
       </c>
       <c r="O13">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="P13">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R13">
         <f t="shared" si="5"/>
@@ -6659,65 +6924,65 @@
       </c>
       <c r="S13">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
-      <c r="B14" t="s">
-        <v>55</v>
+      <c r="B14" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="C14">
-        <v>9.6000000000000014</v>
+        <v>10.9</v>
       </c>
       <c r="D14">
-        <v>1.920000000000001</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="E14">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I14" s="7">
         <f>IFERROR((F14/E14)*100,0)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J14" s="10">
         <f>IFERROR(C14/E14,0)</f>
-        <v>0.43636363636363645</v>
+        <v>2.7250000000000001</v>
       </c>
       <c r="K14" s="10">
         <f>IFERROR(D14/E14,0)</f>
-        <v>8.7272727272727321E-2</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="L14" s="10" t="str">
         <f>LEFT(B14,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N14">
         <f t="shared" si="1"/>
-        <v>9.6000000000000014</v>
+        <v>10.9</v>
       </c>
       <c r="O14">
         <f t="shared" si="2"/>
-        <v>1.920000000000001</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="P14">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="Q14">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R14">
         <f t="shared" si="5"/>
@@ -6725,65 +6990,65 @@
       </c>
       <c r="S14">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>94</v>
+      <c r="B15" t="s">
+        <v>97</v>
       </c>
       <c r="C15">
-        <v>9.1</v>
+        <v>9.9999999999999982</v>
       </c>
       <c r="D15">
-        <v>1.8199999999999998</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15" s="7">
         <f>IFERROR((F15/E15)*100,0)</f>
-        <v>57.142857142857139</v>
+        <v>60</v>
       </c>
       <c r="J15" s="10">
         <f>IFERROR(C15/E15,0)</f>
-        <v>1.3</v>
+        <v>1.9999999999999996</v>
       </c>
       <c r="K15" s="10">
         <f>IFERROR(D15/E15,0)</f>
-        <v>0.25999999999999995</v>
+        <v>0.4</v>
       </c>
       <c r="L15" s="10" t="str">
         <f>LEFT(B15,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N15">
         <f t="shared" si="1"/>
-        <v>9.1</v>
+        <v>9.9999999999999982</v>
       </c>
       <c r="O15">
         <f t="shared" si="2"/>
-        <v>1.8199999999999998</v>
+        <v>2</v>
       </c>
       <c r="P15">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R15">
         <f t="shared" si="5"/>
@@ -6791,7 +7056,7 @@
       </c>
       <c r="S15">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -6799,25 +7064,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="C16">
-        <v>9</v>
+        <v>9.6000000000000014</v>
       </c>
       <c r="D16">
-        <v>1.7999999999999998</v>
+        <v>1.920000000000001</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I16" s="7">
         <f>IFERROR((F16/E16)*100,0)</f>
@@ -6825,31 +7090,31 @@
       </c>
       <c r="J16" s="10">
         <f>IFERROR(C16/E16,0)</f>
-        <v>1.5</v>
+        <v>0.43636363636363645</v>
       </c>
       <c r="K16" s="10">
         <f>IFERROR(D16/E16,0)</f>
-        <v>0.3</v>
+        <v>8.7272727272727321E-2</v>
       </c>
       <c r="L16" s="10" t="str">
         <f>LEFT(B16,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N16">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>9.6000000000000014</v>
       </c>
       <c r="O16">
         <f t="shared" si="2"/>
-        <v>1.7999999999999998</v>
+        <v>1.920000000000001</v>
       </c>
       <c r="P16">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="Q16">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="R16">
         <f t="shared" si="5"/>
@@ -6857,7 +7122,7 @@
       </c>
       <c r="S16">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -6865,25 +7130,25 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C17">
-        <v>7.3000000000000007</v>
+        <v>9.5</v>
       </c>
       <c r="D17">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" s="7">
         <f>IFERROR((F17/E17)*100,0)</f>
@@ -6891,31 +7156,31 @@
       </c>
       <c r="J17" s="10">
         <f>IFERROR(C17/E17,0)</f>
-        <v>1.2166666666666668</v>
+        <v>2.375</v>
       </c>
       <c r="K17" s="10">
         <f>IFERROR(D17/E17,0)</f>
-        <v>0.24333333333333332</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="L17" s="10" t="str">
         <f>LEFT(B17,3)</f>
-        <v>VEG</v>
+        <v>WEG</v>
       </c>
       <c r="N17">
         <f t="shared" si="1"/>
-        <v>7.3000000000000007</v>
+        <v>9.5</v>
       </c>
       <c r="O17">
         <f t="shared" si="2"/>
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="P17">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q17">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R17">
         <f t="shared" si="5"/>
@@ -6923,7 +7188,7 @@
       </c>
       <c r="S17">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -6931,57 +7196,57 @@
         <v>16</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="C18">
-        <v>7.0000000000000009</v>
+        <v>9.5</v>
       </c>
       <c r="D18">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="E18">
+        <v>9</v>
+      </c>
+      <c r="F18">
         <v>5</v>
       </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I18" s="7">
         <f>IFERROR((F18/E18)*100,0)</f>
-        <v>60</v>
+        <v>55.555555555555557</v>
       </c>
       <c r="J18" s="10">
         <f>IFERROR(C18/E18,0)</f>
-        <v>1.4000000000000001</v>
+        <v>1.0555555555555556</v>
       </c>
       <c r="K18" s="10">
         <f>IFERROR(D18/E18,0)</f>
-        <v>0.27999999999999997</v>
+        <v>0.21111111111111111</v>
       </c>
       <c r="L18" s="10" t="str">
         <f>LEFT(B18,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N18">
         <f t="shared" si="1"/>
-        <v>7.0000000000000009</v>
+        <v>9.5</v>
       </c>
       <c r="O18">
         <f t="shared" ref="O18:O53" si="7">D18+V18</f>
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="P18">
         <f t="shared" ref="P18:P53" si="8">E18+W18</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <f t="shared" ref="Q18:Q53" si="9">F18+X18</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <f t="shared" ref="R18:R47" si="10">G18+Y18</f>
@@ -6989,7 +7254,7 @@
       </c>
       <c r="S18">
         <f t="shared" ref="S18:S47" si="11">H18+Z18</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -6997,37 +7262,37 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C19">
-        <v>6.4999999999999929</v>
+        <v>9.2000000000000028</v>
       </c>
       <c r="D19">
-        <v>1.2999999999999989</v>
+        <v>1.8400000000000003</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I19" s="7">
         <f>IFERROR((F19/E19)*100,0)</f>
-        <v>57.692307692307686</v>
+        <v>48</v>
       </c>
       <c r="J19" s="10">
         <f>IFERROR(C19/E19,0)</f>
-        <v>0.24999999999999972</v>
+        <v>0.3680000000000001</v>
       </c>
       <c r="K19" s="10">
         <f>IFERROR(D19/E19,0)</f>
-        <v>4.9999999999999961E-2</v>
+        <v>7.3600000000000013E-2</v>
       </c>
       <c r="L19" s="10" t="str">
         <f>LEFT(B19,3)</f>
@@ -7035,85 +7300,85 @@
       </c>
       <c r="N19">
         <f t="shared" si="1"/>
-        <v>6.4999999999999929</v>
+        <v>9.2000000000000028</v>
       </c>
       <c r="O19">
         <f t="shared" si="7"/>
-        <v>1.2999999999999989</v>
+        <v>1.8400000000000003</v>
       </c>
       <c r="P19">
         <f t="shared" si="8"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q19">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R19">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19">
         <f t="shared" si="11"/>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>140</v>
+      <c r="B20" t="s">
+        <v>86</v>
       </c>
       <c r="C20">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>1.1800000000000002</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" s="7">
         <f>IFERROR((F20/E20)*100,0)</f>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J20" s="10">
         <f>IFERROR(C20/E20,0)</f>
-        <v>2.95</v>
+        <v>1.5</v>
       </c>
       <c r="K20" s="10">
         <f>IFERROR(D20/E20,0)</f>
-        <v>0.59000000000000008</v>
+        <v>0.3</v>
       </c>
       <c r="L20" s="10" t="str">
         <f>LEFT(B20,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N20">
         <f t="shared" si="1"/>
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <f t="shared" si="7"/>
-        <v>1.1800000000000002</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="P20">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R20">
         <f t="shared" si="10"/>
@@ -7121,7 +7386,7 @@
       </c>
       <c r="S20">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -7129,37 +7394,37 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C21">
-        <v>5.0000000000000018</v>
+        <v>7.0000000000000009</v>
       </c>
       <c r="D21">
-        <v>1.0000000000000007</v>
+        <v>1.4</v>
       </c>
       <c r="E21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" s="7">
         <f>IFERROR((F21/E21)*100,0)</f>
-        <v>55.555555555555557</v>
+        <v>60</v>
       </c>
       <c r="J21" s="10">
         <f>IFERROR(C21/E21,0)</f>
-        <v>0.5555555555555558</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="K21" s="10">
         <f>IFERROR(D21/E21,0)</f>
-        <v>0.11111111111111119</v>
+        <v>0.27999999999999997</v>
       </c>
       <c r="L21" s="10" t="str">
         <f>LEFT(B21,3)</f>
@@ -7167,19 +7432,19 @@
       </c>
       <c r="N21">
         <f t="shared" si="1"/>
-        <v>5.0000000000000018</v>
+        <v>7.0000000000000009</v>
       </c>
       <c r="O21">
         <f t="shared" si="7"/>
-        <v>1.0000000000000007</v>
+        <v>1.4</v>
       </c>
       <c r="P21">
         <f t="shared" si="8"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R21">
         <f t="shared" si="10"/>
@@ -7187,7 +7452,7 @@
       </c>
       <c r="S21">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -7195,57 +7460,57 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="C22">
-        <v>2.4000000000000004</v>
+        <v>3.599999999999993</v>
       </c>
       <c r="D22">
-        <v>0.48000000000000004</v>
+        <v>0.71999999999999897</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I22" s="7">
         <f>IFERROR((F22/E22)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>55.555555555555557</v>
       </c>
       <c r="J22" s="10">
         <f>IFERROR(C22/E22,0)</f>
-        <v>0.80000000000000016</v>
+        <v>0.13333333333333308</v>
       </c>
       <c r="K22" s="10">
         <f>IFERROR(D22/E22,0)</f>
-        <v>0.16</v>
+        <v>2.666666666666663E-2</v>
       </c>
       <c r="L22" s="10" t="str">
         <f>LEFT(B22,3)</f>
-        <v>WEG</v>
+        <v>LEG</v>
       </c>
       <c r="N22">
         <f t="shared" si="1"/>
-        <v>2.4000000000000004</v>
+        <v>3.599999999999993</v>
       </c>
       <c r="O22">
         <f t="shared" si="7"/>
-        <v>0.48000000000000004</v>
+        <v>0.71999999999999897</v>
       </c>
       <c r="P22">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="Q22">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R22">
         <f t="shared" si="10"/>
@@ -7253,65 +7518,65 @@
       </c>
       <c r="S22">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>73</v>
+      <c r="B23" s="8" t="s">
+        <v>143</v>
       </c>
       <c r="C23">
-        <v>1.9000000000000004</v>
+        <v>2.6000000000000005</v>
       </c>
       <c r="D23">
-        <v>0.37999999999999989</v>
+        <v>0.52000000000000013</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="7">
         <f>IFERROR((F23/E23)*100,0)</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J23" s="10">
         <f>IFERROR(C23/E23,0)</f>
-        <v>0.38000000000000006</v>
+        <v>1.3000000000000003</v>
       </c>
       <c r="K23" s="10">
         <f>IFERROR(D23/E23,0)</f>
-        <v>7.5999999999999984E-2</v>
+        <v>0.26000000000000006</v>
       </c>
       <c r="L23" s="10" t="str">
         <f>LEFT(B23,3)</f>
-        <v>SEG</v>
+        <v>PEG</v>
       </c>
       <c r="N23">
         <f t="shared" si="1"/>
-        <v>1.9000000000000004</v>
+        <v>2.6000000000000005</v>
       </c>
       <c r="O23">
         <f t="shared" si="7"/>
-        <v>0.37999999999999989</v>
+        <v>0.52000000000000013</v>
       </c>
       <c r="P23">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q23">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R23">
         <f t="shared" si="10"/>
@@ -7319,131 +7584,131 @@
       </c>
       <c r="S23">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>63</v>
+      <c r="B24" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="C24">
-        <v>1.1999999999999993</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>0.23999999999999988</v>
+        <v>0.4</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" s="7">
         <f>IFERROR((F24/E24)*100,0)</f>
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="J24" s="10">
         <f>IFERROR(C24/E24,0)</f>
-        <v>0.14999999999999991</v>
+        <v>2</v>
       </c>
       <c r="K24" s="10">
         <f>IFERROR(D24/E24,0)</f>
-        <v>2.9999999999999985E-2</v>
+        <v>0.4</v>
       </c>
       <c r="L24" s="10" t="str">
         <f>LEFT(B24,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N24">
         <f t="shared" si="1"/>
-        <v>1.1999999999999993</v>
+        <v>2</v>
       </c>
       <c r="O24">
         <f t="shared" si="7"/>
-        <v>0.23999999999999988</v>
+        <v>0.4</v>
       </c>
       <c r="P24">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q24">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R24">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>74</v>
+      <c r="B25" t="s">
+        <v>73</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="D25">
-        <v>0.2</v>
+        <v>0.37999999999999989</v>
       </c>
       <c r="E25">
+        <v>5</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>2</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
       </c>
       <c r="I25" s="7">
         <f>IFERROR((F25/E25)*100,0)</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J25" s="10">
         <f>IFERROR(C25/E25,0)</f>
-        <v>0.5</v>
+        <v>0.38000000000000006</v>
       </c>
       <c r="K25" s="10">
         <f>IFERROR(D25/E25,0)</f>
-        <v>0.1</v>
+        <v>7.5999999999999984E-2</v>
       </c>
       <c r="L25" s="10" t="str">
         <f>LEFT(B25,3)</f>
-        <v>PEG</v>
+        <v>SEG</v>
       </c>
       <c r="N25">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="O25">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.37999999999999989</v>
       </c>
       <c r="P25">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R25">
         <f t="shared" si="10"/>
@@ -7451,45 +7716,45 @@
       </c>
       <c r="S25">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>142</v>
+      <c r="B26" t="s">
+        <v>63</v>
       </c>
       <c r="C26">
-        <v>0.9</v>
+        <v>1.1999999999999993</v>
       </c>
       <c r="D26">
-        <v>0.18</v>
+        <v>0.23999999999999988</v>
       </c>
       <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
         <v>1</v>
       </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
       <c r="H26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" s="7">
         <f>IFERROR((F26/E26)*100,0)</f>
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="J26" s="10">
         <f>IFERROR(C26/E26,0)</f>
-        <v>0.9</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="K26" s="10">
         <f>IFERROR(D26/E26,0)</f>
-        <v>0.18</v>
+        <v>2.9999999999999985E-2</v>
       </c>
       <c r="L26" s="10" t="str">
         <f>LEFT(B26,3)</f>
@@ -7497,27 +7762,27 @@
       </c>
       <c r="N26">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>1.1999999999999993</v>
       </c>
       <c r="O26">
         <f t="shared" si="7"/>
-        <v>0.18</v>
+        <v>0.23999999999999988</v>
       </c>
       <c r="P26">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -7525,16 +7790,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="C27">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -7543,11 +7808,11 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="7">
         <f>IFERROR((F27/E27)*100,0)</f>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J27" s="10">
         <f>IFERROR(C27/E27,0)</f>
@@ -7563,15 +7828,15 @@
       </c>
       <c r="N27">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O27">
         <f t="shared" si="7"/>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="P27">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27">
         <f t="shared" si="9"/>
@@ -7583,7 +7848,7 @@
       </c>
       <c r="S27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -7591,37 +7856,37 @@
         <v>29</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="C28">
-        <v>0.40000000000000024</v>
+        <v>0.5</v>
       </c>
       <c r="D28">
-        <v>8.0000000000000016E-2</v>
+        <v>0.10000000000000026</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I28" s="7">
         <f>IFERROR((F28/E28)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="J28" s="10">
         <f>IFERROR(C28/E28,0)</f>
-        <v>0.13333333333333341</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="K28" s="10">
         <f>IFERROR(D28/E28,0)</f>
-        <v>2.6666666666666672E-2</v>
+        <v>9.0909090909091148E-3</v>
       </c>
       <c r="L28" s="10" t="str">
         <f>LEFT(B28,3)</f>
@@ -7629,19 +7894,19 @@
       </c>
       <c r="N28">
         <f t="shared" si="1"/>
-        <v>0.40000000000000024</v>
+        <v>0.5</v>
       </c>
       <c r="O28">
         <f t="shared" si="7"/>
-        <v>8.0000000000000016E-2</v>
+        <v>0.10000000000000026</v>
       </c>
       <c r="P28">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q28">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R28">
         <f t="shared" si="10"/>
@@ -7649,7 +7914,7 @@
       </c>
       <c r="S28">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -7788,20 +8053,20 @@
       <c r="A31">
         <v>35</v>
       </c>
-      <c r="B31" t="s">
-        <v>81</v>
+      <c r="B31" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="C31">
-        <v>-0.70000000000000107</v>
+        <v>-0.69999999999999984</v>
       </c>
       <c r="D31">
-        <v>-0.14000000000000012</v>
+        <v>-0.13999999999999999</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -7811,35 +8076,35 @@
       </c>
       <c r="I31" s="7">
         <f>IFERROR((F31/E31)*100,0)</f>
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="J31" s="10">
         <f>IFERROR(C31/E31,0)</f>
-        <v>-5.8333333333333424E-2</v>
+        <v>-0.17499999999999996</v>
       </c>
       <c r="K31" s="10">
         <f>IFERROR(D31/E31,0)</f>
-        <v>-1.1666666666666678E-2</v>
+        <v>-3.4999999999999996E-2</v>
       </c>
       <c r="L31" s="10" t="str">
         <f>LEFT(B31,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N31">
         <f t="shared" si="1"/>
-        <v>-0.70000000000000107</v>
+        <v>-0.69999999999999984</v>
       </c>
       <c r="O31">
         <f t="shared" si="7"/>
-        <v>-0.14000000000000012</v>
+        <v>-0.13999999999999999</v>
       </c>
       <c r="P31">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q31">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R31">
         <f t="shared" si="10"/>
@@ -7854,58 +8119,58 @@
       <c r="A32">
         <v>36</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>133</v>
+      <c r="B32" t="s">
+        <v>81</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>-0.70000000000000107</v>
       </c>
       <c r="D32">
-        <v>-0.19999999999999973</v>
+        <v>-0.14000000000000012</v>
       </c>
       <c r="E32">
+        <v>12</v>
+      </c>
+      <c r="F32">
         <v>9</v>
       </c>
-      <c r="F32">
-        <v>5</v>
-      </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I32" s="7">
         <f>IFERROR((F32/E32)*100,0)</f>
-        <v>55.555555555555557</v>
+        <v>75</v>
       </c>
       <c r="J32" s="10">
         <f>IFERROR(C32/E32,0)</f>
-        <v>-0.1111111111111111</v>
+        <v>-5.8333333333333424E-2</v>
       </c>
       <c r="K32" s="10">
         <f>IFERROR(D32/E32,0)</f>
-        <v>-2.2222222222222192E-2</v>
+        <v>-1.1666666666666678E-2</v>
       </c>
       <c r="L32" s="10" t="str">
         <f>LEFT(B32,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N32">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.70000000000000107</v>
       </c>
       <c r="O32">
         <f t="shared" si="7"/>
-        <v>-0.19999999999999973</v>
+        <v>-0.14000000000000012</v>
       </c>
       <c r="P32">
         <f t="shared" si="8"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q32">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <f t="shared" si="10"/>
@@ -7913,7 +8178,7 @@
       </c>
       <c r="S32">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
@@ -8118,58 +8383,58 @@
       <c r="A36">
         <v>30</v>
       </c>
-      <c r="B36" t="s">
-        <v>72</v>
+      <c r="B36" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="C36">
-        <v>-3.0999999999999983</v>
+        <v>-3</v>
       </c>
       <c r="D36">
-        <v>-0.61999999999999988</v>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="E36">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I36" s="7">
         <f>IFERROR((F36/E36)*100,0)</f>
-        <v>38.461538461538467</v>
+        <v>50</v>
       </c>
       <c r="J36" s="10">
         <f>IFERROR(C36/E36,0)</f>
-        <v>-0.23846153846153834</v>
+        <v>-1.5</v>
       </c>
       <c r="K36" s="10">
         <f>IFERROR(D36/E36,0)</f>
-        <v>-4.7692307692307687E-2</v>
+        <v>-0.30000000000000004</v>
       </c>
       <c r="L36" s="10" t="str">
         <f>LEFT(B36,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N36">
         <f t="shared" si="1"/>
-        <v>-3.0999999999999983</v>
+        <v>-3</v>
       </c>
       <c r="O36">
         <f t="shared" si="7"/>
-        <v>-0.61999999999999988</v>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="P36">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Q36">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R36">
         <f t="shared" si="10"/>
@@ -8177,7 +8442,7 @@
       </c>
       <c r="S36">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
@@ -8185,37 +8450,37 @@
         <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C37">
-        <v>-3.0999999999999996</v>
+        <v>-3.0999999999999983</v>
       </c>
       <c r="D37">
         <v>-0.61999999999999988</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I37" s="7">
         <f>IFERROR((F37/E37)*100,0)</f>
-        <v>25</v>
+        <v>38.461538461538467</v>
       </c>
       <c r="J37" s="10">
         <f>IFERROR(C37/E37,0)</f>
-        <v>-0.77499999999999991</v>
+        <v>-0.23846153846153834</v>
       </c>
       <c r="K37" s="10">
         <f>IFERROR(D37/E37,0)</f>
-        <v>-0.15499999999999997</v>
+        <v>-4.7692307692307687E-2</v>
       </c>
       <c r="L37" s="10" t="str">
         <f>LEFT(B37,3)</f>
@@ -8223,7 +8488,7 @@
       </c>
       <c r="N37">
         <f t="shared" si="1"/>
-        <v>-3.0999999999999996</v>
+        <v>-3.0999999999999983</v>
       </c>
       <c r="O37">
         <f t="shared" si="7"/>
@@ -8231,11 +8496,11 @@
       </c>
       <c r="P37">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q37">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R37">
         <f t="shared" si="10"/>
@@ -8243,65 +8508,65 @@
       </c>
       <c r="S37">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>32</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>143</v>
+      <c r="B38" t="s">
+        <v>87</v>
       </c>
       <c r="C38">
-        <v>-4.3</v>
+        <v>-3.0999999999999996</v>
       </c>
       <c r="D38">
-        <v>-0.86</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38">
         <v>1</v>
       </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38" s="7">
         <f>IFERROR((F38/E38)*100,0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J38" s="10">
         <f>IFERROR(C38/E38,0)</f>
-        <v>-4.3</v>
+        <v>-0.77499999999999991</v>
       </c>
       <c r="K38" s="10">
         <f>IFERROR(D38/E38,0)</f>
-        <v>-0.86</v>
+        <v>-0.15499999999999997</v>
       </c>
       <c r="L38" s="10" t="str">
         <f>LEFT(B38,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N38">
         <f t="shared" si="1"/>
-        <v>-4.3</v>
+        <v>-3.0999999999999996</v>
       </c>
       <c r="O38">
         <f t="shared" si="7"/>
-        <v>-0.86</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="P38">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q38">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38">
         <f t="shared" si="10"/>
@@ -8309,7 +8574,7 @@
       </c>
       <c r="S38">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
@@ -8317,19 +8582,19 @@
         <v>33</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="C39">
-        <v>-6</v>
+        <v>-5.6</v>
       </c>
       <c r="D39">
-        <v>-1.2</v>
+        <v>-1.1200000000000001</v>
       </c>
       <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39">
         <v>1</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -8339,35 +8604,35 @@
       </c>
       <c r="I39" s="7">
         <f>IFERROR((F39/E39)*100,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J39" s="10">
         <f>IFERROR(C39/E39,0)</f>
-        <v>-6</v>
+        <v>-2.8</v>
       </c>
       <c r="K39" s="10">
         <f>IFERROR(D39/E39,0)</f>
-        <v>-1.2</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="L39" s="10" t="str">
         <f>LEFT(B39,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N39">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-5.6</v>
       </c>
       <c r="O39">
         <f t="shared" si="7"/>
-        <v>-1.2</v>
+        <v>-1.1200000000000001</v>
       </c>
       <c r="P39">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39">
         <f t="shared" si="10"/>
@@ -8382,62 +8647,62 @@
       <c r="A40">
         <v>34</v>
       </c>
-      <c r="B40" t="s">
-        <v>90</v>
+      <c r="B40" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C40">
-        <v>-6.2</v>
+        <v>-6</v>
       </c>
       <c r="D40">
-        <v>-1.24</v>
+        <v>-1.2</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40" s="7">
         <f>IFERROR((F40/E40)*100,0)</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J40" s="10">
         <f>IFERROR(C40/E40,0)</f>
-        <v>-1.24</v>
+        <v>-6</v>
       </c>
       <c r="K40" s="10">
         <f>IFERROR(D40/E40,0)</f>
-        <v>-0.248</v>
+        <v>-1.2</v>
       </c>
       <c r="L40" s="10" t="str">
         <f>LEFT(B40,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N40">
         <f t="shared" si="1"/>
-        <v>-6.2</v>
+        <v>-6</v>
       </c>
       <c r="O40">
         <f t="shared" si="7"/>
-        <v>-1.24</v>
+        <v>-1.2</v>
       </c>
       <c r="P40">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q40">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R40">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40">
         <f t="shared" si="11"/>
@@ -8449,37 +8714,37 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C41">
-        <v>-7.5</v>
+        <v>-6.2</v>
       </c>
       <c r="D41">
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="E41">
         <v>5</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I41" s="7">
         <f>IFERROR((F41/E41)*100,0)</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J41" s="10">
         <f>IFERROR(C41/E41,0)</f>
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="K41" s="10">
         <f>IFERROR(D41/E41,0)</f>
-        <v>-0.3</v>
+        <v>-0.248</v>
       </c>
       <c r="L41" s="10" t="str">
         <f>LEFT(B41,3)</f>
@@ -8487,11 +8752,11 @@
       </c>
       <c r="N41">
         <f t="shared" si="1"/>
-        <v>-7.5</v>
+        <v>-6.2</v>
       </c>
       <c r="O41">
         <f t="shared" si="7"/>
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="P41">
         <f t="shared" si="8"/>
@@ -8499,35 +8764,35 @@
       </c>
       <c r="Q41">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R41">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>98</v>
+      <c r="B42" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="C42">
-        <v>-7.5</v>
+        <v>-7.4999999999999991</v>
       </c>
       <c r="D42">
-        <v>-1.5</v>
+        <v>-1.4999999999999998</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -8537,35 +8802,35 @@
       </c>
       <c r="I42" s="7">
         <f>IFERROR((F42/E42)*100,0)</f>
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J42" s="10">
         <f>IFERROR(C42/E42,0)</f>
-        <v>-1.5</v>
+        <v>-0.93749999999999989</v>
       </c>
       <c r="K42" s="10">
         <f>IFERROR(D42/E42,0)</f>
-        <v>-0.3</v>
+        <v>-0.18749999999999997</v>
       </c>
       <c r="L42" s="10" t="str">
         <f>LEFT(B42,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N42">
         <f t="shared" si="1"/>
-        <v>-7.5</v>
+        <v>-7.4999999999999991</v>
       </c>
       <c r="O42">
         <f t="shared" si="7"/>
-        <v>-1.5</v>
+        <v>-1.4999999999999998</v>
       </c>
       <c r="P42">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q42">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R42">
         <f t="shared" si="10"/>
@@ -8580,20 +8845,20 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>84</v>
+      <c r="B43" t="s">
+        <v>75</v>
       </c>
       <c r="C43">
-        <v>-7.5000000000000009</v>
+        <v>-7.5</v>
       </c>
       <c r="D43">
         <v>-1.5</v>
       </c>
       <c r="E43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -8603,23 +8868,23 @@
       </c>
       <c r="I43" s="7">
         <f>IFERROR((F43/E43)*100,0)</f>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J43" s="10">
         <f>IFERROR(C43/E43,0)</f>
-        <v>-1.2500000000000002</v>
+        <v>-1.5</v>
       </c>
       <c r="K43" s="10">
         <f>IFERROR(D43/E43,0)</f>
-        <v>-0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="L43" s="10" t="str">
         <f>LEFT(B43,3)</f>
-        <v>WEG</v>
+        <v>PEG</v>
       </c>
       <c r="N43">
         <f t="shared" si="1"/>
-        <v>-7.5000000000000009</v>
+        <v>-7.5</v>
       </c>
       <c r="O43">
         <f t="shared" si="7"/>
@@ -8627,11 +8892,11 @@
       </c>
       <c r="P43">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q43">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R43">
         <f t="shared" si="10"/>
@@ -8647,19 +8912,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C44">
-        <v>-8.8999999999999986</v>
+        <v>-7.5</v>
       </c>
       <c r="D44">
-        <v>-1.7799999999999998</v>
+        <v>-1.5</v>
       </c>
       <c r="E44">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -8669,15 +8934,15 @@
       </c>
       <c r="I44" s="7">
         <f>IFERROR((F44/E44)*100,0)</f>
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J44" s="10">
         <f>IFERROR(C44/E44,0)</f>
-        <v>-1.1124999999999998</v>
+        <v>-1.5</v>
       </c>
       <c r="K44" s="10">
         <f>IFERROR(D44/E44,0)</f>
-        <v>-0.22249999999999998</v>
+        <v>-0.3</v>
       </c>
       <c r="L44" s="10" t="str">
         <f>LEFT(B44,3)</f>
@@ -8685,19 +8950,19 @@
       </c>
       <c r="N44">
         <f t="shared" si="1"/>
-        <v>-8.8999999999999986</v>
+        <v>-7.5</v>
       </c>
       <c r="O44">
         <f t="shared" si="7"/>
-        <v>-1.7799999999999998</v>
+        <v>-1.5</v>
       </c>
       <c r="P44">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q44">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R44">
         <f t="shared" si="10"/>
@@ -8712,58 +8977,58 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
-        <v>93</v>
+      <c r="B45" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="C45">
-        <v>-9.1</v>
+        <v>-7.5000000000000009</v>
       </c>
       <c r="D45">
-        <v>-1.82</v>
+        <v>-1.5</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I45" s="7">
         <f>IFERROR((F45/E45)*100,0)</f>
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J45" s="10">
         <f>IFERROR(C45/E45,0)</f>
-        <v>-1.8199999999999998</v>
+        <v>-1.2500000000000002</v>
       </c>
       <c r="K45" s="10">
         <f>IFERROR(D45/E45,0)</f>
-        <v>-0.36399999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="L45" s="10" t="str">
         <f>LEFT(B45,3)</f>
-        <v>PEG</v>
+        <v>WEG</v>
       </c>
       <c r="N45">
         <f t="shared" si="1"/>
-        <v>-9.1</v>
+        <v>-7.5000000000000009</v>
       </c>
       <c r="O45">
         <f t="shared" si="7"/>
-        <v>-1.82</v>
+        <v>-1.5</v>
       </c>
       <c r="P45">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q45">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R45">
         <f t="shared" si="10"/>
@@ -8771,7 +9036,7 @@
       </c>
       <c r="S45">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -8779,57 +9044,57 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C46">
-        <v>-9.4000000000000021</v>
+        <v>-9.1</v>
       </c>
       <c r="D46">
-        <v>-1.879999999999999</v>
+        <v>-1.82</v>
       </c>
       <c r="E46">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F46">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I46" s="7">
         <f>IFERROR((F46/E46)*100,0)</f>
-        <v>47.058823529411761</v>
+        <v>20</v>
       </c>
       <c r="J46" s="10">
         <f>IFERROR(C46/E46,0)</f>
-        <v>-0.55294117647058838</v>
+        <v>-1.8199999999999998</v>
       </c>
       <c r="K46" s="10">
         <f>IFERROR(D46/E46,0)</f>
-        <v>-0.11058823529411758</v>
+        <v>-0.36399999999999999</v>
       </c>
       <c r="L46" s="10" t="str">
         <f>LEFT(B46,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N46">
         <f t="shared" si="1"/>
-        <v>-9.4000000000000021</v>
+        <v>-9.1</v>
       </c>
       <c r="O46">
         <f t="shared" si="7"/>
-        <v>-1.879999999999999</v>
+        <v>-1.82</v>
       </c>
       <c r="P46">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Q46">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R46">
         <f t="shared" si="10"/>
@@ -8837,7 +9102,7 @@
       </c>
       <c r="S46">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
@@ -8845,57 +9110,57 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C47">
-        <v>-9.6999999999999993</v>
+        <v>-9.4000000000000021</v>
       </c>
       <c r="D47">
-        <v>-1.9400000000000002</v>
+        <v>-1.879999999999999</v>
       </c>
       <c r="E47">
+        <v>17</v>
+      </c>
+      <c r="F47">
         <v>8</v>
       </c>
-      <c r="F47">
-        <v>3</v>
-      </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I47" s="7">
         <f>IFERROR((F47/E47)*100,0)</f>
-        <v>37.5</v>
+        <v>47.058823529411761</v>
       </c>
       <c r="J47" s="10">
         <f>IFERROR(C47/E47,0)</f>
-        <v>-1.2124999999999999</v>
+        <v>-0.55294117647058838</v>
       </c>
       <c r="K47" s="10">
         <f>IFERROR(D47/E47,0)</f>
-        <v>-0.24250000000000002</v>
+        <v>-0.11058823529411758</v>
       </c>
       <c r="L47" s="10" t="str">
         <f>LEFT(B47,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N47">
         <f t="shared" si="1"/>
-        <v>-9.6999999999999993</v>
+        <v>-9.4000000000000021</v>
       </c>
       <c r="O47">
         <f t="shared" si="7"/>
-        <v>-1.9400000000000002</v>
+        <v>-1.879999999999999</v>
       </c>
       <c r="P47">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Q47">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R47">
         <f t="shared" si="10"/>
@@ -8903,7 +9168,7 @@
       </c>
       <c r="S47">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
@@ -8911,41 +9176,41 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="C48">
         <v>-9.6999999999999993</v>
       </c>
       <c r="D48">
-        <v>-1.94</v>
+        <v>-1.9400000000000002</v>
       </c>
       <c r="E48">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I48" s="7">
         <f>IFERROR((F48/E48)*100,0)</f>
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="J48" s="10">
         <f>IFERROR(C48/E48,0)</f>
-        <v>-0.97</v>
+        <v>-1.2124999999999999</v>
       </c>
       <c r="K48" s="10">
         <f>IFERROR(D48/E48,0)</f>
-        <v>-0.19400000000000001</v>
+        <v>-0.24250000000000002</v>
       </c>
       <c r="L48" s="10" t="str">
         <f>LEFT(B48,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N48">
         <f t="shared" si="1"/>
@@ -8953,15 +9218,15 @@
       </c>
       <c r="O48">
         <f t="shared" si="7"/>
-        <v>-1.94</v>
+        <v>-1.9400000000000002</v>
       </c>
       <c r="P48">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q48">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R48">
         <f t="shared" ref="R48:R53" si="12">G48+Y48</f>
@@ -8969,7 +9234,7 @@
       </c>
       <c r="S48">
         <f t="shared" ref="S48:S53" si="13">H48+Z48</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
@@ -9306,58 +9571,58 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="8" t="s">
-        <v>127</v>
+      <c r="B54" t="s">
+        <v>99</v>
       </c>
       <c r="C54">
-        <v>-13.899999999999999</v>
+        <v>-13.299999999999999</v>
       </c>
       <c r="D54">
-        <v>-2.7800000000000002</v>
+        <v>-2.6599999999999997</v>
       </c>
       <c r="E54">
+        <v>9</v>
+      </c>
+      <c r="F54">
         <v>4</v>
       </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I54" s="7">
         <f>IFERROR((F54/E54)*100,0)</f>
-        <v>0</v>
+        <v>44.444444444444443</v>
       </c>
       <c r="J54" s="10">
         <f>IFERROR(C54/E54,0)</f>
-        <v>-3.4749999999999996</v>
+        <v>-1.4777777777777776</v>
       </c>
       <c r="K54" s="10">
         <f>IFERROR(D54/E54,0)</f>
-        <v>-0.69500000000000006</v>
+        <v>-0.29555555555555552</v>
       </c>
       <c r="L54" s="10" t="str">
         <f>LEFT(B54,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N54">
         <f t="shared" ref="N54:N56" si="14">C54+U54</f>
-        <v>-13.899999999999999</v>
+        <v>-13.299999999999999</v>
       </c>
       <c r="O54">
         <f t="shared" ref="O54:O56" si="15">D54+V54</f>
-        <v>-2.7800000000000002</v>
+        <v>-2.6599999999999997</v>
       </c>
       <c r="P54">
         <f t="shared" ref="P54:P56" si="16">E54+W54</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q54">
         <f t="shared" ref="Q54:Q56" si="17">F54+X54</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R54">
         <f t="shared" ref="R54:R56" si="18">G54+Y54</f>
@@ -9365,7 +9630,7 @@
       </c>
       <c r="S54">
         <f t="shared" ref="S54:S56" si="19">H54+Z54</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
@@ -9373,22 +9638,22 @@
         <v>54</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="C55">
-        <v>-14</v>
+        <v>-13.899999999999999</v>
       </c>
       <c r="D55">
-        <v>-2.8</v>
+        <v>-2.7800000000000002</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
         <v>4</v>
@@ -9399,27 +9664,27 @@
       </c>
       <c r="J55" s="10">
         <f>IFERROR(C55/E55,0)</f>
-        <v>-3.5</v>
+        <v>-2.78</v>
       </c>
       <c r="K55" s="10">
         <f>IFERROR(D55/E55,0)</f>
-        <v>-0.7</v>
+        <v>-0.55600000000000005</v>
       </c>
       <c r="L55" s="10" t="str">
         <f>LEFT(B55,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N55">
         <f t="shared" si="14"/>
-        <v>-14</v>
+        <v>-13.899999999999999</v>
       </c>
       <c r="O55">
         <f t="shared" si="15"/>
-        <v>-2.8</v>
+        <v>-2.7800000000000002</v>
       </c>
       <c r="P55">
         <f t="shared" si="16"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q55">
         <f t="shared" si="17"/>
@@ -9427,7 +9692,7 @@
       </c>
       <c r="R55">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55">
         <f t="shared" si="19"/>
@@ -9439,65 +9704,65 @@
         <v>55</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="C56">
-        <v>-15.8</v>
+        <v>-14</v>
       </c>
       <c r="D56">
-        <v>-3.16</v>
+        <v>-2.8</v>
       </c>
       <c r="E56">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I56" s="7">
         <f>IFERROR((F56/E56)*100,0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J56" s="10">
         <f>IFERROR(C56/E56,0)</f>
-        <v>-1.9750000000000001</v>
+        <v>-2.8</v>
       </c>
       <c r="K56" s="10">
         <f>IFERROR(D56/E56,0)</f>
-        <v>-0.39500000000000002</v>
+        <v>-0.55999999999999994</v>
       </c>
       <c r="L56" s="10" t="str">
         <f>LEFT(B56,3)</f>
-        <v>VEG</v>
+        <v>LEG</v>
       </c>
       <c r="N56">
         <f t="shared" si="14"/>
-        <v>-15.8</v>
+        <v>-14</v>
       </c>
       <c r="O56">
         <f t="shared" si="15"/>
-        <v>-3.16</v>
+        <v>-2.8</v>
       </c>
       <c r="P56">
         <f t="shared" si="16"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q56">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R56">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56">
         <f t="shared" si="19"/>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
@@ -9505,57 +9770,57 @@
         <v>56</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C57">
-        <v>-19.5</v>
+        <v>-16.600000000000001</v>
       </c>
       <c r="D57">
-        <v>-3.9</v>
+        <v>-3.3200000000000003</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I57" s="7">
         <f>IFERROR((F57/E57)*100,0)</f>
-        <v>0</v>
+        <v>22.222222222222221</v>
       </c>
       <c r="J57" s="10">
         <f>IFERROR(C57/E57,0)</f>
-        <v>-19.5</v>
+        <v>-1.8444444444444446</v>
       </c>
       <c r="K57" s="10">
         <f>IFERROR(D57/E57,0)</f>
-        <v>-3.9</v>
+        <v>-0.36888888888888893</v>
       </c>
       <c r="L57" s="10" t="str">
         <f>LEFT(B57,3)</f>
-        <v>UEG</v>
+        <v>VEG</v>
       </c>
       <c r="N57">
         <f t="shared" ref="N57:N61" si="20">C57+U57</f>
-        <v>-19.5</v>
+        <v>-16.600000000000001</v>
       </c>
       <c r="O57">
         <f t="shared" ref="O57:O61" si="21">D57+V57</f>
-        <v>-3.9</v>
+        <v>-3.3200000000000003</v>
       </c>
       <c r="P57">
         <f t="shared" ref="P57:P61" si="22">E57+W57</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q57">
         <f t="shared" ref="Q57:Q61" si="23">F57+X57</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R57">
         <f t="shared" ref="R57:R61" si="24">G57+Y57</f>
@@ -9563,45 +9828,45 @@
       </c>
       <c r="S57">
         <f t="shared" ref="S57:S61" si="25">H57+Z57</f>
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>141</v>
+      <c r="B58" t="s">
+        <v>95</v>
       </c>
       <c r="C58">
-        <v>-20.099999999999998</v>
+        <v>-17.299999999999997</v>
       </c>
       <c r="D58">
-        <v>-4.0199999999999996</v>
+        <v>-3.46</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I58" s="7">
         <f>IFERROR((F58/E58)*100,0)</f>
-        <v>0</v>
+        <v>36.363636363636367</v>
       </c>
       <c r="J58" s="10">
         <f>IFERROR(C58/E58,0)</f>
-        <v>-10.049999999999999</v>
+        <v>-1.5727272727272725</v>
       </c>
       <c r="K58" s="10">
         <f>IFERROR(D58/E58,0)</f>
-        <v>-2.0099999999999998</v>
+        <v>-0.31454545454545452</v>
       </c>
       <c r="L58" s="10" t="str">
         <f>LEFT(B58,3)</f>
@@ -9609,19 +9874,19 @@
       </c>
       <c r="N58">
         <f t="shared" si="20"/>
-        <v>-20.099999999999998</v>
+        <v>-17.299999999999997</v>
       </c>
       <c r="O58">
         <f t="shared" si="21"/>
-        <v>-4.0199999999999996</v>
+        <v>-3.46</v>
       </c>
       <c r="P58">
         <f t="shared" si="22"/>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q58">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R58">
         <f t="shared" si="24"/>
@@ -9629,65 +9894,65 @@
       </c>
       <c r="S58">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
-        <v>57</v>
+      <c r="B59" s="8" t="s">
+        <v>141</v>
       </c>
       <c r="C59">
-        <v>-22.700000000000003</v>
+        <v>-18.799999999999997</v>
       </c>
       <c r="D59">
-        <v>-4.5399999999999991</v>
+        <v>-3.76</v>
       </c>
       <c r="E59">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F59">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
       <c r="H59">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I59" s="7">
         <f>IFERROR((F59/E59)*100,0)</f>
-        <v>47.368421052631575</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J59" s="10">
         <f>IFERROR(C59/E59,0)</f>
-        <v>-1.1947368421052633</v>
+        <v>-6.2666666666666657</v>
       </c>
       <c r="K59" s="10">
         <f>IFERROR(D59/E59,0)</f>
-        <v>-0.23894736842105258</v>
+        <v>-1.2533333333333332</v>
       </c>
       <c r="L59" s="10" t="str">
         <f>LEFT(B59,3)</f>
-        <v>VEG</v>
+        <v>PEG</v>
       </c>
       <c r="N59">
         <f t="shared" si="20"/>
-        <v>-22.700000000000003</v>
+        <v>-18.799999999999997</v>
       </c>
       <c r="O59">
         <f t="shared" si="21"/>
-        <v>-4.5399999999999991</v>
+        <v>-3.76</v>
       </c>
       <c r="P59">
         <f t="shared" si="22"/>
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Q59">
         <f t="shared" si="23"/>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R59">
         <f t="shared" si="24"/>
@@ -9695,73 +9960,73 @@
       </c>
       <c r="S59">
         <f t="shared" si="25"/>
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
-        <v>59</v>
+      <c r="B60" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="C60">
-        <v>-42.699999999999996</v>
+        <v>-19.5</v>
       </c>
       <c r="D60">
-        <v>-8.5399999999999991</v>
+        <v>-3.9</v>
       </c>
       <c r="E60">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
         <v>1</v>
-      </c>
-      <c r="H60">
-        <v>9</v>
       </c>
       <c r="I60" s="7">
         <f>IFERROR((F60/E60)*100,0)</f>
-        <v>41.17647058823529</v>
+        <v>0</v>
       </c>
       <c r="J60" s="10">
         <f>IFERROR(C60/E60,0)</f>
-        <v>-2.5117647058823529</v>
+        <v>-19.5</v>
       </c>
       <c r="K60" s="10">
         <f>IFERROR(D60/E60,0)</f>
-        <v>-0.50235294117647056</v>
+        <v>-3.9</v>
       </c>
       <c r="L60" s="10" t="str">
         <f>LEFT(B60,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N60">
         <f t="shared" si="20"/>
-        <v>-42.699999999999996</v>
+        <v>-19.5</v>
       </c>
       <c r="O60">
         <f t="shared" si="21"/>
-        <v>-8.5399999999999991</v>
+        <v>-3.9</v>
       </c>
       <c r="P60">
         <f t="shared" si="22"/>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Q60">
         <f t="shared" si="23"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R60">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60">
         <f t="shared" si="25"/>
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
@@ -9769,57 +10034,57 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="C61">
-        <v>-42.900000000000006</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="D61">
-        <v>-8.58</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
       <c r="H61">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I61" s="7">
         <f>IFERROR((F61/E61)*100,0)</f>
-        <v>0</v>
+        <v>47.368421052631575</v>
       </c>
       <c r="J61" s="10">
         <f>IFERROR(C61/E61,0)</f>
-        <v>-10.725000000000001</v>
+        <v>-1.1947368421052633</v>
       </c>
       <c r="K61" s="10">
         <f>IFERROR(D61/E61,0)</f>
-        <v>-2.145</v>
+        <v>-0.23894736842105258</v>
       </c>
       <c r="L61" s="10" t="str">
         <f>LEFT(B61,3)</f>
-        <v>LEG</v>
+        <v>VEG</v>
       </c>
       <c r="N61">
         <f t="shared" si="20"/>
-        <v>-42.900000000000006</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="O61">
         <f t="shared" si="21"/>
-        <v>-8.58</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="P61">
         <f t="shared" si="22"/>
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="Q61">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R61">
         <f t="shared" si="24"/>
@@ -9827,22 +10092,140 @@
       </c>
       <c r="S61">
         <f t="shared" si="25"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62">
+        <v>-39.599999999999994</v>
+      </c>
+      <c r="D62">
+        <v>-7.919999999999999</v>
+      </c>
+      <c r="E62">
+        <v>18</v>
+      </c>
+      <c r="F62">
+        <v>8</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>9</v>
+      </c>
+      <c r="I62" s="7">
+        <f>IFERROR((F62/E62)*100,0)</f>
+        <v>44.444444444444443</v>
+      </c>
+      <c r="J62" s="10">
+        <f>IFERROR(C62/E62,0)</f>
+        <v>-2.1999999999999997</v>
+      </c>
+      <c r="K62" s="10">
+        <f>IFERROR(D62/E62,0)</f>
+        <v>-0.43999999999999995</v>
+      </c>
+      <c r="L62" s="10" t="str">
+        <f>LEFT(B62,3)</f>
+        <v>PEG</v>
+      </c>
+      <c r="N62">
+        <f t="shared" ref="N62" si="26">C62+U62</f>
+        <v>-39.599999999999994</v>
+      </c>
+      <c r="O62">
+        <f t="shared" ref="O62" si="27">D62+V62</f>
+        <v>-7.919999999999999</v>
+      </c>
+      <c r="P62">
+        <f t="shared" ref="P62" si="28">E62+W62</f>
+        <v>18</v>
+      </c>
+      <c r="Q62">
+        <f t="shared" ref="Q62" si="29">F62+X62</f>
+        <v>8</v>
+      </c>
+      <c r="R62">
+        <f t="shared" ref="R62" si="30">G62+Y62</f>
+        <v>1</v>
+      </c>
+      <c r="S62">
+        <f t="shared" ref="S62" si="31">H62+Z62</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>83</v>
+      </c>
+      <c r="C63">
+        <v>-42.900000000000006</v>
+      </c>
+      <c r="D63">
+        <v>-8.58</v>
+      </c>
+      <c r="E63">
         <v>4</v>
       </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B62" s="8"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="10"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="8"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="10"/>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>4</v>
+      </c>
+      <c r="I63" s="7">
+        <f>IFERROR((F63/E63)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="10">
+        <f>IFERROR(C63/E63,0)</f>
+        <v>-10.725000000000001</v>
+      </c>
+      <c r="K63" s="10">
+        <f>IFERROR(D63/E63,0)</f>
+        <v>-2.145</v>
+      </c>
+      <c r="L63" s="10" t="str">
+        <f>LEFT(B63,3)</f>
+        <v>LEG</v>
+      </c>
+      <c r="N63">
+        <f t="shared" ref="N63" si="32">C63+U63</f>
+        <v>-42.900000000000006</v>
+      </c>
+      <c r="O63">
+        <f t="shared" ref="O63" si="33">D63+V63</f>
+        <v>-8.58</v>
+      </c>
+      <c r="P63">
+        <f t="shared" ref="P63" si="34">E63+W63</f>
+        <v>4</v>
+      </c>
+      <c r="Q63">
+        <f t="shared" ref="Q63" si="35">F63+X63</f>
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <f t="shared" ref="R63" si="36">G63+Y63</f>
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <f t="shared" ref="S63" si="37">H63+Z63</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B64" s="8"/>
@@ -9925,11 +10308,11 @@
       <c r="B75" s="8"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L75">
-    <sortCondition descending="1" ref="C2:C75"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L76">
+    <sortCondition descending="1" ref="C2:C76"/>
   </sortState>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="dataBar" priority="17">
+    <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -9943,7 +10326,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="dataBar" priority="16">
+    <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -9957,7 +10340,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="dataBar" priority="15">
+    <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -9971,7 +10354,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="dataBar" priority="14">
+    <cfRule type="dataBar" priority="21">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -9985,7 +10368,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="dataBar" priority="13">
+    <cfRule type="dataBar" priority="20">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -9999,7 +10382,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="dataBar" priority="12">
+    <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10013,7 +10396,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="dataBar" priority="11">
+    <cfRule type="dataBar" priority="18">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10027,7 +10410,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="dataBar" priority="8">
+    <cfRule type="dataBar" priority="15">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10041,7 +10424,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1048576">
-    <cfRule type="dataBar" priority="9">
+    <cfRule type="dataBar" priority="16">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10054,27 +10437,50 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="PEG">
+  <conditionalFormatting sqref="B1:B62 B64:B1048576">
+    <cfRule type="containsText" dxfId="34" priority="14" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="33" priority="13" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="32" priority="12" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="31" priority="11" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="30" priority="10" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="29" priority="9" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B1)))</formula>
     </cfRule>
+    <cfRule type="containsText" dxfId="28" priority="8" operator="containsText" text="LEG">
+      <formula>NOT(ISERROR(SEARCH("LEG",B1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
     <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="LEG">
-      <formula>NOT(ISERROR(SEARCH("LEG",B1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("LEG",B63)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="VEG">
+      <formula>NOT(ISERROR(SEARCH("VEG",B63)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="VEG">
+      <formula>NOT(ISERROR(SEARCH("VEG",B63)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="WEG">
+      <formula>NOT(ISERROR(SEARCH("WEG",B63)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="UEG">
+      <formula>NOT(ISERROR(SEARCH("UEG",B63)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="SEG">
+      <formula>NOT(ISERROR(SEARCH("SEG",B63)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="PEG">
+      <formula>NOT(ISERROR(SEARCH("PEG",B63)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10196,7 +10602,7 @@
     <col min="8" max="28" width="8.42578125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>104</v>
       </c>
@@ -10204,7 +10610,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" t="s">
         <v>100</v>
@@ -10228,25 +10634,25 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="B3">
         <f>SUM(H3:AB3)</f>
-        <v>22.199999999999996</v>
+        <v>-7.4999999999999991</v>
       </c>
       <c r="C3">
         <f>(B3/$C$1)*100</f>
-        <v>4.4399999999999986</v>
+        <v>-1.4999999999999998</v>
       </c>
       <c r="D3">
         <f>COUNTA(H3:AB3)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <f>COUNTIF(H3:AB3, "&gt;0")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <f>COUNTIF(H3:AB3, "=0")</f>
@@ -10254,40 +10660,52 @@
       </c>
       <c r="G3">
         <f>COUNTIF(H3:AB3, "&lt;0")</f>
-        <v>2</v>
-      </c>
-      <c r="H3" s="17">
-        <v>29.7</v>
-      </c>
-      <c r="I3" s="17">
-        <v>-0.6</v>
-      </c>
-      <c r="J3" s="18">
+        <v>4</v>
+      </c>
+      <c r="H3" s="11">
+        <v>1.2</v>
+      </c>
+      <c r="I3" s="11">
         <v>0.2</v>
       </c>
-      <c r="K3" s="18">
-        <v>-7.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>56</v>
+      <c r="J3" s="11">
+        <v>-0.8</v>
+      </c>
+      <c r="K3" s="11">
+        <v>-2.6</v>
+      </c>
+      <c r="L3" s="11">
+        <v>-3.8</v>
+      </c>
+      <c r="M3" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="N3" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="O3" s="11">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="B4">
         <f>SUM(H4:AB4)</f>
-        <v>-7.1999999999999993</v>
+        <v>-0.79999999999999893</v>
       </c>
       <c r="C4">
         <f>(B4/$C$1)*100</f>
-        <v>-1.4399999999999997</v>
+        <v>-0.15999999999999978</v>
       </c>
       <c r="D4">
         <f>COUNTA(H4:AB4)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <f>COUNTIF(H4:AB4, "&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <f>COUNTIF(H4:AB4, "=0")</f>
@@ -10295,37 +10713,43 @@
       </c>
       <c r="G4">
         <f>COUNTIF(H4:AB4, "&lt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="18">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="I4" s="18">
-        <v>-4.8</v>
+        <v>-0.9</v>
       </c>
       <c r="J4" s="18">
-        <v>-4.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>131</v>
+        <v>-3.5</v>
+      </c>
+      <c r="K4" s="18">
+        <v>-1.4</v>
+      </c>
+      <c r="L4" s="18">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>65</v>
       </c>
       <c r="B5">
         <f>SUM(H5:AB5)</f>
-        <v>8.6000000000000014</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="C5">
         <f>(B5/$C$1)*100</f>
-        <v>1.7200000000000004</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="D5">
         <f>COUNTA(H5:AB5)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <f>COUNTIF(H5:AB5, "&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <f>COUNTIF(H5:AB5, "=0")</f>
@@ -10333,29 +10757,35 @@
       </c>
       <c r="G5">
         <f>COUNTIF(H5:AB5, "&lt;0")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H5" s="17">
-        <v>-1.6</v>
+        <v>-3.4</v>
       </c>
       <c r="I5" s="18">
-        <v>6.4</v>
+        <v>-2.5</v>
       </c>
       <c r="J5" s="18">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>133</v>
+        <v>13.1</v>
+      </c>
+      <c r="K5" s="18">
+        <v>-0.8</v>
+      </c>
+      <c r="L5" s="18">
+        <v>-4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>132</v>
       </c>
       <c r="B6">
         <f>SUM(H6:AB6)</f>
-        <v>-18.5</v>
+        <v>13.7</v>
       </c>
       <c r="C6">
         <f>(B6/$C$1)*100</f>
-        <v>-3.6999999999999997</v>
+        <v>2.7399999999999998</v>
       </c>
       <c r="D6">
         <f>COUNTA(H6:AB6)</f>
@@ -10363,7 +10793,7 @@
       </c>
       <c r="E6">
         <f>COUNTIF(H6:AB6, "&gt;0")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <f>COUNTIF(H6:AB6, "=0")</f>
@@ -10371,29 +10801,29 @@
       </c>
       <c r="G6">
         <f>COUNTIF(H6:AB6, "&lt;0")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="17">
-        <v>-6.5</v>
+        <v>3.3</v>
       </c>
       <c r="I6" s="17">
-        <v>3.4</v>
-      </c>
-      <c r="J6" s="17">
-        <v>-15.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>8.1</v>
+      </c>
+      <c r="J6" s="18">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="B7">
         <f>SUM(H7:AB7)</f>
-        <v>-6.3</v>
+        <v>4.3</v>
       </c>
       <c r="C7">
         <f>(B7/$C$1)*100</f>
-        <v>-1.26</v>
+        <v>0.86</v>
       </c>
       <c r="D7">
         <f>COUNTA(H7:AB7)</f>
@@ -10401,7 +10831,7 @@
       </c>
       <c r="E7">
         <f>COUNTIF(H7:AB7, "&gt;0")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <f>COUNTIF(H7:AB7, "=0")</f>
@@ -10409,26 +10839,26 @@
       </c>
       <c r="G7">
         <f>COUNTIF(H7:AB7, "&lt;0")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="18">
-        <v>-4.8</v>
+        <v>3</v>
       </c>
       <c r="I7" s="18">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B8">
         <f>SUM(H8:AB8)</f>
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="C8">
         <f>(B8/$C$1)*100</f>
-        <v>0.42000000000000004</v>
+        <v>0.3</v>
       </c>
       <c r="D8">
         <f>COUNTA(H8:AB8)</f>
@@ -10436,7 +10866,7 @@
       </c>
       <c r="E8">
         <f>COUNTIF(H8:AB8, "&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <f>COUNTIF(H8:AB8, "=0")</f>
@@ -10444,26 +10874,26 @@
       </c>
       <c r="G8">
         <f>COUNTIF(H8:AB8, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="17">
-        <v>0.8</v>
+        <v>-12.2</v>
       </c>
       <c r="I8" s="18">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>94</v>
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>140</v>
       </c>
       <c r="B9">
         <f>SUM(H9:AB9)</f>
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <f>(B9/$C$1)*100</f>
-        <v>1.42</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <f>COUNTA(H9:AB9)</f>
@@ -10482,23 +10912,23 @@
         <v>0</v>
       </c>
       <c r="H9" s="17">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="I9" s="18">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="B10">
         <f>SUM(H10:AB10)</f>
-        <v>3.2</v>
+        <v>0.40000000000000036</v>
       </c>
       <c r="C10">
         <f>(B10/$C$1)*100</f>
-        <v>0.64</v>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="D10">
         <f>COUNTA(H10:AB10)</f>
@@ -10517,31 +10947,32 @@
         <v>1</v>
       </c>
       <c r="H10" s="17">
-        <v>-0.3</v>
+        <v>7.4</v>
       </c>
       <c r="I10" s="17">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>96</v>
+        <v>-7</v>
+      </c>
+      <c r="J10" s="15"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>138</v>
       </c>
       <c r="B11">
         <f>SUM(H11:AB11)</f>
-        <v>-20.100000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="C11">
         <f>(B11/$C$1)*100</f>
-        <v>-4.0199999999999996</v>
+        <v>1.42</v>
       </c>
       <c r="D11">
         <f>COUNTA(H11:AB11)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <f>COUNTIF(H11:AB11, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <f>COUNTIF(H11:AB11, "=0")</f>
@@ -10549,34 +10980,31 @@
       </c>
       <c r="G11">
         <f>COUNTIF(H11:AB11, "&lt;0")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" s="18">
-        <v>-18.600000000000001</v>
-      </c>
-      <c r="I11" s="18">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>140</v>
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>129</v>
       </c>
       <c r="B12">
         <f>SUM(H12:AB12)</f>
-        <v>5.9</v>
+        <v>-0.8</v>
       </c>
       <c r="C12">
         <f>(B12/$C$1)*100</f>
-        <v>1.1800000000000002</v>
+        <v>-0.16</v>
       </c>
       <c r="D12">
         <f>COUNTA(H12:AB12)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <f>COUNTIF(H12:AB12, "&gt;0")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <f>COUNTIF(H12:AB12, "=0")</f>
@@ -10584,35 +11012,35 @@
       </c>
       <c r="G12">
         <f>COUNTIF(H12:AB12, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="17">
-        <v>3.4</v>
-      </c>
-      <c r="I12" s="17">
-        <v>2.5</v>
-      </c>
+        <v>-0.8</v>
+      </c>
+      <c r="I12" s="15"/>
       <c r="J12" s="15"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>141</v>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="B13">
         <f>SUM(H13:AB13)</f>
-        <v>-20.099999999999998</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C13">
         <f>(B13/$C$1)*100</f>
-        <v>-4.0199999999999996</v>
+        <v>0.98000000000000009</v>
       </c>
       <c r="D13">
         <f>COUNTA(H13:AB13)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <f>COUNTIF(H13:AB13, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <f>COUNTIF(H13:AB13, "=0")</f>
@@ -10620,26 +11048,23 @@
       </c>
       <c r="G13">
         <f>COUNTIF(H13:AB13, "&lt;0")</f>
-        <v>2</v>
-      </c>
-      <c r="H13" s="11">
-        <v>-18.899999999999999</v>
-      </c>
-      <c r="I13" s="18">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>138</v>
+        <v>0</v>
+      </c>
+      <c r="H13" s="18">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="B14">
         <f>SUM(H14:AB14)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <f>(B14/$C$1)*100</f>
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <f>COUNTA(H14:AB14)</f>
@@ -10651,27 +11076,27 @@
       </c>
       <c r="F14">
         <f>COUNTIF(H14:AB14, "=0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <f>COUNTIF(H14:AB14, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H14" s="17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="B15">
         <f>SUM(H15:AB15)</f>
-        <v>5.8</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="C15">
         <f>(B15/$C$1)*100</f>
-        <v>1.1599999999999999</v>
+        <v>-0.22</v>
       </c>
       <c r="D15">
         <f>COUNTA(H15:AB15)</f>
@@ -10679,7 +11104,7 @@
       </c>
       <c r="E15">
         <f>COUNTIF(H15:AB15, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <f>COUNTIF(H15:AB15, "=0")</f>
@@ -10687,23 +11112,23 @@
       </c>
       <c r="G15">
         <f>COUNTIF(H15:AB15, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="18">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="B16">
         <f>SUM(H16:AB16)</f>
-        <v>17.8</v>
+        <v>-7.6</v>
       </c>
       <c r="C16">
         <f>(B16/$C$1)*100</f>
-        <v>3.56</v>
+        <v>-1.52</v>
       </c>
       <c r="D16">
         <f>COUNTA(H16:AB16)</f>
@@ -10711,7 +11136,7 @@
       </c>
       <c r="E16">
         <f>COUNTIF(H16:AB16, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <f>COUNTIF(H16:AB16, "=0")</f>
@@ -10719,23 +11144,23 @@
       </c>
       <c r="G16">
         <f>COUNTIF(H16:AB16, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="18">
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>134</v>
+        <v>-7.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>59</v>
       </c>
       <c r="B17">
         <f>SUM(H17:AB17)</f>
-        <v>-1.8</v>
+        <v>3.1</v>
       </c>
       <c r="C17">
         <f>(B17/$C$1)*100</f>
-        <v>-0.36</v>
+        <v>0.62</v>
       </c>
       <c r="D17">
         <f>COUNTA(H17:AB17)</f>
@@ -10743,7 +11168,7 @@
       </c>
       <c r="E17">
         <f>COUNTIF(H17:AB17, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
         <f>COUNTIF(H17:AB17, "=0")</f>
@@ -10751,23 +11176,23 @@
       </c>
       <c r="G17">
         <f>COUNTIF(H17:AB17, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="17">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>127</v>
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>141</v>
       </c>
       <c r="B18">
         <f>SUM(H18:AB18)</f>
-        <v>-4.7</v>
+        <v>1.3</v>
       </c>
       <c r="C18">
         <f>(B18/$C$1)*100</f>
-        <v>-0.94000000000000006</v>
+        <v>0.26</v>
       </c>
       <c r="D18">
         <f>COUNTA(H18:AB18)</f>
@@ -10775,7 +11200,7 @@
       </c>
       <c r="E18">
         <f>COUNTIF(H18:AB18, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <f>COUNTIF(H18:AB18, "=0")</f>
@@ -10783,25 +11208,24 @@
       </c>
       <c r="G18">
         <f>COUNTIF(H18:AB18, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="17">
-        <v>-4.7</v>
+        <v>1.3</v>
       </c>
       <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="B19">
         <f>SUM(H19:AB19)</f>
-        <v>-0.6</v>
+        <v>6.9</v>
       </c>
       <c r="C19">
         <f>(B19/$C$1)*100</f>
-        <v>-0.12</v>
+        <v>1.3800000000000001</v>
       </c>
       <c r="D19">
         <f>COUNTA(H19:AB19)</f>
@@ -10809,7 +11233,7 @@
       </c>
       <c r="E19">
         <f>COUNTIF(H19:AB19, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <f>COUNTIF(H19:AB19, "=0")</f>
@@ -10817,23 +11241,23 @@
       </c>
       <c r="G19">
         <f>COUNTIF(H19:AB19, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="17">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="B20">
         <f>SUM(H20:AB20)</f>
-        <v>-2.2000000000000002</v>
+        <v>-6.5</v>
       </c>
       <c r="C20">
         <f>(B20/$C$1)*100</f>
-        <v>-0.44</v>
+        <v>-1.3</v>
       </c>
       <c r="D20">
         <f>COUNTA(H20:AB20)</f>
@@ -10852,20 +11276,20 @@
         <v>1</v>
       </c>
       <c r="H20" s="18">
-        <v>-2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>61</v>
+        <v>-6.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="B21">
         <f>SUM(H21:AB21)</f>
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="C21">
         <f>(B21/$C$1)*100</f>
-        <v>-0.74</v>
+        <v>-0.70000000000000007</v>
       </c>
       <c r="D21">
         <f>COUNTA(H21:AB21)</f>
@@ -10884,20 +11308,20 @@
         <v>1</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>64</v>
       </c>
       <c r="B22">
         <f>SUM(H22:AB22)</f>
-        <v>-2.1</v>
+        <v>2.9</v>
       </c>
       <c r="C22">
         <f>(B22/$C$1)*100</f>
-        <v>-0.42000000000000004</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="D22">
         <f>COUNTA(H22:AB22)</f>
@@ -10905,7 +11329,7 @@
       </c>
       <c r="E22">
         <f>COUNTIF(H22:AB22, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
         <f>COUNTIF(H22:AB22, "=0")</f>
@@ -10913,23 +11337,23 @@
       </c>
       <c r="G22">
         <f>COUNTIF(H22:AB22, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="18">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>60</v>
       </c>
       <c r="B23">
         <f>SUM(H23:AB23)</f>
-        <v>-0.3</v>
+        <v>-2.9</v>
       </c>
       <c r="C23">
         <f>(B23/$C$1)*100</f>
-        <v>-0.06</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="D23">
         <f>COUNTA(H23:AB23)</f>
@@ -10948,20 +11372,20 @@
         <v>1</v>
       </c>
       <c r="H23" s="18">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24">
         <f>SUM(H24:AB24)</f>
-        <v>-12.4</v>
+        <v>0</v>
       </c>
       <c r="C24">
         <f>(B24/$C$1)*100</f>
-        <v>-2.48</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <f>COUNTA(H24:AB24)</f>
@@ -10973,27 +11397,27 @@
       </c>
       <c r="F24">
         <f>COUNTIF(H24:AB24, "=0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
         <f>COUNTIF(H24:AB24, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="18">
-        <v>-12.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>80</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>66</v>
       </c>
       <c r="B25">
         <f>SUM(H25:AB25)</f>
-        <v>-0.1</v>
+        <v>-4.7</v>
       </c>
       <c r="C25">
         <f>(B25/$C$1)*100</f>
-        <v>-0.02</v>
+        <v>-0.94000000000000006</v>
       </c>
       <c r="D25">
         <f>COUNTA(H25:AB25)</f>
@@ -11012,20 +11436,20 @@
         <v>1</v>
       </c>
       <c r="H25" s="18">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+        <v>-4.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B26">
         <f>SUM(H26:AB26)</f>
-        <v>-0.7</v>
+        <v>5.4</v>
       </c>
       <c r="C26">
         <f>(B26/$C$1)*100</f>
-        <v>-0.13999999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="D26">
         <f>COUNTA(H26:AB26)</f>
@@ -11033,7 +11457,7 @@
       </c>
       <c r="E26">
         <f>COUNTIF(H26:AB26, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <f>COUNTIF(H26:AB26, "=0")</f>
@@ -11041,23 +11465,23 @@
       </c>
       <c r="G26">
         <f>COUNTIF(H26:AB26, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="18">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>97</v>
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="B27">
         <f>SUM(H27:AB27)</f>
-        <v>-1.9</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="C27">
         <f>(B27/$C$1)*100</f>
-        <v>-0.38</v>
+        <v>-0.88</v>
       </c>
       <c r="D27">
         <f>COUNTA(H27:AB27)</f>
@@ -11076,20 +11500,20 @@
         <v>1</v>
       </c>
       <c r="H27" s="18">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>142</v>
+        <v>-4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="B28">
         <f>SUM(H28:AB28)</f>
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <f>(B28/$C$1)*100</f>
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="D28">
         <f>COUNTA(H28:AB28)</f>
@@ -11108,24 +11532,24 @@
         <v>0</v>
       </c>
       <c r="H28" s="18">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>143</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>84</v>
       </c>
       <c r="B29">
         <f>SUM(H29:AB29)</f>
-        <v>-4.3</v>
+        <v>0</v>
       </c>
       <c r="C29">
         <f>(B29/$C$1)*100</f>
-        <v>-0.86</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <f>COUNTA(H29:AB29)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <f>COUNTIF(H29:AB29, "&gt;0")</f>
@@ -11137,31 +11561,28 @@
       </c>
       <c r="G29">
         <f>COUNTIF(H29:AB29, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H29" s="18">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>144</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>58</v>
       </c>
       <c r="B30">
         <f>SUM(H30:AB30)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C30">
         <f>(B30/$C$1)*100</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <f>COUNTA(H30:AB30)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <f>COUNTIF(H30:AB30, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <f>COUNTIF(H30:AB30, "=0")</f>
@@ -11171,13 +11592,10 @@
         <f>COUNTIF(H30:AB30, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H30" s="18">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>58</v>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="B31">
         <f>SUM(H31:AB31)</f>
@@ -11204,9 +11622,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="B32">
         <f>SUM(H32:AB32)</f>
@@ -11233,10 +11651,11 @@
         <v>0</v>
       </c>
       <c r="H32" s="15"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
-        <v>135</v>
+      <c r="I32" s="15"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="B33">
         <f>SUM(H33:AB33)</f>
@@ -11263,9 +11682,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="B34">
         <f>SUM(H34:AB34)</f>
@@ -11291,9 +11710,10 @@
         <f>COUNTIF(H34:AB34, "&lt;0")</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="H34" s="15"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
         <v>137</v>
       </c>
       <c r="B35">
@@ -11321,8 +11741,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>128</v>
       </c>
       <c r="B36">
@@ -11350,7 +11770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>67</v>
       </c>
@@ -11381,7 +11801,7 @@
       <c r="H37" s="15"/>
       <c r="I37" s="15"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -11414,7 +11834,7 @@
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -11443,8 +11863,9 @@
         <v>0</v>
       </c>
       <c r="H39" s="15"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I39" s="15"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>85</v>
       </c>
@@ -11472,9 +11893,10 @@
         <f>COUNTIF(H40:AB40, "&lt;0")</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="H40" s="15"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>130</v>
       </c>
       <c r="B41">
@@ -11501,9 +11923,10 @@
         <f>COUNTIF(H41:AB41, "&lt;0")</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="H41" s="15"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
         <v>69</v>
       </c>
       <c r="B42">
@@ -11532,7 +11955,7 @@
       </c>
       <c r="H42" s="15"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>54</v>
       </c>
@@ -11562,7 +11985,7 @@
       </c>
       <c r="H43" s="15"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>73</v>
       </c>
@@ -11591,9 +12014,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="15"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
         <v>91</v>
       </c>
       <c r="B45">
@@ -11622,8 +12049,8 @@
       </c>
       <c r="H45" s="15"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
         <v>76</v>
       </c>
       <c r="B46">
@@ -11651,8 +12078,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
         <v>63</v>
       </c>
       <c r="B47">
@@ -11680,8 +12107,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
         <v>75</v>
       </c>
       <c r="B48">
@@ -11708,6 +12135,7 @@
         <f>COUNTIF(H48:AB48, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H48" s="15"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -11737,9 +12165,10 @@
         <f>COUNTIF(H49:AB49, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H49" s="15"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="8" t="s">
         <v>90</v>
       </c>
       <c r="B50">
@@ -11797,10 +12226,11 @@
         <f>COUNTIF(H51:AB51, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H51" s="15"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B52">
         <f>SUM(H52:AB52)</f>
@@ -11828,7 +12258,7 @@
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" t="s">
         <v>89</v>
       </c>
       <c r="B53">
@@ -11858,7 +12288,7 @@
       <c r="H53" s="15"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+      <c r="A54" t="s">
         <v>74</v>
       </c>
       <c r="B54">
@@ -11888,7 +12318,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B55">
         <f>SUM(H55:AB55)</f>
@@ -11918,7 +12348,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B56">
         <f>SUM(H56:AB56)</f>
@@ -11944,10 +12374,11 @@
         <f>COUNTIF(H56:AB56, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H56" s="15"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B57">
         <f>SUM(H57:AB57)</f>
@@ -11977,8 +12408,8 @@
       <c r="I57" s="15"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>83</v>
+      <c r="A58" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="B58">
         <f>SUM(H58:AB58)</f>
@@ -12008,8 +12439,8 @@
       <c r="I58" s="15"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
-        <v>71</v>
+      <c r="A59" t="s">
+        <v>83</v>
       </c>
       <c r="B59">
         <f>SUM(H59:AB59)</f>
@@ -12035,11 +12466,12 @@
         <f>COUNTIF(H59:AB59, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H59" s="15"/>
       <c r="I59" s="15"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B60">
         <f>SUM(H60:AB60)</f>
@@ -12068,8 +12500,8 @@
       <c r="H60" s="15"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>98</v>
+      <c r="A61" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="B61">
         <f>SUM(H61:AB61)</f>
@@ -12098,8 +12530,8 @@
       <c r="H61" s="15"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>99</v>
+      <c r="A62" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="B62">
         <f>SUM(H62:AB62)</f>
@@ -12128,85 +12560,90 @@
       <c r="H62" s="15"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="8"/>
+      <c r="A63" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="B63">
-        <f t="shared" ref="B58:B66" si="0">SUM(H63:AB63)</f>
+        <f>SUM(H63:AB63)</f>
         <v>0</v>
       </c>
       <c r="C63">
-        <f t="shared" ref="C58:C66" si="1">(B63/$C$1)*100</f>
+        <f>(B63/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D63">
-        <f t="shared" ref="D58:D66" si="2">COUNTA(H63:AB63)</f>
+        <f>COUNTA(H63:AB63)</f>
         <v>0</v>
       </c>
       <c r="E63">
-        <f t="shared" ref="E58:E66" si="3">COUNTIF(H63:AB63, "&gt;0")</f>
+        <f>COUNTIF(H63:AB63, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F63">
-        <f t="shared" ref="F58:F66" si="4">COUNTIF(H63:AB63, "=0")</f>
+        <f>COUNTIF(H63:AB63, "=0")</f>
         <v>0</v>
       </c>
       <c r="G63">
-        <f t="shared" ref="G58:G66" si="5">COUNTIF(H63:AB63, "&lt;0")</f>
+        <f>COUNTIF(H63:AB63, "&lt;0")</f>
         <v>0</v>
       </c>
       <c r="H63" s="15"/>
       <c r="I63" s="15"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="8"/>
+      <c r="A64" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="B64">
-        <f t="shared" si="0"/>
+        <f>SUM(H64:AB64)</f>
         <v>0</v>
       </c>
       <c r="C64">
-        <f t="shared" si="1"/>
+        <f>(B64/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D64">
-        <f t="shared" si="2"/>
+        <f>COUNTA(H64:AB64)</f>
         <v>0</v>
       </c>
       <c r="E64">
-        <f t="shared" si="3"/>
+        <f>COUNTIF(H64:AB64, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F64">
-        <f t="shared" si="4"/>
+        <f>COUNTIF(H64:AB64, "=0")</f>
         <v>0</v>
       </c>
       <c r="G64">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+        <f>COUNTIF(H64:AB64, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="H64" s="15"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="8"/>
       <c r="B65">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B63:B66" si="0">SUM(H65:AB65)</f>
         <v>0</v>
       </c>
       <c r="C65">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C63:C66" si="1">(B65/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D65">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D63:D66" si="2">COUNTA(H65:AB65)</f>
         <v>0</v>
       </c>
       <c r="E65">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E63:E66" si="3">COUNTIF(H65:AB65, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F65">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="F63:F66" si="4">COUNTIF(H65:AB65, "=0")</f>
         <v>0</v>
       </c>
       <c r="G65">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="G63:G66" si="5">COUNTIF(H65:AB65, "&lt;0")</f>
         <v>0</v>
       </c>
     </row>
@@ -12493,30 +12930,53 @@
       <c r="H75" s="15"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB62">
-    <sortCondition descending="1" ref="D3:D62"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U64">
+    <sortCondition descending="1" ref="D3:D64"/>
   </sortState>
   <conditionalFormatting sqref="A3:A57">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="LEG">
+    <cfRule type="containsText" dxfId="27" priority="8" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="25" priority="10" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="24" priority="11" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="22" priority="13" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="21" priority="14" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",A3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A64">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="LEG">
+      <formula>NOT(ISERROR(SEARCH("LEG",A64)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="VEG">
+      <formula>NOT(ISERROR(SEARCH("VEG",A64)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="VEG">
+      <formula>NOT(ISERROR(SEARCH("VEG",A64)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="WEG">
+      <formula>NOT(ISERROR(SEARCH("WEG",A64)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="UEG">
+      <formula>NOT(ISERROR(SEARCH("UEG",A64)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="SEG">
+      <formula>NOT(ISERROR(SEARCH("SEG",A64)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="PEG">
+      <formula>NOT(ISERROR(SEARCH("PEG",A64)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1687CF6F-D478-4DF7-88B9-D61411E25716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACA1D5E-450B-4D2D-AF43-7FADA2168185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId6"/>
+    <pivotCache cacheId="3" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -625,7 +625,7 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="28">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -672,55 +672,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1076,10 +1027,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$L$2</c:f>
+              <c:f>Динамика!$B$2:$M$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1112,16 +1063,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46301</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$3:$L$3</c:f>
+              <c:f>Динамика!$B$3:$M$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>-20.100000000000001</c:v>
                 </c:pt>
@@ -1154,6 +1108,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>-27.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-12.000000000000028</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1260,10 +1217,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$L$2</c:f>
+              <c:f>Динамика!$B$2:$M$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1296,16 +1253,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46301</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$4:$L$4</c:f>
+              <c:f>Динамика!$B$4:$M$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>19.7</c:v>
                 </c:pt>
@@ -1338,6 +1298,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>109.69999999999996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>74.499999999999972</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1444,10 +1407,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$L$2</c:f>
+              <c:f>Динамика!$B$2:$M$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1480,16 +1443,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46301</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$5:$L$5</c:f>
+              <c:f>Динамика!$B$5:$M$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1.9</c:v>
                 </c:pt>
@@ -1521,6 +1487,9 @@
                   <c:v>14.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>14.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>14.799999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -1628,10 +1597,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$L$2</c:f>
+              <c:f>Динамика!$B$2:$M$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1664,16 +1633,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46301</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$6:$L$6</c:f>
+              <c:f>Динамика!$B$6:$M$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>-21</c:v>
                 </c:pt>
@@ -1706,6 +1678,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>-16.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-28.299999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1812,10 +1787,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$L$2</c:f>
+              <c:f>Динамика!$B$2:$M$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1848,16 +1823,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46301</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$7:$L$7</c:f>
+              <c:f>Динамика!$B$7:$M$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>-18.100000000000001</c:v>
                 </c:pt>
@@ -1890,6 +1868,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>-27.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-25.800000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1996,10 +1977,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$L$2</c:f>
+              <c:f>Динамика!$B$2:$M$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -2032,16 +2013,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46301</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$8:$L$8</c:f>
+              <c:f>Динамика!$B$8:$M$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>44.5</c:v>
                 </c:pt>
@@ -2074,6 +2058,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2183,10 +2170,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$L$2</c:f>
+              <c:f>Динамика!$B$2:$M$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -2219,16 +2206,19 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>46301</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$9:$L$9</c:f>
+              <c:f>Динамика!$B$9:$M$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>6.8999999999999915</c:v>
                 </c:pt>
@@ -2261,6 +2251,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>116.99999999999994</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>65.199999999999932</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3019,7 +3012,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46301.967136342595" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="77" xr:uid="{3D6F248A-0360-4477-B017-E96CAA4B0EB4}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46302.975628472224" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="75" xr:uid="{3D6F248A-0360-4477-B017-E96CAA4B0EB4}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:L1048576" sheet="Результаты"/>
   </cacheSource>
@@ -3031,40 +3024,40 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Абс" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-42.900000000000006" maxValue="163.89999999999998"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-42.900000000000006" maxValue="163.79999999999998"/>
     </cacheField>
     <cacheField name="Отн" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-8.58" maxValue="32.780000000000008"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-8.58" maxValue="32.760000000000005"/>
     </cacheField>
     <cacheField name="Кол-во" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="78"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="83"/>
     </cacheField>
     <cacheField name="Прибыль" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="51"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="54"/>
     </cacheField>
     <cacheField name="Нейтрал" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
     </cacheField>
     <cacheField name="Убыток" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="27"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="29"/>
     </cacheField>
     <cacheField name="ПроцПД" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="100"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="87.5"/>
     </cacheField>
     <cacheField name="САП" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-19.5" maxValue="2.7250000000000001"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-19.5" maxValue="3.0000000000000004"/>
     </cacheField>
     <cacheField name="СОП" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-3.9" maxValue="0.54500000000000004"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-3.9" maxValue="0.60000000000000009"/>
     </cacheField>
     <cacheField name="Тип" numFmtId="0">
       <sharedItems containsBlank="1" count="7">
         <s v="PEG"/>
+        <s v="LEG"/>
         <s v="WEG"/>
-        <s v="LEG"/>
         <s v="UEG"/>
+        <s v="VEG"/>
         <s v="SEG"/>
-        <s v="VEG"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -3078,104 +3071,104 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="77">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="75">
   <r>
     <n v="1"/>
     <s v="PEG17_PHOENIX"/>
-    <n v="163.89999999999998"/>
-    <n v="32.780000000000008"/>
-    <n v="78"/>
-    <n v="51"/>
+    <n v="163.79999999999998"/>
+    <n v="32.760000000000005"/>
+    <n v="83"/>
+    <n v="54"/>
     <n v="0"/>
-    <n v="27"/>
-    <n v="65.384615384615387"/>
-    <n v="2.1012820512820509"/>
-    <n v="0.42025641025641036"/>
+    <n v="29"/>
+    <n v="65.060240963855421"/>
+    <n v="1.9734939759036143"/>
+    <n v="0.39469879518072293"/>
     <x v="0"/>
   </r>
   <r>
     <n v="2"/>
-    <s v="WEG3_BATYA"/>
-    <n v="45"/>
-    <n v="9.0000000000000018"/>
-    <n v="56"/>
-    <n v="33"/>
+    <s v="PEG11_KUSURUKEN"/>
+    <n v="38.799999999999997"/>
+    <n v="7.7600000000000016"/>
+    <n v="43"/>
+    <n v="22"/>
     <n v="1"/>
-    <n v="22"/>
-    <n v="58.928571428571431"/>
-    <n v="0.8035714285714286"/>
-    <n v="0.16071428571428575"/>
+    <n v="20"/>
+    <n v="51.162790697674424"/>
+    <n v="0.9023255813953488"/>
+    <n v="0.1804651162790698"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <s v="LEG2_FENNEC"/>
+    <n v="38.099999999999994"/>
+    <n v="7.620000000000001"/>
+    <n v="25"/>
+    <n v="17"/>
+    <n v="0"/>
+    <n v="8"/>
+    <n v="68"/>
+    <n v="1.5239999999999998"/>
+    <n v="0.30480000000000002"/>
     <x v="1"/>
   </r>
   <r>
-    <n v="3"/>
-    <s v="PEG11_KUSURUKEN"/>
-    <n v="35.099999999999994"/>
-    <n v="7.0200000000000014"/>
-    <n v="42"/>
-    <n v="21"/>
+    <n v="4"/>
+    <s v="WEG3_BATYA"/>
+    <n v="34"/>
+    <n v="6.8000000000000025"/>
+    <n v="58"/>
+    <n v="34"/>
     <n v="1"/>
-    <n v="20"/>
-    <n v="50"/>
-    <n v="0.83571428571428563"/>
-    <n v="0.16714285714285718"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <s v="LEG2_FENNEC"/>
-    <n v="29.099999999999998"/>
-    <n v="5.8200000000000012"/>
-    <n v="24"/>
-    <n v="16"/>
-    <n v="0"/>
-    <n v="8"/>
-    <n v="66.666666666666657"/>
-    <n v="1.2124999999999999"/>
-    <n v="0.24250000000000005"/>
+    <n v="23"/>
+    <n v="58.620689655172406"/>
+    <n v="0.58620689655172409"/>
+    <n v="0.11724137931034487"/>
     <x v="2"/>
   </r>
   <r>
     <n v="5"/>
+    <s v="LEG1_LAKSAe"/>
+    <n v="24.000000000000004"/>
+    <n v="4.8000000000000007"/>
+    <n v="8"/>
+    <n v="7"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="87.5"/>
+    <n v="3.0000000000000004"/>
+    <n v="0.60000000000000009"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="6"/>
     <s v="UEG9_GRAVY2"/>
-    <n v="18.700000000000003"/>
-    <n v="3.74"/>
-    <n v="12"/>
-    <n v="8"/>
+    <n v="23.200000000000003"/>
+    <n v="4.6400000000000006"/>
+    <n v="15"/>
+    <n v="9"/>
     <n v="0"/>
-    <n v="4"/>
-    <n v="66.666666666666657"/>
-    <n v="1.5583333333333336"/>
-    <n v="0.3116666666666667"/>
+    <n v="6"/>
+    <n v="60"/>
+    <n v="1.5466666666666669"/>
+    <n v="0.30933333333333335"/>
     <x v="3"/>
   </r>
   <r>
-    <n v="6"/>
-    <s v="LEG1_LAKSAe"/>
-    <n v="18.700000000000003"/>
-    <n v="3.74"/>
     <n v="7"/>
-    <n v="6"/>
+    <s v="VEG1_EARTH"/>
+    <n v="17"/>
+    <n v="3.4"/>
+    <n v="9"/>
+    <n v="5"/>
     <n v="0"/>
-    <n v="1"/>
-    <n v="85.714285714285708"/>
-    <n v="2.6714285714285717"/>
-    <n v="0.53428571428571436"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <s v="UEG8_SOLDIER"/>
-    <n v="16.700000000000003"/>
-    <n v="3.3400000000000007"/>
-    <n v="13"/>
-    <n v="8"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="61.53846153846154"/>
-    <n v="1.2846153846153849"/>
-    <n v="0.25692307692307698"/>
-    <x v="3"/>
+    <n v="4"/>
+    <n v="55.555555555555557"/>
+    <n v="1.8888888888888888"/>
+    <n v="0.37777777777777777"/>
+    <x v="4"/>
   </r>
   <r>
     <n v="8"/>
@@ -3189,7 +3182,7 @@
     <n v="61.53846153846154"/>
     <n v="1.2307692307692308"/>
     <n v="0.24615384615384611"/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="9"/>
@@ -3231,38 +3224,10 @@
     <n v="70"/>
     <n v="1.2899999999999996"/>
     <n v="0.25799999999999995"/>
-    <x v="4"/>
+    <x v="5"/>
   </r>
   <r>
     <n v="12"/>
-    <s v="VEG1_EARTH"/>
-    <n v="12.200000000000001"/>
-    <n v="2.44"/>
-    <n v="7"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="57.142857142857139"/>
-    <n v="1.7428571428571431"/>
-    <n v="0.34857142857142859"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <s v="PEG30_ETC2"/>
-    <n v="10.9"/>
-    <n v="2.1800000000000002"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="2.7250000000000001"/>
-    <n v="0.54500000000000004"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="14"/>
     <s v="LEG1_IGOGOSHA2"/>
     <n v="9.9999999999999982"/>
     <n v="2"/>
@@ -3273,10 +3238,10 @@
     <n v="60"/>
     <n v="1.9999999999999996"/>
     <n v="0.4"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
-    <n v="15"/>
+    <n v="10"/>
     <s v="LEG2_DRINKER"/>
     <n v="9.6000000000000014"/>
     <n v="1.920000000000001"/>
@@ -3287,38 +3252,10 @@
     <n v="50"/>
     <n v="0.43636363636363645"/>
     <n v="8.7272727272727321E-2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="17"/>
-    <s v="WEG4_DOG"/>
-    <n v="9.5"/>
-    <n v="1.9"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="50"/>
-    <n v="2.375"/>
-    <n v="0.47499999999999998"/>
     <x v="1"/>
   </r>
   <r>
-    <n v="16"/>
-    <s v="PEG18_ANDUIN"/>
-    <n v="9.5"/>
-    <n v="1.9"/>
-    <n v="9"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="55.555555555555557"/>
-    <n v="1.0555555555555556"/>
-    <n v="0.21111111111111111"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="19"/>
+    <n v="14"/>
     <s v="LEG1_PIN"/>
     <n v="9.2000000000000028"/>
     <n v="1.8400000000000003"/>
@@ -3329,10 +3266,10 @@
     <n v="48"/>
     <n v="0.3680000000000001"/>
     <n v="7.3600000000000013E-2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
-    <n v="18"/>
+    <n v="15"/>
     <s v="UEG6_SHERIFF"/>
     <n v="9"/>
     <n v="1.7999999999999998"/>
@@ -3346,7 +3283,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="20"/>
+    <n v="17"/>
     <s v="UEG7_LOVERGOOSE"/>
     <n v="7.0000000000000009"/>
     <n v="1.4"/>
@@ -3360,49 +3297,49 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="21"/>
+    <n v="16"/>
+    <s v="UEG8_SOLDIER"/>
+    <n v="6.2000000000000028"/>
+    <n v="1.2400000000000007"/>
+    <n v="18"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="9"/>
+    <n v="50"/>
+    <n v="0.34444444444444461"/>
+    <n v="6.888888888888893E-2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="19"/>
     <s v="LEG2_LYNX"/>
-    <n v="3.599999999999993"/>
-    <n v="0.71999999999999897"/>
-    <n v="27"/>
-    <n v="15"/>
+    <n v="4.4999999999999929"/>
+    <n v="0.89999999999999902"/>
+    <n v="28"/>
+    <n v="16"/>
     <n v="0"/>
     <n v="12"/>
-    <n v="55.555555555555557"/>
-    <n v="0.13333333333333308"/>
-    <n v="2.666666666666663E-2"/>
-    <x v="2"/>
+    <n v="57.142857142857139"/>
+    <n v="0.16071428571428545"/>
+    <n v="3.2142857142857105E-2"/>
+    <x v="1"/>
   </r>
   <r>
-    <n v="22"/>
-    <s v="PEG17_TEMPLAR"/>
-    <n v="2.6000000000000005"/>
-    <n v="0.52000000000000013"/>
+    <n v="18"/>
+    <s v="PEG30_ETC2"/>
+    <n v="4.3"/>
+    <n v="0.8600000000000001"/>
+    <n v="6"/>
+    <n v="4"/>
+    <n v="0"/>
     <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="1.3000000000000003"/>
-    <n v="0.26000000000000006"/>
+    <n v="66.666666666666657"/>
+    <n v="0.71666666666666667"/>
+    <n v="0.14333333333333334"/>
     <x v="0"/>
   </r>
   <r>
-    <n v="23"/>
-    <s v="UEG4_CANADIAN"/>
-    <n v="2"/>
-    <n v="0.4"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="2"/>
-    <n v="0.4"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="24"/>
+    <n v="20"/>
     <s v="SEG3_FORCE"/>
     <n v="1.9000000000000004"/>
     <n v="0.37999999999999989"/>
@@ -3413,10 +3350,24 @@
     <n v="60"/>
     <n v="0.38000000000000006"/>
     <n v="7.5999999999999984E-2"/>
-    <x v="4"/>
+    <x v="5"/>
   </r>
   <r>
-    <n v="25"/>
+    <n v="21"/>
+    <s v="UEG4_CANADIAN"/>
+    <n v="1.5"/>
+    <n v="0.30000000000000004"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="0.75"/>
+    <n v="0.15000000000000002"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="22"/>
     <s v="PEG4_U3"/>
     <n v="1.1999999999999993"/>
     <n v="0.23999999999999988"/>
@@ -3430,7 +3381,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="26"/>
+    <n v="23"/>
     <s v="PEG13_DWDDCr"/>
     <n v="1"/>
     <n v="0.2"/>
@@ -3444,21 +3395,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="29"/>
-    <s v="UEG7_CANNIBAL"/>
-    <n v="0.5"/>
-    <n v="0.10000000000000026"/>
-    <n v="11"/>
-    <n v="6"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="54.54545454545454"/>
-    <n v="4.5454545454545456E-2"/>
-    <n v="9.0909090909091148E-3"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="27"/>
+    <n v="24"/>
     <s v="UEG7_DETECTIVE"/>
     <n v="0.39999999999999991"/>
     <n v="8.0000000000000016E-2"/>
@@ -3472,7 +3409,35 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="28"/>
+    <n v="25"/>
+    <s v="UEG7_CANNIBAL"/>
+    <n v="9.9999999999999978E-2"/>
+    <n v="2.0000000000000254E-2"/>
+    <n v="12"/>
+    <n v="6"/>
+    <n v="0"/>
+    <n v="6"/>
+    <n v="50"/>
+    <n v="8.3333333333333315E-3"/>
+    <n v="1.6666666666666878E-3"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <s v="WEG4_DOG"/>
+    <n v="-0.5"/>
+    <n v="-0.10000000000000009"/>
+    <n v="6"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="50"/>
+    <n v="-8.3333333333333329E-2"/>
+    <n v="-1.666666666666668E-2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="29"/>
     <s v="PEG4_UNIVERSAL"/>
     <n v="-0.69999999999999929"/>
     <n v="-0.13999999999999901"/>
@@ -3486,21 +3451,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="35"/>
-    <s v="UEG7_ADVENTURE"/>
-    <n v="-0.69999999999999984"/>
-    <n v="-0.13999999999999999"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="25"/>
-    <n v="-0.17499999999999996"/>
-    <n v="-3.4999999999999996E-2"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="36"/>
+    <n v="27"/>
     <s v="LEG2_LOGAN"/>
     <n v="-0.70000000000000107"/>
     <n v="-0.14000000000000012"/>
@@ -3511,10 +3462,10 @@
     <n v="75"/>
     <n v="-5.8333333333333424E-2"/>
     <n v="-1.1666666666666678E-2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
-    <n v="37"/>
+    <n v="28"/>
     <s v="LEG1_OKROSHKA"/>
     <n v="-1.6"/>
     <n v="-0.32"/>
@@ -3525,10 +3476,24 @@
     <n v="0"/>
     <n v="-1.6"/>
     <n v="-0.32"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
-    <n v="38"/>
+    <n v="35"/>
+    <s v="PEG17_PROBIUS"/>
+    <n v="-1.9"/>
+    <n v="-0.38000000000000012"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="66.666666666666657"/>
+    <n v="-0.6333333333333333"/>
+    <n v="-0.12666666666666671"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="36"/>
     <s v="PEG14_RANGER"/>
     <n v="-1.9000000000000001"/>
     <n v="-0.38"/>
@@ -3542,7 +3507,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="39"/>
+    <n v="37"/>
     <s v="UEG4_PELICAN"/>
     <n v="-2.9000000000000004"/>
     <n v="-0.58000000000000007"/>
@@ -3556,21 +3521,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="30"/>
-    <s v="PEG17_PROBIUS"/>
-    <n v="-3"/>
-    <n v="-0.60000000000000009"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="-1.5"/>
-    <n v="-0.30000000000000004"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="31"/>
+    <n v="38"/>
     <s v="UEG6_PIGEON"/>
     <n v="-3.0999999999999983"/>
     <n v="-0.61999999999999988"/>
@@ -3584,7 +3535,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="32"/>
+    <n v="39"/>
     <s v="UEG7_PIGEON"/>
     <n v="-3.0999999999999996"/>
     <n v="-0.61999999999999988"/>
@@ -3598,7 +3549,35 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="33"/>
+    <n v="30"/>
+    <s v="UEG7_ADVENTURE"/>
+    <n v="-4.7"/>
+    <n v="-0.94000000000000006"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="20"/>
+    <n v="-0.94000000000000006"/>
+    <n v="-0.188"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <s v="PEG17_TEMPLAR"/>
+    <n v="-4.9999999999999991"/>
+    <n v="-0.99999999999999989"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="33.333333333333329"/>
+    <n v="-1.6666666666666663"/>
+    <n v="-0.33333333333333331"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="32"/>
     <s v="PEG17_SELENDIS"/>
     <n v="-5.6"/>
     <n v="-1.1200000000000001"/>
@@ -3612,7 +3591,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="34"/>
+    <n v="33"/>
     <s v="LEG1_PHOGA"/>
     <n v="-6"/>
     <n v="-1.2"/>
@@ -3623,10 +3602,10 @@
     <n v="0"/>
     <n v="-6"/>
     <n v="-1.2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
-    <n v="40"/>
+    <n v="34"/>
     <s v="PEG18_UTER"/>
     <n v="-6.2"/>
     <n v="-1.24"/>
@@ -3640,7 +3619,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="41"/>
+    <n v="40"/>
     <s v="PEG31_HYPERION"/>
     <n v="-7.4999999999999991"/>
     <n v="-1.4999999999999998"/>
@@ -3654,7 +3633,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="42"/>
+    <n v="41"/>
     <s v="PEG26_UNKNOWN"/>
     <n v="-7.5"/>
     <n v="-1.5"/>
@@ -3668,7 +3647,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="43"/>
+    <n v="42"/>
     <s v="LEG1_IRONANNY2"/>
     <n v="-7.5"/>
     <n v="-1.5"/>
@@ -3679,10 +3658,10 @@
     <n v="20"/>
     <n v="-1.5"/>
     <n v="-0.3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
-    <n v="44"/>
+    <n v="43"/>
     <s v="WEG7_PARADOX"/>
     <n v="-7.5000000000000009"/>
     <n v="-1.5"/>
@@ -3693,10 +3672,10 @@
     <n v="50"/>
     <n v="-1.2500000000000002"/>
     <n v="-0.25"/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
-    <n v="45"/>
+    <n v="44"/>
     <s v="PEG18_DIABLO2"/>
     <n v="-9.1"/>
     <n v="-1.82"/>
@@ -3710,7 +3689,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="46"/>
+    <n v="45"/>
     <s v="LEG1_BIBI2"/>
     <n v="-9.4000000000000021"/>
     <n v="-1.879999999999999"/>
@@ -3721,10 +3700,10 @@
     <n v="47.058823529411761"/>
     <n v="-0.55294117647058838"/>
     <n v="-0.11058823529411758"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
-    <n v="47"/>
+    <n v="46"/>
     <s v="UEG6_VULTURE"/>
     <n v="-9.6999999999999993"/>
     <n v="-1.9400000000000002"/>
@@ -3738,7 +3717,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="48"/>
+    <n v="47"/>
     <s v="UEG7_CELEBRITY"/>
     <n v="-10.199999999999999"/>
     <n v="-2.04"/>
@@ -3750,6 +3729,20 @@
     <n v="-2.5499999999999998"/>
     <n v="-0.51"/>
     <x v="3"/>
+  </r>
+  <r>
+    <n v="48"/>
+    <s v="PEG17_ZEALOT"/>
+    <n v="-11.399999999999997"/>
+    <n v="-2.2799999999999998"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="50"/>
+    <n v="-2.8499999999999992"/>
+    <n v="-0.56999999999999995"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="49"/>
@@ -3791,10 +3784,24 @@
     <n v="40"/>
     <n v="-2.4"/>
     <n v="-0.48"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="52"/>
+    <s v="PEG18_ANDUIN"/>
+    <n v="-12.5"/>
+    <n v="-2.4999999999999996"/>
+    <n v="11"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="6"/>
+    <n v="45.454545454545453"/>
+    <n v="-1.1363636363636365"/>
+    <n v="-0.22727272727272724"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="53"/>
     <s v="PEG18_UTER2"/>
     <n v="-13"/>
     <n v="-2.6000000000000005"/>
@@ -3808,7 +3815,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="53"/>
+    <n v="54"/>
     <s v="LEG1_CC2"/>
     <n v="-13.299999999999999"/>
     <n v="-2.6599999999999997"/>
@@ -3819,21 +3826,7 @@
     <n v="44.444444444444443"/>
     <n v="-1.4777777777777776"/>
     <n v="-0.29555555555555552"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="54"/>
-    <s v="UEG7_CARRIER"/>
-    <n v="-13.899999999999999"/>
-    <n v="-2.7800000000000002"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-2.78"/>
-    <n v="-0.55600000000000005"/>
-    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="55"/>
@@ -3847,52 +3840,24 @@
     <n v="0"/>
     <n v="-2.8"/>
     <n v="-0.55999999999999994"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="56"/>
-    <s v="VEG1_MOON"/>
-    <n v="-16.600000000000001"/>
-    <n v="-3.3200000000000003"/>
-    <n v="9"/>
-    <n v="2"/>
+    <s v="UEG7_CARRIER"/>
+    <n v="-15.099999999999998"/>
+    <n v="-3.0200000000000005"/>
+    <n v="6"/>
     <n v="0"/>
-    <n v="7"/>
-    <n v="22.222222222222221"/>
-    <n v="-1.8444444444444446"/>
-    <n v="-0.36888888888888893"/>
-    <x v="5"/>
+    <n v="1"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="-2.5166666666666662"/>
+    <n v="-0.50333333333333341"/>
+    <x v="3"/>
   </r>
   <r>
     <n v="57"/>
-    <s v="PEG19_ANUBARAK"/>
-    <n v="-17.299999999999997"/>
-    <n v="-3.46"/>
-    <n v="11"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="7"/>
-    <n v="36.363636363636367"/>
-    <n v="-1.5727272727272725"/>
-    <n v="-0.31454545454545452"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="58"/>
-    <s v="PEG17_ZEALOT"/>
-    <n v="-18.799999999999997"/>
-    <n v="-3.76"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="33.333333333333329"/>
-    <n v="-6.2666666666666657"/>
-    <n v="-1.2533333333333332"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="59"/>
     <s v="UEG9_BIRDWATCHER2"/>
     <n v="-19.5"/>
     <n v="-3.9"/>
@@ -3906,7 +3871,21 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="60"/>
+    <n v="58"/>
+    <s v="VEG1_MOON"/>
+    <n v="-20.100000000000001"/>
+    <n v="-4.0200000000000005"/>
+    <n v="10"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="8"/>
+    <n v="20"/>
+    <n v="-2.0100000000000002"/>
+    <n v="-0.40200000000000002"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="59"/>
     <s v="VEG1_VENUS"/>
     <n v="-22.700000000000003"/>
     <n v="-4.5399999999999991"/>
@@ -3917,20 +3896,34 @@
     <n v="47.368421052631575"/>
     <n v="-1.1947368421052633"/>
     <n v="-0.23894736842105258"/>
-    <x v="5"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="60"/>
+    <s v="PEG19_ANUBARAK"/>
+    <n v="-25.799999999999997"/>
+    <n v="-5.16"/>
+    <n v="12"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="8"/>
+    <n v="33.333333333333329"/>
+    <n v="-2.15"/>
+    <n v="-0.43"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="61"/>
     <s v="PEG18_BLAZE"/>
-    <n v="-39.599999999999994"/>
-    <n v="-7.919999999999999"/>
-    <n v="18"/>
+    <n v="-42.199999999999996"/>
+    <n v="-8.44"/>
+    <n v="19"/>
     <n v="8"/>
     <n v="1"/>
-    <n v="9"/>
-    <n v="44.444444444444443"/>
-    <n v="-2.1999999999999997"/>
-    <n v="-0.43999999999999995"/>
+    <n v="10"/>
+    <n v="42.105263157894733"/>
+    <n v="-2.2210526315789472"/>
+    <n v="-0.44421052631578944"/>
     <x v="0"/>
   </r>
   <r>
@@ -3945,35 +3938,7 @@
     <n v="0"/>
     <n v="-10.725000000000001"/>
     <n v="-2.145"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="6"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <m/>
@@ -4161,7 +4126,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{08A3FD17-FFE6-464D-A72F-02ADC3CE221B}" name="Сводная таблица3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{08A3FD17-FFE6-464D-A72F-02ADC3CE221B}" name="Сводная таблица3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:G10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -4177,12 +4142,12 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="8">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="4"/>
         <item x="2"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="1"/>
         <item h="1" x="6"/>
         <item t="default"/>
       </items>
@@ -4764,7 +4729,7 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
-        <v>46300</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4795,16 +4760,16 @@
         <v>116</v>
       </c>
       <c r="B4" s="12">
-        <v>-27.200000000000003</v>
+        <v>-12.000000000000028</v>
       </c>
       <c r="C4" s="12">
-        <v>-5.4399999999999968</v>
+        <v>-2.3999999999999977</v>
       </c>
       <c r="D4" s="12">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E4" s="12">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F4" s="12">
         <v>2</v>
@@ -4818,22 +4783,22 @@
         <v>117</v>
       </c>
       <c r="B5" s="12">
-        <v>109.69999999999996</v>
+        <v>74.499999999999972</v>
       </c>
       <c r="C5" s="12">
-        <v>21.940000000000015</v>
+        <v>14.900000000000007</v>
       </c>
       <c r="D5" s="12">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="E5" s="12">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F5" s="12">
         <v>5</v>
       </c>
       <c r="G5" s="12">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4864,22 +4829,22 @@
         <v>119</v>
       </c>
       <c r="B7" s="12">
-        <v>-16.200000000000003</v>
+        <v>-28.299999999999994</v>
       </c>
       <c r="C7" s="12">
-        <v>-3.2399999999999958</v>
+        <v>-5.6599999999999975</v>
       </c>
       <c r="D7" s="12">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E7" s="12">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F7" s="12">
         <v>3</v>
       </c>
       <c r="G7" s="12">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4887,22 +4852,22 @@
         <v>120</v>
       </c>
       <c r="B8" s="12">
-        <v>-27.1</v>
+        <v>-25.800000000000004</v>
       </c>
       <c r="C8" s="12">
-        <v>-5.42</v>
+        <v>-5.16</v>
       </c>
       <c r="D8" s="12">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E8" s="12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="12">
         <v>0</v>
       </c>
       <c r="G8" s="12">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4910,22 +4875,22 @@
         <v>121</v>
       </c>
       <c r="B9" s="12">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C9" s="12">
-        <v>12.600000000000001</v>
+        <v>8.4000000000000021</v>
       </c>
       <c r="D9" s="12">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E9" s="12">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F9" s="12">
         <v>2</v>
       </c>
       <c r="G9" s="12">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4933,22 +4898,22 @@
         <v>114</v>
       </c>
       <c r="B10" s="12">
-        <v>116.99999999999994</v>
+        <v>65.199999999999932</v>
       </c>
       <c r="C10" s="12">
-        <v>23.400000000000027</v>
+        <v>13.040000000000013</v>
       </c>
       <c r="D10" s="12">
-        <v>659</v>
+        <v>696</v>
       </c>
       <c r="E10" s="12">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="F10" s="12">
         <v>12</v>
       </c>
       <c r="G10" s="12">
-        <v>303</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -5360,7 +5325,9 @@
       <c r="L2" s="16">
         <v>46301</v>
       </c>
-      <c r="M2" s="16"/>
+      <c r="M2" s="16">
+        <v>46302</v>
+      </c>
       <c r="N2" s="16"/>
       <c r="O2" s="16"/>
       <c r="P2" s="16"/>
@@ -5410,6 +5377,9 @@
       <c r="L3" s="12">
         <v>-27.200000000000003</v>
       </c>
+      <c r="M3">
+        <v>-12.000000000000028</v>
+      </c>
     </row>
     <row r="4" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -5448,6 +5418,9 @@
       <c r="L4" s="12">
         <v>109.69999999999996</v>
       </c>
+      <c r="M4">
+        <v>74.499999999999972</v>
+      </c>
     </row>
     <row r="5" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -5486,6 +5459,9 @@
       <c r="L5" s="12">
         <v>14.799999999999997</v>
       </c>
+      <c r="M5">
+        <v>14.799999999999997</v>
+      </c>
     </row>
     <row r="6" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -5524,6 +5500,9 @@
       <c r="L6" s="12">
         <v>-16.200000000000003</v>
       </c>
+      <c r="M6">
+        <v>-28.299999999999994</v>
+      </c>
     </row>
     <row r="7" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -5562,6 +5541,9 @@
       <c r="L7" s="12">
         <v>-27.1</v>
       </c>
+      <c r="M7">
+        <v>-25.800000000000004</v>
+      </c>
     </row>
     <row r="8" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -5600,6 +5582,9 @@
       <c r="L8" s="12">
         <v>63</v>
       </c>
+      <c r="M8">
+        <v>42</v>
+      </c>
     </row>
     <row r="9" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -5610,7 +5595,7 @@
         <v>6.8999999999999915</v>
       </c>
       <c r="C9">
-        <f t="shared" ref="C9:L9" si="0">SUM(C3:C8)</f>
+        <f t="shared" ref="C9:M9" si="0">SUM(C3:C8)</f>
         <v>5.7000000000000028</v>
       </c>
       <c r="D9">
@@ -5648,6 +5633,10 @@
       <c r="L9">
         <f t="shared" si="0"/>
         <v>116.99999999999994</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="0"/>
+        <v>65.199999999999932</v>
       </c>
     </row>
     <row r="11" spans="1:121" x14ac:dyDescent="0.25">
@@ -5695,6 +5684,10 @@
         <f t="shared" si="2"/>
         <v>46301</v>
       </c>
+      <c r="M11" s="16">
+        <f t="shared" ref="M11" si="3">M2</f>
+        <v>46302</v>
+      </c>
     </row>
     <row r="12" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -5709,40 +5702,44 @@
         <v>-19.799999999999997</v>
       </c>
       <c r="D12">
-        <f t="shared" ref="D12:L12" si="3">D3-C3</f>
+        <f t="shared" ref="D12:M12" si="4">D3-C3</f>
         <v>17.799999999999997</v>
       </c>
       <c r="E12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21.200000000000003</v>
       </c>
       <c r="F12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29.300000000000011</v>
       </c>
       <c r="G12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13.59999999999998</v>
       </c>
       <c r="H12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-59.000000000000014</v>
       </c>
       <c r="I12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23.500000000000007</v>
       </c>
       <c r="J12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.1999999999999957</v>
       </c>
       <c r="K12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-32.299999999999976</v>
       </c>
       <c r="L12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-6.6000000000000085</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="4"/>
+        <v>15.199999999999974</v>
       </c>
     </row>
     <row r="13" spans="1:121" x14ac:dyDescent="0.25">
@@ -5750,48 +5747,52 @@
         <v>117</v>
       </c>
       <c r="B13">
-        <f t="shared" ref="B13:B17" si="4">B4</f>
+        <f t="shared" ref="B13:B17" si="5">B4</f>
         <v>19.7</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:L17" si="5">C4-B4</f>
+        <f t="shared" ref="C13:M17" si="6">C4-B4</f>
         <v>31.000000000000004</v>
       </c>
       <c r="D13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>17.599999999999994</v>
       </c>
       <c r="E13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.700000000000003</v>
       </c>
       <c r="F13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.19999999999998863</v>
       </c>
       <c r="G13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
       <c r="H13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-15.5</v>
       </c>
       <c r="I13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>15.300000000000011</v>
       </c>
       <c r="J13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>23.200000000000017</v>
       </c>
       <c r="K13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.1999999999999602</v>
       </c>
       <c r="L13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-3.2000000000000171</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="6"/>
+        <v>-35.199999999999989</v>
       </c>
     </row>
     <row r="14" spans="1:121" x14ac:dyDescent="0.25">
@@ -5799,47 +5800,51 @@
         <v>118</v>
       </c>
       <c r="B14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.9</v>
       </c>
       <c r="C14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="D14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="E14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.2000000000000011</v>
       </c>
       <c r="F14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.1999999999999957</v>
       </c>
       <c r="G14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.7000000000000028</v>
       </c>
       <c r="H14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-10.100000000000001</v>
       </c>
       <c r="I14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-5.2000000000000011</v>
       </c>
       <c r="J14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.0999999999999996</v>
       </c>
       <c r="K14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5848,48 +5853,52 @@
         <v>119</v>
       </c>
       <c r="B15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-21</v>
       </c>
       <c r="C15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-20</v>
       </c>
       <c r="D15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>39.6</v>
       </c>
       <c r="E15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.5</v>
       </c>
       <c r="F15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-13.299999999999997</v>
       </c>
       <c r="G15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-36.300000000000004</v>
       </c>
       <c r="H15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-4.0999999999999943</v>
       </c>
       <c r="I15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>31.8</v>
       </c>
       <c r="J15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="K15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-16.500000000000007</v>
       </c>
       <c r="L15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>15.299999999999997</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="6"/>
+        <v>-12.099999999999991</v>
       </c>
     </row>
     <row r="16" spans="1:121" x14ac:dyDescent="0.25">
@@ -5897,100 +5906,108 @@
         <v>120</v>
       </c>
       <c r="B16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-18.100000000000001</v>
       </c>
       <c r="C16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-4.5999999999999979</v>
       </c>
       <c r="F16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-14.799999999999997</v>
       </c>
       <c r="H16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-9.6000000000000014</v>
       </c>
       <c r="J16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-7.7000000000000028</v>
       </c>
       <c r="K16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>23.6</v>
       </c>
       <c r="L16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.1000000000000014</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M16">
+        <f t="shared" si="6"/>
+        <v>1.2999999999999972</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
       <c r="B17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>44.5</v>
       </c>
       <c r="C17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.39999999999999858</v>
       </c>
       <c r="D17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.299999999999997</v>
       </c>
       <c r="F17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.0000000000000071</v>
       </c>
       <c r="G17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.899999999999991</v>
       </c>
       <c r="H17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-2.8999999999999915</v>
       </c>
       <c r="I17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.4000000000000057</v>
       </c>
       <c r="J17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-6.8999999999999915</v>
       </c>
       <c r="K17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-14.500000000000007</v>
       </c>
       <c r="L17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.399999999999999</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M17">
+        <f t="shared" si="6"/>
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>139</v>
       </c>
@@ -5999,44 +6016,48 @@
         <v>6.8999999999999915</v>
       </c>
       <c r="C18">
-        <f t="shared" ref="C18" si="6">SUM(C12:C17)</f>
+        <f t="shared" ref="C18" si="7">SUM(C12:C17)</f>
         <v>-1.1999999999999922</v>
       </c>
       <c r="D18">
-        <f t="shared" ref="D18" si="7">SUM(D12:D17)</f>
+        <f t="shared" ref="D18" si="8">SUM(D12:D17)</f>
         <v>82</v>
       </c>
       <c r="E18">
-        <f t="shared" ref="E18" si="8">SUM(E12:E17)</f>
+        <f t="shared" ref="E18" si="9">SUM(E12:E17)</f>
         <v>47.300000000000011</v>
       </c>
       <c r="F18">
-        <f t="shared" ref="F18" si="9">SUM(F12:F17)</f>
+        <f t="shared" ref="F18" si="10">SUM(F12:F17)</f>
         <v>21.400000000000006</v>
       </c>
       <c r="G18">
-        <f t="shared" ref="G18" si="10">SUM(G12:G17)</f>
+        <f t="shared" ref="G18" si="11">SUM(G12:G17)</f>
         <v>-12.400000000000027</v>
       </c>
       <c r="H18">
-        <f t="shared" ref="H18" si="11">SUM(H12:H17)</f>
+        <f t="shared" ref="H18" si="12">SUM(H12:H17)</f>
         <v>-91.600000000000009</v>
       </c>
       <c r="I18">
-        <f t="shared" ref="I18:J18" si="12">SUM(I12:I17)</f>
+        <f t="shared" ref="I18:J18" si="13">SUM(I12:I17)</f>
         <v>54.400000000000013</v>
       </c>
       <c r="J18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>24.700000000000017</v>
       </c>
       <c r="K18">
-        <f t="shared" ref="K18:L18" si="13">SUM(K12:K17)</f>
+        <f t="shared" ref="K18:L18" si="14">SUM(K12:K17)</f>
         <v>-35.500000000000028</v>
       </c>
       <c r="L18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>20.999999999999972</v>
+      </c>
+      <c r="M18">
+        <f t="shared" ref="M18" si="15">SUM(M12:M17)</f>
+        <v>-51.800000000000011</v>
       </c>
     </row>
   </sheetData>
@@ -6143,34 +6164,34 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>163.89999999999998</v>
+        <v>163.79999999999998</v>
       </c>
       <c r="D2">
-        <v>32.780000000000008</v>
+        <v>32.760000000000005</v>
       </c>
       <c r="E2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I2" s="7">
         <f>IFERROR((F2/E2)*100,0)</f>
-        <v>65.384615384615387</v>
+        <v>65.060240963855421</v>
       </c>
       <c r="J2" s="10">
         <f>IFERROR(C2/E2,0)</f>
-        <v>2.1012820512820509</v>
+        <v>1.9734939759036143</v>
       </c>
       <c r="K2" s="10">
         <f>IFERROR(D2/E2,0)</f>
-        <v>0.42025641025641036</v>
+        <v>0.39469879518072293</v>
       </c>
       <c r="L2" s="10" t="str">
         <f>LEFT(B2,3)</f>
@@ -6178,19 +6199,19 @@
       </c>
       <c r="N2">
         <f t="shared" ref="N2:S2" si="0">C2+U2</f>
-        <v>163.89999999999998</v>
+        <v>163.79999999999998</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>32.780000000000008</v>
+        <v>32.760000000000005</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
@@ -6198,7 +6219,7 @@
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -6206,57 +6227,57 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C3">
-        <v>45</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="D3">
-        <v>9.0000000000000018</v>
+        <v>7.7600000000000016</v>
       </c>
       <c r="E3">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I3" s="7">
         <f>IFERROR((F3/E3)*100,0)</f>
-        <v>58.928571428571431</v>
+        <v>51.162790697674424</v>
       </c>
       <c r="J3" s="10">
         <f>IFERROR(C3/E3,0)</f>
-        <v>0.8035714285714286</v>
+        <v>0.9023255813953488</v>
       </c>
       <c r="K3" s="10">
         <f>IFERROR(D3/E3,0)</f>
-        <v>0.16071428571428575</v>
+        <v>0.1804651162790698</v>
       </c>
       <c r="L3" s="10" t="str">
         <f>LEFT(B3,3)</f>
-        <v>WEG</v>
+        <v>PEG</v>
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N53" si="1">C3+U3</f>
-        <v>45</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O17" si="2">D3+V3</f>
-        <v>9.0000000000000018</v>
+        <v>7.7600000000000016</v>
       </c>
       <c r="P3">
         <f t="shared" ref="P3:P17" si="3">E3+W3</f>
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q17" si="4">F3+X3</f>
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R17" si="5">G3+Y3</f>
@@ -6264,7 +6285,7 @@
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S17" si="6">H3+Z3</f>
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -6272,65 +6293,65 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4">
-        <v>35.099999999999994</v>
+        <v>38.099999999999994</v>
       </c>
       <c r="D4">
-        <v>7.0200000000000014</v>
+        <v>7.620000000000001</v>
       </c>
       <c r="E4">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I4" s="7">
         <f>IFERROR((F4/E4)*100,0)</f>
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="J4" s="10">
         <f>IFERROR(C4/E4,0)</f>
-        <v>0.83571428571428563</v>
+        <v>1.5239999999999998</v>
       </c>
       <c r="K4" s="10">
         <f>IFERROR(D4/E4,0)</f>
-        <v>0.16714285714285718</v>
+        <v>0.30480000000000002</v>
       </c>
       <c r="L4" s="10" t="str">
         <f>LEFT(B4,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N4">
         <f t="shared" si="1"/>
-        <v>35.099999999999994</v>
+        <v>38.099999999999994</v>
       </c>
       <c r="O4">
         <f t="shared" si="2"/>
-        <v>7.0200000000000014</v>
+        <v>7.620000000000001</v>
       </c>
       <c r="P4">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="Q4">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="R4">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -6338,65 +6359,65 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C5">
-        <v>29.099999999999998</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>5.8200000000000012</v>
+        <v>6.8000000000000025</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I5" s="7">
         <f>IFERROR((F5/E5)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>58.620689655172406</v>
       </c>
       <c r="J5" s="10">
         <f>IFERROR(C5/E5,0)</f>
-        <v>1.2124999999999999</v>
+        <v>0.58620689655172409</v>
       </c>
       <c r="K5" s="10">
         <f>IFERROR(D5/E5,0)</f>
-        <v>0.24250000000000005</v>
+        <v>0.11724137931034487</v>
       </c>
       <c r="L5" s="10" t="str">
         <f>LEFT(B5,3)</f>
-        <v>LEG</v>
+        <v>WEG</v>
       </c>
       <c r="N5">
         <f t="shared" si="1"/>
-        <v>29.099999999999998</v>
+        <v>34</v>
       </c>
       <c r="O5">
         <f t="shared" si="2"/>
-        <v>5.8200000000000012</v>
+        <v>6.8000000000000025</v>
       </c>
       <c r="P5">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="Q5">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="R5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -6404,57 +6425,57 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="C6">
-        <v>18.700000000000003</v>
+        <v>24.000000000000004</v>
       </c>
       <c r="D6">
-        <v>3.74</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6" s="7">
         <f>IFERROR((F6/E6)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>87.5</v>
       </c>
       <c r="J6" s="10">
         <f>IFERROR(C6/E6,0)</f>
-        <v>1.5583333333333336</v>
+        <v>3.0000000000000004</v>
       </c>
       <c r="K6" s="10">
         <f>IFERROR(D6/E6,0)</f>
-        <v>0.3116666666666667</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="L6" s="10" t="str">
         <f>LEFT(B6,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N6">
         <f t="shared" si="1"/>
-        <v>18.700000000000003</v>
+        <v>24.000000000000004</v>
       </c>
       <c r="O6">
         <f t="shared" si="2"/>
-        <v>3.74</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="P6">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R6">
         <f t="shared" si="5"/>
@@ -6462,7 +6483,7 @@
       </c>
       <c r="S6">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -6470,57 +6491,57 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="C7">
-        <v>18.700000000000003</v>
+        <v>23.200000000000003</v>
       </c>
       <c r="D7">
-        <v>3.74</v>
+        <v>4.6400000000000006</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F7">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>6</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
       </c>
       <c r="I7" s="7">
         <f>IFERROR((F7/E7)*100,0)</f>
-        <v>85.714285714285708</v>
+        <v>60</v>
       </c>
       <c r="J7" s="10">
         <f>IFERROR(C7/E7,0)</f>
-        <v>2.6714285714285717</v>
+        <v>1.5466666666666669</v>
       </c>
       <c r="K7" s="10">
         <f>IFERROR(D7/E7,0)</f>
-        <v>0.53428571428571436</v>
+        <v>0.30933333333333335</v>
       </c>
       <c r="L7" s="10" t="str">
         <f>LEFT(B7,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N7">
         <f t="shared" si="1"/>
-        <v>18.700000000000003</v>
+        <v>23.200000000000003</v>
       </c>
       <c r="O7">
         <f t="shared" si="2"/>
-        <v>3.74</v>
+        <v>4.6400000000000006</v>
       </c>
       <c r="P7">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q7">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <f t="shared" si="5"/>
@@ -6528,65 +6549,65 @@
       </c>
       <c r="S7">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>131</v>
+      <c r="B8" t="s">
+        <v>136</v>
       </c>
       <c r="C8">
-        <v>16.700000000000003</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>3.3400000000000007</v>
+        <v>3.4</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" s="7">
         <f>IFERROR((F8/E8)*100,0)</f>
-        <v>61.53846153846154</v>
+        <v>55.555555555555557</v>
       </c>
       <c r="J8" s="10">
         <f>IFERROR(C8/E8,0)</f>
-        <v>1.2846153846153849</v>
+        <v>1.8888888888888888</v>
       </c>
       <c r="K8" s="10">
         <f>IFERROR(D8/E8,0)</f>
-        <v>0.25692307692307698</v>
+        <v>0.37777777777777777</v>
       </c>
       <c r="L8" s="10" t="str">
         <f>LEFT(B8,3)</f>
-        <v>UEG</v>
+        <v>VEG</v>
       </c>
       <c r="N8">
         <f t="shared" si="1"/>
-        <v>16.700000000000003</v>
+        <v>17</v>
       </c>
       <c r="O8">
         <f t="shared" si="2"/>
-        <v>3.3400000000000007</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <f t="shared" si="5"/>
@@ -6594,7 +6615,7 @@
       </c>
       <c r="S8">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -6866,57 +6887,57 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="C13">
-        <v>12.200000000000001</v>
+        <v>9.9999999999999982</v>
       </c>
       <c r="D13">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" s="7">
         <f>IFERROR((F13/E13)*100,0)</f>
-        <v>57.142857142857139</v>
+        <v>60</v>
       </c>
       <c r="J13" s="10">
         <f>IFERROR(C13/E13,0)</f>
-        <v>1.7428571428571431</v>
+        <v>1.9999999999999996</v>
       </c>
       <c r="K13" s="10">
         <f>IFERROR(D13/E13,0)</f>
-        <v>0.34857142857142859</v>
+        <v>0.4</v>
       </c>
       <c r="L13" s="10" t="str">
         <f>LEFT(B13,3)</f>
-        <v>VEG</v>
+        <v>LEG</v>
       </c>
       <c r="N13">
         <f t="shared" si="1"/>
-        <v>12.200000000000001</v>
+        <v>9.9999999999999982</v>
       </c>
       <c r="O13">
         <f t="shared" si="2"/>
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="P13">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R13">
         <f t="shared" si="5"/>
@@ -6924,65 +6945,65 @@
       </c>
       <c r="S13">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>140</v>
+      <c r="B14" t="s">
+        <v>55</v>
       </c>
       <c r="C14">
-        <v>10.9</v>
+        <v>9.6000000000000014</v>
       </c>
       <c r="D14">
-        <v>2.1800000000000002</v>
+        <v>1.920000000000001</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I14" s="7">
         <f>IFERROR((F14/E14)*100,0)</f>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J14" s="10">
         <f>IFERROR(C14/E14,0)</f>
-        <v>2.7250000000000001</v>
+        <v>0.43636363636363645</v>
       </c>
       <c r="K14" s="10">
         <f>IFERROR(D14/E14,0)</f>
-        <v>0.54500000000000004</v>
+        <v>8.7272727272727321E-2</v>
       </c>
       <c r="L14" s="10" t="str">
         <f>LEFT(B14,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N14">
         <f t="shared" si="1"/>
-        <v>10.9</v>
+        <v>9.6000000000000014</v>
       </c>
       <c r="O14">
         <f t="shared" si="2"/>
-        <v>2.1800000000000002</v>
+        <v>1.920000000000001</v>
       </c>
       <c r="P14">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="Q14">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R14">
         <f t="shared" si="5"/>
@@ -6990,7 +7011,7 @@
       </c>
       <c r="S14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
@@ -6998,37 +7019,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C15">
-        <v>9.9999999999999982</v>
+        <v>9.2000000000000028</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1.8400000000000003</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I15" s="7">
         <f>IFERROR((F15/E15)*100,0)</f>
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="J15" s="10">
         <f>IFERROR(C15/E15,0)</f>
-        <v>1.9999999999999996</v>
+        <v>0.3680000000000001</v>
       </c>
       <c r="K15" s="10">
         <f>IFERROR(D15/E15,0)</f>
-        <v>0.4</v>
+        <v>7.3600000000000013E-2</v>
       </c>
       <c r="L15" s="10" t="str">
         <f>LEFT(B15,3)</f>
@@ -7036,27 +7057,27 @@
       </c>
       <c r="N15">
         <f t="shared" si="1"/>
-        <v>9.9999999999999982</v>
+        <v>9.2000000000000028</v>
       </c>
       <c r="O15">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1.8400000000000003</v>
       </c>
       <c r="P15">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="Q15">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R15">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -7064,25 +7085,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="C16">
-        <v>9.6000000000000014</v>
+        <v>9</v>
       </c>
       <c r="D16">
-        <v>1.920000000000001</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="E16">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I16" s="7">
         <f>IFERROR((F16/E16)*100,0)</f>
@@ -7090,31 +7111,31 @@
       </c>
       <c r="J16" s="10">
         <f>IFERROR(C16/E16,0)</f>
-        <v>0.43636363636363645</v>
+        <v>1.5</v>
       </c>
       <c r="K16" s="10">
         <f>IFERROR(D16/E16,0)</f>
-        <v>8.7272727272727321E-2</v>
+        <v>0.3</v>
       </c>
       <c r="L16" s="10" t="str">
         <f>LEFT(B16,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N16">
         <f t="shared" si="1"/>
-        <v>9.6000000000000014</v>
+        <v>9</v>
       </c>
       <c r="O16">
         <f t="shared" si="2"/>
-        <v>1.920000000000001</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="P16">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="R16">
         <f t="shared" si="5"/>
@@ -7122,27 +7143,27 @@
       </c>
       <c r="S16">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
-      <c r="B17" t="s">
-        <v>138</v>
+      <c r="B17" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="C17">
-        <v>9.5</v>
+        <v>7.0000000000000009</v>
       </c>
       <c r="D17">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -7152,35 +7173,35 @@
       </c>
       <c r="I17" s="7">
         <f>IFERROR((F17/E17)*100,0)</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J17" s="10">
         <f>IFERROR(C17/E17,0)</f>
-        <v>2.375</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="K17" s="10">
         <f>IFERROR(D17/E17,0)</f>
-        <v>0.47499999999999998</v>
+        <v>0.27999999999999997</v>
       </c>
       <c r="L17" s="10" t="str">
         <f>LEFT(B17,3)</f>
-        <v>WEG</v>
+        <v>UEG</v>
       </c>
       <c r="N17">
         <f t="shared" si="1"/>
-        <v>9.5</v>
+        <v>7.0000000000000009</v>
       </c>
       <c r="O17">
         <f t="shared" si="2"/>
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="P17">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R17">
         <f t="shared" si="5"/>
@@ -7196,57 +7217,57 @@
         <v>16</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="C18">
-        <v>9.5</v>
+        <v>6.2000000000000028</v>
       </c>
       <c r="D18">
-        <v>1.9</v>
+        <v>1.2400000000000007</v>
       </c>
       <c r="E18">
+        <v>18</v>
+      </c>
+      <c r="F18">
         <v>9</v>
       </c>
-      <c r="F18">
-        <v>5</v>
-      </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I18" s="7">
         <f>IFERROR((F18/E18)*100,0)</f>
-        <v>55.555555555555557</v>
+        <v>50</v>
       </c>
       <c r="J18" s="10">
         <f>IFERROR(C18/E18,0)</f>
-        <v>1.0555555555555556</v>
+        <v>0.34444444444444461</v>
       </c>
       <c r="K18" s="10">
         <f>IFERROR(D18/E18,0)</f>
-        <v>0.21111111111111111</v>
+        <v>6.888888888888893E-2</v>
       </c>
       <c r="L18" s="10" t="str">
         <f>LEFT(B18,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N18">
         <f t="shared" si="1"/>
-        <v>9.5</v>
+        <v>6.2000000000000028</v>
       </c>
       <c r="O18">
         <f t="shared" ref="O18:O53" si="7">D18+V18</f>
-        <v>1.9</v>
+        <v>1.2400000000000007</v>
       </c>
       <c r="P18">
         <f t="shared" ref="P18:P53" si="8">E18+W18</f>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Q18">
         <f t="shared" ref="Q18:Q53" si="9">F18+X18</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <f t="shared" ref="R18:R47" si="10">G18+Y18</f>
@@ -7254,7 +7275,7 @@
       </c>
       <c r="S18">
         <f t="shared" ref="S18:S47" si="11">H18+Z18</f>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -7262,37 +7283,37 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C19">
-        <v>9.2000000000000028</v>
+        <v>4.4999999999999929</v>
       </c>
       <c r="D19">
-        <v>1.8400000000000003</v>
+        <v>0.89999999999999902</v>
       </c>
       <c r="E19">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>12</v>
       </c>
       <c r="I19" s="7">
         <f>IFERROR((F19/E19)*100,0)</f>
-        <v>48</v>
+        <v>57.142857142857139</v>
       </c>
       <c r="J19" s="10">
         <f>IFERROR(C19/E19,0)</f>
-        <v>0.3680000000000001</v>
+        <v>0.16071428571428545</v>
       </c>
       <c r="K19" s="10">
         <f>IFERROR(D19/E19,0)</f>
-        <v>7.3600000000000013E-2</v>
+        <v>3.2142857142857105E-2</v>
       </c>
       <c r="L19" s="10" t="str">
         <f>LEFT(B19,3)</f>
@@ -7300,23 +7321,23 @@
       </c>
       <c r="N19">
         <f t="shared" si="1"/>
-        <v>9.2000000000000028</v>
+        <v>4.4999999999999929</v>
       </c>
       <c r="O19">
         <f t="shared" si="7"/>
-        <v>1.8400000000000003</v>
+        <v>0.89999999999999902</v>
       </c>
       <c r="P19">
         <f t="shared" si="8"/>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q19">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R19">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <f t="shared" si="11"/>
@@ -7327,50 +7348,50 @@
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
-        <v>86</v>
+      <c r="B20" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="C20">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="D20">
-        <v>1.7999999999999998</v>
+        <v>0.8600000000000001</v>
       </c>
       <c r="E20">
         <v>6</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" s="7">
         <f>IFERROR((F20/E20)*100,0)</f>
-        <v>50</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J20" s="10">
         <f>IFERROR(C20/E20,0)</f>
-        <v>1.5</v>
+        <v>0.71666666666666667</v>
       </c>
       <c r="K20" s="10">
         <f>IFERROR(D20/E20,0)</f>
-        <v>0.3</v>
+        <v>0.14333333333333334</v>
       </c>
       <c r="L20" s="10" t="str">
         <f>LEFT(B20,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N20">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="O20">
         <f t="shared" si="7"/>
-        <v>1.7999999999999998</v>
+        <v>0.8600000000000001</v>
       </c>
       <c r="P20">
         <f t="shared" si="8"/>
@@ -7378,7 +7399,7 @@
       </c>
       <c r="Q20">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R20">
         <f t="shared" si="10"/>
@@ -7386,21 +7407,21 @@
       </c>
       <c r="S20">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>134</v>
+      <c r="B21" t="s">
+        <v>73</v>
       </c>
       <c r="C21">
-        <v>7.0000000000000009</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="D21">
-        <v>1.4</v>
+        <v>0.37999999999999989</v>
       </c>
       <c r="E21">
         <v>5</v>
@@ -7420,23 +7441,23 @@
       </c>
       <c r="J21" s="10">
         <f>IFERROR(C21/E21,0)</f>
-        <v>1.4000000000000001</v>
+        <v>0.38000000000000006</v>
       </c>
       <c r="K21" s="10">
         <f>IFERROR(D21/E21,0)</f>
-        <v>0.27999999999999997</v>
+        <v>7.5999999999999984E-2</v>
       </c>
       <c r="L21" s="10" t="str">
         <f>LEFT(B21,3)</f>
-        <v>UEG</v>
+        <v>SEG</v>
       </c>
       <c r="N21">
         <f t="shared" si="1"/>
-        <v>7.0000000000000009</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="O21">
         <f t="shared" si="7"/>
-        <v>1.4</v>
+        <v>0.37999999999999989</v>
       </c>
       <c r="P21">
         <f t="shared" si="8"/>
@@ -7459,58 +7480,58 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>60</v>
+      <c r="B22" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="C22">
-        <v>3.599999999999993</v>
+        <v>1.5</v>
       </c>
       <c r="D22">
-        <v>0.71999999999999897</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="E22">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I22" s="7">
         <f>IFERROR((F22/E22)*100,0)</f>
-        <v>55.555555555555557</v>
+        <v>50</v>
       </c>
       <c r="J22" s="10">
         <f>IFERROR(C22/E22,0)</f>
-        <v>0.13333333333333308</v>
+        <v>0.75</v>
       </c>
       <c r="K22" s="10">
         <f>IFERROR(D22/E22,0)</f>
-        <v>2.666666666666663E-2</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="L22" s="10" t="str">
         <f>LEFT(B22,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N22">
         <f t="shared" si="1"/>
-        <v>3.599999999999993</v>
+        <v>1.5</v>
       </c>
       <c r="O22">
         <f t="shared" si="7"/>
-        <v>0.71999999999999897</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="P22">
         <f t="shared" si="8"/>
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="Q22">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="R22">
         <f t="shared" si="10"/>
@@ -7518,45 +7539,45 @@
       </c>
       <c r="S22">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>143</v>
+      <c r="B23" t="s">
+        <v>63</v>
       </c>
       <c r="C23">
-        <v>2.6000000000000005</v>
+        <v>1.1999999999999993</v>
       </c>
       <c r="D23">
-        <v>0.52000000000000013</v>
+        <v>0.23999999999999988</v>
       </c>
       <c r="E23">
+        <v>8</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
         <v>2</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
       </c>
       <c r="I23" s="7">
         <f>IFERROR((F23/E23)*100,0)</f>
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="J23" s="10">
         <f>IFERROR(C23/E23,0)</f>
-        <v>1.3000000000000003</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="K23" s="10">
         <f>IFERROR(D23/E23,0)</f>
-        <v>0.26000000000000006</v>
+        <v>2.9999999999999985E-2</v>
       </c>
       <c r="L23" s="10" t="str">
         <f>LEFT(B23,3)</f>
@@ -7564,27 +7585,27 @@
       </c>
       <c r="N23">
         <f t="shared" si="1"/>
-        <v>2.6000000000000005</v>
+        <v>1.1999999999999993</v>
       </c>
       <c r="O23">
         <f t="shared" si="7"/>
-        <v>0.52000000000000013</v>
+        <v>0.23999999999999988</v>
       </c>
       <c r="P23">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R23">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -7592,16 +7613,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>0.2</v>
+      </c>
+      <c r="E24">
         <v>2</v>
-      </c>
-      <c r="D24">
-        <v>0.4</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -7610,35 +7631,35 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="7">
         <f>IFERROR((F24/E24)*100,0)</f>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J24" s="10">
         <f>IFERROR(C24/E24,0)</f>
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K24" s="10">
         <f>IFERROR(D24/E24,0)</f>
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="10" t="str">
         <f>LEFT(B24,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N24">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24">
         <f t="shared" si="7"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P24">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24">
         <f t="shared" si="9"/>
@@ -7650,7 +7671,7 @@
       </c>
       <c r="S24">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -7658,57 +7679,57 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="C25">
-        <v>1.9000000000000004</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="D25">
-        <v>0.37999999999999989</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="7">
         <f>IFERROR((F25/E25)*100,0)</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J25" s="10">
         <f>IFERROR(C25/E25,0)</f>
-        <v>0.38000000000000006</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="K25" s="10">
         <f>IFERROR(D25/E25,0)</f>
-        <v>7.5999999999999984E-2</v>
+        <v>4.0000000000000008E-2</v>
       </c>
       <c r="L25" s="10" t="str">
         <f>LEFT(B25,3)</f>
-        <v>SEG</v>
+        <v>UEG</v>
       </c>
       <c r="N25">
         <f t="shared" si="1"/>
-        <v>1.9000000000000004</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="O25">
         <f t="shared" si="7"/>
-        <v>0.37999999999999989</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="P25">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q25">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R25">
         <f t="shared" si="10"/>
@@ -7716,99 +7737,99 @@
       </c>
       <c r="S25">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>63</v>
+      <c r="B26" s="8" t="s">
+        <v>133</v>
       </c>
       <c r="C26">
-        <v>1.1999999999999993</v>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="D26">
-        <v>0.23999999999999988</v>
+        <v>2.0000000000000254E-2</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I26" s="7">
         <f>IFERROR((F26/E26)*100,0)</f>
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J26" s="10">
         <f>IFERROR(C26/E26,0)</f>
-        <v>0.14999999999999991</v>
+        <v>8.3333333333333315E-3</v>
       </c>
       <c r="K26" s="10">
         <f>IFERROR(D26/E26,0)</f>
-        <v>2.9999999999999985E-2</v>
+        <v>1.6666666666666878E-3</v>
       </c>
       <c r="L26" s="10" t="str">
         <f>LEFT(B26,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N26">
         <f t="shared" si="1"/>
-        <v>1.1999999999999993</v>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="O26">
         <f t="shared" si="7"/>
-        <v>0.23999999999999988</v>
+        <v>2.0000000000000254E-2</v>
       </c>
       <c r="P26">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q26">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>74</v>
+      <c r="B27" t="s">
+        <v>138</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="D27">
-        <v>0.2</v>
+        <v>-0.10000000000000009</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" s="7">
         <f>IFERROR((F27/E27)*100,0)</f>
@@ -7816,31 +7837,31 @@
       </c>
       <c r="J27" s="10">
         <f>IFERROR(C27/E27,0)</f>
-        <v>0.5</v>
+        <v>-8.3333333333333329E-2</v>
       </c>
       <c r="K27" s="10">
         <f>IFERROR(D27/E27,0)</f>
-        <v>0.1</v>
+        <v>-1.666666666666668E-2</v>
       </c>
       <c r="L27" s="10" t="str">
         <f>LEFT(B27,3)</f>
-        <v>PEG</v>
+        <v>WEG</v>
       </c>
       <c r="N27">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="O27">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>-0.10000000000000009</v>
       </c>
       <c r="P27">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R27">
         <f t="shared" si="10"/>
@@ -7848,33 +7869,33 @@
       </c>
       <c r="S27">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>29</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>133</v>
+      <c r="B28" t="s">
+        <v>76</v>
       </c>
       <c r="C28">
-        <v>0.5</v>
+        <v>-0.69999999999999929</v>
       </c>
       <c r="D28">
-        <v>0.10000000000000026</v>
+        <v>-0.13999999999999901</v>
       </c>
       <c r="E28">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I28" s="7">
         <f>IFERROR((F28/E28)*100,0)</f>
@@ -7882,39 +7903,39 @@
       </c>
       <c r="J28" s="10">
         <f>IFERROR(C28/E28,0)</f>
-        <v>4.5454545454545456E-2</v>
+        <v>-3.1818181818181787E-2</v>
       </c>
       <c r="K28" s="10">
         <f>IFERROR(D28/E28,0)</f>
-        <v>9.0909090909091148E-3</v>
+        <v>-6.3636363636363187E-3</v>
       </c>
       <c r="L28" s="10" t="str">
         <f>LEFT(B28,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N28">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>-0.69999999999999929</v>
       </c>
       <c r="O28">
         <f t="shared" si="7"/>
-        <v>0.10000000000000026</v>
+        <v>-0.13999999999999901</v>
       </c>
       <c r="P28">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="Q28">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R28">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -7922,57 +7943,57 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="C29">
-        <v>0.39999999999999991</v>
+        <v>-0.70000000000000107</v>
       </c>
       <c r="D29">
-        <v>8.0000000000000016E-2</v>
+        <v>-0.14000000000000012</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I29" s="7">
         <f>IFERROR((F29/E29)*100,0)</f>
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J29" s="10">
         <f>IFERROR(C29/E29,0)</f>
-        <v>0.19999999999999996</v>
+        <v>-5.8333333333333424E-2</v>
       </c>
       <c r="K29" s="10">
         <f>IFERROR(D29/E29,0)</f>
-        <v>4.0000000000000008E-2</v>
+        <v>-1.1666666666666678E-2</v>
       </c>
       <c r="L29" s="10" t="str">
         <f>LEFT(B29,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N29">
         <f t="shared" si="1"/>
-        <v>0.39999999999999991</v>
+        <v>-0.70000000000000107</v>
       </c>
       <c r="O29">
         <f t="shared" si="7"/>
-        <v>8.0000000000000016E-2</v>
+        <v>-0.14000000000000012</v>
       </c>
       <c r="P29">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q29">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <f t="shared" si="10"/>
@@ -7980,73 +8001,73 @@
       </c>
       <c r="S29">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" t="s">
-        <v>76</v>
+      <c r="B30" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="C30">
-        <v>-0.69999999999999929</v>
+        <v>-1.6</v>
       </c>
       <c r="D30">
-        <v>-0.13999999999999901</v>
+        <v>-0.32</v>
       </c>
       <c r="E30">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
         <v>1</v>
-      </c>
-      <c r="H30">
-        <v>9</v>
       </c>
       <c r="I30" s="7">
         <f>IFERROR((F30/E30)*100,0)</f>
-        <v>54.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="J30" s="10">
         <f>IFERROR(C30/E30,0)</f>
-        <v>-3.1818181818181787E-2</v>
+        <v>-1.6</v>
       </c>
       <c r="K30" s="10">
         <f>IFERROR(D30/E30,0)</f>
-        <v>-6.3636363636363187E-3</v>
+        <v>-0.32</v>
       </c>
       <c r="L30" s="10" t="str">
         <f>LEFT(B30,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N30">
         <f t="shared" si="1"/>
-        <v>-0.69999999999999929</v>
+        <v>-1.6</v>
       </c>
       <c r="O30">
         <f t="shared" si="7"/>
-        <v>-0.13999999999999901</v>
+        <v>-0.32</v>
       </c>
       <c r="P30">
         <f t="shared" si="8"/>
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="Q30">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R30">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
@@ -8054,57 +8075,57 @@
         <v>35</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="C31">
-        <v>-0.69999999999999984</v>
+        <v>-1.9</v>
       </c>
       <c r="D31">
-        <v>-0.13999999999999999</v>
+        <v>-0.38000000000000012</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
         <v>1</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>3</v>
       </c>
       <c r="I31" s="7">
         <f>IFERROR((F31/E31)*100,0)</f>
-        <v>25</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J31" s="10">
         <f>IFERROR(C31/E31,0)</f>
-        <v>-0.17499999999999996</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="K31" s="10">
         <f>IFERROR(D31/E31,0)</f>
-        <v>-3.4999999999999996E-2</v>
+        <v>-0.12666666666666671</v>
       </c>
       <c r="L31" s="10" t="str">
         <f>LEFT(B31,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N31">
         <f t="shared" si="1"/>
-        <v>-0.69999999999999984</v>
+        <v>-1.9</v>
       </c>
       <c r="O31">
         <f t="shared" si="7"/>
-        <v>-0.13999999999999999</v>
+        <v>-0.38000000000000012</v>
       </c>
       <c r="P31">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q31">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31">
         <f t="shared" si="10"/>
@@ -8112,65 +8133,65 @@
       </c>
       <c r="S31">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>36</v>
       </c>
-      <c r="B32" t="s">
-        <v>81</v>
+      <c r="B32" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="C32">
-        <v>-0.70000000000000107</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="D32">
-        <v>-0.14000000000000012</v>
+        <v>-0.38</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I32" s="7">
         <f>IFERROR((F32/E32)*100,0)</f>
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J32" s="10">
         <f>IFERROR(C32/E32,0)</f>
-        <v>-5.8333333333333424E-2</v>
+        <v>-0.95000000000000007</v>
       </c>
       <c r="K32" s="10">
         <f>IFERROR(D32/E32,0)</f>
-        <v>-1.1666666666666678E-2</v>
+        <v>-0.19</v>
       </c>
       <c r="L32" s="10" t="str">
         <f>LEFT(B32,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N32">
         <f t="shared" si="1"/>
-        <v>-0.70000000000000107</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="O32">
         <f t="shared" si="7"/>
-        <v>-0.14000000000000012</v>
+        <v>-0.38</v>
       </c>
       <c r="P32">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q32">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R32">
         <f t="shared" si="10"/>
@@ -8178,65 +8199,65 @@
       </c>
       <c r="S32">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>37</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>82</v>
+      <c r="B33" t="s">
+        <v>69</v>
       </c>
       <c r="C33">
-        <v>-1.6</v>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="D33">
-        <v>-0.32</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" s="7">
         <f>IFERROR((F33/E33)*100,0)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J33" s="10">
         <f>IFERROR(C33/E33,0)</f>
-        <v>-1.6</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="K33" s="10">
         <f>IFERROR(D33/E33,0)</f>
-        <v>-0.32</v>
+        <v>-0.11600000000000002</v>
       </c>
       <c r="L33" s="10" t="str">
         <f>LEFT(B33,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N33">
         <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="O33">
         <f t="shared" si="7"/>
-        <v>-0.32</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="P33">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R33">
         <f t="shared" si="10"/>
@@ -8244,65 +8265,65 @@
       </c>
       <c r="S33">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>38</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>89</v>
+      <c r="B34" t="s">
+        <v>72</v>
       </c>
       <c r="C34">
-        <v>-1.9000000000000001</v>
+        <v>-3.0999999999999983</v>
       </c>
       <c r="D34">
-        <v>-0.38</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I34" s="7">
         <f>IFERROR((F34/E34)*100,0)</f>
-        <v>50</v>
+        <v>38.461538461538467</v>
       </c>
       <c r="J34" s="10">
         <f>IFERROR(C34/E34,0)</f>
-        <v>-0.95000000000000007</v>
+        <v>-0.23846153846153834</v>
       </c>
       <c r="K34" s="10">
         <f>IFERROR(D34/E34,0)</f>
-        <v>-0.19</v>
+        <v>-4.7692307692307687E-2</v>
       </c>
       <c r="L34" s="10" t="str">
         <f>LEFT(B34,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N34">
         <f t="shared" si="1"/>
-        <v>-1.9000000000000001</v>
+        <v>-3.0999999999999983</v>
       </c>
       <c r="O34">
         <f t="shared" si="7"/>
-        <v>-0.38</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="P34">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Q34">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R34">
         <f t="shared" si="10"/>
@@ -8310,7 +8331,7 @@
       </c>
       <c r="S34">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
@@ -8318,37 +8339,37 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C35">
-        <v>-2.9000000000000004</v>
+        <v>-3.0999999999999996</v>
       </c>
       <c r="D35">
-        <v>-0.58000000000000007</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>3</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>2</v>
       </c>
       <c r="I35" s="7">
         <f>IFERROR((F35/E35)*100,0)</f>
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="J35" s="10">
         <f>IFERROR(C35/E35,0)</f>
-        <v>-0.58000000000000007</v>
+        <v>-0.77499999999999991</v>
       </c>
       <c r="K35" s="10">
         <f>IFERROR(D35/E35,0)</f>
-        <v>-0.11600000000000002</v>
+        <v>-0.15499999999999997</v>
       </c>
       <c r="L35" s="10" t="str">
         <f>LEFT(B35,3)</f>
@@ -8356,19 +8377,19 @@
       </c>
       <c r="N35">
         <f t="shared" si="1"/>
-        <v>-2.9000000000000004</v>
+        <v>-3.0999999999999996</v>
       </c>
       <c r="O35">
         <f t="shared" si="7"/>
-        <v>-0.58000000000000007</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="P35">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q35">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R35">
         <f t="shared" si="10"/>
@@ -8376,7 +8397,7 @@
       </c>
       <c r="S35">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
@@ -8384,16 +8405,16 @@
         <v>30</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>144</v>
+        <v>88</v>
       </c>
       <c r="C36">
-        <v>-3</v>
+        <v>-4.7</v>
       </c>
       <c r="D36">
-        <v>-0.60000000000000009</v>
+        <v>-0.94000000000000006</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -8402,35 +8423,35 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I36" s="7">
         <f>IFERROR((F36/E36)*100,0)</f>
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J36" s="10">
         <f>IFERROR(C36/E36,0)</f>
-        <v>-1.5</v>
+        <v>-0.94000000000000006</v>
       </c>
       <c r="K36" s="10">
         <f>IFERROR(D36/E36,0)</f>
-        <v>-0.30000000000000004</v>
+        <v>-0.188</v>
       </c>
       <c r="L36" s="10" t="str">
         <f>LEFT(B36,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N36">
         <f t="shared" si="1"/>
-        <v>-3</v>
+        <v>-4.7</v>
       </c>
       <c r="O36">
         <f t="shared" si="7"/>
-        <v>-0.60000000000000009</v>
+        <v>-0.94000000000000006</v>
       </c>
       <c r="P36">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q36">
         <f t="shared" si="9"/>
@@ -8442,65 +8463,65 @@
       </c>
       <c r="S36">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>31</v>
       </c>
-      <c r="B37" t="s">
-        <v>72</v>
+      <c r="B37" s="8" t="s">
+        <v>143</v>
       </c>
       <c r="C37">
-        <v>-3.0999999999999983</v>
+        <v>-4.9999999999999991</v>
       </c>
       <c r="D37">
-        <v>-0.61999999999999988</v>
+        <v>-0.99999999999999989</v>
       </c>
       <c r="E37">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I37" s="7">
         <f>IFERROR((F37/E37)*100,0)</f>
-        <v>38.461538461538467</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J37" s="10">
         <f>IFERROR(C37/E37,0)</f>
-        <v>-0.23846153846153834</v>
+        <v>-1.6666666666666663</v>
       </c>
       <c r="K37" s="10">
         <f>IFERROR(D37/E37,0)</f>
-        <v>-4.7692307692307687E-2</v>
+        <v>-0.33333333333333331</v>
       </c>
       <c r="L37" s="10" t="str">
         <f>LEFT(B37,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N37">
         <f t="shared" si="1"/>
-        <v>-3.0999999999999983</v>
+        <v>-4.9999999999999991</v>
       </c>
       <c r="O37">
         <f t="shared" si="7"/>
-        <v>-0.61999999999999988</v>
+        <v>-0.99999999999999989</v>
       </c>
       <c r="P37">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q37">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R37">
         <f t="shared" si="10"/>
@@ -8508,24 +8529,24 @@
       </c>
       <c r="S37">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>32</v>
       </c>
-      <c r="B38" t="s">
-        <v>87</v>
+      <c r="B38" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="C38">
-        <v>-3.0999999999999996</v>
+        <v>-5.6</v>
       </c>
       <c r="D38">
-        <v>-0.61999999999999988</v>
+        <v>-1.1200000000000001</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -8534,35 +8555,35 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I38" s="7">
         <f>IFERROR((F38/E38)*100,0)</f>
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J38" s="10">
         <f>IFERROR(C38/E38,0)</f>
-        <v>-0.77499999999999991</v>
+        <v>-2.8</v>
       </c>
       <c r="K38" s="10">
         <f>IFERROR(D38/E38,0)</f>
-        <v>-0.15499999999999997</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="L38" s="10" t="str">
         <f>LEFT(B38,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N38">
         <f t="shared" si="1"/>
-        <v>-3.0999999999999996</v>
+        <v>-5.6</v>
       </c>
       <c r="O38">
         <f t="shared" si="7"/>
-        <v>-0.61999999999999988</v>
+        <v>-1.1200000000000001</v>
       </c>
       <c r="P38">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q38">
         <f t="shared" si="9"/>
@@ -8574,7 +8595,7 @@
       </c>
       <c r="S38">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
@@ -8582,19 +8603,19 @@
         <v>33</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="C39">
-        <v>-5.6</v>
+        <v>-6</v>
       </c>
       <c r="D39">
-        <v>-1.1200000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -8604,35 +8625,35 @@
       </c>
       <c r="I39" s="7">
         <f>IFERROR((F39/E39)*100,0)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J39" s="10">
         <f>IFERROR(C39/E39,0)</f>
-        <v>-2.8</v>
+        <v>-6</v>
       </c>
       <c r="K39" s="10">
         <f>IFERROR(D39/E39,0)</f>
-        <v>-0.56000000000000005</v>
+        <v>-1.2</v>
       </c>
       <c r="L39" s="10" t="str">
         <f>LEFT(B39,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N39">
         <f t="shared" si="1"/>
-        <v>-5.6</v>
+        <v>-6</v>
       </c>
       <c r="O39">
         <f t="shared" si="7"/>
-        <v>-1.1200000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="P39">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q39">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39">
         <f t="shared" si="10"/>
@@ -8647,62 +8668,62 @@
       <c r="A40">
         <v>34</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>71</v>
+      <c r="B40" t="s">
+        <v>90</v>
       </c>
       <c r="C40">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="D40">
-        <v>-1.2</v>
+        <v>-1.24</v>
       </c>
       <c r="E40">
+        <v>5</v>
+      </c>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40">
         <v>1</v>
-      </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40" s="7">
         <f>IFERROR((F40/E40)*100,0)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J40" s="10">
         <f>IFERROR(C40/E40,0)</f>
-        <v>-6</v>
+        <v>-1.24</v>
       </c>
       <c r="K40" s="10">
         <f>IFERROR(D40/E40,0)</f>
-        <v>-1.2</v>
+        <v>-0.248</v>
       </c>
       <c r="L40" s="10" t="str">
         <f>LEFT(B40,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N40">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="O40">
         <f t="shared" si="7"/>
-        <v>-1.2</v>
+        <v>-1.24</v>
       </c>
       <c r="P40">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40">
         <f t="shared" si="11"/>
@@ -8713,38 +8734,38 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>90</v>
+      <c r="B41" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="C41">
-        <v>-6.2</v>
+        <v>-7.4999999999999991</v>
       </c>
       <c r="D41">
-        <v>-1.24</v>
+        <v>-1.4999999999999998</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I41" s="7">
         <f>IFERROR((F41/E41)*100,0)</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J41" s="10">
         <f>IFERROR(C41/E41,0)</f>
-        <v>-1.24</v>
+        <v>-0.93749999999999989</v>
       </c>
       <c r="K41" s="10">
         <f>IFERROR(D41/E41,0)</f>
-        <v>-0.248</v>
+        <v>-0.18749999999999997</v>
       </c>
       <c r="L41" s="10" t="str">
         <f>LEFT(B41,3)</f>
@@ -8752,65 +8773,65 @@
       </c>
       <c r="N41">
         <f t="shared" si="1"/>
-        <v>-6.2</v>
+        <v>-7.4999999999999991</v>
       </c>
       <c r="O41">
         <f t="shared" si="7"/>
-        <v>-1.24</v>
+        <v>-1.4999999999999998</v>
       </c>
       <c r="P41">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q41">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R41">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>145</v>
+      <c r="B42" t="s">
+        <v>75</v>
       </c>
       <c r="C42">
-        <v>-7.4999999999999991</v>
+        <v>-7.5</v>
       </c>
       <c r="D42">
-        <v>-1.4999999999999998</v>
+        <v>-1.5</v>
       </c>
       <c r="E42">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I42" s="7">
         <f>IFERROR((F42/E42)*100,0)</f>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J42" s="10">
         <f>IFERROR(C42/E42,0)</f>
-        <v>-0.93749999999999989</v>
+        <v>-1.5</v>
       </c>
       <c r="K42" s="10">
         <f>IFERROR(D42/E42,0)</f>
-        <v>-0.18749999999999997</v>
+        <v>-0.3</v>
       </c>
       <c r="L42" s="10" t="str">
         <f>LEFT(B42,3)</f>
@@ -8818,19 +8839,19 @@
       </c>
       <c r="N42">
         <f t="shared" si="1"/>
-        <v>-7.4999999999999991</v>
+        <v>-7.5</v>
       </c>
       <c r="O42">
         <f t="shared" si="7"/>
-        <v>-1.4999999999999998</v>
+        <v>-1.5</v>
       </c>
       <c r="P42">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q42">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R42">
         <f t="shared" si="10"/>
@@ -8838,7 +8859,7 @@
       </c>
       <c r="S42">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
@@ -8846,7 +8867,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C43">
         <v>-7.5</v>
@@ -8858,17 +8879,17 @@
         <v>5</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" s="7">
         <f>IFERROR((F43/E43)*100,0)</f>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J43" s="10">
         <f>IFERROR(C43/E43,0)</f>
@@ -8880,7 +8901,7 @@
       </c>
       <c r="L43" s="10" t="str">
         <f>LEFT(B43,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N43">
         <f t="shared" si="1"/>
@@ -8896,7 +8917,7 @@
       </c>
       <c r="Q43">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43">
         <f t="shared" si="10"/>
@@ -8904,53 +8925,53 @@
       </c>
       <c r="S43">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
-        <v>98</v>
+      <c r="B44" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="C44">
-        <v>-7.5</v>
+        <v>-7.5000000000000009</v>
       </c>
       <c r="D44">
         <v>-1.5</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44" s="7">
         <f>IFERROR((F44/E44)*100,0)</f>
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J44" s="10">
         <f>IFERROR(C44/E44,0)</f>
-        <v>-1.5</v>
+        <v>-1.2500000000000002</v>
       </c>
       <c r="K44" s="10">
         <f>IFERROR(D44/E44,0)</f>
-        <v>-0.3</v>
+        <v>-0.25</v>
       </c>
       <c r="L44" s="10" t="str">
         <f>LEFT(B44,3)</f>
-        <v>LEG</v>
+        <v>WEG</v>
       </c>
       <c r="N44">
         <f t="shared" si="1"/>
-        <v>-7.5</v>
+        <v>-7.5000000000000009</v>
       </c>
       <c r="O44">
         <f t="shared" si="7"/>
@@ -8958,11 +8979,11 @@
       </c>
       <c r="P44">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q44">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R44">
         <f t="shared" si="10"/>
@@ -8970,65 +8991,65 @@
       </c>
       <c r="S44">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>84</v>
+      <c r="B45" t="s">
+        <v>93</v>
       </c>
       <c r="C45">
-        <v>-7.5000000000000009</v>
+        <v>-9.1</v>
       </c>
       <c r="D45">
-        <v>-1.5</v>
+        <v>-1.82</v>
       </c>
       <c r="E45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" s="7">
         <f>IFERROR((F45/E45)*100,0)</f>
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J45" s="10">
         <f>IFERROR(C45/E45,0)</f>
-        <v>-1.2500000000000002</v>
+        <v>-1.8199999999999998</v>
       </c>
       <c r="K45" s="10">
         <f>IFERROR(D45/E45,0)</f>
-        <v>-0.25</v>
+        <v>-0.36399999999999999</v>
       </c>
       <c r="L45" s="10" t="str">
         <f>LEFT(B45,3)</f>
-        <v>WEG</v>
+        <v>PEG</v>
       </c>
       <c r="N45">
         <f t="shared" si="1"/>
-        <v>-7.5000000000000009</v>
+        <v>-9.1</v>
       </c>
       <c r="O45">
         <f t="shared" si="7"/>
-        <v>-1.5</v>
+        <v>-1.82</v>
       </c>
       <c r="P45">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q45">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R45">
         <f t="shared" si="10"/>
@@ -9036,7 +9057,7 @@
       </c>
       <c r="S45">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -9044,57 +9065,57 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C46">
-        <v>-9.1</v>
+        <v>-9.4000000000000021</v>
       </c>
       <c r="D46">
-        <v>-1.82</v>
+        <v>-1.879999999999999</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I46" s="7">
         <f>IFERROR((F46/E46)*100,0)</f>
-        <v>20</v>
+        <v>47.058823529411761</v>
       </c>
       <c r="J46" s="10">
         <f>IFERROR(C46/E46,0)</f>
-        <v>-1.8199999999999998</v>
+        <v>-0.55294117647058838</v>
       </c>
       <c r="K46" s="10">
         <f>IFERROR(D46/E46,0)</f>
-        <v>-0.36399999999999999</v>
+        <v>-0.11058823529411758</v>
       </c>
       <c r="L46" s="10" t="str">
         <f>LEFT(B46,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N46">
         <f t="shared" si="1"/>
-        <v>-9.1</v>
+        <v>-9.4000000000000021</v>
       </c>
       <c r="O46">
         <f t="shared" si="7"/>
-        <v>-1.82</v>
+        <v>-1.879999999999999</v>
       </c>
       <c r="P46">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="Q46">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R46">
         <f t="shared" si="10"/>
@@ -9102,7 +9123,7 @@
       </c>
       <c r="S46">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
@@ -9110,57 +9131,57 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="C47">
-        <v>-9.4000000000000021</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="D47">
-        <v>-1.879999999999999</v>
+        <v>-1.9400000000000002</v>
       </c>
       <c r="E47">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F47">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I47" s="7">
         <f>IFERROR((F47/E47)*100,0)</f>
-        <v>47.058823529411761</v>
+        <v>37.5</v>
       </c>
       <c r="J47" s="10">
         <f>IFERROR(C47/E47,0)</f>
-        <v>-0.55294117647058838</v>
+        <v>-1.2124999999999999</v>
       </c>
       <c r="K47" s="10">
         <f>IFERROR(D47/E47,0)</f>
-        <v>-0.11058823529411758</v>
+        <v>-0.24250000000000002</v>
       </c>
       <c r="L47" s="10" t="str">
         <f>LEFT(B47,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N47">
         <f t="shared" si="1"/>
-        <v>-9.4000000000000021</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="O47">
         <f t="shared" si="7"/>
-        <v>-1.879999999999999</v>
+        <v>-1.9400000000000002</v>
       </c>
       <c r="P47">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Q47">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R47">
         <f t="shared" si="10"/>
@@ -9168,45 +9189,45 @@
       </c>
       <c r="S47">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>67</v>
+      <c r="B48" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="C48">
-        <v>-9.6999999999999993</v>
+        <v>-10.199999999999999</v>
       </c>
       <c r="D48">
-        <v>-1.9400000000000002</v>
+        <v>-2.04</v>
       </c>
       <c r="E48">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I48" s="7">
         <f>IFERROR((F48/E48)*100,0)</f>
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="J48" s="10">
         <f>IFERROR(C48/E48,0)</f>
-        <v>-1.2124999999999999</v>
+        <v>-2.5499999999999998</v>
       </c>
       <c r="K48" s="10">
         <f>IFERROR(D48/E48,0)</f>
-        <v>-0.24250000000000002</v>
+        <v>-0.51</v>
       </c>
       <c r="L48" s="10" t="str">
         <f>LEFT(B48,3)</f>
@@ -9214,19 +9235,19 @@
       </c>
       <c r="N48">
         <f t="shared" si="1"/>
-        <v>-9.6999999999999993</v>
+        <v>-10.199999999999999</v>
       </c>
       <c r="O48">
         <f t="shared" si="7"/>
-        <v>-1.9400000000000002</v>
+        <v>-2.04</v>
       </c>
       <c r="P48">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q48">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R48">
         <f t="shared" ref="R48:R53" si="12">G48+Y48</f>
@@ -9234,7 +9255,7 @@
       </c>
       <c r="S48">
         <f t="shared" ref="S48:S53" si="13">H48+Z48</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
@@ -9242,49 +9263,49 @@
         <v>48</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="C49">
-        <v>-10.199999999999999</v>
+        <v>-11.399999999999997</v>
       </c>
       <c r="D49">
-        <v>-2.04</v>
+        <v>-2.2799999999999998</v>
       </c>
       <c r="E49">
         <v>4</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I49" s="7">
         <f>IFERROR((F49/E49)*100,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J49" s="10">
         <f>IFERROR(C49/E49,0)</f>
-        <v>-2.5499999999999998</v>
+        <v>-2.8499999999999992</v>
       </c>
       <c r="K49" s="10">
         <f>IFERROR(D49/E49,0)</f>
-        <v>-0.51</v>
+        <v>-0.56999999999999995</v>
       </c>
       <c r="L49" s="10" t="str">
         <f>LEFT(B49,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N49">
         <f t="shared" si="1"/>
-        <v>-10.199999999999999</v>
+        <v>-11.399999999999997</v>
       </c>
       <c r="O49">
         <f t="shared" si="7"/>
-        <v>-2.04</v>
+        <v>-2.2799999999999998</v>
       </c>
       <c r="P49">
         <f t="shared" si="8"/>
@@ -9292,7 +9313,7 @@
       </c>
       <c r="Q49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R49">
         <f t="shared" si="12"/>
@@ -9300,7 +9321,7 @@
       </c>
       <c r="S49">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
@@ -9505,38 +9526,38 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
-        <v>92</v>
+      <c r="B53" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="C53">
-        <v>-13</v>
+        <v>-12.5</v>
       </c>
       <c r="D53">
-        <v>-2.6000000000000005</v>
+        <v>-2.4999999999999996</v>
       </c>
       <c r="E53">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I53" s="7">
         <f>IFERROR((F53/E53)*100,0)</f>
-        <v>42.857142857142854</v>
+        <v>45.454545454545453</v>
       </c>
       <c r="J53" s="10">
         <f>IFERROR(C53/E53,0)</f>
-        <v>-1.8571428571428572</v>
+        <v>-1.1363636363636365</v>
       </c>
       <c r="K53" s="10">
         <f>IFERROR(D53/E53,0)</f>
-        <v>-0.3714285714285715</v>
+        <v>-0.22727272727272724</v>
       </c>
       <c r="L53" s="10" t="str">
         <f>LEFT(B53,3)</f>
@@ -9544,19 +9565,19 @@
       </c>
       <c r="N53">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>-12.5</v>
       </c>
       <c r="O53">
         <f t="shared" si="7"/>
-        <v>-2.6000000000000005</v>
+        <v>-2.4999999999999996</v>
       </c>
       <c r="P53">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q53">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R53">
         <f t="shared" si="12"/>
@@ -9564,7 +9585,7 @@
       </c>
       <c r="S53">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
@@ -9572,57 +9593,57 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C54">
-        <v>-13.299999999999999</v>
+        <v>-13</v>
       </c>
       <c r="D54">
-        <v>-2.6599999999999997</v>
+        <v>-2.6000000000000005</v>
       </c>
       <c r="E54">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
         <v>4</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54">
-        <v>5</v>
       </c>
       <c r="I54" s="7">
         <f>IFERROR((F54/E54)*100,0)</f>
-        <v>44.444444444444443</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="J54" s="10">
         <f>IFERROR(C54/E54,0)</f>
-        <v>-1.4777777777777776</v>
+        <v>-1.8571428571428572</v>
       </c>
       <c r="K54" s="10">
         <f>IFERROR(D54/E54,0)</f>
-        <v>-0.29555555555555552</v>
+        <v>-0.3714285714285715</v>
       </c>
       <c r="L54" s="10" t="str">
         <f>LEFT(B54,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N54">
         <f t="shared" ref="N54:N56" si="14">C54+U54</f>
-        <v>-13.299999999999999</v>
+        <v>-13</v>
       </c>
       <c r="O54">
         <f t="shared" ref="O54:O56" si="15">D54+V54</f>
-        <v>-2.6599999999999997</v>
+        <v>-2.6000000000000005</v>
       </c>
       <c r="P54">
         <f t="shared" ref="P54:P56" si="16">E54+W54</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q54">
         <f t="shared" ref="Q54:Q56" si="17">F54+X54</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R54">
         <f t="shared" ref="R54:R56" si="18">G54+Y54</f>
@@ -9630,73 +9651,73 @@
       </c>
       <c r="S54">
         <f t="shared" ref="S54:S56" si="19">H54+Z54</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="8" t="s">
-        <v>127</v>
+      <c r="B55" t="s">
+        <v>99</v>
       </c>
       <c r="C55">
-        <v>-13.899999999999999</v>
+        <v>-13.299999999999999</v>
       </c>
       <c r="D55">
-        <v>-2.7800000000000002</v>
+        <v>-2.6599999999999997</v>
       </c>
       <c r="E55">
+        <v>9</v>
+      </c>
+      <c r="F55">
+        <v>4</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
         <v>5</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-      <c r="H55">
-        <v>4</v>
       </c>
       <c r="I55" s="7">
         <f>IFERROR((F55/E55)*100,0)</f>
-        <v>0</v>
+        <v>44.444444444444443</v>
       </c>
       <c r="J55" s="10">
         <f>IFERROR(C55/E55,0)</f>
-        <v>-2.78</v>
+        <v>-1.4777777777777776</v>
       </c>
       <c r="K55" s="10">
         <f>IFERROR(D55/E55,0)</f>
-        <v>-0.55600000000000005</v>
+        <v>-0.29555555555555552</v>
       </c>
       <c r="L55" s="10" t="str">
         <f>LEFT(B55,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N55">
         <f t="shared" si="14"/>
-        <v>-13.899999999999999</v>
+        <v>-13.299999999999999</v>
       </c>
       <c r="O55">
         <f t="shared" si="15"/>
-        <v>-2.7800000000000002</v>
+        <v>-2.6599999999999997</v>
       </c>
       <c r="P55">
         <f t="shared" si="16"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q55">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R55">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55">
         <f t="shared" si="19"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
@@ -9770,123 +9791,123 @@
         <v>56</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C57">
-        <v>-16.600000000000001</v>
+        <v>-15.099999999999998</v>
       </c>
       <c r="D57">
-        <v>-3.3200000000000003</v>
+        <v>-3.0200000000000005</v>
       </c>
       <c r="E57">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I57" s="7">
         <f>IFERROR((F57/E57)*100,0)</f>
-        <v>22.222222222222221</v>
+        <v>0</v>
       </c>
       <c r="J57" s="10">
         <f>IFERROR(C57/E57,0)</f>
-        <v>-1.8444444444444446</v>
+        <v>-2.5166666666666662</v>
       </c>
       <c r="K57" s="10">
         <f>IFERROR(D57/E57,0)</f>
-        <v>-0.36888888888888893</v>
+        <v>-0.50333333333333341</v>
       </c>
       <c r="L57" s="10" t="str">
         <f>LEFT(B57,3)</f>
-        <v>VEG</v>
+        <v>UEG</v>
       </c>
       <c r="N57">
         <f t="shared" ref="N57:N61" si="20">C57+U57</f>
-        <v>-16.600000000000001</v>
+        <v>-15.099999999999998</v>
       </c>
       <c r="O57">
         <f t="shared" ref="O57:O61" si="21">D57+V57</f>
-        <v>-3.3200000000000003</v>
+        <v>-3.0200000000000005</v>
       </c>
       <c r="P57">
         <f t="shared" ref="P57:P61" si="22">E57+W57</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q57">
         <f t="shared" ref="Q57:Q61" si="23">F57+X57</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R57">
         <f t="shared" ref="R57:R61" si="24">G57+Y57</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57">
         <f t="shared" ref="S57:S61" si="25">H57+Z57</f>
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
-        <v>95</v>
+      <c r="B58" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="C58">
-        <v>-17.299999999999997</v>
+        <v>-19.5</v>
       </c>
       <c r="D58">
-        <v>-3.46</v>
+        <v>-3.9</v>
       </c>
       <c r="E58">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I58" s="7">
         <f>IFERROR((F58/E58)*100,0)</f>
-        <v>36.363636363636367</v>
+        <v>0</v>
       </c>
       <c r="J58" s="10">
         <f>IFERROR(C58/E58,0)</f>
-        <v>-1.5727272727272725</v>
+        <v>-19.5</v>
       </c>
       <c r="K58" s="10">
         <f>IFERROR(D58/E58,0)</f>
-        <v>-0.31454545454545452</v>
+        <v>-3.9</v>
       </c>
       <c r="L58" s="10" t="str">
         <f>LEFT(B58,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N58">
         <f t="shared" si="20"/>
-        <v>-17.299999999999997</v>
+        <v>-19.5</v>
       </c>
       <c r="O58">
         <f t="shared" si="21"/>
-        <v>-3.46</v>
+        <v>-3.9</v>
       </c>
       <c r="P58">
         <f t="shared" si="22"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q58">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R58">
         <f t="shared" si="24"/>
@@ -9894,7 +9915,7 @@
       </c>
       <c r="S58">
         <f t="shared" si="25"/>
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
@@ -9902,57 +9923,57 @@
         <v>58</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="C59">
-        <v>-18.799999999999997</v>
+        <v>-20.100000000000001</v>
       </c>
       <c r="D59">
-        <v>-3.76</v>
+        <v>-4.0200000000000005</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I59" s="7">
         <f>IFERROR((F59/E59)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>20</v>
       </c>
       <c r="J59" s="10">
         <f>IFERROR(C59/E59,0)</f>
-        <v>-6.2666666666666657</v>
+        <v>-2.0100000000000002</v>
       </c>
       <c r="K59" s="10">
         <f>IFERROR(D59/E59,0)</f>
-        <v>-1.2533333333333332</v>
+        <v>-0.40200000000000002</v>
       </c>
       <c r="L59" s="10" t="str">
         <f>LEFT(B59,3)</f>
-        <v>PEG</v>
+        <v>VEG</v>
       </c>
       <c r="N59">
         <f t="shared" si="20"/>
-        <v>-18.799999999999997</v>
+        <v>-20.100000000000001</v>
       </c>
       <c r="O59">
         <f t="shared" si="21"/>
-        <v>-3.76</v>
+        <v>-4.0200000000000005</v>
       </c>
       <c r="P59">
         <f t="shared" si="22"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q59">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R59">
         <f t="shared" si="24"/>
@@ -9960,65 +9981,65 @@
       </c>
       <c r="S59">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>135</v>
+      <c r="B60" t="s">
+        <v>57</v>
       </c>
       <c r="C60">
-        <v>-19.5</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="D60">
-        <v>-3.9</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I60" s="7">
         <f>IFERROR((F60/E60)*100,0)</f>
-        <v>0</v>
+        <v>47.368421052631575</v>
       </c>
       <c r="J60" s="10">
         <f>IFERROR(C60/E60,0)</f>
-        <v>-19.5</v>
+        <v>-1.1947368421052633</v>
       </c>
       <c r="K60" s="10">
         <f>IFERROR(D60/E60,0)</f>
-        <v>-3.9</v>
+        <v>-0.23894736842105258</v>
       </c>
       <c r="L60" s="10" t="str">
         <f>LEFT(B60,3)</f>
-        <v>UEG</v>
+        <v>VEG</v>
       </c>
       <c r="N60">
         <f t="shared" si="20"/>
-        <v>-19.5</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="O60">
         <f t="shared" si="21"/>
-        <v>-3.9</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="P60">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Q60">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R60">
         <f t="shared" si="24"/>
@@ -10026,7 +10047,7 @@
       </c>
       <c r="S60">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
@@ -10034,57 +10055,57 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="C61">
-        <v>-22.700000000000003</v>
+        <v>-25.799999999999997</v>
       </c>
       <c r="D61">
-        <v>-4.5399999999999991</v>
+        <v>-5.16</v>
       </c>
       <c r="E61">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F61">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
       <c r="H61">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I61" s="7">
         <f>IFERROR((F61/E61)*100,0)</f>
-        <v>47.368421052631575</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J61" s="10">
         <f>IFERROR(C61/E61,0)</f>
-        <v>-1.1947368421052633</v>
+        <v>-2.15</v>
       </c>
       <c r="K61" s="10">
         <f>IFERROR(D61/E61,0)</f>
-        <v>-0.23894736842105258</v>
+        <v>-0.43</v>
       </c>
       <c r="L61" s="10" t="str">
         <f>LEFT(B61,3)</f>
-        <v>VEG</v>
+        <v>PEG</v>
       </c>
       <c r="N61">
         <f t="shared" si="20"/>
-        <v>-22.700000000000003</v>
+        <v>-25.799999999999997</v>
       </c>
       <c r="O61">
         <f t="shared" si="21"/>
-        <v>-4.5399999999999991</v>
+        <v>-5.16</v>
       </c>
       <c r="P61">
         <f t="shared" si="22"/>
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q61">
         <f t="shared" si="23"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="R61">
         <f t="shared" si="24"/>
@@ -10092,7 +10113,7 @@
       </c>
       <c r="S61">
         <f t="shared" si="25"/>
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
@@ -10103,13 +10124,13 @@
         <v>59</v>
       </c>
       <c r="C62">
-        <v>-39.599999999999994</v>
+        <v>-42.199999999999996</v>
       </c>
       <c r="D62">
-        <v>-7.919999999999999</v>
+        <v>-8.44</v>
       </c>
       <c r="E62">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F62">
         <v>8</v>
@@ -10118,19 +10139,19 @@
         <v>1</v>
       </c>
       <c r="H62">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I62" s="7">
         <f>IFERROR((F62/E62)*100,0)</f>
-        <v>44.444444444444443</v>
+        <v>42.105263157894733</v>
       </c>
       <c r="J62" s="10">
         <f>IFERROR(C62/E62,0)</f>
-        <v>-2.1999999999999997</v>
+        <v>-2.2210526315789472</v>
       </c>
       <c r="K62" s="10">
         <f>IFERROR(D62/E62,0)</f>
-        <v>-0.43999999999999995</v>
+        <v>-0.44421052631578944</v>
       </c>
       <c r="L62" s="10" t="str">
         <f>LEFT(B62,3)</f>
@@ -10138,15 +10159,15 @@
       </c>
       <c r="N62">
         <f t="shared" ref="N62" si="26">C62+U62</f>
-        <v>-39.599999999999994</v>
+        <v>-42.199999999999996</v>
       </c>
       <c r="O62">
         <f t="shared" ref="O62" si="27">D62+V62</f>
-        <v>-7.919999999999999</v>
+        <v>-8.44</v>
       </c>
       <c r="P62">
         <f t="shared" ref="P62" si="28">E62+W62</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q62">
         <f t="shared" ref="Q62" si="29">F62+X62</f>
@@ -10158,7 +10179,7 @@
       </c>
       <c r="S62">
         <f t="shared" ref="S62" si="31">H62+Z62</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
@@ -10308,8 +10329,8 @@
       <c r="B75" s="8"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L76">
-    <sortCondition descending="1" ref="C2:C76"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L75">
+    <sortCondition descending="1" ref="C2:C75"/>
   </sortState>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="dataBar" priority="24">
@@ -10438,48 +10459,48 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B62 B64:B1048576">
-    <cfRule type="containsText" dxfId="34" priority="14" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="27" priority="14" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="13" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="26" priority="13" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="12" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="25" priority="12" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="11" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="24" priority="11" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="10" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="23" priority="10" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="9" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="22" priority="9" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="8" operator="containsText" text="LEG">
+    <cfRule type="containsText" dxfId="21" priority="8" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="LEG">
+    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",B63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",B63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",B63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="15" priority="6" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",B63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="14" priority="7" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",B63)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10602,7 +10623,7 @@
     <col min="8" max="28" width="8.42578125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>104</v>
       </c>
@@ -10610,7 +10631,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" t="s">
         <v>100</v>
@@ -10634,25 +10655,25 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>145</v>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="B3">
         <f>SUM(H3:AB3)</f>
-        <v>-7.4999999999999991</v>
+        <v>-10.5</v>
       </c>
       <c r="C3">
         <f>(B3/$C$1)*100</f>
-        <v>-1.4999999999999998</v>
+        <v>-2.1</v>
       </c>
       <c r="D3">
         <f>COUNTA(H3:AB3)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <f>COUNTIF(H3:AB3, "&gt;0")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <f>COUNTIF(H3:AB3, "=0")</f>
@@ -10662,42 +10683,33 @@
         <f>COUNTIF(H3:AB3, "&lt;0")</f>
         <v>4</v>
       </c>
-      <c r="H3" s="11">
-        <v>1.2</v>
-      </c>
-      <c r="I3" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="J3" s="11">
-        <v>-0.8</v>
-      </c>
-      <c r="K3" s="11">
-        <v>-2.6</v>
-      </c>
-      <c r="L3" s="11">
-        <v>-3.8</v>
-      </c>
-      <c r="M3" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="N3" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="O3" s="11">
+      <c r="H3" s="18">
         <v>-2.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I3" s="18">
+        <v>-0.6</v>
+      </c>
+      <c r="J3" s="18">
+        <v>-10.3</v>
+      </c>
+      <c r="K3" s="18">
+        <v>-2.1</v>
+      </c>
+      <c r="L3" s="18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="B4">
         <f>SUM(H4:AB4)</f>
-        <v>-0.79999999999999893</v>
+        <v>-9.9999999999999867E-2</v>
       </c>
       <c r="C4">
         <f>(B4/$C$1)*100</f>
-        <v>-0.15999999999999978</v>
+        <v>-1.9999999999999973E-2</v>
       </c>
       <c r="D4">
         <f>COUNTA(H4:AB4)</f>
@@ -10705,7 +10717,7 @@
       </c>
       <c r="E4">
         <f>COUNTIF(H4:AB4, "&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <f>COUNTIF(H4:AB4, "=0")</f>
@@ -10713,39 +10725,39 @@
       </c>
       <c r="G4">
         <f>COUNTIF(H4:AB4, "&lt;0")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" s="18">
-        <v>0.1</v>
+        <v>-8.5</v>
       </c>
       <c r="I4" s="18">
-        <v>-0.9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="18">
-        <v>-3.5</v>
+        <v>1.2</v>
       </c>
       <c r="K4" s="18">
-        <v>-1.4</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="L4" s="18">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="B5">
         <f>SUM(H5:AB5)</f>
-        <v>2.2999999999999998</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
         <f>(B5/$C$1)*100</f>
-        <v>0.45999999999999996</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="D5">
         <f>COUNTA(H5:AB5)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <f>COUNTIF(H5:AB5, "&gt;0")</f>
@@ -10757,43 +10769,37 @@
       </c>
       <c r="G5">
         <f>COUNTIF(H5:AB5, "&lt;0")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5" s="17">
-        <v>-3.4</v>
-      </c>
-      <c r="I5" s="18">
-        <v>-2.5</v>
+        <v>-4.5</v>
+      </c>
+      <c r="I5" s="17">
+        <v>14.5</v>
       </c>
       <c r="J5" s="18">
-        <v>13.1</v>
-      </c>
-      <c r="K5" s="18">
-        <v>-0.8</v>
-      </c>
-      <c r="L5" s="18">
-        <v>-4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B6">
         <f>SUM(H6:AB6)</f>
-        <v>13.7</v>
+        <v>-10</v>
       </c>
       <c r="C6">
         <f>(B6/$C$1)*100</f>
-        <v>2.7399999999999998</v>
+        <v>-2</v>
       </c>
       <c r="D6">
         <f>COUNTA(H6:AB6)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <f>COUNTIF(H6:AB6, "&gt;0")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <f>COUNTIF(H6:AB6, "=0")</f>
@@ -10801,29 +10807,26 @@
       </c>
       <c r="G6">
         <f>COUNTIF(H6:AB6, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="17">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="I6" s="17">
-        <v>8.1</v>
-      </c>
-      <c r="J6" s="18">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+        <v>-11.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>56</v>
       </c>
       <c r="B7">
         <f>SUM(H7:AB7)</f>
-        <v>4.3</v>
+        <v>-11</v>
       </c>
       <c r="C7">
         <f>(B7/$C$1)*100</f>
-        <v>0.86</v>
+        <v>-2.1999999999999997</v>
       </c>
       <c r="D7">
         <f>COUNTA(H7:AB7)</f>
@@ -10831,7 +10834,7 @@
       </c>
       <c r="E7">
         <f>COUNTIF(H7:AB7, "&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <f>COUNTIF(H7:AB7, "=0")</f>
@@ -10839,26 +10842,26 @@
       </c>
       <c r="G7">
         <f>COUNTIF(H7:AB7, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="18">
-        <v>3</v>
+        <v>-13</v>
       </c>
       <c r="I7" s="18">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>133</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>136</v>
       </c>
       <c r="B8">
         <f>SUM(H8:AB8)</f>
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="C8">
         <f>(B8/$C$1)*100</f>
-        <v>0.3</v>
+        <v>0.96</v>
       </c>
       <c r="D8">
         <f>COUNTA(H8:AB8)</f>
@@ -10877,23 +10880,23 @@
         <v>1</v>
       </c>
       <c r="H8" s="17">
-        <v>-12.2</v>
+        <v>-2.7</v>
       </c>
       <c r="I8" s="18">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>140</v>
       </c>
       <c r="B9">
         <f>SUM(H9:AB9)</f>
-        <v>5</v>
+        <v>-6.6000000000000005</v>
       </c>
       <c r="C9">
         <f>(B9/$C$1)*100</f>
-        <v>1</v>
+        <v>-1.32</v>
       </c>
       <c r="D9">
         <f>COUNTA(H9:AB9)</f>
@@ -10901,7 +10904,7 @@
       </c>
       <c r="E9">
         <f>COUNTIF(H9:AB9, "&gt;0")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <f>COUNTIF(H9:AB9, "=0")</f>
@@ -10909,26 +10912,26 @@
       </c>
       <c r="G9">
         <f>COUNTIF(H9:AB9, "&lt;0")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="17">
-        <v>3.5</v>
-      </c>
-      <c r="I9" s="18">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>-0.4</v>
+      </c>
+      <c r="I9" s="17">
+        <v>-6.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>94</v>
       </c>
       <c r="B10">
         <f>SUM(H10:AB10)</f>
-        <v>0.40000000000000036</v>
+        <v>-22</v>
       </c>
       <c r="C10">
         <f>(B10/$C$1)*100</f>
-        <v>8.0000000000000071E-2</v>
+        <v>-4.3999999999999995</v>
       </c>
       <c r="D10">
         <f>COUNTA(H10:AB10)</f>
@@ -10936,7 +10939,7 @@
       </c>
       <c r="E10">
         <f>COUNTIF(H10:AB10, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <f>COUNTIF(H10:AB10, "=0")</f>
@@ -10944,27 +10947,27 @@
       </c>
       <c r="G10">
         <f>COUNTIF(H10:AB10, "&lt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="17">
-        <v>7.4</v>
+        <v>-2.4</v>
       </c>
       <c r="I10" s="17">
-        <v>-7</v>
+        <v>-19.600000000000001</v>
       </c>
       <c r="J10" s="15"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B11">
         <f>SUM(H11:AB11)</f>
-        <v>7.1</v>
+        <v>-3.5</v>
       </c>
       <c r="C11">
         <f>(B11/$C$1)*100</f>
-        <v>1.42</v>
+        <v>-0.70000000000000007</v>
       </c>
       <c r="D11">
         <f>COUNTA(H11:AB11)</f>
@@ -10972,7 +10975,7 @@
       </c>
       <c r="E11">
         <f>COUNTIF(H11:AB11, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <f>COUNTIF(H11:AB11, "=0")</f>
@@ -10980,23 +10983,23 @@
       </c>
       <c r="G11">
         <f>COUNTIF(H11:AB11, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="18">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>129</v>
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>127</v>
       </c>
       <c r="B12">
         <f>SUM(H12:AB12)</f>
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="C12">
         <f>(B12/$C$1)*100</f>
-        <v>-0.16</v>
+        <v>-0.24</v>
       </c>
       <c r="D12">
         <f>COUNTA(H12:AB12)</f>
@@ -11015,24 +11018,24 @@
         <v>1</v>
       </c>
       <c r="H12" s="17">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
       <c r="L12" s="15"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>136</v>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>133</v>
       </c>
       <c r="B13">
         <f>SUM(H13:AB13)</f>
-        <v>4.9000000000000004</v>
+        <v>-0.4</v>
       </c>
       <c r="C13">
         <f>(B13/$C$1)*100</f>
-        <v>0.98000000000000009</v>
+        <v>-0.08</v>
       </c>
       <c r="D13">
         <f>COUNTA(H13:AB13)</f>
@@ -11040,7 +11043,7 @@
       </c>
       <c r="E13">
         <f>COUNTIF(H13:AB13, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <f>COUNTIF(H13:AB13, "=0")</f>
@@ -11048,23 +11051,23 @@
       </c>
       <c r="G13">
         <f>COUNTIF(H13:AB13, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="18">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="B14">
         <f>SUM(H14:AB14)</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="C14">
         <f>(B14/$C$1)*100</f>
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="D14">
         <f>COUNTA(H14:AB14)</f>
@@ -11076,27 +11079,27 @@
       </c>
       <c r="F14">
         <f>COUNTIF(H14:AB14, "=0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <f>COUNTIF(H14:AB14, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>88</v>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>146</v>
       </c>
       <c r="B15">
         <f>SUM(H15:AB15)</f>
-        <v>-1.1000000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="C15">
         <f>(B15/$C$1)*100</f>
-        <v>-0.22</v>
+        <v>-0.1</v>
       </c>
       <c r="D15">
         <f>COUNTA(H15:AB15)</f>
@@ -11115,20 +11118,20 @@
         <v>1</v>
       </c>
       <c r="H15" s="18">
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
         <v>95</v>
       </c>
       <c r="B16">
         <f>SUM(H16:AB16)</f>
-        <v>-7.6</v>
+        <v>-8.5</v>
       </c>
       <c r="C16">
         <f>(B16/$C$1)*100</f>
-        <v>-1.52</v>
+        <v>-1.7000000000000002</v>
       </c>
       <c r="D16">
         <f>COUNTA(H16:AB16)</f>
@@ -11147,20 +11150,20 @@
         <v>1</v>
       </c>
       <c r="H16" s="18">
-        <v>-7.6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>-8.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>59</v>
       </c>
       <c r="B17">
         <f>SUM(H17:AB17)</f>
-        <v>3.1</v>
+        <v>-2.6</v>
       </c>
       <c r="C17">
         <f>(B17/$C$1)*100</f>
-        <v>0.62</v>
+        <v>-0.52</v>
       </c>
       <c r="D17">
         <f>COUNTA(H17:AB17)</f>
@@ -11168,7 +11171,7 @@
       </c>
       <c r="E17">
         <f>COUNTIF(H17:AB17, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <f>COUNTIF(H17:AB17, "=0")</f>
@@ -11176,23 +11179,23 @@
       </c>
       <c r="G17">
         <f>COUNTIF(H17:AB17, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="17">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>141</v>
       </c>
       <c r="B18">
         <f>SUM(H18:AB18)</f>
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="C18">
         <f>(B18/$C$1)*100</f>
-        <v>0.26</v>
+        <v>1.48</v>
       </c>
       <c r="D18">
         <f>COUNTA(H18:AB18)</f>
@@ -11211,21 +11214,20 @@
         <v>0</v>
       </c>
       <c r="H18" s="17">
-        <v>1.3</v>
-      </c>
-      <c r="I18" s="15"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B19">
         <f>SUM(H19:AB19)</f>
-        <v>6.9</v>
+        <v>-7.6</v>
       </c>
       <c r="C19">
         <f>(B19/$C$1)*100</f>
-        <v>1.3800000000000001</v>
+        <v>-1.52</v>
       </c>
       <c r="D19">
         <f>COUNTA(H19:AB19)</f>
@@ -11233,7 +11235,7 @@
       </c>
       <c r="E19">
         <f>COUNTIF(H19:AB19, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <f>COUNTIF(H19:AB19, "=0")</f>
@@ -11241,23 +11243,23 @@
       </c>
       <c r="G19">
         <f>COUNTIF(H19:AB19, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>-7.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B20">
         <f>SUM(H20:AB20)</f>
-        <v>-6.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C20">
         <f>(B20/$C$1)*100</f>
-        <v>-1.3</v>
+        <v>0.22</v>
       </c>
       <c r="D20">
         <f>COUNTA(H20:AB20)</f>
@@ -11265,7 +11267,7 @@
       </c>
       <c r="E20">
         <f>COUNTIF(H20:AB20, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
         <f>COUNTIF(H20:AB20, "=0")</f>
@@ -11273,23 +11275,23 @@
       </c>
       <c r="G20">
         <f>COUNTIF(H20:AB20, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="18">
-        <v>-6.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>144</v>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>64</v>
       </c>
       <c r="B21">
         <f>SUM(H21:AB21)</f>
-        <v>-3.5</v>
+        <v>3.7</v>
       </c>
       <c r="C21">
         <f>(B21/$C$1)*100</f>
-        <v>-0.70000000000000007</v>
+        <v>0.74</v>
       </c>
       <c r="D21">
         <f>COUNTA(H21:AB21)</f>
@@ -11297,7 +11299,7 @@
       </c>
       <c r="E21">
         <f>COUNTIF(H21:AB21, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
         <f>COUNTIF(H21:AB21, "=0")</f>
@@ -11305,23 +11307,23 @@
       </c>
       <c r="G21">
         <f>COUNTIF(H21:AB21, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>64</v>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="B22">
         <f>SUM(H22:AB22)</f>
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="C22">
         <f>(B22/$C$1)*100</f>
-        <v>0.57999999999999996</v>
+        <v>0.18</v>
       </c>
       <c r="D22">
         <f>COUNTA(H22:AB22)</f>
@@ -11340,20 +11342,20 @@
         <v>0</v>
       </c>
       <c r="H22" s="18">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B23">
         <f>SUM(H23:AB23)</f>
-        <v>-2.9</v>
+        <v>9</v>
       </c>
       <c r="C23">
         <f>(B23/$C$1)*100</f>
-        <v>-0.57999999999999996</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="D23">
         <f>COUNTA(H23:AB23)</f>
@@ -11361,7 +11363,7 @@
       </c>
       <c r="E23">
         <f>COUNTIF(H23:AB23, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <f>COUNTIF(H23:AB23, "=0")</f>
@@ -11369,23 +11371,23 @@
       </c>
       <c r="G23">
         <f>COUNTIF(H23:AB23, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="18">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>80</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="B24">
         <f>SUM(H24:AB24)</f>
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="C24">
         <f>(B24/$C$1)*100</f>
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="D24">
         <f>COUNTA(H24:AB24)</f>
@@ -11393,35 +11395,35 @@
       </c>
       <c r="E24">
         <f>COUNTIF(H24:AB24, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
         <f>COUNTIF(H24:AB24, "=0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
         <f>COUNTIF(H24:AB24, "&lt;0")</f>
         <v>0</v>
       </c>
       <c r="H24" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B25">
         <f>SUM(H25:AB25)</f>
-        <v>-4.7</v>
+        <v>0</v>
       </c>
       <c r="C25">
         <f>(B25/$C$1)*100</f>
-        <v>-0.94000000000000006</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <f>COUNTA(H25:AB25)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <f>COUNTIF(H25:AB25, "&gt;0")</f>
@@ -11433,31 +11435,28 @@
       </c>
       <c r="G25">
         <f>COUNTIF(H25:AB25, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H25" s="18">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>68</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="B26">
         <f>SUM(H26:AB26)</f>
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="C26">
         <f>(B26/$C$1)*100</f>
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <f>COUNTA(H26:AB26)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <f>COUNTIF(H26:AB26, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <f>COUNTIF(H26:AB26, "=0")</f>
@@ -11467,25 +11466,22 @@
         <f>COUNTIF(H26:AB26, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H26" s="18">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>99</v>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="B27">
         <f>SUM(H27:AB27)</f>
-        <v>-4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <f>(B27/$C$1)*100</f>
-        <v>-0.88</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <f>COUNTA(H27:AB27)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <f>COUNTIF(H27:AB27, "&gt;0")</f>
@@ -11497,31 +11493,29 @@
       </c>
       <c r="G27">
         <f>COUNTIF(H27:AB27, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H27" s="18">
-        <v>-4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H27" s="15"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B28">
         <f>SUM(H28:AB28)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C28">
         <f>(B28/$C$1)*100</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <f>COUNTA(H28:AB28)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <f>COUNTIF(H28:AB28, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <f>COUNTIF(H28:AB28, "=0")</f>
@@ -11531,13 +11525,10 @@
         <f>COUNTIF(H28:AB28, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H28" s="18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>84</v>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="B29">
         <f>SUM(H29:AB29)</f>
@@ -11564,9 +11555,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>58</v>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="B30">
         <f>SUM(H30:AB30)</f>
@@ -11593,9 +11584,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="B31">
         <f>SUM(H31:AB31)</f>
@@ -11622,9 +11613,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B32">
         <f>SUM(H32:AB32)</f>
@@ -11650,12 +11641,10 @@
         <f>COUNTIF(H32:AB32, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>87</v>
+      <c r="A33" t="s">
+        <v>67</v>
       </c>
       <c r="B33">
         <f>SUM(H33:AB33)</f>
@@ -11681,10 +11670,12 @@
         <f>COUNTIF(H33:AB33, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>134</v>
+      <c r="A34" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="B34">
         <f>SUM(H34:AB34)</f>
@@ -11710,11 +11701,10 @@
         <f>COUNTIF(H34:AB34, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H34" s="15"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
-        <v>137</v>
+      <c r="A35" t="s">
+        <v>72</v>
       </c>
       <c r="B35">
         <f>SUM(H35:AB35)</f>
@@ -11740,10 +11730,11 @@
         <f>COUNTIF(H35:AB35, "&lt;0")</f>
         <v>0</v>
       </c>
+      <c r="H35" s="15"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="B36">
         <f>SUM(H36:AB36)</f>
@@ -11772,7 +11763,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="B37">
         <f>SUM(H37:AB37)</f>
@@ -11803,7 +11794,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B38">
         <f>SUM(H38:AB38)</f>
@@ -11835,8 +11826,8 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>72</v>
+      <c r="A39" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="B39">
         <f>SUM(H39:AB39)</f>
@@ -11866,8 +11857,8 @@
       <c r="I39" s="15"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>85</v>
+      <c r="A40" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="B40">
         <f>SUM(H40:AB40)</f>
@@ -11894,10 +11885,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="B41">
         <f>SUM(H41:AB41)</f>
@@ -11926,8 +11918,8 @@
       <c r="H41" s="15"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
-        <v>69</v>
+      <c r="A42" t="s">
+        <v>76</v>
       </c>
       <c r="B42">
         <f>SUM(H42:AB42)</f>
@@ -11957,7 +11949,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B43">
         <f>SUM(H43:AB43)</f>
@@ -11987,7 +11979,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="B44">
         <f>SUM(H44:AB44)</f>
@@ -12020,8 +12012,8 @@
       <c r="L44" s="15"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
-        <v>91</v>
+      <c r="A45" t="s">
+        <v>75</v>
       </c>
       <c r="B45">
         <f>SUM(H45:AB45)</f>
@@ -12048,10 +12040,14 @@
         <v>0</v>
       </c>
       <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>76</v>
+      <c r="A46" t="s">
+        <v>92</v>
       </c>
       <c r="B46">
         <f>SUM(H46:AB46)</f>
@@ -12079,8 +12075,8 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>63</v>
+      <c r="A47" t="s">
+        <v>90</v>
       </c>
       <c r="B47">
         <f>SUM(H47:AB47)</f>
@@ -12108,8 +12104,8 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
-        <v>75</v>
+      <c r="A48" t="s">
+        <v>93</v>
       </c>
       <c r="B48">
         <f>SUM(H48:AB48)</f>
@@ -12138,8 +12134,8 @@
       <c r="H48" s="15"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>92</v>
+      <c r="A49" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="B49">
         <f>SUM(H49:AB49)</f>
@@ -12168,8 +12164,8 @@
       <c r="H49" s="15"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
-        <v>90</v>
+      <c r="A50" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B50">
         <f>SUM(H50:AB50)</f>
@@ -12199,8 +12195,8 @@
       <c r="I50" s="15"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>93</v>
+      <c r="A51" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="B51">
         <f>SUM(H51:AB51)</f>
@@ -12229,8 +12225,8 @@
       <c r="H51" s="15"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>61</v>
+      <c r="A52" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="B52">
         <f>SUM(H52:AB52)</f>
@@ -12259,7 +12255,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B53">
         <f>SUM(H53:AB53)</f>
@@ -12289,7 +12285,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B54">
         <f>SUM(H54:AB54)</f>
@@ -12318,7 +12314,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B55">
         <f>SUM(H55:AB55)</f>
@@ -12348,7 +12344,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B56">
         <f>SUM(H56:AB56)</f>
@@ -12377,8 +12373,8 @@
       <c r="H56" s="15"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
-        <v>55</v>
+      <c r="A57" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="B57">
         <f>SUM(H57:AB57)</f>
@@ -12408,8 +12404,8 @@
       <c r="I57" s="15"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
-        <v>70</v>
+      <c r="A58" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="B58">
         <f>SUM(H58:AB58)</f>
@@ -12439,8 +12435,8 @@
       <c r="I58" s="15"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>83</v>
+      <c r="A59" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="B59">
         <f>SUM(H59:AB59)</f>
@@ -12470,8 +12466,8 @@
       <c r="I59" s="15"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
-        <v>71</v>
+      <c r="A60" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="B60">
         <f>SUM(H60:AB60)</f>
@@ -12501,7 +12497,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B61">
         <f>SUM(H61:AB61)</f>
@@ -12531,7 +12527,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B62">
         <f>SUM(H62:AB62)</f>
@@ -12561,7 +12557,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B63">
         <f>SUM(H63:AB63)</f>
@@ -12623,27 +12619,27 @@
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="8"/>
       <c r="B65">
-        <f t="shared" ref="B63:B66" si="0">SUM(H65:AB65)</f>
+        <f t="shared" ref="B65:B66" si="0">SUM(H65:AB65)</f>
         <v>0</v>
       </c>
       <c r="C65">
-        <f t="shared" ref="C63:C66" si="1">(B65/$C$1)*100</f>
+        <f t="shared" ref="C65:C66" si="1">(B65/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D65">
-        <f t="shared" ref="D63:D66" si="2">COUNTA(H65:AB65)</f>
+        <f t="shared" ref="D65:D66" si="2">COUNTA(H65:AB65)</f>
         <v>0</v>
       </c>
       <c r="E65">
-        <f t="shared" ref="E63:E66" si="3">COUNTIF(H65:AB65, "&gt;0")</f>
+        <f t="shared" ref="E65:E66" si="3">COUNTIF(H65:AB65, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F65">
-        <f t="shared" ref="F63:F66" si="4">COUNTIF(H65:AB65, "=0")</f>
+        <f t="shared" ref="F65:F66" si="4">COUNTIF(H65:AB65, "=0")</f>
         <v>0</v>
       </c>
       <c r="G65">
-        <f t="shared" ref="G63:G66" si="5">COUNTIF(H65:AB65, "&lt;0")</f>
+        <f t="shared" ref="G65:G66" si="5">COUNTIF(H65:AB65, "&lt;0")</f>
         <v>0</v>
       </c>
     </row>
@@ -12930,29 +12926,29 @@
       <c r="H75" s="15"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U64">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AA64">
     <sortCondition descending="1" ref="D3:D64"/>
   </sortState>
   <conditionalFormatting sqref="A3:A57">
-    <cfRule type="containsText" dxfId="27" priority="8" operator="containsText" text="LEG">
+    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="12" priority="9" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="10" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="11" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="9" priority="12" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="13" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="14" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="7" priority="14" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",A3)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACA1D5E-450B-4D2D-AF43-7FADA2168185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA44755-96E4-4C25-BE18-072E48980F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="149">
   <si>
     <t>AQUA</t>
   </si>
@@ -482,6 +482,12 @@
   </si>
   <si>
     <t>UEG4_CANADIAN</t>
+  </si>
+  <si>
+    <t>WEG8_MOUSE</t>
+  </si>
+  <si>
+    <t>WEG7_PARADOX2</t>
   </si>
 </sst>
 </file>
@@ -625,7 +631,105 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="42">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1027,10 +1131,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$M$2</c:f>
+              <c:f>Динамика!$B$2:$N$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1066,16 +1170,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$3:$M$3</c:f>
+              <c:f>Динамика!$B$3:$N$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>-20.100000000000001</c:v>
                 </c:pt>
@@ -1111,6 +1218,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>-12.000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1217,10 +1327,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$M$2</c:f>
+              <c:f>Динамика!$B$2:$N$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1256,16 +1366,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$4:$M$4</c:f>
+              <c:f>Динамика!$B$4:$N$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>19.7</c:v>
                 </c:pt>
@@ -1301,6 +1414,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>74.499999999999972</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>43.700000000000024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1407,10 +1523,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$M$2</c:f>
+              <c:f>Динамика!$B$2:$N$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1446,16 +1562,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$5:$M$5</c:f>
+              <c:f>Динамика!$B$5:$N$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>1.9</c:v>
                 </c:pt>
@@ -1490,6 +1609,9 @@
                   <c:v>14.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>14.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>14.799999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -1597,10 +1719,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$M$2</c:f>
+              <c:f>Динамика!$B$2:$N$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1636,16 +1758,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$6:$M$6</c:f>
+              <c:f>Динамика!$B$6:$N$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>-21</c:v>
                 </c:pt>
@@ -1681,6 +1806,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>-28.299999999999994</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-65.099999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1787,10 +1915,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$M$2</c:f>
+              <c:f>Динамика!$B$2:$N$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1826,16 +1954,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$7:$M$7</c:f>
+              <c:f>Динамика!$B$7:$N$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>-18.100000000000001</c:v>
                 </c:pt>
@@ -1871,6 +2002,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>-25.800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-32.600000000000009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1977,10 +2111,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$M$2</c:f>
+              <c:f>Динамика!$B$2:$N$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -2016,16 +2150,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$8:$M$8</c:f>
+              <c:f>Динамика!$B$8:$N$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>44.5</c:v>
                 </c:pt>
@@ -2061,6 +2198,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2170,10 +2310,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$M$2</c:f>
+              <c:f>Динамика!$B$2:$N$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -2209,16 +2349,19 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$9:$M$9</c:f>
+              <c:f>Динамика!$B$9:$N$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>6.8999999999999915</c:v>
                 </c:pt>
@@ -2254,6 +2397,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>65.199999999999932</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.8000000000000185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3012,43 +3158,43 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46302.975628472224" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="75" xr:uid="{3D6F248A-0360-4477-B017-E96CAA4B0EB4}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46304.937350115739" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="76" xr:uid="{3D6F248A-0360-4477-B017-E96CAA4B0EB4}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:L1048576" sheet="Результаты"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="Номер" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="62"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="64"/>
     </cacheField>
     <cacheField name="Стратегия" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Абс" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-42.900000000000006" maxValue="163.79999999999998"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-42.900000000000006" maxValue="153.19999999999999"/>
     </cacheField>
     <cacheField name="Отн" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-8.58" maxValue="32.760000000000005"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-8.58" maxValue="30.640000000000004"/>
     </cacheField>
     <cacheField name="Кол-во" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="83"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="88"/>
     </cacheField>
     <cacheField name="Прибыль" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="54"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="57"/>
     </cacheField>
     <cacheField name="Нейтрал" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
     </cacheField>
     <cacheField name="Убыток" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="29"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="31"/>
     </cacheField>
     <cacheField name="ПроцПД" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="87.5"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="100"/>
     </cacheField>
     <cacheField name="САП" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-19.5" maxValue="3.0000000000000004"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-19.5" maxValue="3.5111111111111111"/>
     </cacheField>
     <cacheField name="СОП" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-3.9" maxValue="0.60000000000000009"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-3.9" maxValue="0.7022222222222223"/>
     </cacheField>
     <cacheField name="Тип" numFmtId="0">
       <sharedItems containsBlank="1" count="7">
@@ -3056,8 +3202,8 @@
         <s v="LEG"/>
         <s v="WEG"/>
         <s v="UEG"/>
+        <s v="SEG"/>
         <s v="VEG"/>
-        <s v="SEG"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -3071,107 +3217,79 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="75">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="76">
   <r>
     <n v="1"/>
     <s v="PEG17_PHOENIX"/>
-    <n v="163.79999999999998"/>
-    <n v="32.760000000000005"/>
-    <n v="83"/>
-    <n v="54"/>
+    <n v="153.19999999999999"/>
+    <n v="30.640000000000004"/>
+    <n v="88"/>
+    <n v="57"/>
     <n v="0"/>
-    <n v="29"/>
-    <n v="65.060240963855421"/>
-    <n v="1.9734939759036143"/>
-    <n v="0.39469879518072293"/>
+    <n v="31"/>
+    <n v="64.772727272727266"/>
+    <n v="1.7409090909090907"/>
+    <n v="0.3481818181818182"/>
     <x v="0"/>
   </r>
   <r>
     <n v="2"/>
+    <s v="LEG2_FENNEC"/>
+    <n v="42.199999999999996"/>
+    <n v="8.4400000000000013"/>
+    <n v="26"/>
+    <n v="18"/>
+    <n v="0"/>
+    <n v="8"/>
+    <n v="69.230769230769226"/>
+    <n v="1.6230769230769229"/>
+    <n v="0.32461538461538464"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <s v="WEG3_BATYA"/>
+    <n v="35.9"/>
+    <n v="7.1800000000000024"/>
+    <n v="59"/>
+    <n v="35"/>
+    <n v="1"/>
+    <n v="23"/>
+    <n v="59.322033898305079"/>
+    <n v="0.6084745762711864"/>
+    <n v="0.12169491525423733"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <s v="LEG1_LAKSAe"/>
+    <n v="31.6"/>
+    <n v="6.32"/>
+    <n v="9"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="88.888888888888886"/>
+    <n v="3.5111111111111111"/>
+    <n v="0.7022222222222223"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="5"/>
     <s v="PEG11_KUSURUKEN"/>
-    <n v="38.799999999999997"/>
-    <n v="7.7600000000000016"/>
-    <n v="43"/>
+    <n v="23.4"/>
+    <n v="4.6800000000000015"/>
+    <n v="44"/>
     <n v="22"/>
     <n v="1"/>
-    <n v="20"/>
-    <n v="51.162790697674424"/>
-    <n v="0.9023255813953488"/>
-    <n v="0.1804651162790698"/>
+    <n v="21"/>
+    <n v="50"/>
+    <n v="0.53181818181818175"/>
+    <n v="0.1063636363636364"/>
     <x v="0"/>
   </r>
   <r>
-    <n v="3"/>
-    <s v="LEG2_FENNEC"/>
-    <n v="38.099999999999994"/>
-    <n v="7.620000000000001"/>
-    <n v="25"/>
-    <n v="17"/>
-    <n v="0"/>
-    <n v="8"/>
-    <n v="68"/>
-    <n v="1.5239999999999998"/>
-    <n v="0.30480000000000002"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <s v="WEG3_BATYA"/>
-    <n v="34"/>
-    <n v="6.8000000000000025"/>
-    <n v="58"/>
-    <n v="34"/>
-    <n v="1"/>
-    <n v="23"/>
-    <n v="58.620689655172406"/>
-    <n v="0.58620689655172409"/>
-    <n v="0.11724137931034487"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <s v="LEG1_LAKSAe"/>
-    <n v="24.000000000000004"/>
-    <n v="4.8000000000000007"/>
-    <n v="8"/>
-    <n v="7"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="87.5"/>
-    <n v="3.0000000000000004"/>
-    <n v="0.60000000000000009"/>
-    <x v="1"/>
-  </r>
-  <r>
     <n v="6"/>
-    <s v="UEG9_GRAVY2"/>
-    <n v="23.200000000000003"/>
-    <n v="4.6400000000000006"/>
-    <n v="15"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="6"/>
-    <n v="60"/>
-    <n v="1.5466666666666669"/>
-    <n v="0.30933333333333335"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <s v="VEG1_EARTH"/>
-    <n v="17"/>
-    <n v="3.4"/>
-    <n v="9"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="55.555555555555557"/>
-    <n v="1.8888888888888888"/>
-    <n v="0.37777777777777777"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="8"/>
     <s v="WEG4_PUPPY"/>
     <n v="16"/>
     <n v="3.1999999999999993"/>
@@ -3185,7 +3303,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="9"/>
+    <n v="7"/>
     <s v="UEG6_ADVENTURE"/>
     <n v="16"/>
     <n v="3.1999999999999993"/>
@@ -3199,7 +3317,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="11"/>
+    <n v="8"/>
     <s v="PEG14_RENEGADE"/>
     <n v="15.7"/>
     <n v="3.1400000000000006"/>
@@ -3213,7 +3331,21 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="13"/>
+    <n v="9"/>
+    <s v="UEG9_GRAVY2"/>
+    <n v="13.800000000000004"/>
+    <n v="2.7600000000000007"/>
+    <n v="17"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="8"/>
+    <n v="52.941176470588239"/>
+    <n v="0.81176470588235317"/>
+    <n v="0.16235294117647062"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="11"/>
     <s v="SEG1_LITE"/>
     <n v="12.899999999999997"/>
     <n v="2.5799999999999996"/>
@@ -3224,6 +3356,20 @@
     <n v="70"/>
     <n v="1.2899999999999996"/>
     <n v="0.25799999999999995"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <s v="VEG1_EARTH"/>
+    <n v="10.199999999999999"/>
+    <n v="2.04"/>
+    <n v="11"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="6"/>
+    <n v="45.454545454545453"/>
+    <n v="0.92727272727272725"/>
+    <n v="0.18545454545454546"/>
     <x v="5"/>
   </r>
   <r>
@@ -3270,6 +3416,20 @@
   </r>
   <r>
     <n v="15"/>
+    <s v="PEG30_ETC2"/>
+    <n v="9.1999999999999993"/>
+    <n v="1.8400000000000003"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="71.428571428571431"/>
+    <n v="1.3142857142857143"/>
+    <n v="0.2628571428571429"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="17"/>
     <s v="UEG6_SHERIFF"/>
     <n v="9"/>
     <n v="1.7999999999999998"/>
@@ -3283,7 +3443,21 @@
     <x v="3"/>
   </r>
   <r>
+    <n v="16"/>
+    <s v="LEG2_LYNX"/>
+    <n v="7.2999999999999927"/>
+    <n v="1.4599999999999991"/>
+    <n v="29"/>
     <n v="17"/>
+    <n v="0"/>
+    <n v="12"/>
+    <n v="58.620689655172406"/>
+    <n v="0.25172413793103421"/>
+    <n v="5.0344827586206863E-2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="19"/>
     <s v="UEG7_LOVERGOOSE"/>
     <n v="7.0000000000000009"/>
     <n v="1.4"/>
@@ -3297,49 +3471,35 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="16"/>
-    <s v="UEG8_SOLDIER"/>
-    <n v="6.2000000000000028"/>
-    <n v="1.2400000000000007"/>
     <n v="18"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="9"/>
-    <n v="50"/>
-    <n v="0.34444444444444461"/>
-    <n v="6.888888888888893E-2"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="19"/>
-    <s v="LEG2_LYNX"/>
-    <n v="4.4999999999999929"/>
-    <n v="0.89999999999999902"/>
-    <n v="28"/>
-    <n v="16"/>
-    <n v="0"/>
-    <n v="12"/>
-    <n v="57.142857142857139"/>
-    <n v="0.16071428571428545"/>
-    <n v="3.2142857142857105E-2"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="18"/>
-    <s v="PEG30_ETC2"/>
-    <n v="4.3"/>
-    <n v="0.8600000000000001"/>
-    <n v="6"/>
+    <s v="WEG4_DOG"/>
+    <n v="5.0999999999999996"/>
+    <n v="1.0199999999999998"/>
+    <n v="7"/>
     <n v="4"/>
     <n v="0"/>
-    <n v="2"/>
-    <n v="66.666666666666657"/>
-    <n v="0.71666666666666667"/>
-    <n v="0.14333333333333334"/>
-    <x v="0"/>
+    <n v="3"/>
+    <n v="57.142857142857139"/>
+    <n v="0.72857142857142854"/>
+    <n v="0.14571428571428569"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="20"/>
+    <s v="WEG8_MOUSE"/>
+    <n v="2.8"/>
+    <n v="0.55999999999999994"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="100"/>
+    <n v="2.8"/>
+    <n v="0.55999999999999994"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="21"/>
     <s v="SEG3_FORCE"/>
     <n v="1.9000000000000004"/>
     <n v="0.37999999999999989"/>
@@ -3350,21 +3510,7 @@
     <n v="60"/>
     <n v="0.38000000000000006"/>
     <n v="7.5999999999999984E-2"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <n v="21"/>
-    <s v="UEG4_CANADIAN"/>
-    <n v="1.5"/>
-    <n v="0.30000000000000004"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="0.75"/>
-    <n v="0.15000000000000002"/>
-    <x v="3"/>
+    <x v="4"/>
   </r>
   <r>
     <n v="22"/>
@@ -3410,34 +3556,6 @@
   </r>
   <r>
     <n v="25"/>
-    <s v="UEG7_CANNIBAL"/>
-    <n v="9.9999999999999978E-2"/>
-    <n v="2.0000000000000254E-2"/>
-    <n v="12"/>
-    <n v="6"/>
-    <n v="0"/>
-    <n v="6"/>
-    <n v="50"/>
-    <n v="8.3333333333333315E-3"/>
-    <n v="1.6666666666666878E-3"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="26"/>
-    <s v="WEG4_DOG"/>
-    <n v="-0.5"/>
-    <n v="-0.10000000000000009"/>
-    <n v="6"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="50"/>
-    <n v="-8.3333333333333329E-2"/>
-    <n v="-1.666666666666668E-2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <n v="29"/>
     <s v="PEG4_UNIVERSAL"/>
     <n v="-0.69999999999999929"/>
     <n v="-0.13999999999999901"/>
@@ -3451,7 +3569,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="27"/>
+    <n v="26"/>
     <s v="LEG2_LOGAN"/>
     <n v="-0.70000000000000107"/>
     <n v="-0.14000000000000012"/>
@@ -3465,7 +3583,21 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="28"/>
+    <n v="29"/>
+    <s v="UEG8_SOLDIER"/>
+    <n v="-1.3999999999999986"/>
+    <n v="-0.27999999999999958"/>
+    <n v="21"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="11"/>
+    <n v="47.619047619047613"/>
+    <n v="-6.6666666666666596E-2"/>
+    <n v="-1.3333333333333313E-2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="27"/>
     <s v="LEG1_OKROSHKA"/>
     <n v="-1.6"/>
     <n v="-0.32"/>
@@ -3479,21 +3611,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="35"/>
-    <s v="PEG17_PROBIUS"/>
-    <n v="-1.9"/>
-    <n v="-0.38000000000000012"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="66.666666666666657"/>
-    <n v="-0.6333333333333333"/>
-    <n v="-0.12666666666666671"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="36"/>
+    <n v="28"/>
     <s v="PEG14_RANGER"/>
     <n v="-1.9000000000000001"/>
     <n v="-0.38"/>
@@ -3507,7 +3625,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="37"/>
+    <n v="35"/>
     <s v="UEG4_PELICAN"/>
     <n v="-2.9000000000000004"/>
     <n v="-0.58000000000000007"/>
@@ -3521,7 +3639,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="38"/>
+    <n v="36"/>
     <s v="UEG6_PIGEON"/>
     <n v="-3.0999999999999983"/>
     <n v="-0.61999999999999988"/>
@@ -3535,7 +3653,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="39"/>
+    <n v="37"/>
     <s v="UEG7_PIGEON"/>
     <n v="-3.0999999999999996"/>
     <n v="-0.61999999999999988"/>
@@ -3547,6 +3665,34 @@
     <n v="-0.77499999999999991"/>
     <n v="-0.15499999999999997"/>
     <x v="3"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <s v="UEG7_CANNIBAL"/>
+    <n v="-3.3"/>
+    <n v="-0.6599999999999997"/>
+    <n v="13"/>
+    <n v="6"/>
+    <n v="0"/>
+    <n v="7"/>
+    <n v="46.153846153846153"/>
+    <n v="-0.25384615384615383"/>
+    <n v="-5.0769230769230747E-2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <s v="PEG17_PROBIUS"/>
+    <n v="-4.6999999999999993"/>
+    <n v="-0.94000000000000006"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="50"/>
+    <n v="-1.1749999999999998"/>
+    <n v="-0.23500000000000001"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="30"/>
@@ -3592,6 +3738,20 @@
   </r>
   <r>
     <n v="33"/>
+    <s v="WEG7_PARADOX2"/>
+    <n v="-5.8000000000000007"/>
+    <n v="-1.1600000000000001"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="66.666666666666657"/>
+    <n v="-1.9333333333333336"/>
+    <n v="-0.38666666666666671"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="34"/>
     <s v="LEG1_PHOGA"/>
     <n v="-6"/>
     <n v="-1.2"/>
@@ -3605,7 +3765,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="34"/>
+    <n v="40"/>
     <s v="PEG18_UTER"/>
     <n v="-6.2"/>
     <n v="-1.24"/>
@@ -3619,7 +3779,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="40"/>
+    <n v="41"/>
     <s v="PEG31_HYPERION"/>
     <n v="-7.4999999999999991"/>
     <n v="-1.4999999999999998"/>
@@ -3633,7 +3793,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="41"/>
+    <n v="42"/>
     <s v="PEG26_UNKNOWN"/>
     <n v="-7.5"/>
     <n v="-1.5"/>
@@ -3647,7 +3807,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="42"/>
+    <n v="43"/>
     <s v="LEG1_IRONANNY2"/>
     <n v="-7.5"/>
     <n v="-1.5"/>
@@ -3661,7 +3821,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="43"/>
+    <n v="44"/>
     <s v="WEG7_PARADOX"/>
     <n v="-7.5000000000000009"/>
     <n v="-1.5"/>
@@ -3675,7 +3835,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="44"/>
+    <n v="45"/>
     <s v="PEG18_DIABLO2"/>
     <n v="-9.1"/>
     <n v="-1.82"/>
@@ -3689,7 +3849,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="45"/>
+    <n v="46"/>
     <s v="LEG1_BIBI2"/>
     <n v="-9.4000000000000021"/>
     <n v="-1.879999999999999"/>
@@ -3703,7 +3863,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="46"/>
+    <n v="47"/>
     <s v="UEG6_VULTURE"/>
     <n v="-9.6999999999999993"/>
     <n v="-1.9400000000000002"/>
@@ -3717,7 +3877,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="47"/>
+    <n v="48"/>
     <s v="UEG7_CELEBRITY"/>
     <n v="-10.199999999999999"/>
     <n v="-2.04"/>
@@ -3731,21 +3891,21 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="48"/>
+    <n v="49"/>
     <s v="PEG17_ZEALOT"/>
-    <n v="-11.399999999999997"/>
-    <n v="-2.2799999999999998"/>
-    <n v="4"/>
-    <n v="2"/>
+    <n v="-11.199999999999998"/>
+    <n v="-2.2399999999999998"/>
+    <n v="5"/>
+    <n v="3"/>
     <n v="0"/>
     <n v="2"/>
-    <n v="50"/>
-    <n v="-2.8499999999999992"/>
-    <n v="-0.56999999999999995"/>
+    <n v="60"/>
+    <n v="-2.2399999999999993"/>
+    <n v="-0.44799999999999995"/>
     <x v="0"/>
   </r>
   <r>
-    <n v="49"/>
+    <n v="50"/>
     <s v="UEG4_PELICAN2"/>
     <n v="-11.4"/>
     <n v="-2.2800000000000002"/>
@@ -3759,7 +3919,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="50"/>
+    <n v="51"/>
     <s v="UEG4_FALCON"/>
     <n v="-12"/>
     <n v="-2.4"/>
@@ -3773,7 +3933,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="51"/>
+    <n v="52"/>
     <s v="LEG2_DRG"/>
     <n v="-12"/>
     <n v="-2.4"/>
@@ -3785,20 +3945,6 @@
     <n v="-2.4"/>
     <n v="-0.48"/>
     <x v="1"/>
-  </r>
-  <r>
-    <n v="52"/>
-    <s v="PEG18_ANDUIN"/>
-    <n v="-12.5"/>
-    <n v="-2.4999999999999996"/>
-    <n v="11"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="6"/>
-    <n v="45.454545454545453"/>
-    <n v="-1.1363636363636365"/>
-    <n v="-0.22727272727272724"/>
-    <x v="0"/>
   </r>
   <r>
     <n v="53"/>
@@ -3844,6 +3990,20 @@
   </r>
   <r>
     <n v="56"/>
+    <s v="UEG4_CANADIAN"/>
+    <n v="-14.899999999999999"/>
+    <n v="-2.9799999999999995"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="33.333333333333329"/>
+    <n v="-4.9666666666666659"/>
+    <n v="-0.99333333333333318"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="57"/>
     <s v="UEG7_CARRIER"/>
     <n v="-15.099999999999998"/>
     <n v="-3.0200000000000005"/>
@@ -3857,7 +4017,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="57"/>
+    <n v="58"/>
     <s v="UEG9_BIRDWATCHER2"/>
     <n v="-19.5"/>
     <n v="-3.9"/>
@@ -3871,7 +4031,21 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="58"/>
+    <n v="59"/>
+    <s v="PEG18_ANDUIN"/>
+    <n v="-19.600000000000001"/>
+    <n v="-3.9199999999999995"/>
+    <n v="12"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="7"/>
+    <n v="41.666666666666671"/>
+    <n v="-1.6333333333333335"/>
+    <n v="-0.32666666666666661"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="60"/>
     <s v="VEG1_MOON"/>
     <n v="-20.100000000000001"/>
     <n v="-4.0200000000000005"/>
@@ -3882,10 +4056,10 @@
     <n v="20"/>
     <n v="-2.0100000000000002"/>
     <n v="-0.40200000000000002"/>
-    <x v="4"/>
+    <x v="5"/>
   </r>
   <r>
-    <n v="59"/>
+    <n v="61"/>
     <s v="VEG1_VENUS"/>
     <n v="-22.700000000000003"/>
     <n v="-4.5399999999999991"/>
@@ -3896,10 +4070,10 @@
     <n v="47.368421052631575"/>
     <n v="-1.1947368421052633"/>
     <n v="-0.23894736842105258"/>
-    <x v="4"/>
+    <x v="5"/>
   </r>
   <r>
-    <n v="60"/>
+    <n v="62"/>
     <s v="PEG19_ANUBARAK"/>
     <n v="-25.799999999999997"/>
     <n v="-5.16"/>
@@ -3913,7 +4087,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="61"/>
+    <n v="63"/>
     <s v="PEG18_BLAZE"/>
     <n v="-42.199999999999996"/>
     <n v="-8.44"/>
@@ -3927,7 +4101,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="62"/>
+    <n v="64"/>
     <s v="LEG2_ALKASH"/>
     <n v="-42.900000000000006"/>
     <n v="-8.58"/>
@@ -3939,20 +4113,6 @@
     <n v="-10.725000000000001"/>
     <n v="-2.145"/>
     <x v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="6"/>
   </r>
   <r>
     <m/>
@@ -4144,9 +4304,9 @@
       <items count="8">
         <item x="1"/>
         <item x="0"/>
+        <item x="4"/>
+        <item x="3"/>
         <item x="5"/>
-        <item x="3"/>
-        <item x="4"/>
         <item x="2"/>
         <item h="1" x="6"/>
         <item t="default"/>
@@ -4729,7 +4889,7 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
-        <v>46302</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4760,16 +4920,16 @@
         <v>116</v>
       </c>
       <c r="B4" s="12">
-        <v>-12.000000000000028</v>
+        <v>2.5</v>
       </c>
       <c r="C4" s="12">
-        <v>-2.3999999999999977</v>
+        <v>0.50000000000000533</v>
       </c>
       <c r="D4" s="12">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E4" s="12">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F4" s="12">
         <v>2</v>
@@ -4783,22 +4943,22 @@
         <v>117</v>
       </c>
       <c r="B5" s="12">
-        <v>74.499999999999972</v>
+        <v>43.700000000000024</v>
       </c>
       <c r="C5" s="12">
-        <v>14.900000000000007</v>
+        <v>8.740000000000018</v>
       </c>
       <c r="D5" s="12">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="E5" s="12">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F5" s="12">
         <v>5</v>
       </c>
       <c r="G5" s="12">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4829,22 +4989,22 @@
         <v>119</v>
       </c>
       <c r="B7" s="12">
-        <v>-28.299999999999994</v>
+        <v>-65.099999999999994</v>
       </c>
       <c r="C7" s="12">
-        <v>-5.6599999999999975</v>
+        <v>-13.020000000000001</v>
       </c>
       <c r="D7" s="12">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E7" s="12">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" s="12">
         <v>3</v>
       </c>
       <c r="G7" s="12">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4852,13 +5012,13 @@
         <v>120</v>
       </c>
       <c r="B8" s="12">
-        <v>-25.800000000000004</v>
+        <v>-32.600000000000009</v>
       </c>
       <c r="C8" s="12">
-        <v>-5.16</v>
+        <v>-6.52</v>
       </c>
       <c r="D8" s="12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8" s="12">
         <v>16</v>
@@ -4867,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="12">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4875,22 +5035,22 @@
         <v>121</v>
       </c>
       <c r="B9" s="12">
-        <v>42</v>
+        <v>46.5</v>
       </c>
       <c r="C9" s="12">
-        <v>8.4000000000000021</v>
+        <v>9.3000000000000025</v>
       </c>
       <c r="D9" s="12">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E9" s="12">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F9" s="12">
         <v>2</v>
       </c>
       <c r="G9" s="12">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4898,22 +5058,22 @@
         <v>114</v>
       </c>
       <c r="B10" s="12">
-        <v>65.199999999999932</v>
+        <v>9.8000000000000185</v>
       </c>
       <c r="C10" s="12">
-        <v>13.040000000000013</v>
+        <v>1.9600000000000239</v>
       </c>
       <c r="D10" s="12">
-        <v>696</v>
+        <v>724</v>
       </c>
       <c r="E10" s="12">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="F10" s="12">
         <v>12</v>
       </c>
       <c r="G10" s="12">
-        <v>326</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -5328,7 +5488,9 @@
       <c r="M2" s="16">
         <v>46302</v>
       </c>
-      <c r="N2" s="16"/>
+      <c r="N2" s="16">
+        <v>46304</v>
+      </c>
       <c r="O2" s="16"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="16"/>
@@ -5380,6 +5542,9 @@
       <c r="M3">
         <v>-12.000000000000028</v>
       </c>
+      <c r="N3">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="4" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -5421,6 +5586,9 @@
       <c r="M4">
         <v>74.499999999999972</v>
       </c>
+      <c r="N4">
+        <v>43.700000000000024</v>
+      </c>
     </row>
     <row r="5" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -5462,6 +5630,9 @@
       <c r="M5">
         <v>14.799999999999997</v>
       </c>
+      <c r="N5">
+        <v>14.799999999999997</v>
+      </c>
     </row>
     <row r="6" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -5503,6 +5674,9 @@
       <c r="M6">
         <v>-28.299999999999994</v>
       </c>
+      <c r="N6">
+        <v>-65.099999999999994</v>
+      </c>
     </row>
     <row r="7" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -5544,6 +5718,9 @@
       <c r="M7">
         <v>-25.800000000000004</v>
       </c>
+      <c r="N7">
+        <v>-32.600000000000009</v>
+      </c>
     </row>
     <row r="8" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -5585,6 +5762,9 @@
       <c r="M8">
         <v>42</v>
       </c>
+      <c r="N8">
+        <v>46.5</v>
+      </c>
     </row>
     <row r="9" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -5595,7 +5775,7 @@
         <v>6.8999999999999915</v>
       </c>
       <c r="C9">
-        <f t="shared" ref="C9:M9" si="0">SUM(C3:C8)</f>
+        <f t="shared" ref="C9:N9" si="0">SUM(C3:C8)</f>
         <v>5.7000000000000028</v>
       </c>
       <c r="D9">
@@ -5637,6 +5817,10 @@
       <c r="M9">
         <f t="shared" si="0"/>
         <v>65.199999999999932</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="0"/>
+        <v>9.8000000000000185</v>
       </c>
     </row>
     <row r="11" spans="1:121" x14ac:dyDescent="0.25">
@@ -5685,8 +5869,12 @@
         <v>46301</v>
       </c>
       <c r="M11" s="16">
-        <f t="shared" ref="M11" si="3">M2</f>
+        <f t="shared" ref="M11:N11" si="3">M2</f>
         <v>46302</v>
+      </c>
+      <c r="N11" s="16">
+        <f t="shared" si="3"/>
+        <v>46304</v>
       </c>
     </row>
     <row r="12" spans="1:121" x14ac:dyDescent="0.25">
@@ -5702,7 +5890,7 @@
         <v>-19.799999999999997</v>
       </c>
       <c r="D12">
-        <f t="shared" ref="D12:M12" si="4">D3-C3</f>
+        <f t="shared" ref="D12:N12" si="4">D3-C3</f>
         <v>17.799999999999997</v>
       </c>
       <c r="E12">
@@ -5741,6 +5929,10 @@
         <f t="shared" si="4"/>
         <v>15.199999999999974</v>
       </c>
+      <c r="N12">
+        <f t="shared" si="4"/>
+        <v>14.500000000000028</v>
+      </c>
     </row>
     <row r="13" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -5751,7 +5943,7 @@
         <v>19.7</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:M17" si="6">C4-B4</f>
+        <f t="shared" ref="C13:N17" si="6">C4-B4</f>
         <v>31.000000000000004</v>
       </c>
       <c r="D13">
@@ -5794,6 +5986,10 @@
         <f t="shared" si="6"/>
         <v>-35.199999999999989</v>
       </c>
+      <c r="N13">
+        <f t="shared" si="6"/>
+        <v>-30.799999999999947</v>
+      </c>
     </row>
     <row r="14" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -5847,6 +6043,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="N14">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -5900,6 +6100,10 @@
         <f t="shared" si="6"/>
         <v>-12.099999999999991</v>
       </c>
+      <c r="N15">
+        <f t="shared" si="6"/>
+        <v>-36.799999999999997</v>
+      </c>
     </row>
     <row r="16" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -5953,8 +6157,12 @@
         <f t="shared" si="6"/>
         <v>1.2999999999999972</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N16">
+        <f t="shared" si="6"/>
+        <v>-6.8000000000000043</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -6006,8 +6214,12 @@
         <f t="shared" si="6"/>
         <v>-21</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N17">
+        <f t="shared" si="6"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>139</v>
       </c>
@@ -6056,8 +6268,12 @@
         <v>20.999999999999972</v>
       </c>
       <c r="M18">
-        <f t="shared" ref="M18" si="15">SUM(M12:M17)</f>
+        <f t="shared" ref="M18:N18" si="15">SUM(M12:M17)</f>
         <v>-51.800000000000011</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="15"/>
+        <v>-55.39999999999992</v>
       </c>
     </row>
   </sheetData>
@@ -6164,34 +6380,34 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>163.79999999999998</v>
+        <v>153.19999999999999</v>
       </c>
       <c r="D2">
-        <v>32.760000000000005</v>
+        <v>30.640000000000004</v>
       </c>
       <c r="E2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I2" s="7">
         <f>IFERROR((F2/E2)*100,0)</f>
-        <v>65.060240963855421</v>
+        <v>64.772727272727266</v>
       </c>
       <c r="J2" s="10">
         <f>IFERROR(C2/E2,0)</f>
-        <v>1.9734939759036143</v>
+        <v>1.7409090909090907</v>
       </c>
       <c r="K2" s="10">
         <f>IFERROR(D2/E2,0)</f>
-        <v>0.39469879518072293</v>
+        <v>0.3481818181818182</v>
       </c>
       <c r="L2" s="10" t="str">
         <f>LEFT(B2,3)</f>
@@ -6199,19 +6415,19 @@
       </c>
       <c r="N2">
         <f t="shared" ref="N2:S2" si="0">C2+U2</f>
-        <v>163.79999999999998</v>
+        <v>153.19999999999999</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>32.760000000000005</v>
+        <v>30.640000000000004</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
@@ -6219,7 +6435,7 @@
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -6227,65 +6443,65 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C3">
-        <v>38.799999999999997</v>
+        <v>42.199999999999996</v>
       </c>
       <c r="D3">
-        <v>7.7600000000000016</v>
+        <v>8.4400000000000013</v>
       </c>
       <c r="E3">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I3" s="7">
         <f>IFERROR((F3/E3)*100,0)</f>
-        <v>51.162790697674424</v>
+        <v>69.230769230769226</v>
       </c>
       <c r="J3" s="10">
         <f>IFERROR(C3/E3,0)</f>
-        <v>0.9023255813953488</v>
+        <v>1.6230769230769229</v>
       </c>
       <c r="K3" s="10">
         <f>IFERROR(D3/E3,0)</f>
-        <v>0.1804651162790698</v>
+        <v>0.32461538461538464</v>
       </c>
       <c r="L3" s="10" t="str">
         <f>LEFT(B3,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N53" si="1">C3+U3</f>
-        <v>38.799999999999997</v>
+        <v>42.199999999999996</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O17" si="2">D3+V3</f>
-        <v>7.7600000000000016</v>
+        <v>8.4400000000000013</v>
       </c>
       <c r="P3">
         <f t="shared" ref="P3:P17" si="3">E3+W3</f>
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q17" si="4">F3+X3</f>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R17" si="5">G3+Y3</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S17" si="6">H3+Z3</f>
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -6293,263 +6509,263 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C4">
-        <v>38.099999999999994</v>
+        <v>35.9</v>
       </c>
       <c r="D4">
-        <v>7.620000000000001</v>
+        <v>7.1800000000000024</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I4" s="7">
         <f>IFERROR((F4/E4)*100,0)</f>
-        <v>68</v>
+        <v>59.322033898305079</v>
       </c>
       <c r="J4" s="10">
         <f>IFERROR(C4/E4,0)</f>
-        <v>1.5239999999999998</v>
+        <v>0.6084745762711864</v>
       </c>
       <c r="K4" s="10">
         <f>IFERROR(D4/E4,0)</f>
-        <v>0.30480000000000002</v>
+        <v>0.12169491525423733</v>
       </c>
       <c r="L4" s="10" t="str">
         <f>LEFT(B4,3)</f>
-        <v>LEG</v>
+        <v>WEG</v>
       </c>
       <c r="N4">
         <f t="shared" si="1"/>
-        <v>38.099999999999994</v>
+        <v>35.9</v>
       </c>
       <c r="O4">
         <f t="shared" si="2"/>
-        <v>7.620000000000001</v>
+        <v>7.1800000000000024</v>
       </c>
       <c r="P4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="Q4">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="R4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>56</v>
+      <c r="B5" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>31.6</v>
       </c>
       <c r="D5">
-        <v>6.8000000000000025</v>
+        <v>6.32</v>
       </c>
       <c r="E5">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>1</v>
-      </c>
-      <c r="H5">
-        <v>23</v>
       </c>
       <c r="I5" s="7">
         <f>IFERROR((F5/E5)*100,0)</f>
-        <v>58.620689655172406</v>
+        <v>88.888888888888886</v>
       </c>
       <c r="J5" s="10">
         <f>IFERROR(C5/E5,0)</f>
-        <v>0.58620689655172409</v>
+        <v>3.5111111111111111</v>
       </c>
       <c r="K5" s="10">
         <f>IFERROR(D5/E5,0)</f>
-        <v>0.11724137931034487</v>
+        <v>0.7022222222222223</v>
       </c>
       <c r="L5" s="10" t="str">
         <f>LEFT(B5,3)</f>
-        <v>WEG</v>
+        <v>LEG</v>
       </c>
       <c r="N5">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>31.6</v>
       </c>
       <c r="O5">
         <f t="shared" si="2"/>
-        <v>6.8000000000000025</v>
+        <v>6.32</v>
       </c>
       <c r="P5">
         <f t="shared" si="3"/>
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <f t="shared" si="4"/>
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="R5">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>68</v>
+      <c r="B6" t="s">
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>24.000000000000004</v>
+        <v>23.4</v>
       </c>
       <c r="D6">
-        <v>4.8000000000000007</v>
+        <v>4.6800000000000015</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I6" s="7">
         <f>IFERROR((F6/E6)*100,0)</f>
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="J6" s="10">
         <f>IFERROR(C6/E6,0)</f>
-        <v>3.0000000000000004</v>
+        <v>0.53181818181818175</v>
       </c>
       <c r="K6" s="10">
         <f>IFERROR(D6/E6,0)</f>
-        <v>0.60000000000000009</v>
+        <v>0.1063636363636364</v>
       </c>
       <c r="L6" s="10" t="str">
         <f>LEFT(B6,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N6">
         <f t="shared" si="1"/>
-        <v>24.000000000000004</v>
+        <v>23.4</v>
       </c>
       <c r="O6">
         <f t="shared" si="2"/>
-        <v>4.8000000000000007</v>
+        <v>4.6800000000000015</v>
       </c>
       <c r="P6">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="Q6">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>132</v>
+      <c r="B7" t="s">
+        <v>58</v>
       </c>
       <c r="C7">
-        <v>23.200000000000003</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>4.6400000000000006</v>
+        <v>3.1999999999999993</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I7" s="7">
         <f>IFERROR((F7/E7)*100,0)</f>
-        <v>60</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="J7" s="10">
         <f>IFERROR(C7/E7,0)</f>
-        <v>1.5466666666666669</v>
+        <v>1.2307692307692308</v>
       </c>
       <c r="K7" s="10">
         <f>IFERROR(D7/E7,0)</f>
-        <v>0.30933333333333335</v>
+        <v>0.24615384615384611</v>
       </c>
       <c r="L7" s="10" t="str">
         <f>LEFT(B7,3)</f>
-        <v>UEG</v>
+        <v>WEG</v>
       </c>
       <c r="N7">
         <f t="shared" si="1"/>
-        <v>23.200000000000003</v>
+        <v>16</v>
       </c>
       <c r="O7">
         <f t="shared" si="2"/>
-        <v>4.6400000000000006</v>
+        <v>3.1999999999999993</v>
       </c>
       <c r="P7">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q7">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -6557,65 +6773,65 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8">
-        <v>3.4</v>
+        <v>3.1999999999999993</v>
       </c>
       <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
         <v>9</v>
       </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I8" s="7">
         <f>IFERROR((F8/E8)*100,0)</f>
-        <v>55.555555555555557</v>
+        <v>47.368421052631575</v>
       </c>
       <c r="J8" s="10">
         <f>IFERROR(C8/E8,0)</f>
-        <v>1.8888888888888888</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="K8" s="10">
         <f>IFERROR(D8/E8,0)</f>
-        <v>0.37777777777777777</v>
+        <v>0.16842105263157892</v>
       </c>
       <c r="L8" s="10" t="str">
         <f>LEFT(B8,3)</f>
-        <v>VEG</v>
+        <v>UEG</v>
       </c>
       <c r="N8">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O8">
         <f t="shared" si="2"/>
-        <v>3.4</v>
+        <v>3.1999999999999993</v>
       </c>
       <c r="P8">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="Q8">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -6623,103 +6839,103 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C9">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="D9">
-        <v>3.1999999999999993</v>
+        <v>3.1400000000000006</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="7">
         <f>IFERROR((F9/E9)*100,0)</f>
-        <v>61.53846153846154</v>
+        <v>50</v>
       </c>
       <c r="J9" s="10">
         <f>IFERROR(C9/E9,0)</f>
-        <v>1.2307692307692308</v>
+        <v>1.5699999999999998</v>
       </c>
       <c r="K9" s="10">
         <f>IFERROR(D9/E9,0)</f>
-        <v>0.24615384615384611</v>
+        <v>0.31400000000000006</v>
       </c>
       <c r="L9" s="10" t="str">
         <f>LEFT(B9,3)</f>
-        <v>WEG</v>
+        <v>PEG</v>
       </c>
       <c r="N9">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="O9">
         <f t="shared" si="2"/>
-        <v>3.1999999999999993</v>
+        <v>3.1400000000000006</v>
       </c>
       <c r="P9">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>85</v>
+      <c r="B10" s="8" t="s">
+        <v>132</v>
       </c>
       <c r="C10">
-        <v>16</v>
+        <v>13.800000000000004</v>
       </c>
       <c r="D10">
-        <v>3.1999999999999993</v>
+        <v>2.7600000000000007</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F10">
         <v>9</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>8</v>
       </c>
       <c r="I10" s="7">
         <f>IFERROR((F10/E10)*100,0)</f>
-        <v>47.368421052631575</v>
+        <v>52.941176470588239</v>
       </c>
       <c r="J10" s="10">
         <f>IFERROR(C10/E10,0)</f>
-        <v>0.84210526315789469</v>
+        <v>0.81176470588235317</v>
       </c>
       <c r="K10" s="10">
         <f>IFERROR(D10/E10,0)</f>
-        <v>0.16842105263157892</v>
+        <v>0.16235294117647062</v>
       </c>
       <c r="L10" s="10" t="str">
         <f>LEFT(B10,3)</f>
@@ -6727,15 +6943,15 @@
       </c>
       <c r="N10">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>13.800000000000004</v>
       </c>
       <c r="O10">
         <f t="shared" si="2"/>
-        <v>3.1999999999999993</v>
+        <v>2.7600000000000007</v>
       </c>
       <c r="P10">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q10">
         <f t="shared" si="4"/>
@@ -6743,7 +6959,7 @@
       </c>
       <c r="R10">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <f t="shared" si="6"/>
@@ -6755,49 +6971,49 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="C11">
-        <v>15.7</v>
+        <v>12.899999999999997</v>
       </c>
       <c r="D11">
-        <v>3.1400000000000006</v>
+        <v>2.5799999999999996</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I11" s="7">
         <f>IFERROR((F11/E11)*100,0)</f>
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J11" s="10">
         <f>IFERROR(C11/E11,0)</f>
-        <v>1.5699999999999998</v>
+        <v>1.2899999999999996</v>
       </c>
       <c r="K11" s="10">
         <f>IFERROR(D11/E11,0)</f>
-        <v>0.31400000000000006</v>
+        <v>0.25799999999999995</v>
       </c>
       <c r="L11" s="10" t="str">
         <f>LEFT(B11,3)</f>
-        <v>PEG</v>
+        <v>SEG</v>
       </c>
       <c r="N11">
         <f t="shared" si="1"/>
-        <v>15.7</v>
+        <v>12.899999999999997</v>
       </c>
       <c r="O11">
         <f t="shared" si="2"/>
-        <v>3.1400000000000006</v>
+        <v>2.5799999999999996</v>
       </c>
       <c r="P11">
         <f t="shared" si="3"/>
@@ -6805,7 +7021,7 @@
       </c>
       <c r="Q11">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <f t="shared" si="5"/>
@@ -6813,7 +7029,7 @@
       </c>
       <c r="S11">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -6821,57 +7037,57 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="C12">
-        <v>12.899999999999997</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D12">
-        <v>2.5799999999999996</v>
+        <v>2.04</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I12" s="7">
         <f>IFERROR((F12/E12)*100,0)</f>
-        <v>70</v>
+        <v>45.454545454545453</v>
       </c>
       <c r="J12" s="10">
         <f>IFERROR(C12/E12,0)</f>
-        <v>1.2899999999999996</v>
+        <v>0.92727272727272725</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(D12/E12,0)</f>
-        <v>0.25799999999999995</v>
+        <v>0.18545454545454546</v>
       </c>
       <c r="L12" s="10" t="str">
         <f>LEFT(B12,3)</f>
-        <v>SEG</v>
+        <v>VEG</v>
       </c>
       <c r="N12">
         <f t="shared" si="1"/>
-        <v>12.899999999999997</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="O12">
         <f t="shared" si="2"/>
-        <v>2.5799999999999996</v>
+        <v>2.04</v>
       </c>
       <c r="P12">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q12">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <f t="shared" si="5"/>
@@ -6879,7 +7095,7 @@
       </c>
       <c r="S12">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -7084,58 +7300,58 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>86</v>
+      <c r="B16" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="C16">
-        <v>9</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D16">
-        <v>1.7999999999999998</v>
+        <v>1.8400000000000003</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" s="7">
         <f>IFERROR((F16/E16)*100,0)</f>
-        <v>50</v>
+        <v>71.428571428571431</v>
       </c>
       <c r="J16" s="10">
         <f>IFERROR(C16/E16,0)</f>
-        <v>1.5</v>
+        <v>1.3142857142857143</v>
       </c>
       <c r="K16" s="10">
         <f>IFERROR(D16/E16,0)</f>
-        <v>0.3</v>
+        <v>0.2628571428571429</v>
       </c>
       <c r="L16" s="10" t="str">
         <f>LEFT(B16,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N16">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="O16">
         <f t="shared" si="2"/>
-        <v>1.7999999999999998</v>
+        <v>1.8400000000000003</v>
       </c>
       <c r="P16">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <f t="shared" si="5"/>
@@ -7143,24 +7359,24 @@
       </c>
       <c r="S16">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>134</v>
+      <c r="B17" t="s">
+        <v>86</v>
       </c>
       <c r="C17">
-        <v>7.0000000000000009</v>
+        <v>9</v>
       </c>
       <c r="D17">
-        <v>1.4</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>3</v>
@@ -7169,19 +7385,19 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="7">
         <f>IFERROR((F17/E17)*100,0)</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J17" s="10">
         <f>IFERROR(C17/E17,0)</f>
-        <v>1.4000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="K17" s="10">
         <f>IFERROR(D17/E17,0)</f>
-        <v>0.27999999999999997</v>
+        <v>0.3</v>
       </c>
       <c r="L17" s="10" t="str">
         <f>LEFT(B17,3)</f>
@@ -7189,15 +7405,15 @@
       </c>
       <c r="N17">
         <f t="shared" si="1"/>
-        <v>7.0000000000000009</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <f t="shared" si="2"/>
-        <v>1.4</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="P17">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <f t="shared" si="4"/>
@@ -7209,65 +7425,65 @@
       </c>
       <c r="S17">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>131</v>
+      <c r="B18" t="s">
+        <v>60</v>
       </c>
       <c r="C18">
-        <v>6.2000000000000028</v>
+        <v>7.2999999999999927</v>
       </c>
       <c r="D18">
-        <v>1.2400000000000007</v>
+        <v>1.4599999999999991</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F18">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I18" s="7">
         <f>IFERROR((F18/E18)*100,0)</f>
-        <v>50</v>
+        <v>58.620689655172406</v>
       </c>
       <c r="J18" s="10">
         <f>IFERROR(C18/E18,0)</f>
-        <v>0.34444444444444461</v>
+        <v>0.25172413793103421</v>
       </c>
       <c r="K18" s="10">
         <f>IFERROR(D18/E18,0)</f>
-        <v>6.888888888888893E-2</v>
+        <v>5.0344827586206863E-2</v>
       </c>
       <c r="L18" s="10" t="str">
         <f>LEFT(B18,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N18">
         <f t="shared" si="1"/>
-        <v>6.2000000000000028</v>
+        <v>7.2999999999999927</v>
       </c>
       <c r="O18">
         <f t="shared" ref="O18:O53" si="7">D18+V18</f>
-        <v>1.2400000000000007</v>
+        <v>1.4599999999999991</v>
       </c>
       <c r="P18">
         <f t="shared" ref="P18:P53" si="8">E18+W18</f>
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="Q18">
         <f t="shared" ref="Q18:Q53" si="9">F18+X18</f>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="R18">
         <f t="shared" ref="R18:R47" si="10">G18+Y18</f>
@@ -7275,65 +7491,65 @@
       </c>
       <c r="S18">
         <f t="shared" ref="S18:S47" si="11">H18+Z18</f>
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
-      <c r="B19" t="s">
-        <v>60</v>
+      <c r="B19" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="C19">
-        <v>4.4999999999999929</v>
+        <v>7.0000000000000009</v>
       </c>
       <c r="D19">
-        <v>0.89999999999999902</v>
+        <v>1.4</v>
       </c>
       <c r="E19">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F19">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I19" s="7">
         <f>IFERROR((F19/E19)*100,0)</f>
-        <v>57.142857142857139</v>
+        <v>60</v>
       </c>
       <c r="J19" s="10">
         <f>IFERROR(C19/E19,0)</f>
-        <v>0.16071428571428545</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="K19" s="10">
         <f>IFERROR(D19/E19,0)</f>
-        <v>3.2142857142857105E-2</v>
+        <v>0.27999999999999997</v>
       </c>
       <c r="L19" s="10" t="str">
         <f>LEFT(B19,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N19">
         <f t="shared" si="1"/>
-        <v>4.4999999999999929</v>
+        <v>7.0000000000000009</v>
       </c>
       <c r="O19">
         <f t="shared" si="7"/>
-        <v>0.89999999999999902</v>
+        <v>1.4</v>
       </c>
       <c r="P19">
         <f t="shared" si="8"/>
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <f t="shared" si="9"/>
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="R19">
         <f t="shared" si="10"/>
@@ -7341,24 +7557,24 @@
       </c>
       <c r="S19">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>140</v>
+      <c r="B20" t="s">
+        <v>138</v>
       </c>
       <c r="C20">
-        <v>4.3</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="D20">
-        <v>0.8600000000000001</v>
+        <v>1.0199999999999998</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20">
         <v>4</v>
@@ -7367,35 +7583,35 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="7">
         <f>IFERROR((F20/E20)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>57.142857142857139</v>
       </c>
       <c r="J20" s="10">
         <f>IFERROR(C20/E20,0)</f>
-        <v>0.71666666666666667</v>
+        <v>0.72857142857142854</v>
       </c>
       <c r="K20" s="10">
         <f>IFERROR(D20/E20,0)</f>
-        <v>0.14333333333333334</v>
+        <v>0.14571428571428569</v>
       </c>
       <c r="L20" s="10" t="str">
         <f>LEFT(B20,3)</f>
-        <v>PEG</v>
+        <v>WEG</v>
       </c>
       <c r="N20">
         <f t="shared" si="1"/>
-        <v>4.3</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="O20">
         <f t="shared" si="7"/>
-        <v>0.8600000000000001</v>
+        <v>1.0199999999999998</v>
       </c>
       <c r="P20">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <f t="shared" si="9"/>
@@ -7407,65 +7623,65 @@
       </c>
       <c r="S20">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>73</v>
+      <c r="B21" s="8" t="s">
+        <v>147</v>
       </c>
       <c r="C21">
-        <v>1.9000000000000004</v>
+        <v>2.8</v>
       </c>
       <c r="D21">
-        <v>0.37999999999999989</v>
+        <v>0.55999999999999994</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" s="7">
         <f>IFERROR((F21/E21)*100,0)</f>
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J21" s="10">
         <f>IFERROR(C21/E21,0)</f>
-        <v>0.38000000000000006</v>
+        <v>2.8</v>
       </c>
       <c r="K21" s="10">
         <f>IFERROR(D21/E21,0)</f>
-        <v>7.5999999999999984E-2</v>
+        <v>0.55999999999999994</v>
       </c>
       <c r="L21" s="10" t="str">
         <f>LEFT(B21,3)</f>
-        <v>SEG</v>
+        <v>WEG</v>
       </c>
       <c r="N21">
         <f t="shared" si="1"/>
-        <v>1.9000000000000004</v>
+        <v>2.8</v>
       </c>
       <c r="O21">
         <f t="shared" si="7"/>
-        <v>0.37999999999999989</v>
+        <v>0.55999999999999994</v>
       </c>
       <c r="P21">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q21">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R21">
         <f t="shared" si="10"/>
@@ -7473,65 +7689,65 @@
       </c>
       <c r="S21">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>146</v>
+      <c r="B22" t="s">
+        <v>73</v>
       </c>
       <c r="C22">
-        <v>1.5</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="D22">
-        <v>0.30000000000000004</v>
+        <v>0.37999999999999989</v>
       </c>
       <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>2</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
       </c>
       <c r="I22" s="7">
         <f>IFERROR((F22/E22)*100,0)</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J22" s="10">
         <f>IFERROR(C22/E22,0)</f>
-        <v>0.75</v>
+        <v>0.38000000000000006</v>
       </c>
       <c r="K22" s="10">
         <f>IFERROR(D22/E22,0)</f>
-        <v>0.15000000000000002</v>
+        <v>7.5999999999999984E-2</v>
       </c>
       <c r="L22" s="10" t="str">
         <f>LEFT(B22,3)</f>
-        <v>UEG</v>
+        <v>SEG</v>
       </c>
       <c r="N22">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="O22">
         <f t="shared" si="7"/>
-        <v>0.30000000000000004</v>
+        <v>0.37999999999999989</v>
       </c>
       <c r="P22">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R22">
         <f t="shared" si="10"/>
@@ -7539,7 +7755,7 @@
       </c>
       <c r="S22">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
@@ -7744,66 +7960,66 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>133</v>
+      <c r="B26" t="s">
+        <v>76</v>
       </c>
       <c r="C26">
-        <v>9.9999999999999978E-2</v>
+        <v>-0.69999999999999929</v>
       </c>
       <c r="D26">
-        <v>2.0000000000000254E-2</v>
+        <v>-0.13999999999999901</v>
       </c>
       <c r="E26">
+        <v>22</v>
+      </c>
+      <c r="F26">
         <v>12</v>
       </c>
-      <c r="F26">
-        <v>6</v>
-      </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I26" s="7">
         <f>IFERROR((F26/E26)*100,0)</f>
-        <v>50</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="J26" s="10">
         <f>IFERROR(C26/E26,0)</f>
-        <v>8.3333333333333315E-3</v>
+        <v>-3.1818181818181787E-2</v>
       </c>
       <c r="K26" s="10">
         <f>IFERROR(D26/E26,0)</f>
-        <v>1.6666666666666878E-3</v>
+        <v>-6.3636363636363187E-3</v>
       </c>
       <c r="L26" s="10" t="str">
         <f>LEFT(B26,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N26">
         <f t="shared" si="1"/>
-        <v>9.9999999999999978E-2</v>
+        <v>-0.69999999999999929</v>
       </c>
       <c r="O26">
         <f t="shared" si="7"/>
-        <v>2.0000000000000254E-2</v>
+        <v>-0.13999999999999901</v>
       </c>
       <c r="P26">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q26">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R26">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -7811,19 +8027,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="C27">
-        <v>-0.5</v>
+        <v>-0.70000000000000107</v>
       </c>
       <c r="D27">
-        <v>-0.10000000000000009</v>
+        <v>-0.14000000000000012</v>
       </c>
       <c r="E27">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -7833,35 +8049,35 @@
       </c>
       <c r="I27" s="7">
         <f>IFERROR((F27/E27)*100,0)</f>
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J27" s="10">
         <f>IFERROR(C27/E27,0)</f>
-        <v>-8.3333333333333329E-2</v>
+        <v>-5.8333333333333424E-2</v>
       </c>
       <c r="K27" s="10">
         <f>IFERROR(D27/E27,0)</f>
-        <v>-1.666666666666668E-2</v>
+        <v>-1.1666666666666678E-2</v>
       </c>
       <c r="L27" s="10" t="str">
         <f>LEFT(B27,3)</f>
-        <v>WEG</v>
+        <v>LEG</v>
       </c>
       <c r="N27">
         <f t="shared" si="1"/>
-        <v>-0.5</v>
+        <v>-0.70000000000000107</v>
       </c>
       <c r="O27">
         <f t="shared" si="7"/>
-        <v>-0.10000000000000009</v>
+        <v>-0.14000000000000012</v>
       </c>
       <c r="P27">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q27">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <f t="shared" si="10"/>
@@ -7876,104 +8092,104 @@
       <c r="A28">
         <v>29</v>
       </c>
-      <c r="B28" t="s">
-        <v>76</v>
+      <c r="B28" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="C28">
-        <v>-0.69999999999999929</v>
+        <v>-1.3999999999999986</v>
       </c>
       <c r="D28">
-        <v>-0.13999999999999901</v>
+        <v>-0.27999999999999958</v>
       </c>
       <c r="E28">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F28">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I28" s="7">
         <f>IFERROR((F28/E28)*100,0)</f>
-        <v>54.54545454545454</v>
+        <v>47.619047619047613</v>
       </c>
       <c r="J28" s="10">
         <f>IFERROR(C28/E28,0)</f>
-        <v>-3.1818181818181787E-2</v>
+        <v>-6.6666666666666596E-2</v>
       </c>
       <c r="K28" s="10">
         <f>IFERROR(D28/E28,0)</f>
-        <v>-6.3636363636363187E-3</v>
+        <v>-1.3333333333333313E-2</v>
       </c>
       <c r="L28" s="10" t="str">
         <f>LEFT(B28,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N28">
         <f t="shared" si="1"/>
-        <v>-0.69999999999999929</v>
+        <v>-1.3999999999999986</v>
       </c>
       <c r="O28">
         <f t="shared" si="7"/>
-        <v>-0.13999999999999901</v>
+        <v>-0.27999999999999958</v>
       </c>
       <c r="P28">
         <f t="shared" si="8"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q28">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
-        <v>81</v>
+      <c r="B29" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="C29">
-        <v>-0.70000000000000107</v>
+        <v>-1.6</v>
       </c>
       <c r="D29">
-        <v>-0.14000000000000012</v>
+        <v>-0.32</v>
       </c>
       <c r="E29">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29" s="7">
         <f>IFERROR((F29/E29)*100,0)</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J29" s="10">
         <f>IFERROR(C29/E29,0)</f>
-        <v>-5.8333333333333424E-2</v>
+        <v>-1.6</v>
       </c>
       <c r="K29" s="10">
         <f>IFERROR(D29/E29,0)</f>
-        <v>-1.1666666666666678E-2</v>
+        <v>-0.32</v>
       </c>
       <c r="L29" s="10" t="str">
         <f>LEFT(B29,3)</f>
@@ -7981,19 +8197,19 @@
       </c>
       <c r="N29">
         <f t="shared" si="1"/>
-        <v>-0.70000000000000107</v>
+        <v>-1.6</v>
       </c>
       <c r="O29">
         <f t="shared" si="7"/>
-        <v>-0.14000000000000012</v>
+        <v>-0.32</v>
       </c>
       <c r="P29">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Q29">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R29">
         <f t="shared" si="10"/>
@@ -8001,7 +8217,7 @@
       </c>
       <c r="S29">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
@@ -8009,19 +8225,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C30">
-        <v>-1.6</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="D30">
-        <v>-0.32</v>
+        <v>-0.38</v>
       </c>
       <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30">
         <v>1</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -8031,35 +8247,35 @@
       </c>
       <c r="I30" s="7">
         <f>IFERROR((F30/E30)*100,0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J30" s="10">
         <f>IFERROR(C30/E30,0)</f>
-        <v>-1.6</v>
+        <v>-0.95000000000000007</v>
       </c>
       <c r="K30" s="10">
         <f>IFERROR(D30/E30,0)</f>
-        <v>-0.32</v>
+        <v>-0.19</v>
       </c>
       <c r="L30" s="10" t="str">
         <f>LEFT(B30,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N30">
         <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>-1.9000000000000001</v>
       </c>
       <c r="O30">
         <f t="shared" si="7"/>
-        <v>-0.32</v>
+        <v>-0.38</v>
       </c>
       <c r="P30">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30">
         <f t="shared" si="10"/>
@@ -8074,58 +8290,58 @@
       <c r="A31">
         <v>35</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>144</v>
+      <c r="B31" t="s">
+        <v>69</v>
       </c>
       <c r="C31">
-        <v>-1.9</v>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="D31">
-        <v>-0.38000000000000012</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="E31">
+        <v>5</v>
+      </c>
+      <c r="F31">
         <v>3</v>
       </c>
-      <c r="F31">
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
         <v>2</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>1</v>
       </c>
       <c r="I31" s="7">
         <f>IFERROR((F31/E31)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>60</v>
       </c>
       <c r="J31" s="10">
         <f>IFERROR(C31/E31,0)</f>
-        <v>-0.6333333333333333</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="K31" s="10">
         <f>IFERROR(D31/E31,0)</f>
-        <v>-0.12666666666666671</v>
+        <v>-0.11600000000000002</v>
       </c>
       <c r="L31" s="10" t="str">
         <f>LEFT(B31,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N31">
         <f t="shared" si="1"/>
-        <v>-1.9</v>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="O31">
         <f t="shared" si="7"/>
-        <v>-0.38000000000000012</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="P31">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R31">
         <f t="shared" si="10"/>
@@ -8133,65 +8349,65 @@
       </c>
       <c r="S31">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>36</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>89</v>
+      <c r="B32" t="s">
+        <v>72</v>
       </c>
       <c r="C32">
-        <v>-1.9000000000000001</v>
+        <v>-3.0999999999999983</v>
       </c>
       <c r="D32">
-        <v>-0.38</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I32" s="7">
         <f>IFERROR((F32/E32)*100,0)</f>
-        <v>50</v>
+        <v>38.461538461538467</v>
       </c>
       <c r="J32" s="10">
         <f>IFERROR(C32/E32,0)</f>
-        <v>-0.95000000000000007</v>
+        <v>-0.23846153846153834</v>
       </c>
       <c r="K32" s="10">
         <f>IFERROR(D32/E32,0)</f>
-        <v>-0.19</v>
+        <v>-4.7692307692307687E-2</v>
       </c>
       <c r="L32" s="10" t="str">
         <f>LEFT(B32,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N32">
         <f t="shared" si="1"/>
-        <v>-1.9000000000000001</v>
+        <v>-3.0999999999999983</v>
       </c>
       <c r="O32">
         <f t="shared" si="7"/>
-        <v>-0.38</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="P32">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Q32">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R32">
         <f t="shared" si="10"/>
@@ -8199,7 +8415,7 @@
       </c>
       <c r="S32">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
@@ -8207,37 +8423,37 @@
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C33">
-        <v>-2.9000000000000004</v>
+        <v>-3.0999999999999996</v>
       </c>
       <c r="D33">
-        <v>-0.58000000000000007</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>3</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>2</v>
       </c>
       <c r="I33" s="7">
         <f>IFERROR((F33/E33)*100,0)</f>
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="J33" s="10">
         <f>IFERROR(C33/E33,0)</f>
-        <v>-0.58000000000000007</v>
+        <v>-0.77499999999999991</v>
       </c>
       <c r="K33" s="10">
         <f>IFERROR(D33/E33,0)</f>
-        <v>-0.11600000000000002</v>
+        <v>-0.15499999999999997</v>
       </c>
       <c r="L33" s="10" t="str">
         <f>LEFT(B33,3)</f>
@@ -8245,19 +8461,19 @@
       </c>
       <c r="N33">
         <f t="shared" si="1"/>
-        <v>-2.9000000000000004</v>
+        <v>-3.0999999999999996</v>
       </c>
       <c r="O33">
         <f t="shared" si="7"/>
-        <v>-0.58000000000000007</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="P33">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q33">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R33">
         <f t="shared" si="10"/>
@@ -8265,45 +8481,45 @@
       </c>
       <c r="S33">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>38</v>
       </c>
-      <c r="B34" t="s">
-        <v>72</v>
+      <c r="B34" s="8" t="s">
+        <v>133</v>
       </c>
       <c r="C34">
-        <v>-3.0999999999999983</v>
+        <v>-3.3</v>
       </c>
       <c r="D34">
-        <v>-0.61999999999999988</v>
+        <v>-0.6599999999999997</v>
       </c>
       <c r="E34">
         <v>13</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I34" s="7">
         <f>IFERROR((F34/E34)*100,0)</f>
-        <v>38.461538461538467</v>
+        <v>46.153846153846153</v>
       </c>
       <c r="J34" s="10">
         <f>IFERROR(C34/E34,0)</f>
-        <v>-0.23846153846153834</v>
+        <v>-0.25384615384615383</v>
       </c>
       <c r="K34" s="10">
         <f>IFERROR(D34/E34,0)</f>
-        <v>-4.7692307692307687E-2</v>
+        <v>-5.0769230769230747E-2</v>
       </c>
       <c r="L34" s="10" t="str">
         <f>LEFT(B34,3)</f>
@@ -8311,11 +8527,11 @@
       </c>
       <c r="N34">
         <f t="shared" si="1"/>
-        <v>-3.0999999999999983</v>
+        <v>-3.3</v>
       </c>
       <c r="O34">
         <f t="shared" si="7"/>
-        <v>-0.61999999999999988</v>
+        <v>-0.6599999999999997</v>
       </c>
       <c r="P34">
         <f t="shared" si="8"/>
@@ -8323,7 +8539,7 @@
       </c>
       <c r="Q34">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <f t="shared" si="10"/>
@@ -8331,57 +8547,57 @@
       </c>
       <c r="S34">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>39</v>
       </c>
-      <c r="B35" t="s">
-        <v>87</v>
+      <c r="B35" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="C35">
-        <v>-3.0999999999999996</v>
+        <v>-4.6999999999999993</v>
       </c>
       <c r="D35">
-        <v>-0.61999999999999988</v>
+        <v>-0.94000000000000006</v>
       </c>
       <c r="E35">
         <v>4</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" s="7">
         <f>IFERROR((F35/E35)*100,0)</f>
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J35" s="10">
         <f>IFERROR(C35/E35,0)</f>
-        <v>-0.77499999999999991</v>
+        <v>-1.1749999999999998</v>
       </c>
       <c r="K35" s="10">
         <f>IFERROR(D35/E35,0)</f>
-        <v>-0.15499999999999997</v>
+        <v>-0.23500000000000001</v>
       </c>
       <c r="L35" s="10" t="str">
         <f>LEFT(B35,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N35">
         <f t="shared" si="1"/>
-        <v>-3.0999999999999996</v>
+        <v>-4.6999999999999993</v>
       </c>
       <c r="O35">
         <f t="shared" si="7"/>
-        <v>-0.61999999999999988</v>
+        <v>-0.94000000000000006</v>
       </c>
       <c r="P35">
         <f t="shared" si="8"/>
@@ -8389,7 +8605,7 @@
       </c>
       <c r="Q35">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35">
         <f t="shared" si="10"/>
@@ -8397,7 +8613,7 @@
       </c>
       <c r="S35">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
@@ -8603,19 +8819,19 @@
         <v>33</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="C39">
-        <v>-6</v>
+        <v>-5.8000000000000007</v>
       </c>
       <c r="D39">
-        <v>-1.2</v>
+        <v>-1.1600000000000001</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -8625,35 +8841,35 @@
       </c>
       <c r="I39" s="7">
         <f>IFERROR((F39/E39)*100,0)</f>
-        <v>0</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J39" s="10">
         <f>IFERROR(C39/E39,0)</f>
-        <v>-6</v>
+        <v>-1.9333333333333336</v>
       </c>
       <c r="K39" s="10">
         <f>IFERROR(D39/E39,0)</f>
-        <v>-1.2</v>
+        <v>-0.38666666666666671</v>
       </c>
       <c r="L39" s="10" t="str">
         <f>LEFT(B39,3)</f>
-        <v>LEG</v>
+        <v>WEG</v>
       </c>
       <c r="N39">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-5.8000000000000007</v>
       </c>
       <c r="O39">
         <f t="shared" si="7"/>
-        <v>-1.2</v>
+        <v>-1.1600000000000001</v>
       </c>
       <c r="P39">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q39">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R39">
         <f t="shared" si="10"/>
@@ -8668,62 +8884,62 @@
       <c r="A40">
         <v>34</v>
       </c>
-      <c r="B40" t="s">
-        <v>90</v>
+      <c r="B40" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C40">
-        <v>-6.2</v>
+        <v>-6</v>
       </c>
       <c r="D40">
-        <v>-1.24</v>
+        <v>-1.2</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40" s="7">
         <f>IFERROR((F40/E40)*100,0)</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J40" s="10">
         <f>IFERROR(C40/E40,0)</f>
-        <v>-1.24</v>
+        <v>-6</v>
       </c>
       <c r="K40" s="10">
         <f>IFERROR(D40/E40,0)</f>
-        <v>-0.248</v>
+        <v>-1.2</v>
       </c>
       <c r="L40" s="10" t="str">
         <f>LEFT(B40,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N40">
         <f t="shared" si="1"/>
-        <v>-6.2</v>
+        <v>-6</v>
       </c>
       <c r="O40">
         <f t="shared" si="7"/>
-        <v>-1.24</v>
+        <v>-1.2</v>
       </c>
       <c r="P40">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q40">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R40">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40">
         <f t="shared" si="11"/>
@@ -8734,38 +8950,38 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>145</v>
+      <c r="B41" t="s">
+        <v>90</v>
       </c>
       <c r="C41">
-        <v>-7.4999999999999991</v>
+        <v>-6.2</v>
       </c>
       <c r="D41">
-        <v>-1.4999999999999998</v>
+        <v>-1.24</v>
       </c>
       <c r="E41">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I41" s="7">
         <f>IFERROR((F41/E41)*100,0)</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J41" s="10">
         <f>IFERROR(C41/E41,0)</f>
-        <v>-0.93749999999999989</v>
+        <v>-1.24</v>
       </c>
       <c r="K41" s="10">
         <f>IFERROR(D41/E41,0)</f>
-        <v>-0.18749999999999997</v>
+        <v>-0.248</v>
       </c>
       <c r="L41" s="10" t="str">
         <f>LEFT(B41,3)</f>
@@ -8773,65 +8989,65 @@
       </c>
       <c r="N41">
         <f t="shared" si="1"/>
-        <v>-7.4999999999999991</v>
+        <v>-6.2</v>
       </c>
       <c r="O41">
         <f t="shared" si="7"/>
-        <v>-1.4999999999999998</v>
+        <v>-1.24</v>
       </c>
       <c r="P41">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q41">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R41">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>75</v>
+      <c r="B42" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="C42">
-        <v>-7.5</v>
+        <v>-7.4999999999999991</v>
       </c>
       <c r="D42">
-        <v>-1.5</v>
+        <v>-1.4999999999999998</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I42" s="7">
         <f>IFERROR((F42/E42)*100,0)</f>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J42" s="10">
         <f>IFERROR(C42/E42,0)</f>
-        <v>-1.5</v>
+        <v>-0.93749999999999989</v>
       </c>
       <c r="K42" s="10">
         <f>IFERROR(D42/E42,0)</f>
-        <v>-0.3</v>
+        <v>-0.18749999999999997</v>
       </c>
       <c r="L42" s="10" t="str">
         <f>LEFT(B42,3)</f>
@@ -8839,19 +9055,19 @@
       </c>
       <c r="N42">
         <f t="shared" si="1"/>
-        <v>-7.5</v>
+        <v>-7.4999999999999991</v>
       </c>
       <c r="O42">
         <f t="shared" si="7"/>
-        <v>-1.5</v>
+        <v>-1.4999999999999998</v>
       </c>
       <c r="P42">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q42">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R42">
         <f t="shared" si="10"/>
@@ -8859,7 +9075,7 @@
       </c>
       <c r="S42">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
@@ -8867,7 +9083,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="C43">
         <v>-7.5</v>
@@ -8879,17 +9095,17 @@
         <v>5</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I43" s="7">
         <f>IFERROR((F43/E43)*100,0)</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J43" s="10">
         <f>IFERROR(C43/E43,0)</f>
@@ -8901,7 +9117,7 @@
       </c>
       <c r="L43" s="10" t="str">
         <f>LEFT(B43,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N43">
         <f t="shared" si="1"/>
@@ -8917,7 +9133,7 @@
       </c>
       <c r="Q43">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R43">
         <f t="shared" si="10"/>
@@ -8925,53 +9141,53 @@
       </c>
       <c r="S43">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>84</v>
+      <c r="B44" t="s">
+        <v>98</v>
       </c>
       <c r="C44">
-        <v>-7.5000000000000009</v>
+        <v>-7.5</v>
       </c>
       <c r="D44">
         <v>-1.5</v>
       </c>
       <c r="E44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" s="7">
         <f>IFERROR((F44/E44)*100,0)</f>
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J44" s="10">
         <f>IFERROR(C44/E44,0)</f>
-        <v>-1.2500000000000002</v>
+        <v>-1.5</v>
       </c>
       <c r="K44" s="10">
         <f>IFERROR(D44/E44,0)</f>
-        <v>-0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="L44" s="10" t="str">
         <f>LEFT(B44,3)</f>
-        <v>WEG</v>
+        <v>LEG</v>
       </c>
       <c r="N44">
         <f t="shared" si="1"/>
-        <v>-7.5000000000000009</v>
+        <v>-7.5</v>
       </c>
       <c r="O44">
         <f t="shared" si="7"/>
@@ -8979,11 +9195,11 @@
       </c>
       <c r="P44">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q44">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R44">
         <f t="shared" si="10"/>
@@ -8991,65 +9207,65 @@
       </c>
       <c r="S44">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
-        <v>93</v>
+      <c r="B45" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="C45">
-        <v>-9.1</v>
+        <v>-7.5000000000000009</v>
       </c>
       <c r="D45">
-        <v>-1.82</v>
+        <v>-1.5</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I45" s="7">
         <f>IFERROR((F45/E45)*100,0)</f>
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J45" s="10">
         <f>IFERROR(C45/E45,0)</f>
-        <v>-1.8199999999999998</v>
+        <v>-1.2500000000000002</v>
       </c>
       <c r="K45" s="10">
         <f>IFERROR(D45/E45,0)</f>
-        <v>-0.36399999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="L45" s="10" t="str">
         <f>LEFT(B45,3)</f>
-        <v>PEG</v>
+        <v>WEG</v>
       </c>
       <c r="N45">
         <f t="shared" si="1"/>
-        <v>-9.1</v>
+        <v>-7.5000000000000009</v>
       </c>
       <c r="O45">
         <f t="shared" si="7"/>
-        <v>-1.82</v>
+        <v>-1.5</v>
       </c>
       <c r="P45">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q45">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R45">
         <f t="shared" si="10"/>
@@ -9057,7 +9273,7 @@
       </c>
       <c r="S45">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -9065,57 +9281,57 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C46">
-        <v>-9.4000000000000021</v>
+        <v>-9.1</v>
       </c>
       <c r="D46">
-        <v>-1.879999999999999</v>
+        <v>-1.82</v>
       </c>
       <c r="E46">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F46">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I46" s="7">
         <f>IFERROR((F46/E46)*100,0)</f>
-        <v>47.058823529411761</v>
+        <v>20</v>
       </c>
       <c r="J46" s="10">
         <f>IFERROR(C46/E46,0)</f>
-        <v>-0.55294117647058838</v>
+        <v>-1.8199999999999998</v>
       </c>
       <c r="K46" s="10">
         <f>IFERROR(D46/E46,0)</f>
-        <v>-0.11058823529411758</v>
+        <v>-0.36399999999999999</v>
       </c>
       <c r="L46" s="10" t="str">
         <f>LEFT(B46,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N46">
         <f t="shared" si="1"/>
-        <v>-9.4000000000000021</v>
+        <v>-9.1</v>
       </c>
       <c r="O46">
         <f t="shared" si="7"/>
-        <v>-1.879999999999999</v>
+        <v>-1.82</v>
       </c>
       <c r="P46">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Q46">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R46">
         <f t="shared" si="10"/>
@@ -9123,7 +9339,7 @@
       </c>
       <c r="S46">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
@@ -9131,57 +9347,57 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C47">
-        <v>-9.6999999999999993</v>
+        <v>-9.4000000000000021</v>
       </c>
       <c r="D47">
-        <v>-1.9400000000000002</v>
+        <v>-1.879999999999999</v>
       </c>
       <c r="E47">
+        <v>17</v>
+      </c>
+      <c r="F47">
         <v>8</v>
       </c>
-      <c r="F47">
-        <v>3</v>
-      </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I47" s="7">
         <f>IFERROR((F47/E47)*100,0)</f>
-        <v>37.5</v>
+        <v>47.058823529411761</v>
       </c>
       <c r="J47" s="10">
         <f>IFERROR(C47/E47,0)</f>
-        <v>-1.2124999999999999</v>
+        <v>-0.55294117647058838</v>
       </c>
       <c r="K47" s="10">
         <f>IFERROR(D47/E47,0)</f>
-        <v>-0.24250000000000002</v>
+        <v>-0.11058823529411758</v>
       </c>
       <c r="L47" s="10" t="str">
         <f>LEFT(B47,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N47">
         <f t="shared" si="1"/>
-        <v>-9.6999999999999993</v>
+        <v>-9.4000000000000021</v>
       </c>
       <c r="O47">
         <f t="shared" si="7"/>
-        <v>-1.9400000000000002</v>
+        <v>-1.879999999999999</v>
       </c>
       <c r="P47">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Q47">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R47">
         <f t="shared" si="10"/>
@@ -9189,45 +9405,45 @@
       </c>
       <c r="S47">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>128</v>
+      <c r="B48" t="s">
+        <v>67</v>
       </c>
       <c r="C48">
-        <v>-10.199999999999999</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="D48">
-        <v>-2.04</v>
+        <v>-1.9400000000000002</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I48" s="7">
         <f>IFERROR((F48/E48)*100,0)</f>
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="J48" s="10">
         <f>IFERROR(C48/E48,0)</f>
-        <v>-2.5499999999999998</v>
+        <v>-1.2124999999999999</v>
       </c>
       <c r="K48" s="10">
         <f>IFERROR(D48/E48,0)</f>
-        <v>-0.51</v>
+        <v>-0.24250000000000002</v>
       </c>
       <c r="L48" s="10" t="str">
         <f>LEFT(B48,3)</f>
@@ -9235,19 +9451,19 @@
       </c>
       <c r="N48">
         <f t="shared" si="1"/>
-        <v>-10.199999999999999</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="O48">
         <f t="shared" si="7"/>
-        <v>-2.04</v>
+        <v>-1.9400000000000002</v>
       </c>
       <c r="P48">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q48">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R48">
         <f t="shared" ref="R48:R53" si="12">G48+Y48</f>
@@ -9255,7 +9471,7 @@
       </c>
       <c r="S48">
         <f t="shared" ref="S48:S53" si="13">H48+Z48</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
@@ -9263,49 +9479,49 @@
         <v>48</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C49">
-        <v>-11.399999999999997</v>
+        <v>-10.199999999999999</v>
       </c>
       <c r="D49">
-        <v>-2.2799999999999998</v>
+        <v>-2.04</v>
       </c>
       <c r="E49">
         <v>4</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I49" s="7">
         <f>IFERROR((F49/E49)*100,0)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J49" s="10">
         <f>IFERROR(C49/E49,0)</f>
-        <v>-2.8499999999999992</v>
+        <v>-2.5499999999999998</v>
       </c>
       <c r="K49" s="10">
         <f>IFERROR(D49/E49,0)</f>
-        <v>-0.56999999999999995</v>
+        <v>-0.51</v>
       </c>
       <c r="L49" s="10" t="str">
         <f>LEFT(B49,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N49">
         <f t="shared" si="1"/>
-        <v>-11.399999999999997</v>
+        <v>-10.199999999999999</v>
       </c>
       <c r="O49">
         <f t="shared" si="7"/>
-        <v>-2.2799999999999998</v>
+        <v>-2.04</v>
       </c>
       <c r="P49">
         <f t="shared" si="8"/>
@@ -9313,7 +9529,7 @@
       </c>
       <c r="Q49">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R49">
         <f t="shared" si="12"/>
@@ -9321,7 +9537,7 @@
       </c>
       <c r="S49">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
@@ -9329,57 +9545,57 @@
         <v>49</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="C50">
-        <v>-11.4</v>
+        <v>-11.199999999999998</v>
       </c>
       <c r="D50">
-        <v>-2.2800000000000002</v>
+        <v>-2.2399999999999998</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" s="7">
         <f>IFERROR((F50/E50)*100,0)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J50" s="10">
         <f>IFERROR(C50/E50,0)</f>
-        <v>-11.4</v>
+        <v>-2.2399999999999993</v>
       </c>
       <c r="K50" s="10">
         <f>IFERROR(D50/E50,0)</f>
-        <v>-2.2800000000000002</v>
+        <v>-0.44799999999999995</v>
       </c>
       <c r="L50" s="10" t="str">
         <f>LEFT(B50,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N50">
         <f t="shared" si="1"/>
-        <v>-11.4</v>
+        <v>-11.199999999999998</v>
       </c>
       <c r="O50">
         <f t="shared" si="7"/>
-        <v>-2.2800000000000002</v>
+        <v>-2.2399999999999998</v>
       </c>
       <c r="P50">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q50">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R50">
         <f t="shared" si="12"/>
@@ -9387,7 +9603,7 @@
       </c>
       <c r="S50">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
@@ -9395,16 +9611,16 @@
         <v>50</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="C51">
-        <v>-12</v>
+        <v>-11.4</v>
       </c>
       <c r="D51">
-        <v>-2.4</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -9413,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" s="7">
         <f>IFERROR((F51/E51)*100,0)</f>
@@ -9421,11 +9637,11 @@
       </c>
       <c r="J51" s="10">
         <f>IFERROR(C51/E51,0)</f>
-        <v>-6</v>
+        <v>-11.4</v>
       </c>
       <c r="K51" s="10">
         <f>IFERROR(D51/E51,0)</f>
-        <v>-1.2</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="L51" s="10" t="str">
         <f>LEFT(B51,3)</f>
@@ -9433,15 +9649,15 @@
       </c>
       <c r="N51">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>-11.4</v>
       </c>
       <c r="O51">
         <f t="shared" si="7"/>
-        <v>-2.4</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="P51">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q51">
         <f t="shared" si="9"/>
@@ -9453,7 +9669,7 @@
       </c>
       <c r="S51">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
@@ -9461,7 +9677,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C52">
         <v>-12</v>
@@ -9470,32 +9686,32 @@
         <v>-2.4</v>
       </c>
       <c r="E52">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
         <v>2</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>3</v>
       </c>
       <c r="I52" s="7">
         <f>IFERROR((F52/E52)*100,0)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J52" s="10">
         <f>IFERROR(C52/E52,0)</f>
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="K52" s="10">
         <f>IFERROR(D52/E52,0)</f>
-        <v>-0.48</v>
+        <v>-1.2</v>
       </c>
       <c r="L52" s="10" t="str">
         <f>LEFT(B52,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N52">
         <f t="shared" si="1"/>
@@ -9507,11 +9723,11 @@
       </c>
       <c r="P52">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q52">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R52">
         <f t="shared" si="12"/>
@@ -9519,7 +9735,7 @@
       </c>
       <c r="S52">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
@@ -9527,57 +9743,57 @@
         <v>52</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="C53">
-        <v>-12.5</v>
+        <v>-12</v>
       </c>
       <c r="D53">
-        <v>-2.4999999999999996</v>
+        <v>-2.4</v>
       </c>
       <c r="E53">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I53" s="7">
         <f>IFERROR((F53/E53)*100,0)</f>
-        <v>45.454545454545453</v>
+        <v>40</v>
       </c>
       <c r="J53" s="10">
         <f>IFERROR(C53/E53,0)</f>
-        <v>-1.1363636363636365</v>
+        <v>-2.4</v>
       </c>
       <c r="K53" s="10">
         <f>IFERROR(D53/E53,0)</f>
-        <v>-0.22727272727272724</v>
+        <v>-0.48</v>
       </c>
       <c r="L53" s="10" t="str">
         <f>LEFT(B53,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N53">
         <f t="shared" si="1"/>
-        <v>-12.5</v>
+        <v>-12</v>
       </c>
       <c r="O53">
         <f t="shared" si="7"/>
-        <v>-2.4999999999999996</v>
+        <v>-2.4</v>
       </c>
       <c r="P53">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q53">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R53">
         <f t="shared" si="12"/>
@@ -9585,7 +9801,7 @@
       </c>
       <c r="S53">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
@@ -9791,37 +10007,37 @@
         <v>56</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="C57">
-        <v>-15.099999999999998</v>
+        <v>-14.899999999999999</v>
       </c>
       <c r="D57">
-        <v>-3.0200000000000005</v>
+        <v>-2.9799999999999995</v>
       </c>
       <c r="E57">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I57" s="7">
         <f>IFERROR((F57/E57)*100,0)</f>
-        <v>0</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J57" s="10">
         <f>IFERROR(C57/E57,0)</f>
-        <v>-2.5166666666666662</v>
+        <v>-4.9666666666666659</v>
       </c>
       <c r="K57" s="10">
         <f>IFERROR(D57/E57,0)</f>
-        <v>-0.50333333333333341</v>
+        <v>-0.99333333333333318</v>
       </c>
       <c r="L57" s="10" t="str">
         <f>LEFT(B57,3)</f>
@@ -9829,27 +10045,27 @@
       </c>
       <c r="N57">
         <f t="shared" ref="N57:N61" si="20">C57+U57</f>
-        <v>-15.099999999999998</v>
+        <v>-14.899999999999999</v>
       </c>
       <c r="O57">
         <f t="shared" ref="O57:O61" si="21">D57+V57</f>
-        <v>-3.0200000000000005</v>
+        <v>-2.9799999999999995</v>
       </c>
       <c r="P57">
         <f t="shared" ref="P57:P61" si="22">E57+W57</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q57">
         <f t="shared" ref="Q57:Q61" si="23">F57+X57</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57">
         <f t="shared" ref="R57:R61" si="24">G57+Y57</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57">
         <f t="shared" ref="S57:S61" si="25">H57+Z57</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
@@ -9857,25 +10073,25 @@
         <v>57</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C58">
-        <v>-19.5</v>
+        <v>-15.099999999999998</v>
       </c>
       <c r="D58">
-        <v>-3.9</v>
+        <v>-3.0200000000000005</v>
       </c>
       <c r="E58">
+        <v>6</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
         <v>1</v>
       </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
       <c r="H58">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I58" s="7">
         <f>IFERROR((F58/E58)*100,0)</f>
@@ -9883,11 +10099,11 @@
       </c>
       <c r="J58" s="10">
         <f>IFERROR(C58/E58,0)</f>
-        <v>-19.5</v>
+        <v>-2.5166666666666662</v>
       </c>
       <c r="K58" s="10">
         <f>IFERROR(D58/E58,0)</f>
-        <v>-3.9</v>
+        <v>-0.50333333333333341</v>
       </c>
       <c r="L58" s="10" t="str">
         <f>LEFT(B58,3)</f>
@@ -9895,15 +10111,15 @@
       </c>
       <c r="N58">
         <f t="shared" si="20"/>
-        <v>-19.5</v>
+        <v>-15.099999999999998</v>
       </c>
       <c r="O58">
         <f t="shared" si="21"/>
-        <v>-3.9</v>
+        <v>-3.0200000000000005</v>
       </c>
       <c r="P58">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q58">
         <f t="shared" si="23"/>
@@ -9911,11 +10127,11 @@
       </c>
       <c r="R58">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
@@ -9923,57 +10139,57 @@
         <v>58</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C59">
-        <v>-20.100000000000001</v>
+        <v>-19.5</v>
       </c>
       <c r="D59">
-        <v>-4.0200000000000005</v>
+        <v>-3.9</v>
       </c>
       <c r="E59">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
       <c r="H59">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I59" s="7">
         <f>IFERROR((F59/E59)*100,0)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J59" s="10">
         <f>IFERROR(C59/E59,0)</f>
-        <v>-2.0100000000000002</v>
+        <v>-19.5</v>
       </c>
       <c r="K59" s="10">
         <f>IFERROR(D59/E59,0)</f>
-        <v>-0.40200000000000002</v>
+        <v>-3.9</v>
       </c>
       <c r="L59" s="10" t="str">
         <f>LEFT(B59,3)</f>
-        <v>VEG</v>
+        <v>UEG</v>
       </c>
       <c r="N59">
         <f t="shared" si="20"/>
-        <v>-20.100000000000001</v>
+        <v>-19.5</v>
       </c>
       <c r="O59">
         <f t="shared" si="21"/>
-        <v>-4.0200000000000005</v>
+        <v>-3.9</v>
       </c>
       <c r="P59">
         <f t="shared" si="22"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q59">
         <f t="shared" si="23"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R59">
         <f t="shared" si="24"/>
@@ -9981,65 +10197,65 @@
       </c>
       <c r="S59">
         <f t="shared" si="25"/>
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
-        <v>57</v>
+      <c r="B60" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="C60">
-        <v>-22.700000000000003</v>
+        <v>-19.600000000000001</v>
       </c>
       <c r="D60">
-        <v>-4.5399999999999991</v>
+        <v>-3.9199999999999995</v>
       </c>
       <c r="E60">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F60">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I60" s="7">
         <f>IFERROR((F60/E60)*100,0)</f>
-        <v>47.368421052631575</v>
+        <v>41.666666666666671</v>
       </c>
       <c r="J60" s="10">
         <f>IFERROR(C60/E60,0)</f>
-        <v>-1.1947368421052633</v>
+        <v>-1.6333333333333335</v>
       </c>
       <c r="K60" s="10">
         <f>IFERROR(D60/E60,0)</f>
-        <v>-0.23894736842105258</v>
+        <v>-0.32666666666666661</v>
       </c>
       <c r="L60" s="10" t="str">
         <f>LEFT(B60,3)</f>
-        <v>VEG</v>
+        <v>PEG</v>
       </c>
       <c r="N60">
         <f t="shared" si="20"/>
-        <v>-22.700000000000003</v>
+        <v>-19.600000000000001</v>
       </c>
       <c r="O60">
         <f t="shared" si="21"/>
-        <v>-4.5399999999999991</v>
+        <v>-3.9199999999999995</v>
       </c>
       <c r="P60">
         <f t="shared" si="22"/>
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q60">
         <f t="shared" si="23"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R60">
         <f t="shared" si="24"/>
@@ -10047,27 +10263,27 @@
       </c>
       <c r="S60">
         <f t="shared" si="25"/>
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
-        <v>95</v>
+      <c r="B61" s="8" t="s">
+        <v>129</v>
       </c>
       <c r="C61">
-        <v>-25.799999999999997</v>
+        <v>-20.100000000000001</v>
       </c>
       <c r="D61">
-        <v>-5.16</v>
+        <v>-4.0200000000000005</v>
       </c>
       <c r="E61">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -10077,35 +10293,35 @@
       </c>
       <c r="I61" s="7">
         <f>IFERROR((F61/E61)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>20</v>
       </c>
       <c r="J61" s="10">
         <f>IFERROR(C61/E61,0)</f>
-        <v>-2.15</v>
+        <v>-2.0100000000000002</v>
       </c>
       <c r="K61" s="10">
         <f>IFERROR(D61/E61,0)</f>
-        <v>-0.43</v>
+        <v>-0.40200000000000002</v>
       </c>
       <c r="L61" s="10" t="str">
         <f>LEFT(B61,3)</f>
-        <v>PEG</v>
+        <v>VEG</v>
       </c>
       <c r="N61">
         <f t="shared" si="20"/>
-        <v>-25.799999999999997</v>
+        <v>-20.100000000000001</v>
       </c>
       <c r="O61">
         <f t="shared" si="21"/>
-        <v>-5.16</v>
+        <v>-4.0200000000000005</v>
       </c>
       <c r="P61">
         <f t="shared" si="22"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q61">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R61">
         <f t="shared" si="24"/>
@@ -10121,49 +10337,49 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C62">
-        <v>-42.199999999999996</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="D62">
-        <v>-8.44</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="E62">
         <v>19</v>
       </c>
       <c r="F62">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62">
         <v>10</v>
       </c>
       <c r="I62" s="7">
         <f>IFERROR((F62/E62)*100,0)</f>
-        <v>42.105263157894733</v>
+        <v>47.368421052631575</v>
       </c>
       <c r="J62" s="10">
         <f>IFERROR(C62/E62,0)</f>
-        <v>-2.2210526315789472</v>
+        <v>-1.1947368421052633</v>
       </c>
       <c r="K62" s="10">
         <f>IFERROR(D62/E62,0)</f>
-        <v>-0.44421052631578944</v>
+        <v>-0.23894736842105258</v>
       </c>
       <c r="L62" s="10" t="str">
         <f>LEFT(B62,3)</f>
-        <v>PEG</v>
+        <v>VEG</v>
       </c>
       <c r="N62">
         <f t="shared" ref="N62" si="26">C62+U62</f>
-        <v>-42.199999999999996</v>
+        <v>-22.700000000000003</v>
       </c>
       <c r="O62">
         <f t="shared" ref="O62" si="27">D62+V62</f>
-        <v>-8.44</v>
+        <v>-4.5399999999999991</v>
       </c>
       <c r="P62">
         <f t="shared" ref="P62" si="28">E62+W62</f>
@@ -10171,11 +10387,11 @@
       </c>
       <c r="Q62">
         <f t="shared" ref="Q62" si="29">F62+X62</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R62">
         <f t="shared" ref="R62" si="30">G62+Y62</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62">
         <f t="shared" ref="S62" si="31">H62+Z62</f>
@@ -10187,57 +10403,57 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C63">
-        <v>-42.900000000000006</v>
+        <v>-25.799999999999997</v>
       </c>
       <c r="D63">
-        <v>-8.58</v>
+        <v>-5.16</v>
       </c>
       <c r="E63">
+        <v>12</v>
+      </c>
+      <c r="F63">
         <v>4</v>
       </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I63" s="7">
         <f>IFERROR((F63/E63)*100,0)</f>
-        <v>0</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J63" s="10">
         <f>IFERROR(C63/E63,0)</f>
-        <v>-10.725000000000001</v>
+        <v>-2.15</v>
       </c>
       <c r="K63" s="10">
         <f>IFERROR(D63/E63,0)</f>
-        <v>-2.145</v>
+        <v>-0.43</v>
       </c>
       <c r="L63" s="10" t="str">
         <f>LEFT(B63,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N63">
         <f t="shared" ref="N63" si="32">C63+U63</f>
-        <v>-42.900000000000006</v>
+        <v>-25.799999999999997</v>
       </c>
       <c r="O63">
         <f t="shared" ref="O63" si="33">D63+V63</f>
-        <v>-8.58</v>
+        <v>-5.16</v>
       </c>
       <c r="P63">
         <f t="shared" ref="P63" si="34">E63+W63</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q63">
         <f t="shared" ref="Q63" si="35">F63+X63</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R63">
         <f t="shared" ref="R63" si="36">G63+Y63</f>
@@ -10245,87 +10461,205 @@
       </c>
       <c r="S63">
         <f t="shared" ref="S63" si="37">H63+Z63</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>59</v>
+      </c>
+      <c r="C64">
+        <v>-42.199999999999996</v>
+      </c>
+      <c r="D64">
+        <v>-8.44</v>
+      </c>
+      <c r="E64">
+        <v>19</v>
+      </c>
+      <c r="F64">
+        <v>8</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>10</v>
+      </c>
+      <c r="I64" s="7">
+        <f>IFERROR((F64/E64)*100,0)</f>
+        <v>42.105263157894733</v>
+      </c>
+      <c r="J64" s="10">
+        <f>IFERROR(C64/E64,0)</f>
+        <v>-2.2210526315789472</v>
+      </c>
+      <c r="K64" s="10">
+        <f>IFERROR(D64/E64,0)</f>
+        <v>-0.44421052631578944</v>
+      </c>
+      <c r="L64" s="10" t="str">
+        <f>LEFT(B64,3)</f>
+        <v>PEG</v>
+      </c>
+      <c r="N64">
+        <f t="shared" ref="N64:N65" si="38">C64+U64</f>
+        <v>-42.199999999999996</v>
+      </c>
+      <c r="O64">
+        <f t="shared" ref="O64:O65" si="39">D64+V64</f>
+        <v>-8.44</v>
+      </c>
+      <c r="P64">
+        <f t="shared" ref="P64:P65" si="40">E64+W64</f>
+        <v>19</v>
+      </c>
+      <c r="Q64">
+        <f t="shared" ref="Q64:Q65" si="41">F64+X64</f>
+        <v>8</v>
+      </c>
+      <c r="R64">
+        <f t="shared" ref="R64:R65" si="42">G64+Y64</f>
+        <v>1</v>
+      </c>
+      <c r="S64">
+        <f t="shared" ref="S64:S65" si="43">H64+Z64</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65">
+        <v>-42.900000000000006</v>
+      </c>
+      <c r="D65">
+        <v>-8.58</v>
+      </c>
+      <c r="E65">
         <v>4</v>
       </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="8"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
-      <c r="L64" s="10"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B65" s="8"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="10"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>4</v>
+      </c>
+      <c r="I65" s="7">
+        <f>IFERROR((F65/E65)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="10">
+        <f>IFERROR(C65/E65,0)</f>
+        <v>-10.725000000000001</v>
+      </c>
+      <c r="K65" s="10">
+        <f>IFERROR(D65/E65,0)</f>
+        <v>-2.145</v>
+      </c>
+      <c r="L65" s="10" t="str">
+        <f>LEFT(B65,3)</f>
+        <v>LEG</v>
+      </c>
+      <c r="N65">
+        <f t="shared" si="38"/>
+        <v>-42.900000000000006</v>
+      </c>
+      <c r="O65">
+        <f t="shared" si="39"/>
+        <v>-8.58</v>
+      </c>
+      <c r="P65">
+        <f t="shared" si="40"/>
+        <v>4</v>
+      </c>
+      <c r="Q65">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <f t="shared" si="43"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B66" s="8"/>
       <c r="I66" s="7"/>
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
       <c r="L66" s="10"/>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B67" s="8"/>
       <c r="I67" s="7"/>
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
       <c r="L67" s="10"/>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B68" s="8"/>
       <c r="I68" s="7"/>
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
       <c r="L68" s="10"/>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B69" s="8"/>
       <c r="I69" s="7"/>
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B70" s="8"/>
       <c r="I70" s="7"/>
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
       <c r="L70" s="10"/>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B71" s="8"/>
       <c r="I71" s="7"/>
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
       <c r="L71" s="10"/>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B72" s="8"/>
       <c r="I72" s="7"/>
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
       <c r="L72" s="10"/>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B73" s="8"/>
       <c r="I73" s="7"/>
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
       <c r="L73" s="10"/>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B74" s="8"/>
       <c r="I74" s="7"/>
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
       <c r="L74" s="10"/>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B75" s="8"/>
     </row>
   </sheetData>
@@ -10459,48 +10793,48 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B62 B64:B1048576">
-    <cfRule type="containsText" dxfId="27" priority="14" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="41" priority="14" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="13" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="40" priority="13" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="12" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="39" priority="12" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="11" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="38" priority="11" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="10" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="37" priority="10" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="9" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="36" priority="9" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="8" operator="containsText" text="LEG">
+    <cfRule type="containsText" dxfId="35" priority="8" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="LEG">
+    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",B63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="33" priority="2" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="31" priority="4" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",B63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="30" priority="5" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",B63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="6" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",B63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="7" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="28" priority="7" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",B63)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10656,16 +10990,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>131</v>
+      <c r="A3" t="s">
+        <v>65</v>
       </c>
       <c r="B3">
         <f>SUM(H3:AB3)</f>
-        <v>-10.5</v>
+        <v>-10.600000000000001</v>
       </c>
       <c r="C3">
         <f>(B3/$C$1)*100</f>
-        <v>-2.1</v>
+        <v>-2.1200000000000006</v>
       </c>
       <c r="D3">
         <f>COUNTA(H3:AB3)</f>
@@ -10673,7 +11007,7 @@
       </c>
       <c r="E3">
         <f>COUNTIF(H3:AB3, "&gt;0")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <f>COUNTIF(H3:AB3, "=0")</f>
@@ -10681,43 +11015,43 @@
       </c>
       <c r="G3">
         <f>COUNTIF(H3:AB3, "&lt;0")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" s="18">
-        <v>-2.5</v>
+        <v>-19.2</v>
       </c>
       <c r="I3" s="18">
-        <v>-0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J3" s="18">
-        <v>-10.3</v>
+        <v>0.7</v>
       </c>
       <c r="K3" s="18">
-        <v>-2.1</v>
+        <v>-1.6</v>
       </c>
       <c r="L3" s="18">
-        <v>5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>65</v>
+      <c r="A4" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="B4">
         <f>SUM(H4:AB4)</f>
-        <v>-9.9999999999999867E-2</v>
+        <v>-7.6000000000000014</v>
       </c>
       <c r="C4">
         <f>(B4/$C$1)*100</f>
-        <v>-1.9999999999999973E-2</v>
+        <v>-1.5200000000000002</v>
       </c>
       <c r="D4">
         <f>COUNTA(H4:AB4)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <f>COUNTIF(H4:AB4, "&gt;0")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <f>COUNTIF(H4:AB4, "=0")</f>
@@ -10728,32 +11062,26 @@
         <v>2</v>
       </c>
       <c r="H4" s="18">
-        <v>-8.5</v>
+        <v>-11.3</v>
       </c>
       <c r="I4" s="18">
-        <v>8</v>
+        <v>-0.8</v>
       </c>
       <c r="J4" s="18">
-        <v>1.2</v>
-      </c>
-      <c r="K4" s="18">
-        <v>-2.2999999999999998</v>
-      </c>
-      <c r="L4" s="18">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>132</v>
+      <c r="A5" s="8" t="s">
+        <v>148</v>
       </c>
       <c r="B5">
         <f>SUM(H5:AB5)</f>
-        <v>4.5</v>
+        <v>-5.8000000000000007</v>
       </c>
       <c r="C5">
         <f>(B5/$C$1)*100</f>
-        <v>0.89999999999999991</v>
+        <v>-1.1600000000000001</v>
       </c>
       <c r="D5">
         <f>COUNTA(H5:AB5)</f>
@@ -10761,7 +11089,7 @@
       </c>
       <c r="E5">
         <f>COUNTIF(H5:AB5, "&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <f>COUNTIF(H5:AB5, "=0")</f>
@@ -10769,29 +11097,29 @@
       </c>
       <c r="G5">
         <f>COUNTIF(H5:AB5, "&lt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="17">
-        <v>-4.5</v>
-      </c>
-      <c r="I5" s="17">
-        <v>14.5</v>
+        <v>1.2</v>
+      </c>
+      <c r="I5" s="18">
+        <v>2.4</v>
       </c>
       <c r="J5" s="18">
-        <v>-5.5</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B6">
         <f>SUM(H6:AB6)</f>
-        <v>-10</v>
+        <v>-6.8</v>
       </c>
       <c r="C6">
         <f>(B6/$C$1)*100</f>
-        <v>-2</v>
+        <v>-1.3599999999999999</v>
       </c>
       <c r="D6">
         <f>COUNTA(H6:AB6)</f>
@@ -10799,7 +11127,7 @@
       </c>
       <c r="E6">
         <f>COUNTIF(H6:AB6, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <f>COUNTIF(H6:AB6, "=0")</f>
@@ -10807,26 +11135,26 @@
       </c>
       <c r="G6">
         <f>COUNTIF(H6:AB6, "&lt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="17">
-        <v>1.2</v>
-      </c>
-      <c r="I6" s="17">
-        <v>-11.2</v>
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="I6" s="18">
+        <v>-2.7</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>56</v>
+      <c r="A7" s="8" t="s">
+        <v>132</v>
       </c>
       <c r="B7">
         <f>SUM(H7:AB7)</f>
-        <v>-11</v>
+        <v>-9.3999999999999986</v>
       </c>
       <c r="C7">
         <f>(B7/$C$1)*100</f>
-        <v>-2.1999999999999997</v>
+        <v>-1.8799999999999997</v>
       </c>
       <c r="D7">
         <f>COUNTA(H7:AB7)</f>
@@ -10834,7 +11162,7 @@
       </c>
       <c r="E7">
         <f>COUNTIF(H7:AB7, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <f>COUNTIF(H7:AB7, "=0")</f>
@@ -10842,30 +11170,30 @@
       </c>
       <c r="G7">
         <f>COUNTIF(H7:AB7, "&lt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="18">
-        <v>-13</v>
+        <v>-3.3</v>
       </c>
       <c r="I7" s="18">
-        <v>2</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B8">
         <f>SUM(H8:AB8)</f>
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="C8">
         <f>(B8/$C$1)*100</f>
-        <v>0.96</v>
+        <v>1.1199999999999999</v>
       </c>
       <c r="D8">
         <f>COUNTA(H8:AB8)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <f>COUNTIF(H8:AB8, "&gt;0")</f>
@@ -10877,34 +11205,31 @@
       </c>
       <c r="G8">
         <f>COUNTIF(H8:AB8, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H8" s="17">
-        <v>-2.7</v>
-      </c>
-      <c r="I8" s="18">
-        <v>7.5</v>
+        <v>0</v>
+      </c>
+      <c r="H8" s="18">
+        <v>5.6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>140</v>
+      <c r="A9" t="s">
+        <v>56</v>
       </c>
       <c r="B9">
         <f>SUM(H9:AB9)</f>
-        <v>-6.6000000000000005</v>
+        <v>1.9</v>
       </c>
       <c r="C9">
         <f>(B9/$C$1)*100</f>
-        <v>-1.32</v>
+        <v>0.38</v>
       </c>
       <c r="D9">
         <f>COUNTA(H9:AB9)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <f>COUNTIF(H9:AB9, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <f>COUNTIF(H9:AB9, "=0")</f>
@@ -10912,30 +11237,28 @@
       </c>
       <c r="G9">
         <f>COUNTIF(H9:AB9, "&lt;0")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" s="17">
-        <v>-0.4</v>
-      </c>
-      <c r="I9" s="17">
-        <v>-6.2</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="I9" s="15"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>94</v>
+      <c r="A10" s="8" t="s">
+        <v>133</v>
       </c>
       <c r="B10">
         <f>SUM(H10:AB10)</f>
-        <v>-22</v>
+        <v>-3.4</v>
       </c>
       <c r="C10">
         <f>(B10/$C$1)*100</f>
-        <v>-4.3999999999999995</v>
+        <v>-0.67999999999999994</v>
       </c>
       <c r="D10">
         <f>COUNTA(H10:AB10)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <f>COUNTIF(H10:AB10, "&gt;0")</f>
@@ -10947,27 +11270,24 @@
       </c>
       <c r="G10">
         <f>COUNTIF(H10:AB10, "&lt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="17">
-        <v>-2.4</v>
-      </c>
-      <c r="I10" s="17">
-        <v>-19.600000000000001</v>
-      </c>
-      <c r="J10" s="15"/>
+        <v>-3.4</v>
+      </c>
+      <c r="I10" s="15"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="B11">
         <f>SUM(H11:AB11)</f>
-        <v>-3.5</v>
+        <v>-16.399999999999999</v>
       </c>
       <c r="C11">
         <f>(B11/$C$1)*100</f>
-        <v>-0.70000000000000007</v>
+        <v>-3.2799999999999994</v>
       </c>
       <c r="D11">
         <f>COUNTA(H11:AB11)</f>
@@ -10986,20 +11306,20 @@
         <v>1</v>
       </c>
       <c r="H11" s="18">
-        <v>-3.5</v>
+        <v>-16.399999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>127</v>
+      <c r="A12" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="B12">
         <f>SUM(H12:AB12)</f>
-        <v>-1.2</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C12">
         <f>(B12/$C$1)*100</f>
-        <v>-0.24</v>
+        <v>0.98000000000000009</v>
       </c>
       <c r="D12">
         <f>COUNTA(H12:AB12)</f>
@@ -11007,7 +11327,7 @@
       </c>
       <c r="E12">
         <f>COUNTIF(H12:AB12, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <f>COUNTIF(H12:AB12, "=0")</f>
@@ -11015,27 +11335,25 @@
       </c>
       <c r="G12">
         <f>COUNTIF(H12:AB12, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="17">
-        <v>-1.2</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>133</v>
+      <c r="A13" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="B13">
         <f>SUM(H13:AB13)</f>
-        <v>-0.4</v>
+        <v>-7.1</v>
       </c>
       <c r="C13">
         <f>(B13/$C$1)*100</f>
-        <v>-0.08</v>
+        <v>-1.42</v>
       </c>
       <c r="D13">
         <f>COUNTA(H13:AB13)</f>
@@ -11054,20 +11372,20 @@
         <v>1</v>
       </c>
       <c r="H13" s="18">
-        <v>-0.4</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="B14">
         <f>SUM(H14:AB14)</f>
-        <v>-4</v>
+        <v>0.2</v>
       </c>
       <c r="C14">
         <f>(B14/$C$1)*100</f>
-        <v>-0.8</v>
+        <v>0.04</v>
       </c>
       <c r="D14">
         <f>COUNTA(H14:AB14)</f>
@@ -11075,7 +11393,7 @@
       </c>
       <c r="E14">
         <f>COUNTIF(H14:AB14, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <f>COUNTIF(H14:AB14, "=0")</f>
@@ -11083,23 +11401,23 @@
       </c>
       <c r="G14">
         <f>COUNTIF(H14:AB14, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="18">
-        <v>-4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>146</v>
+      <c r="A15" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="B15">
         <f>SUM(H15:AB15)</f>
-        <v>-0.5</v>
+        <v>-2.8</v>
       </c>
       <c r="C15">
         <f>(B15/$C$1)*100</f>
-        <v>-0.1</v>
+        <v>-0.55999999999999994</v>
       </c>
       <c r="D15">
         <f>COUNTA(H15:AB15)</f>
@@ -11118,20 +11436,20 @@
         <v>1</v>
       </c>
       <c r="H15" s="18">
-        <v>-0.5</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>95</v>
+      <c r="A16" t="s">
+        <v>64</v>
       </c>
       <c r="B16">
         <f>SUM(H16:AB16)</f>
-        <v>-8.5</v>
+        <v>-15.4</v>
       </c>
       <c r="C16">
         <f>(B16/$C$1)*100</f>
-        <v>-1.7000000000000002</v>
+        <v>-3.08</v>
       </c>
       <c r="D16">
         <f>COUNTA(H16:AB16)</f>
@@ -11150,20 +11468,20 @@
         <v>1</v>
       </c>
       <c r="H16" s="18">
-        <v>-8.5</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17">
         <f>SUM(H17:AB17)</f>
-        <v>-2.6</v>
+        <v>2.8</v>
       </c>
       <c r="C17">
         <f>(B17/$C$1)*100</f>
-        <v>-0.52</v>
+        <v>0.55999999999999994</v>
       </c>
       <c r="D17">
         <f>COUNTA(H17:AB17)</f>
@@ -11171,7 +11489,7 @@
       </c>
       <c r="E17">
         <f>COUNTIF(H17:AB17, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
         <f>COUNTIF(H17:AB17, "=0")</f>
@@ -11179,23 +11497,23 @@
       </c>
       <c r="G17">
         <f>COUNTIF(H17:AB17, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H17" s="17">
-        <v>-2.6</v>
+        <v>0</v>
+      </c>
+      <c r="H17" s="18">
+        <v>2.8</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>141</v>
+        <v>62</v>
       </c>
       <c r="B18">
         <f>SUM(H18:AB18)</f>
-        <v>7.4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C18">
         <f>(B18/$C$1)*100</f>
-        <v>1.48</v>
+        <v>0.81999999999999984</v>
       </c>
       <c r="D18">
         <f>COUNTA(H18:AB18)</f>
@@ -11214,20 +11532,20 @@
         <v>0</v>
       </c>
       <c r="H18" s="17">
-        <v>7.4</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="B19">
         <f>SUM(H19:AB19)</f>
-        <v>-7.6</v>
+        <v>7.6</v>
       </c>
       <c r="C19">
         <f>(B19/$C$1)*100</f>
-        <v>-1.52</v>
+        <v>1.52</v>
       </c>
       <c r="D19">
         <f>COUNTA(H19:AB19)</f>
@@ -11235,7 +11553,7 @@
       </c>
       <c r="E19">
         <f>COUNTIF(H19:AB19, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <f>COUNTIF(H19:AB19, "=0")</f>
@@ -11243,23 +11561,23 @@
       </c>
       <c r="G19">
         <f>COUNTIF(H19:AB19, "&lt;0")</f>
-        <v>1</v>
-      </c>
-      <c r="H19" s="17">
-        <v>-7.6</v>
+        <v>0</v>
+      </c>
+      <c r="H19" s="18">
+        <v>7.6</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>144</v>
+      <c r="A20" s="8" t="s">
+        <v>147</v>
       </c>
       <c r="B20">
         <f>SUM(H20:AB20)</f>
-        <v>1.1000000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="C20">
         <f>(B20/$C$1)*100</f>
-        <v>0.22</v>
+        <v>0.55999999999999994</v>
       </c>
       <c r="D20">
         <f>COUNTA(H20:AB20)</f>
@@ -11278,28 +11596,28 @@
         <v>0</v>
       </c>
       <c r="H20" s="18">
-        <v>1.1000000000000001</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>64</v>
+      <c r="A21" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="B21">
         <f>SUM(H21:AB21)</f>
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <f>(B21/$C$1)*100</f>
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <f>COUNTA(H21:AB21)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <f>COUNTIF(H21:AB21, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <f>COUNTIF(H21:AB21, "=0")</f>
@@ -11309,29 +11627,26 @@
         <f>COUNTIF(H21:AB21, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="18">
-        <v>3.7</v>
-      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>60</v>
+      <c r="A22" t="s">
+        <v>58</v>
       </c>
       <c r="B22">
         <f>SUM(H22:AB22)</f>
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="C22">
         <f>(B22/$C$1)*100</f>
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <f>COUNTA(H22:AB22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <f>COUNTIF(H22:AB22, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <f>COUNTIF(H22:AB22, "=0")</f>
@@ -11341,29 +11656,26 @@
         <f>COUNTIF(H22:AB22, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H22" s="18">
-        <v>0.9</v>
-      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B23">
         <f>SUM(H23:AB23)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <f>(B23/$C$1)*100</f>
-        <v>1.7999999999999998</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <f>COUNTA(H23:AB23)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <f>COUNTIF(H23:AB23, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <f>COUNTIF(H23:AB23, "=0")</f>
@@ -11373,29 +11685,26 @@
         <f>COUNTIF(H23:AB23, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H23" s="18">
-        <v>9</v>
-      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>68</v>
+      <c r="A24" s="8" t="s">
+        <v>129</v>
       </c>
       <c r="B24">
         <f>SUM(H24:AB24)</f>
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="C24">
         <f>(B24/$C$1)*100</f>
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <f>COUNTA(H24:AB24)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <f>COUNTIF(H24:AB24, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <f>COUNTIF(H24:AB24, "=0")</f>
@@ -11405,13 +11714,10 @@
         <f>COUNTIF(H24:AB24, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H24" s="18">
-        <v>5.3</v>
-      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>84</v>
+      <c r="A25" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="B25">
         <f>SUM(H25:AB25)</f>
@@ -11439,8 +11745,8 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>58</v>
+      <c r="A26" t="s">
+        <v>87</v>
       </c>
       <c r="B26">
         <f>SUM(H26:AB26)</f>
@@ -11469,7 +11775,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>57</v>
+        <v>134</v>
       </c>
       <c r="B27">
         <f>SUM(H27:AB27)</f>
@@ -11498,8 +11804,8 @@
       <c r="H27" s="15"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>135</v>
+      <c r="A28" t="s">
+        <v>137</v>
       </c>
       <c r="B28">
         <f>SUM(H28:AB28)</f>
@@ -11528,7 +11834,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="B29">
         <f>SUM(H29:AB29)</f>
@@ -11557,7 +11863,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B30">
         <f>SUM(H30:AB30)</f>
@@ -11586,7 +11892,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="B31">
         <f>SUM(H31:AB31)</f>
@@ -11615,7 +11921,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="B32">
         <f>SUM(H32:AB32)</f>
@@ -11644,7 +11950,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="B33">
         <f>SUM(H33:AB33)</f>
@@ -11674,8 +11980,8 @@
       <c r="I33" s="15"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>86</v>
+      <c r="A34" t="s">
+        <v>72</v>
       </c>
       <c r="B34">
         <f>SUM(H34:AB34)</f>
@@ -11704,7 +12010,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="B35">
         <f>SUM(H35:AB35)</f>
@@ -11733,8 +12039,8 @@
       <c r="H35" s="15"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>85</v>
+      <c r="A36" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="B36">
         <f>SUM(H36:AB36)</f>
@@ -11763,7 +12069,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="B37">
         <f>SUM(H37:AB37)</f>
@@ -11793,8 +12099,8 @@
       <c r="I37" s="15"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>69</v>
+      <c r="A38" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="B38">
         <f>SUM(H38:AB38)</f>
@@ -11826,8 +12132,8 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>54</v>
+      <c r="A39" t="s">
+        <v>73</v>
       </c>
       <c r="B39">
         <f>SUM(H39:AB39)</f>
@@ -11857,8 +12163,8 @@
       <c r="I39" s="15"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
-        <v>73</v>
+      <c r="A40" t="s">
+        <v>91</v>
       </c>
       <c r="B40">
         <f>SUM(H40:AB40)</f>
@@ -11889,7 +12195,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B41">
         <f>SUM(H41:AB41)</f>
@@ -11919,7 +12225,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="B42">
         <f>SUM(H42:AB42)</f>
@@ -11949,7 +12255,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="B43">
         <f>SUM(H43:AB43)</f>
@@ -11979,7 +12285,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="B44">
         <f>SUM(H44:AB44)</f>
@@ -12013,7 +12319,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B45">
         <f>SUM(H45:AB45)</f>
@@ -12134,8 +12440,8 @@
       <c r="H48" s="15"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
-        <v>142</v>
+      <c r="A49" t="s">
+        <v>59</v>
       </c>
       <c r="B49">
         <f>SUM(H49:AB49)</f>
@@ -12164,8 +12470,8 @@
       <c r="H49" s="15"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>61</v>
+      <c r="A50" s="8" t="s">
+        <v>143</v>
       </c>
       <c r="B50">
         <f>SUM(H50:AB50)</f>
@@ -12195,8 +12501,8 @@
       <c r="I50" s="15"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>89</v>
+      <c r="A51" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="B51">
         <f>SUM(H51:AB51)</f>
@@ -12225,8 +12531,8 @@
       <c r="H51" s="15"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
-        <v>74</v>
+      <c r="A52" t="s">
+        <v>61</v>
       </c>
       <c r="B52">
         <f>SUM(H52:AB52)</f>
@@ -12254,8 +12560,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>81</v>
+      <c r="A53" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="B53">
         <f>SUM(H53:AB53)</f>
@@ -12284,8 +12590,8 @@
       <c r="H53" s="15"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>80</v>
+      <c r="A54" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="B54">
         <f>SUM(H54:AB54)</f>
@@ -12314,7 +12620,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B55">
         <f>SUM(H55:AB55)</f>
@@ -12343,8 +12649,8 @@
       <c r="H55" s="15"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>70</v>
+      <c r="A56" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="B56">
         <f>SUM(H56:AB56)</f>
@@ -12373,8 +12679,8 @@
       <c r="H56" s="15"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>83</v>
+      <c r="A57" t="s">
+        <v>55</v>
       </c>
       <c r="B57">
         <f>SUM(H57:AB57)</f>
@@ -12404,8 +12710,8 @@
       <c r="I57" s="15"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>66</v>
+      <c r="A58" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="B58">
         <f>SUM(H58:AB58)</f>
@@ -12435,8 +12741,8 @@
       <c r="I58" s="15"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>71</v>
+      <c r="A59" t="s">
+        <v>83</v>
       </c>
       <c r="B59">
         <f>SUM(H59:AB59)</f>
@@ -12466,8 +12772,8 @@
       <c r="I59" s="15"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>82</v>
+      <c r="A60" t="s">
+        <v>66</v>
       </c>
       <c r="B60">
         <f>SUM(H60:AB60)</f>
@@ -12496,8 +12802,8 @@
       <c r="H60" s="15"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>98</v>
+      <c r="A61" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="B61">
         <f>SUM(H61:AB61)</f>
@@ -12526,8 +12832,8 @@
       <c r="H61" s="15"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>97</v>
+      <c r="A62" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="B62">
         <f>SUM(H62:AB62)</f>
@@ -12556,8 +12862,8 @@
       <c r="H62" s="15"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>99</v>
+      <c r="A63" t="s">
+        <v>98</v>
       </c>
       <c r="B63">
         <f>SUM(H63:AB63)</f>
@@ -12587,8 +12893,8 @@
       <c r="I63" s="15"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>96</v>
+      <c r="A64" t="s">
+        <v>97</v>
       </c>
       <c r="B64">
         <f>SUM(H64:AB64)</f>
@@ -12617,84 +12923,91 @@
       <c r="H64" s="15"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="8"/>
+      <c r="A65" t="s">
+        <v>99</v>
+      </c>
       <c r="B65">
-        <f t="shared" ref="B65:B66" si="0">SUM(H65:AB65)</f>
+        <f>SUM(H65:AB65)</f>
         <v>0</v>
       </c>
       <c r="C65">
-        <f t="shared" ref="C65:C66" si="1">(B65/$C$1)*100</f>
+        <f>(B65/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D65">
-        <f t="shared" ref="D65:D66" si="2">COUNTA(H65:AB65)</f>
+        <f>COUNTA(H65:AB65)</f>
         <v>0</v>
       </c>
       <c r="E65">
-        <f t="shared" ref="E65:E66" si="3">COUNTIF(H65:AB65, "&gt;0")</f>
+        <f>COUNTIF(H65:AB65, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F65">
-        <f t="shared" ref="F65:F66" si="4">COUNTIF(H65:AB65, "=0")</f>
+        <f>COUNTIF(H65:AB65, "=0")</f>
         <v>0</v>
       </c>
       <c r="G65">
-        <f t="shared" ref="G65:G66" si="5">COUNTIF(H65:AB65, "&lt;0")</f>
-        <v>0</v>
-      </c>
+        <f>COUNTIF(H65:AB65, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="H65" s="15"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="8"/>
+      <c r="A66" t="s">
+        <v>96</v>
+      </c>
       <c r="B66">
-        <f t="shared" si="0"/>
+        <f>SUM(H66:AB66)</f>
         <v>0</v>
       </c>
       <c r="C66">
-        <f t="shared" si="1"/>
+        <f>(B66/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D66">
-        <f t="shared" si="2"/>
+        <f>COUNTA(H66:AB66)</f>
         <v>0</v>
       </c>
       <c r="E66">
-        <f t="shared" si="3"/>
+        <f>COUNTIF(H66:AB66, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F66">
-        <f t="shared" si="4"/>
+        <f>COUNTIF(H66:AB66, "=0")</f>
         <v>0</v>
       </c>
       <c r="G66">
-        <f t="shared" si="5"/>
+        <f>COUNTIF(H66:AB66, "&lt;0")</f>
         <v>0</v>
       </c>
       <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="8"/>
       <c r="B67">
-        <f t="shared" ref="B67:B75" si="6">SUM(H67:AB67)</f>
+        <f t="shared" ref="B67:B75" si="0">SUM(H67:AB67)</f>
         <v>0</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:C75" si="7">(B67/$C$1)*100</f>
+        <f t="shared" ref="C67:C75" si="1">(B67/$C$1)*100</f>
         <v>0</v>
       </c>
       <c r="D67">
-        <f t="shared" ref="D67:D75" si="8">COUNTA(H67:AB67)</f>
+        <f t="shared" ref="D67:D75" si="2">COUNTA(H67:AB67)</f>
         <v>0</v>
       </c>
       <c r="E67">
-        <f t="shared" ref="E67:E75" si="9">COUNTIF(H67:AB67, "&gt;0")</f>
+        <f t="shared" ref="E67:E75" si="3">COUNTIF(H67:AB67, "&gt;0")</f>
         <v>0</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F75" si="10">COUNTIF(H67:AB67, "=0")</f>
+        <f t="shared" ref="F67:F75" si="4">COUNTIF(H67:AB67, "=0")</f>
         <v>0</v>
       </c>
       <c r="G67">
-        <f t="shared" ref="G67:G75" si="11">COUNTIF(H67:AB67, "&lt;0")</f>
+        <f t="shared" ref="G67:G75" si="5">COUNTIF(H67:AB67, "&lt;0")</f>
         <v>0</v>
       </c>
       <c r="H67" s="15"/>
@@ -12702,27 +13015,27 @@
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="8"/>
       <c r="B68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E68">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F68">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G68">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I68" s="15"/>
@@ -12730,27 +13043,27 @@
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="8"/>
       <c r="B69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C69">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D69">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E69">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I69" s="15"/>
@@ -12758,54 +13071,54 @@
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="8"/>
       <c r="B70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E70">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F70">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G70">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="8"/>
       <c r="B71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E71">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F71">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G71">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H71" s="15"/>
@@ -12815,27 +13128,27 @@
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="8"/>
       <c r="B72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E72">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F72">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G72">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H72" s="15"/>
@@ -12845,54 +13158,54 @@
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="8"/>
       <c r="B73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E73">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F73">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G73">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="8"/>
       <c r="B74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E74">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F74">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G74">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H74" s="15"/>
@@ -12900,55 +13213,55 @@
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="8"/>
       <c r="B75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H75" s="15"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AA64">
-    <sortCondition descending="1" ref="D3:D64"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB66">
+    <sortCondition descending="1" ref="D3:D66"/>
   </sortState>
-  <conditionalFormatting sqref="A3:A57">
-    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="LEG">
+  <conditionalFormatting sqref="A3:A63">
+    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="9" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",A3)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="12" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="11" priority="12" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="14" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="13" priority="14" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",A3)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5015E1A-FCBA-4058-9FA3-542D8195C4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4348F9F3-48B1-4EB8-BDBD-3CF5B0CD0051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="156">
   <si>
     <t>AQUA</t>
   </si>
@@ -506,6 +506,9 @@
   </si>
   <si>
     <t>PEG30_ETC</t>
+  </si>
+  <si>
+    <t>UEG6_SURVIVALIST</t>
   </si>
 </sst>
 </file>
@@ -649,252 +652,7 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="105">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="70">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1590,10 +1348,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$P$2</c:f>
+              <c:f>Динамика!$B$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1638,16 +1396,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46308</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$3:$P$3</c:f>
+              <c:f>Динамика!$B$3:$Q$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>-20.100000000000001</c:v>
                 </c:pt>
@@ -1692,6 +1453,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18.600000000000009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1798,10 +1562,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$P$2</c:f>
+              <c:f>Динамика!$B$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -1846,16 +1610,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46308</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$4:$P$4</c:f>
+              <c:f>Динамика!$B$4:$Q$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>19.7</c:v>
                 </c:pt>
@@ -1900,6 +1667,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>214.19999999999993</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>243.99999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2006,10 +1776,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$P$2</c:f>
+              <c:f>Динамика!$B$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -2054,16 +1824,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46308</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$5:$P$5</c:f>
+              <c:f>Динамика!$B$5:$Q$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>1.9</c:v>
                 </c:pt>
@@ -2108,6 +1881,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>22.099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2214,10 +1990,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$P$2</c:f>
+              <c:f>Динамика!$B$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -2262,16 +2038,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46308</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$6:$P$6</c:f>
+              <c:f>Динамика!$B$6:$Q$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>-21</c:v>
                 </c:pt>
@@ -2316,6 +2095,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>-55.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-75.999999999999972</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2422,10 +2204,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$P$2</c:f>
+              <c:f>Динамика!$B$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -2470,16 +2252,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46308</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$7:$P$7</c:f>
+              <c:f>Динамика!$B$7:$Q$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>-18.100000000000001</c:v>
                 </c:pt>
@@ -2524,6 +2309,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>-41.100000000000009</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-32.800000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2630,10 +2418,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$P$2</c:f>
+              <c:f>Динамика!$B$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -2678,16 +2466,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46308</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$8:$P$8</c:f>
+              <c:f>Динамика!$B$8:$Q$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>44.5</c:v>
                 </c:pt>
@@ -2732,6 +2523,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>37.499999999999986</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>38.899999999999991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2841,10 +2635,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Динамика!$B$2:$P$2</c:f>
+              <c:f>Динамика!$B$2:$Q$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>46285</c:v>
                 </c:pt>
@@ -2889,16 +2683,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46308</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Динамика!$B$9:$P$9</c:f>
+              <c:f>Динамика!$B$9:$Q$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>6.8999999999999915</c:v>
                 </c:pt>
@@ -2943,6 +2740,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>209.09999999999997</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>212.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3701,43 +3501,43 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46308.963488425929" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="74" xr:uid="{3D6F248A-0360-4477-B017-E96CAA4B0EB4}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Пользователь" refreshedDate="46309.960605787041" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="74" xr:uid="{3D6F248A-0360-4477-B017-E96CAA4B0EB4}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:L1048576" sheet="Результаты"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="Номер" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="70"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="71"/>
     </cacheField>
     <cacheField name="Стратегия" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Абс" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-42.900000000000006" maxValue="177"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-42.900000000000006" maxValue="181.3"/>
     </cacheField>
     <cacheField name="Отн" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-8.58" maxValue="35.400000000000006"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-8.58" maxValue="36.260000000000005"/>
     </cacheField>
     <cacheField name="Кол-во" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="95"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="100"/>
     </cacheField>
     <cacheField name="Прибыль" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="62"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="64"/>
     </cacheField>
     <cacheField name="Нейтрал" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
     </cacheField>
     <cacheField name="Убыток" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="33"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="36"/>
     </cacheField>
     <cacheField name="ПроцПД" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="100"/>
     </cacheField>
     <cacheField name="САП" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-19.5" maxValue="7.7750000000000004"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-19.5" maxValue="8"/>
     </cacheField>
     <cacheField name="СОП" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-3.9" maxValue="1.5550000000000002"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-3.9" maxValue="1.6"/>
     </cacheField>
     <cacheField name="Тип" numFmtId="0">
       <sharedItems containsBlank="1" count="7">
@@ -3764,75 +3564,61 @@
   <r>
     <n v="1"/>
     <s v="PEG17_PHOENIX"/>
-    <n v="177"/>
-    <n v="35.400000000000006"/>
-    <n v="95"/>
-    <n v="62"/>
+    <n v="181.3"/>
+    <n v="36.260000000000005"/>
+    <n v="100"/>
+    <n v="64"/>
     <n v="0"/>
-    <n v="33"/>
-    <n v="65.26315789473685"/>
-    <n v="1.8631578947368421"/>
-    <n v="0.37263157894736848"/>
+    <n v="36"/>
+    <n v="64"/>
+    <n v="1.8130000000000002"/>
+    <n v="0.36260000000000003"/>
     <x v="0"/>
   </r>
   <r>
     <n v="2"/>
     <s v="LEG2_FENNEC"/>
-    <n v="71.699999999999989"/>
-    <n v="14.340000000000002"/>
-    <n v="29"/>
-    <n v="21"/>
+    <n v="63.299999999999983"/>
+    <n v="12.66"/>
+    <n v="31"/>
+    <n v="22"/>
     <n v="0"/>
-    <n v="8"/>
-    <n v="72.41379310344827"/>
-    <n v="2.4724137931034478"/>
-    <n v="0.49448275862068969"/>
+    <n v="9"/>
+    <n v="70.967741935483872"/>
+    <n v="2.0419354838709673"/>
+    <n v="0.40838709677419355"/>
     <x v="1"/>
   </r>
   <r>
     <n v="3"/>
     <s v="PEG30_ETC2"/>
-    <n v="51.599999999999994"/>
-    <n v="10.32"/>
-    <n v="11"/>
-    <n v="9"/>
+    <n v="58.399999999999991"/>
+    <n v="11.68"/>
+    <n v="13"/>
+    <n v="10"/>
     <n v="0"/>
-    <n v="2"/>
-    <n v="81.818181818181827"/>
-    <n v="4.6909090909090905"/>
-    <n v="0.93818181818181823"/>
+    <n v="3"/>
+    <n v="76.923076923076934"/>
+    <n v="4.4923076923076914"/>
+    <n v="0.89846153846153842"/>
     <x v="0"/>
   </r>
   <r>
     <n v="4"/>
     <s v="PEG14_RENEGADE"/>
-    <n v="44.4"/>
-    <n v="8.8800000000000008"/>
-    <n v="11"/>
+    <n v="44.199999999999996"/>
+    <n v="8.8400000000000016"/>
+    <n v="12"/>
     <n v="6"/>
     <n v="0"/>
-    <n v="5"/>
-    <n v="54.54545454545454"/>
-    <n v="4.0363636363636362"/>
-    <n v="0.80727272727272736"/>
+    <n v="6"/>
+    <n v="50"/>
+    <n v="3.6833333333333331"/>
+    <n v="0.7366666666666668"/>
     <x v="0"/>
   </r>
   <r>
     <n v="5"/>
-    <s v="LEG1_LAKSAe"/>
-    <n v="34.200000000000003"/>
-    <n v="6.8400000000000007"/>
-    <n v="11"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="81.818181818181827"/>
-    <n v="3.1090909090909093"/>
-    <n v="0.62181818181818194"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <n v="6"/>
     <s v="WEG3_BATYA"/>
     <n v="33.999999999999993"/>
     <n v="6.8000000000000025"/>
@@ -3846,49 +3632,49 @@
     <x v="2"/>
   </r>
   <r>
+    <n v="6"/>
+    <s v="LEG1_LAKSAe"/>
+    <n v="33.300000000000004"/>
+    <n v="6.660000000000001"/>
+    <n v="12"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="75"/>
+    <n v="2.7750000000000004"/>
+    <n v="0.55500000000000005"/>
+    <x v="1"/>
+  </r>
+  <r>
     <n v="7"/>
-    <s v="PEG11_RAYMIYAMOTO"/>
-    <n v="31.1"/>
-    <n v="6.2200000000000006"/>
-    <n v="4"/>
-    <n v="4"/>
+    <s v="PEG13_DUNE"/>
+    <n v="32"/>
+    <n v="6.4"/>
+    <n v="7"/>
+    <n v="7"/>
     <n v="0"/>
     <n v="0"/>
     <n v="100"/>
-    <n v="7.7750000000000004"/>
-    <n v="1.5550000000000002"/>
+    <n v="4.5714285714285712"/>
+    <n v="0.91428571428571437"/>
     <x v="0"/>
   </r>
   <r>
     <n v="8"/>
-    <s v="UEG9_GRAVY2"/>
-    <n v="29.200000000000003"/>
-    <n v="5.8400000000000007"/>
-    <n v="19"/>
-    <n v="11"/>
+    <s v="PEG11_RAYMIYAMOTO"/>
+    <n v="25.6"/>
+    <n v="5.120000000000001"/>
+    <n v="6"/>
+    <n v="4"/>
     <n v="0"/>
-    <n v="8"/>
-    <n v="57.894736842105267"/>
-    <n v="1.536842105263158"/>
-    <n v="0.30736842105263162"/>
-    <x v="3"/>
+    <n v="2"/>
+    <n v="66.666666666666657"/>
+    <n v="4.2666666666666666"/>
+    <n v="0.8533333333333335"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="9"/>
-    <s v="PEG13_DUNE"/>
-    <n v="25.4"/>
-    <n v="5.08"/>
-    <n v="5"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="100"/>
-    <n v="5.08"/>
-    <n v="1.016"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="11"/>
     <s v="PEG11_KUSURUKEN"/>
     <n v="23.4"/>
     <n v="4.6800000000000015"/>
@@ -3902,35 +3688,49 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="13"/>
+    <n v="10"/>
+    <s v="UEG9_GRAVY2"/>
+    <n v="23.1"/>
+    <n v="4.620000000000001"/>
+    <n v="20"/>
+    <n v="11"/>
+    <n v="0"/>
+    <n v="9"/>
+    <n v="55.000000000000007"/>
+    <n v="1.155"/>
+    <n v="0.23100000000000004"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="11"/>
     <s v="SEG1_LITE"/>
-    <n v="17.099999999999998"/>
-    <n v="3.42"/>
-    <n v="11"/>
-    <n v="8"/>
+    <n v="22.4"/>
+    <n v="4.4800000000000004"/>
+    <n v="12"/>
+    <n v="9"/>
     <n v="0"/>
     <n v="3"/>
-    <n v="72.727272727272734"/>
-    <n v="1.5545454545454545"/>
-    <n v="0.31090909090909091"/>
+    <n v="75"/>
+    <n v="1.8666666666666665"/>
+    <n v="0.37333333333333335"/>
     <x v="4"/>
   </r>
   <r>
     <n v="12"/>
-    <s v="LEG1_IGOGOSHA2"/>
-    <n v="16.799999999999997"/>
-    <n v="3.36"/>
+    <s v="PEG17_ZEALOT"/>
+    <n v="20.6"/>
+    <n v="4.12"/>
     <n v="7"/>
     <n v="5"/>
     <n v="0"/>
     <n v="2"/>
     <n v="71.428571428571431"/>
-    <n v="2.3999999999999995"/>
-    <n v="0.48"/>
-    <x v="1"/>
+    <n v="2.9428571428571431"/>
+    <n v="0.58857142857142863"/>
+    <x v="0"/>
   </r>
   <r>
-    <n v="10"/>
+    <n v="13"/>
     <s v="WEG4_PUPPY"/>
     <n v="16"/>
     <n v="3.1999999999999993"/>
@@ -3959,16 +3759,30 @@
   </r>
   <r>
     <n v="15"/>
-    <s v="PEG17_ZEALOT"/>
-    <n v="13.800000000000002"/>
-    <n v="2.7600000000000002"/>
-    <n v="6"/>
+    <s v="LEG1_IGOGOSHA2"/>
+    <n v="12.699999999999998"/>
+    <n v="2.54"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="62.5"/>
+    <n v="1.5874999999999997"/>
+    <n v="0.3175"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <s v="PEG14_RANGER"/>
+    <n v="12.3"/>
+    <n v="2.46"/>
+    <n v="5"/>
     <n v="4"/>
     <n v="0"/>
-    <n v="2"/>
-    <n v="66.666666666666657"/>
-    <n v="2.3000000000000003"/>
-    <n v="0.46"/>
+    <n v="1"/>
+    <n v="80"/>
+    <n v="2.46"/>
+    <n v="0.49199999999999999"/>
     <x v="0"/>
   </r>
   <r>
@@ -3986,7 +3800,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="16"/>
+    <n v="18"/>
     <s v="LEG1_PIN"/>
     <n v="9.2000000000000028"/>
     <n v="1.8400000000000003"/>
@@ -4014,77 +3828,77 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="18"/>
+    <n v="20"/>
     <s v="UEG7_LOVERGOOSE"/>
+    <n v="8.9"/>
+    <n v="1.7799999999999998"/>
     <n v="8"/>
-    <n v="1.5999999999999999"/>
-    <n v="7"/>
-    <n v="4"/>
+    <n v="5"/>
     <n v="0"/>
     <n v="3"/>
-    <n v="57.142857142857139"/>
-    <n v="1.1428571428571428"/>
-    <n v="0.22857142857142856"/>
+    <n v="62.5"/>
+    <n v="1.1125"/>
+    <n v="0.22249999999999998"/>
     <x v="3"/>
   </r>
   <r>
-    <n v="20"/>
-    <s v="SEG3_FORCE"/>
-    <n v="5.0000000000000009"/>
-    <n v="0.99999999999999978"/>
-    <n v="7"/>
-    <n v="5"/>
+    <n v="21"/>
+    <s v="UEG6_SURVIVALIST"/>
+    <n v="8"/>
+    <n v="1.6"/>
+    <n v="1"/>
+    <n v="1"/>
     <n v="0"/>
-    <n v="2"/>
-    <n v="71.428571428571431"/>
-    <n v="0.71428571428571441"/>
-    <n v="0.14285714285714282"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <n v="21"/>
-    <s v="PEG14_RANGER"/>
-    <n v="4.8999999999999995"/>
-    <n v="0.98"/>
-    <n v="4"/>
-    <n v="3"/>
     <n v="0"/>
-    <n v="1"/>
-    <n v="75"/>
-    <n v="1.2249999999999999"/>
-    <n v="0.245"/>
-    <x v="0"/>
+    <n v="100"/>
+    <n v="8"/>
+    <n v="1.6"/>
+    <x v="3"/>
   </r>
   <r>
     <n v="22"/>
     <s v="WEG4_DOG"/>
-    <n v="4.8"/>
-    <n v="0.95999999999999974"/>
-    <n v="9"/>
-    <n v="5"/>
+    <n v="6.1999999999999993"/>
+    <n v="1.2399999999999998"/>
+    <n v="10"/>
+    <n v="6"/>
     <n v="0"/>
     <n v="4"/>
-    <n v="55.555555555555557"/>
-    <n v="0.53333333333333333"/>
-    <n v="0.10666666666666663"/>
+    <n v="60"/>
+    <n v="0.61999999999999988"/>
+    <n v="0.12399999999999997"/>
     <x v="2"/>
   </r>
   <r>
     <n v="23"/>
-    <s v="VEG1_EARTH"/>
-    <n v="2.2999999999999994"/>
-    <n v="0.46000000000000019"/>
-    <n v="14"/>
-    <n v="5"/>
+    <s v="PEG11_ALICEMARASATO"/>
+    <n v="4.6999999999999993"/>
+    <n v="0.93999999999999972"/>
+    <n v="3"/>
+    <n v="2"/>
     <n v="0"/>
-    <n v="9"/>
-    <n v="35.714285714285715"/>
-    <n v="0.16428571428571423"/>
-    <n v="3.2857142857142869E-2"/>
-    <x v="5"/>
+    <n v="1"/>
+    <n v="66.666666666666657"/>
+    <n v="1.5666666666666664"/>
+    <n v="0.31333333333333324"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="24"/>
+    <s v="UEG9_POLITICIAN"/>
+    <n v="1.3"/>
+    <n v="0.26"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="66.666666666666657"/>
+    <n v="0.43333333333333335"/>
+    <n v="8.666666666666667E-2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="25"/>
     <s v="PEG4_U3"/>
     <n v="1.1999999999999993"/>
     <n v="0.23999999999999988"/>
@@ -4098,7 +3912,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="25"/>
+    <n v="26"/>
     <s v="PEG13_DWDDCr"/>
     <n v="1"/>
     <n v="0.2"/>
@@ -4112,21 +3926,21 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="26"/>
-    <s v="UEG9_POLITICIAN"/>
-    <n v="0.4"/>
-    <n v="0.08"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="1"/>
+    <n v="27"/>
+    <s v="VEG1_EARTH"/>
+    <n v="0.79999999999999938"/>
+    <n v="0.1600000000000002"/>
+    <n v="15"/>
+    <n v="5"/>
     <n v="0"/>
-    <n v="50"/>
-    <n v="0.2"/>
-    <n v="0.04"/>
-    <x v="3"/>
+    <n v="10"/>
+    <n v="33.333333333333329"/>
+    <n v="5.3333333333333295E-2"/>
+    <n v="1.066666666666668E-2"/>
+    <x v="5"/>
   </r>
   <r>
-    <n v="29"/>
+    <n v="28"/>
     <s v="LEG2_LYNX"/>
     <n v="9.9999999999992539E-2"/>
     <n v="1.999999999999913E-2"/>
@@ -4140,7 +3954,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="27"/>
+    <n v="29"/>
     <s v="PEG4_UNIVERSAL"/>
     <n v="-0.69999999999999929"/>
     <n v="-0.13999999999999901"/>
@@ -4154,7 +3968,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="28"/>
+    <n v="30"/>
     <s v="LEG2_LOGAN"/>
     <n v="-0.70000000000000107"/>
     <n v="-0.14000000000000012"/>
@@ -4168,21 +3982,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="35"/>
-    <s v="PEG11_ALICEMARASATO"/>
-    <n v="-0.90000000000000036"/>
-    <n v="-0.18000000000000016"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="-0.45000000000000018"/>
-    <n v="-9.000000000000008E-2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="36"/>
+    <n v="31"/>
     <s v="LEG1_OKROSHKA"/>
     <n v="-1.6"/>
     <n v="-0.32"/>
@@ -4196,7 +3996,21 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="37"/>
+    <n v="32"/>
+    <s v="SEG3_FORCE"/>
+    <n v="-2.3999999999999995"/>
+    <n v="-0.4800000000000002"/>
+    <n v="8"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="62.5"/>
+    <n v="-0.29999999999999993"/>
+    <n v="-6.0000000000000026E-2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="33"/>
     <s v="UEG4_PELICAN"/>
     <n v="-2.9000000000000004"/>
     <n v="-0.58000000000000007"/>
@@ -4210,7 +4024,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="38"/>
+    <n v="34"/>
     <s v="PEG14_REGAL"/>
     <n v="-2.9999999999999996"/>
     <n v="-0.59999999999999987"/>
@@ -4224,7 +4038,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="39"/>
+    <n v="35"/>
     <s v="UEG6_PIGEON"/>
     <n v="-3.0999999999999983"/>
     <n v="-0.61999999999999988"/>
@@ -4238,7 +4052,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="30"/>
+    <n v="36"/>
     <s v="UEG7_PIGEON"/>
     <n v="-3.0999999999999996"/>
     <n v="-0.61999999999999988"/>
@@ -4252,7 +4066,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="31"/>
+    <n v="37"/>
     <s v="UEG7_CANNIBAL"/>
     <n v="-3.3"/>
     <n v="-0.6599999999999997"/>
@@ -4266,21 +4080,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="32"/>
-    <s v="UEG8_SOLDIER"/>
-    <n v="-3.7999999999999989"/>
-    <n v="-0.75999999999999979"/>
-    <n v="24"/>
-    <n v="11"/>
-    <n v="0"/>
-    <n v="13"/>
-    <n v="45.833333333333329"/>
-    <n v="-0.1583333333333333"/>
-    <n v="-3.1666666666666655E-2"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <n v="33"/>
+    <n v="38"/>
     <s v="UEG7_DETECTIVE"/>
     <n v="-3.8"/>
     <n v="-0.75999999999999979"/>
@@ -4294,7 +4094,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="34"/>
+    <n v="39"/>
     <s v="WEG8_MOUSE"/>
     <n v="-4"/>
     <n v="-0.79999999999999993"/>
@@ -4365,20 +4165,6 @@
   </r>
   <r>
     <n v="44"/>
-    <s v="PEG17_SELENDIS"/>
-    <n v="-5.6"/>
-    <n v="-1.1200000000000001"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="-2.8"/>
-    <n v="-0.56000000000000005"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="45"/>
     <s v="WEG7_PARADOX2"/>
     <n v="-5.8000000000000007"/>
     <n v="-1.1600000000000001"/>
@@ -4392,7 +4178,7 @@
     <x v="2"/>
   </r>
   <r>
-    <n v="46"/>
+    <n v="45"/>
     <s v="LEG1_PHOGA"/>
     <n v="-6"/>
     <n v="-1.2"/>
@@ -4406,7 +4192,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="47"/>
+    <n v="46"/>
     <s v="PEG18_UTER"/>
     <n v="-6.2"/>
     <n v="-1.24"/>
@@ -4417,6 +4203,20 @@
     <n v="60"/>
     <n v="-1.24"/>
     <n v="-0.248"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="47"/>
+    <s v="PEG17_SELENDIS"/>
+    <n v="-6.8"/>
+    <n v="-1.36"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="33.333333333333329"/>
+    <n v="-2.2666666666666666"/>
+    <n v="-0.45333333333333337"/>
     <x v="0"/>
   </r>
   <r>
@@ -4463,20 +4263,6 @@
   </r>
   <r>
     <n v="51"/>
-    <s v="PEG30_ETC"/>
-    <n v="-8.8000000000000007"/>
-    <n v="-1.76"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="-8.8000000000000007"/>
-    <n v="-1.76"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="52"/>
     <s v="PEG18_DIABLO2"/>
     <n v="-9.1"/>
     <n v="-1.82"/>
@@ -4487,6 +4273,20 @@
     <n v="20"/>
     <n v="-1.8199999999999998"/>
     <n v="-0.36399999999999999"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="52"/>
+    <s v="PEG30_ETC"/>
+    <n v="-9.6000000000000014"/>
+    <n v="-1.92"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="-4.8000000000000007"/>
+    <n v="-0.96"/>
     <x v="0"/>
   </r>
   <r>
@@ -4519,6 +4319,20 @@
   </r>
   <r>
     <n v="55"/>
+    <s v="VEG1_MOON"/>
+    <n v="-10.900000000000002"/>
+    <n v="-2.1800000000000006"/>
+    <n v="17"/>
+    <n v="6"/>
+    <n v="0"/>
+    <n v="11"/>
+    <n v="35.294117647058826"/>
+    <n v="-0.64117647058823546"/>
+    <n v="-0.12823529411764709"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="56"/>
     <s v="UEG4_PELICAN2"/>
     <n v="-11.4"/>
     <n v="-2.2800000000000002"/>
@@ -4532,7 +4346,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="56"/>
+    <n v="57"/>
     <s v="UEG4_FALCON"/>
     <n v="-12"/>
     <n v="-2.4"/>
@@ -4546,7 +4360,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="57"/>
+    <n v="58"/>
     <s v="LEG2_DRG"/>
     <n v="-12"/>
     <n v="-2.4"/>
@@ -4560,7 +4374,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="58"/>
+    <n v="59"/>
     <s v="PEG18_UTER2"/>
     <n v="-13"/>
     <n v="-2.6000000000000005"/>
@@ -4574,7 +4388,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="59"/>
+    <n v="60"/>
     <s v="LEG1_CC2"/>
     <n v="-13.299999999999999"/>
     <n v="-2.6599999999999997"/>
@@ -4588,7 +4402,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="60"/>
+    <n v="61"/>
     <s v="LEG2_HOTS"/>
     <n v="-14"/>
     <n v="-2.8"/>
@@ -4602,7 +4416,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="61"/>
+    <n v="62"/>
     <s v="LEG1_BIBI2"/>
     <n v="-14.700000000000003"/>
     <n v="-2.9399999999999991"/>
@@ -4616,7 +4430,7 @@
     <x v="1"/>
   </r>
   <r>
-    <n v="62"/>
+    <n v="63"/>
     <s v="UEG4_CANADIAN"/>
     <n v="-14.899999999999999"/>
     <n v="-2.9799999999999995"/>
@@ -4630,7 +4444,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="63"/>
+    <n v="64"/>
     <s v="UEG7_CARRIER"/>
     <n v="-15.099999999999998"/>
     <n v="-3.0200000000000005"/>
@@ -4644,7 +4458,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="64"/>
+    <n v="65"/>
     <s v="UEG9_BIRDWATCHER2"/>
     <n v="-19.5"/>
     <n v="-3.9"/>
@@ -4658,7 +4472,7 @@
     <x v="3"/>
   </r>
   <r>
-    <n v="65"/>
+    <n v="66"/>
     <s v="PEG18_ANDUIN"/>
     <n v="-19.600000000000001"/>
     <n v="-3.9199999999999995"/>
@@ -4670,20 +4484,6 @@
     <n v="-1.6333333333333335"/>
     <n v="-0.32666666666666661"/>
     <x v="0"/>
-  </r>
-  <r>
-    <n v="66"/>
-    <s v="VEG1_MOON"/>
-    <n v="-20.700000000000003"/>
-    <n v="-4.1400000000000006"/>
-    <n v="15"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="10"/>
-    <n v="33.333333333333329"/>
-    <n v="-1.3800000000000001"/>
-    <n v="-0.27600000000000002"/>
-    <x v="5"/>
   </r>
   <r>
     <n v="67"/>
@@ -4715,6 +4515,20 @@
   </r>
   <r>
     <n v="69"/>
+    <s v="UEG8_SOLDIER"/>
+    <n v="-27.9"/>
+    <n v="-5.58"/>
+    <n v="27"/>
+    <n v="12"/>
+    <n v="0"/>
+    <n v="15"/>
+    <n v="44.444444444444443"/>
+    <n v="-1.0333333333333332"/>
+    <n v="-0.20666666666666667"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="70"/>
     <s v="PEG18_BLAZE"/>
     <n v="-42.199999999999996"/>
     <n v="-8.44"/>
@@ -4728,7 +4542,7 @@
     <x v="0"/>
   </r>
   <r>
-    <n v="70"/>
+    <n v="71"/>
     <s v="LEG2_ALKASH"/>
     <n v="-42.900000000000006"/>
     <n v="-8.58"/>
@@ -4740,20 +4554,6 @@
     <n v="-10.725000000000001"/>
     <n v="-2.145"/>
     <x v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="6"/>
   </r>
   <r>
     <m/>
@@ -5404,7 +5204,7 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5435,22 +5235,22 @@
         <v>116</v>
       </c>
       <c r="B4" s="12">
-        <v>32</v>
+        <v>18.600000000000009</v>
       </c>
       <c r="C4" s="12">
-        <v>6.4000000000000057</v>
+        <v>3.7200000000000024</v>
       </c>
       <c r="D4" s="12">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E4" s="12">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F4" s="12">
         <v>2</v>
       </c>
       <c r="G4" s="12">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5458,22 +5258,22 @@
         <v>117</v>
       </c>
       <c r="B5" s="12">
-        <v>214.19999999999993</v>
+        <v>243.99999999999994</v>
       </c>
       <c r="C5" s="12">
-        <v>42.840000000000018</v>
+        <v>48.80000000000004</v>
       </c>
       <c r="D5" s="12">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="E5" s="12">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="F5" s="12">
         <v>5</v>
       </c>
       <c r="G5" s="12">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5481,22 +5281,22 @@
         <v>118</v>
       </c>
       <c r="B6" s="12">
-        <v>22.099999999999998</v>
+        <v>20</v>
       </c>
       <c r="C6" s="12">
-        <v>4.42</v>
+        <v>4</v>
       </c>
       <c r="D6" s="12">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="12">
         <v>0</v>
       </c>
       <c r="G6" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5504,22 +5304,22 @@
         <v>119</v>
       </c>
       <c r="B7" s="12">
-        <v>-55.599999999999994</v>
+        <v>-75.999999999999972</v>
       </c>
       <c r="C7" s="12">
-        <v>-11.12</v>
+        <v>-15.2</v>
       </c>
       <c r="D7" s="12">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E7" s="12">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F7" s="12">
         <v>4</v>
       </c>
       <c r="G7" s="12">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5527,22 +5327,22 @@
         <v>120</v>
       </c>
       <c r="B8" s="12">
-        <v>-41.100000000000009</v>
+        <v>-32.800000000000004</v>
       </c>
       <c r="C8" s="12">
-        <v>-8.2199999999999989</v>
+        <v>-6.56</v>
       </c>
       <c r="D8" s="12">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E8" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="12">
         <v>0</v>
       </c>
       <c r="G8" s="12">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5550,16 +5350,16 @@
         <v>121</v>
       </c>
       <c r="B9" s="12">
-        <v>37.499999999999986</v>
+        <v>38.899999999999991</v>
       </c>
       <c r="C9" s="12">
-        <v>7.5</v>
+        <v>7.7800000000000011</v>
       </c>
       <c r="D9" s="12">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E9" s="12">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F9" s="12">
         <v>2</v>
@@ -5573,22 +5373,22 @@
         <v>114</v>
       </c>
       <c r="B10" s="12">
-        <v>209.09999999999997</v>
+        <v>212.7</v>
       </c>
       <c r="C10" s="12">
-        <v>41.820000000000029</v>
+        <v>42.540000000000035</v>
       </c>
       <c r="D10" s="12">
-        <v>791</v>
+        <v>825</v>
       </c>
       <c r="E10" s="12">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="F10" s="12">
         <v>13</v>
       </c>
       <c r="G10" s="12">
-        <v>362</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -6012,7 +5812,9 @@
       <c r="P2" s="16">
         <v>46308</v>
       </c>
-      <c r="Q2" s="16"/>
+      <c r="Q2" s="16">
+        <v>46309</v>
+      </c>
       <c r="R2" s="16"/>
       <c r="S2" s="16"/>
       <c r="T2" s="16"/>
@@ -6070,6 +5872,9 @@
       <c r="P3">
         <v>32</v>
       </c>
+      <c r="Q3">
+        <v>18.600000000000009</v>
+      </c>
     </row>
     <row r="4" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -6120,6 +5925,9 @@
       <c r="P4">
         <v>214.19999999999993</v>
       </c>
+      <c r="Q4">
+        <v>243.99999999999994</v>
+      </c>
     </row>
     <row r="5" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -6170,6 +5978,9 @@
       <c r="P5">
         <v>22.099999999999998</v>
       </c>
+      <c r="Q5">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -6220,6 +6031,9 @@
       <c r="P6">
         <v>-55.599999999999994</v>
       </c>
+      <c r="Q6">
+        <v>-75.999999999999972</v>
+      </c>
     </row>
     <row r="7" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -6270,6 +6084,9 @@
       <c r="P7">
         <v>-41.100000000000009</v>
       </c>
+      <c r="Q7">
+        <v>-32.800000000000004</v>
+      </c>
     </row>
     <row r="8" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -6320,6 +6137,9 @@
       <c r="P8">
         <v>37.499999999999986</v>
       </c>
+      <c r="Q8">
+        <v>38.899999999999991</v>
+      </c>
     </row>
     <row r="9" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -6369,6 +6189,9 @@
       </c>
       <c r="P9">
         <v>209.09999999999997</v>
+      </c>
+      <c r="Q9">
+        <v>212.7</v>
       </c>
     </row>
     <row r="11" spans="1:121" x14ac:dyDescent="0.25">
@@ -6432,6 +6255,10 @@
         <f t="shared" si="3"/>
         <v>46308</v>
       </c>
+      <c r="Q11" s="16">
+        <f t="shared" ref="Q11" si="4">Q2</f>
+        <v>46309</v>
+      </c>
     </row>
     <row r="12" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -6446,56 +6273,60 @@
         <v>-19.799999999999997</v>
       </c>
       <c r="D12">
-        <f t="shared" ref="D12:P12" si="4">D3-C3</f>
+        <f t="shared" ref="D12:Q12" si="5">D3-C3</f>
         <v>17.799999999999997</v>
       </c>
       <c r="E12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>21.200000000000003</v>
       </c>
       <c r="F12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>29.300000000000011</v>
       </c>
       <c r="G12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13.59999999999998</v>
       </c>
       <c r="H12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-59.000000000000014</v>
       </c>
       <c r="I12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>23.500000000000007</v>
       </c>
       <c r="J12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.1999999999999957</v>
       </c>
       <c r="K12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-32.299999999999976</v>
       </c>
       <c r="L12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-6.6000000000000085</v>
       </c>
       <c r="M12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15.199999999999974</v>
       </c>
       <c r="N12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14.500000000000028</v>
       </c>
       <c r="O12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13.699999999999989</v>
       </c>
       <c r="P12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15.800000000000011</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="5"/>
+        <v>-13.399999999999991</v>
       </c>
     </row>
     <row r="13" spans="1:121" x14ac:dyDescent="0.25">
@@ -6503,64 +6334,68 @@
         <v>117</v>
       </c>
       <c r="B13">
-        <f t="shared" ref="B13:B17" si="5">B4</f>
+        <f t="shared" ref="B13:B17" si="6">B4</f>
         <v>19.7</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:P17" si="6">C4-B4</f>
+        <f t="shared" ref="C13:Q17" si="7">C4-B4</f>
         <v>31.000000000000004</v>
       </c>
       <c r="D13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>17.599999999999994</v>
       </c>
       <c r="E13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.700000000000003</v>
       </c>
       <c r="F13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.19999999999998863</v>
       </c>
       <c r="G13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.5</v>
       </c>
       <c r="H13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-15.5</v>
       </c>
       <c r="I13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>15.300000000000011</v>
       </c>
       <c r="J13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>23.200000000000017</v>
       </c>
       <c r="K13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.1999999999999602</v>
       </c>
       <c r="L13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-3.2000000000000171</v>
       </c>
       <c r="M13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-35.199999999999989</v>
       </c>
       <c r="N13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-30.799999999999947</v>
       </c>
       <c r="O13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>136.30000000000004</v>
       </c>
       <c r="P13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>34.199999999999875</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="7"/>
+        <v>29.800000000000011</v>
       </c>
     </row>
     <row r="14" spans="1:121" x14ac:dyDescent="0.25">
@@ -6568,64 +6403,68 @@
         <v>118</v>
       </c>
       <c r="B14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.9</v>
       </c>
       <c r="C14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="D14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="E14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.2000000000000011</v>
       </c>
       <c r="F14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.1999999999999957</v>
       </c>
       <c r="G14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.7000000000000028</v>
       </c>
       <c r="H14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-10.100000000000001</v>
       </c>
       <c r="I14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-5.2000000000000011</v>
       </c>
       <c r="J14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.0999999999999996</v>
       </c>
       <c r="K14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.1999999999999993</v>
       </c>
       <c r="P14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.1000000000000014</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="7"/>
+        <v>-2.0999999999999979</v>
       </c>
     </row>
     <row r="15" spans="1:121" x14ac:dyDescent="0.25">
@@ -6633,64 +6472,68 @@
         <v>119</v>
       </c>
       <c r="B15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-21</v>
       </c>
       <c r="C15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-20</v>
       </c>
       <c r="D15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>39.6</v>
       </c>
       <c r="E15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-0.5</v>
       </c>
       <c r="F15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-13.299999999999997</v>
       </c>
       <c r="G15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-36.300000000000004</v>
       </c>
       <c r="H15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-4.0999999999999943</v>
       </c>
       <c r="I15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>31.8</v>
       </c>
       <c r="J15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="K15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-16.500000000000007</v>
       </c>
       <c r="L15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>15.299999999999997</v>
       </c>
       <c r="M15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-12.099999999999991</v>
       </c>
       <c r="N15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-36.799999999999997</v>
       </c>
       <c r="O15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10.500000000000014</v>
       </c>
       <c r="P15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.0000000000000142</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="7"/>
+        <v>-20.399999999999977</v>
       </c>
     </row>
     <row r="16" spans="1:121" x14ac:dyDescent="0.25">
@@ -6698,132 +6541,140 @@
         <v>120</v>
       </c>
       <c r="B16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-18.100000000000001</v>
       </c>
       <c r="C16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-4.5999999999999979</v>
       </c>
       <c r="F16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-14.799999999999997</v>
       </c>
       <c r="H16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-9.6000000000000014</v>
       </c>
       <c r="J16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-7.7000000000000028</v>
       </c>
       <c r="K16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>23.6</v>
       </c>
       <c r="L16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.1000000000000014</v>
       </c>
       <c r="M16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.2999999999999972</v>
       </c>
       <c r="N16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-6.8000000000000043</v>
       </c>
       <c r="O16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-4.7999999999999972</v>
       </c>
       <c r="P16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-3.7000000000000028</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q16">
+        <f t="shared" si="7"/>
+        <v>8.3000000000000043</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
       <c r="B17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>44.5</v>
       </c>
       <c r="C17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-0.39999999999999858</v>
       </c>
       <c r="D17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.299999999999997</v>
       </c>
       <c r="F17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.0000000000000071</v>
       </c>
       <c r="G17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.899999999999991</v>
       </c>
       <c r="H17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2.8999999999999915</v>
       </c>
       <c r="I17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.4000000000000057</v>
       </c>
       <c r="J17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-6.8999999999999915</v>
       </c>
       <c r="K17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-14.500000000000007</v>
       </c>
       <c r="L17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.399999999999999</v>
       </c>
       <c r="M17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-21</v>
       </c>
       <c r="N17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.5</v>
       </c>
       <c r="O17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-10.300000000000011</v>
       </c>
       <c r="P17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.2999999999999972</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q17">
+        <f t="shared" si="7"/>
+        <v>1.4000000000000057</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>139</v>
       </c>
@@ -6832,60 +6683,64 @@
         <v>6.8999999999999915</v>
       </c>
       <c r="C18">
-        <f t="shared" ref="C18" si="7">SUM(C12:C17)</f>
+        <f t="shared" ref="C18" si="8">SUM(C12:C17)</f>
         <v>-1.1999999999999922</v>
       </c>
       <c r="D18">
-        <f t="shared" ref="D18" si="8">SUM(D12:D17)</f>
+        <f t="shared" ref="D18" si="9">SUM(D12:D17)</f>
         <v>82</v>
       </c>
       <c r="E18">
-        <f t="shared" ref="E18" si="9">SUM(E12:E17)</f>
+        <f t="shared" ref="E18" si="10">SUM(E12:E17)</f>
         <v>47.300000000000011</v>
       </c>
       <c r="F18">
-        <f t="shared" ref="F18" si="10">SUM(F12:F17)</f>
+        <f t="shared" ref="F18" si="11">SUM(F12:F17)</f>
         <v>21.400000000000006</v>
       </c>
       <c r="G18">
-        <f t="shared" ref="G18" si="11">SUM(G12:G17)</f>
+        <f t="shared" ref="G18" si="12">SUM(G12:G17)</f>
         <v>-12.400000000000027</v>
       </c>
       <c r="H18">
-        <f t="shared" ref="H18" si="12">SUM(H12:H17)</f>
+        <f t="shared" ref="H18" si="13">SUM(H12:H17)</f>
         <v>-91.600000000000009</v>
       </c>
       <c r="I18">
-        <f t="shared" ref="I18:J18" si="13">SUM(I12:I17)</f>
+        <f t="shared" ref="I18:J18" si="14">SUM(I12:I17)</f>
         <v>54.400000000000013</v>
       </c>
       <c r="J18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>24.700000000000017</v>
       </c>
       <c r="K18">
-        <f t="shared" ref="K18:L18" si="14">SUM(K12:K17)</f>
+        <f t="shared" ref="K18:L18" si="15">SUM(K12:K17)</f>
         <v>-35.500000000000028</v>
       </c>
       <c r="L18">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>20.999999999999972</v>
       </c>
       <c r="M18">
-        <f t="shared" ref="M18:N18" si="15">SUM(M12:M17)</f>
+        <f t="shared" ref="M18:N18" si="16">SUM(M12:M17)</f>
         <v>-51.800000000000011</v>
       </c>
       <c r="N18">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-55.39999999999992</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:P18" si="16">SUM(O12:O17)</f>
+        <f t="shared" ref="O18:P18" si="17">SUM(O12:O17)</f>
         <v>147.60000000000002</v>
       </c>
       <c r="P18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>51.699999999999868</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" ref="Q18" si="18">SUM(Q12:Q17)</f>
+        <v>3.6000000000000547</v>
       </c>
     </row>
   </sheetData>
@@ -6992,34 +6847,34 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>177</v>
+        <v>181.3</v>
       </c>
       <c r="D2">
-        <v>35.400000000000006</v>
+        <v>36.260000000000005</v>
       </c>
       <c r="E2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I2" s="7">
         <f>IFERROR((F2/E2)*100,0)</f>
-        <v>65.26315789473685</v>
+        <v>64</v>
       </c>
       <c r="J2" s="10">
         <f>IFERROR(C2/E2,0)</f>
-        <v>1.8631578947368421</v>
+        <v>1.8130000000000002</v>
       </c>
       <c r="K2" s="10">
         <f>IFERROR(D2/E2,0)</f>
-        <v>0.37263157894736848</v>
+        <v>0.36260000000000003</v>
       </c>
       <c r="L2" s="10" t="str">
         <f>LEFT(B2,3)</f>
@@ -7027,19 +6882,19 @@
       </c>
       <c r="N2">
         <f t="shared" ref="N2:S2" si="0">C2+U2</f>
-        <v>177</v>
+        <v>181.3</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>35.400000000000006</v>
+        <v>36.260000000000005</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
@@ -7047,7 +6902,7 @@
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -7058,34 +6913,34 @@
         <v>62</v>
       </c>
       <c r="C3">
-        <v>71.699999999999989</v>
+        <v>63.299999999999983</v>
       </c>
       <c r="D3">
-        <v>14.340000000000002</v>
+        <v>12.66</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="7">
         <f>IFERROR((F3/E3)*100,0)</f>
-        <v>72.41379310344827</v>
+        <v>70.967741935483872</v>
       </c>
       <c r="J3" s="10">
         <f>IFERROR(C3/E3,0)</f>
-        <v>2.4724137931034478</v>
+        <v>2.0419354838709673</v>
       </c>
       <c r="K3" s="10">
         <f>IFERROR(D3/E3,0)</f>
-        <v>0.49448275862068969</v>
+        <v>0.40838709677419355</v>
       </c>
       <c r="L3" s="10" t="str">
         <f>LEFT(B3,3)</f>
@@ -7093,19 +6948,19 @@
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N53" si="1">C3+U3</f>
-        <v>71.699999999999989</v>
+        <v>63.299999999999983</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O17" si="2">D3+V3</f>
-        <v>14.340000000000002</v>
+        <v>12.66</v>
       </c>
       <c r="P3">
         <f t="shared" ref="P3:P17" si="3">E3+W3</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q17" si="4">F3+X3</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R17" si="5">G3+Y3</f>
@@ -7113,7 +6968,7 @@
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S17" si="6">H3+Z3</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -7124,34 +6979,34 @@
         <v>140</v>
       </c>
       <c r="C4">
-        <v>51.599999999999994</v>
+        <v>58.399999999999991</v>
       </c>
       <c r="D4">
-        <v>10.32</v>
+        <v>11.68</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="7">
         <f>IFERROR((F4/E4)*100,0)</f>
-        <v>81.818181818181827</v>
+        <v>76.923076923076934</v>
       </c>
       <c r="J4" s="10">
         <f>IFERROR(C4/E4,0)</f>
-        <v>4.6909090909090905</v>
+        <v>4.4923076923076914</v>
       </c>
       <c r="K4" s="10">
         <f>IFERROR(D4/E4,0)</f>
-        <v>0.93818181818181823</v>
+        <v>0.89846153846153842</v>
       </c>
       <c r="L4" s="10" t="str">
         <f>LEFT(B4,3)</f>
@@ -7159,19 +7014,19 @@
       </c>
       <c r="N4">
         <f t="shared" si="1"/>
-        <v>51.599999999999994</v>
+        <v>58.399999999999991</v>
       </c>
       <c r="O4">
         <f t="shared" si="2"/>
-        <v>10.32</v>
+        <v>11.68</v>
       </c>
       <c r="P4">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q4">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <f t="shared" si="5"/>
@@ -7179,7 +7034,7 @@
       </c>
       <c r="S4">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -7190,13 +7045,13 @@
         <v>61</v>
       </c>
       <c r="C5">
-        <v>44.4</v>
+        <v>44.199999999999996</v>
       </c>
       <c r="D5">
-        <v>8.8800000000000008</v>
+        <v>8.8400000000000016</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>6</v>
@@ -7205,19 +7060,19 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7">
         <f>IFERROR((F5/E5)*100,0)</f>
-        <v>54.54545454545454</v>
+        <v>50</v>
       </c>
       <c r="J5" s="10">
         <f>IFERROR(C5/E5,0)</f>
-        <v>4.0363636363636362</v>
+        <v>3.6833333333333331</v>
       </c>
       <c r="K5" s="10">
         <f>IFERROR(D5/E5,0)</f>
-        <v>0.80727272727272736</v>
+        <v>0.7366666666666668</v>
       </c>
       <c r="L5" s="10" t="str">
         <f>LEFT(B5,3)</f>
@@ -7225,15 +7080,15 @@
       </c>
       <c r="N5">
         <f t="shared" si="1"/>
-        <v>44.4</v>
+        <v>44.199999999999996</v>
       </c>
       <c r="O5">
         <f t="shared" si="2"/>
-        <v>8.8800000000000008</v>
+        <v>8.8400000000000016</v>
       </c>
       <c r="P5">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q5">
         <f t="shared" si="4"/>
@@ -7245,139 +7100,139 @@
       </c>
       <c r="S5">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>68</v>
+      <c r="B6" t="s">
+        <v>56</v>
       </c>
       <c r="C6">
-        <v>34.200000000000003</v>
+        <v>33.999999999999993</v>
       </c>
       <c r="D6">
-        <v>6.8400000000000007</v>
+        <v>6.8000000000000025</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I6" s="7">
         <f>IFERROR((F6/E6)*100,0)</f>
-        <v>81.818181818181827</v>
+        <v>57.377049180327866</v>
       </c>
       <c r="J6" s="10">
         <f>IFERROR(C6/E6,0)</f>
-        <v>3.1090909090909093</v>
+        <v>0.55737704918032771</v>
       </c>
       <c r="K6" s="10">
         <f>IFERROR(D6/E6,0)</f>
-        <v>0.62181818181818194</v>
+        <v>0.11147540983606562</v>
       </c>
       <c r="L6" s="10" t="str">
         <f>LEFT(B6,3)</f>
-        <v>LEG</v>
+        <v>WEG</v>
       </c>
       <c r="N6">
         <f t="shared" si="1"/>
-        <v>34.200000000000003</v>
+        <v>33.999999999999993</v>
       </c>
       <c r="O6">
         <f t="shared" si="2"/>
-        <v>6.8400000000000007</v>
+        <v>6.8000000000000025</v>
       </c>
       <c r="P6">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="Q6">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="R6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>56</v>
+      <c r="B7" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="C7">
-        <v>33.999999999999993</v>
+        <v>33.300000000000004</v>
       </c>
       <c r="D7">
-        <v>6.8000000000000025</v>
+        <v>6.660000000000001</v>
       </c>
       <c r="E7">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I7" s="7">
         <f>IFERROR((F7/E7)*100,0)</f>
-        <v>57.377049180327866</v>
+        <v>75</v>
       </c>
       <c r="J7" s="10">
         <f>IFERROR(C7/E7,0)</f>
-        <v>0.55737704918032771</v>
+        <v>2.7750000000000004</v>
       </c>
       <c r="K7" s="10">
         <f>IFERROR(D7/E7,0)</f>
-        <v>0.11147540983606562</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="L7" s="10" t="str">
         <f>LEFT(B7,3)</f>
-        <v>WEG</v>
+        <v>LEG</v>
       </c>
       <c r="N7">
         <f t="shared" si="1"/>
-        <v>33.999999999999993</v>
+        <v>33.300000000000004</v>
       </c>
       <c r="O7">
         <f t="shared" si="2"/>
-        <v>6.8000000000000025</v>
+        <v>6.660000000000001</v>
       </c>
       <c r="P7">
         <f t="shared" si="3"/>
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="Q7">
         <f t="shared" si="4"/>
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -7385,19 +7240,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C8">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="D8">
-        <v>6.2200000000000006</v>
+        <v>6.4</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -7411,11 +7266,11 @@
       </c>
       <c r="J8" s="10">
         <f>IFERROR(C8/E8,0)</f>
-        <v>7.7750000000000004</v>
+        <v>4.5714285714285712</v>
       </c>
       <c r="K8" s="10">
         <f>IFERROR(D8/E8,0)</f>
-        <v>1.5550000000000002</v>
+        <v>0.91428571428571437</v>
       </c>
       <c r="L8" s="10" t="str">
         <f>LEFT(B8,3)</f>
@@ -7423,19 +7278,19 @@
       </c>
       <c r="N8">
         <f t="shared" si="1"/>
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="O8">
         <f t="shared" si="2"/>
-        <v>6.2200000000000006</v>
+        <v>6.4</v>
       </c>
       <c r="P8">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <f t="shared" si="5"/>
@@ -7450,58 +7305,58 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>132</v>
+      <c r="B9" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="C9">
-        <v>29.200000000000003</v>
+        <v>25.6</v>
       </c>
       <c r="D9">
-        <v>5.8400000000000007</v>
+        <v>5.120000000000001</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I9" s="7">
         <f>IFERROR((F9/E9)*100,0)</f>
-        <v>57.894736842105267</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J9" s="10">
         <f>IFERROR(C9/E9,0)</f>
-        <v>1.536842105263158</v>
+        <v>4.2666666666666666</v>
       </c>
       <c r="K9" s="10">
         <f>IFERROR(D9/E9,0)</f>
-        <v>0.30736842105263162</v>
+        <v>0.8533333333333335</v>
       </c>
       <c r="L9" s="10" t="str">
         <f>LEFT(B9,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N9">
         <f t="shared" si="1"/>
-        <v>29.200000000000003</v>
+        <v>25.6</v>
       </c>
       <c r="O9">
         <f t="shared" si="2"/>
-        <v>5.8400000000000007</v>
+        <v>5.120000000000001</v>
       </c>
       <c r="P9">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R9">
         <f t="shared" si="5"/>
@@ -7509,45 +7364,45 @@
       </c>
       <c r="S9">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>150</v>
+      <c r="B10" t="s">
+        <v>64</v>
       </c>
       <c r="C10">
-        <v>25.4</v>
+        <v>23.4</v>
       </c>
       <c r="D10">
-        <v>5.08</v>
+        <v>4.6800000000000015</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I10" s="7">
         <f>IFERROR((F10/E10)*100,0)</f>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J10" s="10">
         <f>IFERROR(C10/E10,0)</f>
-        <v>5.08</v>
+        <v>0.53181818181818175</v>
       </c>
       <c r="K10" s="10">
         <f>IFERROR(D10/E10,0)</f>
-        <v>1.016</v>
+        <v>0.1063636363636364</v>
       </c>
       <c r="L10" s="10" t="str">
         <f>LEFT(B10,3)</f>
@@ -7555,93 +7410,93 @@
       </c>
       <c r="N10">
         <f t="shared" si="1"/>
-        <v>25.4</v>
+        <v>23.4</v>
       </c>
       <c r="O10">
         <f t="shared" si="2"/>
-        <v>5.08</v>
+        <v>4.6800000000000015</v>
       </c>
       <c r="P10">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="Q10">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="R10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>64</v>
+      <c r="B11" s="8" t="s">
+        <v>132</v>
       </c>
       <c r="C11">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="D11">
-        <v>4.6800000000000015</v>
+        <v>4.620000000000001</v>
       </c>
       <c r="E11">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I11" s="7">
         <f>IFERROR((F11/E11)*100,0)</f>
-        <v>50</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J11" s="10">
         <f>IFERROR(C11/E11,0)</f>
-        <v>0.53181818181818175</v>
+        <v>1.155</v>
       </c>
       <c r="K11" s="10">
         <f>IFERROR(D11/E11,0)</f>
-        <v>0.1063636363636364</v>
+        <v>0.23100000000000004</v>
       </c>
       <c r="L11" s="10" t="str">
         <f>LEFT(B11,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N11">
         <f t="shared" si="1"/>
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="O11">
         <f t="shared" si="2"/>
-        <v>4.6800000000000015</v>
+        <v>4.620000000000001</v>
       </c>
       <c r="P11">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="Q11">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="R11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -7652,16 +7507,16 @@
         <v>91</v>
       </c>
       <c r="C12">
-        <v>17.099999999999998</v>
+        <v>22.4</v>
       </c>
       <c r="D12">
-        <v>3.42</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -7671,15 +7526,15 @@
       </c>
       <c r="I12" s="7">
         <f>IFERROR((F12/E12)*100,0)</f>
-        <v>72.727272727272734</v>
+        <v>75</v>
       </c>
       <c r="J12" s="10">
         <f>IFERROR(C12/E12,0)</f>
-        <v>1.5545454545454545</v>
+        <v>1.8666666666666665</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(D12/E12,0)</f>
-        <v>0.31090909090909091</v>
+        <v>0.37333333333333335</v>
       </c>
       <c r="L12" s="10" t="str">
         <f>LEFT(B12,3)</f>
@@ -7687,19 +7542,19 @@
       </c>
       <c r="N12">
         <f t="shared" si="1"/>
-        <v>17.099999999999998</v>
+        <v>22.4</v>
       </c>
       <c r="O12">
         <f t="shared" si="2"/>
-        <v>3.42</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="P12">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q12">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <f t="shared" si="5"/>
@@ -7714,14 +7569,14 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>97</v>
+      <c r="B13" s="8" t="s">
+        <v>141</v>
       </c>
       <c r="C13">
-        <v>16.799999999999997</v>
+        <v>20.6</v>
       </c>
       <c r="D13">
-        <v>3.36</v>
+        <v>4.12</v>
       </c>
       <c r="E13">
         <v>7</v>
@@ -7741,23 +7596,23 @@
       </c>
       <c r="J13" s="10">
         <f>IFERROR(C13/E13,0)</f>
-        <v>2.3999999999999995</v>
+        <v>2.9428571428571431</v>
       </c>
       <c r="K13" s="10">
         <f>IFERROR(D13/E13,0)</f>
-        <v>0.48</v>
+        <v>0.58857142857142863</v>
       </c>
       <c r="L13" s="10" t="str">
         <f>LEFT(B13,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N13">
         <f t="shared" si="1"/>
-        <v>16.799999999999997</v>
+        <v>20.6</v>
       </c>
       <c r="O13">
         <f t="shared" si="2"/>
-        <v>3.36</v>
+        <v>4.12</v>
       </c>
       <c r="P13">
         <f t="shared" si="3"/>
@@ -7912,58 +7767,58 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>141</v>
+      <c r="B16" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="C16">
-        <v>13.800000000000002</v>
+        <v>12.699999999999998</v>
       </c>
       <c r="D16">
-        <v>2.7600000000000002</v>
+        <v>2.54</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="7">
         <f>IFERROR((F16/E16)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>62.5</v>
       </c>
       <c r="J16" s="10">
         <f>IFERROR(C16/E16,0)</f>
-        <v>2.3000000000000003</v>
+        <v>1.5874999999999997</v>
       </c>
       <c r="K16" s="10">
         <f>IFERROR(D16/E16,0)</f>
-        <v>0.46</v>
+        <v>0.3175</v>
       </c>
       <c r="L16" s="10" t="str">
         <f>LEFT(B16,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N16">
         <f t="shared" si="1"/>
-        <v>13.800000000000002</v>
+        <v>12.699999999999998</v>
       </c>
       <c r="O16">
         <f t="shared" si="2"/>
-        <v>2.7600000000000002</v>
+        <v>2.54</v>
       </c>
       <c r="P16">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <f t="shared" si="5"/>
@@ -7971,65 +7826,65 @@
       </c>
       <c r="S16">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>55</v>
+      <c r="B17" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="C17">
-        <v>9.6000000000000014</v>
+        <v>12.3</v>
       </c>
       <c r="D17">
-        <v>1.920000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="E17">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I17" s="7">
         <f>IFERROR((F17/E17)*100,0)</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J17" s="10">
         <f>IFERROR(C17/E17,0)</f>
-        <v>0.43636363636363645</v>
+        <v>2.46</v>
       </c>
       <c r="K17" s="10">
         <f>IFERROR(D17/E17,0)</f>
-        <v>8.7272727272727321E-2</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="L17" s="10" t="str">
         <f>LEFT(B17,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N17">
         <f t="shared" si="1"/>
-        <v>9.6000000000000014</v>
+        <v>12.3</v>
       </c>
       <c r="O17">
         <f t="shared" si="2"/>
-        <v>1.920000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="P17">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R17">
         <f t="shared" si="5"/>
@@ -8037,7 +7892,7 @@
       </c>
       <c r="S17">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -8045,37 +7900,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C18">
-        <v>9.2000000000000028</v>
+        <v>9.6000000000000014</v>
       </c>
       <c r="D18">
-        <v>1.8400000000000003</v>
+        <v>1.920000000000001</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I18" s="7">
         <f>IFERROR((F18/E18)*100,0)</f>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J18" s="10">
         <f>IFERROR(C18/E18,0)</f>
-        <v>0.3680000000000001</v>
+        <v>0.43636363636363645</v>
       </c>
       <c r="K18" s="10">
         <f>IFERROR(D18/E18,0)</f>
-        <v>7.3600000000000013E-2</v>
+        <v>8.7272727272727321E-2</v>
       </c>
       <c r="L18" s="10" t="str">
         <f>LEFT(B18,3)</f>
@@ -8083,27 +7938,27 @@
       </c>
       <c r="N18">
         <f t="shared" si="1"/>
-        <v>9.2000000000000028</v>
+        <v>9.6000000000000014</v>
       </c>
       <c r="O18">
         <f t="shared" ref="O18:O53" si="7">D18+V18</f>
-        <v>1.8400000000000003</v>
+        <v>1.920000000000001</v>
       </c>
       <c r="P18">
         <f t="shared" ref="P18:P53" si="8">E18+W18</f>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q18">
         <f t="shared" ref="Q18:Q53" si="9">F18+X18</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R18">
         <f t="shared" ref="R18:R47" si="10">G18+Y18</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <f t="shared" ref="S18:S47" si="11">H18+Z18</f>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -8111,85 +7966,85 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C19">
-        <v>9</v>
+        <v>9.2000000000000028</v>
       </c>
       <c r="D19">
-        <v>1.7999999999999998</v>
+        <v>1.8400000000000003</v>
       </c>
       <c r="E19">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I19" s="7">
         <f>IFERROR((F19/E19)*100,0)</f>
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J19" s="10">
         <f>IFERROR(C19/E19,0)</f>
-        <v>1.5</v>
+        <v>0.3680000000000001</v>
       </c>
       <c r="K19" s="10">
         <f>IFERROR(D19/E19,0)</f>
-        <v>0.3</v>
+        <v>7.3600000000000013E-2</v>
       </c>
       <c r="L19" s="10" t="str">
         <f>LEFT(B19,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N19">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>9.2000000000000028</v>
       </c>
       <c r="O19">
         <f t="shared" si="7"/>
-        <v>1.7999999999999998</v>
+        <v>1.8400000000000003</v>
       </c>
       <c r="P19">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="Q19">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R19">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>134</v>
+      <c r="B20" t="s">
+        <v>86</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>1.5999999999999999</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="E20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -8199,15 +8054,15 @@
       </c>
       <c r="I20" s="7">
         <f>IFERROR((F20/E20)*100,0)</f>
-        <v>57.142857142857139</v>
+        <v>50</v>
       </c>
       <c r="J20" s="10">
         <f>IFERROR(C20/E20,0)</f>
-        <v>1.1428571428571428</v>
+        <v>1.5</v>
       </c>
       <c r="K20" s="10">
         <f>IFERROR(D20/E20,0)</f>
-        <v>0.22857142857142856</v>
+        <v>0.3</v>
       </c>
       <c r="L20" s="10" t="str">
         <f>LEFT(B20,3)</f>
@@ -8215,19 +8070,19 @@
       </c>
       <c r="N20">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <f t="shared" si="7"/>
-        <v>1.5999999999999999</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="P20">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R20">
         <f t="shared" si="10"/>
@@ -8242,17 +8097,17 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>73</v>
+      <c r="B21" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="C21">
-        <v>5.0000000000000009</v>
+        <v>8.9</v>
       </c>
       <c r="D21">
-        <v>0.99999999999999978</v>
+        <v>1.7799999999999998</v>
       </c>
       <c r="E21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -8261,35 +8116,35 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="7">
         <f>IFERROR((F21/E21)*100,0)</f>
-        <v>71.428571428571431</v>
+        <v>62.5</v>
       </c>
       <c r="J21" s="10">
         <f>IFERROR(C21/E21,0)</f>
-        <v>0.71428571428571441</v>
+        <v>1.1125</v>
       </c>
       <c r="K21" s="10">
         <f>IFERROR(D21/E21,0)</f>
-        <v>0.14285714285714282</v>
+        <v>0.22249999999999998</v>
       </c>
       <c r="L21" s="10" t="str">
         <f>LEFT(B21,3)</f>
-        <v>SEG</v>
+        <v>UEG</v>
       </c>
       <c r="N21">
         <f t="shared" si="1"/>
-        <v>5.0000000000000009</v>
+        <v>8.9</v>
       </c>
       <c r="O21">
         <f t="shared" si="7"/>
-        <v>0.99999999999999978</v>
+        <v>1.7799999999999998</v>
       </c>
       <c r="P21">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <f t="shared" si="9"/>
@@ -8301,7 +8156,7 @@
       </c>
       <c r="S21">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -8309,57 +8164,57 @@
         <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="C22">
-        <v>4.8999999999999995</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>0.98</v>
+        <v>1.6</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="7">
         <f>IFERROR((F22/E22)*100,0)</f>
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J22" s="10">
         <f>IFERROR(C22/E22,0)</f>
-        <v>1.2249999999999999</v>
+        <v>8</v>
       </c>
       <c r="K22" s="10">
         <f>IFERROR(D22/E22,0)</f>
-        <v>0.245</v>
+        <v>1.6</v>
       </c>
       <c r="L22" s="10" t="str">
         <f>LEFT(B22,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N22">
         <f t="shared" si="1"/>
-        <v>4.8999999999999995</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <f t="shared" si="7"/>
-        <v>0.98</v>
+        <v>1.6</v>
       </c>
       <c r="P22">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q22">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R22">
         <f t="shared" si="10"/>
@@ -8367,7 +8222,7 @@
       </c>
       <c r="S22">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
@@ -8378,16 +8233,16 @@
         <v>138</v>
       </c>
       <c r="C23">
-        <v>4.8</v>
+        <v>6.1999999999999993</v>
       </c>
       <c r="D23">
-        <v>0.95999999999999974</v>
+        <v>1.2399999999999998</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -8397,15 +8252,15 @@
       </c>
       <c r="I23" s="7">
         <f>IFERROR((F23/E23)*100,0)</f>
-        <v>55.555555555555557</v>
+        <v>60</v>
       </c>
       <c r="J23" s="10">
         <f>IFERROR(C23/E23,0)</f>
-        <v>0.53333333333333333</v>
+        <v>0.61999999999999988</v>
       </c>
       <c r="K23" s="10">
         <f>IFERROR(D23/E23,0)</f>
-        <v>0.10666666666666663</v>
+        <v>0.12399999999999997</v>
       </c>
       <c r="L23" s="10" t="str">
         <f>LEFT(B23,3)</f>
@@ -8413,19 +8268,19 @@
       </c>
       <c r="N23">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>6.1999999999999993</v>
       </c>
       <c r="O23">
         <f t="shared" si="7"/>
-        <v>0.95999999999999974</v>
+        <v>1.2399999999999998</v>
       </c>
       <c r="P23">
         <f t="shared" si="8"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <f t="shared" si="10"/>
@@ -8440,58 +8295,58 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>136</v>
+      <c r="B24" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="C24">
-        <v>2.2999999999999994</v>
+        <v>4.6999999999999993</v>
       </c>
       <c r="D24">
-        <v>0.46000000000000019</v>
+        <v>0.93999999999999972</v>
       </c>
       <c r="E24">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I24" s="7">
         <f>IFERROR((F24/E24)*100,0)</f>
-        <v>35.714285714285715</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J24" s="10">
         <f>IFERROR(C24/E24,0)</f>
-        <v>0.16428571428571423</v>
+        <v>1.5666666666666664</v>
       </c>
       <c r="K24" s="10">
         <f>IFERROR(D24/E24,0)</f>
-        <v>3.2857142857142869E-2</v>
+        <v>0.31333333333333324</v>
       </c>
       <c r="L24" s="10" t="str">
         <f>LEFT(B24,3)</f>
-        <v>VEG</v>
+        <v>PEG</v>
       </c>
       <c r="N24">
         <f t="shared" si="1"/>
-        <v>2.2999999999999994</v>
+        <v>4.6999999999999993</v>
       </c>
       <c r="O24">
         <f t="shared" si="7"/>
-        <v>0.46000000000000019</v>
+        <v>0.93999999999999972</v>
       </c>
       <c r="P24">
         <f t="shared" si="8"/>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Q24">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R24">
         <f t="shared" si="10"/>
@@ -8499,65 +8354,65 @@
       </c>
       <c r="S24">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>63</v>
+      <c r="B25" s="8" t="s">
+        <v>152</v>
       </c>
       <c r="C25">
-        <v>1.1999999999999993</v>
+        <v>1.3</v>
       </c>
       <c r="D25">
-        <v>0.23999999999999988</v>
+        <v>0.26</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" s="7">
         <f>IFERROR((F25/E25)*100,0)</f>
-        <v>62.5</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J25" s="10">
         <f>IFERROR(C25/E25,0)</f>
-        <v>0.14999999999999991</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="K25" s="10">
         <f>IFERROR(D25/E25,0)</f>
-        <v>2.9999999999999985E-2</v>
+        <v>8.666666666666667E-2</v>
       </c>
       <c r="L25" s="10" t="str">
         <f>LEFT(B25,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N25">
         <f t="shared" si="1"/>
-        <v>1.1999999999999993</v>
+        <v>1.3</v>
       </c>
       <c r="O25">
         <f t="shared" si="7"/>
-        <v>0.23999999999999988</v>
+        <v>0.26</v>
       </c>
       <c r="P25">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q25">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R25">
         <f t="shared" si="10"/>
@@ -8565,45 +8420,45 @@
       </c>
       <c r="S25">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>74</v>
+      <c r="B26" t="s">
+        <v>63</v>
       </c>
       <c r="C26">
+        <v>1.1999999999999993</v>
+      </c>
+      <c r="D26">
+        <v>0.23999999999999988</v>
+      </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
         <v>1</v>
       </c>
-      <c r="D26">
-        <v>0.2</v>
-      </c>
-      <c r="E26">
+      <c r="H26">
         <v>2</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
       </c>
       <c r="I26" s="7">
         <f>IFERROR((F26/E26)*100,0)</f>
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="J26" s="10">
         <f>IFERROR(C26/E26,0)</f>
-        <v>0.5</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="K26" s="10">
         <f>IFERROR(D26/E26,0)</f>
-        <v>0.1</v>
+        <v>2.9999999999999985E-2</v>
       </c>
       <c r="L26" s="10" t="str">
         <f>LEFT(B26,3)</f>
@@ -8611,27 +8466,27 @@
       </c>
       <c r="N26">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.1999999999999993</v>
       </c>
       <c r="O26">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.23999999999999988</v>
       </c>
       <c r="P26">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -8639,13 +8494,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="C27">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -8654,10 +8509,10 @@
         <v>1</v>
       </c>
       <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>1</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
       </c>
       <c r="I27" s="7">
         <f>IFERROR((F27/E27)*100,0)</f>
@@ -8665,23 +8520,23 @@
       </c>
       <c r="J27" s="10">
         <f>IFERROR(C27/E27,0)</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="K27" s="10">
         <f>IFERROR(D27/E27,0)</f>
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="L27" s="10" t="str">
         <f>LEFT(B27,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N27">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="O27">
         <f t="shared" si="7"/>
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="P27">
         <f t="shared" si="8"/>
@@ -8693,11 +8548,11 @@
       </c>
       <c r="R27">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -8705,57 +8560,57 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="C28">
-        <v>9.9999999999992539E-2</v>
+        <v>0.79999999999999938</v>
       </c>
       <c r="D28">
-        <v>1.999999999999913E-2</v>
+        <v>0.1600000000000002</v>
       </c>
       <c r="E28">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F28">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I28" s="7">
         <f>IFERROR((F28/E28)*100,0)</f>
-        <v>56.666666666666664</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J28" s="10">
         <f>IFERROR(C28/E28,0)</f>
-        <v>3.3333333333330846E-3</v>
+        <v>5.3333333333333295E-2</v>
       </c>
       <c r="K28" s="10">
         <f>IFERROR(D28/E28,0)</f>
-        <v>6.666666666666377E-4</v>
+        <v>1.066666666666668E-2</v>
       </c>
       <c r="L28" s="10" t="str">
         <f>LEFT(B28,3)</f>
-        <v>LEG</v>
+        <v>VEG</v>
       </c>
       <c r="N28">
         <f t="shared" si="1"/>
-        <v>9.9999999999992539E-2</v>
+        <v>0.79999999999999938</v>
       </c>
       <c r="O28">
         <f t="shared" si="7"/>
-        <v>1.999999999999913E-2</v>
+        <v>0.1600000000000002</v>
       </c>
       <c r="P28">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="Q28">
         <f t="shared" si="9"/>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <f t="shared" si="10"/>
@@ -8763,7 +8618,7 @@
       </c>
       <c r="S28">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -8771,65 +8626,65 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C29">
-        <v>-0.69999999999999929</v>
+        <v>9.9999999999992539E-2</v>
       </c>
       <c r="D29">
-        <v>-0.13999999999999901</v>
+        <v>1.999999999999913E-2</v>
       </c>
       <c r="E29">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F29">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I29" s="7">
         <f>IFERROR((F29/E29)*100,0)</f>
-        <v>54.54545454545454</v>
+        <v>56.666666666666664</v>
       </c>
       <c r="J29" s="10">
         <f>IFERROR(C29/E29,0)</f>
-        <v>-3.1818181818181787E-2</v>
+        <v>3.3333333333330846E-3</v>
       </c>
       <c r="K29" s="10">
         <f>IFERROR(D29/E29,0)</f>
-        <v>-6.3636363636363187E-3</v>
+        <v>6.666666666666377E-4</v>
       </c>
       <c r="L29" s="10" t="str">
         <f>LEFT(B29,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N29">
         <f t="shared" si="1"/>
-        <v>-0.69999999999999929</v>
+        <v>9.9999999999992539E-2</v>
       </c>
       <c r="O29">
         <f t="shared" si="7"/>
-        <v>-0.13999999999999901</v>
+        <v>1.999999999999913E-2</v>
       </c>
       <c r="P29">
         <f t="shared" si="8"/>
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Q29">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R29">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
@@ -8837,123 +8692,123 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C30">
-        <v>-0.70000000000000107</v>
+        <v>-0.69999999999999929</v>
       </c>
       <c r="D30">
-        <v>-0.14000000000000012</v>
+        <v>-0.13999999999999901</v>
       </c>
       <c r="E30">
+        <v>22</v>
+      </c>
+      <c r="F30">
         <v>12</v>
       </c>
-      <c r="F30">
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
         <v>9</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>3</v>
       </c>
       <c r="I30" s="7">
         <f>IFERROR((F30/E30)*100,0)</f>
-        <v>75</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="J30" s="10">
         <f>IFERROR(C30/E30,0)</f>
-        <v>-5.8333333333333424E-2</v>
+        <v>-3.1818181818181787E-2</v>
       </c>
       <c r="K30" s="10">
         <f>IFERROR(D30/E30,0)</f>
-        <v>-1.1666666666666678E-2</v>
+        <v>-6.3636363636363187E-3</v>
       </c>
       <c r="L30" s="10" t="str">
         <f>LEFT(B30,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N30">
         <f t="shared" si="1"/>
-        <v>-0.70000000000000107</v>
+        <v>-0.69999999999999929</v>
       </c>
       <c r="O30">
         <f t="shared" si="7"/>
-        <v>-0.14000000000000012</v>
+        <v>-0.13999999999999901</v>
       </c>
       <c r="P30">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q30">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R30">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>149</v>
+      <c r="B31" t="s">
+        <v>81</v>
       </c>
       <c r="C31">
-        <v>-0.90000000000000036</v>
+        <v>-0.70000000000000107</v>
       </c>
       <c r="D31">
-        <v>-0.18000000000000016</v>
+        <v>-0.14000000000000012</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" s="7">
         <f>IFERROR((F31/E31)*100,0)</f>
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J31" s="10">
         <f>IFERROR(C31/E31,0)</f>
-        <v>-0.45000000000000018</v>
+        <v>-5.8333333333333424E-2</v>
       </c>
       <c r="K31" s="10">
         <f>IFERROR(D31/E31,0)</f>
-        <v>-9.000000000000008E-2</v>
+        <v>-1.1666666666666678E-2</v>
       </c>
       <c r="L31" s="10" t="str">
         <f>LEFT(B31,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N31">
         <f t="shared" si="1"/>
-        <v>-0.90000000000000036</v>
+        <v>-0.70000000000000107</v>
       </c>
       <c r="O31">
         <f t="shared" si="7"/>
-        <v>-0.18000000000000016</v>
+        <v>-0.14000000000000012</v>
       </c>
       <c r="P31">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q31">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R31">
         <f t="shared" si="10"/>
@@ -8961,7 +8816,7 @@
       </c>
       <c r="S31">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
@@ -9035,57 +8890,57 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C33">
-        <v>-2.9000000000000004</v>
+        <v>-2.3999999999999995</v>
       </c>
       <c r="D33">
-        <v>-0.58000000000000007</v>
+        <v>-0.4800000000000002</v>
       </c>
       <c r="E33">
+        <v>8</v>
+      </c>
+      <c r="F33">
         <v>5</v>
       </c>
-      <c r="F33">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>3</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>2</v>
       </c>
       <c r="I33" s="7">
         <f>IFERROR((F33/E33)*100,0)</f>
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="J33" s="10">
         <f>IFERROR(C33/E33,0)</f>
-        <v>-0.58000000000000007</v>
+        <v>-0.29999999999999993</v>
       </c>
       <c r="K33" s="10">
         <f>IFERROR(D33/E33,0)</f>
-        <v>-0.11600000000000002</v>
+        <v>-6.0000000000000026E-2</v>
       </c>
       <c r="L33" s="10" t="str">
         <f>LEFT(B33,3)</f>
-        <v>UEG</v>
+        <v>SEG</v>
       </c>
       <c r="N33">
         <f t="shared" si="1"/>
-        <v>-2.9000000000000004</v>
+        <v>-2.3999999999999995</v>
       </c>
       <c r="O33">
         <f t="shared" si="7"/>
-        <v>-0.58000000000000007</v>
+        <v>-0.4800000000000002</v>
       </c>
       <c r="P33">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <f t="shared" si="10"/>
@@ -9093,65 +8948,65 @@
       </c>
       <c r="S33">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>153</v>
+      <c r="B34" t="s">
+        <v>69</v>
       </c>
       <c r="C34">
-        <v>-2.9999999999999996</v>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="D34">
-        <v>-0.59999999999999987</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="E34">
+        <v>5</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <v>2</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>1</v>
       </c>
       <c r="I34" s="7">
         <f>IFERROR((F34/E34)*100,0)</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J34" s="10">
         <f>IFERROR(C34/E34,0)</f>
-        <v>-1.4999999999999998</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="K34" s="10">
         <f>IFERROR(D34/E34,0)</f>
-        <v>-0.29999999999999993</v>
+        <v>-0.11600000000000002</v>
       </c>
       <c r="L34" s="10" t="str">
         <f>LEFT(B34,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N34">
         <f t="shared" si="1"/>
-        <v>-2.9999999999999996</v>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="O34">
         <f t="shared" si="7"/>
-        <v>-0.59999999999999987</v>
+        <v>-0.58000000000000007</v>
       </c>
       <c r="P34">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R34">
         <f t="shared" si="10"/>
@@ -9159,65 +9014,65 @@
       </c>
       <c r="S34">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>72</v>
+      <c r="B35" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="C35">
-        <v>-3.0999999999999983</v>
+        <v>-2.9999999999999996</v>
       </c>
       <c r="D35">
-        <v>-0.61999999999999988</v>
+        <v>-0.59999999999999987</v>
       </c>
       <c r="E35">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I35" s="7">
         <f>IFERROR((F35/E35)*100,0)</f>
-        <v>38.461538461538467</v>
+        <v>50</v>
       </c>
       <c r="J35" s="10">
         <f>IFERROR(C35/E35,0)</f>
-        <v>-0.23846153846153834</v>
+        <v>-1.4999999999999998</v>
       </c>
       <c r="K35" s="10">
         <f>IFERROR(D35/E35,0)</f>
-        <v>-4.7692307692307687E-2</v>
+        <v>-0.29999999999999993</v>
       </c>
       <c r="L35" s="10" t="str">
         <f>LEFT(B35,3)</f>
-        <v>UEG</v>
+        <v>PEG</v>
       </c>
       <c r="N35">
         <f t="shared" si="1"/>
-        <v>-3.0999999999999983</v>
+        <v>-2.9999999999999996</v>
       </c>
       <c r="O35">
         <f t="shared" si="7"/>
-        <v>-0.61999999999999988</v>
+        <v>-0.59999999999999987</v>
       </c>
       <c r="P35">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Q35">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R35">
         <f t="shared" si="10"/>
@@ -9225,7 +9080,7 @@
       </c>
       <c r="S35">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
@@ -9233,37 +9088,37 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C36">
-        <v>-3.0999999999999996</v>
+        <v>-3.0999999999999983</v>
       </c>
       <c r="D36">
         <v>-0.61999999999999988</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
         <f>IFERROR((F36/E36)*100,0)</f>
-        <v>25</v>
+        <v>38.461538461538467</v>
       </c>
       <c r="J36" s="10">
         <f>IFERROR(C36/E36,0)</f>
-        <v>-0.77499999999999991</v>
+        <v>-0.23846153846153834</v>
       </c>
       <c r="K36" s="10">
         <f>IFERROR(D36/E36,0)</f>
-        <v>-0.15499999999999997</v>
+        <v>-4.7692307692307687E-2</v>
       </c>
       <c r="L36" s="10" t="str">
         <f>LEFT(B36,3)</f>
@@ -9271,7 +9126,7 @@
       </c>
       <c r="N36">
         <f t="shared" si="1"/>
-        <v>-3.0999999999999996</v>
+        <v>-3.0999999999999983</v>
       </c>
       <c r="O36">
         <f t="shared" si="7"/>
@@ -9279,11 +9134,11 @@
       </c>
       <c r="P36">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q36">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R36">
         <f t="shared" si="10"/>
@@ -9291,45 +9146,45 @@
       </c>
       <c r="S36">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>133</v>
+      <c r="B37" t="s">
+        <v>87</v>
       </c>
       <c r="C37">
-        <v>-3.3</v>
+        <v>-3.0999999999999996</v>
       </c>
       <c r="D37">
-        <v>-0.6599999999999997</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="E37">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I37" s="7">
         <f>IFERROR((F37/E37)*100,0)</f>
-        <v>46.153846153846153</v>
+        <v>25</v>
       </c>
       <c r="J37" s="10">
         <f>IFERROR(C37/E37,0)</f>
-        <v>-0.25384615384615383</v>
+        <v>-0.77499999999999991</v>
       </c>
       <c r="K37" s="10">
         <f>IFERROR(D37/E37,0)</f>
-        <v>-5.0769230769230747E-2</v>
+        <v>-0.15499999999999997</v>
       </c>
       <c r="L37" s="10" t="str">
         <f>LEFT(B37,3)</f>
@@ -9337,19 +9192,19 @@
       </c>
       <c r="N37">
         <f t="shared" si="1"/>
-        <v>-3.3</v>
+        <v>-3.0999999999999996</v>
       </c>
       <c r="O37">
         <f t="shared" si="7"/>
-        <v>-0.6599999999999997</v>
+        <v>-0.61999999999999988</v>
       </c>
       <c r="P37">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q37">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R37">
         <f t="shared" si="10"/>
@@ -9357,7 +9212,7 @@
       </c>
       <c r="S37">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
@@ -9365,37 +9220,37 @@
         <v>37</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C38">
-        <v>-3.7999999999999989</v>
+        <v>-3.3</v>
       </c>
       <c r="D38">
-        <v>-0.75999999999999979</v>
+        <v>-0.6599999999999997</v>
       </c>
       <c r="E38">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F38">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I38" s="7">
         <f>IFERROR((F38/E38)*100,0)</f>
-        <v>45.833333333333329</v>
+        <v>46.153846153846153</v>
       </c>
       <c r="J38" s="10">
         <f>IFERROR(C38/E38,0)</f>
-        <v>-0.1583333333333333</v>
+        <v>-0.25384615384615383</v>
       </c>
       <c r="K38" s="10">
         <f>IFERROR(D38/E38,0)</f>
-        <v>-3.1666666666666655E-2</v>
+        <v>-5.0769230769230747E-2</v>
       </c>
       <c r="L38" s="10" t="str">
         <f>LEFT(B38,3)</f>
@@ -9403,19 +9258,19 @@
       </c>
       <c r="N38">
         <f t="shared" si="1"/>
-        <v>-3.7999999999999989</v>
+        <v>-3.3</v>
       </c>
       <c r="O38">
         <f t="shared" si="7"/>
-        <v>-0.75999999999999979</v>
+        <v>-0.6599999999999997</v>
       </c>
       <c r="P38">
         <f t="shared" si="8"/>
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="Q38">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R38">
         <f t="shared" si="10"/>
@@ -9423,7 +9278,7 @@
       </c>
       <c r="S38">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
@@ -9827,19 +9682,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C45">
-        <v>-5.6</v>
+        <v>-5.8000000000000007</v>
       </c>
       <c r="D45">
-        <v>-1.1200000000000001</v>
+        <v>-1.1600000000000001</v>
       </c>
       <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45">
         <v>2</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -9849,35 +9704,35 @@
       </c>
       <c r="I45" s="7">
         <f>IFERROR((F45/E45)*100,0)</f>
-        <v>50</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="J45" s="10">
         <f>IFERROR(C45/E45,0)</f>
-        <v>-2.8</v>
+        <v>-1.9333333333333336</v>
       </c>
       <c r="K45" s="10">
         <f>IFERROR(D45/E45,0)</f>
-        <v>-0.56000000000000005</v>
+        <v>-0.38666666666666671</v>
       </c>
       <c r="L45" s="10" t="str">
         <f>LEFT(B45,3)</f>
-        <v>PEG</v>
+        <v>WEG</v>
       </c>
       <c r="N45">
         <f t="shared" si="1"/>
-        <v>-5.6</v>
+        <v>-5.8000000000000007</v>
       </c>
       <c r="O45">
         <f t="shared" si="7"/>
-        <v>-1.1200000000000001</v>
+        <v>-1.1600000000000001</v>
       </c>
       <c r="P45">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45">
         <f t="shared" si="10"/>
@@ -9893,19 +9748,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>148</v>
+        <v>71</v>
       </c>
       <c r="C46">
-        <v>-5.8000000000000007</v>
+        <v>-6</v>
       </c>
       <c r="D46">
-        <v>-1.1600000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -9915,35 +9770,35 @@
       </c>
       <c r="I46" s="7">
         <f>IFERROR((F46/E46)*100,0)</f>
-        <v>66.666666666666657</v>
+        <v>0</v>
       </c>
       <c r="J46" s="10">
         <f>IFERROR(C46/E46,0)</f>
-        <v>-1.9333333333333336</v>
+        <v>-6</v>
       </c>
       <c r="K46" s="10">
         <f>IFERROR(D46/E46,0)</f>
-        <v>-0.38666666666666671</v>
+        <v>-1.2</v>
       </c>
       <c r="L46" s="10" t="str">
         <f>LEFT(B46,3)</f>
-        <v>WEG</v>
+        <v>LEG</v>
       </c>
       <c r="N46">
         <f t="shared" si="1"/>
-        <v>-5.8000000000000007</v>
+        <v>-6</v>
       </c>
       <c r="O46">
         <f t="shared" si="7"/>
-        <v>-1.1600000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="P46">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q46">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R46">
         <f t="shared" si="10"/>
@@ -9958,62 +9813,62 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>71</v>
+      <c r="B47" t="s">
+        <v>90</v>
       </c>
       <c r="C47">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="D47">
-        <v>-1.2</v>
+        <v>-1.24</v>
       </c>
       <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47">
+        <v>3</v>
+      </c>
+      <c r="G47">
         <v>1</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" s="7">
         <f>IFERROR((F47/E47)*100,0)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J47" s="10">
         <f>IFERROR(C47/E47,0)</f>
-        <v>-6</v>
+        <v>-1.24</v>
       </c>
       <c r="K47" s="10">
         <f>IFERROR(D47/E47,0)</f>
-        <v>-1.2</v>
+        <v>-0.248</v>
       </c>
       <c r="L47" s="10" t="str">
         <f>LEFT(B47,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N47">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="O47">
         <f t="shared" si="7"/>
-        <v>-1.2</v>
+        <v>-1.24</v>
       </c>
       <c r="P47">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q47">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R47">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47">
         <f t="shared" si="11"/>
@@ -10024,38 +9879,38 @@
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>90</v>
+      <c r="B48" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="C48">
-        <v>-6.2</v>
+        <v>-6.8</v>
       </c>
       <c r="D48">
-        <v>-1.24</v>
+        <v>-1.36</v>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="7">
         <f>IFERROR((F48/E48)*100,0)</f>
-        <v>60</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J48" s="10">
         <f>IFERROR(C48/E48,0)</f>
-        <v>-1.24</v>
+        <v>-2.2666666666666666</v>
       </c>
       <c r="K48" s="10">
         <f>IFERROR(D48/E48,0)</f>
-        <v>-0.248</v>
+        <v>-0.45333333333333337</v>
       </c>
       <c r="L48" s="10" t="str">
         <f>LEFT(B48,3)</f>
@@ -10063,27 +9918,27 @@
       </c>
       <c r="N48">
         <f t="shared" si="1"/>
-        <v>-6.2</v>
+        <v>-6.8</v>
       </c>
       <c r="O48">
         <f t="shared" si="7"/>
-        <v>-1.24</v>
+        <v>-1.36</v>
       </c>
       <c r="P48">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q48">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R48">
         <f t="shared" ref="R48:R53" si="12">G48+Y48</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <f t="shared" ref="S48:S53" si="13">H48+Z48</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
@@ -10289,37 +10144,37 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>154</v>
+        <v>93</v>
       </c>
       <c r="C52">
-        <v>-8.8000000000000007</v>
+        <v>-9.1</v>
       </c>
       <c r="D52">
-        <v>-1.76</v>
+        <v>-1.82</v>
       </c>
       <c r="E52">
+        <v>5</v>
+      </c>
+      <c r="F52">
         <v>1</v>
       </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I52" s="7">
         <f>IFERROR((F52/E52)*100,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J52" s="10">
         <f>IFERROR(C52/E52,0)</f>
-        <v>-8.8000000000000007</v>
+        <v>-1.8199999999999998</v>
       </c>
       <c r="K52" s="10">
         <f>IFERROR(D52/E52,0)</f>
-        <v>-1.76</v>
+        <v>-0.36399999999999999</v>
       </c>
       <c r="L52" s="10" t="str">
         <f>LEFT(B52,3)</f>
@@ -10327,19 +10182,19 @@
       </c>
       <c r="N52">
         <f t="shared" si="1"/>
-        <v>-8.8000000000000007</v>
+        <v>-9.1</v>
       </c>
       <c r="O52">
         <f t="shared" si="7"/>
-        <v>-1.76</v>
+        <v>-1.82</v>
       </c>
       <c r="P52">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q52">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52">
         <f t="shared" si="12"/>
@@ -10347,7 +10202,7 @@
       </c>
       <c r="S52">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
@@ -10355,37 +10210,37 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="C53">
-        <v>-9.1</v>
+        <v>-9.6000000000000014</v>
       </c>
       <c r="D53">
-        <v>-1.82</v>
+        <v>-1.92</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I53" s="7">
         <f>IFERROR((F53/E53)*100,0)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J53" s="10">
         <f>IFERROR(C53/E53,0)</f>
-        <v>-1.8199999999999998</v>
+        <v>-4.8000000000000007</v>
       </c>
       <c r="K53" s="10">
         <f>IFERROR(D53/E53,0)</f>
-        <v>-0.36399999999999999</v>
+        <v>-0.96</v>
       </c>
       <c r="L53" s="10" t="str">
         <f>LEFT(B53,3)</f>
@@ -10393,19 +10248,19 @@
       </c>
       <c r="N53">
         <f t="shared" si="1"/>
-        <v>-9.1</v>
+        <v>-9.6000000000000014</v>
       </c>
       <c r="O53">
         <f t="shared" si="7"/>
-        <v>-1.82</v>
+        <v>-1.92</v>
       </c>
       <c r="P53">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q53">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53">
         <f t="shared" si="12"/>
@@ -10413,7 +10268,7 @@
       </c>
       <c r="S53">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
@@ -10552,58 +10407,58 @@
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>130</v>
+      <c r="B56" t="s">
+        <v>129</v>
       </c>
       <c r="C56">
-        <v>-11.4</v>
+        <v>-10.900000000000002</v>
       </c>
       <c r="D56">
-        <v>-2.2800000000000002</v>
+        <v>-2.1800000000000006</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I56" s="7">
         <f>IFERROR((F56/E56)*100,0)</f>
-        <v>0</v>
+        <v>35.294117647058826</v>
       </c>
       <c r="J56" s="10">
         <f>IFERROR(C56/E56,0)</f>
-        <v>-11.4</v>
+        <v>-0.64117647058823546</v>
       </c>
       <c r="K56" s="10">
         <f>IFERROR(D56/E56,0)</f>
-        <v>-2.2800000000000002</v>
+        <v>-0.12823529411764709</v>
       </c>
       <c r="L56" s="10" t="str">
         <f>LEFT(B56,3)</f>
-        <v>UEG</v>
+        <v>VEG</v>
       </c>
       <c r="N56">
         <f t="shared" ref="N56:N60" si="20">C56+U56</f>
-        <v>-11.4</v>
+        <v>-10.900000000000002</v>
       </c>
       <c r="O56">
         <f t="shared" ref="O56:O60" si="21">D56+V56</f>
-        <v>-2.2800000000000002</v>
+        <v>-2.1800000000000006</v>
       </c>
       <c r="P56">
         <f t="shared" ref="P56:P60" si="22">E56+W56</f>
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Q56">
         <f t="shared" ref="Q56:Q60" si="23">F56+X56</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R56">
         <f t="shared" ref="R56:R60" si="24">G56+Y56</f>
@@ -10611,7 +10466,7 @@
       </c>
       <c r="S56">
         <f t="shared" ref="S56:S60" si="25">H56+Z56</f>
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
@@ -10619,16 +10474,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="C57">
-        <v>-12</v>
+        <v>-11.4</v>
       </c>
       <c r="D57">
-        <v>-2.4</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -10637,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57" s="7">
         <f>IFERROR((F57/E57)*100,0)</f>
@@ -10645,11 +10500,11 @@
       </c>
       <c r="J57" s="10">
         <f>IFERROR(C57/E57,0)</f>
-        <v>-6</v>
+        <v>-11.4</v>
       </c>
       <c r="K57" s="10">
         <f>IFERROR(D57/E57,0)</f>
-        <v>-1.2</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="L57" s="10" t="str">
         <f>LEFT(B57,3)</f>
@@ -10657,15 +10512,15 @@
       </c>
       <c r="N57">
         <f t="shared" si="20"/>
-        <v>-12</v>
+        <v>-11.4</v>
       </c>
       <c r="O57">
         <f t="shared" si="21"/>
-        <v>-2.4</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="P57">
         <f t="shared" si="22"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q57">
         <f t="shared" si="23"/>
@@ -10677,7 +10532,7 @@
       </c>
       <c r="S57">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
@@ -10685,7 +10540,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C58">
         <v>-12</v>
@@ -10694,32 +10549,32 @@
         <v>-2.4</v>
       </c>
       <c r="E58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
         <v>2</v>
-      </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>3</v>
       </c>
       <c r="I58" s="7">
         <f>IFERROR((F58/E58)*100,0)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J58" s="10">
         <f>IFERROR(C58/E58,0)</f>
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="K58" s="10">
         <f>IFERROR(D58/E58,0)</f>
-        <v>-0.48</v>
+        <v>-1.2</v>
       </c>
       <c r="L58" s="10" t="str">
         <f>LEFT(B58,3)</f>
-        <v>LEG</v>
+        <v>UEG</v>
       </c>
       <c r="N58">
         <f t="shared" si="20"/>
@@ -10731,11 +10586,11 @@
       </c>
       <c r="P58">
         <f t="shared" si="22"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q58">
         <f t="shared" si="23"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R58">
         <f t="shared" si="24"/>
@@ -10743,65 +10598,65 @@
       </c>
       <c r="S58">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
-        <v>92</v>
+      <c r="B59" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="C59">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="D59">
-        <v>-2.6000000000000005</v>
+        <v>-2.4</v>
       </c>
       <c r="E59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
         <v>3</v>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59">
-        <v>4</v>
       </c>
       <c r="I59" s="7">
         <f>IFERROR((F59/E59)*100,0)</f>
-        <v>42.857142857142854</v>
+        <v>40</v>
       </c>
       <c r="J59" s="10">
         <f>IFERROR(C59/E59,0)</f>
-        <v>-1.8571428571428572</v>
+        <v>-2.4</v>
       </c>
       <c r="K59" s="10">
         <f>IFERROR(D59/E59,0)</f>
-        <v>-0.3714285714285715</v>
+        <v>-0.48</v>
       </c>
       <c r="L59" s="10" t="str">
         <f>LEFT(B59,3)</f>
-        <v>PEG</v>
+        <v>LEG</v>
       </c>
       <c r="N59">
         <f t="shared" si="20"/>
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="O59">
         <f t="shared" si="21"/>
-        <v>-2.6000000000000005</v>
+        <v>-2.4</v>
       </c>
       <c r="P59">
         <f t="shared" si="22"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q59">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R59">
         <f t="shared" si="24"/>
@@ -10809,65 +10664,65 @@
       </c>
       <c r="S59">
         <f t="shared" si="25"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>99</v>
+      <c r="B60" t="s">
+        <v>92</v>
       </c>
       <c r="C60">
-        <v>-13.299999999999999</v>
+        <v>-13</v>
       </c>
       <c r="D60">
-        <v>-2.6599999999999997</v>
+        <v>-2.6000000000000005</v>
       </c>
       <c r="E60">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
         <v>4</v>
-      </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-      <c r="H60">
-        <v>5</v>
       </c>
       <c r="I60" s="7">
         <f>IFERROR((F60/E60)*100,0)</f>
-        <v>44.444444444444443</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="J60" s="10">
         <f>IFERROR(C60/E60,0)</f>
-        <v>-1.4777777777777776</v>
+        <v>-1.8571428571428572</v>
       </c>
       <c r="K60" s="10">
         <f>IFERROR(D60/E60,0)</f>
-        <v>-0.29555555555555552</v>
+        <v>-0.3714285714285715</v>
       </c>
       <c r="L60" s="10" t="str">
         <f>LEFT(B60,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N60">
         <f t="shared" si="20"/>
-        <v>-13.299999999999999</v>
+        <v>-13</v>
       </c>
       <c r="O60">
         <f t="shared" si="21"/>
-        <v>-2.6599999999999997</v>
+        <v>-2.6000000000000005</v>
       </c>
       <c r="P60">
         <f t="shared" si="22"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q60">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R60">
         <f t="shared" si="24"/>
@@ -10875,45 +10730,45 @@
       </c>
       <c r="S60">
         <f t="shared" si="25"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="8" t="s">
-        <v>80</v>
+      <c r="B61" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="C61">
-        <v>-14</v>
+        <v>-13.299999999999999</v>
       </c>
       <c r="D61">
-        <v>-2.8</v>
+        <v>-2.6599999999999997</v>
       </c>
       <c r="E61">
+        <v>9</v>
+      </c>
+      <c r="F61">
+        <v>4</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
         <v>5</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61">
-        <v>1</v>
-      </c>
-      <c r="H61">
-        <v>4</v>
       </c>
       <c r="I61" s="7">
         <f>IFERROR((F61/E61)*100,0)</f>
-        <v>0</v>
+        <v>44.444444444444443</v>
       </c>
       <c r="J61" s="10">
         <f>IFERROR(C61/E61,0)</f>
-        <v>-2.8</v>
+        <v>-1.4777777777777776</v>
       </c>
       <c r="K61" s="10">
         <f>IFERROR(D61/E61,0)</f>
-        <v>-0.55999999999999994</v>
+        <v>-0.29555555555555552</v>
       </c>
       <c r="L61" s="10" t="str">
         <f>LEFT(B61,3)</f>
@@ -10921,65 +10776,65 @@
       </c>
       <c r="N61">
         <f t="shared" ref="N61" si="26">C61+U61</f>
-        <v>-14</v>
+        <v>-13.299999999999999</v>
       </c>
       <c r="O61">
         <f t="shared" ref="O61" si="27">D61+V61</f>
-        <v>-2.8</v>
+        <v>-2.6599999999999997</v>
       </c>
       <c r="P61">
         <f t="shared" ref="P61" si="28">E61+W61</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q61">
         <f t="shared" ref="Q61" si="29">F61+X61</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R61">
         <f t="shared" ref="R61" si="30">G61+Y61</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61">
         <f t="shared" ref="S61" si="31">H61+Z61</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>96</v>
+      <c r="B62" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C62">
-        <v>-14.700000000000003</v>
+        <v>-14</v>
       </c>
       <c r="D62">
-        <v>-2.9399999999999991</v>
+        <v>-2.8</v>
       </c>
       <c r="E62">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F62">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I62" s="7">
         <f>IFERROR((F62/E62)*100,0)</f>
-        <v>44.444444444444443</v>
+        <v>0</v>
       </c>
       <c r="J62" s="10">
         <f>IFERROR(C62/E62,0)</f>
-        <v>-0.81666666666666687</v>
+        <v>-2.8</v>
       </c>
       <c r="K62" s="10">
         <f>IFERROR(D62/E62,0)</f>
-        <v>-0.16333333333333327</v>
+        <v>-0.55999999999999994</v>
       </c>
       <c r="L62" s="10" t="str">
         <f>LEFT(B62,3)</f>
@@ -10987,85 +10842,85 @@
       </c>
       <c r="N62">
         <f t="shared" ref="N62" si="32">C62+U62</f>
-        <v>-14.700000000000003</v>
+        <v>-14</v>
       </c>
       <c r="O62">
         <f t="shared" ref="O62" si="33">D62+V62</f>
-        <v>-2.9399999999999991</v>
+        <v>-2.8</v>
       </c>
       <c r="P62">
         <f t="shared" ref="P62" si="34">E62+W62</f>
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q62">
         <f t="shared" ref="Q62" si="35">F62+X62</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R62">
         <f t="shared" ref="R62" si="36">G62+Y62</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62">
         <f t="shared" ref="S62" si="37">H62+Z62</f>
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" s="8" t="s">
-        <v>146</v>
+      <c r="B63" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="C63">
-        <v>-14.899999999999999</v>
+        <v>-14.700000000000003</v>
       </c>
       <c r="D63">
-        <v>-2.9799999999999995</v>
+        <v>-2.9399999999999991</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I63" s="7">
         <f>IFERROR((F63/E63)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>44.444444444444443</v>
       </c>
       <c r="J63" s="10">
         <f>IFERROR(C63/E63,0)</f>
-        <v>-4.9666666666666659</v>
+        <v>-0.81666666666666687</v>
       </c>
       <c r="K63" s="10">
         <f>IFERROR(D63/E63,0)</f>
-        <v>-0.99333333333333318</v>
+        <v>-0.16333333333333327</v>
       </c>
       <c r="L63" s="10" t="str">
         <f>LEFT(B63,3)</f>
-        <v>UEG</v>
+        <v>LEG</v>
       </c>
       <c r="N63">
         <f t="shared" ref="N63:N64" si="38">C63+U63</f>
-        <v>-14.899999999999999</v>
+        <v>-14.700000000000003</v>
       </c>
       <c r="O63">
         <f t="shared" ref="O63:O64" si="39">D63+V63</f>
-        <v>-2.9799999999999995</v>
+        <v>-2.9399999999999991</v>
       </c>
       <c r="P63">
         <f t="shared" ref="P63:P64" si="40">E63+W63</f>
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Q63">
         <f t="shared" ref="Q63:Q64" si="41">F63+X63</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R63">
         <f t="shared" ref="R63:R64" si="42">G63+Y63</f>
@@ -11073,7 +10928,7 @@
       </c>
       <c r="S63">
         <f t="shared" ref="S63:S64" si="43">H63+Z63</f>
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
@@ -11081,37 +10936,37 @@
         <v>63</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="C64">
-        <v>-15.099999999999998</v>
+        <v>-14.899999999999999</v>
       </c>
       <c r="D64">
-        <v>-3.0200000000000005</v>
+        <v>-2.9799999999999995</v>
       </c>
       <c r="E64">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I64" s="7">
         <f>IFERROR((F64/E64)*100,0)</f>
-        <v>0</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="J64" s="10">
         <f>IFERROR(C64/E64,0)</f>
-        <v>-2.5166666666666662</v>
+        <v>-4.9666666666666659</v>
       </c>
       <c r="K64" s="10">
         <f>IFERROR(D64/E64,0)</f>
-        <v>-0.50333333333333341</v>
+        <v>-0.99333333333333318</v>
       </c>
       <c r="L64" s="10" t="str">
         <f>LEFT(B64,3)</f>
@@ -11119,27 +10974,27 @@
       </c>
       <c r="N64">
         <f t="shared" si="38"/>
-        <v>-15.099999999999998</v>
+        <v>-14.899999999999999</v>
       </c>
       <c r="O64">
         <f t="shared" si="39"/>
-        <v>-3.0200000000000005</v>
+        <v>-2.9799999999999995</v>
       </c>
       <c r="P64">
         <f t="shared" si="40"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q64">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64">
         <f t="shared" si="43"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
@@ -11147,25 +11002,25 @@
         <v>64</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C65">
-        <v>-19.5</v>
+        <v>-15.099999999999998</v>
       </c>
       <c r="D65">
-        <v>-3.9</v>
+        <v>-3.0200000000000005</v>
       </c>
       <c r="E65">
+        <v>6</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
         <v>1</v>
       </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
       <c r="H65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I65" s="7">
         <f>IFERROR((F65/E65)*100,0)</f>
@@ -11173,11 +11028,11 @@
       </c>
       <c r="J65" s="10">
         <f>IFERROR(C65/E65,0)</f>
-        <v>-19.5</v>
+        <v>-2.5166666666666662</v>
       </c>
       <c r="K65" s="10">
         <f>IFERROR(D65/E65,0)</f>
-        <v>-3.9</v>
+        <v>-0.50333333333333341</v>
       </c>
       <c r="L65" s="10" t="str">
         <f>LEFT(B65,3)</f>
@@ -11185,15 +11040,15 @@
       </c>
       <c r="N65">
         <f t="shared" ref="N65:N70" si="44">C65+U65</f>
-        <v>-19.5</v>
+        <v>-15.099999999999998</v>
       </c>
       <c r="O65">
         <f t="shared" ref="O65:O70" si="45">D65+V65</f>
-        <v>-3.9</v>
+        <v>-3.0200000000000005</v>
       </c>
       <c r="P65">
         <f t="shared" ref="P65:P70" si="46">E65+W65</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q65">
         <f t="shared" ref="Q65:Q70" si="47">F65+X65</f>
@@ -11201,69 +11056,69 @@
       </c>
       <c r="R65">
         <f t="shared" ref="R65:R70" si="48">G65+Y65</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65">
         <f t="shared" ref="S65:S70" si="49">H65+Z65</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>94</v>
+      <c r="B66" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="C66">
-        <v>-19.600000000000001</v>
+        <v>-19.5</v>
       </c>
       <c r="D66">
-        <v>-3.9199999999999995</v>
+        <v>-3.9</v>
       </c>
       <c r="E66">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I66" s="7">
         <f>IFERROR((F66/E66)*100,0)</f>
-        <v>41.666666666666671</v>
+        <v>0</v>
       </c>
       <c r="J66" s="10">
         <f>IFERROR(C66/E66,0)</f>
-        <v>-1.6333333333333335</v>
+        <v>-19.5</v>
       </c>
       <c r="K66" s="10">
         <f>IFERROR(D66/E66,0)</f>
-        <v>-0.32666666666666661</v>
+        <v>-3.9</v>
       </c>
       <c r="L66" s="10" t="str">
         <f>LEFT(B66,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N66">
         <f t="shared" si="44"/>
-        <v>-19.600000000000001</v>
+        <v>-19.5</v>
       </c>
       <c r="O66">
         <f t="shared" si="45"/>
-        <v>-3.9199999999999995</v>
+        <v>-3.9</v>
       </c>
       <c r="P66">
         <f t="shared" si="46"/>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Q66">
         <f t="shared" si="47"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R66">
         <f t="shared" si="48"/>
@@ -11271,24 +11126,24 @@
       </c>
       <c r="S66">
         <f t="shared" si="49"/>
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
-        <v>129</v>
+      <c r="B67" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="C67">
-        <v>-20.700000000000003</v>
+        <v>-19.600000000000001</v>
       </c>
       <c r="D67">
-        <v>-4.1400000000000006</v>
+        <v>-3.9199999999999995</v>
       </c>
       <c r="E67">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F67">
         <v>5</v>
@@ -11297,35 +11152,35 @@
         <v>0</v>
       </c>
       <c r="H67">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I67" s="7">
         <f>IFERROR((F67/E67)*100,0)</f>
-        <v>33.333333333333329</v>
+        <v>41.666666666666671</v>
       </c>
       <c r="J67" s="10">
         <f>IFERROR(C67/E67,0)</f>
-        <v>-1.3800000000000001</v>
+        <v>-1.6333333333333335</v>
       </c>
       <c r="K67" s="10">
         <f>IFERROR(D67/E67,0)</f>
-        <v>-0.27600000000000002</v>
+        <v>-0.32666666666666661</v>
       </c>
       <c r="L67" s="10" t="str">
         <f>LEFT(B67,3)</f>
-        <v>VEG</v>
+        <v>PEG</v>
       </c>
       <c r="N67">
         <f t="shared" si="44"/>
-        <v>-20.700000000000003</v>
+        <v>-19.600000000000001</v>
       </c>
       <c r="O67">
         <f t="shared" si="45"/>
-        <v>-4.1400000000000006</v>
+        <v>-3.9199999999999995</v>
       </c>
       <c r="P67">
         <f t="shared" si="46"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q67">
         <f t="shared" si="47"/>
@@ -11337,7 +11192,7 @@
       </c>
       <c r="S67">
         <f t="shared" si="49"/>
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
@@ -11476,140 +11331,199 @@
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" s="6" t="s">
-        <v>59</v>
+      <c r="B70" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="C70">
-        <v>-42.199999999999996</v>
+        <v>-27.9</v>
       </c>
       <c r="D70">
-        <v>-8.44</v>
+        <v>-5.58</v>
       </c>
       <c r="E70">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F70">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I70" s="7">
         <f>IFERROR((F70/E70)*100,0)</f>
-        <v>42.105263157894733</v>
+        <v>44.444444444444443</v>
       </c>
       <c r="J70" s="10">
         <f>IFERROR(C70/E70,0)</f>
-        <v>-2.2210526315789472</v>
+        <v>-1.0333333333333332</v>
       </c>
       <c r="K70" s="10">
         <f>IFERROR(D70/E70,0)</f>
-        <v>-0.44421052631578944</v>
+        <v>-0.20666666666666667</v>
       </c>
       <c r="L70" s="10" t="str">
         <f>LEFT(B70,3)</f>
-        <v>PEG</v>
+        <v>UEG</v>
       </c>
       <c r="N70">
         <f t="shared" si="44"/>
-        <v>-42.199999999999996</v>
+        <v>-27.9</v>
       </c>
       <c r="O70">
         <f t="shared" si="45"/>
-        <v>-8.44</v>
+        <v>-5.58</v>
       </c>
       <c r="P70">
         <f t="shared" si="46"/>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="Q70">
         <f t="shared" si="47"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R70">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <f t="shared" si="49"/>
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="4" t="s">
-        <v>83</v>
+      <c r="B71" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="C71">
-        <v>-42.900000000000006</v>
+        <v>-42.199999999999996</v>
       </c>
       <c r="D71">
-        <v>-8.58</v>
+        <v>-8.44</v>
       </c>
       <c r="E71">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I71" s="7">
         <f>IFERROR((F71/E71)*100,0)</f>
-        <v>0</v>
+        <v>42.105263157894733</v>
       </c>
       <c r="J71" s="10">
         <f>IFERROR(C71/E71,0)</f>
-        <v>-10.725000000000001</v>
+        <v>-2.2210526315789472</v>
       </c>
       <c r="K71" s="10">
         <f>IFERROR(D71/E71,0)</f>
-        <v>-2.145</v>
+        <v>-0.44421052631578944</v>
       </c>
       <c r="L71" s="10" t="str">
         <f>LEFT(B71,3)</f>
-        <v>LEG</v>
+        <v>PEG</v>
       </c>
       <c r="N71">
         <f t="shared" ref="N71" si="50">C71+U71</f>
-        <v>-42.900000000000006</v>
+        <v>-42.199999999999996</v>
       </c>
       <c r="O71">
         <f t="shared" ref="O71" si="51">D71+V71</f>
-        <v>-8.58</v>
+        <v>-8.44</v>
       </c>
       <c r="P71">
         <f t="shared" ref="P71" si="52">E71+W71</f>
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="Q71">
         <f t="shared" ref="Q71" si="53">F71+X71</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R71">
         <f t="shared" ref="R71" si="54">G71+Y71</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71">
         <f t="shared" ref="S71" si="55">H71+Z71</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C72">
+        <v>-42.900000000000006</v>
+      </c>
+      <c r="D72">
+        <v>-8.58</v>
+      </c>
+      <c r="E72">
         <v>4</v>
       </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="8"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="10"/>
-      <c r="K72" s="10"/>
-      <c r="L72" s="10"/>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>4</v>
+      </c>
+      <c r="I72" s="7">
+        <f>IFERROR((F72/E72)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="10">
+        <f>IFERROR(C72/E72,0)</f>
+        <v>-10.725000000000001</v>
+      </c>
+      <c r="K72" s="10">
+        <f>IFERROR(D72/E72,0)</f>
+        <v>-2.145</v>
+      </c>
+      <c r="L72" s="10" t="str">
+        <f>LEFT(B72,3)</f>
+        <v>LEG</v>
+      </c>
+      <c r="N72">
+        <f t="shared" ref="N72" si="56">C72+U72</f>
+        <v>-42.900000000000006</v>
+      </c>
+      <c r="O72">
+        <f t="shared" ref="O72" si="57">D72+V72</f>
+        <v>-8.58</v>
+      </c>
+      <c r="P72">
+        <f t="shared" ref="P72" si="58">E72+W72</f>
+        <v>4</v>
+      </c>
+      <c r="Q72">
+        <f t="shared" ref="Q72" si="59">F72+X72</f>
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <f t="shared" ref="R72" si="60">G72+Y72</f>
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <f t="shared" ref="S72" si="61">H72+Z72</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B73" s="8"/>
@@ -11622,8 +11536,8 @@
       <c r="B74" s="8"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L76">
-    <sortCondition descending="1" ref="C2:C76"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L75">
+    <sortCondition descending="1" ref="C2:C75"/>
   </sortState>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="dataBar" priority="58">
@@ -11752,140 +11666,140 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63:B64 B72:B1048576 B1:B61">
-    <cfRule type="containsText" dxfId="104" priority="42" operator="containsText" text="LEG">
+    <cfRule type="containsText" dxfId="69" priority="42" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="103" priority="43" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="68" priority="43" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="102" priority="44" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="67" priority="44" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="101" priority="45" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="66" priority="45" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="100" priority="46" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="65" priority="46" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="99" priority="47" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="64" priority="47" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="98" priority="48" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="63" priority="48" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B62">
-    <cfRule type="containsText" dxfId="97" priority="35" operator="containsText" text="LEG">
+    <cfRule type="containsText" dxfId="62" priority="35" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",B62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="96" priority="36" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="61" priority="36" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="95" priority="37" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="60" priority="37" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="94" priority="38" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="59" priority="38" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",B62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="93" priority="39" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="58" priority="39" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",B62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="92" priority="40" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="57" priority="40" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",B62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="91" priority="41" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="56" priority="41" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",B62)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="containsText" dxfId="90" priority="28" operator="containsText" text="LEG">
+    <cfRule type="containsText" dxfId="55" priority="28" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",B68)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="89" priority="29" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="54" priority="29" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B68)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="30" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="53" priority="30" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B68)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="87" priority="31" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="52" priority="31" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",B68)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="86" priority="32" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="51" priority="32" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",B68)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="33" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="50" priority="33" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",B68)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="34" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="49" priority="34" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",B68)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66:B67">
-    <cfRule type="containsText" dxfId="83" priority="21" operator="containsText" text="LEG">
+    <cfRule type="containsText" dxfId="48" priority="21" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",B66)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="22" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="47" priority="22" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B66)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="23" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="46" priority="23" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B66)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="80" priority="24" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="45" priority="24" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",B66)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="79" priority="25" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="44" priority="25" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",B66)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="26" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="43" priority="26" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",B66)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="77" priority="27" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="42" priority="27" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",B66)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="containsText" dxfId="48" priority="8" operator="containsText" text="LEG">
+    <cfRule type="containsText" dxfId="41" priority="8" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",B71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="47" priority="9" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="40" priority="9" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="10" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="39" priority="10" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="45" priority="11" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="38" priority="11" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",B71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="12" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="37" priority="12" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",B71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="13" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="36" priority="13" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",B71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="14" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="35" priority="14" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",B71)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="LEG">
+    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="LEG">
       <formula>NOT(ISERROR(SEARCH("LEG",B65)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="33" priority="2" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B65)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="VEG">
+    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="VEG">
       <formula>NOT(ISERROR(SEARCH("VEG",B65)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="WEG">
+    <cfRule type="containsText" dxfId="31" priority="4" operator="containsText" text="WEG">
       <formula>NOT(ISERROR(SEARCH("WEG",B65)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="UEG">
+    <cfRule type="containsText" dxfId="30" priority="5" operator="containsText" text="UEG">
       <formula>NOT(ISERROR(SEARCH("UEG",B65)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="SEG">
+    <cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="SEG">
       <formula>NOT(ISERROR(SEARCH("SEG",B65)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="PEG">
+    <cfRule type="containsText" dxfId="28" priority="7" operator="containsText" text="PEG">
       <formula>NOT(ISERROR(SEARCH("PEG",B65)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12008,7 +11922,7 @@
     <col min="8" max="28" width="8.42578125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>104</v>
       </c>
@@ -12016,7 +11930,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" t="s">
         <v>100</v>
@@ -12040,21 +11954,21 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>129</v>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="B3">
         <f>SUM(H3:AB3)</f>
-        <v>-0.10000000000000009</v>
+        <v>4.3000000000000007</v>
       </c>
       <c r="C3">
         <f>(B3/$C$1)*100</f>
-        <v>-2.0000000000000018E-2</v>
+        <v>0.86000000000000021</v>
       </c>
       <c r="D3">
         <f>COUNTA(H3:AB3)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <f>COUNTIF(H3:AB3, "&gt;0")</f>
@@ -12066,29 +11980,35 @@
       </c>
       <c r="G3">
         <f>COUNTIF(H3:AB3, "&lt;0")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" s="18">
-        <v>-6.7</v>
+        <v>11.5</v>
       </c>
       <c r="I3" s="18">
-        <v>5.2</v>
+        <v>-3.8</v>
       </c>
       <c r="J3" s="18">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>65</v>
+        <v>3.2</v>
+      </c>
+      <c r="K3" s="18">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="L3" s="18">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>131</v>
       </c>
       <c r="B4">
         <f>SUM(H4:AB4)</f>
-        <v>13.400000000000002</v>
+        <v>-24.1</v>
       </c>
       <c r="C4">
         <f>(B4/$C$1)*100</f>
-        <v>2.6800000000000006</v>
+        <v>-4.82</v>
       </c>
       <c r="D4">
         <f>COUNTA(H4:AB4)</f>
@@ -12096,7 +12016,7 @@
       </c>
       <c r="E4">
         <f>COUNTIF(H4:AB4, "&gt;0")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <f>COUNTIF(H4:AB4, "=0")</f>
@@ -12104,29 +12024,29 @@
       </c>
       <c r="G4">
         <f>COUNTIF(H4:AB4, "&lt;0")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" s="18">
-        <v>0.3</v>
+        <v>-23.6</v>
       </c>
       <c r="I4" s="18">
-        <v>8.9</v>
+        <v>-6.2</v>
       </c>
       <c r="J4" s="18">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>140</v>
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>129</v>
       </c>
       <c r="B5">
         <f>SUM(H5:AB5)</f>
-        <v>9.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="C5">
         <f>(B5/$C$1)*100</f>
-        <v>1.9</v>
+        <v>1.9600000000000002</v>
       </c>
       <c r="D5">
         <f>COUNTA(H5:AB5)</f>
@@ -12134,7 +12054,7 @@
       </c>
       <c r="E5">
         <f>COUNTIF(H5:AB5, "&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <f>COUNTIF(H5:AB5, "=0")</f>
@@ -12142,26 +12062,26 @@
       </c>
       <c r="G5">
         <f>COUNTIF(H5:AB5, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="18">
-        <v>7.7</v>
+        <v>13.5</v>
       </c>
       <c r="I5" s="18">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B6">
         <f>SUM(H6:AB6)</f>
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="C6">
         <f>(B6/$C$1)*100</f>
-        <v>1.3800000000000001</v>
+        <v>1.3599999999999999</v>
       </c>
       <c r="D6">
         <f>COUNTA(H6:AB6)</f>
@@ -12169,7 +12089,7 @@
       </c>
       <c r="E6">
         <f>COUNTIF(H6:AB6, "&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <f>COUNTIF(H6:AB6, "=0")</f>
@@ -12177,26 +12097,26 @@
       </c>
       <c r="G6">
         <f>COUNTIF(H6:AB6, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="18">
-        <v>3.6</v>
+        <v>-0.7</v>
       </c>
       <c r="I6" s="18">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>151</v>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>150</v>
       </c>
       <c r="B7">
         <f>SUM(H7:AB7)</f>
-        <v>24.5</v>
+        <v>6.6</v>
       </c>
       <c r="C7">
         <f>(B7/$C$1)*100</f>
-        <v>4.9000000000000004</v>
+        <v>1.32</v>
       </c>
       <c r="D7">
         <f>COUNTA(H7:AB7)</f>
@@ -12215,31 +12135,31 @@
         <v>0</v>
       </c>
       <c r="H7" s="17">
-        <v>11.2</v>
+        <v>4.5</v>
       </c>
       <c r="I7" s="18">
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B8">
         <f>SUM(H8:AB8)</f>
-        <v>3</v>
+        <v>-5.5</v>
       </c>
       <c r="C8">
         <f>(B8/$C$1)*100</f>
-        <v>0.6</v>
+        <v>-1.0999999999999999</v>
       </c>
       <c r="D8">
         <f>COUNTA(H8:AB8)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <f>COUNTIF(H8:AB8, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <f>COUNTIF(H8:AB8, "=0")</f>
@@ -12247,31 +12167,34 @@
       </c>
       <c r="G8">
         <f>COUNTIF(H8:AB8, "&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H8" s="18">
+        <v>-1.8</v>
+      </c>
+      <c r="I8" s="18">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B9">
         <f>SUM(H9:AB9)</f>
-        <v>-1.7</v>
+        <v>-8.4000000000000021</v>
       </c>
       <c r="C9">
         <f>(B9/$C$1)*100</f>
-        <v>-0.33999999999999997</v>
+        <v>-1.6800000000000006</v>
       </c>
       <c r="D9">
         <f>COUNTA(H9:AB9)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <f>COUNTIF(H9:AB9, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <f>COUNTIF(H9:AB9, "=0")</f>
@@ -12282,20 +12205,23 @@
         <v>1</v>
       </c>
       <c r="H9" s="18">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-16.100000000000001</v>
+      </c>
+      <c r="I9" s="18">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B10">
         <f>SUM(H10:AB10)</f>
-        <v>-3.6</v>
+        <v>1.4</v>
       </c>
       <c r="C10">
         <f>(B10/$C$1)*100</f>
-        <v>-0.72</v>
+        <v>0.27999999999999997</v>
       </c>
       <c r="D10">
         <f>COUNTA(H10:AB10)</f>
@@ -12303,7 +12229,7 @@
       </c>
       <c r="E10">
         <f>COUNTIF(H10:AB10, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <f>COUNTIF(H10:AB10, "=0")</f>
@@ -12311,25 +12237,24 @@
       </c>
       <c r="G10">
         <f>COUNTIF(H10:AB10, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="17">
-        <v>-3.6</v>
+        <v>1.4</v>
       </c>
       <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B11">
         <f>SUM(H11:AB11)</f>
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="C11">
         <f>(B11/$C$1)*100</f>
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="D11">
         <f>COUNTA(H11:AB11)</f>
@@ -12341,27 +12266,27 @@
       </c>
       <c r="F11">
         <f>COUNTIF(H11:AB11, "=0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <f>COUNTIF(H11:AB11, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="B12">
         <f>SUM(H12:AB12)</f>
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="C12">
         <f>(B12/$C$1)*100</f>
-        <v>0.27999999999999997</v>
+        <v>0.18</v>
       </c>
       <c r="D12">
         <f>COUNTA(H12:AB12)</f>
@@ -12380,20 +12305,20 @@
         <v>0</v>
       </c>
       <c r="H12" s="17">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B13">
         <f>SUM(H13:AB13)</f>
-        <v>5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="C13">
         <f>(B13/$C$1)*100</f>
-        <v>1.1199999999999999</v>
+        <v>-1.22</v>
       </c>
       <c r="D13">
         <f>COUNTA(H13:AB13)</f>
@@ -12401,7 +12326,7 @@
       </c>
       <c r="E13">
         <f>COUNTIF(H13:AB13, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <f>COUNTIF(H13:AB13, "=0")</f>
@@ -12409,23 +12334,23 @@
       </c>
       <c r="G13">
         <f>COUNTIF(H13:AB13, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="17">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-6.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>134</v>
       </c>
       <c r="B14">
         <f>SUM(H14:AB14)</f>
-        <v>-0.5</v>
+        <v>0.9</v>
       </c>
       <c r="C14">
         <f>(B14/$C$1)*100</f>
-        <v>-0.1</v>
+        <v>0.18</v>
       </c>
       <c r="D14">
         <f>COUNTA(H14:AB14)</f>
@@ -12433,7 +12358,7 @@
       </c>
       <c r="E14">
         <f>COUNTIF(H14:AB14, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <f>COUNTIF(H14:AB14, "=0")</f>
@@ -12441,23 +12366,23 @@
       </c>
       <c r="G14">
         <f>COUNTIF(H14:AB14, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="18">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>137</v>
+        <v>73</v>
       </c>
       <c r="B15">
         <f>SUM(H15:AB15)</f>
-        <v>-6.8</v>
+        <v>-7.4</v>
       </c>
       <c r="C15">
         <f>(B15/$C$1)*100</f>
-        <v>-1.3599999999999999</v>
+        <v>-1.48</v>
       </c>
       <c r="D15">
         <f>COUNTA(H15:AB15)</f>
@@ -12476,20 +12401,22 @@
         <v>1</v>
       </c>
       <c r="H15" s="17">
-        <v>-6.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>85</v>
+        <v>-7.4</v>
+      </c>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="B16">
         <f>SUM(H16:AB16)</f>
-        <v>-0.7</v>
+        <v>5.3</v>
       </c>
       <c r="C16">
         <f>(B16/$C$1)*100</f>
-        <v>-0.13999999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="D16">
         <f>COUNTA(H16:AB16)</f>
@@ -12497,7 +12424,7 @@
       </c>
       <c r="E16">
         <f>COUNTIF(H16:AB16, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <f>COUNTIF(H16:AB16, "=0")</f>
@@ -12505,23 +12432,23 @@
       </c>
       <c r="G16">
         <f>COUNTIF(H16:AB16, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="18">
-        <v>-0.7</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>73</v>
+      <c r="A17" t="s">
+        <v>154</v>
       </c>
       <c r="B17">
         <f>SUM(H17:AB17)</f>
-        <v>0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="C17">
         <f>(B17/$C$1)*100</f>
-        <v>0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="D17">
         <f>COUNTA(H17:AB17)</f>
@@ -12529,7 +12456,7 @@
       </c>
       <c r="E17">
         <f>COUNTIF(H17:AB17, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <f>COUNTIF(H17:AB17, "=0")</f>
@@ -12537,23 +12464,23 @@
       </c>
       <c r="G17">
         <f>COUNTIF(H17:AB17, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="17">
-        <v>0.9</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>91</v>
+      <c r="A18" s="8" t="s">
+        <v>141</v>
       </c>
       <c r="B18">
         <f>SUM(H18:AB18)</f>
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="C18">
         <f>(B18/$C$1)*100</f>
-        <v>0.84000000000000008</v>
+        <v>1.3599999999999999</v>
       </c>
       <c r="D18">
         <f>COUNTA(H18:AB18)</f>
@@ -12571,21 +12498,21 @@
         <f>COUNTIF(H18:AB18, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H18" s="17">
-        <v>4.2</v>
+      <c r="H18" s="18">
+        <v>6.8</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>153</v>
+      <c r="A19" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="B19">
         <f>SUM(H19:AB19)</f>
-        <v>-4.5999999999999996</v>
+        <v>-1.2</v>
       </c>
       <c r="C19">
         <f>(B19/$C$1)*100</f>
-        <v>-0.91999999999999993</v>
+        <v>-0.24</v>
       </c>
       <c r="D19">
         <f>COUNTA(H19:AB19)</f>
@@ -12604,20 +12531,20 @@
         <v>1</v>
       </c>
       <c r="H19" s="18">
-        <v>-4.5999999999999996</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="B20">
         <f>SUM(H20:AB20)</f>
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="C20">
         <f>(B20/$C$1)*100</f>
-        <v>0.36</v>
+        <v>-0.04</v>
       </c>
       <c r="D20">
         <f>COUNTA(H20:AB20)</f>
@@ -12625,7 +12552,7 @@
       </c>
       <c r="E20">
         <f>COUNTIF(H20:AB20, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <f>COUNTIF(H20:AB20, "=0")</f>
@@ -12633,23 +12560,23 @@
       </c>
       <c r="G20">
         <f>COUNTIF(H20:AB20, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="18">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>149</v>
+      <c r="A21" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="B21">
         <f>SUM(H21:AB21)</f>
-        <v>-8.5</v>
+        <v>7.4</v>
       </c>
       <c r="C21">
         <f>(B21/$C$1)*100</f>
-        <v>-1.7000000000000002</v>
+        <v>1.48</v>
       </c>
       <c r="D21">
         <f>COUNTA(H21:AB21)</f>
@@ -12657,7 +12584,7 @@
       </c>
       <c r="E21">
         <f>COUNTIF(H21:AB21, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
         <f>COUNTIF(H21:AB21, "=0")</f>
@@ -12665,23 +12592,23 @@
       </c>
       <c r="G21">
         <f>COUNTIF(H21:AB21, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>62</v>
+      <c r="A22" s="8" t="s">
+        <v>149</v>
       </c>
       <c r="B22">
         <f>SUM(H22:AB22)</f>
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="C22">
         <f>(B22/$C$1)*100</f>
-        <v>2.4</v>
+        <v>1.1199999999999999</v>
       </c>
       <c r="D22">
         <f>COUNTA(H22:AB22)</f>
@@ -12700,7 +12627,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="18">
-        <v>12</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -12709,11 +12636,11 @@
       </c>
       <c r="B23">
         <f>SUM(H23:AB23)</f>
-        <v>-1.5</v>
+        <v>-0.9</v>
       </c>
       <c r="C23">
         <f>(B23/$C$1)*100</f>
-        <v>-0.3</v>
+        <v>-0.18</v>
       </c>
       <c r="D23">
         <f>COUNTA(H23:AB23)</f>
@@ -12732,7 +12659,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="18">
-        <v>-1.5</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -12741,11 +12668,11 @@
       </c>
       <c r="B24">
         <f>SUM(H24:AB24)</f>
-        <v>5.3</v>
+        <v>-4.0999999999999996</v>
       </c>
       <c r="C24">
         <f>(B24/$C$1)*100</f>
-        <v>1.06</v>
+        <v>-0.81999999999999984</v>
       </c>
       <c r="D24">
         <f>COUNTA(H24:AB24)</f>
@@ -12753,7 +12680,7 @@
       </c>
       <c r="E24">
         <f>COUNTIF(H24:AB24, "&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <f>COUNTIF(H24:AB24, "=0")</f>
@@ -12761,23 +12688,23 @@
       </c>
       <c r="G24">
         <f>COUNTIF(H24:AB24, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="18">
-        <v>5.3</v>
+        <v>-4.0999999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>154</v>
+      <c r="A25" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="B25">
         <f>SUM(H25:AB25)</f>
-        <v>-8.8000000000000007</v>
+        <v>8</v>
       </c>
       <c r="C25">
         <f>(B25/$C$1)*100</f>
-        <v>-1.76</v>
+        <v>1.6</v>
       </c>
       <c r="D25">
         <f>COUNTA(H25:AB25)</f>
@@ -12785,7 +12712,7 @@
       </c>
       <c r="E25">
         <f>COUNTIF(H25:AB25, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <f>COUNTIF(H25:AB25, "=0")</f>
@@ -12793,10 +12720,10 @@
       </c>
       <c r="G25">
         <f>COUNTIF(H25:AB25, "&lt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="18">
-        <v>-8.8000000000000007</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -12827,10 +12754,9 @@
         <f>COUNTIF(H26:AB26, "&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="H26" s="15"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="8" t="s">
         <v>148</v>
       </c>
       <c r="B27">
@@ -12859,7 +12785,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="A28" t="s">
         <v>84</v>
       </c>
       <c r="B28">
@@ -12888,7 +12814,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="A29" t="s">
         <v>58</v>
       </c>
       <c r="B29">
@@ -12917,8 +12843,8 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>57</v>
+      <c r="A30" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="B30">
         <f>SUM(H30:AB30)</f>
@@ -12947,7 +12873,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="B31">
         <f>SUM(H31:AB31)</f>
@@ -12977,7 +12903,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="B32">
         <f>SUM(H32:AB32)</f>
@@ -13006,8 +12932,8 @@
       <c r="H32" s="15"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>128</v>
+      <c r="A33" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="B33">
         <f>SUM(H33:AB33)</f>
@@ -13036,7 +12962,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B34">
         <f>SUM(H34:AB34)</f>
@@ -13064,8 +12990,8 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
-        <v>133</v>
+      <c r="A35" t="s">
+        <v>128</v>
       </c>
       <c r="B35">
         <f>SUM(H35:AB35)</f>
@@ -13096,7 +13022,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B36">
         <f>SUM(H36:AB36)</f>
@@ -13127,7 +13053,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="B37">
         <f>SUM(H37:AB37)</f>
@@ -13158,7 +13084,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B38">
         <f>SUM(H38:AB38)</f>
@@ -13190,8 +13116,8 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>72</v>
+      <c r="A39" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="B39">
         <f>SUM(H39:AB39)</f>
@@ -13221,8 +13147,8 @@
       <c r="I39" s="15"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
-        <v>130</v>
+      <c r="A40" t="s">
+        <v>86</v>
       </c>
       <c r="B40">
         <f>SUM(H40:AB40)</f>
@@ -13252,8 +13178,8 @@
       <c r="I40" s="15"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
-        <v>69</v>
+      <c r="A41" t="s">
+        <v>72</v>
       </c>
       <c r="B41">
         <f>SUM(H41:AB41)</f>
@@ -13282,8 +13208,8 @@
       <c r="H41" s="15"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>54</v>
+      <c r="A42" t="s">
+        <v>85</v>
       </c>
       <c r="B42">
         <f>SUM(H42:AB42)</f>
@@ -13312,8 +13238,8 @@
       <c r="H42" s="15"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
-        <v>146</v>
+      <c r="A43" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="B43">
         <f>SUM(H43:AB43)</f>
@@ -13342,8 +13268,8 @@
       <c r="H43" s="15"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>76</v>
+      <c r="A44" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="B44">
         <f>SUM(H44:AB44)</f>
@@ -13377,7 +13303,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B45">
         <f>SUM(H45:AB45)</f>
@@ -13410,8 +13336,8 @@
       <c r="L45" s="15"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
-        <v>145</v>
+      <c r="A46" t="s">
+        <v>146</v>
       </c>
       <c r="B46">
         <f>SUM(H46:AB46)</f>
@@ -13439,8 +13365,8 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
-        <v>75</v>
+      <c r="A47" t="s">
+        <v>76</v>
       </c>
       <c r="B47">
         <f>SUM(H47:AB47)</f>
@@ -13472,8 +13398,8 @@
       <c r="K47" s="15"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
-        <v>95</v>
+      <c r="A48" t="s">
+        <v>63</v>
       </c>
       <c r="B48">
         <f>SUM(H48:AB48)</f>
@@ -13503,9 +13429,9 @@
       <c r="I48" s="15"/>
       <c r="J48" s="15"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="B49">
         <f>SUM(H49:AB49)</f>
@@ -13532,10 +13458,14 @@
         <v>0</v>
       </c>
       <c r="H49" s="15"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="15"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="B50">
         <f>SUM(H50:AB50)</f>
@@ -13564,9 +13494,9 @@
       <c r="H50" s="15"/>
       <c r="I50" s="15"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>93</v>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="B51">
         <f>SUM(H51:AB51)</f>
@@ -13594,9 +13524,9 @@
       </c>
       <c r="H51" s="15"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="B52">
         <f>SUM(H52:AB52)</f>
@@ -13624,9 +13554,9 @@
       </c>
       <c r="H52" s="15"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
-        <v>94</v>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="B53">
         <f>SUM(H53:AB53)</f>
@@ -13655,9 +13585,9 @@
       <c r="H53" s="15"/>
       <c r="I53" s="15"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>141</v>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="B54">
         <f>SUM(H54:AB54)</f>
@@ -13686,9 +13616,9 @@
       <c r="H54" s="15"/>
       <c r="I54" s="15"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="B55">
         <f>SUM(H55:AB55)</f>
@@ -13715,10 +13645,11 @@
         <v>0</v>
       </c>
       <c r="H55" s="15"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I55" s="15"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="B56">
         <f>SUM(H56:AB56)</f>
@@ -13747,9 +13678,9 @@
       <c r="H56" s="15"/>
       <c r="I56" s="15"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B57">
         <f>SUM(H57:AB57)</f>
@@ -13778,9 +13709,9 @@
       <c r="H57" s="15"/>
       <c r="I57" s="15"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>61</v>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="B58">
         <f>SUM(H58:AB58)</f>
@@ -13809,9 +13740,9 @@
       <c r="H58" s="15"/>
       <c r="I58" s="15"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
-        <v>74</v>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>153</v>
       </c>
       <c r="B59">
         <f>SUM(H59:AB59)</f>
@@ -13839,9 +13770,9 @@
       </c>
       <c r="H59" s="15"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>64</v>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="B60">
         <f>SUM(H60:AB60)</f>
@@ -13869,9 +13800,9 @@
       </c>
       <c r="H60" s="15"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B61">
         <f>SUM(H61:AB61)</f>
@@ -13898,10 +13829,11 @@
         <v>0</v>
       </c>
       <c r="H61" s="15"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I61" s="15"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="B62">
         <f>SUM(H62:AB62)</f>
@@ -13930,9 +13862,9 @@
       <c r="H62" s="15"/>
       <c r="I62" s="15"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>80</v>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="B63">
         <f>SUM(H63:AB63)</f>
@@ -13960,9 +13892,9 @@
       </c>
       <c r="H63" s="15"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
-        <v>55</v>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>80</v>
       </c>
       <c r="B64">
         <f>SUM(H64:AB64)</f>
@@ -13991,8 +13923,8 @@
       <c r="H64" s="15"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
-        <v>70</v>
+      <c r="A65" t="s">
+        <v>55</v>
       </c>
       <c r="B65">
         <f>SUM(H65:AB65)</f>
@@ -14023,8 +13955,8 @@
       <c r="J65" s="15"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="s">
-        <v>83</v>
+      <c r="A66" t="s">
+        <v>70</v>
       </c>
       <c r="B66">
         <f>SUM(H66:AB66)</f>
@@ -14054,7 +13986,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B67">
         <f>SUM(H67:AB67)</f>
@@ -14086,7 +14018,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B68">
         <f>SUM(H68:AB68)</f>
@@ -14116,8 +14048,8 @@
       <c r="I68" s="15"/>
     </row>
     <row r="69" spans="1:10" x14